--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -62871,7 +62871,7 @@
         <v>6472</v>
       </c>
       <c r="C2718" t="n">
-        <v>1.57400000095367</v>
+        <v>1.57599997520447</v>
       </c>
       <c r="D2718" t="n">
         <v>1.57000005245209</v>
@@ -62883,6 +62883,29 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>57975</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>1.58599996566772</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>1.48800003528595</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>1.57599997520447</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>1.55799996852875</v>
+      </c>
+      <c r="G2719" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>9256</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>1.52799999713898</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>3158</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>6066</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>1.59599995613098</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>52557</v>
+        <v>18759</v>
       </c>
       <c r="C2715" t="n">
+        <v>1.60599994659424</v>
+      </c>
+      <c r="D2715" t="n">
+        <v>1.58200001716614</v>
+      </c>
+      <c r="E2715" t="n">
+        <v>1.60599994659424</v>
+      </c>
+      <c r="F2715" t="n">
         <v>1.58399999141693</v>
-      </c>
-      <c r="D2715" t="n">
-        <v>1.57799994945526</v>
-      </c>
-      <c r="E2715" t="n">
-        <v>1.58200001716614</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>1.58000004291534</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>26088</v>
+        <v>52557</v>
       </c>
       <c r="C2716" t="n">
-        <v>1.5900000333786</v>
+        <v>1.58399999141693</v>
       </c>
       <c r="D2716" t="n">
-        <v>1.57000005245209</v>
+        <v>1.57799994945526</v>
       </c>
       <c r="E2716" t="n">
+        <v>1.58200001716614</v>
+      </c>
+      <c r="F2716" t="n">
         <v>1.58000004291534</v>
-      </c>
-      <c r="F2716" t="n">
-        <v>1.57200002670288</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>18940</v>
+        <v>26088</v>
       </c>
       <c r="C2717" t="n">
         <v>1.5900000333786</v>
       </c>
       <c r="D2717" t="n">
-        <v>1.55400002002716</v>
+        <v>1.57000005245209</v>
       </c>
       <c r="E2717" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="F2717" t="n">
         <v>1.57200002670288</v>
-      </c>
-      <c r="F2717" t="n">
-        <v>1.57000005245209</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>6472</v>
+        <v>18940</v>
       </c>
       <c r="C2718" t="n">
-        <v>1.57599997520447</v>
+        <v>1.5900000333786</v>
       </c>
       <c r="D2718" t="n">
+        <v>1.55400002002716</v>
+      </c>
+      <c r="E2718" t="n">
+        <v>1.57200002670288</v>
+      </c>
+      <c r="F2718" t="n">
         <v>1.57000005245209</v>
-      </c>
-      <c r="E2718" t="n">
-        <v>1.57000005245209</v>
-      </c>
-      <c r="F2718" t="n">
-        <v>1.57599997520447</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>57975</v>
+        <v>6472</v>
       </c>
       <c r="C2719" t="n">
-        <v>1.58599996566772</v>
+        <v>1.57599997520447</v>
       </c>
       <c r="D2719" t="n">
-        <v>1.48800003528595</v>
+        <v>1.57000005245209</v>
       </c>
       <c r="E2719" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="F2719" t="n">
         <v>1.57599997520447</v>
-      </c>
-      <c r="F2719" t="n">
-        <v>1.55799996852875</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>9256</v>
+        <v>57975</v>
       </c>
       <c r="C2720" t="n">
-        <v>1.60000002384186</v>
+        <v>1.58599996566772</v>
       </c>
       <c r="D2720" t="n">
-        <v>1.52799999713898</v>
+        <v>1.48800003528595</v>
       </c>
       <c r="E2720" t="n">
-        <v>1.60000002384186</v>
+        <v>1.57599997520447</v>
       </c>
       <c r="F2720" t="n">
-        <v>1.53999996185303</v>
+        <v>1.55799996852875</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>3158</v>
+        <v>9256</v>
       </c>
       <c r="C2721" t="n">
         <v>1.60000002384186</v>
       </c>
       <c r="D2721" t="n">
-        <v>1.54999995231628</v>
+        <v>1.52799999713898</v>
       </c>
       <c r="E2721" t="n">
         <v>1.60000002384186</v>
       </c>
       <c r="F2721" t="n">
-        <v>1.54999995231628</v>
+        <v>1.53999996185303</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>6066</v>
+        <v>3158</v>
       </c>
       <c r="C2722" t="n">
-        <v>1.59599995613098</v>
+        <v>1.60000002384186</v>
       </c>
       <c r="D2722" t="n">
-        <v>1.53999996185303</v>
+        <v>1.54999995231628</v>
       </c>
       <c r="E2722" t="n">
-        <v>1.53999996185303</v>
+        <v>1.60000002384186</v>
       </c>
       <c r="F2722" t="n">
-        <v>1.58000004291534</v>
+        <v>1.54999995231628</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>65436</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>1.58599996566772</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>1.59399998188019</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>1.58599996566772</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -499,7 +499,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G5" t="n">
-        <v>2.68630075454712</v>
+        <v>2.68630051612854</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G9" t="n">
-        <v>2.71730732917786</v>
+        <v>2.71730709075928</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>2.60737490653992</v>
+        <v>2.6073751449585</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G11" t="n">
-        <v>2.48757672309875</v>
+        <v>2.4875762462616</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36073160171509</v>
+        <v>2.36073136329651</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G13" t="n">
-        <v>2.39314746856689</v>
+        <v>2.39314723014832</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.50167059898376</v>
+        <v>2.50167036056519</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G18" t="n">
-        <v>2.39737558364868</v>
+        <v>2.3973753452301</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G21" t="n">
-        <v>2.39455652236938</v>
+        <v>2.39455628395081</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G24" t="n">
-        <v>1.97455823421478</v>
+        <v>1.97455775737762</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G25" t="n">
-        <v>1.8744912147522</v>
+        <v>1.87449109554291</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G26" t="n">
-        <v>1.86885321140289</v>
+        <v>1.86885380744934</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G28" t="n">
-        <v>1.71100175380707</v>
+        <v>1.71100163459778</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G29" t="n">
-        <v>1.86039745807648</v>
+        <v>1.8603972196579</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.5</v>
       </c>
       <c r="G30" t="n">
-        <v>1.76173996925354</v>
+        <v>1.76173973083496</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G32" t="n">
-        <v>1.94777977466583</v>
+        <v>1.94777929782867</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G33" t="n">
-        <v>2.03657126426697</v>
+        <v>2.03657150268555</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G34" t="n">
-        <v>2.07039666175842</v>
+        <v>2.07039642333984</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G36" t="n">
-        <v>2.09294676780701</v>
+        <v>2.09294700622559</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G38" t="n">
-        <v>2.1605978012085</v>
+        <v>2.16059756278992</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G39" t="n">
-        <v>2.04784631729126</v>
+        <v>2.04784607887268</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G40" t="n">
-        <v>2.06616878509521</v>
+        <v>2.06616830825806</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>2.0577118396759</v>
+        <v>2.05771231651306</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G42" t="n">
-        <v>2.06334948539734</v>
+        <v>2.06334972381592</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G43" t="n">
-        <v>2.07321524620056</v>
+        <v>2.07321548461914</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G45" t="n">
-        <v>2.13522887229919</v>
+        <v>2.13522863388062</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G46" t="n">
-        <v>2.15777897834778</v>
+        <v>2.1577787399292</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12113451957703</v>
+        <v>2.12113475799561</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G50" t="n">
-        <v>2.12677264213562</v>
+        <v>2.12677216529846</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G52" t="n">
-        <v>2.26348304748535</v>
+        <v>2.26348328590393</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G53" t="n">
-        <v>2.27052998542786</v>
+        <v>2.27053046226501</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G54" t="n">
-        <v>2.17469167709351</v>
+        <v>2.17469143867493</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G57" t="n">
-        <v>2.20147013664246</v>
+        <v>2.20146989822388</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G58" t="n">
-        <v>2.2367045879364</v>
+        <v>2.23670530319214</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G64" t="n">
-        <v>1.89281344413757</v>
+        <v>1.89281332492828</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G66" t="n">
-        <v>1.94496059417725</v>
+        <v>1.94496071338654</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G67" t="n">
-        <v>1.95482671260834</v>
+        <v>1.95482647418976</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.71600008010864</v>
       </c>
       <c r="G68" t="n">
-        <v>1.91395425796509</v>
+        <v>1.9139541387558</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.97455823421478</v>
+        <v>1.97455775737762</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>1.92382025718689</v>
+        <v>1.92382037639618</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>1.98019576072693</v>
+        <v>1.98019540309906</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G73" t="n">
-        <v>2.00838327407837</v>
+        <v>2.00838351249695</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G74" t="n">
-        <v>2.06616878509521</v>
+        <v>2.06616830825806</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G75" t="n">
-        <v>2.10704064369202</v>
+        <v>2.1070408821106</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>2.17046356201172</v>
+        <v>2.17046332359314</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G80" t="n">
-        <v>2.12113451957703</v>
+        <v>2.12113475799561</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>2.10704064369202</v>
+        <v>2.1070408821106</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G82" t="n">
-        <v>2.0577118396759</v>
+        <v>2.05771231651306</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G83" t="n">
-        <v>2.02670526504517</v>
+        <v>2.02670550346375</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G85" t="n">
-        <v>1.94918918609619</v>
+        <v>1.9491890668869</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>1.97314870357513</v>
+        <v>1.97314846515656</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G87" t="n">
-        <v>1.95623588562012</v>
+        <v>1.95623600482941</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G89" t="n">
-        <v>1.86321616172791</v>
+        <v>1.86321651935577</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>1.87687909603119</v>
+        <v>1.8768789768219</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.5</v>
       </c>
       <c r="G91" t="n">
-        <v>1.79777717590332</v>
+        <v>1.79777669906616</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>1.74024820327759</v>
+        <v>1.74024832248688</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G94" t="n">
-        <v>1.68128132820129</v>
+        <v>1.68128097057343</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G95" t="n">
-        <v>1.61224639415741</v>
+        <v>1.6122465133667</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62662863731384</v>
+        <v>1.62662875652313</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G102" t="n">
-        <v>1.78914773464203</v>
+        <v>1.78914737701416</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G104" t="n">
-        <v>1.83373248577118</v>
+        <v>1.83373260498047</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G106" t="n">
-        <v>1.84092354774475</v>
+        <v>1.84092378616333</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>1.8121589422226</v>
+        <v>1.81215929985046</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G109" t="n">
-        <v>1.79490065574646</v>
+        <v>1.79490041732788</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G110" t="n">
-        <v>1.83517062664032</v>
+        <v>1.83517098426819</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G111" t="n">
-        <v>1.83948540687561</v>
+        <v>1.8394855260849</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>1.80640637874603</v>
+        <v>1.80640625953674</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G113" t="n">
-        <v>1.80496835708618</v>
+        <v>1.80496823787689</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.5</v>
       </c>
       <c r="G114" t="n">
-        <v>1.79777717590332</v>
+        <v>1.79777669906616</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G115" t="n">
-        <v>1.73305690288544</v>
+        <v>1.73305714130402</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G116" t="n">
-        <v>1.7201132774353</v>
+        <v>1.72011303901672</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G117" t="n">
-        <v>1.73880982398987</v>
+        <v>1.73881006240845</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G118" t="n">
-        <v>1.63381969928741</v>
+        <v>1.6338198184967</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G120" t="n">
-        <v>1.75606858730316</v>
+        <v>1.75606846809387</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G121" t="n">
-        <v>1.75319230556488</v>
+        <v>1.7531920671463</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>1.8121589422226</v>
+        <v>1.81215929985046</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G123" t="n">
-        <v>1.83804714679718</v>
+        <v>1.83804726600647</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G124" t="n">
-        <v>1.61224639415741</v>
+        <v>1.6122465133667</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G125" t="n">
-        <v>1.48999774456024</v>
+        <v>1.48999762535095</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G127" t="n">
-        <v>1.49431228637695</v>
+        <v>1.49431240558624</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G129" t="n">
-        <v>1.47561538219452</v>
+        <v>1.47561526298523</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G130" t="n">
-        <v>1.49287402629852</v>
+        <v>1.49287390708923</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G133" t="n">
-        <v>1.50869452953339</v>
+        <v>1.5086944103241</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G134" t="n">
-        <v>1.55615568161011</v>
+        <v>1.5561558008194</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G135" t="n">
-        <v>1.56047034263611</v>
+        <v>1.5604704618454</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G136" t="n">
-        <v>1.63238167762756</v>
+        <v>1.63238143920898</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G137" t="n">
-        <v>1.63381969928741</v>
+        <v>1.6338198184967</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G138" t="n">
-        <v>1.65395474433899</v>
+        <v>1.6539546251297</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G139" t="n">
-        <v>1.6208758354187</v>
+        <v>1.62087571620941</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G140" t="n">
-        <v>1.6208758354187</v>
+        <v>1.62087571620941</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G141" t="n">
-        <v>1.61224639415741</v>
+        <v>1.6122465133667</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.25</v>
       </c>
       <c r="G142" t="n">
-        <v>1.61799907684326</v>
+        <v>1.61799943447113</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.25</v>
       </c>
       <c r="G143" t="n">
-        <v>1.61799907684326</v>
+        <v>1.61799943447113</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G144" t="n">
-        <v>1.56190872192383</v>
+        <v>1.56190848350525</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.12599992752075</v>
       </c>
       <c r="G146" t="n">
-        <v>1.52882945537567</v>
+        <v>1.52882957458496</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G147" t="n">
-        <v>1.56766152381897</v>
+        <v>1.56766164302826</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G152" t="n">
-        <v>1.33754587173462</v>
+        <v>1.3375461101532</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G157" t="n">
-        <v>1.48999774456024</v>
+        <v>1.48999762535095</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G158" t="n">
-        <v>1.48136830329895</v>
+        <v>1.48136818408966</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G161" t="n">
-        <v>1.50437963008881</v>
+        <v>1.50437986850739</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G162" t="n">
-        <v>1.50581812858582</v>
+        <v>1.50581800937653</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G163" t="n">
-        <v>1.4914356470108</v>
+        <v>1.49143576622009</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G164" t="n">
-        <v>1.51732385158539</v>
+        <v>1.51732361316681</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G165" t="n">
-        <v>1.53602051734924</v>
+        <v>1.53602075576782</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G167" t="n">
-        <v>1.54608833789825</v>
+        <v>1.54608798027039</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G168" t="n">
-        <v>1.52307653427124</v>
+        <v>1.52307677268982</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G171" t="n">
-        <v>1.50869452953339</v>
+        <v>1.5086944103241</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G172" t="n">
-        <v>1.53745901584625</v>
+        <v>1.53745889663696</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G174" t="n">
-        <v>1.56478524208069</v>
+        <v>1.5647851228714</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G176" t="n">
-        <v>1.55471754074097</v>
+        <v>1.55471742153168</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G177" t="n">
-        <v>1.56047034263611</v>
+        <v>1.5604704618454</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G179" t="n">
-        <v>1.50725626945496</v>
+        <v>1.50725615024567</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G180" t="n">
-        <v>1.49287402629852</v>
+        <v>1.49287390708923</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G183" t="n">
-        <v>1.45979499816895</v>
+        <v>1.45979487895966</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G185" t="n">
-        <v>1.47705340385437</v>
+        <v>1.47705364227295</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G187" t="n">
-        <v>1.48280656337738</v>
+        <v>1.48280644416809</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G188" t="n">
-        <v>1.48999774456024</v>
+        <v>1.48999762535095</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G189" t="n">
-        <v>1.45979499816895</v>
+        <v>1.45979487895966</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G191" t="n">
-        <v>1.48424470424652</v>
+        <v>1.48424458503723</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G198" t="n">
-        <v>1.60936987400055</v>
+        <v>1.60936999320984</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.25</v>
       </c>
       <c r="G199" t="n">
-        <v>1.61799907684326</v>
+        <v>1.61799943447113</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>1.67552816867828</v>
+        <v>1.67552781105042</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G206" t="n">
-        <v>1.7273041009903</v>
+        <v>1.72730398178101</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G207" t="n">
-        <v>1.7316187620163</v>
+        <v>1.73161900043488</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G208" t="n">
-        <v>1.73449516296387</v>
+        <v>1.73449540138245</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>1.74743902683258</v>
+        <v>1.74743938446045</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G210" t="n">
-        <v>1.77332735061646</v>
+        <v>1.77332723140717</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G211" t="n">
-        <v>1.75606858730316</v>
+        <v>1.75606846809387</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>1.74743902683258</v>
+        <v>1.74743938446045</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G214" t="n">
-        <v>1.71867501735687</v>
+        <v>1.71867489814758</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>1.67552816867828</v>
+        <v>1.67552781105042</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G222" t="n">
-        <v>1.43246877193451</v>
+        <v>1.43246865272522</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G223" t="n">
-        <v>1.42383933067322</v>
+        <v>1.42383944988251</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>1.40586161613464</v>
+        <v>1.40586173534393</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G225" t="n">
-        <v>1.45691847801208</v>
+        <v>1.45691859722137</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G226" t="n">
-        <v>1.39004111289978</v>
+        <v>1.39004123210907</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G229" t="n">
-        <v>1.33754587173462</v>
+        <v>1.3375461101532</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G230" t="n">
-        <v>1.35840034484863</v>
+        <v>1.35840022563934</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G231" t="n">
-        <v>1.33754587173462</v>
+        <v>1.3375461101532</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G233" t="n">
-        <v>1.3332314491272</v>
+        <v>1.33323132991791</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G234" t="n">
-        <v>1.29799485206604</v>
+        <v>1.29799497127533</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G235" t="n">
-        <v>1.30806267261505</v>
+        <v>1.30806243419647</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G238" t="n">
-        <v>1.38069272041321</v>
+        <v>1.38069260120392</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G239" t="n">
-        <v>1.34545624256134</v>
+        <v>1.34545636177063</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G242" t="n">
-        <v>1.48712110519409</v>
+        <v>1.48712122440338</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G246" t="n">
-        <v>1.45979499816895</v>
+        <v>1.45979487895966</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G248" t="n">
-        <v>1.53602051734924</v>
+        <v>1.53602075576782</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G250" t="n">
-        <v>1.54464995861053</v>
+        <v>1.54465007781982</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G251" t="n">
-        <v>1.51732385158539</v>
+        <v>1.51732361316681</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G252" t="n">
-        <v>1.54608833789825</v>
+        <v>1.54608798027039</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G253" t="n">
-        <v>1.56190872192383</v>
+        <v>1.56190848350525</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>1.56047034263611</v>
+        <v>1.5604704618454</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G255" t="n">
-        <v>1.56047034263611</v>
+        <v>1.5604704618454</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G257" t="n">
-        <v>1.5820437669754</v>
+        <v>1.58204388618469</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G258" t="n">
-        <v>1.60649359226227</v>
+        <v>1.60649347305298</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G259" t="n">
-        <v>1.64388716220856</v>
+        <v>1.64388751983643</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G262" t="n">
-        <v>1.66546082496643</v>
+        <v>1.66546046733856</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>1.66114568710327</v>
+        <v>1.66114580631256</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>1.66546082496643</v>
+        <v>1.66546046733856</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G266" t="n">
-        <v>1.67408990859985</v>
+        <v>1.67408978939056</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>1.697101354599</v>
+        <v>1.69710147380829</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G268" t="n">
-        <v>1.7201132774353</v>
+        <v>1.72011303901672</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G269" t="n">
-        <v>1.722989320755</v>
+        <v>1.72298943996429</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G270" t="n">
-        <v>1.72442746162415</v>
+        <v>1.72442781925201</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G271" t="n">
-        <v>1.7747654914856</v>
+        <v>1.77476537227631</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G272" t="n">
-        <v>1.78483307361603</v>
+        <v>1.78483319282532</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G273" t="n">
-        <v>1.74168634414673</v>
+        <v>1.74168622493744</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G274" t="n">
-        <v>1.7488774061203</v>
+        <v>1.74887752532959</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>1.66114568710327</v>
+        <v>1.66114580631256</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G279" t="n">
-        <v>1.64244890213013</v>
+        <v>1.642449259758</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G282" t="n">
-        <v>1.71436023712158</v>
+        <v>1.71436011791229</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G284" t="n">
-        <v>1.6208758354187</v>
+        <v>1.62087571620941</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G285" t="n">
-        <v>1.65395474433899</v>
+        <v>1.6539546251297</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G287" t="n">
-        <v>1.66833710670471</v>
+        <v>1.66833698749542</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G288" t="n">
-        <v>1.64244890213013</v>
+        <v>1.642449259758</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G289" t="n">
-        <v>1.65970766544342</v>
+        <v>1.65970778465271</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G291" t="n">
-        <v>1.63094317913055</v>
+        <v>1.63094329833984</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G294" t="n">
-        <v>1.51732385158539</v>
+        <v>1.51732361316681</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G295" t="n">
-        <v>1.48136830329895</v>
+        <v>1.48136818408966</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G296" t="n">
-        <v>1.4914356470108</v>
+        <v>1.49143576622009</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G298" t="n">
-        <v>1.48280656337738</v>
+        <v>1.48280644416809</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G299" t="n">
-        <v>1.45979499816895</v>
+        <v>1.45979487895966</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>1.52451479434967</v>
+        <v>1.52451491355896</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G301" t="n">
-        <v>1.5216383934021</v>
+        <v>1.52163851261139</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G305" t="n">
-        <v>1.49718868732452</v>
+        <v>1.49718856811523</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G306" t="n">
-        <v>1.51157081127167</v>
+        <v>1.51157104969025</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G307" t="n">
-        <v>1.54464995861053</v>
+        <v>1.54465007781982</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G308" t="n">
-        <v>1.55903220176697</v>
+        <v>1.55903196334839</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>1.53889715671539</v>
+        <v>1.53889739513397</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G310" t="n">
-        <v>1.73305690288544</v>
+        <v>1.73305714130402</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G312" t="n">
-        <v>1.81503546237946</v>
+        <v>1.81503570079803</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>1.76901257038116</v>
+        <v>1.76901245117188</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G314" t="n">
-        <v>1.75750684738159</v>
+        <v>1.75750708580017</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G315" t="n">
-        <v>1.73305690288544</v>
+        <v>1.73305714130402</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>1.8121589422226</v>
+        <v>1.81215929985046</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>2.04946565628052</v>
+        <v>2.04946541786194</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G318" t="n">
-        <v>1.99049842357635</v>
+        <v>1.99049878120422</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>1.95166659355164</v>
+        <v>1.95166683197021</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G322" t="n">
-        <v>1.96317279338837</v>
+        <v>1.96317255496979</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G324" t="n">
-        <v>1.97467839717865</v>
+        <v>1.97467803955078</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G325" t="n">
-        <v>1.9588577747345</v>
+        <v>1.95885765552521</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G326" t="n">
-        <v>1.97036337852478</v>
+        <v>1.97036361694336</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G328" t="n">
-        <v>1.99625170230865</v>
+        <v>1.99625158309937</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>1.96317279338837</v>
+        <v>1.96317255496979</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G330" t="n">
-        <v>1.87400257587433</v>
+        <v>1.87400269508362</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>1.77620363235474</v>
+        <v>1.77620375156403</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G332" t="n">
-        <v>1.71004545688629</v>
+        <v>1.71004557609558</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G334" t="n">
-        <v>1.81359767913818</v>
+        <v>1.8135974407196</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G335" t="n">
-        <v>1.79058599472046</v>
+        <v>1.79058575630188</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G336" t="n">
-        <v>1.85386753082275</v>
+        <v>1.85386788845062</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G337" t="n">
-        <v>1.90851986408234</v>
+        <v>1.90852010250092</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G339" t="n">
-        <v>1.9674870967865</v>
+        <v>1.96748721599579</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.5</v>
       </c>
       <c r="G340" t="n">
-        <v>1.79777717590332</v>
+        <v>1.79777669906616</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G342" t="n">
-        <v>1.70136153697968</v>
+        <v>1.70136141777039</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G343" t="n">
-        <v>1.72954440116882</v>
+        <v>1.72954428195953</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G346" t="n">
-        <v>1.71619462966919</v>
+        <v>1.7161945104599</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G347" t="n">
-        <v>1.76514399051666</v>
+        <v>1.76514387130737</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G348" t="n">
-        <v>1.75179409980774</v>
+        <v>1.75179421901703</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G349" t="n">
-        <v>1.71471130847931</v>
+        <v>1.7147114276886</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G350" t="n">
-        <v>1.71322786808014</v>
+        <v>1.71322810649872</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G352" t="n">
-        <v>1.68652820587158</v>
+        <v>1.68652808666229</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G353" t="n">
-        <v>1.66279530525208</v>
+        <v>1.66279542446136</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G354" t="n">
-        <v>1.67169535160065</v>
+        <v>1.67169523239136</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G355" t="n">
-        <v>1.67911183834076</v>
+        <v>1.67911159992218</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G357" t="n">
-        <v>1.73547768592834</v>
+        <v>1.73547780513763</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G358" t="n">
-        <v>1.72509431838989</v>
+        <v>1.72509467601776</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G359" t="n">
-        <v>1.72064471244812</v>
+        <v>1.72064459323883</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G360" t="n">
-        <v>1.69394481182098</v>
+        <v>1.69394505023956</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G361" t="n">
-        <v>1.69246160984039</v>
+        <v>1.69246184825897</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207836151123</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G363" t="n">
-        <v>1.67911183834076</v>
+        <v>1.67911159992218</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G365" t="n">
-        <v>1.70284473896027</v>
+        <v>1.70284497737885</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G368" t="n">
-        <v>1.72212791442871</v>
+        <v>1.72212779521942</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>1.72064471244812</v>
+        <v>1.72064459323883</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G370" t="n">
-        <v>1.70136153697968</v>
+        <v>1.70136141777039</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G371" t="n">
-        <v>1.70432841777802</v>
+        <v>1.70432817935944</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G373" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207836151123</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G375" t="n">
-        <v>1.74141120910645</v>
+        <v>1.74141097068787</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>1.72806119918823</v>
+        <v>1.72806131839752</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G379" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G381" t="n">
-        <v>1.71916127204895</v>
+        <v>1.71916139125824</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G383" t="n">
-        <v>1.72806119918823</v>
+        <v>1.72806131839752</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>1.75031077861786</v>
+        <v>1.75031101703644</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G387" t="n">
-        <v>1.73696112632751</v>
+        <v>1.7369612455368</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G388" t="n">
-        <v>1.71174466609955</v>
+        <v>1.71174454689026</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G389" t="n">
-        <v>1.70284473896027</v>
+        <v>1.70284497737885</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G390" t="n">
-        <v>1.69394481182098</v>
+        <v>1.69394505023956</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G391" t="n">
-        <v>1.69394481182098</v>
+        <v>1.69394505023956</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G393" t="n">
-        <v>1.71471130847931</v>
+        <v>1.7147114276886</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G396" t="n">
-        <v>1.72212791442871</v>
+        <v>1.72212779521942</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G397" t="n">
-        <v>1.70136153697968</v>
+        <v>1.70136141777039</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G398" t="n">
-        <v>1.71322786808014</v>
+        <v>1.71322810649872</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G400" t="n">
-        <v>1.68949496746063</v>
+        <v>1.68949508666992</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G401" t="n">
-        <v>1.68504512310028</v>
+        <v>1.68504524230957</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G406" t="n">
-        <v>1.63312888145447</v>
+        <v>1.63312911987305</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>1.59456300735474</v>
+        <v>1.59456312656403</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G408" t="n">
-        <v>1.61384618282318</v>
+        <v>1.61384606361389</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G409" t="n">
-        <v>1.59159624576569</v>
+        <v>1.5915961265564</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G411" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207836151123</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G414" t="n">
-        <v>1.65686213970184</v>
+        <v>1.65686190128326</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G415" t="n">
-        <v>1.67466175556183</v>
+        <v>1.67466163635254</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G416" t="n">
-        <v>1.66576194763184</v>
+        <v>1.66576206684113</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G417" t="n">
-        <v>1.63312888145447</v>
+        <v>1.63312911987305</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G418" t="n">
-        <v>1.60346269607544</v>
+        <v>1.60346293449402</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G419" t="n">
-        <v>1.60494601726532</v>
+        <v>1.60494613647461</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G420" t="n">
-        <v>1.5975296497345</v>
+        <v>1.59752941131592</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>1.59456300735474</v>
+        <v>1.59456312656403</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G425" t="n">
-        <v>1.57082974910736</v>
+        <v>1.57082986831665</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G426" t="n">
-        <v>1.55896329879761</v>
+        <v>1.5589634180069</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G427" t="n">
-        <v>1.5826963186264</v>
+        <v>1.58269643783569</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G428" t="n">
-        <v>1.60049617290497</v>
+        <v>1.60049605369568</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G429" t="n">
-        <v>1.59159624576569</v>
+        <v>1.5915961265564</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G430" t="n">
-        <v>1.58714640140533</v>
+        <v>1.58714628219604</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G431" t="n">
-        <v>1.57824647426605</v>
+        <v>1.57824635505676</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G432" t="n">
-        <v>1.58121299743652</v>
+        <v>1.58121311664581</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G433" t="n">
-        <v>1.56786334514618</v>
+        <v>1.56786322593689</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>1.59456300735474</v>
+        <v>1.59456312656403</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G435" t="n">
-        <v>1.59901261329651</v>
+        <v>1.5990127325058</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G436" t="n">
-        <v>1.58121299743652</v>
+        <v>1.58121311664581</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>1.57231307029724</v>
+        <v>1.57231318950653</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G438" t="n">
-        <v>1.56192994117737</v>
+        <v>1.56192982196808</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>1.57231307029724</v>
+        <v>1.57231318950653</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G440" t="n">
-        <v>1.57231307029724</v>
+        <v>1.57231318950653</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G441" t="n">
-        <v>1.56637990474701</v>
+        <v>1.56637978553772</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G443" t="n">
-        <v>1.5737966299057</v>
+        <v>1.57379639148712</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>1.58714640140533</v>
+        <v>1.58714628219604</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G447" t="n">
-        <v>1.66576194763184</v>
+        <v>1.66576206684113</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G450" t="n">
-        <v>1.74882757663727</v>
+        <v>1.74882781505585</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>1.72806119918823</v>
+        <v>1.72806131839752</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G452" t="n">
-        <v>1.70136153697968</v>
+        <v>1.70136141777039</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G453" t="n">
-        <v>1.72509431838989</v>
+        <v>1.72509467601776</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G454" t="n">
-        <v>1.70432841777802</v>
+        <v>1.70432817935944</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G456" t="n">
-        <v>1.7933269739151</v>
+        <v>1.79332709312439</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G457" t="n">
-        <v>1.79629361629486</v>
+        <v>1.79629349708557</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G458" t="n">
-        <v>1.83189308643341</v>
+        <v>1.8318932056427</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>1.83930969238281</v>
+        <v>1.8393098115921</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G460" t="n">
-        <v>1.93720865249634</v>
+        <v>1.93720877170563</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G461" t="n">
-        <v>1.92089211940765</v>
+        <v>1.92089200019836</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.5</v>
       </c>
       <c r="G462" t="n">
-        <v>1.8541431427002</v>
+        <v>1.85414290428162</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.87490916252136</v>
+        <v>1.87490928173065</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G466" t="n">
-        <v>1.91199195384979</v>
+        <v>1.91199243068695</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G467" t="n">
-        <v>1.93572509288788</v>
+        <v>1.93572497367859</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G468" t="n">
-        <v>1.92089211940765</v>
+        <v>1.92089200019836</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G470" t="n">
-        <v>1.7933269739151</v>
+        <v>1.79332709312439</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G471" t="n">
-        <v>1.82892668247223</v>
+        <v>1.82892656326294</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G473" t="n">
-        <v>1.76514399051666</v>
+        <v>1.76514387130737</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G475" t="n">
-        <v>1.7072948217392</v>
+        <v>1.70729470252991</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G476" t="n">
-        <v>1.66279530525208</v>
+        <v>1.66279542446136</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G477" t="n">
-        <v>1.6375789642334</v>
+        <v>1.63757908344269</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G478" t="n">
-        <v>1.64054560661316</v>
+        <v>1.64054548740387</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G480" t="n">
-        <v>1.61829602718353</v>
+        <v>1.61829590797424</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G481" t="n">
-        <v>1.60049617290497</v>
+        <v>1.60049605369568</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G484" t="n">
-        <v>1.64796221256256</v>
+        <v>1.64796197414398</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G485" t="n">
-        <v>1.68652820587158</v>
+        <v>1.68652808666229</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G486" t="n">
-        <v>1.67021203041077</v>
+        <v>1.67021214962006</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.25</v>
       </c>
       <c r="G488" t="n">
-        <v>1.66872847080231</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G489" t="n">
-        <v>1.6375789642334</v>
+        <v>1.63757908344269</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G490" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207836151123</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G491" t="n">
-        <v>1.66724538803101</v>
+        <v>1.66724526882172</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G492" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G493" t="n">
-        <v>1.66131222248077</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G494" t="n">
-        <v>1.68652820587158</v>
+        <v>1.68652808666229</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G495" t="n">
-        <v>1.68949496746063</v>
+        <v>1.68949508666992</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G496" t="n">
-        <v>1.68949496746063</v>
+        <v>1.68949508666992</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.25</v>
       </c>
       <c r="G497" t="n">
-        <v>1.66872847080231</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G498" t="n">
-        <v>1.68949496746063</v>
+        <v>1.68949508666992</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G499" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G501" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207836151123</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G502" t="n">
-        <v>1.67466175556183</v>
+        <v>1.67466163635254</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G504" t="n">
-        <v>1.66724538803101</v>
+        <v>1.66724526882172</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G505" t="n">
-        <v>1.65834534168243</v>
+        <v>1.65834546089172</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G506" t="n">
-        <v>1.67169535160065</v>
+        <v>1.67169523239136</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G509" t="n">
-        <v>1.68504512310028</v>
+        <v>1.68504524230957</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G510" t="n">
-        <v>1.69542813301086</v>
+        <v>1.69542825222015</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G511" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207836151123</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G512" t="n">
-        <v>1.67466175556183</v>
+        <v>1.67466163635254</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G514" t="n">
-        <v>1.67985367774963</v>
+        <v>1.67985355854034</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G517" t="n">
-        <v>1.77256083488464</v>
+        <v>1.77256047725677</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G518" t="n">
-        <v>1.75031077861786</v>
+        <v>1.75031101703644</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>1.79110217094421</v>
+        <v>1.79110205173492</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76514399051666</v>
+        <v>1.76514387130737</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.7466025352478</v>
+        <v>1.74660265445709</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G526" t="n">
-        <v>1.79110217094421</v>
+        <v>1.79110205173492</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G527" t="n">
-        <v>1.78739368915558</v>
+        <v>1.78739380836487</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G528" t="n">
-        <v>1.77256083488464</v>
+        <v>1.77256047725677</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>1.79481041431427</v>
+        <v>1.79481029510498</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G531" t="n">
-        <v>1.82818484306335</v>
+        <v>1.82818472385406</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G532" t="n">
-        <v>1.77256083488464</v>
+        <v>1.77256047725677</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G534" t="n">
-        <v>1.70951974391937</v>
+        <v>1.70951998233795</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G537" t="n">
-        <v>1.66502034664154</v>
+        <v>1.66502010822296</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.25</v>
       </c>
       <c r="G539" t="n">
-        <v>1.66872847080231</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G540" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G541" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>1.63906228542328</v>
+        <v>1.63906216621399</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G544" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G545" t="n">
-        <v>1.69468665122986</v>
+        <v>1.69468653202057</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G546" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G547" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243707180023</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G548" t="n">
-        <v>1.64277052879333</v>
+        <v>1.64277040958405</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G549" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>1.66502034664154</v>
+        <v>1.66502010822296</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>1.66131222248077</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.25</v>
       </c>
       <c r="G553" t="n">
-        <v>1.66872847080231</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G554" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>1.65018701553345</v>
+        <v>1.65018725395203</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G559" t="n">
-        <v>1.64647889137268</v>
+        <v>1.64647901058197</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.25</v>
       </c>
       <c r="G560" t="n">
-        <v>1.66872847080231</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G561" t="n">
-        <v>1.69468665122986</v>
+        <v>1.69468653202057</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G563" t="n">
-        <v>1.66131222248077</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G564" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243707180023</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.25</v>
       </c>
       <c r="G565" t="n">
-        <v>1.66872847080231</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.25</v>
       </c>
       <c r="G566" t="n">
-        <v>1.66872847080231</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.25</v>
       </c>
       <c r="G567" t="n">
-        <v>1.66872847080231</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G568" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243707180023</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>1.63906228542328</v>
+        <v>1.63906216621399</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.25</v>
       </c>
       <c r="G570" t="n">
-        <v>1.66872847080231</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G571" t="n">
-        <v>1.64647889137268</v>
+        <v>1.64647901058197</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.25</v>
       </c>
       <c r="G573" t="n">
-        <v>1.66872847080231</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G574" t="n">
-        <v>1.66131222248077</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G575" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243707180023</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G576" t="n">
-        <v>1.64647889137268</v>
+        <v>1.64647901058197</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G577" t="n">
-        <v>1.67985367774963</v>
+        <v>1.67985355854034</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>1.68727004528046</v>
+        <v>1.68726992607117</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G581" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.25</v>
       </c>
       <c r="G583" t="n">
-        <v>1.66872847080231</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G584" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243707180023</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.25</v>
       </c>
       <c r="G586" t="n">
-        <v>1.66872847080231</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G587" t="n">
-        <v>1.64647889137268</v>
+        <v>1.64647901058197</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G588" t="n">
-        <v>1.66131222248077</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>1.66131222248077</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.25</v>
       </c>
       <c r="G590" t="n">
-        <v>1.66872847080231</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G591" t="n">
-        <v>1.66131222248077</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G596" t="n">
-        <v>1.69468665122986</v>
+        <v>1.69468653202057</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G598" t="n">
-        <v>1.72984218597412</v>
+        <v>1.7298424243927</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G599" t="n">
-        <v>1.72984218597412</v>
+        <v>1.7298424243927</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G600" t="n">
-        <v>1.74140012264252</v>
+        <v>1.74140024185181</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G601" t="n">
-        <v>1.725989818573</v>
+        <v>1.72598969936371</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>1.70287370681763</v>
+        <v>1.70287382602692</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G605" t="n">
-        <v>1.62967336177826</v>
+        <v>1.62967312335968</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G606" t="n">
-        <v>1.64893651008606</v>
+        <v>1.64893674850464</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G607" t="n">
-        <v>1.55262017250061</v>
+        <v>1.5526202917099</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G608" t="n">
-        <v>1.55262017250061</v>
+        <v>1.5526202917099</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G609" t="n">
-        <v>1.49791240692139</v>
+        <v>1.49791252613068</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G610" t="n">
-        <v>1.48096084594727</v>
+        <v>1.48096072673798</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G611" t="n">
-        <v>1.53489804267883</v>
+        <v>1.53489792346954</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G612" t="n">
-        <v>1.52102839946747</v>
+        <v>1.52102828025818</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G617" t="n">
-        <v>1.51332306861877</v>
+        <v>1.51332318782806</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G618" t="n">
-        <v>1.49791240692139</v>
+        <v>1.49791252613068</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G619" t="n">
-        <v>1.49174809455872</v>
+        <v>1.49174833297729</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G624" t="n">
-        <v>1.568030834198</v>
+        <v>1.56803095340729</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G625" t="n">
-        <v>1.62196803092957</v>
+        <v>1.62196815013885</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>1.62196803092957</v>
+        <v>1.62196815013885</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G627" t="n">
-        <v>1.59499943256378</v>
+        <v>1.59499931335449</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.65664184093475</v>
+        <v>1.65664172172546</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G632" t="n">
-        <v>1.61040997505188</v>
+        <v>1.61040985584259</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G635" t="n">
-        <v>1.57573616504669</v>
+        <v>1.5757360458374</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G636" t="n">
-        <v>1.568030834198</v>
+        <v>1.56803095340729</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>1.56032562255859</v>
+        <v>1.5603255033493</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G638" t="n">
-        <v>1.568030834198</v>
+        <v>1.56803095340729</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>1.59499943256378</v>
+        <v>1.59499931335449</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G642" t="n">
-        <v>1.59499943256378</v>
+        <v>1.59499931335449</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G643" t="n">
-        <v>1.61811542510986</v>
+        <v>1.61811530590057</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>1.62196803092957</v>
+        <v>1.62196815013885</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>1.59499943256378</v>
+        <v>1.59499931335449</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>1.60655748844147</v>
+        <v>1.60655736923218</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G649" t="n">
-        <v>1.59499943256378</v>
+        <v>1.59499931335449</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>1.568030834198</v>
+        <v>1.56803095340729</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G657" t="n">
-        <v>1.62967336177826</v>
+        <v>1.62967312335968</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G659" t="n">
-        <v>1.61426270008087</v>
+        <v>1.61426258087158</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G660" t="n">
-        <v>1.62196803092957</v>
+        <v>1.62196815013885</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G669" t="n">
-        <v>1.54876756668091</v>
+        <v>1.54876744747162</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G670" t="n">
-        <v>1.5449150800705</v>
+        <v>1.54491496086121</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G672" t="n">
-        <v>1.52102839946747</v>
+        <v>1.52102828025818</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G674" t="n">
-        <v>1.55262017250061</v>
+        <v>1.5526202917099</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G675" t="n">
-        <v>1.53489804267883</v>
+        <v>1.53489792346954</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>1.57573616504669</v>
+        <v>1.5757360458374</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>1.56032562255859</v>
+        <v>1.5603255033493</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G680" t="n">
-        <v>1.5449150800705</v>
+        <v>1.54491496086121</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2</v>
       </c>
       <c r="G681" t="n">
-        <v>1.54106211662292</v>
+        <v>1.54106223583221</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G682" t="n">
-        <v>1.54876756668091</v>
+        <v>1.54876744747162</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G684" t="n">
-        <v>1.57573616504669</v>
+        <v>1.5757360458374</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G686" t="n">
-        <v>1.5449150800705</v>
+        <v>1.54491496086121</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G691" t="n">
-        <v>1.568030834198</v>
+        <v>1.56803095340729</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G692" t="n">
-        <v>1.57573616504669</v>
+        <v>1.5757360458374</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>1.57573616504669</v>
+        <v>1.5757360458374</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>1.57573616504669</v>
+        <v>1.5757360458374</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G698" t="n">
-        <v>1.61040997505188</v>
+        <v>1.61040985584259</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G699" t="n">
-        <v>1.61811542510986</v>
+        <v>1.61811530590057</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>1.65664184093475</v>
+        <v>1.65664172172546</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G701" t="n">
-        <v>1.61040997505188</v>
+        <v>1.61040985584259</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>1.54876756668091</v>
+        <v>1.54876744747162</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G704" t="n">
-        <v>1.55262017250061</v>
+        <v>1.5526202917099</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2</v>
       </c>
       <c r="G706" t="n">
-        <v>1.54106211662292</v>
+        <v>1.54106223583221</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G709" t="n">
-        <v>1.48096084594727</v>
+        <v>1.48096072673798</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G711" t="n">
-        <v>1.4347288608551</v>
+        <v>1.43472898006439</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G714" t="n">
-        <v>1.42394161224365</v>
+        <v>1.42394149303436</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G716" t="n">
-        <v>1.39157927036285</v>
+        <v>1.39157903194427</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G717" t="n">
-        <v>1.32377231121063</v>
+        <v>1.32377254962921</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G719" t="n">
-        <v>1.21281588077545</v>
+        <v>1.21281599998474</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G720" t="n">
-        <v>1.25288355350494</v>
+        <v>1.25288367271423</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G724" t="n">
-        <v>1.29449212551117</v>
+        <v>1.29449224472046</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G725" t="n">
-        <v>1.30990290641785</v>
+        <v>1.30990278720856</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G727" t="n">
-        <v>1.29295110702515</v>
+        <v>1.29295134544373</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G732" t="n">
-        <v>1.28370487689972</v>
+        <v>1.28370475769043</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G733" t="n">
-        <v>1.2806224822998</v>
+        <v>1.28062260150909</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G735" t="n">
-        <v>1.18353569507599</v>
+        <v>1.18353581428528</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G737" t="n">
-        <v>1.19894647598267</v>
+        <v>1.19894635677338</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G742" t="n">
-        <v>1.17274844646454</v>
+        <v>1.17274832725525</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G743" t="n">
-        <v>1.22976756095886</v>
+        <v>1.22976768016815</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G748" t="n">
-        <v>1.23593175411224</v>
+        <v>1.23593199253082</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G751" t="n">
-        <v>1.26213002204895</v>
+        <v>1.26212990283966</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G754" t="n">
-        <v>1.18045353889465</v>
+        <v>1.18045365810394</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G755" t="n">
-        <v>1.17274844646454</v>
+        <v>1.17274832725525</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G756" t="n">
-        <v>1.15733778476715</v>
+        <v>1.15733766555786</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G758" t="n">
-        <v>1.0956951379776</v>
+        <v>1.09569525718689</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G759" t="n">
-        <v>1.10185945034027</v>
+        <v>1.10185933113098</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G761" t="n">
-        <v>1.07566142082214</v>
+        <v>1.07566130161285</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G763" t="n">
-        <v>1.10802364349365</v>
+        <v>1.10802352428436</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G764" t="n">
-        <v>1.11264681816101</v>
+        <v>1.1126469373703</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G766" t="n">
-        <v>1.15733778476715</v>
+        <v>1.15733766555786</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.5</v>
       </c>
       <c r="G768" t="n">
-        <v>1.15579652786255</v>
+        <v>1.15579664707184</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G769" t="n">
-        <v>1.16350185871124</v>
+        <v>1.16350209712982</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G770" t="n">
-        <v>1.15425550937653</v>
+        <v>1.15425562858582</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.5</v>
       </c>
       <c r="G771" t="n">
-        <v>1.15579652786255</v>
+        <v>1.15579664707184</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G773" t="n">
-        <v>1.11727023124695</v>
+        <v>1.11727011203766</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G775" t="n">
-        <v>1.14655029773712</v>
+        <v>1.14655041694641</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>1.5</v>
       </c>
       <c r="G777" t="n">
-        <v>1.15579652786255</v>
+        <v>1.15579664707184</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G778" t="n">
-        <v>1.14655029773712</v>
+        <v>1.14655041694641</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G779" t="n">
-        <v>1.13268089294434</v>
+        <v>1.13268065452576</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>1.12497532367706</v>
+        <v>1.12497544288635</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G781" t="n">
-        <v>1.13268089294434</v>
+        <v>1.13268065452576</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G782" t="n">
-        <v>1.12651634216309</v>
+        <v>1.12651646137238</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G784" t="n">
-        <v>1.10802364349365</v>
+        <v>1.10802352428436</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G785" t="n">
-        <v>1.10340058803558</v>
+        <v>1.10340046882629</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G786" t="n">
-        <v>1.07412052154541</v>
+        <v>1.07412040233612</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G792" t="n">
-        <v>1.15425550937653</v>
+        <v>1.15425562858582</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G793" t="n">
-        <v>1.17428958415985</v>
+        <v>1.17428946495056</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G797" t="n">
-        <v>1.24671936035156</v>
+        <v>1.24671924114227</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G798" t="n">
-        <v>1.23593175411224</v>
+        <v>1.23593199253082</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G808" t="n">
-        <v>1.28678703308105</v>
+        <v>1.28678691387177</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G809" t="n">
-        <v>1.27754056453705</v>
+        <v>1.27754044532776</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G811" t="n">
-        <v>1.21589815616608</v>
+        <v>1.21589803695679</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G812" t="n">
-        <v>1.18199467658997</v>
+        <v>1.18199479579926</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G813" t="n">
-        <v>1.16504299640656</v>
+        <v>1.16504287719727</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G814" t="n">
-        <v>1.16504299640656</v>
+        <v>1.16504287719727</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G816" t="n">
-        <v>1.16658401489258</v>
+        <v>1.16658413410187</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G817" t="n">
-        <v>1.16658401489258</v>
+        <v>1.16658413410187</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G818" t="n">
-        <v>1.16504299640656</v>
+        <v>1.16504287719727</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.5</v>
       </c>
       <c r="G819" t="n">
-        <v>1.15579652786255</v>
+        <v>1.15579664707184</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G823" t="n">
-        <v>1.14192712306976</v>
+        <v>1.14192700386047</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G825" t="n">
-        <v>1.15425550937653</v>
+        <v>1.15425562858582</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>1.5</v>
       </c>
       <c r="G826" t="n">
-        <v>1.15579652786255</v>
+        <v>1.15579664707184</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.5</v>
       </c>
       <c r="G829" t="n">
-        <v>1.15579652786255</v>
+        <v>1.15579664707184</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G830" t="n">
-        <v>1.15733778476715</v>
+        <v>1.15733766555786</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.5</v>
       </c>
       <c r="G831" t="n">
-        <v>1.15579652786255</v>
+        <v>1.15579664707184</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G832" t="n">
-        <v>1.16041994094849</v>
+        <v>1.1604198217392</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G833" t="n">
-        <v>1.16196095943451</v>
+        <v>1.16196084022522</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G835" t="n">
-        <v>1.26367092132568</v>
+        <v>1.26367104053497</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G837" t="n">
-        <v>1.29295110702515</v>
+        <v>1.29295134544373</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G840" t="n">
-        <v>1.29295110702515</v>
+        <v>1.29295134544373</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G841" t="n">
-        <v>1.28678703308105</v>
+        <v>1.28678691387177</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G842" t="n">
-        <v>1.26367092132568</v>
+        <v>1.26367104053497</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G844" t="n">
-        <v>1.2806224822998</v>
+        <v>1.28062260150909</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G850" t="n">
-        <v>1.26629877090454</v>
+        <v>1.26629853248596</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.5</v>
       </c>
       <c r="G852" t="n">
-        <v>1.21915781497955</v>
+        <v>1.21915793418884</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G853" t="n">
-        <v>1.22240889072418</v>
+        <v>1.22240900993347</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G857" t="n">
-        <v>1.12162530422211</v>
+        <v>1.12162518501282</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G858" t="n">
-        <v>1.11349749565125</v>
+        <v>1.11349761486053</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G861" t="n">
-        <v>1.0858633518219</v>
+        <v>1.08586323261261</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G864" t="n">
-        <v>1.07285904884338</v>
+        <v>1.07285892963409</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G868" t="n">
-        <v>1.00458610057831</v>
+        <v>1.0045862197876</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G869" t="n">
-        <v>1.01271367073059</v>
+        <v>1.01271378993988</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G872" t="n">
-        <v>0.976951956748962</v>
+        <v>0.976951897144318</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G873" t="n">
-        <v>0.967198669910431</v>
+        <v>0.967198610305786</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G876" t="n">
-        <v>0.936313152313232</v>
+        <v>0.936313271522522</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G877" t="n">
-        <v>0.91193014383316</v>
+        <v>0.911930084228516</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G879" t="n">
-        <v>0.92818546295166</v>
+        <v>0.928185522556305</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G880" t="n">
-        <v>0.924934446811676</v>
+        <v>0.924934387207031</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G881" t="n">
-        <v>0.936313152313232</v>
+        <v>0.936313271522522</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G882" t="n">
-        <v>0.950943112373352</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G883" t="n">
-        <v>0.957445323467255</v>
+        <v>0.95744526386261</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G885" t="n">
-        <v>0.933062136173248</v>
+        <v>0.933062255382538</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G887" t="n">
-        <v>0.965572953224182</v>
+        <v>0.965573012828827</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G888" t="n">
-        <v>0.965572953224182</v>
+        <v>0.965573012828827</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G889" t="n">
-        <v>0.98345410823822</v>
+        <v>0.983454048633575</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G890" t="n">
-        <v>0.976951956748962</v>
+        <v>0.976951897144318</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.25</v>
       </c>
       <c r="G895" t="n">
-        <v>1.0159649848938</v>
+        <v>1.01596486568451</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G896" t="n">
-        <v>1.03059494495392</v>
+        <v>1.03059482574463</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>1.25</v>
       </c>
       <c r="G897" t="n">
-        <v>1.0159649848938</v>
+        <v>1.01596486568451</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G898" t="n">
-        <v>1.01271367073059</v>
+        <v>1.01271378993988</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G899" t="n">
-        <v>0.976951956748962</v>
+        <v>0.976951897144318</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G900" t="n">
-        <v>0.994832754135132</v>
+        <v>0.994832813739777</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G901" t="n">
-        <v>0.981828272342682</v>
+        <v>0.981828331947327</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G902" t="n">
-        <v>1.01271367073059</v>
+        <v>1.01271378993988</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G904" t="n">
-        <v>0.98345410823822</v>
+        <v>0.983454048633575</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>1.25</v>
       </c>
       <c r="G909" t="n">
-        <v>1.0159649848938</v>
+        <v>1.01596486568451</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G914" t="n">
-        <v>1.01108813285828</v>
+        <v>1.01108825206757</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>0.950943112373352</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G920" t="n">
-        <v>0.952568650245667</v>
+        <v>0.952568709850311</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G922" t="n">
-        <v>0.92818546295166</v>
+        <v>0.928185522556305</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G925" t="n">
-        <v>0.967198669910431</v>
+        <v>0.967198610305786</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G926" t="n">
-        <v>0.981828272342682</v>
+        <v>0.981828331947327</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G927" t="n">
-        <v>0.978577435016632</v>
+        <v>0.978577375411987</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>0.975326478481293</v>
+        <v>0.975326418876648</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G929" t="n">
-        <v>0.973700702190399</v>
+        <v>0.973700821399689</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G931" t="n">
-        <v>0.98507958650589</v>
+        <v>0.985079526901245</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G932" t="n">
-        <v>0.980202913284302</v>
+        <v>0.980202972888947</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G933" t="n">
-        <v>0.965572953224182</v>
+        <v>0.965573012828827</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G934" t="n">
-        <v>0.950943112373352</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.25</v>
       </c>
       <c r="G935" t="n">
-        <v>1.0159649848938</v>
+        <v>1.01596486568451</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G949" t="n">
-        <v>1.15738713741302</v>
+        <v>1.15738725662231</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G955" t="n">
-        <v>1.12325072288513</v>
+        <v>1.12325084209442</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G956" t="n">
-        <v>1.09561669826508</v>
+        <v>1.09561657905579</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G963" t="n">
-        <v>1.17364263534546</v>
+        <v>1.17364275455475</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G967" t="n">
-        <v>1.18827247619629</v>
+        <v>1.18827259540558</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G969" t="n">
-        <v>1.18502140045166</v>
+        <v>1.18502151966095</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G974" t="n">
-        <v>1.2728009223938</v>
+        <v>1.27280080318451</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G975" t="n">
-        <v>1.25491988658905</v>
+        <v>1.25491976737976</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G985" t="n">
-        <v>1.34920132160187</v>
+        <v>1.34920144081116</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G986" t="n">
-        <v>1.36870801448822</v>
+        <v>1.36870789527893</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G993" t="n">
-        <v>1.52313458919525</v>
+        <v>1.52313446998596</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G996" t="n">
-        <v>1.50037705898285</v>
+        <v>1.50037693977356</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G997" t="n">
-        <v>1.50200271606445</v>
+        <v>1.50200247764587</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G998" t="n">
-        <v>1.45811283588409</v>
+        <v>1.45811295509338</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G999" t="n">
-        <v>1.45486164093018</v>
+        <v>1.45486176013947</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.4711172580719</v>
+        <v>1.47111713886261</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.51500678062439</v>
+        <v>1.51500689983368</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.54101550579071</v>
+        <v>1.541015625</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.55401980876923</v>
+        <v>1.55401992797852</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.60116064548492</v>
+        <v>1.60116076469421</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.55889666080475</v>
+        <v>1.55889654159546</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.54426670074463</v>
+        <v>1.54426658153534</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.55889666080475</v>
+        <v>1.55889654159546</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.54589211940765</v>
+        <v>1.54589223861694</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.50200271606445</v>
+        <v>1.50200247764587</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.45161056518555</v>
+        <v>1.45161068439484</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.46298944950104</v>
+        <v>1.46298933029175</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.47924494743347</v>
+        <v>1.47924506664276</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.46298944950104</v>
+        <v>1.46298933029175</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.47924494743347</v>
+        <v>1.47924506664276</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.45811283588409</v>
+        <v>1.45811295509338</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.43047869205475</v>
+        <v>1.43047857284546</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.57677757740021</v>
+        <v>1.5767776966095</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.59790945053101</v>
+        <v>1.5979095697403</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.7393319606781</v>
+        <v>1.73933207988739</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.70682108402252</v>
+        <v>1.70682096481323</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.68243789672852</v>
+        <v>1.68243777751923</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.45486164093018</v>
+        <v>1.45486176013947</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.34920132160187</v>
+        <v>1.34920144081116</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.31343948841095</v>
+        <v>1.31343936920166</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.18177044391632</v>
+        <v>1.18177032470703</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.978577435016632</v>
+        <v>0.978577375411987</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.897300243377686</v>
+        <v>0.897300183773041</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.902176797389984</v>
+        <v>0.902176856994629</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.817648649215698</v>
+        <v>0.817648589611053</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.845282733440399</v>
+        <v>0.845282793045044</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.861538231372833</v>
+        <v>0.861538171768188</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.88592141866684</v>
+        <v>0.885921478271484</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.950943112373352</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.942815482616425</v>
+        <v>0.94281542301178</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.881044805049896</v>
+        <v>0.881044745445251</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.879419207572937</v>
+        <v>0.879419267177582</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.921683311462402</v>
+        <v>0.921683251857758</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.98345410823822</v>
+        <v>0.983454048633575</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.965572953224182</v>
+        <v>0.965573012828827</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.25</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.0159649848938</v>
+        <v>1.01596486568451</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.01921594142914</v>
+        <v>1.01921582221985</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.978577435016632</v>
+        <v>0.978577375411987</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.996458292007446</v>
+        <v>0.996458411216736</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.04685020446777</v>
+        <v>1.04685032367706</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.25</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.0159649848938</v>
+        <v>1.01596486568451</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.996458292007446</v>
+        <v>0.996458411216736</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.978577435016632</v>
+        <v>0.978577375411987</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.01108813285828</v>
+        <v>1.01108825206757</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.28199994564056</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.04197359085083</v>
+        <v>1.04197347164154</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.08098661899567</v>
+        <v>1.08098673820496</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.08098661899567</v>
+        <v>1.08098673820496</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.03872263431549</v>
+        <v>1.0387225151062</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.03059494495392</v>
+        <v>1.03059482574463</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.02896928787231</v>
+        <v>1.0289694070816</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.01433944702148</v>
+        <v>1.01433932781219</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.980202913284302</v>
+        <v>0.980202972888947</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.980202913284302</v>
+        <v>0.980202972888947</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.01271367073059</v>
+        <v>1.01271378993988</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.959070801734924</v>
+        <v>0.95907074213028</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.975326478481293</v>
+        <v>0.975326418876648</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.999709606170654</v>
+        <v>0.999709486961365</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.0858633518219</v>
+        <v>1.08586323261261</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.13950622081757</v>
+        <v>1.13950610160828</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.18989813327789</v>
+        <v>1.1898980140686</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.22403454780579</v>
+        <v>1.2240344285965</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.21915781497955</v>
+        <v>1.21915793418884</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.11349749565125</v>
+        <v>1.11349761486053</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.11187195777893</v>
+        <v>1.11187207698822</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.09886753559113</v>
+        <v>1.09886765480042</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.09724199771881</v>
+        <v>1.0972421169281</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.0874890089035</v>
+        <v>1.08748888969421</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.09886753559113</v>
+        <v>1.09886765480042</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.06798231601715</v>
+        <v>1.06798243522644</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.09561669826508</v>
+        <v>1.09561657905579</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.18502140045166</v>
+        <v>1.18502151966095</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.27930295467377</v>
+        <v>1.27930307388306</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.43047869205475</v>
+        <v>1.43047857284546</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.44998502731323</v>
+        <v>1.44998514652252</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.45161056518555</v>
+        <v>1.45161068439484</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.47924494743347</v>
+        <v>1.47924506664276</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.46298944950104</v>
+        <v>1.46298933029175</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.47924494743347</v>
+        <v>1.47924506664276</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.4142233133316</v>
+        <v>1.41422319412231</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.4142233133316</v>
+        <v>1.41422319412231</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.44510865211487</v>
+        <v>1.44510853290558</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.44185745716095</v>
+        <v>1.44185733795166</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.44673407077789</v>
+        <v>1.4467339515686</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.52313458919525</v>
+        <v>1.52313446998596</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.54264104366302</v>
+        <v>1.54264116287231</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.52476024627686</v>
+        <v>1.52476012706757</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.55401980876923</v>
+        <v>1.55401992797852</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.51175570487976</v>
+        <v>1.51175582408905</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.45811283588409</v>
+        <v>1.45811295509338</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.47924494743347</v>
+        <v>1.47924506664276</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.47924494743347</v>
+        <v>1.47924506664276</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1185" t="n">
-        <v>1.4711172580719</v>
+        <v>1.47111713886261</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.44510865211487</v>
+        <v>1.44510853290558</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.39959335327148</v>
+        <v>1.39959323406219</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.41584873199463</v>
+        <v>1.41584861278534</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.43047869205475</v>
+        <v>1.43047857284546</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.76400005817413</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.43372976779938</v>
+        <v>1.43372964859009</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.33294582366943</v>
+        <v>1.33294594287872</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.31994163990021</v>
+        <v>1.31994152069092</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.31669044494629</v>
+        <v>1.31669056415558</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.3638311624527</v>
+        <v>1.36383128166199</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.34432482719421</v>
+        <v>1.34432470798492</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.39959335327148</v>
+        <v>1.39959323406219</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.35407817363739</v>
+        <v>1.3540780544281</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.33619701862335</v>
+        <v>1.33619713783264</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.38658893108368</v>
+        <v>1.38658881187439</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.29718410968781</v>
+        <v>1.29718387126923</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.25004327297211</v>
+        <v>1.25004315376282</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.1330041885376</v>
+        <v>1.13300406932831</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.1541360616684</v>
+        <v>1.15413618087769</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.15088510513306</v>
+        <v>1.15088498592377</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.22891116142273</v>
+        <v>1.22891104221344</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.24191558361053</v>
+        <v>1.24191546440125</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.25491988658905</v>
+        <v>1.25491976737976</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G1235" t="n">
-        <v>1.31181395053864</v>
+        <v>1.31181383132935</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.31994163990021</v>
+        <v>1.31994152069092</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.39959335327148</v>
+        <v>1.39959323406219</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.76400005817413</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.43372976779938</v>
+        <v>1.43372964859009</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.44673407077789</v>
+        <v>1.4467339515686</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.44673407077789</v>
+        <v>1.4467339515686</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.45486164093018</v>
+        <v>1.45486176013947</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.38983988761902</v>
+        <v>1.3898401260376</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.34432482719421</v>
+        <v>1.34432470798492</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.33294582366943</v>
+        <v>1.33294594287872</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.31669044494629</v>
+        <v>1.31669056415558</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1260" t="n">
-        <v>1.35407817363739</v>
+        <v>1.3540780544281</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.34920132160187</v>
+        <v>1.34920144081116</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.2841796875</v>
+        <v>1.28417956829071</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.36870801448822</v>
+        <v>1.36870789527893</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.35407817363739</v>
+        <v>1.3540780544281</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.38983988761902</v>
+        <v>1.3898401260376</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.39471650123596</v>
+        <v>1.39471662044525</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.40934646129608</v>
+        <v>1.40934658050537</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.42072522640228</v>
+        <v>1.42072534561157</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.38983988761902</v>
+        <v>1.3898401260376</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.38658893108368</v>
+        <v>1.38658881187439</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.39471650123596</v>
+        <v>1.39471662044525</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.41097211837769</v>
+        <v>1.4109719991684</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.40934646129608</v>
+        <v>1.40934658050537</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.32319283485413</v>
+        <v>1.32319271564484</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.34920132160187</v>
+        <v>1.34920144081116</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.35407817363739</v>
+        <v>1.3540780544281</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.33457136154175</v>
+        <v>1.33457148075104</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.36545670032501</v>
+        <v>1.3654568195343</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.41909980773926</v>
+        <v>1.41909992694855</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.4711172580719</v>
+        <v>1.47111713886261</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.54264104366302</v>
+        <v>1.54264116287231</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.57352638244629</v>
+        <v>1.57352650165558</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.55564558506012</v>
+        <v>1.55564546585083</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.50200271606445</v>
+        <v>1.50200247764587</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.46298944950104</v>
+        <v>1.46298933029175</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.47761940956116</v>
+        <v>1.47761929035187</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.61253952980042</v>
+        <v>1.61253941059113</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.60116064548492</v>
+        <v>1.60116076469421</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.62066721916199</v>
+        <v>1.62066733837128</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.60441184043884</v>
+        <v>1.60441172122955</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.59303307533264</v>
+        <v>1.59303295612335</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.64992713928223</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.71088480949402</v>
+        <v>1.7108850479126</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.65399086475372</v>
+        <v>1.65399098396301</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.63773536682129</v>
+        <v>1.63773560523987</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.62229287624359</v>
+        <v>1.6222927570343</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.60441184043884</v>
+        <v>1.60441172122955</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.68243789672852</v>
+        <v>1.68243777751923</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.69462943077087</v>
+        <v>1.69462954998016</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.70682108402252</v>
+        <v>1.70682096481323</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.69462943077087</v>
+        <v>1.69462954998016</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.62229287624359</v>
+        <v>1.6222927570343</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.6296079158783</v>
+        <v>1.62960779666901</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.66618239879608</v>
+        <v>1.66618251800537</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.66618239879608</v>
+        <v>1.66618251800537</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.69869327545166</v>
+        <v>1.69869315624237</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.68243789672852</v>
+        <v>1.68243777751923</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.68243789672852</v>
+        <v>1.68243777751923</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.69869327545166</v>
+        <v>1.69869315624237</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.68243789672852</v>
+        <v>1.68243777751923</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.70682108402252</v>
+        <v>1.70682096481323</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.72307646274567</v>
+        <v>1.72307634353638</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.64992713928223</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.66618239879608</v>
+        <v>1.66618251800537</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.64992713928223</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.64992713928223</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.64992713928223</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.64992713928223</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.65399086475372</v>
+        <v>1.65399098396301</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.69869327545166</v>
+        <v>1.69869315624237</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.75152361392975</v>
+        <v>1.75152349472046</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.75558733940125</v>
+        <v>1.75558745861053</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.75152361392975</v>
+        <v>1.75152349472046</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.75558733940125</v>
+        <v>1.75558745861053</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.7393319606781</v>
+        <v>1.73933207988739</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.71088480949402</v>
+        <v>1.7108850479126</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.69869327545166</v>
+        <v>1.69869315624237</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.68243789672852</v>
+        <v>1.68243777751923</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.70682108402252</v>
+        <v>1.70682096481323</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.70682108402252</v>
+        <v>1.70682096481323</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.70682108402252</v>
+        <v>1.70682096481323</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.66618239879608</v>
+        <v>1.66618251800537</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.69869327545166</v>
+        <v>1.69869315624237</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.68243789672852</v>
+        <v>1.68243777751923</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.66618239879608</v>
+        <v>1.66618251800537</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.63773536682129</v>
+        <v>1.63773560523987</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.64992713928223</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.65399086475372</v>
+        <v>1.65399098396301</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.66618239879608</v>
+        <v>1.66618251800537</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.7393319606781</v>
+        <v>1.73933207988739</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.73120427131653</v>
+        <v>1.73120439052582</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.73120427131653</v>
+        <v>1.73120439052582</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.72307646274567</v>
+        <v>1.72307634353638</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.66618239879608</v>
+        <v>1.66618251800537</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.69869327545166</v>
+        <v>1.69869315624237</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.72307646274567</v>
+        <v>1.72307634353638</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.75152361392975</v>
+        <v>1.75152349472046</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.75152361392975</v>
+        <v>1.75152349472046</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.75965106487274</v>
+        <v>1.75965118408203</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.74339580535889</v>
+        <v>1.7433956861496</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.80841755867004</v>
+        <v>1.80841743946075</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.77997064590454</v>
+        <v>1.77997052669525</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.77590668201447</v>
+        <v>1.77590656280518</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.83686459064484</v>
+        <v>1.83686447143555</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.79216194152832</v>
+        <v>1.79216182231903</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.83686459064484</v>
+        <v>1.83686447143555</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.8775030374527</v>
+        <v>1.87750315666199</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.92626953125</v>
+        <v>1.92626941204071</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.91407799720764</v>
+        <v>1.91407787799835</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.89782238006592</v>
+        <v>1.8978226184845</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.91814160346985</v>
+        <v>1.91814148426056</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.88563096523285</v>
+        <v>1.88563084602356</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.91407799720764</v>
+        <v>1.91407787799835</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.91001391410828</v>
+        <v>1.91001403331757</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.89375865459442</v>
+        <v>1.89375853538513</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.86124765872955</v>
+        <v>1.86124789714813</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.84499228000641</v>
+        <v>1.84499216079712</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>2.25</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.82873690128326</v>
+        <v>1.82873666286469</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>2.25</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.82873690128326</v>
+        <v>1.82873666286469</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.85718405246735</v>
+        <v>1.85718381404877</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.85718405246735</v>
+        <v>1.85718381404877</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>2.25</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.82873690128326</v>
+        <v>1.82873666286469</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.83686459064484</v>
+        <v>1.83686447143555</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.86124765872955</v>
+        <v>1.86124789714813</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.89375865459442</v>
+        <v>1.89375853538513</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.88156700134277</v>
+        <v>1.88156676292419</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.89375865459442</v>
+        <v>1.89375853538513</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>2.25</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.82873690128326</v>
+        <v>1.82873666286469</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.85718405246735</v>
+        <v>1.85718381404877</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1462" t="n">
-        <v>1.84499228000641</v>
+        <v>1.84499216079712</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.84905636310577</v>
+        <v>1.84905624389648</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.81248140335083</v>
+        <v>1.81248128414154</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.85718405246735</v>
+        <v>1.85718381404877</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.84905636310577</v>
+        <v>1.84905624389648</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.88563096523285</v>
+        <v>1.88563084602356</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.84905636310577</v>
+        <v>1.84905624389648</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.9018862247467</v>
+        <v>1.90188610553741</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.86124765872955</v>
+        <v>1.86124789714813</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1472" t="n">
-        <v>1.88156700134277</v>
+        <v>1.88156676292419</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.8775030374527</v>
+        <v>1.87750315666199</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1475" t="n">
-        <v>1.83280074596405</v>
+        <v>1.83280062675476</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1477" t="n">
-        <v>1.82467293739319</v>
+        <v>1.82467305660248</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.8775030374527</v>
+        <v>1.87750315666199</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.92220568656921</v>
+        <v>1.92220556735992</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1480" t="n">
-        <v>1.90595006942749</v>
+        <v>1.90595018863678</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.88156700134277</v>
+        <v>1.88156676292419</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.88156700134277</v>
+        <v>1.88156676292419</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.84092855453491</v>
+        <v>1.8409286737442</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.89375865459442</v>
+        <v>1.89375853538513</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.8775030374527</v>
+        <v>1.87750315666199</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>1.91001391410828</v>
+        <v>1.91001403331757</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.91001391410828</v>
+        <v>1.91001403331757</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.97097170352936</v>
+        <v>1.97097194194794</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.9298369884491</v>
+        <v>1.92983675003052</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.8466922044754</v>
+        <v>1.84669196605682</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.80730783939362</v>
+        <v>1.80730772018433</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1498" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.73641574382782</v>
+        <v>1.73641562461853</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.73291504383087</v>
+        <v>1.73291492462158</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.81605982780457</v>
+        <v>1.81605994701385</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.82918798923492</v>
+        <v>1.82918775081635</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.83356404304504</v>
+        <v>1.83356392383575</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.83356404304504</v>
+        <v>1.83356392383575</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.82918798923492</v>
+        <v>1.82918775081635</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.81605982780457</v>
+        <v>1.81605994701385</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.80293166637421</v>
+        <v>1.80293154716492</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.85106825828552</v>
+        <v>1.85106813907623</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.89045262336731</v>
+        <v>1.8904527425766</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.8466922044754</v>
+        <v>1.84669196605682</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>2.125</v>
       </c>
       <c r="G1535" t="n">
-        <v>1.85982012748718</v>
+        <v>1.85982036590576</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.8466922044754</v>
+        <v>1.84669196605682</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1540" t="n">
-        <v>1.80730783939362</v>
+        <v>1.80730772018433</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>2</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.75041913986206</v>
+        <v>1.75041902065277</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.8466922044754</v>
+        <v>1.84669196605682</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.82918798923492</v>
+        <v>1.82918775081635</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1554" t="n">
-        <v>1.80293166637421</v>
+        <v>1.80293154716492</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.85106825828552</v>
+        <v>1.85106813907623</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.8466922044754</v>
+        <v>1.84669196605682</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.89045262336731</v>
+        <v>1.8904527425766</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.89482867717743</v>
+        <v>1.89482855796814</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>2.125</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.85982012748718</v>
+        <v>1.85982036590576</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.80293166637421</v>
+        <v>1.80293154716492</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.72416269779205</v>
+        <v>1.72416281700134</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1569" t="n">
-        <v>1.70665872097015</v>
+        <v>1.70665860176086</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1571" t="n">
-        <v>1.51936364173889</v>
+        <v>1.51936376094818</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.51586294174194</v>
+        <v>1.51586282253265</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1574" t="n">
-        <v>1.62438881397247</v>
+        <v>1.62438893318176</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.58938038349152</v>
+        <v>1.58938050270081</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G1577" t="n">
-        <v>1.61213600635529</v>
+        <v>1.612135887146</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.633141040802</v>
+        <v>1.63314116001129</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>1.95200002193451</v>
       </c>
       <c r="G1579" t="n">
-        <v>1.70840907096863</v>
+        <v>1.70840895175934</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.63139069080353</v>
+        <v>1.63139057159424</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.70665872097015</v>
+        <v>1.70665860176086</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.74166703224182</v>
+        <v>1.74166691303253</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.72766375541687</v>
+        <v>1.72766363620758</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.72766375541687</v>
+        <v>1.72766363620758</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.73116457462311</v>
+        <v>1.7311646938324</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.83356404304504</v>
+        <v>1.83356392383575</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.82918798923492</v>
+        <v>1.82918775081635</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1597" t="n">
-        <v>1.76354742050171</v>
+        <v>1.76354730129242</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>2</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.75041913986206</v>
+        <v>1.75041902065277</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>2</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.75041913986206</v>
+        <v>1.75041902065277</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.75041913986206</v>
+        <v>1.75041902065277</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.75479531288147</v>
+        <v>1.75479519367218</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.79855573177338</v>
+        <v>1.79855561256409</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>2</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.75041913986206</v>
+        <v>1.75041902065277</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>1.59399998188019</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>16013</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>1.57799994945526</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>1.59399998188019</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>1.57799994945526</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>1.57799994945526</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>2.69898533821106</v>
+        <v>2.69898557662964</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G5" t="n">
-        <v>2.68630051612854</v>
+        <v>2.68630075454712</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G6" t="n">
-        <v>2.75958919525146</v>
+        <v>2.75958943367004</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G7" t="n">
-        <v>2.74690461158752</v>
+        <v>2.7469048500061</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8187837600708</v>
+        <v>2.81878399848938</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G9" t="n">
-        <v>2.71730709075928</v>
+        <v>2.71730756759644</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4875762462616</v>
+        <v>2.48757672309875</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>2.43824815750122</v>
+        <v>2.43824791908264</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.50167036056519</v>
+        <v>2.50167059898376</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>2.45234179496765</v>
+        <v>2.45234203338623</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.25</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29026174545288</v>
+        <v>2.29026198387146</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G20" t="n">
-        <v>2.29730892181396</v>
+        <v>2.29730868339539</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G21" t="n">
-        <v>2.39455628395081</v>
+        <v>2.39455652236938</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G22" t="n">
-        <v>2.29871821403503</v>
+        <v>2.29871797561646</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G24" t="n">
-        <v>1.97455775737762</v>
+        <v>1.97455787658691</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G25" t="n">
-        <v>1.87449109554291</v>
+        <v>1.87449133396149</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G26" t="n">
-        <v>1.86885380744934</v>
+        <v>1.86885356903076</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G27" t="n">
-        <v>1.72650504112244</v>
+        <v>1.72650516033173</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G28" t="n">
-        <v>1.71100163459778</v>
+        <v>1.71100151538849</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G29" t="n">
-        <v>1.8603972196579</v>
+        <v>1.86039733886719</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G31" t="n">
-        <v>1.8773101568222</v>
+        <v>1.87730979919434</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G32" t="n">
-        <v>1.94777929782867</v>
+        <v>1.94777941703796</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G34" t="n">
-        <v>2.07039642333984</v>
+        <v>2.070396900177</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G36" t="n">
-        <v>2.09294700622559</v>
+        <v>2.09294676780701</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G37" t="n">
-        <v>2.15918827056885</v>
+        <v>2.15918850898743</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G38" t="n">
-        <v>2.16059756278992</v>
+        <v>2.1605978012085</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G39" t="n">
-        <v>2.04784607887268</v>
+        <v>2.04784631729126</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>2.05771231651306</v>
+        <v>2.05771255493164</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G42" t="n">
-        <v>2.06334972381592</v>
+        <v>2.0633499622345</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G44" t="n">
-        <v>2.08730936050415</v>
+        <v>2.08730912208557</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G47" t="n">
-        <v>2.1493227481842</v>
+        <v>2.14932250976562</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>2.12818169593811</v>
+        <v>2.12818193435669</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G53" t="n">
-        <v>2.27053046226501</v>
+        <v>2.27053022384644</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G55" t="n">
-        <v>2.1859667301178</v>
+        <v>2.18596696853638</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G56" t="n">
-        <v>2.17891979217529</v>
+        <v>2.17891955375671</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G57" t="n">
-        <v>2.20146989822388</v>
+        <v>2.20147013664246</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G58" t="n">
-        <v>2.23670530319214</v>
+        <v>2.2367045879364</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G61" t="n">
-        <v>2.18314814567566</v>
+        <v>2.18314790725708</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>2.12818169593811</v>
+        <v>2.12818193435669</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G63" t="n">
-        <v>1.97737658023834</v>
+        <v>1.97737669944763</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G66" t="n">
-        <v>1.94496071338654</v>
+        <v>1.94496059417725</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.71600008010864</v>
       </c>
       <c r="G68" t="n">
-        <v>1.9139541387558</v>
+        <v>1.91395425796509</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.97455775737762</v>
+        <v>1.97455787658691</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>1.92382037639618</v>
+        <v>1.92381978034973</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G73" t="n">
-        <v>2.00838351249695</v>
+        <v>2.00838327407837</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G79" t="n">
-        <v>2.18032908439636</v>
+        <v>2.18032932281494</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G82" t="n">
-        <v>2.05771231651306</v>
+        <v>2.05771255493164</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G85" t="n">
-        <v>1.9491890668869</v>
+        <v>1.94918882846832</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>1.97314846515656</v>
+        <v>1.97314858436584</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G87" t="n">
-        <v>1.95623600482941</v>
+        <v>1.9562361240387</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G88" t="n">
-        <v>1.89845085144043</v>
+        <v>1.89845097064972</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G89" t="n">
-        <v>1.86321651935577</v>
+        <v>1.86321640014648</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>1.74024832248688</v>
+        <v>1.74024820327759</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G93" t="n">
-        <v>1.68559563159943</v>
+        <v>1.68559575080872</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G95" t="n">
-        <v>1.6122465133667</v>
+        <v>1.61224663257599</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62662875652313</v>
+        <v>1.62662851810455</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G97" t="n">
-        <v>1.63957262039185</v>
+        <v>1.63957250118256</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.60361707210541</v>
+        <v>1.6036171913147</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.60361707210541</v>
+        <v>1.6036171913147</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G100" t="n">
-        <v>1.63957262039185</v>
+        <v>1.63957250118256</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G102" t="n">
-        <v>1.78914737701416</v>
+        <v>1.78914749622345</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G103" t="n">
-        <v>1.86249709129333</v>
+        <v>1.86249685287476</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G104" t="n">
-        <v>1.83373260498047</v>
+        <v>1.83373248577118</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G105" t="n">
-        <v>1.86249709129333</v>
+        <v>1.86249685287476</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G106" t="n">
-        <v>1.84092378616333</v>
+        <v>1.84092354774475</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>1.81215929985046</v>
+        <v>1.81215918064117</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>1.8265415430069</v>
+        <v>1.82654142379761</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G109" t="n">
-        <v>1.79490041732788</v>
+        <v>1.79490053653717</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G110" t="n">
-        <v>1.83517098426819</v>
+        <v>1.8351708650589</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>1.80640625953674</v>
+        <v>1.80640637874603</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G113" t="n">
-        <v>1.80496823787689</v>
+        <v>1.80496835708618</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G115" t="n">
-        <v>1.73305714130402</v>
+        <v>1.73305702209473</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G116" t="n">
-        <v>1.72011303901672</v>
+        <v>1.72011291980743</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G117" t="n">
-        <v>1.73881006240845</v>
+        <v>1.73881018161774</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G118" t="n">
-        <v>1.6338198184967</v>
+        <v>1.63381969928741</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G119" t="n">
-        <v>1.68559563159943</v>
+        <v>1.68559575080872</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G120" t="n">
-        <v>1.75606846809387</v>
+        <v>1.75606834888458</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>1.81215929985046</v>
+        <v>1.81215918064117</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G124" t="n">
-        <v>1.6122465133667</v>
+        <v>1.61224663257599</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G126" t="n">
-        <v>1.53026783466339</v>
+        <v>1.53026759624481</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G127" t="n">
-        <v>1.49431240558624</v>
+        <v>1.49431228637695</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G129" t="n">
-        <v>1.47561526298523</v>
+        <v>1.47561550140381</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G130" t="n">
-        <v>1.49287390708923</v>
+        <v>1.49287402629852</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G131" t="n">
-        <v>1.49862706661224</v>
+        <v>1.49862694740295</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2</v>
       </c>
       <c r="G132" t="n">
-        <v>1.43822157382965</v>
+        <v>1.43822145462036</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G133" t="n">
-        <v>1.5086944103241</v>
+        <v>1.50869452953339</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G136" t="n">
-        <v>1.63238143920898</v>
+        <v>1.63238155841827</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G137" t="n">
-        <v>1.6338198184967</v>
+        <v>1.63381969928741</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G138" t="n">
-        <v>1.6539546251297</v>
+        <v>1.65395486354828</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G141" t="n">
-        <v>1.6122465133667</v>
+        <v>1.61224663257599</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.25</v>
       </c>
       <c r="G142" t="n">
-        <v>1.61799943447113</v>
+        <v>1.61799919605255</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.25</v>
       </c>
       <c r="G143" t="n">
-        <v>1.61799943447113</v>
+        <v>1.61799919605255</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G144" t="n">
-        <v>1.56190848350525</v>
+        <v>1.56190860271454</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G145" t="n">
-        <v>1.51300919055939</v>
+        <v>1.5130090713501</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G147" t="n">
-        <v>1.56766164302826</v>
+        <v>1.56766152381897</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G148" t="n">
-        <v>1.48855924606323</v>
+        <v>1.48855936527252</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G150" t="n">
-        <v>1.48855924606323</v>
+        <v>1.48855936527252</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G152" t="n">
-        <v>1.3375461101532</v>
+        <v>1.33754599094391</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G160" t="n">
-        <v>1.53314411640167</v>
+        <v>1.53314423561096</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G164" t="n">
-        <v>1.51732361316681</v>
+        <v>1.51732385158539</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G165" t="n">
-        <v>1.53602075576782</v>
+        <v>1.53602051734924</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G166" t="n">
-        <v>1.52595317363739</v>
+        <v>1.5259530544281</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G167" t="n">
-        <v>1.54608798027039</v>
+        <v>1.54608833789825</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G168" t="n">
-        <v>1.52307677268982</v>
+        <v>1.52307665348053</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G171" t="n">
-        <v>1.5086944103241</v>
+        <v>1.50869452953339</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G173" t="n">
-        <v>1.55759394168854</v>
+        <v>1.55759382247925</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G176" t="n">
-        <v>1.55471742153168</v>
+        <v>1.55471765995026</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G180" t="n">
-        <v>1.49287390708923</v>
+        <v>1.49287402629852</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G181" t="n">
-        <v>1.49862706661224</v>
+        <v>1.49862694740295</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G183" t="n">
-        <v>1.45979487895966</v>
+        <v>1.45979499816895</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G184" t="n">
-        <v>1.48855924606323</v>
+        <v>1.48855936527252</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G185" t="n">
-        <v>1.47705364227295</v>
+        <v>1.47705340385437</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G186" t="n">
-        <v>1.48855924606323</v>
+        <v>1.48855936527252</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G187" t="n">
-        <v>1.48280644416809</v>
+        <v>1.48280656337738</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G189" t="n">
-        <v>1.45979487895966</v>
+        <v>1.45979499816895</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G191" t="n">
-        <v>1.48424458503723</v>
+        <v>1.48424470424652</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G198" t="n">
-        <v>1.60936999320984</v>
+        <v>1.60937011241913</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.25</v>
       </c>
       <c r="G199" t="n">
-        <v>1.61799943447113</v>
+        <v>1.61799919605255</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>1.67552781105042</v>
+        <v>1.67552828788757</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G205" t="n">
-        <v>1.70429265499115</v>
+        <v>1.70429253578186</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G207" t="n">
-        <v>1.73161900043488</v>
+        <v>1.73161864280701</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G208" t="n">
-        <v>1.73449540138245</v>
+        <v>1.73449516296387</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>1.74743938446045</v>
+        <v>1.74743914604187</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G210" t="n">
-        <v>1.77332723140717</v>
+        <v>1.77332735061646</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G211" t="n">
-        <v>1.75606846809387</v>
+        <v>1.75606834888458</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>1.74743938446045</v>
+        <v>1.74743914604187</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G214" t="n">
-        <v>1.71867489814758</v>
+        <v>1.71867477893829</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>1.67552781105042</v>
+        <v>1.67552828788757</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G216" t="n">
-        <v>1.58348190784454</v>
+        <v>1.58348178863525</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G217" t="n">
-        <v>1.55327928066254</v>
+        <v>1.55327939987183</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G221" t="n">
-        <v>1.42743492126465</v>
+        <v>1.42743480205536</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G223" t="n">
-        <v>1.42383944988251</v>
+        <v>1.42383933067322</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>1.40586173534393</v>
+        <v>1.40586149692535</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G225" t="n">
-        <v>1.45691859722137</v>
+        <v>1.45691847801208</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G229" t="n">
-        <v>1.3375461101532</v>
+        <v>1.33754599094391</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G231" t="n">
-        <v>1.3375461101532</v>
+        <v>1.33754599094391</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G233" t="n">
-        <v>1.33323132991791</v>
+        <v>1.3332314491272</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G234" t="n">
-        <v>1.29799497127533</v>
+        <v>1.29799485206604</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G237" t="n">
-        <v>1.34257984161377</v>
+        <v>1.34257972240448</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G238" t="n">
-        <v>1.38069260120392</v>
+        <v>1.3806928396225</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G240" t="n">
-        <v>1.4022661447525</v>
+        <v>1.40226590633392</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G245" t="n">
-        <v>1.48855924606323</v>
+        <v>1.48855936527252</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G246" t="n">
-        <v>1.45979487895966</v>
+        <v>1.45979499816895</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G247" t="n">
-        <v>1.55327928066254</v>
+        <v>1.55327939987183</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G248" t="n">
-        <v>1.53602075576782</v>
+        <v>1.53602051734924</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G249" t="n">
-        <v>1.54177367687225</v>
+        <v>1.54177355766296</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G250" t="n">
-        <v>1.54465007781982</v>
+        <v>1.54464983940125</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G251" t="n">
-        <v>1.51732361316681</v>
+        <v>1.51732385158539</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G252" t="n">
-        <v>1.54608798027039</v>
+        <v>1.54608833789825</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G253" t="n">
-        <v>1.56190848350525</v>
+        <v>1.56190860271454</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G256" t="n">
-        <v>1.55759394168854</v>
+        <v>1.55759382247925</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G257" t="n">
-        <v>1.58204388618469</v>
+        <v>1.58204364776611</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G258" t="n">
-        <v>1.60649347305298</v>
+        <v>1.60649359226227</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G259" t="n">
-        <v>1.64388751983643</v>
+        <v>1.64388728141785</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G261" t="n">
-        <v>1.65826940536499</v>
+        <v>1.65826952457428</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G262" t="n">
-        <v>1.66546046733856</v>
+        <v>1.66546070575714</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>1.66114580631256</v>
+        <v>1.66114568710327</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>1.66546046733856</v>
+        <v>1.66546070575714</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G266" t="n">
-        <v>1.67408978939056</v>
+        <v>1.67409014701843</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>1.69710147380829</v>
+        <v>1.69710159301758</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G268" t="n">
-        <v>1.72011303901672</v>
+        <v>1.72011291980743</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G269" t="n">
-        <v>1.72298943996429</v>
+        <v>1.722989320755</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G270" t="n">
-        <v>1.72442781925201</v>
+        <v>1.72442758083344</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G272" t="n">
-        <v>1.78483319282532</v>
+        <v>1.78483283519745</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G273" t="n">
-        <v>1.74168622493744</v>
+        <v>1.74168634414673</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G274" t="n">
-        <v>1.74887752532959</v>
+        <v>1.7488774061203</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>1.70429265499115</v>
+        <v>1.70429253578186</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>1.66114580631256</v>
+        <v>1.66114568710327</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G279" t="n">
-        <v>1.642449259758</v>
+        <v>1.64244890213013</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>1.70429265499115</v>
+        <v>1.70429253578186</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G282" t="n">
-        <v>1.71436011791229</v>
+        <v>1.714359998703</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.63957262039185</v>
+        <v>1.63957250118256</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G285" t="n">
-        <v>1.6539546251297</v>
+        <v>1.65395486354828</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>1.70429265499115</v>
+        <v>1.70429253578186</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G287" t="n">
-        <v>1.66833698749542</v>
+        <v>1.66833686828613</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G288" t="n">
-        <v>1.642449259758</v>
+        <v>1.64244890213013</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G289" t="n">
-        <v>1.65970778465271</v>
+        <v>1.65970766544342</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>1.63957262039185</v>
+        <v>1.63957250118256</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G291" t="n">
-        <v>1.63094329833984</v>
+        <v>1.63094317913055</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G293" t="n">
-        <v>1.5863584280014</v>
+        <v>1.58635830879211</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G294" t="n">
-        <v>1.51732361316681</v>
+        <v>1.51732385158539</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2</v>
       </c>
       <c r="G297" t="n">
-        <v>1.43822157382965</v>
+        <v>1.43822145462036</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G298" t="n">
-        <v>1.48280644416809</v>
+        <v>1.48280656337738</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G299" t="n">
-        <v>1.45979487895966</v>
+        <v>1.45979499816895</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G301" t="n">
-        <v>1.52163851261139</v>
+        <v>1.5216383934021</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G304" t="n">
-        <v>1.50150346755981</v>
+        <v>1.50150322914124</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G305" t="n">
-        <v>1.49718856811523</v>
+        <v>1.49718844890594</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G307" t="n">
-        <v>1.54465007781982</v>
+        <v>1.54464983940125</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G308" t="n">
-        <v>1.55903196334839</v>
+        <v>1.55903232097626</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>1.53889739513397</v>
+        <v>1.5388970375061</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G310" t="n">
-        <v>1.73305714130402</v>
+        <v>1.73305702209473</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>1.8265415430069</v>
+        <v>1.82654142379761</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G312" t="n">
-        <v>1.81503570079803</v>
+        <v>1.81503546237946</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>1.76901245117188</v>
+        <v>1.76901257038116</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G314" t="n">
-        <v>1.75750708580017</v>
+        <v>1.75750696659088</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G315" t="n">
-        <v>1.73305714130402</v>
+        <v>1.73305702209473</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>1.81215929985046</v>
+        <v>1.81215918064117</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>2.04946541786194</v>
+        <v>2.04946565628052</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G318" t="n">
-        <v>1.99049878120422</v>
+        <v>1.99049842357635</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G320" t="n">
-        <v>1.98043096065521</v>
+        <v>1.9804310798645</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G321" t="n">
-        <v>1.96604883670807</v>
+        <v>1.96604919433594</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G322" t="n">
-        <v>1.96317255496979</v>
+        <v>1.9631724357605</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G323" t="n">
-        <v>1.94303727149963</v>
+        <v>1.94303750991821</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G324" t="n">
-        <v>1.97467803955078</v>
+        <v>1.97467815876007</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G325" t="n">
-        <v>1.95885765552521</v>
+        <v>1.95885789394379</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G326" t="n">
-        <v>1.97036361694336</v>
+        <v>1.97036349773407</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.71199989318848</v>
       </c>
       <c r="G327" t="n">
-        <v>1.95022857189178</v>
+        <v>1.9502284526825</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>1.96317255496979</v>
+        <v>1.9631724357605</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G330" t="n">
-        <v>1.87400269508362</v>
+        <v>1.87400281429291</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G334" t="n">
-        <v>1.8135974407196</v>
+        <v>1.81359767913818</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G335" t="n">
-        <v>1.79058575630188</v>
+        <v>1.79058587551117</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G336" t="n">
-        <v>1.85386788845062</v>
+        <v>1.85386776924133</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G337" t="n">
-        <v>1.90852010250092</v>
+        <v>1.90851986408234</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G338" t="n">
-        <v>2.00488090515137</v>
+        <v>2.00488114356995</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G339" t="n">
-        <v>1.96748721599579</v>
+        <v>1.9674870967865</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G341" t="n">
-        <v>1.74586093425751</v>
+        <v>1.7458610534668</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G343" t="n">
-        <v>1.72954428195953</v>
+        <v>1.72954452037811</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G346" t="n">
-        <v>1.7161945104599</v>
+        <v>1.71619462966919</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G347" t="n">
-        <v>1.76514387130737</v>
+        <v>1.76514410972595</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G349" t="n">
-        <v>1.7147114276886</v>
+        <v>1.71471130847931</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G350" t="n">
-        <v>1.71322810649872</v>
+        <v>1.71322786808014</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G352" t="n">
-        <v>1.68652808666229</v>
+        <v>1.68652820587158</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G353" t="n">
-        <v>1.66279542446136</v>
+        <v>1.66279554367065</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G355" t="n">
-        <v>1.67911159992218</v>
+        <v>1.67911171913147</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G358" t="n">
-        <v>1.72509467601776</v>
+        <v>1.72509443759918</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G361" t="n">
-        <v>1.69246184825897</v>
+        <v>1.69246160984039</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="n">
-        <v>1.68207836151123</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G363" t="n">
-        <v>1.67911159992218</v>
+        <v>1.67911171913147</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G368" t="n">
-        <v>1.72212779521942</v>
+        <v>1.722128033638</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G371" t="n">
-        <v>1.70432817935944</v>
+        <v>1.70432806015015</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>1.69097828865051</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G373" t="n">
-        <v>1.68207836151123</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G374" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G375" t="n">
-        <v>1.74141097068787</v>
+        <v>1.74141120910645</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G376" t="n">
-        <v>1.69097828865051</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G381" t="n">
-        <v>1.71916139125824</v>
+        <v>1.71916127204895</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G382" t="n">
-        <v>1.73102784156799</v>
+        <v>1.73102796077728</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>1.75031101703644</v>
+        <v>1.75031077861786</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G385" t="n">
-        <v>1.75921070575714</v>
+        <v>1.75921082496643</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G386" t="n">
-        <v>1.75921070575714</v>
+        <v>1.75921082496643</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G387" t="n">
-        <v>1.7369612455368</v>
+        <v>1.73696112632751</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G388" t="n">
-        <v>1.71174454689026</v>
+        <v>1.71174466609955</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G393" t="n">
-        <v>1.7147114276886</v>
+        <v>1.71471130847931</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G394" t="n">
-        <v>1.7087779045105</v>
+        <v>1.70877802371979</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G396" t="n">
-        <v>1.72212779521942</v>
+        <v>1.722128033638</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G398" t="n">
-        <v>1.71322810649872</v>
+        <v>1.71322786808014</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G399" t="n">
-        <v>1.69097828865051</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G400" t="n">
-        <v>1.68949508666992</v>
+        <v>1.68949520587921</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G401" t="n">
-        <v>1.68504524230957</v>
+        <v>1.68504512310028</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G406" t="n">
-        <v>1.63312911987305</v>
+        <v>1.63312900066376</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>1.59456312656403</v>
+        <v>1.59456288814545</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G410" t="n">
-        <v>1.61087942123413</v>
+        <v>1.61087930202484</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G411" t="n">
-        <v>1.68207836151123</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G414" t="n">
-        <v>1.65686190128326</v>
+        <v>1.65686213970184</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G415" t="n">
-        <v>1.67466163635254</v>
+        <v>1.67466175556183</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G417" t="n">
-        <v>1.63312911987305</v>
+        <v>1.63312900066376</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G419" t="n">
-        <v>1.60494613647461</v>
+        <v>1.60494601726532</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G420" t="n">
-        <v>1.59752941131592</v>
+        <v>1.5975296497345</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G422" t="n">
-        <v>1.60197949409485</v>
+        <v>1.60197961330414</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>1.59456312656403</v>
+        <v>1.59456288814545</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G426" t="n">
-        <v>1.5589634180069</v>
+        <v>1.55896329879761</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G427" t="n">
-        <v>1.58269643783569</v>
+        <v>1.5826963186264</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G431" t="n">
-        <v>1.57824635505676</v>
+        <v>1.57824647426605</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G432" t="n">
-        <v>1.58121311664581</v>
+        <v>1.58121299743652</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G433" t="n">
-        <v>1.56786322593689</v>
+        <v>1.56786334514618</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>1.59456312656403</v>
+        <v>1.59456288814545</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G436" t="n">
-        <v>1.58121311664581</v>
+        <v>1.58121299743652</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G438" t="n">
-        <v>1.56192982196808</v>
+        <v>1.56192994117737</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G441" t="n">
-        <v>1.56637978553772</v>
+        <v>1.56637990474701</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G442" t="n">
-        <v>1.59307956695557</v>
+        <v>1.59307944774628</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G444" t="n">
-        <v>1.58566308021545</v>
+        <v>1.58566296100616</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G448" t="n">
-        <v>1.76217722892761</v>
+        <v>1.7621773481369</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G449" t="n">
-        <v>1.76217722892761</v>
+        <v>1.7621773481369</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G450" t="n">
-        <v>1.74882781505585</v>
+        <v>1.74882769584656</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G453" t="n">
-        <v>1.72509467601776</v>
+        <v>1.72509443759918</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G454" t="n">
-        <v>1.70432817935944</v>
+        <v>1.70432806015015</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G455" t="n">
-        <v>1.74437761306763</v>
+        <v>1.74437773227692</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G457" t="n">
-        <v>1.79629349708557</v>
+        <v>1.79629361629486</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G458" t="n">
-        <v>1.8318932056427</v>
+        <v>1.83189332485199</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>1.8393098115921</v>
+        <v>1.83930993080139</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G460" t="n">
-        <v>1.93720877170563</v>
+        <v>1.93720853328705</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.5</v>
       </c>
       <c r="G462" t="n">
-        <v>1.85414290428162</v>
+        <v>1.85414266586304</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G463" t="n">
-        <v>1.90605878829956</v>
+        <v>1.90605854988098</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.87490928173065</v>
+        <v>1.87490963935852</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G465" t="n">
-        <v>1.89122569561005</v>
+        <v>1.89122557640076</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G467" t="n">
-        <v>1.93572497367859</v>
+        <v>1.93572509288788</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G469" t="n">
-        <v>1.78887701034546</v>
+        <v>1.78887712955475</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G471" t="n">
-        <v>1.82892656326294</v>
+        <v>1.82892644405365</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G472" t="n">
-        <v>1.78887701034546</v>
+        <v>1.78887712955475</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G473" t="n">
-        <v>1.76514387130737</v>
+        <v>1.76514410972595</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G474" t="n">
-        <v>1.73102784156799</v>
+        <v>1.73102796077728</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G475" t="n">
-        <v>1.70729470252991</v>
+        <v>1.70729458332062</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G476" t="n">
-        <v>1.66279542446136</v>
+        <v>1.66279554367065</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G477" t="n">
-        <v>1.63757908344269</v>
+        <v>1.6375789642334</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G479" t="n">
-        <v>1.61977922916412</v>
+        <v>1.61977934837341</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G480" t="n">
-        <v>1.61829590797424</v>
+        <v>1.61829578876495</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G482" t="n">
-        <v>1.61681258678436</v>
+        <v>1.61681246757507</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G484" t="n">
-        <v>1.64796197414398</v>
+        <v>1.64796221256256</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G485" t="n">
-        <v>1.68652808666229</v>
+        <v>1.68652820587158</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G487" t="n">
-        <v>1.69097828865051</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G489" t="n">
-        <v>1.63757908344269</v>
+        <v>1.6375789642334</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G490" t="n">
-        <v>1.68207836151123</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G491" t="n">
-        <v>1.66724526882172</v>
+        <v>1.66724514961243</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G494" t="n">
-        <v>1.68652808666229</v>
+        <v>1.68652820587158</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G495" t="n">
-        <v>1.68949508666992</v>
+        <v>1.68949520587921</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G496" t="n">
-        <v>1.68949508666992</v>
+        <v>1.68949520587921</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G498" t="n">
-        <v>1.68949508666992</v>
+        <v>1.68949520587921</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G499" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.69097828865051</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G501" t="n">
-        <v>1.68207836151123</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G502" t="n">
-        <v>1.67466163635254</v>
+        <v>1.67466175556183</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G503" t="n">
-        <v>1.62867915630341</v>
+        <v>1.6286792755127</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G504" t="n">
-        <v>1.66724526882172</v>
+        <v>1.66724514961243</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.69097828865051</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G509" t="n">
-        <v>1.68504524230957</v>
+        <v>1.68504512310028</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G510" t="n">
-        <v>1.69542825222015</v>
+        <v>1.69542813301086</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G511" t="n">
-        <v>1.68207836151123</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G512" t="n">
-        <v>1.67466163635254</v>
+        <v>1.67466175556183</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G513" t="n">
-        <v>1.69097828865051</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G514" t="n">
-        <v>1.67985355854034</v>
+        <v>1.67985343933105</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>1.69097828865051</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G517" t="n">
-        <v>1.77256047725677</v>
+        <v>1.77256059646606</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G518" t="n">
-        <v>1.75031101703644</v>
+        <v>1.75031077861786</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G519" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.375</v>
       </c>
       <c r="G520" t="n">
-        <v>1.7614358663559</v>
+        <v>1.76143574714661</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76514387130737</v>
+        <v>1.76514410972595</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.74660265445709</v>
+        <v>1.74660241603851</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G525" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G527" t="n">
-        <v>1.78739380836487</v>
+        <v>1.78739368915558</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G528" t="n">
-        <v>1.77256047725677</v>
+        <v>1.77256059646606</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>1.79481029510498</v>
+        <v>1.79481053352356</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G531" t="n">
-        <v>1.82818472385406</v>
+        <v>1.82818496227264</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G532" t="n">
-        <v>1.77256047725677</v>
+        <v>1.77256059646606</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>1.74289417266846</v>
+        <v>1.74289405345917</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G534" t="n">
-        <v>1.70951998233795</v>
+        <v>1.70951986312866</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G536" t="n">
-        <v>1.69097828865051</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G538" t="n">
-        <v>1.69097828865051</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G542" t="n">
-        <v>1.62052094936371</v>
+        <v>1.620521068573</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>1.63906216621399</v>
+        <v>1.63906228542328</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G545" t="n">
-        <v>1.69468653202057</v>
+        <v>1.69468665122986</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G546" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G547" t="n">
-        <v>1.67243707180023</v>
+        <v>1.67243695259094</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G549" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G554" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>1.65018725395203</v>
+        <v>1.65018713474274</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G556" t="n">
-        <v>1.63535380363464</v>
+        <v>1.63535392284393</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>1.63535380363464</v>
+        <v>1.63535392284393</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G559" t="n">
-        <v>1.64647901058197</v>
+        <v>1.64647889137268</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G561" t="n">
-        <v>1.69468653202057</v>
+        <v>1.69468665122986</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G564" t="n">
-        <v>1.67243707180023</v>
+        <v>1.67243695259094</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G568" t="n">
-        <v>1.67243707180023</v>
+        <v>1.67243695259094</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>1.63906216621399</v>
+        <v>1.63906228542328</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G571" t="n">
-        <v>1.64647901058197</v>
+        <v>1.64647889137268</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G575" t="n">
-        <v>1.67243707180023</v>
+        <v>1.67243695259094</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G576" t="n">
-        <v>1.64647901058197</v>
+        <v>1.64647889137268</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G577" t="n">
-        <v>1.67985355854034</v>
+        <v>1.67985343933105</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>1.68726992607117</v>
+        <v>1.68727016448975</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>1.70210313796997</v>
+        <v>1.70210337638855</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G584" t="n">
-        <v>1.67243707180023</v>
+        <v>1.67243695259094</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G587" t="n">
-        <v>1.64647901058197</v>
+        <v>1.64647889137268</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G594" t="n">
-        <v>1.69097828865051</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G596" t="n">
-        <v>1.69468653202057</v>
+        <v>1.69468665122986</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>1.70210313796997</v>
+        <v>1.70210337638855</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.25</v>
       </c>
       <c r="G602" t="n">
-        <v>1.73369491100311</v>
+        <v>1.7336950302124</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>1.70287382602692</v>
+        <v>1.70287370681763</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>1.69902086257935</v>
+        <v>1.69902098178864</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G605" t="n">
-        <v>1.62967312335968</v>
+        <v>1.62967336177826</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G609" t="n">
-        <v>1.49791252613068</v>
+        <v>1.49791240692139</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G611" t="n">
-        <v>1.53489792346954</v>
+        <v>1.53489804267883</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G612" t="n">
-        <v>1.52102828025818</v>
+        <v>1.52102839946747</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G616" t="n">
-        <v>1.48404288291931</v>
+        <v>1.4840430021286</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G617" t="n">
-        <v>1.51332318782806</v>
+        <v>1.51332306861877</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G618" t="n">
-        <v>1.49791252613068</v>
+        <v>1.49791240692139</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G619" t="n">
-        <v>1.49174833297729</v>
+        <v>1.49174821376801</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G620" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G623" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G625" t="n">
-        <v>1.62196815013885</v>
+        <v>1.62196791172028</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>1.62196815013885</v>
+        <v>1.62196791172028</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G627" t="n">
-        <v>1.59499931335449</v>
+        <v>1.59499943256378</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G628" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>1.59114682674408</v>
+        <v>1.59114694595337</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G630" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.65664172172546</v>
+        <v>1.65664184093475</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G635" t="n">
-        <v>1.5757360458374</v>
+        <v>1.57573616504669</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>1.5603255033493</v>
+        <v>1.56032538414001</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>1.59499931335449</v>
+        <v>1.59499943256378</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G642" t="n">
-        <v>1.59499931335449</v>
+        <v>1.59499943256378</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>1.62196815013885</v>
+        <v>1.62196791172028</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G645" t="n">
-        <v>1.59885215759277</v>
+        <v>1.59885203838348</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>1.59499931335449</v>
+        <v>1.59499943256378</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G649" t="n">
-        <v>1.59499931335449</v>
+        <v>1.59499943256378</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G650" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G651" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G652" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G655" t="n">
-        <v>1.59114682674408</v>
+        <v>1.59114694595337</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G657" t="n">
-        <v>1.62967312335968</v>
+        <v>1.62967336177826</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G660" t="n">
-        <v>1.62196815013885</v>
+        <v>1.62196791172028</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G661" t="n">
-        <v>1.59114682674408</v>
+        <v>1.59114694595337</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G662" t="n">
-        <v>1.59114682674408</v>
+        <v>1.59114694595337</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G663" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G668" t="n">
-        <v>1.5641782283783</v>
+        <v>1.56417810916901</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G672" t="n">
-        <v>1.52102828025818</v>
+        <v>1.52102839946747</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G673" t="n">
-        <v>1.5641782283783</v>
+        <v>1.56417810916901</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G675" t="n">
-        <v>1.53489792346954</v>
+        <v>1.53489804267883</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>1.5757360458374</v>
+        <v>1.57573616504669</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>1.5603255033493</v>
+        <v>1.56032538414001</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G683" t="n">
-        <v>1.5641782283783</v>
+        <v>1.56417810916901</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G684" t="n">
-        <v>1.5757360458374</v>
+        <v>1.57573616504669</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G685" t="n">
-        <v>1.59114682674408</v>
+        <v>1.59114694595337</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G687" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G688" t="n">
-        <v>1.5641782283783</v>
+        <v>1.56417810916901</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>1.5641782283783</v>
+        <v>1.56417810916901</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G692" t="n">
-        <v>1.5757360458374</v>
+        <v>1.57573616504669</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>1.5757360458374</v>
+        <v>1.57573616504669</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>1.5757360458374</v>
+        <v>1.57573616504669</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G695" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G697" t="n">
-        <v>1.59114682674408</v>
+        <v>1.59114694595337</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>1.65664172172546</v>
+        <v>1.65664184093475</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G702" t="n">
-        <v>1.5641782283783</v>
+        <v>1.56417810916901</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G705" t="n">
-        <v>1.5641782283783</v>
+        <v>1.56417810916901</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G707" t="n">
-        <v>1.47479653358459</v>
+        <v>1.47479641437531</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G710" t="n">
-        <v>1.42548263072968</v>
+        <v>1.4254823923111</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G712" t="n">
-        <v>1.41777718067169</v>
+        <v>1.41777729988098</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G716" t="n">
-        <v>1.39157903194427</v>
+        <v>1.39157915115356</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G718" t="n">
-        <v>1.25442469120026</v>
+        <v>1.25442457199097</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G719" t="n">
-        <v>1.21281599998474</v>
+        <v>1.21281588077545</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G721" t="n">
-        <v>1.24209606647491</v>
+        <v>1.2420961856842</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G722" t="n">
-        <v>1.29911541938782</v>
+        <v>1.29911553859711</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G725" t="n">
-        <v>1.30990278720856</v>
+        <v>1.30990290641785</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G726" t="n">
-        <v>1.31144404411316</v>
+        <v>1.31144392490387</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G727" t="n">
-        <v>1.29295134544373</v>
+        <v>1.29295110702515</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G728" t="n">
-        <v>1.29911541938782</v>
+        <v>1.29911553859711</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G729" t="n">
-        <v>1.31144404411316</v>
+        <v>1.31144392490387</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G732" t="n">
-        <v>1.28370475769043</v>
+        <v>1.28370487689972</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G733" t="n">
-        <v>1.28062260150909</v>
+        <v>1.28062272071838</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G735" t="n">
-        <v>1.18353581428528</v>
+        <v>1.18353569507599</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G736" t="n">
-        <v>1.19278204441071</v>
+        <v>1.19278216362</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G737" t="n">
-        <v>1.19894635677338</v>
+        <v>1.19894647598267</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G739" t="n">
-        <v>1.14963245391846</v>
+        <v>1.14963233470917</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G740" t="n">
-        <v>1.13730382919312</v>
+        <v>1.1373039484024</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G741" t="n">
-        <v>1.13113975524902</v>
+        <v>1.13113963603973</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G745" t="n">
-        <v>1.27137625217438</v>
+        <v>1.27137637138367</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G747" t="n">
-        <v>1.24055516719818</v>
+        <v>1.24055504798889</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G748" t="n">
-        <v>1.23593199253082</v>
+        <v>1.23593187332153</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G749" t="n">
-        <v>1.27908158302307</v>
+        <v>1.27908170223236</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G750" t="n">
-        <v>1.24363720417023</v>
+        <v>1.24363708496094</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G751" t="n">
-        <v>1.26212990283966</v>
+        <v>1.26213002204895</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G752" t="n">
-        <v>1.22668564319611</v>
+        <v>1.22668540477753</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G753" t="n">
-        <v>1.20665168762207</v>
+        <v>1.20665156841278</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G756" t="n">
-        <v>1.15733766555786</v>
+        <v>1.15733754634857</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G758" t="n">
-        <v>1.09569525718689</v>
+        <v>1.09569537639618</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G759" t="n">
-        <v>1.10185933113098</v>
+        <v>1.10185945034027</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G761" t="n">
-        <v>1.07566130161285</v>
+        <v>1.07566154003143</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G763" t="n">
-        <v>1.10802352428436</v>
+        <v>1.10802376270294</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G766" t="n">
-        <v>1.15733766555786</v>
+        <v>1.15733754634857</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.5</v>
       </c>
       <c r="G768" t="n">
-        <v>1.15579664707184</v>
+        <v>1.15579652786255</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G769" t="n">
-        <v>1.16350209712982</v>
+        <v>1.16350197792053</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G770" t="n">
-        <v>1.15425562858582</v>
+        <v>1.15425550937653</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.5</v>
       </c>
       <c r="G771" t="n">
-        <v>1.15579664707184</v>
+        <v>1.15579652786255</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G774" t="n">
-        <v>1.14346814155579</v>
+        <v>1.14346826076508</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G775" t="n">
-        <v>1.14655041694641</v>
+        <v>1.14655029773712</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>1.5</v>
       </c>
       <c r="G777" t="n">
-        <v>1.15579664707184</v>
+        <v>1.15579652786255</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G778" t="n">
-        <v>1.14655041694641</v>
+        <v>1.14655029773712</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G779" t="n">
-        <v>1.13268065452576</v>
+        <v>1.13268077373505</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>1.12497544288635</v>
+        <v>1.12497532367706</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G781" t="n">
-        <v>1.13268065452576</v>
+        <v>1.13268077373505</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G783" t="n">
-        <v>1.10956490039825</v>
+        <v>1.10956478118896</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G784" t="n">
-        <v>1.10802352428436</v>
+        <v>1.10802376270294</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G786" t="n">
-        <v>1.07412040233612</v>
+        <v>1.07412028312683</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G787" t="n">
-        <v>1.06641507148743</v>
+        <v>1.06641495227814</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G788" t="n">
-        <v>1.06641507148743</v>
+        <v>1.06641495227814</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G789" t="n">
-        <v>1.13884496688843</v>
+        <v>1.13884508609772</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G792" t="n">
-        <v>1.15425562858582</v>
+        <v>1.15425550937653</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G793" t="n">
-        <v>1.17428946495056</v>
+        <v>1.17428934574127</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G796" t="n">
-        <v>1.22668564319611</v>
+        <v>1.22668540477753</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G797" t="n">
-        <v>1.24671924114227</v>
+        <v>1.24671947956085</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G798" t="n">
-        <v>1.23593199253082</v>
+        <v>1.23593187332153</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G799" t="n">
-        <v>1.24363720417023</v>
+        <v>1.24363708496094</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G800" t="n">
-        <v>1.24363720417023</v>
+        <v>1.24363708496094</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G801" t="n">
-        <v>1.24055516719818</v>
+        <v>1.24055504798889</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G804" t="n">
-        <v>1.24209606647491</v>
+        <v>1.2420961856842</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G808" t="n">
-        <v>1.28678691387177</v>
+        <v>1.28678679466248</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G809" t="n">
-        <v>1.27754044532776</v>
+        <v>1.27754056453705</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G810" t="n">
-        <v>1.24055516719818</v>
+        <v>1.24055504798889</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G813" t="n">
-        <v>1.16504287719727</v>
+        <v>1.16504299640656</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G814" t="n">
-        <v>1.16504287719727</v>
+        <v>1.16504299640656</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>1.17120718955994</v>
+        <v>1.17120730876923</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G816" t="n">
-        <v>1.16658413410187</v>
+        <v>1.16658425331116</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G817" t="n">
-        <v>1.16658413410187</v>
+        <v>1.16658425331116</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G818" t="n">
-        <v>1.16504287719727</v>
+        <v>1.16504299640656</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.5</v>
       </c>
       <c r="G819" t="n">
-        <v>1.15579664707184</v>
+        <v>1.15579652786255</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.17120718955994</v>
+        <v>1.17120730876923</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G822" t="n">
-        <v>1.17120718955994</v>
+        <v>1.17120730876923</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G823" t="n">
-        <v>1.14192700386047</v>
+        <v>1.14192712306976</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G825" t="n">
-        <v>1.15425562858582</v>
+        <v>1.15425550937653</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>1.5</v>
       </c>
       <c r="G826" t="n">
-        <v>1.15579664707184</v>
+        <v>1.15579652786255</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G827" t="n">
-        <v>1.17120718955994</v>
+        <v>1.17120730876923</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G828" t="n">
-        <v>1.14963245391846</v>
+        <v>1.14963233470917</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.5</v>
       </c>
       <c r="G829" t="n">
-        <v>1.15579664707184</v>
+        <v>1.15579652786255</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G830" t="n">
-        <v>1.15733766555786</v>
+        <v>1.15733754634857</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.5</v>
       </c>
       <c r="G831" t="n">
-        <v>1.15579664707184</v>
+        <v>1.15579652786255</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G833" t="n">
-        <v>1.16196084022522</v>
+        <v>1.16196095943451</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G836" t="n">
-        <v>1.27908158302307</v>
+        <v>1.27908170223236</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G837" t="n">
-        <v>1.29295134544373</v>
+        <v>1.29295110702515</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G840" t="n">
-        <v>1.29295134544373</v>
+        <v>1.29295110702515</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G841" t="n">
-        <v>1.28678691387177</v>
+        <v>1.28678679466248</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G843" t="n">
-        <v>1.27137625217438</v>
+        <v>1.27137637138367</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G844" t="n">
-        <v>1.28062260150909</v>
+        <v>1.28062272071838</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G845" t="n">
-        <v>1.28832805156708</v>
+        <v>1.28832793235779</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G846" t="n">
-        <v>1.29141008853912</v>
+        <v>1.29140996932983</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G850" t="n">
-        <v>1.26629853248596</v>
+        <v>1.26629865169525</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G851" t="n">
-        <v>1.24029004573822</v>
+        <v>1.24028992652893</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.5</v>
       </c>
       <c r="G852" t="n">
-        <v>1.21915793418884</v>
+        <v>1.21915781497955</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G853" t="n">
-        <v>1.22240900993347</v>
+        <v>1.22240889072418</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G856" t="n">
-        <v>1.11512303352356</v>
+        <v>1.11512315273285</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G858" t="n">
-        <v>1.11349761486053</v>
+        <v>1.11349749565125</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G859" t="n">
-        <v>1.0842376947403</v>
+        <v>1.08423781394958</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G868" t="n">
-        <v>1.0045862197876</v>
+        <v>1.00458610057831</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G869" t="n">
-        <v>1.01271378993988</v>
+        <v>1.01271390914917</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G870" t="n">
-        <v>1.03222036361694</v>
+        <v>1.03222024440765</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G871" t="n">
-        <v>1.00783729553223</v>
+        <v>1.00783717632294</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G872" t="n">
-        <v>0.976951897144318</v>
+        <v>0.976951837539673</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G874" t="n">
-        <v>0.972075223922729</v>
+        <v>0.972075164318085</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G875" t="n">
-        <v>0.95581978559494</v>
+        <v>0.955819845199585</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G876" t="n">
-        <v>0.936313271522522</v>
+        <v>0.936313152313232</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G877" t="n">
-        <v>0.911930084228516</v>
+        <v>0.91193014383316</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G879" t="n">
-        <v>0.928185522556305</v>
+        <v>0.92818558216095</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G880" t="n">
-        <v>0.924934387207031</v>
+        <v>0.924934506416321</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G881" t="n">
-        <v>0.936313271522522</v>
+        <v>0.936313152313232</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G883" t="n">
-        <v>0.95744526386261</v>
+        <v>0.957445323467255</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G885" t="n">
-        <v>0.933062255382538</v>
+        <v>0.933062195777893</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G886" t="n">
-        <v>0.95581978559494</v>
+        <v>0.955819845199585</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G890" t="n">
-        <v>0.976951897144318</v>
+        <v>0.976951837539673</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>1.03222036361694</v>
+        <v>1.03222024440765</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G894" t="n">
-        <v>1.04034793376923</v>
+        <v>1.04034805297852</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.25</v>
       </c>
       <c r="G895" t="n">
-        <v>1.01596486568451</v>
+        <v>1.0159649848938</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>1.25</v>
       </c>
       <c r="G897" t="n">
-        <v>1.01596486568451</v>
+        <v>1.0159649848938</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G898" t="n">
-        <v>1.01271378993988</v>
+        <v>1.01271390914917</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G899" t="n">
-        <v>0.976951897144318</v>
+        <v>0.976951837539673</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G900" t="n">
-        <v>0.994832813739777</v>
+        <v>0.994832873344421</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G901" t="n">
-        <v>0.981828331947327</v>
+        <v>0.981828391551971</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G902" t="n">
-        <v>1.01271378993988</v>
+        <v>1.01271390914917</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G903" t="n">
-        <v>0.991581797599792</v>
+        <v>0.991581678390503</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G907" t="n">
-        <v>1.03222036361694</v>
+        <v>1.03222024440765</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G908" t="n">
-        <v>1.02246713638306</v>
+        <v>1.02246701717377</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>1.25</v>
       </c>
       <c r="G909" t="n">
-        <v>1.01596486568451</v>
+        <v>1.0159649848938</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G910" t="n">
-        <v>1.00783729553223</v>
+        <v>1.00783717632294</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G915" t="n">
-        <v>1.00783729553223</v>
+        <v>1.00783717632294</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G916" t="n">
-        <v>0.986705124378204</v>
+        <v>0.986705005168915</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G917" t="n">
-        <v>1.00783729553223</v>
+        <v>1.00783717632294</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G920" t="n">
-        <v>0.952568709850311</v>
+        <v>0.952568650245667</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G921" t="n">
-        <v>0.920057773590088</v>
+        <v>0.920057833194733</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G922" t="n">
-        <v>0.928185522556305</v>
+        <v>0.92818558216095</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G923" t="n">
-        <v>0.954194307327271</v>
+        <v>0.954194247722626</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G926" t="n">
-        <v>0.981828331947327</v>
+        <v>0.981828391551971</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G927" t="n">
-        <v>0.978577375411987</v>
+        <v>0.978577435016632</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>0.975326418876648</v>
+        <v>0.975326359272003</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G929" t="n">
-        <v>0.973700821399689</v>
+        <v>0.973700761795044</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G930" t="n">
-        <v>0.972075223922729</v>
+        <v>0.972075164318085</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G932" t="n">
-        <v>0.980202972888947</v>
+        <v>0.980202913284302</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.25</v>
       </c>
       <c r="G935" t="n">
-        <v>1.01596486568451</v>
+        <v>1.0159649848938</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.04034793376923</v>
+        <v>1.04034805297852</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G938" t="n">
-        <v>1.09236550331116</v>
+        <v>1.09236538410187</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G940" t="n">
-        <v>1.17851936817169</v>
+        <v>1.1785192489624</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G944" t="n">
-        <v>1.17851936817169</v>
+        <v>1.1785192489624</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G945" t="n">
-        <v>1.21753239631653</v>
+        <v>1.21753227710724</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G954" t="n">
-        <v>1.13462960720062</v>
+        <v>1.13462972640991</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G955" t="n">
-        <v>1.12325084209442</v>
+        <v>1.12325072288513</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G960" t="n">
-        <v>1.11674869060516</v>
+        <v>1.11674857139587</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G961" t="n">
-        <v>1.13462960720062</v>
+        <v>1.13462972640991</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G963" t="n">
-        <v>1.17364275455475</v>
+        <v>1.17364263534546</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G964" t="n">
-        <v>1.16226375102997</v>
+        <v>1.16226387023926</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G968" t="n">
-        <v>1.18339598178864</v>
+        <v>1.18339586257935</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G969" t="n">
-        <v>1.18502151966095</v>
+        <v>1.18502140045166</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G970" t="n">
-        <v>1.17851936817169</v>
+        <v>1.1785192489624</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G972" t="n">
-        <v>1.1671404838562</v>
+        <v>1.16714036464691</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G975" t="n">
-        <v>1.25491976737976</v>
+        <v>1.25492000579834</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G978" t="n">
-        <v>1.38008666038513</v>
+        <v>1.38008677959442</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G981" t="n">
-        <v>1.38008666038513</v>
+        <v>1.38008677959442</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G984" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G988" t="n">
-        <v>1.49224925041199</v>
+        <v>1.49224936962128</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G989" t="n">
-        <v>1.50362813472748</v>
+        <v>1.50362801551819</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G993" t="n">
-        <v>1.52313446998596</v>
+        <v>1.52313458919525</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G995" t="n">
-        <v>1.52801120281219</v>
+        <v>1.52801132202148</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G996" t="n">
-        <v>1.50037693977356</v>
+        <v>1.50037682056427</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G997" t="n">
-        <v>1.50200247764587</v>
+        <v>1.50200259685516</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G998" t="n">
-        <v>1.45811295509338</v>
+        <v>1.45811283588409</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G999" t="n">
-        <v>1.45486176013947</v>
+        <v>1.45486164093018</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.48412144184113</v>
+        <v>1.48412156105042</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.51500689983368</v>
+        <v>1.51500678062439</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.50850462913513</v>
+        <v>1.50850450992584</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.55401992797852</v>
+        <v>1.55401980876923</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.60116076469421</v>
+        <v>1.60116064548492</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.58327960968018</v>
+        <v>1.58327972888947</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.58490526676178</v>
+        <v>1.58490538597107</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.54589223861694</v>
+        <v>1.54589211940765</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.50200247764587</v>
+        <v>1.50200259685516</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.46624052524567</v>
+        <v>1.46624064445496</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.46298933029175</v>
+        <v>1.46298944950104</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.46298933029175</v>
+        <v>1.46298944950104</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.48737275600433</v>
+        <v>1.48737263679504</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.45811295509338</v>
+        <v>1.45811283588409</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.46624052524567</v>
+        <v>1.46624064445496</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.48737275600433</v>
+        <v>1.48737263679504</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.45323622226715</v>
+        <v>1.45323610305786</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.37358450889587</v>
+        <v>1.37358462810516</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.43047857284546</v>
+        <v>1.43047869205475</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.48737275600433</v>
+        <v>1.48737263679504</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.49550032615662</v>
+        <v>1.49550044536591</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.50362813472748</v>
+        <v>1.50362801551819</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.5767776966095</v>
+        <v>1.57677757740021</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.58002865314484</v>
+        <v>1.58002853393555</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.5979095697403</v>
+        <v>1.59790945053101</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.68243777751923</v>
+        <v>1.68243789672852</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.49224925041199</v>
+        <v>1.49224936962128</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.45486176013947</v>
+        <v>1.45486164093018</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.31343936920166</v>
+        <v>1.31343948841095</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.978577375411987</v>
+        <v>0.978577435016632</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.97044974565506</v>
+        <v>0.970449686050415</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.897300183773041</v>
+        <v>0.897300124168396</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.902176856994629</v>
+        <v>0.902176797389984</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.817648589611053</v>
+        <v>0.817648649215698</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.845282793045044</v>
+        <v>0.845282733440399</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.94281542301178</v>
+        <v>0.942815482616425</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.879419267177582</v>
+        <v>0.879419207572937</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.921683251857758</v>
+        <v>0.921683311462402</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.25</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.01596486568451</v>
+        <v>1.0159649848938</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.01921582221985</v>
+        <v>1.01921606063843</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.978577375411987</v>
+        <v>0.978577435016632</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.996458411216736</v>
+        <v>0.996458351612091</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.04685032367706</v>
+        <v>1.04685020446777</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.25</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.01596486568451</v>
+        <v>1.0159649848938</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.996458411216736</v>
+        <v>0.996458351612091</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.978577375411987</v>
+        <v>0.978577435016632</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.02246713638306</v>
+        <v>1.02246701717377</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.04522466659546</v>
+        <v>1.04522478580475</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.08098673820496</v>
+        <v>1.08098661899567</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.08098673820496</v>
+        <v>1.08098661899567</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.05497789382935</v>
+        <v>1.05497801303864</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.04034793376923</v>
+        <v>1.04034805297852</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.0289694070816</v>
+        <v>1.02896928787231</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.01433932781219</v>
+        <v>1.01433944702148</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.980202972888947</v>
+        <v>0.980202913284302</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.980202972888947</v>
+        <v>0.980202913284302</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.01271378993988</v>
+        <v>1.01271390914917</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.97044974565506</v>
+        <v>0.970449686050415</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.95907074213028</v>
+        <v>0.959070920944214</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.97044974565506</v>
+        <v>0.970449686050415</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.975326418876648</v>
+        <v>0.975326359272003</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.999709486961365</v>
+        <v>0.99970954656601</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.03222036361694</v>
+        <v>1.03222024440765</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.05660355091095</v>
+        <v>1.05660343170166</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.11512303352356</v>
+        <v>1.11512315273285</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.13950610160828</v>
+        <v>1.13950622081757</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.15576171875</v>
+        <v>1.15576183795929</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.1898980140686</v>
+        <v>1.18989813327789</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.2240344285965</v>
+        <v>1.22403454780579</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.23866450786591</v>
+        <v>1.23866438865662</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.29068183898926</v>
+        <v>1.29068195819855</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.21915793418884</v>
+        <v>1.21915781497955</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.19965124130249</v>
+        <v>1.19965136051178</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.11349761486053</v>
+        <v>1.11349749565125</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.09886765480042</v>
+        <v>1.0988677740097</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.09886765480042</v>
+        <v>1.0988677740097</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.06798243522644</v>
+        <v>1.06798231601715</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.04522466659546</v>
+        <v>1.04522478580475</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.18502151966095</v>
+        <v>1.18502140045166</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.18339598178864</v>
+        <v>1.18339586257935</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.23053669929504</v>
+        <v>1.23053681850433</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.2597963809967</v>
+        <v>1.25979650020599</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.27930307388306</v>
+        <v>1.27930295467377</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.3410736322403</v>
+        <v>1.34107375144958</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.43047857284546</v>
+        <v>1.43047869205475</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.44998514652252</v>
+        <v>1.44998502731323</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.46298933029175</v>
+        <v>1.46298944950104</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.42722749710083</v>
+        <v>1.42722761631012</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.41422319412231</v>
+        <v>1.41422307491302</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.37358450889587</v>
+        <v>1.37358462810516</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.41422319412231</v>
+        <v>1.41422307491302</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.43860626220703</v>
+        <v>1.43860638141632</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.44185733795166</v>
+        <v>1.44185757637024</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.4467339515686</v>
+        <v>1.44673407077789</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.52313446998596</v>
+        <v>1.52313458919525</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.55401992797852</v>
+        <v>1.55401980876923</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.48412144184113</v>
+        <v>1.48412156105042</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.45811295509338</v>
+        <v>1.45811283588409</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.50525367259979</v>
+        <v>1.5052535533905</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.48412144184113</v>
+        <v>1.48412156105042</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.45323622226715</v>
+        <v>1.45323610305786</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.41584861278534</v>
+        <v>1.41584873199463</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.43047857284546</v>
+        <v>1.43047869205475</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.76400005817413</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.43372964859009</v>
+        <v>1.43372976779938</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.43698084354401</v>
+        <v>1.43698072433472</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.32806932926178</v>
+        <v>1.32806921005249</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.31994152069092</v>
+        <v>1.31994163990021</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.35082685947418</v>
+        <v>1.35082697868347</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.36383128166199</v>
+        <v>1.3638311624527</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.34432470798492</v>
+        <v>1.34432482719421</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.37033343315125</v>
+        <v>1.37033355236053</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.35895478725433</v>
+        <v>1.35895466804504</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.38658881187439</v>
+        <v>1.38658893108368</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.29718387126923</v>
+        <v>1.29718399047852</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.25004315376282</v>
+        <v>1.25004327297211</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.15088498592377</v>
+        <v>1.15088510513306</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.24191546440125</v>
+        <v>1.24191558361053</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.25491976737976</v>
+        <v>1.25492000579834</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.32806932926178</v>
+        <v>1.32806921005249</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.31994152069092</v>
+        <v>1.31994163990021</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.35082685947418</v>
+        <v>1.35082697868347</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.76400005817413</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.43372964859009</v>
+        <v>1.43372976779938</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.4467339515686</v>
+        <v>1.44673407077789</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.4467339515686</v>
+        <v>1.44673407077789</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.45486176013947</v>
+        <v>1.45486164093018</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.3898401260376</v>
+        <v>1.38984000682831</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.39146554470062</v>
+        <v>1.39146566390991</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.35082685947418</v>
+        <v>1.35082697868347</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.34432470798492</v>
+        <v>1.34432482719421</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.32969498634338</v>
+        <v>1.3296947479248</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.28417956829071</v>
+        <v>1.2841796875</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.35245251655579</v>
+        <v>1.35245263576508</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.3898401260376</v>
+        <v>1.38984000682831</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.40934658050537</v>
+        <v>1.40934646129608</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.42072534561157</v>
+        <v>1.42072546482086</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.3898401260376</v>
+        <v>1.38984000682831</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.38658881187439</v>
+        <v>1.38658893108368</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.40934658050537</v>
+        <v>1.40934646129608</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.37033343315125</v>
+        <v>1.37033355236053</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.3654568195343</v>
+        <v>1.36545670032501</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.41909992694855</v>
+        <v>1.41909968852997</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.54751789569855</v>
+        <v>1.54751777648926</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.54751789569855</v>
+        <v>1.54751777648926</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.56052207946777</v>
+        <v>1.56052196025848</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.52801120281219</v>
+        <v>1.52801132202148</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.50200247764587</v>
+        <v>1.50200259685516</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.46298933029175</v>
+        <v>1.46298944950104</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.49550032615662</v>
+        <v>1.49550044536591</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.47761929035187</v>
+        <v>1.47761940956116</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.46624052524567</v>
+        <v>1.46624064445496</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.49224925041199</v>
+        <v>1.49224936962128</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.60116076469421</v>
+        <v>1.60116064548492</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.58002865314484</v>
+        <v>1.58002853393555</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.62066733837128</v>
+        <v>1.62066721916199</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.58815634250641</v>
+        <v>1.5881564617157</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992690086365</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.7108850479126</v>
+        <v>1.71088480949402</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.67431008815765</v>
+        <v>1.67431020736694</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.63773560523987</v>
+        <v>1.63773548603058</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.58490526676178</v>
+        <v>1.58490538597107</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.58490526676178</v>
+        <v>1.58490538597107</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.6222927570343</v>
+        <v>1.62229287624359</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.69056558609009</v>
+        <v>1.6905654668808</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.7677788734436</v>
+        <v>1.76777899265289</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.67431008815765</v>
+        <v>1.67431020736694</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.68243777751923</v>
+        <v>1.68243789672852</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.69056558609009</v>
+        <v>1.6905654668808</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.69462954998016</v>
+        <v>1.69462943077087</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.69462954998016</v>
+        <v>1.69462943077087</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.6222927570343</v>
+        <v>1.62229287624359</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.69869315624237</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.69056558609009</v>
+        <v>1.6905654668808</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.69056558609009</v>
+        <v>1.6905654668808</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.68243777751923</v>
+        <v>1.68243789672852</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.68243777751923</v>
+        <v>1.68243789672852</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.69869315624237</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.68243777751923</v>
+        <v>1.68243789672852</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992690086365</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.67837405204773</v>
+        <v>1.67837417125702</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.67837405204773</v>
+        <v>1.67837417125702</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992690086365</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992690086365</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992690086365</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992690086365</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.67431008815765</v>
+        <v>1.67431020736694</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.69056558609009</v>
+        <v>1.6905654668808</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.69869315624237</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.75558745861053</v>
+        <v>1.75558733940125</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.7677788734436</v>
+        <v>1.76777899265289</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.75558745861053</v>
+        <v>1.75558733940125</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.7108850479126</v>
+        <v>1.71088480949402</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.69869315624237</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.68243777751923</v>
+        <v>1.68243789672852</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.69056558609009</v>
+        <v>1.6905654668808</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.69056558609009</v>
+        <v>1.6905654668808</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.73526811599731</v>
+        <v>1.73526799678802</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.69056558609009</v>
+        <v>1.6905654668808</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.68650186061859</v>
+        <v>1.6865017414093</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.69869315624237</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.68243777751923</v>
+        <v>1.68243789672852</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.70275712013245</v>
+        <v>1.70275723934174</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.63773560523987</v>
+        <v>1.63773548603058</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992690086365</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1409" t="n">
-        <v>1.58490526676178</v>
+        <v>1.58490538597107</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.73526811599731</v>
+        <v>1.73526799678802</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.73120439052582</v>
+        <v>1.73120427131653</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.73120439052582</v>
+        <v>1.73120427131653</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.69869315624237</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.73526811599731</v>
+        <v>1.73526799678802</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.75965118408203</v>
+        <v>1.75965130329132</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.77997052669525</v>
+        <v>1.77997064590454</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.79216182231903</v>
+        <v>1.79216206073761</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.92626941204071</v>
+        <v>1.92626953125</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.91814148426056</v>
+        <v>1.91814184188843</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.88563084602356</v>
+        <v>1.88563096523285</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.91001403331757</v>
+        <v>1.91001391410828</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.89375853538513</v>
+        <v>1.89375841617584</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.86124789714813</v>
+        <v>1.86124765872955</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>2.25</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.82873666286469</v>
+        <v>1.82873690128326</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>2.25</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.82873666286469</v>
+        <v>1.82873690128326</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.85718381404877</v>
+        <v>1.85718393325806</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.85718381404877</v>
+        <v>1.85718393325806</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>2.25</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.82873666286469</v>
+        <v>1.82873690128326</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.86124789714813</v>
+        <v>1.86124765872955</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.89375853538513</v>
+        <v>1.89375841617584</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.88156676292419</v>
+        <v>1.88156700134277</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.89375853538513</v>
+        <v>1.89375841617584</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>2.25</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.82873666286469</v>
+        <v>1.82873690128326</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.85718381404877</v>
+        <v>1.85718393325806</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.81248128414154</v>
+        <v>1.81248140335083</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.85718381404877</v>
+        <v>1.85718393325806</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.88563084602356</v>
+        <v>1.88563096523285</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.86124789714813</v>
+        <v>1.86124765872955</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1472" t="n">
-        <v>1.88156676292419</v>
+        <v>1.88156700134277</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1475" t="n">
-        <v>1.83280062675476</v>
+        <v>1.83280074596405</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1480" t="n">
-        <v>1.90595018863678</v>
+        <v>1.90595030784607</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.88156676292419</v>
+        <v>1.88156700134277</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.88156676292419</v>
+        <v>1.88156700134277</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.8409286737442</v>
+        <v>1.84092843532562</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.89375853538513</v>
+        <v>1.89375841617584</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>1.91001403331757</v>
+        <v>1.91001391410828</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.91001403331757</v>
+        <v>1.91001391410828</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.92983675003052</v>
+        <v>1.9298369884491</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.84669196605682</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1502" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.73641562461853</v>
+        <v>1.73641574382782</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.81605994701385</v>
+        <v>1.81605982780457</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.82918775081635</v>
+        <v>1.82918787002563</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.8204357624054</v>
+        <v>1.82043588161469</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.82918775081635</v>
+        <v>1.82918787002563</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.8204357624054</v>
+        <v>1.82043588161469</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.81605994701385</v>
+        <v>1.81605982780457</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1520" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.80293154716492</v>
+        <v>1.80293166637421</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.85106813907623</v>
+        <v>1.85106825828552</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419630050659</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.90358066558838</v>
+        <v>1.90358078479767</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419630050659</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419630050659</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.84669196605682</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>2.125</v>
       </c>
       <c r="G1535" t="n">
-        <v>1.85982036590576</v>
+        <v>1.85982024669647</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.84669196605682</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.8204357624054</v>
+        <v>1.82043588161469</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>2</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.75041902065277</v>
+        <v>1.75041913986206</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.84669196605682</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.82918775081635</v>
+        <v>1.82918787002563</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1554" t="n">
-        <v>1.80293154716492</v>
+        <v>1.80293166637421</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.85106813907623</v>
+        <v>1.85106825828552</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.84669196605682</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.89482855796814</v>
+        <v>1.89482879638672</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419630050659</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>2.125</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.85982036590576</v>
+        <v>1.85982024669647</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.80293154716492</v>
+        <v>1.80293166637421</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.72416281700134</v>
+        <v>1.72416293621063</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.71716117858887</v>
+        <v>1.71716105937958</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1569" t="n">
-        <v>1.70665860176086</v>
+        <v>1.70665872097015</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1570" t="n">
-        <v>1.64539396762848</v>
+        <v>1.64539408683777</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.51586282253265</v>
+        <v>1.51586294174194</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1574" t="n">
-        <v>1.62438893318176</v>
+        <v>1.62438881397247</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.58938050270081</v>
+        <v>1.5893806219101</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G1577" t="n">
-        <v>1.612135887146</v>
+        <v>1.61213600635529</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>1.95200002193451</v>
       </c>
       <c r="G1579" t="n">
-        <v>1.70840895175934</v>
+        <v>1.70840907096863</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.63139057159424</v>
+        <v>1.63139069080353</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.70665860176086</v>
+        <v>1.70665872097015</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.74166691303253</v>
+        <v>1.74166703224182</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.72766363620758</v>
+        <v>1.72766375541687</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.72766363620758</v>
+        <v>1.72766375541687</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.7311646938324</v>
+        <v>1.73116445541382</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.82918775081635</v>
+        <v>1.82918787002563</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>2</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.75041902065277</v>
+        <v>1.75041913986206</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>2</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.75041902065277</v>
+        <v>1.75041913986206</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.75041902065277</v>
+        <v>1.75041913986206</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.8204357624054</v>
+        <v>1.82043588161469</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>2</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.75041902065277</v>
+        <v>1.75041913986206</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.81932306289673</v>
+        <v>1.81932294368744</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.81932306289673</v>
+        <v>1.81932294368744</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.84200775623322</v>
+        <v>1.84200763702393</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.80389726161957</v>
+        <v>1.80389714241028</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.8329336643219</v>
+        <v>1.83293378353119</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1636" t="n">
-        <v>1.8329336643219</v>
+        <v>1.83293378353119</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.72767615318298</v>
+        <v>1.72767627239227</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1645" t="n">
-        <v>1.73312044143677</v>
+        <v>1.73312056064606</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.52260541915894</v>
+        <v>1.52260529994965</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.49356877803802</v>
+        <v>1.49356889724731</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1659" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.4227921962738</v>
+        <v>1.42279207706451</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.30301630496979</v>
+        <v>1.3030161857605</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.34294164180756</v>
+        <v>1.34294152259827</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.33023798465729</v>
+        <v>1.33023810386658</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1678" t="n">
-        <v>1.48449492454529</v>
+        <v>1.484494805336</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.46271753311157</v>
+        <v>1.46271741390228</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.44638431072235</v>
+        <v>1.44638442993164</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.46271753311157</v>
+        <v>1.46271741390228</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.46997654438019</v>
+        <v>1.46997666358948</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.41734790802002</v>
+        <v>1.41734778881073</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.38649642467499</v>
+        <v>1.38649654388428</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>1.5</v>
       </c>
       <c r="G1701" t="n">
-        <v>1.36108946800232</v>
+        <v>1.36108934879303</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>1.5</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.36108946800232</v>
+        <v>1.36108934879303</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>1.35599994659424</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.23042476177216</v>
+        <v>1.23042488098145</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.27760934829712</v>
+        <v>1.27760922908783</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.26127624511719</v>
+        <v>1.2612761259079</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.24312841892242</v>
+        <v>1.24312829971313</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.34657108783722</v>
+        <v>1.34657120704651</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.33023798465729</v>
+        <v>1.33023810386658</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.29031276702881</v>
+        <v>1.2903128862381</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.37923717498779</v>
+        <v>1.37923729419708</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.34475636482239</v>
+        <v>1.3447562456131</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.34294164180756</v>
+        <v>1.34294152259827</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.40101480484009</v>
+        <v>1.4010146856308</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.40101480484009</v>
+        <v>1.4010146856308</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.41734790802002</v>
+        <v>1.41734778881073</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>1.5</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.36108946800232</v>
+        <v>1.36108934879303</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.37742257118225</v>
+        <v>1.37742245197296</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.37742257118225</v>
+        <v>1.37742245197296</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.34657108783722</v>
+        <v>1.34657120704651</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.37923717498779</v>
+        <v>1.37923729419708</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1787" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.46271753311157</v>
+        <v>1.46271741390228</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.49356877803802</v>
+        <v>1.49356889724731</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.46997654438019</v>
+        <v>1.46997666358948</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.48449492454529</v>
+        <v>1.484494805336</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.6242333650589</v>
+        <v>1.62423324584961</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.62786293029785</v>
+        <v>1.62786304950714</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1814" t="n">
-        <v>1.48449492454529</v>
+        <v>1.484494805336</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1819" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.37742257118225</v>
+        <v>1.37742245197296</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.37923717498779</v>
+        <v>1.37923729419708</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1829" t="n">
-        <v>1.38286697864532</v>
+        <v>1.38286685943604</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.27397966384888</v>
+        <v>1.27397978305817</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.24675786495209</v>
+        <v>1.24675798416138</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1843" t="n">
-        <v>1.21409177780151</v>
+        <v>1.2140918970108</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.23949873447418</v>
+        <v>1.23949885368347</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.21409177780151</v>
+        <v>1.2140918970108</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.21409177780151</v>
+        <v>1.2140918970108</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>1.57799994945526</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>4292</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>1.59599995613098</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>1.59399998188019</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>1.59399998188019</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74831438064575</v>
+        <v>2.74831414222717</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>2.69898557662964</v>
+        <v>2.69898509979248</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74831438064575</v>
+        <v>2.74831414222717</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G5" t="n">
-        <v>2.68630075454712</v>
+        <v>2.68630123138428</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G6" t="n">
-        <v>2.75958943367004</v>
+        <v>2.75958919525146</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.81878399848938</v>
+        <v>2.8187837600708</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G9" t="n">
-        <v>2.71730756759644</v>
+        <v>2.71730732917786</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6073751449585</v>
+        <v>2.60737490653992</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G13" t="n">
-        <v>2.39314723014832</v>
+        <v>2.39314746856689</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.50167059898376</v>
+        <v>2.50167036056519</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>2.56368398666382</v>
+        <v>2.56368327140808</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>2.45234203338623</v>
+        <v>2.45234179496765</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.25</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29026198387146</v>
+        <v>2.2902615070343</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G20" t="n">
-        <v>2.29730868339539</v>
+        <v>2.29730892181396</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G24" t="n">
-        <v>1.97455787658691</v>
+        <v>1.97455823421478</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G25" t="n">
-        <v>1.87449133396149</v>
+        <v>1.8744912147522</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G26" t="n">
-        <v>1.86885356903076</v>
+        <v>1.86885368824005</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G28" t="n">
-        <v>1.71100151538849</v>
+        <v>1.71100187301636</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G29" t="n">
-        <v>1.86039733886719</v>
+        <v>1.86039745807648</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.5</v>
       </c>
       <c r="G30" t="n">
-        <v>1.76173973083496</v>
+        <v>1.76173996925354</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G31" t="n">
-        <v>1.87730979919434</v>
+        <v>1.87731027603149</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G33" t="n">
-        <v>2.03657150268555</v>
+        <v>2.03657126426697</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G35" t="n">
-        <v>2.05207467079163</v>
+        <v>2.05207443237305</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G37" t="n">
-        <v>2.15918850898743</v>
+        <v>2.15918827056885</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G38" t="n">
-        <v>2.1605978012085</v>
+        <v>2.16059732437134</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>2.05771255493164</v>
+        <v>2.05771207809448</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G42" t="n">
-        <v>2.0633499622345</v>
+        <v>2.06334972381592</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G43" t="n">
-        <v>2.07321548461914</v>
+        <v>2.07321524620056</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G44" t="n">
-        <v>2.08730912208557</v>
+        <v>2.08730936050415</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G45" t="n">
-        <v>2.13522863388062</v>
+        <v>2.13522887229919</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G46" t="n">
-        <v>2.1577787399292</v>
+        <v>2.15777897834778</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12113475799561</v>
+        <v>2.12113451957703</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>2.12818193435669</v>
+        <v>2.12818145751953</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G51" t="n">
-        <v>2.21274542808533</v>
+        <v>2.21274518966675</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G52" t="n">
-        <v>2.26348328590393</v>
+        <v>2.26348304748535</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G54" t="n">
-        <v>2.17469143867493</v>
+        <v>2.17469167709351</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G55" t="n">
-        <v>2.18596696853638</v>
+        <v>2.1859667301178</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G56" t="n">
-        <v>2.17891955375671</v>
+        <v>2.17891979217529</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G57" t="n">
-        <v>2.20147013664246</v>
+        <v>2.20147037506104</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G58" t="n">
-        <v>2.2367045879364</v>
+        <v>2.23670506477356</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>2.17751049995422</v>
+        <v>2.17751026153564</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G61" t="n">
-        <v>2.18314790725708</v>
+        <v>2.18314814567566</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>2.12818193435669</v>
+        <v>2.12818145751953</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G63" t="n">
-        <v>1.97737669944763</v>
+        <v>1.97737681865692</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>1.98724246025085</v>
+        <v>1.98724257946014</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G66" t="n">
-        <v>1.94496059417725</v>
+        <v>1.94496083259583</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G67" t="n">
-        <v>1.95482647418976</v>
+        <v>1.95482623577118</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G69" t="n">
-        <v>1.98724246025085</v>
+        <v>1.98724257946014</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.97455787658691</v>
+        <v>1.97455823421478</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>1.92381978034973</v>
+        <v>1.92382025718689</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>1.98019540309906</v>
+        <v>1.98019564151764</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G73" t="n">
-        <v>2.00838327407837</v>
+        <v>2.00838303565979</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>2.17046332359314</v>
+        <v>2.17046356201172</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G77" t="n">
-        <v>2.14791321754456</v>
+        <v>2.14791345596313</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G78" t="n">
-        <v>2.17751049995422</v>
+        <v>2.17751026153564</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G79" t="n">
-        <v>2.18032932281494</v>
+        <v>2.18032908439636</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G80" t="n">
-        <v>2.12113475799561</v>
+        <v>2.12113451957703</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G82" t="n">
-        <v>2.05771255493164</v>
+        <v>2.05771207809448</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G83" t="n">
-        <v>2.02670550346375</v>
+        <v>2.02670574188232</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G84" t="n">
-        <v>1.98724246025085</v>
+        <v>1.98724257946014</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G85" t="n">
-        <v>1.94918882846832</v>
+        <v>1.94918918609619</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G87" t="n">
-        <v>1.9562361240387</v>
+        <v>1.95623600482941</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G88" t="n">
-        <v>1.89845097064972</v>
+        <v>1.89845061302185</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G89" t="n">
-        <v>1.86321640014648</v>
+        <v>1.86321592330933</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.5</v>
       </c>
       <c r="G91" t="n">
-        <v>1.79777669906616</v>
+        <v>1.79777705669403</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>1.74024820327759</v>
+        <v>1.74024832248688</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G93" t="n">
-        <v>1.68559575080872</v>
+        <v>1.68559598922729</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G94" t="n">
-        <v>1.68128097057343</v>
+        <v>1.68128108978271</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G95" t="n">
-        <v>1.61224663257599</v>
+        <v>1.6122465133667</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62662851810455</v>
+        <v>1.62662887573242</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G97" t="n">
-        <v>1.63957250118256</v>
+        <v>1.63957262039185</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.6036171913147</v>
+        <v>1.60361695289612</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.6036171913147</v>
+        <v>1.60361695289612</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G100" t="n">
-        <v>1.63957250118256</v>
+        <v>1.63957262039185</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G102" t="n">
-        <v>1.78914749622345</v>
+        <v>1.78914761543274</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G104" t="n">
-        <v>1.83373248577118</v>
+        <v>1.8337322473526</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G106" t="n">
-        <v>1.84092354774475</v>
+        <v>1.84092342853546</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>1.82654142379761</v>
+        <v>1.82654130458832</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G109" t="n">
-        <v>1.79490053653717</v>
+        <v>1.79490089416504</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G110" t="n">
-        <v>1.8351708650589</v>
+        <v>1.83517062664032</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G111" t="n">
-        <v>1.8394855260849</v>
+        <v>1.83948564529419</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G113" t="n">
-        <v>1.80496835708618</v>
+        <v>1.8049681186676</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.5</v>
       </c>
       <c r="G114" t="n">
-        <v>1.79777669906616</v>
+        <v>1.79777705669403</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G115" t="n">
-        <v>1.73305702209473</v>
+        <v>1.73305714130402</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G117" t="n">
-        <v>1.73881018161774</v>
+        <v>1.73880994319916</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G119" t="n">
-        <v>1.68559575080872</v>
+        <v>1.68559598922729</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G120" t="n">
-        <v>1.75606834888458</v>
+        <v>1.75606846809387</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G121" t="n">
-        <v>1.7531920671463</v>
+        <v>1.75319230556488</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G123" t="n">
-        <v>1.83804726600647</v>
+        <v>1.83804714679718</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G124" t="n">
-        <v>1.61224663257599</v>
+        <v>1.6122465133667</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G126" t="n">
-        <v>1.53026759624481</v>
+        <v>1.5302677154541</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G127" t="n">
-        <v>1.49431228637695</v>
+        <v>1.49431216716766</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G130" t="n">
-        <v>1.49287402629852</v>
+        <v>1.49287390708923</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2</v>
       </c>
       <c r="G132" t="n">
-        <v>1.43822145462036</v>
+        <v>1.43822157382965</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G134" t="n">
-        <v>1.5561558008194</v>
+        <v>1.55615568161011</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G136" t="n">
-        <v>1.63238155841827</v>
+        <v>1.63238143920898</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G138" t="n">
-        <v>1.65395486354828</v>
+        <v>1.65395474433899</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G141" t="n">
-        <v>1.61224663257599</v>
+        <v>1.6122465133667</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.25</v>
       </c>
       <c r="G142" t="n">
-        <v>1.61799919605255</v>
+        <v>1.61799943447113</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.25</v>
       </c>
       <c r="G143" t="n">
-        <v>1.61799919605255</v>
+        <v>1.61799943447113</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G144" t="n">
-        <v>1.56190860271454</v>
+        <v>1.56190848350525</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G145" t="n">
-        <v>1.5130090713501</v>
+        <v>1.51300930976868</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G147" t="n">
-        <v>1.56766152381897</v>
+        <v>1.56766164302826</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G148" t="n">
-        <v>1.48855936527252</v>
+        <v>1.48855924606323</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G150" t="n">
-        <v>1.48855936527252</v>
+        <v>1.48855924606323</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39579403400421</v>
+        <v>1.39579391479492</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G154" t="n">
-        <v>1.42959225177765</v>
+        <v>1.42959237098694</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G155" t="n">
-        <v>1.43462610244751</v>
+        <v>1.43462598323822</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G160" t="n">
-        <v>1.53314423561096</v>
+        <v>1.53314411640167</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G161" t="n">
-        <v>1.50437986850739</v>
+        <v>1.50437998771667</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G162" t="n">
-        <v>1.50581800937653</v>
+        <v>1.50581812858582</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G164" t="n">
-        <v>1.51732385158539</v>
+        <v>1.5173237323761</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G165" t="n">
-        <v>1.53602051734924</v>
+        <v>1.53602075576782</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>1.51013255119324</v>
+        <v>1.51013267040253</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G170" t="n">
-        <v>1.51588559150696</v>
+        <v>1.51588547229767</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G173" t="n">
-        <v>1.55759382247925</v>
+        <v>1.55759394168854</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G174" t="n">
-        <v>1.5647851228714</v>
+        <v>1.56478524208069</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G175" t="n">
-        <v>1.54896473884583</v>
+        <v>1.54896461963654</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G176" t="n">
-        <v>1.55471765995026</v>
+        <v>1.55471742153168</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G178" t="n">
-        <v>1.54896473884583</v>
+        <v>1.54896461963654</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G179" t="n">
-        <v>1.50725615024567</v>
+        <v>1.50725626945496</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G180" t="n">
-        <v>1.49287402629852</v>
+        <v>1.49287390708923</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G182" t="n">
-        <v>1.4698623418808</v>
+        <v>1.46986222267151</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G184" t="n">
-        <v>1.48855936527252</v>
+        <v>1.48855924606323</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G185" t="n">
-        <v>1.47705340385437</v>
+        <v>1.47705352306366</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G186" t="n">
-        <v>1.48855936527252</v>
+        <v>1.48855924606323</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G187" t="n">
-        <v>1.48280656337738</v>
+        <v>1.48280644416809</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G190" t="n">
-        <v>1.4698623418808</v>
+        <v>1.46986222267151</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G191" t="n">
-        <v>1.48424470424652</v>
+        <v>1.48424458503723</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G193" t="n">
-        <v>1.4698623418808</v>
+        <v>1.46986222267151</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G197" t="n">
-        <v>1.54896473884583</v>
+        <v>1.54896461963654</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G198" t="n">
-        <v>1.60937011241913</v>
+        <v>1.60936975479126</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.25</v>
       </c>
       <c r="G199" t="n">
-        <v>1.61799919605255</v>
+        <v>1.61799943447113</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>1.67552828788757</v>
+        <v>1.6755279302597</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G204" t="n">
-        <v>1.68703389167786</v>
+        <v>1.68703413009644</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G206" t="n">
-        <v>1.72730398178101</v>
+        <v>1.72730386257172</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G207" t="n">
-        <v>1.73161864280701</v>
+        <v>1.73161888122559</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G210" t="n">
-        <v>1.77332735061646</v>
+        <v>1.77332723140717</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G211" t="n">
-        <v>1.75606834888458</v>
+        <v>1.75606846809387</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>1.67552828788757</v>
+        <v>1.6755279302597</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G216" t="n">
-        <v>1.58348178863525</v>
+        <v>1.58348190784454</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G217" t="n">
-        <v>1.55327939987183</v>
+        <v>1.55327928066254</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>1.51013255119324</v>
+        <v>1.51013267040253</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>1.51013255119324</v>
+        <v>1.51013267040253</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G221" t="n">
-        <v>1.42743480205536</v>
+        <v>1.42743492126465</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G223" t="n">
-        <v>1.42383933067322</v>
+        <v>1.42383944988251</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>1.40586149692535</v>
+        <v>1.40586173534393</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G226" t="n">
-        <v>1.39004123210907</v>
+        <v>1.39004111289978</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G227" t="n">
-        <v>1.41664826869965</v>
+        <v>1.41664814949036</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G228" t="n">
-        <v>1.39579403400421</v>
+        <v>1.39579391479492</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G230" t="n">
-        <v>1.35840022563934</v>
+        <v>1.35840034484863</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G234" t="n">
-        <v>1.29799485206604</v>
+        <v>1.29799497127533</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G237" t="n">
-        <v>1.34257972240448</v>
+        <v>1.34257984161377</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G240" t="n">
-        <v>1.40226590633392</v>
+        <v>1.4022661447525</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.95299994945526</v>
       </c>
       <c r="G241" t="n">
-        <v>1.40442335605621</v>
+        <v>1.40442323684692</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G242" t="n">
-        <v>1.48712122440338</v>
+        <v>1.48712110519409</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G245" t="n">
-        <v>1.48855936527252</v>
+        <v>1.48855924606323</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G247" t="n">
-        <v>1.55327939987183</v>
+        <v>1.55327928066254</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G248" t="n">
-        <v>1.53602051734924</v>
+        <v>1.53602075576782</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G250" t="n">
-        <v>1.54464983940125</v>
+        <v>1.54465007781982</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G251" t="n">
-        <v>1.51732385158539</v>
+        <v>1.5173237323761</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G253" t="n">
-        <v>1.56190860271454</v>
+        <v>1.56190848350525</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G256" t="n">
-        <v>1.55759382247925</v>
+        <v>1.55759394168854</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G257" t="n">
-        <v>1.58204364776611</v>
+        <v>1.5820437669754</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G258" t="n">
-        <v>1.60649359226227</v>
+        <v>1.60649347305298</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G259" t="n">
-        <v>1.64388728141785</v>
+        <v>1.64388740062714</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>1.64676380157471</v>
+        <v>1.64676356315613</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G262" t="n">
-        <v>1.66546070575714</v>
+        <v>1.66546034812927</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>1.66114568710327</v>
+        <v>1.66114580631256</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>1.66546070575714</v>
+        <v>1.66546034812927</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G265" t="n">
-        <v>1.65683114528656</v>
+        <v>1.65683102607727</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G266" t="n">
-        <v>1.67409014701843</v>
+        <v>1.67408990859985</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>1.69710159301758</v>
+        <v>1.697101354599</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G270" t="n">
-        <v>1.72442758083344</v>
+        <v>1.72442770004272</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G271" t="n">
-        <v>1.77476537227631</v>
+        <v>1.77476525306702</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G272" t="n">
-        <v>1.78483283519745</v>
+        <v>1.78483307361603</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G273" t="n">
-        <v>1.74168634414673</v>
+        <v>1.74168646335602</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>1.66114568710327</v>
+        <v>1.66114580631256</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G279" t="n">
-        <v>1.64244890213013</v>
+        <v>1.64244902133942</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G282" t="n">
-        <v>1.714359998703</v>
+        <v>1.71436023712158</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.63957250118256</v>
+        <v>1.63957262039185</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G285" t="n">
-        <v>1.65395486354828</v>
+        <v>1.65395474433899</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G287" t="n">
-        <v>1.66833686828613</v>
+        <v>1.66833698749542</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G288" t="n">
-        <v>1.64244890213013</v>
+        <v>1.64244902133942</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G289" t="n">
-        <v>1.65970766544342</v>
+        <v>1.65970778465271</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>1.63957250118256</v>
+        <v>1.63957262039185</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G292" t="n">
-        <v>1.62375211715698</v>
+        <v>1.62375199794769</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G293" t="n">
-        <v>1.58635830879211</v>
+        <v>1.58635854721069</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G294" t="n">
-        <v>1.51732385158539</v>
+        <v>1.5173237323761</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2</v>
       </c>
       <c r="G297" t="n">
-        <v>1.43822145462036</v>
+        <v>1.43822157382965</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G298" t="n">
-        <v>1.48280656337738</v>
+        <v>1.48280644416809</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>1.52451491355896</v>
+        <v>1.52451455593109</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>1.51013255119324</v>
+        <v>1.51013267040253</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G305" t="n">
-        <v>1.49718844890594</v>
+        <v>1.49718868732452</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G306" t="n">
-        <v>1.51157104969025</v>
+        <v>1.51157081127167</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G307" t="n">
-        <v>1.54464983940125</v>
+        <v>1.54465007781982</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>1.5388970375061</v>
+        <v>1.53889715671539</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G310" t="n">
-        <v>1.73305702209473</v>
+        <v>1.73305714130402</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>1.82654142379761</v>
+        <v>1.82654130458832</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G312" t="n">
-        <v>1.81503546237946</v>
+        <v>1.81503558158875</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>1.76901257038116</v>
+        <v>1.76901245117188</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G315" t="n">
-        <v>1.73305702209473</v>
+        <v>1.73305714130402</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G318" t="n">
-        <v>1.99049842357635</v>
+        <v>1.99049866199493</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>1.95166683197021</v>
+        <v>1.95166671276093</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G320" t="n">
-        <v>1.9804310798645</v>
+        <v>1.98043119907379</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G321" t="n">
-        <v>1.96604919433594</v>
+        <v>1.96604907512665</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G322" t="n">
-        <v>1.9631724357605</v>
+        <v>1.96317267417908</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G324" t="n">
-        <v>1.97467815876007</v>
+        <v>1.97467827796936</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G326" t="n">
-        <v>1.97036349773407</v>
+        <v>1.97036361694336</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.71199989318848</v>
       </c>
       <c r="G327" t="n">
-        <v>1.9502284526825</v>
+        <v>1.95022821426392</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>1.9631724357605</v>
+        <v>1.96317267417908</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G330" t="n">
-        <v>1.87400281429291</v>
+        <v>1.87400257587433</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G332" t="n">
-        <v>1.71004557609558</v>
+        <v>1.71004545688629</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G333" t="n">
-        <v>1.76182150840759</v>
+        <v>1.7618213891983</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G334" t="n">
-        <v>1.81359767913818</v>
+        <v>1.8135974407196</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G335" t="n">
-        <v>1.79058587551117</v>
+        <v>1.79058575630188</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G337" t="n">
-        <v>1.90851986408234</v>
+        <v>1.90852010250092</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G338" t="n">
-        <v>2.00488114356995</v>
+        <v>2.00488066673279</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G339" t="n">
-        <v>1.9674870967865</v>
+        <v>1.96748733520508</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.5</v>
       </c>
       <c r="G340" t="n">
-        <v>1.79777669906616</v>
+        <v>1.79777705669403</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G342" t="n">
-        <v>1.70136141777039</v>
+        <v>1.70136153697968</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G345" t="n">
-        <v>1.67762851715088</v>
+        <v>1.67762875556946</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G346" t="n">
-        <v>1.71619462966919</v>
+        <v>1.7161945104599</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G347" t="n">
-        <v>1.76514410972595</v>
+        <v>1.76514399051666</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G350" t="n">
-        <v>1.71322786808014</v>
+        <v>1.71322798728943</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G352" t="n">
-        <v>1.68652820587158</v>
+        <v>1.68652844429016</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G353" t="n">
-        <v>1.66279554367065</v>
+        <v>1.66279530525208</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G354" t="n">
-        <v>1.67169523239136</v>
+        <v>1.67169511318207</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G355" t="n">
-        <v>1.67911171913147</v>
+        <v>1.67911159992218</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G356" t="n">
-        <v>1.67762851715088</v>
+        <v>1.67762875556946</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G358" t="n">
-        <v>1.72509443759918</v>
+        <v>1.72509431838989</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G360" t="n">
-        <v>1.69394505023956</v>
+        <v>1.69394493103027</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G361" t="n">
-        <v>1.69246160984039</v>
+        <v>1.69246172904968</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207848072052</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G363" t="n">
-        <v>1.67911171913147</v>
+        <v>1.67911159992218</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>1.69839489459991</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G365" t="n">
-        <v>1.70284497737885</v>
+        <v>1.70284485816956</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G366" t="n">
-        <v>1.69839489459991</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>1.69839489459991</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G368" t="n">
-        <v>1.722128033638</v>
+        <v>1.72212791442871</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G370" t="n">
-        <v>1.70136141777039</v>
+        <v>1.70136153697968</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G371" t="n">
-        <v>1.70432806015015</v>
+        <v>1.70432817935944</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>1.69097816944122</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G373" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207848072052</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G374" t="n">
-        <v>1.75772738456726</v>
+        <v>1.75772750377655</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G375" t="n">
-        <v>1.74141120910645</v>
+        <v>1.74141108989716</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G376" t="n">
-        <v>1.69097816944122</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>1.72806131839752</v>
+        <v>1.72806096076965</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G378" t="n">
-        <v>1.67762851715088</v>
+        <v>1.67762875556946</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.68356168270111</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G381" t="n">
-        <v>1.71916127204895</v>
+        <v>1.71916139125824</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G382" t="n">
-        <v>1.73102796077728</v>
+        <v>1.73102784156799</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G383" t="n">
-        <v>1.72806131839752</v>
+        <v>1.72806096076965</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G387" t="n">
-        <v>1.73696112632751</v>
+        <v>1.73696100711823</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G388" t="n">
-        <v>1.71174466609955</v>
+        <v>1.71174478530884</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G389" t="n">
-        <v>1.70284497737885</v>
+        <v>1.70284485816956</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G390" t="n">
-        <v>1.69394505023956</v>
+        <v>1.69394493103027</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G391" t="n">
-        <v>1.69394505023956</v>
+        <v>1.69394493103027</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>1.69839489459991</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G394" t="n">
-        <v>1.70877802371979</v>
+        <v>1.7087779045105</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G396" t="n">
-        <v>1.722128033638</v>
+        <v>1.72212791442871</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G397" t="n">
-        <v>1.70136141777039</v>
+        <v>1.70136153697968</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G398" t="n">
-        <v>1.71322786808014</v>
+        <v>1.71322798728943</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G399" t="n">
-        <v>1.69097816944122</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G400" t="n">
-        <v>1.68949520587921</v>
+        <v>1.68949496746063</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G402" t="n">
-        <v>1.67762851715088</v>
+        <v>1.67762875556946</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>1.68356168270111</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G405" t="n">
-        <v>1.64351224899292</v>
+        <v>1.64351212978363</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G406" t="n">
-        <v>1.63312900066376</v>
+        <v>1.63312888145447</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>1.59456288814545</v>
+        <v>1.59456300735474</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G408" t="n">
-        <v>1.61384606361389</v>
+        <v>1.61384618282318</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G411" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207848072052</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>1.68356168270111</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G413" t="n">
-        <v>1.67762851715088</v>
+        <v>1.67762875556946</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G414" t="n">
-        <v>1.65686213970184</v>
+        <v>1.65686202049255</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G416" t="n">
-        <v>1.66576206684113</v>
+        <v>1.66576194763184</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G417" t="n">
-        <v>1.63312900066376</v>
+        <v>1.63312888145447</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G418" t="n">
-        <v>1.60346293449402</v>
+        <v>1.60346269607544</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G420" t="n">
-        <v>1.5975296497345</v>
+        <v>1.59752941131592</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G422" t="n">
-        <v>1.60197961330414</v>
+        <v>1.60197949409485</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>1.59456288814545</v>
+        <v>1.59456300735474</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G427" t="n">
-        <v>1.5826963186264</v>
+        <v>1.58269643783569</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G428" t="n">
-        <v>1.60049605369568</v>
+        <v>1.60049617290497</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G432" t="n">
-        <v>1.58121299743652</v>
+        <v>1.58121311664581</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G433" t="n">
-        <v>1.56786334514618</v>
+        <v>1.56786322593689</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>1.59456288814545</v>
+        <v>1.59456300735474</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G436" t="n">
-        <v>1.58121299743652</v>
+        <v>1.58121311664581</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>1.57231318950653</v>
+        <v>1.57231295108795</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G438" t="n">
-        <v>1.56192994117737</v>
+        <v>1.56192982196808</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>1.57231318950653</v>
+        <v>1.57231295108795</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G440" t="n">
-        <v>1.57231318950653</v>
+        <v>1.57231295108795</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G442" t="n">
-        <v>1.59307944774628</v>
+        <v>1.59307968616486</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G443" t="n">
-        <v>1.57379639148712</v>
+        <v>1.57379627227783</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G446" t="n">
-        <v>1.57972979545593</v>
+        <v>1.57972991466522</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G447" t="n">
-        <v>1.66576206684113</v>
+        <v>1.66576194763184</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>1.72806131839752</v>
+        <v>1.72806096076965</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G452" t="n">
-        <v>1.70136141777039</v>
+        <v>1.70136153697968</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G453" t="n">
-        <v>1.72509443759918</v>
+        <v>1.72509431838989</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G454" t="n">
-        <v>1.70432806015015</v>
+        <v>1.70432817935944</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G455" t="n">
-        <v>1.74437773227692</v>
+        <v>1.74437761306763</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G456" t="n">
-        <v>1.79332709312439</v>
+        <v>1.7933269739151</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G457" t="n">
-        <v>1.79629361629486</v>
+        <v>1.79629373550415</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G458" t="n">
-        <v>1.83189332485199</v>
+        <v>1.8318932056427</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>1.83930993080139</v>
+        <v>1.8393098115921</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G460" t="n">
-        <v>1.93720853328705</v>
+        <v>1.93720841407776</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G461" t="n">
-        <v>1.92089200019836</v>
+        <v>1.92089211940765</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.5</v>
       </c>
       <c r="G462" t="n">
-        <v>1.85414266586304</v>
+        <v>1.85414290428162</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G463" t="n">
-        <v>1.90605854988098</v>
+        <v>1.90605890750885</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.87490963935852</v>
+        <v>1.87490952014923</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G465" t="n">
-        <v>1.89122557640076</v>
+        <v>1.89122533798218</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G466" t="n">
-        <v>1.91199243068695</v>
+        <v>1.91199231147766</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G467" t="n">
-        <v>1.93572509288788</v>
+        <v>1.93572497367859</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G468" t="n">
-        <v>1.92089200019836</v>
+        <v>1.92089211940765</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G470" t="n">
-        <v>1.79332709312439</v>
+        <v>1.7933269739151</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G473" t="n">
-        <v>1.76514410972595</v>
+        <v>1.76514399051666</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G474" t="n">
-        <v>1.73102796077728</v>
+        <v>1.73102784156799</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G475" t="n">
-        <v>1.70729458332062</v>
+        <v>1.7072948217392</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G476" t="n">
-        <v>1.66279554367065</v>
+        <v>1.66279530525208</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G478" t="n">
-        <v>1.64054548740387</v>
+        <v>1.64054560661316</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G479" t="n">
-        <v>1.61977934837341</v>
+        <v>1.61977922916412</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G481" t="n">
-        <v>1.60049605369568</v>
+        <v>1.60049617290497</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G482" t="n">
-        <v>1.61681246757507</v>
+        <v>1.61681270599365</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G483" t="n">
-        <v>1.63164567947388</v>
+        <v>1.63164579868317</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G484" t="n">
-        <v>1.64796221256256</v>
+        <v>1.64796209335327</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G485" t="n">
-        <v>1.68652820587158</v>
+        <v>1.68652844429016</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G486" t="n">
-        <v>1.67021214962006</v>
+        <v>1.67021203041077</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G487" t="n">
-        <v>1.69097816944122</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.25</v>
       </c>
       <c r="G488" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872870922089</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G490" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207848072052</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G493" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131186485291</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G494" t="n">
-        <v>1.68652820587158</v>
+        <v>1.68652844429016</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G495" t="n">
-        <v>1.68949520587921</v>
+        <v>1.68949496746063</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G496" t="n">
-        <v>1.68949520587921</v>
+        <v>1.68949496746063</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.25</v>
       </c>
       <c r="G497" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872870922089</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G498" t="n">
-        <v>1.68949520587921</v>
+        <v>1.68949496746063</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G499" t="n">
-        <v>1.68356168270111</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.69097816944122</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G501" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207848072052</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G503" t="n">
-        <v>1.6286792755127</v>
+        <v>1.62867915630341</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G505" t="n">
-        <v>1.65834546089172</v>
+        <v>1.65834558010101</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G506" t="n">
-        <v>1.67169523239136</v>
+        <v>1.67169511318207</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.69097816944122</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>1.69839489459991</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G510" t="n">
-        <v>1.69542813301086</v>
+        <v>1.69542837142944</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G511" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207848072052</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G513" t="n">
-        <v>1.69097816944122</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>1.69097816944122</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G519" t="n">
-        <v>1.75772738456726</v>
+        <v>1.75772750377655</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.375</v>
       </c>
       <c r="G520" t="n">
-        <v>1.76143574714661</v>
+        <v>1.76143550872803</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76514410972595</v>
+        <v>1.76514399051666</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>1.75772738456726</v>
+        <v>1.75772750377655</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.74660241603851</v>
+        <v>1.74660277366638</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G525" t="n">
-        <v>1.75772738456726</v>
+        <v>1.75772750377655</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G527" t="n">
-        <v>1.78739368915558</v>
+        <v>1.78739380836487</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>1.75772738456726</v>
+        <v>1.75772750377655</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G531" t="n">
-        <v>1.82818496227264</v>
+        <v>1.82818472385406</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>1.74289405345917</v>
+        <v>1.74289429187775</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G536" t="n">
-        <v>1.69097816944122</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G537" t="n">
-        <v>1.66502010822296</v>
+        <v>1.66502022743225</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G538" t="n">
-        <v>1.69097816944122</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.25</v>
       </c>
       <c r="G539" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872870922089</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G542" t="n">
-        <v>1.620521068573</v>
+        <v>1.62052094936371</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>1.63906228542328</v>
+        <v>1.63906240463257</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G545" t="n">
-        <v>1.69468665122986</v>
+        <v>1.69468677043915</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G546" t="n">
-        <v>1.68356168270111</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G548" t="n">
-        <v>1.64277040958405</v>
+        <v>1.64277052879333</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G549" t="n">
-        <v>1.68356168270111</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>1.66502010822296</v>
+        <v>1.66502022743225</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131186485291</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.25</v>
       </c>
       <c r="G553" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872870922089</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G554" t="n">
-        <v>1.68356168270111</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G558" t="n">
-        <v>1.63164567947388</v>
+        <v>1.63164579868317</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.25</v>
       </c>
       <c r="G560" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872870922089</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G561" t="n">
-        <v>1.69468665122986</v>
+        <v>1.69468677043915</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G563" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131186485291</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.25</v>
       </c>
       <c r="G565" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872870922089</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.25</v>
       </c>
       <c r="G566" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872870922089</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.25</v>
       </c>
       <c r="G567" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872870922089</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>1.63906228542328</v>
+        <v>1.63906240463257</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.25</v>
       </c>
       <c r="G570" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872870922089</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.25</v>
       </c>
       <c r="G573" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872870922089</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G574" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131186485291</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>1.68727016448975</v>
+        <v>1.68726992607117</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>1.70210337638855</v>
+        <v>1.70210313796997</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.69839489459991</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>1.68356168270111</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.25</v>
       </c>
       <c r="G583" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872870922089</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>1.68356168270111</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.25</v>
       </c>
       <c r="G586" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872870922089</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G588" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131186485291</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131186485291</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.25</v>
       </c>
       <c r="G590" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872870922089</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G591" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131186485291</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G593" t="n">
-        <v>1.69839489459991</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G594" t="n">
-        <v>1.69097816944122</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G596" t="n">
-        <v>1.69468665122986</v>
+        <v>1.69468677043915</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>1.70210337638855</v>
+        <v>1.70210313796997</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G598" t="n">
-        <v>1.7298424243927</v>
+        <v>1.72984218597412</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G599" t="n">
-        <v>1.7298424243927</v>
+        <v>1.72984218597412</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G601" t="n">
-        <v>1.72598969936371</v>
+        <v>1.72598946094513</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.25</v>
       </c>
       <c r="G602" t="n">
-        <v>1.7336950302124</v>
+        <v>1.73369514942169</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>1.70287370681763</v>
+        <v>1.70287382602692</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G605" t="n">
-        <v>1.62967336177826</v>
+        <v>1.62967324256897</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G606" t="n">
-        <v>1.64893674850464</v>
+        <v>1.64893662929535</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G607" t="n">
-        <v>1.5526202917099</v>
+        <v>1.55262041091919</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G608" t="n">
-        <v>1.5526202917099</v>
+        <v>1.55262041091919</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G609" t="n">
-        <v>1.49791240692139</v>
+        <v>1.49791252613068</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G611" t="n">
-        <v>1.53489804267883</v>
+        <v>1.53489792346954</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G612" t="n">
-        <v>1.52102839946747</v>
+        <v>1.52102851867676</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G616" t="n">
-        <v>1.4840430021286</v>
+        <v>1.48404288291931</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G618" t="n">
-        <v>1.49791240692139</v>
+        <v>1.49791252613068</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G619" t="n">
-        <v>1.49174821376801</v>
+        <v>1.49174833297729</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G620" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G621" t="n">
-        <v>1.5834413766861</v>
+        <v>1.58344149589539</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G623" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G624" t="n">
-        <v>1.56803095340729</v>
+        <v>1.568030834198</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G625" t="n">
-        <v>1.62196791172028</v>
+        <v>1.62196803092957</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>1.62196791172028</v>
+        <v>1.62196803092957</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G627" t="n">
-        <v>1.59499943256378</v>
+        <v>1.59499931335449</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G628" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>1.59114694595337</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G630" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.65664184093475</v>
+        <v>1.65664196014404</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G632" t="n">
-        <v>1.61040985584259</v>
+        <v>1.61040997505188</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G635" t="n">
-        <v>1.57573616504669</v>
+        <v>1.5757360458374</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G636" t="n">
-        <v>1.56803095340729</v>
+        <v>1.568030834198</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>1.56032538414001</v>
+        <v>1.5603255033493</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G638" t="n">
-        <v>1.56803095340729</v>
+        <v>1.568030834198</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>1.59499943256378</v>
+        <v>1.59499931335449</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G642" t="n">
-        <v>1.59499943256378</v>
+        <v>1.59499931335449</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>1.62196791172028</v>
+        <v>1.62196803092957</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>1.59499943256378</v>
+        <v>1.59499931335449</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G648" t="n">
-        <v>1.5834413766861</v>
+        <v>1.58344149589539</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G649" t="n">
-        <v>1.59499943256378</v>
+        <v>1.59499931335449</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G650" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G651" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G652" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>1.56803095340729</v>
+        <v>1.568030834198</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>1.5834413766861</v>
+        <v>1.58344149589539</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G655" t="n">
-        <v>1.59114694595337</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G656" t="n">
-        <v>1.62582051753998</v>
+        <v>1.62582063674927</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G657" t="n">
-        <v>1.62967336177826</v>
+        <v>1.62967324256897</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G658" t="n">
-        <v>1.66049456596375</v>
+        <v>1.66049444675446</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G659" t="n">
-        <v>1.61426258087158</v>
+        <v>1.61426270008087</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G660" t="n">
-        <v>1.62196791172028</v>
+        <v>1.62196803092957</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G661" t="n">
-        <v>1.59114694595337</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G662" t="n">
-        <v>1.59114694595337</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G663" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G664" t="n">
-        <v>1.5834413766861</v>
+        <v>1.58344149589539</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G666" t="n">
-        <v>1.5834413766861</v>
+        <v>1.58344149589539</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G668" t="n">
-        <v>1.56417810916901</v>
+        <v>1.5641782283783</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G671" t="n">
-        <v>1.53643906116486</v>
+        <v>1.53643894195557</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G672" t="n">
-        <v>1.52102839946747</v>
+        <v>1.52102851867676</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G673" t="n">
-        <v>1.56417810916901</v>
+        <v>1.5641782283783</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G674" t="n">
-        <v>1.5526202917099</v>
+        <v>1.55262041091919</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G675" t="n">
-        <v>1.53489804267883</v>
+        <v>1.53489792346954</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>1.57573616504669</v>
+        <v>1.5757360458374</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>1.56032538414001</v>
+        <v>1.5603255033493</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G683" t="n">
-        <v>1.56417810916901</v>
+        <v>1.5641782283783</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G684" t="n">
-        <v>1.57573616504669</v>
+        <v>1.5757360458374</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G685" t="n">
-        <v>1.59114694595337</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G687" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G688" t="n">
-        <v>1.56417810916901</v>
+        <v>1.5641782283783</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>1.56417810916901</v>
+        <v>1.5641782283783</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G691" t="n">
-        <v>1.56803095340729</v>
+        <v>1.568030834198</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G692" t="n">
-        <v>1.57573616504669</v>
+        <v>1.5757360458374</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>1.57573616504669</v>
+        <v>1.5757360458374</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>1.57573616504669</v>
+        <v>1.5757360458374</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G695" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G697" t="n">
-        <v>1.59114694595337</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G698" t="n">
-        <v>1.61040985584259</v>
+        <v>1.61040997505188</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>1.65664184093475</v>
+        <v>1.65664196014404</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G701" t="n">
-        <v>1.61040985584259</v>
+        <v>1.61040997505188</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G702" t="n">
-        <v>1.56417810916901</v>
+        <v>1.5641782283783</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G704" t="n">
-        <v>1.5526202917099</v>
+        <v>1.55262041091919</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G705" t="n">
-        <v>1.56417810916901</v>
+        <v>1.5641782283783</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G707" t="n">
-        <v>1.47479641437531</v>
+        <v>1.47479665279388</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G708" t="n">
-        <v>1.49328923225403</v>
+        <v>1.49328935146332</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G710" t="n">
-        <v>1.4254823923111</v>
+        <v>1.42548251152039</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G714" t="n">
-        <v>1.42394149303436</v>
+        <v>1.42394161224365</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G715" t="n">
-        <v>1.44089317321777</v>
+        <v>1.44089329242706</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G717" t="n">
-        <v>1.32377254962921</v>
+        <v>1.32377243041992</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G719" t="n">
-        <v>1.21281588077545</v>
+        <v>1.21281611919403</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G720" t="n">
-        <v>1.25288367271423</v>
+        <v>1.25288343429565</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G727" t="n">
-        <v>1.29295110702515</v>
+        <v>1.29295122623444</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G730" t="n">
-        <v>1.30682075023651</v>
+        <v>1.30682063102722</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G731" t="n">
-        <v>1.29757440090179</v>
+        <v>1.29757452011108</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G733" t="n">
-        <v>1.28062272071838</v>
+        <v>1.28062260150909</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G736" t="n">
-        <v>1.19278216362</v>
+        <v>1.19278204441071</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.5460000038147</v>
       </c>
       <c r="G738" t="n">
-        <v>1.19124114513397</v>
+        <v>1.19124102592468</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G744" t="n">
-        <v>1.24980139732361</v>
+        <v>1.2498015165329</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G745" t="n">
-        <v>1.27137637138367</v>
+        <v>1.27137625217438</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G749" t="n">
-        <v>1.27908170223236</v>
+        <v>1.27908158302307</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G752" t="n">
-        <v>1.22668540477753</v>
+        <v>1.22668552398682</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G753" t="n">
-        <v>1.20665156841278</v>
+        <v>1.20665168762207</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G756" t="n">
-        <v>1.15733754634857</v>
+        <v>1.15733766555786</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G758" t="n">
-        <v>1.09569537639618</v>
+        <v>1.0956951379776</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G760" t="n">
-        <v>1.0710381269455</v>
+        <v>1.07103824615479</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G761" t="n">
-        <v>1.07566154003143</v>
+        <v>1.07566142082214</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G762" t="n">
-        <v>1.08182573318481</v>
+        <v>1.08182561397552</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G766" t="n">
-        <v>1.15733754634857</v>
+        <v>1.15733766555786</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.5</v>
       </c>
       <c r="G768" t="n">
-        <v>1.15579652786255</v>
+        <v>1.15579664707184</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.5</v>
       </c>
       <c r="G771" t="n">
-        <v>1.15579652786255</v>
+        <v>1.15579664707184</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G774" t="n">
-        <v>1.14346826076508</v>
+        <v>1.14346814155579</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>1.5</v>
       </c>
       <c r="G777" t="n">
-        <v>1.15579652786255</v>
+        <v>1.15579664707184</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G779" t="n">
-        <v>1.13268077373505</v>
+        <v>1.13268065452576</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>1.12497532367706</v>
+        <v>1.12497544288635</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G781" t="n">
-        <v>1.13268077373505</v>
+        <v>1.13268065452576</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G782" t="n">
-        <v>1.12651646137238</v>
+        <v>1.12651658058167</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G783" t="n">
-        <v>1.10956478118896</v>
+        <v>1.10956490039825</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G785" t="n">
-        <v>1.10340046882629</v>
+        <v>1.10340058803558</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G786" t="n">
-        <v>1.07412028312683</v>
+        <v>1.07412040233612</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G787" t="n">
-        <v>1.06641495227814</v>
+        <v>1.06641507148743</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G788" t="n">
-        <v>1.06641495227814</v>
+        <v>1.06641507148743</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G793" t="n">
-        <v>1.17428934574127</v>
+        <v>1.17428958415985</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G796" t="n">
-        <v>1.22668540477753</v>
+        <v>1.22668552398682</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G802" t="n">
-        <v>1.23439085483551</v>
+        <v>1.23439073562622</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G803" t="n">
-        <v>1.23439085483551</v>
+        <v>1.23439073562622</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G808" t="n">
-        <v>1.28678679466248</v>
+        <v>1.28678691387177</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G809" t="n">
-        <v>1.27754056453705</v>
+        <v>1.27754044532776</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G812" t="n">
-        <v>1.18199479579926</v>
+        <v>1.18199467658997</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>1.17120730876923</v>
+        <v>1.17120718955994</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G816" t="n">
-        <v>1.16658425331116</v>
+        <v>1.16658401489258</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G817" t="n">
-        <v>1.16658425331116</v>
+        <v>1.16658401489258</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.5</v>
       </c>
       <c r="G819" t="n">
-        <v>1.15579652786255</v>
+        <v>1.15579664707184</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.17120730876923</v>
+        <v>1.17120718955994</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G822" t="n">
-        <v>1.17120730876923</v>
+        <v>1.17120718955994</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G824" t="n">
-        <v>1.13422179222107</v>
+        <v>1.13422167301178</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>1.5</v>
       </c>
       <c r="G826" t="n">
-        <v>1.15579652786255</v>
+        <v>1.15579664707184</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G827" t="n">
-        <v>1.17120730876923</v>
+        <v>1.17120718955994</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.5</v>
       </c>
       <c r="G829" t="n">
-        <v>1.15579652786255</v>
+        <v>1.15579664707184</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G830" t="n">
-        <v>1.15733754634857</v>
+        <v>1.15733766555786</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.5</v>
       </c>
       <c r="G831" t="n">
-        <v>1.15579652786255</v>
+        <v>1.15579664707184</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G832" t="n">
-        <v>1.1604198217392</v>
+        <v>1.16041994094849</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G836" t="n">
-        <v>1.27908170223236</v>
+        <v>1.27908158302307</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G837" t="n">
-        <v>1.29295110702515</v>
+        <v>1.29295122623444</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G839" t="n">
-        <v>1.30527973175049</v>
+        <v>1.3052796125412</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G840" t="n">
-        <v>1.29295110702515</v>
+        <v>1.29295122623444</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G841" t="n">
-        <v>1.28678679466248</v>
+        <v>1.28678691387177</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G843" t="n">
-        <v>1.27137637138367</v>
+        <v>1.27137625217438</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G844" t="n">
-        <v>1.28062272071838</v>
+        <v>1.28062260150909</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G845" t="n">
-        <v>1.28832793235779</v>
+        <v>1.28832805156708</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G846" t="n">
-        <v>1.29140996932983</v>
+        <v>1.29141008853912</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G847" t="n">
-        <v>1.2898690700531</v>
+        <v>1.28986895084381</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G848" t="n">
-        <v>1.33944809436798</v>
+        <v>1.33944821357727</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.5</v>
       </c>
       <c r="G852" t="n">
-        <v>1.21915781497955</v>
+        <v>1.21915793418884</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G855" t="n">
-        <v>1.14113187789917</v>
+        <v>1.14113175868988</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G856" t="n">
-        <v>1.11512315273285</v>
+        <v>1.11512303352356</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G857" t="n">
-        <v>1.12162518501282</v>
+        <v>1.12162530422211</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G858" t="n">
-        <v>1.11349749565125</v>
+        <v>1.11349761486053</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G870" t="n">
-        <v>1.03222024440765</v>
+        <v>1.03222036361694</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G875" t="n">
-        <v>0.955819845199585</v>
+        <v>0.95581978559494</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>0.910304605960846</v>
+        <v>0.910304486751556</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G879" t="n">
-        <v>0.92818558216095</v>
+        <v>0.928185522556305</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G880" t="n">
-        <v>0.924934506416321</v>
+        <v>0.924934387207031</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G882" t="n">
-        <v>0.950943052768707</v>
+        <v>0.950943112373352</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G883" t="n">
-        <v>0.957445323467255</v>
+        <v>0.957445383071899</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G884" t="n">
-        <v>0.939564406871796</v>
+        <v>0.939564347267151</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G886" t="n">
-        <v>0.955819845199585</v>
+        <v>0.95581978559494</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G889" t="n">
-        <v>0.983454048633575</v>
+        <v>0.983454167842865</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G891" t="n">
-        <v>0.988330602645874</v>
+        <v>0.988330721855164</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>1.03222024440765</v>
+        <v>1.03222036361694</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G894" t="n">
-        <v>1.04034805297852</v>
+        <v>1.04034793376923</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G896" t="n">
-        <v>1.03059482574463</v>
+        <v>1.03059470653534</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G900" t="n">
-        <v>0.994832873344421</v>
+        <v>0.994832754135132</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G901" t="n">
-        <v>0.981828391551971</v>
+        <v>0.981828451156616</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G903" t="n">
-        <v>0.991581678390503</v>
+        <v>0.991581797599792</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G904" t="n">
-        <v>0.983454048633575</v>
+        <v>0.983454167842865</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.02409255504608</v>
+        <v>1.02409267425537</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G907" t="n">
-        <v>1.03222024440765</v>
+        <v>1.03222036361694</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G908" t="n">
-        <v>1.02246701717377</v>
+        <v>1.02246713638306</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G912" t="n">
-        <v>1.02409255504608</v>
+        <v>1.02409267425537</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G913" t="n">
-        <v>1.02409255504608</v>
+        <v>1.02409267425537</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G916" t="n">
-        <v>0.986705005168915</v>
+        <v>0.986705124378204</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>0.950943052768707</v>
+        <v>0.950943112373352</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G920" t="n">
-        <v>0.952568650245667</v>
+        <v>0.952568829059601</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G921" t="n">
-        <v>0.920057833194733</v>
+        <v>0.920057773590088</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G922" t="n">
-        <v>0.92818558216095</v>
+        <v>0.928185522556305</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G923" t="n">
-        <v>0.954194247722626</v>
+        <v>0.954194307327271</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G926" t="n">
-        <v>0.981828391551971</v>
+        <v>0.981828451156616</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G927" t="n">
-        <v>0.978577435016632</v>
+        <v>0.978577375411987</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G932" t="n">
-        <v>0.980202913284302</v>
+        <v>0.980202853679657</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G934" t="n">
-        <v>0.950943052768707</v>
+        <v>0.950943112373352</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.04034805297852</v>
+        <v>1.04034793376923</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G937" t="n">
-        <v>1.02409255504608</v>
+        <v>1.02409267425537</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G939" t="n">
-        <v>1.14275729656219</v>
+        <v>1.14275741577148</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G940" t="n">
-        <v>1.1785192489624</v>
+        <v>1.17851936817169</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G942" t="n">
-        <v>1.19640028476715</v>
+        <v>1.19640016555786</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G943" t="n">
-        <v>1.20290243625641</v>
+        <v>1.2029025554657</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G944" t="n">
-        <v>1.1785192489624</v>
+        <v>1.17851936817169</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G952" t="n">
-        <v>1.14925956726074</v>
+        <v>1.14925968647003</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G954" t="n">
-        <v>1.13462972640991</v>
+        <v>1.13462960720062</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G961" t="n">
-        <v>1.13462972640991</v>
+        <v>1.13462960720062</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G962" t="n">
-        <v>1.17039155960083</v>
+        <v>1.17039167881012</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G963" t="n">
-        <v>1.17364263534546</v>
+        <v>1.17364275455475</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G964" t="n">
-        <v>1.16226387023926</v>
+        <v>1.16226375102997</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G965" t="n">
-        <v>1.17039155960083</v>
+        <v>1.17039167881012</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G969" t="n">
-        <v>1.18502140045166</v>
+        <v>1.18502151966095</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G970" t="n">
-        <v>1.1785192489624</v>
+        <v>1.17851936817169</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G971" t="n">
-        <v>1.17039155960083</v>
+        <v>1.17039167881012</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G972" t="n">
-        <v>1.16714036464691</v>
+        <v>1.1671404838562</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G973" t="n">
-        <v>1.26467311382294</v>
+        <v>1.26467323303223</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G975" t="n">
-        <v>1.25492000579834</v>
+        <v>1.25491988658905</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G976" t="n">
-        <v>1.31018829345703</v>
+        <v>1.31018841266632</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G978" t="n">
-        <v>1.38008677959442</v>
+        <v>1.38008666038513</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G981" t="n">
-        <v>1.38008677959442</v>
+        <v>1.38008666038513</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G985" t="n">
-        <v>1.34920144081116</v>
+        <v>1.34920132160187</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G986" t="n">
-        <v>1.36870789527893</v>
+        <v>1.36870801448822</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G988" t="n">
-        <v>1.49224936962128</v>
+        <v>1.49224925041199</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G991" t="n">
-        <v>1.51988351345062</v>
+        <v>1.51988363265991</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G992" t="n">
-        <v>1.52150905132294</v>
+        <v>1.52150893211365</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G994" t="n">
-        <v>1.53451347351074</v>
+        <v>1.53451335430145</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G995" t="n">
-        <v>1.52801132202148</v>
+        <v>1.52801120281219</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G996" t="n">
-        <v>1.50037682056427</v>
+        <v>1.50037693977356</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G999" t="n">
-        <v>1.45486164093018</v>
+        <v>1.45486176013947</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.51500678062439</v>
+        <v>1.51500689983368</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.50850450992584</v>
+        <v>1.50850462913513</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.541015625</v>
+        <v>1.54101550579071</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.55401980876923</v>
+        <v>1.55401992797852</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.60116064548492</v>
+        <v>1.60116052627563</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.58327972888947</v>
+        <v>1.58327960968018</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.54426658153534</v>
+        <v>1.54426670074463</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.51988351345062</v>
+        <v>1.51988363265991</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.51663255691528</v>
+        <v>1.51663243770599</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.52150905132294</v>
+        <v>1.52150893211365</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.46624064445496</v>
+        <v>1.46624052524567</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.46298944950104</v>
+        <v>1.46298933029175</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.46298944950104</v>
+        <v>1.46298933029175</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.53451347351074</v>
+        <v>1.53451335430145</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.46624064445496</v>
+        <v>1.46624052524567</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.45323610305786</v>
+        <v>1.45323634147644</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.43047869205475</v>
+        <v>1.43047857284546</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.49387490749359</v>
+        <v>1.4938747882843</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.58002853393555</v>
+        <v>1.58002865314484</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.59790945053101</v>
+        <v>1.5979095697403</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.61416494846344</v>
+        <v>1.61416506767273</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.64179933071136</v>
+        <v>1.64179921150208</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.73933207988739</v>
+        <v>1.7393319606781</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.68243789672852</v>
+        <v>1.68243777751923</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.51988351345062</v>
+        <v>1.51988363265991</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.49224936962128</v>
+        <v>1.49224925041199</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.49387490749359</v>
+        <v>1.4938747882843</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.45486164093018</v>
+        <v>1.45486176013947</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.34920144081116</v>
+        <v>1.34920132160187</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.28580522537231</v>
+        <v>1.28580510616302</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.20777904987335</v>
+        <v>1.20777916908264</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.02409255504608</v>
+        <v>1.02409267425537</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.978577435016632</v>
+        <v>0.978577375411987</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.897300124168396</v>
+        <v>0.897300183773041</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.902176797389984</v>
+        <v>0.902176856994629</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.817648649215698</v>
+        <v>0.817648589611053</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.820899665355682</v>
+        <v>0.820899605751038</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.950943052768707</v>
+        <v>0.950943112373352</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.942815482616425</v>
+        <v>0.94281542301178</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.881044745445251</v>
+        <v>0.881044805049896</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.921683311462402</v>
+        <v>0.921683371067047</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.983454048633575</v>
+        <v>0.983454167842865</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.978577435016632</v>
+        <v>0.978577375411987</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.04685020446777</v>
+        <v>1.04685032367706</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.978577435016632</v>
+        <v>0.978577375411987</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.02246701717377</v>
+        <v>1.02246713638306</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.28199994564056</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.04197347164154</v>
+        <v>1.04197359085083</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.04522478580475</v>
+        <v>1.04522466659546</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.08098661899567</v>
+        <v>1.08098673820496</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.08098661899567</v>
+        <v>1.08098673820496</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.05497801303864</v>
+        <v>1.05497789382935</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.03059482574463</v>
+        <v>1.03059470653534</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.04034805297852</v>
+        <v>1.04034793376923</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.02896928787231</v>
+        <v>1.0289694070816</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.980202913284302</v>
+        <v>0.980202853679657</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.980202913284302</v>
+        <v>0.980202853679657</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.959070920944214</v>
+        <v>0.959070861339569</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.99970954656601</v>
+        <v>0.99970942735672</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.03222024440765</v>
+        <v>1.03222036361694</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.11512315273285</v>
+        <v>1.11512303352356</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.13950622081757</v>
+        <v>1.13950634002686</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.15576183795929</v>
+        <v>1.15576159954071</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.23866438865662</v>
+        <v>1.23866450786591</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.29068195819855</v>
+        <v>1.29068183898926</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.21915781497955</v>
+        <v>1.21915793418884</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.11349749565125</v>
+        <v>1.11349761486053</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.14113187789917</v>
+        <v>1.14113175868988</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.11024653911591</v>
+        <v>1.11024641990662</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.0988677740097</v>
+        <v>1.09886765480042</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.0988677740097</v>
+        <v>1.09886765480042</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.04522478580475</v>
+        <v>1.04522466659546</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.18502140045166</v>
+        <v>1.18502151966095</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.23053681850433</v>
+        <v>1.23053669929504</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.27930295467377</v>
+        <v>1.27930307388306</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.34107375144958</v>
+        <v>1.3410736322403</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.35570359230042</v>
+        <v>1.35570347309113</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.43047869205475</v>
+        <v>1.43047857284546</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.44998502731323</v>
+        <v>1.44998526573181</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.46298944950104</v>
+        <v>1.46298933029175</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.42722761631012</v>
+        <v>1.42722749710083</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.40609550476074</v>
+        <v>1.40609538555145</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.43860638141632</v>
+        <v>1.43860626220703</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.44510853290558</v>
+        <v>1.44510841369629</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.44185757637024</v>
+        <v>1.44185733795166</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.44673407077789</v>
+        <v>1.4467339515686</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.52476012706757</v>
+        <v>1.52476024627686</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.55401980876923</v>
+        <v>1.55401992797852</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.5052535533905</v>
+        <v>1.50525367259979</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.48899817466736</v>
+        <v>1.48899829387665</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.45323610305786</v>
+        <v>1.45323634147644</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.44510853290558</v>
+        <v>1.44510841369629</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.39959323406219</v>
+        <v>1.39959335327148</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.41584873199463</v>
+        <v>1.41584861278534</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.43047869205475</v>
+        <v>1.43047857284546</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.32806921005249</v>
+        <v>1.32806932926178</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.33294594287872</v>
+        <v>1.33294606208801</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.31994163990021</v>
+        <v>1.31994152069092</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.35082697868347</v>
+        <v>1.35082685947418</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.31669056415558</v>
+        <v>1.31669044494629</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.3638311624527</v>
+        <v>1.36383140087128</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.35895466804504</v>
+        <v>1.35895478725433</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.39959323406219</v>
+        <v>1.39959335327148</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.33944809436798</v>
+        <v>1.33944821357727</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.20290243625641</v>
+        <v>1.2029025554657</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.15088510513306</v>
+        <v>1.15088498592377</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.22891104221344</v>
+        <v>1.22891116142273</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.24191558361053</v>
+        <v>1.24191546440125</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1232" t="n">
-        <v>1.23378777503967</v>
+        <v>1.23378789424896</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.25492000579834</v>
+        <v>1.25491988658905</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.23378777503967</v>
+        <v>1.23378789424896</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.32806921005249</v>
+        <v>1.32806932926178</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.31994163990021</v>
+        <v>1.31994152069092</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.35082697868347</v>
+        <v>1.35082685947418</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.35570359230042</v>
+        <v>1.35570347309113</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.39959323406219</v>
+        <v>1.39959335327148</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.44673407077789</v>
+        <v>1.4467339515686</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.44673407077789</v>
+        <v>1.4467339515686</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.45486164093018</v>
+        <v>1.45486176013947</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.38984000682831</v>
+        <v>1.3898401260376</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.39146566390991</v>
+        <v>1.39146554470062</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.35082697868347</v>
+        <v>1.35082685947418</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.33294594287872</v>
+        <v>1.33294606208801</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.31669056415558</v>
+        <v>1.31669044494629</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.35570359230042</v>
+        <v>1.35570347309113</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.34920144081116</v>
+        <v>1.34920132160187</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.3296947479248</v>
+        <v>1.32969498634338</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.28580522537231</v>
+        <v>1.28580510616302</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.31018829345703</v>
+        <v>1.31018841266632</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.33944809436798</v>
+        <v>1.33944821357727</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.36870789527893</v>
+        <v>1.36870801448822</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.35245263576508</v>
+        <v>1.3524523973465</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.38984000682831</v>
+        <v>1.3898401260376</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.39471662044525</v>
+        <v>1.39471673965454</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.42072546482086</v>
+        <v>1.42072534561157</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.38984000682831</v>
+        <v>1.3898401260376</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.39471662044525</v>
+        <v>1.39471673965454</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.4109719991684</v>
+        <v>1.41097187995911</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.34920144081116</v>
+        <v>1.34920132160187</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.35570359230042</v>
+        <v>1.35570347309113</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.35570359230042</v>
+        <v>1.35570347309113</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.36545670032501</v>
+        <v>1.3654568195343</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.41909968852997</v>
+        <v>1.41909992694855</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.48899817466736</v>
+        <v>1.48899829387665</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.56052196025848</v>
+        <v>1.56052219867706</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.55564546585083</v>
+        <v>1.55564558506012</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.52801132202148</v>
+        <v>1.52801120281219</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.46298944950104</v>
+        <v>1.46298933029175</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.47761940956116</v>
+        <v>1.47761929035187</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.46624064445496</v>
+        <v>1.46624052524567</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.49224936962128</v>
+        <v>1.49224925041199</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.61253941059113</v>
+        <v>1.61253952980042</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.61416494846344</v>
+        <v>1.61416506767273</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.60928845405579</v>
+        <v>1.60928857326508</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.60116064548492</v>
+        <v>1.60116052627563</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.58002853393555</v>
+        <v>1.58002865314484</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.60441172122955</v>
+        <v>1.60441184043884</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.5881564617157</v>
+        <v>1.58815634250641</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.64992690086365</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.71088480949402</v>
+        <v>1.71088492870331</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.63773548603058</v>
+        <v>1.63773560523987</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.61416494846344</v>
+        <v>1.61416506767273</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.62229287624359</v>
+        <v>1.6222927570343</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.60441172122955</v>
+        <v>1.60441184043884</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.76777899265289</v>
+        <v>1.7677788734436</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.7149486541748</v>
+        <v>1.71494877338409</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.68243789672852</v>
+        <v>1.68243777751923</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.64179933071136</v>
+        <v>1.64179921150208</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.64179933071136</v>
+        <v>1.64179921150208</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.62229287624359</v>
+        <v>1.6222927570343</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.62960779666901</v>
+        <v>1.6296079158783</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.64179933071136</v>
+        <v>1.64179921150208</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.66211867332458</v>
+        <v>1.6621185541153</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.69869327545166</v>
+        <v>1.69869339466095</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.68243789672852</v>
+        <v>1.68243777751923</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.68243789672852</v>
+        <v>1.68243777751923</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.69869327545166</v>
+        <v>1.69869339466095</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.68243789672852</v>
+        <v>1.68243777751923</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.64992690086365</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.64992690086365</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.64992690086365</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.64992690086365</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.64992690086365</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.69869327545166</v>
+        <v>1.69869339466095</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.74745965003967</v>
+        <v>1.74745976924896</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.75152349472046</v>
+        <v>1.75152337551117</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.74745965003967</v>
+        <v>1.74745976924896</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.75152349472046</v>
+        <v>1.75152337551117</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.76777899265289</v>
+        <v>1.7677788734436</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.73933207988739</v>
+        <v>1.7393319606781</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.71088480949402</v>
+        <v>1.71088492870331</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.69869327545166</v>
+        <v>1.69869339466095</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.68243789672852</v>
+        <v>1.68243777751923</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.73526799678802</v>
+        <v>1.73526811599731</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.69869327545166</v>
+        <v>1.69869339466095</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.68243789672852</v>
+        <v>1.68243777751923</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.63773548603058</v>
+        <v>1.63773560523987</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.66211867332458</v>
+        <v>1.6621185541153</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.64992690086365</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.66211867332458</v>
+        <v>1.6621185541153</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.73526799678802</v>
+        <v>1.73526811599731</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.73933207988739</v>
+        <v>1.7393319606781</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.7149486541748</v>
+        <v>1.71494877338409</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.73120427131653</v>
+        <v>1.73120439052582</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.73120427131653</v>
+        <v>1.73120439052582</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.7149486541748</v>
+        <v>1.71494877338409</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.66211867332458</v>
+        <v>1.6621185541153</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.69869327545166</v>
+        <v>1.69869339466095</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.73526799678802</v>
+        <v>1.73526811599731</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.74745965003967</v>
+        <v>1.74745976924896</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.75152349472046</v>
+        <v>1.75152337551117</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.75152349472046</v>
+        <v>1.75152337551117</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.75965130329132</v>
+        <v>1.75965118408203</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.7433956861496</v>
+        <v>1.74339580535889</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.77997064590454</v>
+        <v>1.77997052669525</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.77590656280518</v>
+        <v>1.77590668201447</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.83686447143555</v>
+        <v>1.83686459064484</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.83686447143555</v>
+        <v>1.83686459064484</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.87750315666199</v>
+        <v>1.8775030374527</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.92626953125</v>
+        <v>1.92626941204071</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.91407787799835</v>
+        <v>1.91407799720764</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.8978226184845</v>
+        <v>1.89782249927521</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.91814184188843</v>
+        <v>1.91814172267914</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.88563096523285</v>
+        <v>1.88563084602356</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.91407787799835</v>
+        <v>1.91407799720764</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.91001391410828</v>
+        <v>1.91001403331757</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.89375841617584</v>
+        <v>1.89375829696655</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.84499216079712</v>
+        <v>1.84499228000641</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>2.25</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.82873690128326</v>
+        <v>1.82873702049255</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>2.25</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.82873690128326</v>
+        <v>1.82873702049255</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.85718393325806</v>
+        <v>1.85718405246735</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.85718393325806</v>
+        <v>1.85718405246735</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>2.25</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.82873690128326</v>
+        <v>1.82873702049255</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.83686447143555</v>
+        <v>1.83686459064484</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.89375841617584</v>
+        <v>1.89375829696655</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.89375841617584</v>
+        <v>1.89375829696655</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>2.25</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.82873690128326</v>
+        <v>1.82873702049255</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.85718393325806</v>
+        <v>1.85718405246735</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1462" t="n">
-        <v>1.84499216079712</v>
+        <v>1.84499228000641</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.84905624389648</v>
+        <v>1.84905600547791</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.85718393325806</v>
+        <v>1.85718405246735</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.84905624389648</v>
+        <v>1.84905600547791</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.88563096523285</v>
+        <v>1.88563084602356</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.84905624389648</v>
+        <v>1.84905600547791</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.90188610553741</v>
+        <v>1.9018862247467</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.87750315666199</v>
+        <v>1.8775030374527</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.82060921192169</v>
+        <v>1.82060897350311</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1477" t="n">
-        <v>1.82467305660248</v>
+        <v>1.8246728181839</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.87750315666199</v>
+        <v>1.8775030374527</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.92220556735992</v>
+        <v>1.92220568656921</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.84092843532562</v>
+        <v>1.84092855453491</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.89375841617584</v>
+        <v>1.89375829696655</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.87750315666199</v>
+        <v>1.8775030374527</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>1.91001391410828</v>
+        <v>1.91001403331757</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.91001391410828</v>
+        <v>1.91001403331757</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.97097194194794</v>
+        <v>1.97097182273865</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.84669208526611</v>
+        <v>1.8466922044754</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.80730772018433</v>
+        <v>1.80730783939362</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1498" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1502" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.73291492462158</v>
+        <v>1.73291504383087</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.82918787002563</v>
+        <v>1.82918798923492</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.83356392383575</v>
+        <v>1.83356404304504</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.83356392383575</v>
+        <v>1.83356404304504</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.82043588161469</v>
+        <v>1.8204357624054</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.82918787002563</v>
+        <v>1.82918798923492</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.82043588161469</v>
+        <v>1.8204357624054</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1520" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.86419630050659</v>
+        <v>1.86419653892517</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.90358078479767</v>
+        <v>1.90358066558838</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.8904527425766</v>
+        <v>1.89045262336731</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.86419630050659</v>
+        <v>1.86419653892517</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.86419630050659</v>
+        <v>1.86419653892517</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.84669208526611</v>
+        <v>1.8466922044754</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>2.125</v>
       </c>
       <c r="G1535" t="n">
-        <v>1.85982024669647</v>
+        <v>1.85982012748718</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.84669208526611</v>
+        <v>1.8466922044754</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.82043588161469</v>
+        <v>1.8204357624054</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1540" t="n">
-        <v>1.80730772018433</v>
+        <v>1.80730783939362</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.84669208526611</v>
+        <v>1.8466922044754</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.82918787002563</v>
+        <v>1.82918798923492</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.84669208526611</v>
+        <v>1.8466922044754</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.8904527425766</v>
+        <v>1.89045262336731</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.89482879638672</v>
+        <v>1.89482867717743</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.86419630050659</v>
+        <v>1.86419653892517</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>2.125</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.85982024669647</v>
+        <v>1.85982012748718</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.72416293621063</v>
+        <v>1.72416269779205</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.71716105937958</v>
+        <v>1.71716117858887</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1570" t="n">
-        <v>1.64539408683777</v>
+        <v>1.64539396762848</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1571" t="n">
-        <v>1.51936376094818</v>
+        <v>1.51936364173889</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.5893806219101</v>
+        <v>1.58938038349152</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.63314116001129</v>
+        <v>1.633141040802</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.73116445541382</v>
+        <v>1.73116457462311</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.83356392383575</v>
+        <v>1.83356404304504</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.82918787002563</v>
+        <v>1.82918798923492</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1597" t="n">
-        <v>1.76354730129242</v>
+        <v>1.76354742050171</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.75479519367218</v>
+        <v>1.75479531288147</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.79855561256409</v>
+        <v>1.79855573177338</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.82043588161469</v>
+        <v>1.8204357624054</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.81932294368744</v>
+        <v>1.81932306289673</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.81932294368744</v>
+        <v>1.81932306289673</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.84200763702393</v>
+        <v>1.84200775623322</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.80389714241028</v>
+        <v>1.80389726161957</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.83293378353119</v>
+        <v>1.8329336643219</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1636" t="n">
-        <v>1.83293378353119</v>
+        <v>1.8329336643219</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.72767627239227</v>
+        <v>1.72767615318298</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1645" t="n">
-        <v>1.73312056064606</v>
+        <v>1.73312044143677</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.52260529994965</v>
+        <v>1.52260541915894</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.49356889724731</v>
+        <v>1.49356877803802</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.4427547454834</v>
+        <v>1.44275486469269</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1659" t="n">
-        <v>1.4427547454834</v>
+        <v>1.44275486469269</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.42279207706451</v>
+        <v>1.4227921962738</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.3030161857605</v>
+        <v>1.30301630496979</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.34294152259827</v>
+        <v>1.34294164180756</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.33023810386658</v>
+        <v>1.33023798465729</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1678" t="n">
-        <v>1.484494805336</v>
+        <v>1.48449492454529</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.46271741390228</v>
+        <v>1.46271753311157</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.44638442993164</v>
+        <v>1.44638431072235</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.46271741390228</v>
+        <v>1.46271753311157</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.46997666358948</v>
+        <v>1.46997654438019</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.41734778881073</v>
+        <v>1.41734790802002</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.38649654388428</v>
+        <v>1.38649642467499</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>1.5</v>
       </c>
       <c r="G1701" t="n">
-        <v>1.36108934879303</v>
+        <v>1.36108946800232</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.3737930059433</v>
+        <v>1.37379288673401</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>1.5</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.36108934879303</v>
+        <v>1.36108946800232</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>1.35599994659424</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.23042488098145</v>
+        <v>1.23042476177216</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.27760922908783</v>
+        <v>1.27760934829712</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.2612761259079</v>
+        <v>1.26127624511719</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.24312829971313</v>
+        <v>1.24312841892242</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.34657120704651</v>
+        <v>1.34657108783722</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.33023810386658</v>
+        <v>1.33023798465729</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.2903128862381</v>
+        <v>1.29031276702881</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.37923729419708</v>
+        <v>1.37923717498779</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.3447562456131</v>
+        <v>1.34475636482239</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.34294152259827</v>
+        <v>1.34294164180756</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.4010146856308</v>
+        <v>1.40101480484009</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.4010146856308</v>
+        <v>1.40101480484009</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.41734778881073</v>
+        <v>1.41734790802002</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.3737930059433</v>
+        <v>1.37379288673401</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>1.5</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.36108934879303</v>
+        <v>1.36108946800232</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.37742245197296</v>
+        <v>1.37742257118225</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.37742245197296</v>
+        <v>1.37742257118225</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.34657120704651</v>
+        <v>1.34657108783722</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.37923729419708</v>
+        <v>1.37923717498779</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1787" t="n">
-        <v>1.4427547454834</v>
+        <v>1.44275486469269</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.46271741390228</v>
+        <v>1.46271753311157</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.49356889724731</v>
+        <v>1.49356877803802</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.46997666358948</v>
+        <v>1.46997654438019</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.484494805336</v>
+        <v>1.48449492454529</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.62423324584961</v>
+        <v>1.6242333650589</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.62786304950714</v>
+        <v>1.62786293029785</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1814" t="n">
-        <v>1.484494805336</v>
+        <v>1.48449492454529</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1819" t="n">
-        <v>1.4427547454834</v>
+        <v>1.44275486469269</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.37742245197296</v>
+        <v>1.37742257118225</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.3737930059433</v>
+        <v>1.37379288673401</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.37923729419708</v>
+        <v>1.37923717498779</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1829" t="n">
-        <v>1.38286685943604</v>
+        <v>1.38286697864532</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.3737930059433</v>
+        <v>1.37379288673401</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.27397978305817</v>
+        <v>1.27397966384888</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.24675798416138</v>
+        <v>1.24675786495209</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1843" t="n">
-        <v>1.2140918970108</v>
+        <v>1.21409177780151</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.23949885368347</v>
+        <v>1.23949873447418</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.2340544462204</v>
+        <v>1.23405432701111</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.2340544462204</v>
+        <v>1.23405432701111</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.2340544462204</v>
+        <v>1.23405432701111</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.2340544462204</v>
+        <v>1.23405432701111</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.2140918970108</v>
+        <v>1.21409177780151</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.2140918970108</v>
+        <v>1.21409177780151</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>1.59399998188019</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>3702</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>1.59599995613098</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>1.56200003623962</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>1.56200003623962</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>1.5900000333786</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>1.5900000333786</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74831414222717</v>
+        <v>2.74831390380859</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>2.69898509979248</v>
+        <v>2.69898533821106</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74831414222717</v>
+        <v>2.74831390380859</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G5" t="n">
-        <v>2.68630123138428</v>
+        <v>2.6863009929657</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G6" t="n">
-        <v>2.75958919525146</v>
+        <v>2.75958943367004</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>2.60737490653992</v>
+        <v>2.6073751449585</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G11" t="n">
-        <v>2.48757672309875</v>
+        <v>2.48757648468018</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>2.43824791908264</v>
+        <v>2.43824815750122</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.50167036056519</v>
+        <v>2.50167059898376</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>2.56368327140808</v>
+        <v>2.56368374824524</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.25</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2902615070343</v>
+        <v>2.29026174545288</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G20" t="n">
-        <v>2.29730892181396</v>
+        <v>2.29730868339539</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G21" t="n">
-        <v>2.39455652236938</v>
+        <v>2.39455699920654</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G22" t="n">
-        <v>2.29871797561646</v>
+        <v>2.29871845245361</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>2.11408758163452</v>
+        <v>2.11408805847168</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G24" t="n">
-        <v>1.97455823421478</v>
+        <v>1.9745579957962</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G25" t="n">
-        <v>1.8744912147522</v>
+        <v>1.87449133396149</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G26" t="n">
-        <v>1.86885368824005</v>
+        <v>1.86885344982147</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G28" t="n">
-        <v>1.71100187301636</v>
+        <v>1.71100163459778</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G29" t="n">
-        <v>1.86039745807648</v>
+        <v>1.8603972196579</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G31" t="n">
-        <v>1.87731027603149</v>
+        <v>1.8773101568222</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G32" t="n">
-        <v>1.94777941703796</v>
+        <v>1.94777953624725</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G33" t="n">
-        <v>2.03657126426697</v>
+        <v>2.03657150268555</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G34" t="n">
-        <v>2.070396900177</v>
+        <v>2.07039666175842</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G36" t="n">
-        <v>2.09294676780701</v>
+        <v>2.09294700622559</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G37" t="n">
-        <v>2.15918827056885</v>
+        <v>2.15918803215027</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G38" t="n">
-        <v>2.16059732437134</v>
+        <v>2.1605978012085</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G40" t="n">
-        <v>2.06616830825806</v>
+        <v>2.06616806983948</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>2.05771207809448</v>
+        <v>2.05771231651306</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G42" t="n">
-        <v>2.06334972381592</v>
+        <v>2.0633499622345</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G45" t="n">
-        <v>2.13522887229919</v>
+        <v>2.13522863388062</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G47" t="n">
-        <v>2.14932250976562</v>
+        <v>2.14932227134705</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12113451957703</v>
+        <v>2.12113499641418</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>2.12818145751953</v>
+        <v>2.12818169593811</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G50" t="n">
-        <v>2.12677216529846</v>
+        <v>2.12677240371704</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G51" t="n">
-        <v>2.21274518966675</v>
+        <v>2.21274542808533</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G52" t="n">
-        <v>2.26348304748535</v>
+        <v>2.26348328590393</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G55" t="n">
-        <v>2.1859667301178</v>
+        <v>2.18596696853638</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G57" t="n">
-        <v>2.20147037506104</v>
+        <v>2.20147013664246</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G58" t="n">
-        <v>2.23670506477356</v>
+        <v>2.23670482635498</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>2.17751026153564</v>
+        <v>2.17751049995422</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3</v>
       </c>
       <c r="G60" t="n">
-        <v>2.11408758163452</v>
+        <v>2.11408805847168</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G61" t="n">
-        <v>2.18314814567566</v>
+        <v>2.18314790725708</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>2.12818145751953</v>
+        <v>2.12818169593811</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G63" t="n">
-        <v>1.97737681865692</v>
+        <v>1.97737658023834</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>1.98724257946014</v>
+        <v>1.98724246025085</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G69" t="n">
-        <v>1.98724257946014</v>
+        <v>1.98724246025085</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.97455823421478</v>
+        <v>1.9745579957962</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>1.92382025718689</v>
+        <v>1.92381989955902</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>1.98019564151764</v>
+        <v>1.98019552230835</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G74" t="n">
-        <v>2.06616830825806</v>
+        <v>2.06616806983948</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>2.17046356201172</v>
+        <v>2.17046332359314</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G77" t="n">
-        <v>2.14791345596313</v>
+        <v>2.14791321754456</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G78" t="n">
-        <v>2.17751026153564</v>
+        <v>2.17751049995422</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G80" t="n">
-        <v>2.12113451957703</v>
+        <v>2.12113499641418</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G82" t="n">
-        <v>2.05771207809448</v>
+        <v>2.05771231651306</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G83" t="n">
-        <v>2.02670574188232</v>
+        <v>2.02670526504517</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G84" t="n">
-        <v>1.98724257946014</v>
+        <v>1.98724246025085</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G85" t="n">
-        <v>1.94918918609619</v>
+        <v>1.94918894767761</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>1.97314858436584</v>
+        <v>1.97314846515656</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G87" t="n">
-        <v>1.95623600482941</v>
+        <v>1.9562361240387</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G88" t="n">
-        <v>1.89845061302185</v>
+        <v>1.89845073223114</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G89" t="n">
-        <v>1.86321592330933</v>
+        <v>1.86321604251862</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>1.8768789768219</v>
+        <v>1.87687909603119</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>1.74024832248688</v>
+        <v>1.74024820327759</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G93" t="n">
-        <v>1.68559598922729</v>
+        <v>1.68559587001801</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62662887573242</v>
+        <v>1.62662863731384</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G97" t="n">
-        <v>1.63957262039185</v>
+        <v>1.63957250118256</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.60361695289612</v>
+        <v>1.6036171913147</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.60361695289612</v>
+        <v>1.6036171913147</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G100" t="n">
-        <v>1.63957262039185</v>
+        <v>1.63957250118256</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G102" t="n">
-        <v>1.78914761543274</v>
+        <v>1.78914773464203</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G103" t="n">
-        <v>1.86249685287476</v>
+        <v>1.86249709129333</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G104" t="n">
-        <v>1.8337322473526</v>
+        <v>1.83373248577118</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G105" t="n">
-        <v>1.86249685287476</v>
+        <v>1.86249709129333</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G106" t="n">
-        <v>1.84092342853546</v>
+        <v>1.84092354774475</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>1.82654130458832</v>
+        <v>1.8265415430069</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G109" t="n">
-        <v>1.79490089416504</v>
+        <v>1.79490053653717</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G110" t="n">
-        <v>1.83517062664032</v>
+        <v>1.8351708650589</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G111" t="n">
-        <v>1.83948564529419</v>
+        <v>1.8394855260849</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>1.80640637874603</v>
+        <v>1.80640625953674</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G113" t="n">
-        <v>1.8049681186676</v>
+        <v>1.80496788024902</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G115" t="n">
-        <v>1.73305714130402</v>
+        <v>1.73305690288544</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G119" t="n">
-        <v>1.68559598922729</v>
+        <v>1.68559587001801</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G120" t="n">
-        <v>1.75606846809387</v>
+        <v>1.75606858730316</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G121" t="n">
-        <v>1.75319230556488</v>
+        <v>1.7531920671463</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G123" t="n">
-        <v>1.83804714679718</v>
+        <v>1.83804738521576</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G125" t="n">
-        <v>1.48999762535095</v>
+        <v>1.48999750614166</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G126" t="n">
-        <v>1.5302677154541</v>
+        <v>1.53026783466339</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G127" t="n">
-        <v>1.49431216716766</v>
+        <v>1.49431228637695</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>1.46698606014252</v>
+        <v>1.46698594093323</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G129" t="n">
-        <v>1.47561550140381</v>
+        <v>1.47561538219452</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G130" t="n">
-        <v>1.49287390708923</v>
+        <v>1.49287402629852</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G131" t="n">
-        <v>1.49862694740295</v>
+        <v>1.49862706661224</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G133" t="n">
-        <v>1.50869452953339</v>
+        <v>1.5086944103241</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G134" t="n">
-        <v>1.55615568161011</v>
+        <v>1.5561558008194</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G136" t="n">
-        <v>1.63238143920898</v>
+        <v>1.63238131999969</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G138" t="n">
-        <v>1.65395474433899</v>
+        <v>1.65395486354828</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G139" t="n">
-        <v>1.62087571620941</v>
+        <v>1.62087559700012</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G140" t="n">
-        <v>1.62087571620941</v>
+        <v>1.62087559700012</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.25</v>
       </c>
       <c r="G142" t="n">
-        <v>1.61799943447113</v>
+        <v>1.61799919605255</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.25</v>
       </c>
       <c r="G143" t="n">
-        <v>1.61799943447113</v>
+        <v>1.61799919605255</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G144" t="n">
-        <v>1.56190848350525</v>
+        <v>1.56190872192383</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G145" t="n">
-        <v>1.51300930976868</v>
+        <v>1.51300919055939</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.12599992752075</v>
       </c>
       <c r="G146" t="n">
-        <v>1.52882957458496</v>
+        <v>1.52882945537567</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G147" t="n">
-        <v>1.56766164302826</v>
+        <v>1.56766152381897</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39579391479492</v>
+        <v>1.3957941532135</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G155" t="n">
-        <v>1.43462598323822</v>
+        <v>1.43462610244751</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G156" t="n">
-        <v>1.44828915596008</v>
+        <v>1.44828903675079</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G157" t="n">
-        <v>1.48999762535095</v>
+        <v>1.48999750614166</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G158" t="n">
-        <v>1.48136818408966</v>
+        <v>1.48136830329895</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G161" t="n">
-        <v>1.50437998771667</v>
+        <v>1.5043797492981</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G162" t="n">
-        <v>1.50581812858582</v>
+        <v>1.50581800937653</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G163" t="n">
-        <v>1.49143576622009</v>
+        <v>1.4914356470108</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G164" t="n">
-        <v>1.5173237323761</v>
+        <v>1.51732385158539</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G165" t="n">
-        <v>1.53602075576782</v>
+        <v>1.53602051734924</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G167" t="n">
-        <v>1.54608833789825</v>
+        <v>1.54608821868896</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G170" t="n">
-        <v>1.51588547229767</v>
+        <v>1.51588559150696</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G171" t="n">
-        <v>1.50869452953339</v>
+        <v>1.5086944103241</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G174" t="n">
-        <v>1.56478524208069</v>
+        <v>1.5647851228714</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G175" t="n">
-        <v>1.54896461963654</v>
+        <v>1.54896473884583</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G176" t="n">
-        <v>1.55471742153168</v>
+        <v>1.55471754074097</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G178" t="n">
-        <v>1.54896461963654</v>
+        <v>1.54896473884583</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G179" t="n">
-        <v>1.50725626945496</v>
+        <v>1.50725615024567</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G180" t="n">
-        <v>1.49287390708923</v>
+        <v>1.49287402629852</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G181" t="n">
-        <v>1.49862694740295</v>
+        <v>1.49862706661224</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G182" t="n">
-        <v>1.46986222267151</v>
+        <v>1.4698623418808</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G187" t="n">
-        <v>1.48280644416809</v>
+        <v>1.4828063249588</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G188" t="n">
-        <v>1.48999762535095</v>
+        <v>1.48999750614166</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G190" t="n">
-        <v>1.46986222267151</v>
+        <v>1.4698623418808</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G191" t="n">
-        <v>1.48424458503723</v>
+        <v>1.48424446582794</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>1.46698606014252</v>
+        <v>1.46698594093323</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G193" t="n">
-        <v>1.46986222267151</v>
+        <v>1.4698623418808</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>1.46698606014252</v>
+        <v>1.46698594093323</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G197" t="n">
-        <v>1.54896461963654</v>
+        <v>1.54896473884583</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.25</v>
       </c>
       <c r="G199" t="n">
-        <v>1.61799943447113</v>
+        <v>1.61799919605255</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G204" t="n">
-        <v>1.68703413009644</v>
+        <v>1.68703389167786</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G206" t="n">
-        <v>1.72730386257172</v>
+        <v>1.72730422019958</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>1.74743914604187</v>
+        <v>1.74743926525116</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G211" t="n">
-        <v>1.75606846809387</v>
+        <v>1.75606858730316</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>1.74743914604187</v>
+        <v>1.74743926525116</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G214" t="n">
-        <v>1.71867477893829</v>
+        <v>1.71867489814758</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G216" t="n">
-        <v>1.58348190784454</v>
+        <v>1.58348166942596</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G217" t="n">
-        <v>1.55327928066254</v>
+        <v>1.55327951908112</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>1.46698606014252</v>
+        <v>1.46698594093323</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G222" t="n">
-        <v>1.43246865272522</v>
+        <v>1.43246877193451</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G223" t="n">
-        <v>1.42383944988251</v>
+        <v>1.42383933067322</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>1.40586173534393</v>
+        <v>1.40586161613464</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G225" t="n">
-        <v>1.45691847801208</v>
+        <v>1.45691859722137</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G227" t="n">
-        <v>1.41664814949036</v>
+        <v>1.41664838790894</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G228" t="n">
-        <v>1.39579391479492</v>
+        <v>1.3957941532135</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G230" t="n">
-        <v>1.35840034484863</v>
+        <v>1.35840022563934</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G232" t="n">
-        <v>1.34473729133606</v>
+        <v>1.34473717212677</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G233" t="n">
-        <v>1.3332314491272</v>
+        <v>1.33323132991791</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G235" t="n">
-        <v>1.30806243419647</v>
+        <v>1.30806255340576</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G236" t="n">
-        <v>1.32316386699677</v>
+        <v>1.32316398620605</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G237" t="n">
-        <v>1.34257984161377</v>
+        <v>1.34257996082306</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G238" t="n">
-        <v>1.3806928396225</v>
+        <v>1.38069272041321</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G240" t="n">
-        <v>1.4022661447525</v>
+        <v>1.40226590633392</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.95299994945526</v>
       </c>
       <c r="G241" t="n">
-        <v>1.40442323684692</v>
+        <v>1.40442335605621</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>1.46698606014252</v>
+        <v>1.46698594093323</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G244" t="n">
-        <v>1.44828915596008</v>
+        <v>1.44828903675079</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G247" t="n">
-        <v>1.55327928066254</v>
+        <v>1.55327951908112</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G248" t="n">
-        <v>1.53602075576782</v>
+        <v>1.53602051734924</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G250" t="n">
-        <v>1.54465007781982</v>
+        <v>1.54464983940125</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G251" t="n">
-        <v>1.5173237323761</v>
+        <v>1.51732385158539</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G252" t="n">
-        <v>1.54608833789825</v>
+        <v>1.54608821868896</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G253" t="n">
-        <v>1.56190848350525</v>
+        <v>1.56190872192383</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G257" t="n">
-        <v>1.5820437669754</v>
+        <v>1.58204388618469</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G258" t="n">
-        <v>1.60649347305298</v>
+        <v>1.60649371147156</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>1.64676356315613</v>
+        <v>1.64676380157471</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G261" t="n">
-        <v>1.65826952457428</v>
+        <v>1.65826940536499</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G262" t="n">
-        <v>1.66546034812927</v>
+        <v>1.66546046733856</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>1.66114580631256</v>
+        <v>1.66114592552185</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>1.66546034812927</v>
+        <v>1.66546046733856</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G265" t="n">
-        <v>1.65683102607727</v>
+        <v>1.65683126449585</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G266" t="n">
-        <v>1.67408990859985</v>
+        <v>1.67409002780914</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>1.697101354599</v>
+        <v>1.69710147380829</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G270" t="n">
-        <v>1.72442770004272</v>
+        <v>1.72442781925201</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G271" t="n">
-        <v>1.77476525306702</v>
+        <v>1.7747654914856</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G275" t="n">
-        <v>1.75463044643402</v>
+        <v>1.75463056564331</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>1.66114580631256</v>
+        <v>1.66114592552185</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G282" t="n">
-        <v>1.71436023712158</v>
+        <v>1.71436011791229</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.63957262039185</v>
+        <v>1.63957250118256</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G284" t="n">
-        <v>1.62087571620941</v>
+        <v>1.62087559700012</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G285" t="n">
-        <v>1.65395474433899</v>
+        <v>1.65395486354828</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>1.63957262039185</v>
+        <v>1.63957250118256</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G292" t="n">
-        <v>1.62375199794769</v>
+        <v>1.62375211715698</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G293" t="n">
-        <v>1.58635854721069</v>
+        <v>1.5863584280014</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G294" t="n">
-        <v>1.5173237323761</v>
+        <v>1.51732385158539</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G295" t="n">
-        <v>1.48136818408966</v>
+        <v>1.48136830329895</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G296" t="n">
-        <v>1.49143576622009</v>
+        <v>1.4914356470108</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G298" t="n">
-        <v>1.48280644416809</v>
+        <v>1.4828063249588</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>1.52451455593109</v>
+        <v>1.52451467514038</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G304" t="n">
-        <v>1.50150322914124</v>
+        <v>1.5015035867691</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G306" t="n">
-        <v>1.51157081127167</v>
+        <v>1.51157104969025</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G307" t="n">
-        <v>1.54465007781982</v>
+        <v>1.54464983940125</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>1.53889715671539</v>
+        <v>1.5388970375061</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G310" t="n">
-        <v>1.73305714130402</v>
+        <v>1.73305690288544</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>1.82654130458832</v>
+        <v>1.8265415430069</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G312" t="n">
-        <v>1.81503558158875</v>
+        <v>1.81503570079803</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>1.76901245117188</v>
+        <v>1.76901257038116</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G314" t="n">
-        <v>1.75750696659088</v>
+        <v>1.7575067281723</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G315" t="n">
-        <v>1.73305714130402</v>
+        <v>1.73305690288544</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>1.95166671276093</v>
+        <v>1.95166659355164</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G320" t="n">
-        <v>1.98043119907379</v>
+        <v>1.98043096065521</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G321" t="n">
-        <v>1.96604907512665</v>
+        <v>1.96604883670807</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G322" t="n">
-        <v>1.96317267417908</v>
+        <v>1.96317231655121</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G323" t="n">
-        <v>1.94303750991821</v>
+        <v>1.94303727149963</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G324" t="n">
-        <v>1.97467827796936</v>
+        <v>1.97467815876007</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G325" t="n">
-        <v>1.95885789394379</v>
+        <v>1.95885801315308</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.71199989318848</v>
       </c>
       <c r="G327" t="n">
-        <v>1.95022821426392</v>
+        <v>1.95022833347321</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G328" t="n">
-        <v>1.99625158309937</v>
+        <v>1.99625194072723</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>1.96317267417908</v>
+        <v>1.96317231655121</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>1.77620375156403</v>
+        <v>1.77620363235474</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G332" t="n">
-        <v>1.71004545688629</v>
+        <v>1.710045337677</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G333" t="n">
-        <v>1.7618213891983</v>
+        <v>1.76182150840759</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G334" t="n">
-        <v>1.8135974407196</v>
+        <v>1.81359767913818</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G335" t="n">
-        <v>1.79058575630188</v>
+        <v>1.79058599472046</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G337" t="n">
-        <v>1.90852010250092</v>
+        <v>1.90852022171021</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G341" t="n">
-        <v>1.7458610534668</v>
+        <v>1.74586093425751</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G342" t="n">
-        <v>1.70136153697968</v>
+        <v>1.70136141777039</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G344" t="n">
-        <v>1.72361123561859</v>
+        <v>1.7236111164093</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G345" t="n">
-        <v>1.67762875556946</v>
+        <v>1.67762851715088</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G347" t="n">
-        <v>1.76514399051666</v>
+        <v>1.76514410972595</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G350" t="n">
-        <v>1.71322798728943</v>
+        <v>1.71322786808014</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G351" t="n">
-        <v>1.70581138134003</v>
+        <v>1.70581150054932</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G352" t="n">
-        <v>1.68652844429016</v>
+        <v>1.68652832508087</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G356" t="n">
-        <v>1.67762875556946</v>
+        <v>1.67762851715088</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G357" t="n">
-        <v>1.73547780513763</v>
+        <v>1.73547768592834</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G358" t="n">
-        <v>1.72509431838989</v>
+        <v>1.72509443759918</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G361" t="n">
-        <v>1.69246172904968</v>
+        <v>1.69246184825897</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="n">
-        <v>1.68207848072052</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>1.69839477539062</v>
+        <v>1.6983950138092</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G366" t="n">
-        <v>1.69839477539062</v>
+        <v>1.6983950138092</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>1.69839477539062</v>
+        <v>1.6983950138092</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G368" t="n">
-        <v>1.72212791442871</v>
+        <v>1.72212779521942</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G370" t="n">
-        <v>1.70136153697968</v>
+        <v>1.70136141777039</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G373" t="n">
-        <v>1.68207848072052</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G374" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G378" t="n">
-        <v>1.67762875556946</v>
+        <v>1.67762851715088</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G379" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>1.75031077861786</v>
+        <v>1.75031089782715</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G385" t="n">
-        <v>1.75921082496643</v>
+        <v>1.75921058654785</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G386" t="n">
-        <v>1.75921082496643</v>
+        <v>1.75921058654785</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G387" t="n">
-        <v>1.73696100711823</v>
+        <v>1.7369612455368</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>1.69839477539062</v>
+        <v>1.6983950138092</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G394" t="n">
-        <v>1.7087779045105</v>
+        <v>1.70877802371979</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G395" t="n">
-        <v>1.70581138134003</v>
+        <v>1.70581150054932</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G396" t="n">
-        <v>1.72212791442871</v>
+        <v>1.72212779521942</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G397" t="n">
-        <v>1.70136153697968</v>
+        <v>1.70136141777039</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G398" t="n">
-        <v>1.71322798728943</v>
+        <v>1.71322786808014</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G400" t="n">
-        <v>1.68949496746063</v>
+        <v>1.68949508666992</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G402" t="n">
-        <v>1.67762875556946</v>
+        <v>1.67762851715088</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G405" t="n">
-        <v>1.64351212978363</v>
+        <v>1.64351236820221</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G406" t="n">
-        <v>1.63312888145447</v>
+        <v>1.63312876224518</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>1.59456300735474</v>
+        <v>1.59456288814545</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G408" t="n">
-        <v>1.61384618282318</v>
+        <v>1.61384606361389</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G409" t="n">
-        <v>1.5915961265564</v>
+        <v>1.59159600734711</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G410" t="n">
-        <v>1.61087930202484</v>
+        <v>1.61087942123413</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G411" t="n">
-        <v>1.68207848072052</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G413" t="n">
-        <v>1.67762875556946</v>
+        <v>1.67762851715088</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G414" t="n">
-        <v>1.65686202049255</v>
+        <v>1.65686213970184</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G415" t="n">
-        <v>1.67466175556183</v>
+        <v>1.67466187477112</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G417" t="n">
-        <v>1.63312888145447</v>
+        <v>1.63312876224518</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G419" t="n">
-        <v>1.60494601726532</v>
+        <v>1.60494613647461</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G420" t="n">
-        <v>1.59752941131592</v>
+        <v>1.5975296497345</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G422" t="n">
-        <v>1.60197949409485</v>
+        <v>1.60197961330414</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>1.59456300735474</v>
+        <v>1.59456288814545</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G426" t="n">
-        <v>1.55896329879761</v>
+        <v>1.5589634180069</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G427" t="n">
-        <v>1.58269643783569</v>
+        <v>1.5826963186264</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G428" t="n">
-        <v>1.60049617290497</v>
+        <v>1.60049629211426</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G429" t="n">
-        <v>1.5915961265564</v>
+        <v>1.59159600734711</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G430" t="n">
-        <v>1.58714628219604</v>
+        <v>1.58714640140533</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G432" t="n">
-        <v>1.58121311664581</v>
+        <v>1.58121299743652</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G433" t="n">
-        <v>1.56786322593689</v>
+        <v>1.56786346435547</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>1.59456300735474</v>
+        <v>1.59456288814545</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G435" t="n">
-        <v>1.5990127325058</v>
+        <v>1.59901285171509</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G436" t="n">
-        <v>1.58121311664581</v>
+        <v>1.58121299743652</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G438" t="n">
-        <v>1.56192982196808</v>
+        <v>1.56192994117737</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G442" t="n">
-        <v>1.59307968616486</v>
+        <v>1.59307944774628</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G443" t="n">
-        <v>1.57379627227783</v>
+        <v>1.57379651069641</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>1.58714628219604</v>
+        <v>1.58714640140533</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G446" t="n">
-        <v>1.57972991466522</v>
+        <v>1.57972979545593</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G450" t="n">
-        <v>1.74882769584656</v>
+        <v>1.74882757663727</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G452" t="n">
-        <v>1.70136153697968</v>
+        <v>1.70136141777039</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G453" t="n">
-        <v>1.72509431838989</v>
+        <v>1.72509443759918</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G455" t="n">
-        <v>1.74437761306763</v>
+        <v>1.74437773227692</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G457" t="n">
-        <v>1.79629373550415</v>
+        <v>1.79629361629486</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>1.8393098115921</v>
+        <v>1.83930957317352</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G460" t="n">
-        <v>1.93720841407776</v>
+        <v>1.93720865249634</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.5</v>
       </c>
       <c r="G462" t="n">
-        <v>1.85414290428162</v>
+        <v>1.85414302349091</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G463" t="n">
-        <v>1.90605890750885</v>
+        <v>1.90605878829956</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.87490952014923</v>
+        <v>1.87490940093994</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G465" t="n">
-        <v>1.89122533798218</v>
+        <v>1.89122569561005</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G466" t="n">
-        <v>1.91199231147766</v>
+        <v>1.91199219226837</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G467" t="n">
-        <v>1.93572497367859</v>
+        <v>1.93572509288788</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G469" t="n">
-        <v>1.78887712955475</v>
+        <v>1.78887701034546</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G471" t="n">
-        <v>1.82892644405365</v>
+        <v>1.82892656326294</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G472" t="n">
-        <v>1.78887712955475</v>
+        <v>1.78887701034546</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G473" t="n">
-        <v>1.76514399051666</v>
+        <v>1.76514410972595</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G478" t="n">
-        <v>1.64054560661316</v>
+        <v>1.64054572582245</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G480" t="n">
-        <v>1.61829578876495</v>
+        <v>1.61829590797424</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G481" t="n">
-        <v>1.60049617290497</v>
+        <v>1.60049629211426</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G482" t="n">
-        <v>1.61681270599365</v>
+        <v>1.61681258678436</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G484" t="n">
-        <v>1.64796209335327</v>
+        <v>1.64796221256256</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G485" t="n">
-        <v>1.68652844429016</v>
+        <v>1.68652832508087</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G486" t="n">
-        <v>1.67021203041077</v>
+        <v>1.67021191120148</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.25</v>
       </c>
       <c r="G488" t="n">
-        <v>1.66872870922089</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G490" t="n">
-        <v>1.68207848072052</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G491" t="n">
-        <v>1.66724514961243</v>
+        <v>1.66724538803101</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G492" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G493" t="n">
-        <v>1.66131186485291</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G494" t="n">
-        <v>1.68652844429016</v>
+        <v>1.68652832508087</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G495" t="n">
-        <v>1.68949496746063</v>
+        <v>1.68949508666992</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G496" t="n">
-        <v>1.68949496746063</v>
+        <v>1.68949508666992</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.25</v>
       </c>
       <c r="G497" t="n">
-        <v>1.66872870922089</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G498" t="n">
-        <v>1.68949496746063</v>
+        <v>1.68949508666992</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G499" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G501" t="n">
-        <v>1.68207848072052</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G502" t="n">
-        <v>1.67466175556183</v>
+        <v>1.67466187477112</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G504" t="n">
-        <v>1.66724514961243</v>
+        <v>1.66724538803101</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G505" t="n">
-        <v>1.65834558010101</v>
+        <v>1.65834546089172</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>1.69839477539062</v>
+        <v>1.6983950138092</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G511" t="n">
-        <v>1.68207848072052</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G512" t="n">
-        <v>1.67466175556183</v>
+        <v>1.67466187477112</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G516" t="n">
-        <v>1.70581138134003</v>
+        <v>1.70581150054932</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G517" t="n">
-        <v>1.77256059646606</v>
+        <v>1.77256071567535</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G518" t="n">
-        <v>1.75031077861786</v>
+        <v>1.75031089782715</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G519" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.375</v>
       </c>
       <c r="G520" t="n">
-        <v>1.76143550872803</v>
+        <v>1.7614358663559</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>1.79110205173492</v>
+        <v>1.79110193252563</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76514399051666</v>
+        <v>1.76514410972595</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.74660277366638</v>
+        <v>1.7466025352478</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G525" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G526" t="n">
-        <v>1.79110205173492</v>
+        <v>1.79110193252563</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G527" t="n">
-        <v>1.78739380836487</v>
+        <v>1.78739368915558</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G528" t="n">
-        <v>1.77256059646606</v>
+        <v>1.77256071567535</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>1.79481053352356</v>
+        <v>1.79481029510498</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G531" t="n">
-        <v>1.82818472385406</v>
+        <v>1.82818484306335</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G532" t="n">
-        <v>1.77256059646606</v>
+        <v>1.77256071567535</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>1.74289429187775</v>
+        <v>1.74289417266846</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G534" t="n">
-        <v>1.70951986312866</v>
+        <v>1.70951974391937</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.25</v>
       </c>
       <c r="G539" t="n">
-        <v>1.66872870922089</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G540" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G541" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G542" t="n">
-        <v>1.62052094936371</v>
+        <v>1.62052083015442</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>1.63906240463257</v>
+        <v>1.63906216621399</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G544" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G545" t="n">
-        <v>1.69468677043915</v>
+        <v>1.69468665122986</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G546" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G547" t="n">
-        <v>1.67243695259094</v>
+        <v>1.67243683338165</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G549" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>1.66131186485291</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.25</v>
       </c>
       <c r="G553" t="n">
-        <v>1.66872870922089</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G554" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>1.65018713474274</v>
+        <v>1.65018725395203</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G559" t="n">
-        <v>1.64647889137268</v>
+        <v>1.64647901058197</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.25</v>
       </c>
       <c r="G560" t="n">
-        <v>1.66872870922089</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G561" t="n">
-        <v>1.69468677043915</v>
+        <v>1.69468665122986</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G563" t="n">
-        <v>1.66131186485291</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G564" t="n">
-        <v>1.67243695259094</v>
+        <v>1.67243683338165</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.25</v>
       </c>
       <c r="G565" t="n">
-        <v>1.66872870922089</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.25</v>
       </c>
       <c r="G566" t="n">
-        <v>1.66872870922089</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.25</v>
       </c>
       <c r="G567" t="n">
-        <v>1.66872870922089</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G568" t="n">
-        <v>1.67243695259094</v>
+        <v>1.67243683338165</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>1.63906240463257</v>
+        <v>1.63906216621399</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.25</v>
       </c>
       <c r="G570" t="n">
-        <v>1.66872870922089</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G571" t="n">
-        <v>1.64647889137268</v>
+        <v>1.64647901058197</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.25</v>
       </c>
       <c r="G573" t="n">
-        <v>1.66872870922089</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G574" t="n">
-        <v>1.66131186485291</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G575" t="n">
-        <v>1.67243695259094</v>
+        <v>1.67243683338165</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G576" t="n">
-        <v>1.64647889137268</v>
+        <v>1.64647901058197</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>1.68726992607117</v>
+        <v>1.68727016448975</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>1.70210313796997</v>
+        <v>1.70210325717926</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.69839477539062</v>
+        <v>1.6983950138092</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G581" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.25</v>
       </c>
       <c r="G583" t="n">
-        <v>1.66872870922089</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G584" t="n">
-        <v>1.67243695259094</v>
+        <v>1.67243683338165</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>1.6835618019104</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.25</v>
       </c>
       <c r="G586" t="n">
-        <v>1.66872870922089</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G587" t="n">
-        <v>1.64647889137268</v>
+        <v>1.64647901058197</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G588" t="n">
-        <v>1.66131186485291</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>1.66131186485291</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.25</v>
       </c>
       <c r="G590" t="n">
-        <v>1.66872870922089</v>
+        <v>1.6687285900116</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G591" t="n">
-        <v>1.66131186485291</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G592" t="n">
-        <v>1.65389549732208</v>
+        <v>1.65389561653137</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G593" t="n">
-        <v>1.69839477539062</v>
+        <v>1.6983950138092</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>1.70581138134003</v>
+        <v>1.70581150054932</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G596" t="n">
-        <v>1.69468677043915</v>
+        <v>1.69468665122986</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>1.70210313796997</v>
+        <v>1.70210325717926</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G601" t="n">
-        <v>1.72598946094513</v>
+        <v>1.72598969936371</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.25</v>
       </c>
       <c r="G602" t="n">
-        <v>1.73369514942169</v>
+        <v>1.73369491100311</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>1.70287382602692</v>
+        <v>1.70287358760834</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G606" t="n">
-        <v>1.64893662929535</v>
+        <v>1.64893651008606</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G607" t="n">
-        <v>1.55262041091919</v>
+        <v>1.55262017250061</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G608" t="n">
-        <v>1.55262041091919</v>
+        <v>1.55262017250061</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G609" t="n">
-        <v>1.49791252613068</v>
+        <v>1.49791240692139</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G611" t="n">
-        <v>1.53489792346954</v>
+        <v>1.53489804267883</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G612" t="n">
-        <v>1.52102851867676</v>
+        <v>1.52102839946747</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G615" t="n">
-        <v>1.51024103164673</v>
+        <v>1.51024091243744</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G618" t="n">
-        <v>1.49791252613068</v>
+        <v>1.49791240692139</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G619" t="n">
-        <v>1.49174833297729</v>
+        <v>1.49174809455872</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G621" t="n">
-        <v>1.58344149589539</v>
+        <v>1.5834413766861</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G622" t="n">
-        <v>1.55647277832031</v>
+        <v>1.55647265911102</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G625" t="n">
-        <v>1.62196803092957</v>
+        <v>1.62196791172028</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>1.62196803092957</v>
+        <v>1.62196791172028</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G627" t="n">
-        <v>1.59499931335449</v>
+        <v>1.5949991941452</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.65664196014404</v>
+        <v>1.65664184093475</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>1.6027045249939</v>
+        <v>1.60270464420319</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G634" t="n">
-        <v>1.55647277832031</v>
+        <v>1.55647265911102</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>1.5603255033493</v>
+        <v>1.56032562255859</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>1.5872939825058</v>
+        <v>1.58729410171509</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>1.59499931335449</v>
+        <v>1.5949991941452</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G641" t="n">
-        <v>1.5872939825058</v>
+        <v>1.58729410171509</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G642" t="n">
-        <v>1.59499931335449</v>
+        <v>1.5949991941452</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>1.62196803092957</v>
+        <v>1.62196791172028</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>1.59499931335449</v>
+        <v>1.5949991941452</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>1.60655736923218</v>
+        <v>1.60655748844147</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G648" t="n">
-        <v>1.58344149589539</v>
+        <v>1.5834413766861</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G649" t="n">
-        <v>1.59499931335449</v>
+        <v>1.5949991941452</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>1.58344149589539</v>
+        <v>1.5834413766861</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G658" t="n">
-        <v>1.66049444675446</v>
+        <v>1.66049456596375</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G660" t="n">
-        <v>1.62196803092957</v>
+        <v>1.62196791172028</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G664" t="n">
-        <v>1.58344149589539</v>
+        <v>1.5834413766861</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G665" t="n">
-        <v>1.5872939825058</v>
+        <v>1.58729410171509</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G666" t="n">
-        <v>1.58344149589539</v>
+        <v>1.5834413766861</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G672" t="n">
-        <v>1.52102851867676</v>
+        <v>1.52102839946747</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G674" t="n">
-        <v>1.55262041091919</v>
+        <v>1.55262017250061</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G675" t="n">
-        <v>1.53489792346954</v>
+        <v>1.53489804267883</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G676" t="n">
-        <v>1.5872939825058</v>
+        <v>1.58729410171509</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>1.5603255033493</v>
+        <v>1.56032562255859</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G679" t="n">
-        <v>1.55647277832031</v>
+        <v>1.55647265911102</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G696" t="n">
-        <v>1.5872939825058</v>
+        <v>1.58729410171509</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>1.65664196014404</v>
+        <v>1.65664184093475</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G704" t="n">
-        <v>1.55262041091919</v>
+        <v>1.55262017250061</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G707" t="n">
-        <v>1.47479665279388</v>
+        <v>1.47479653358459</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G708" t="n">
-        <v>1.49328935146332</v>
+        <v>1.49328911304474</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G710" t="n">
-        <v>1.42548251152039</v>
+        <v>1.42548274993896</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G711" t="n">
-        <v>1.43472898006439</v>
+        <v>1.4347288608551</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G712" t="n">
-        <v>1.41777729988098</v>
+        <v>1.41777718067169</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G715" t="n">
-        <v>1.44089329242706</v>
+        <v>1.44089317321777</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G716" t="n">
-        <v>1.39157915115356</v>
+        <v>1.39157927036285</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G719" t="n">
-        <v>1.21281611919403</v>
+        <v>1.21281576156616</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G720" t="n">
-        <v>1.25288343429565</v>
+        <v>1.25288367271423</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G721" t="n">
-        <v>1.2420961856842</v>
+        <v>1.24209606647491</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G722" t="n">
-        <v>1.29911553859711</v>
+        <v>1.29911541938782</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G725" t="n">
-        <v>1.30990290641785</v>
+        <v>1.30990278720856</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G727" t="n">
-        <v>1.29295122623444</v>
+        <v>1.29295110702515</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G728" t="n">
-        <v>1.29911553859711</v>
+        <v>1.29911541938782</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G730" t="n">
-        <v>1.30682063102722</v>
+        <v>1.30682075023651</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G731" t="n">
-        <v>1.29757452011108</v>
+        <v>1.2975742816925</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G732" t="n">
-        <v>1.28370487689972</v>
+        <v>1.28370475769043</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G734" t="n">
-        <v>1.23747289180756</v>
+        <v>1.23747301101685</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G735" t="n">
-        <v>1.18353569507599</v>
+        <v>1.18353581428528</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G736" t="n">
-        <v>1.19278204441071</v>
+        <v>1.19278216362</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.5460000038147</v>
       </c>
       <c r="G738" t="n">
-        <v>1.19124102592468</v>
+        <v>1.19124114513397</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G740" t="n">
-        <v>1.1373039484024</v>
+        <v>1.13730382919312</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G745" t="n">
-        <v>1.27137625217438</v>
+        <v>1.27137613296509</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G746" t="n">
-        <v>1.23747289180756</v>
+        <v>1.23747301101685</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G750" t="n">
-        <v>1.24363708496094</v>
+        <v>1.24363720417023</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G754" t="n">
-        <v>1.18045365810394</v>
+        <v>1.18045353889465</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G756" t="n">
-        <v>1.15733766555786</v>
+        <v>1.15733778476715</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G758" t="n">
-        <v>1.0956951379776</v>
+        <v>1.09569525718689</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G762" t="n">
-        <v>1.08182561397552</v>
+        <v>1.0818258523941</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G763" t="n">
-        <v>1.10802376270294</v>
+        <v>1.10802364349365</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G765" t="n">
-        <v>1.13576281070709</v>
+        <v>1.13576292991638</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G766" t="n">
-        <v>1.15733766555786</v>
+        <v>1.15733778476715</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G767" t="n">
-        <v>1.15117347240448</v>
+        <v>1.15117335319519</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.5</v>
       </c>
       <c r="G768" t="n">
-        <v>1.15579664707184</v>
+        <v>1.15579676628113</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G770" t="n">
-        <v>1.15425550937653</v>
+        <v>1.15425562858582</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.5</v>
       </c>
       <c r="G771" t="n">
-        <v>1.15579664707184</v>
+        <v>1.15579676628113</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G772" t="n">
-        <v>1.15117347240448</v>
+        <v>1.15117335319519</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G775" t="n">
-        <v>1.14655029773712</v>
+        <v>1.14655041694641</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G776" t="n">
-        <v>1.15117347240448</v>
+        <v>1.15117335319519</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>1.5</v>
       </c>
       <c r="G777" t="n">
-        <v>1.15579664707184</v>
+        <v>1.15579676628113</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G778" t="n">
-        <v>1.14655029773712</v>
+        <v>1.14655041694641</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G779" t="n">
-        <v>1.13268065452576</v>
+        <v>1.13268077373505</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G781" t="n">
-        <v>1.13268065452576</v>
+        <v>1.13268077373505</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G782" t="n">
-        <v>1.12651658058167</v>
+        <v>1.12651646137238</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G783" t="n">
-        <v>1.10956490039825</v>
+        <v>1.10956478118896</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G784" t="n">
-        <v>1.10802376270294</v>
+        <v>1.10802364349365</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G787" t="n">
-        <v>1.06641507148743</v>
+        <v>1.06641495227814</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G788" t="n">
-        <v>1.06641507148743</v>
+        <v>1.06641495227814</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G789" t="n">
-        <v>1.13884508609772</v>
+        <v>1.13884496688843</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G792" t="n">
-        <v>1.15425550937653</v>
+        <v>1.15425562858582</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G793" t="n">
-        <v>1.17428958415985</v>
+        <v>1.17428946495056</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G797" t="n">
-        <v>1.24671947956085</v>
+        <v>1.24671924114227</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G799" t="n">
-        <v>1.24363708496094</v>
+        <v>1.24363720417023</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G800" t="n">
-        <v>1.24363708496094</v>
+        <v>1.24363720417023</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G804" t="n">
-        <v>1.2420961856842</v>
+        <v>1.24209606647491</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G806" t="n">
-        <v>1.30219757556915</v>
+        <v>1.30219769477844</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G809" t="n">
-        <v>1.27754044532776</v>
+        <v>1.27754056453705</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G812" t="n">
-        <v>1.18199467658997</v>
+        <v>1.18199479579926</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G813" t="n">
-        <v>1.16504299640656</v>
+        <v>1.16504311561584</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G814" t="n">
-        <v>1.16504299640656</v>
+        <v>1.16504311561584</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G816" t="n">
-        <v>1.16658401489258</v>
+        <v>1.16658413410187</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G817" t="n">
-        <v>1.16658401489258</v>
+        <v>1.16658413410187</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G818" t="n">
-        <v>1.16504299640656</v>
+        <v>1.16504311561584</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.5</v>
       </c>
       <c r="G819" t="n">
-        <v>1.15579664707184</v>
+        <v>1.15579676628113</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G821" t="n">
-        <v>1.13576281070709</v>
+        <v>1.13576292991638</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G823" t="n">
-        <v>1.14192712306976</v>
+        <v>1.14192700386047</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G824" t="n">
-        <v>1.13422167301178</v>
+        <v>1.13422191143036</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G825" t="n">
-        <v>1.15425550937653</v>
+        <v>1.15425562858582</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>1.5</v>
       </c>
       <c r="G826" t="n">
-        <v>1.15579664707184</v>
+        <v>1.15579676628113</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.5</v>
       </c>
       <c r="G829" t="n">
-        <v>1.15579664707184</v>
+        <v>1.15579676628113</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G830" t="n">
-        <v>1.15733766555786</v>
+        <v>1.15733778476715</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.5</v>
       </c>
       <c r="G831" t="n">
-        <v>1.15579664707184</v>
+        <v>1.15579676628113</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G834" t="n">
-        <v>1.19586431980133</v>
+        <v>1.19586420059204</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G837" t="n">
-        <v>1.29295122623444</v>
+        <v>1.29295110702515</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G838" t="n">
-        <v>1.30836176872253</v>
+        <v>1.30836188793182</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G840" t="n">
-        <v>1.29295122623444</v>
+        <v>1.29295110702515</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G843" t="n">
-        <v>1.27137625217438</v>
+        <v>1.27137613296509</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G845" t="n">
-        <v>1.28832805156708</v>
+        <v>1.28832793235779</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G847" t="n">
-        <v>1.28986895084381</v>
+        <v>1.2898690700531</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G848" t="n">
-        <v>1.33944821357727</v>
+        <v>1.33944809436798</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G851" t="n">
-        <v>1.24028992652893</v>
+        <v>1.24029004573822</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.5</v>
       </c>
       <c r="G852" t="n">
-        <v>1.21915793418884</v>
+        <v>1.21915781497955</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G855" t="n">
-        <v>1.14113175868988</v>
+        <v>1.14113187789917</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G856" t="n">
-        <v>1.11512303352356</v>
+        <v>1.11512315273285</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G858" t="n">
-        <v>1.11349761486053</v>
+        <v>1.11349749565125</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G864" t="n">
-        <v>1.07285892963409</v>
+        <v>1.07285904884338</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G865" t="n">
-        <v>1.05010139942169</v>
+        <v>1.05010151863098</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G866" t="n">
-        <v>1.00133502483368</v>
+        <v>1.00133490562439</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G869" t="n">
-        <v>1.01271390914917</v>
+        <v>1.01271378993988</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G870" t="n">
-        <v>1.03222036361694</v>
+        <v>1.03222024440765</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G873" t="n">
-        <v>0.967198610305786</v>
+        <v>0.967198550701141</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G874" t="n">
-        <v>0.972075164318085</v>
+        <v>0.97207510471344</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G875" t="n">
-        <v>0.95581978559494</v>
+        <v>0.955819845199585</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G877" t="n">
-        <v>0.91193014383316</v>
+        <v>0.911930084228516</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>0.910304486751556</v>
+        <v>0.910304546356201</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G880" t="n">
-        <v>0.924934387207031</v>
+        <v>0.924934506416321</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G882" t="n">
-        <v>0.950943112373352</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G883" t="n">
-        <v>0.957445383071899</v>
+        <v>0.957445323467255</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G884" t="n">
-        <v>0.939564347267151</v>
+        <v>0.939564406871796</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G886" t="n">
-        <v>0.95581978559494</v>
+        <v>0.955819845199585</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G887" t="n">
-        <v>0.965573012828827</v>
+        <v>0.965573072433472</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G888" t="n">
-        <v>0.965573012828827</v>
+        <v>0.965573072433472</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G889" t="n">
-        <v>0.983454167842865</v>
+        <v>0.98345410823822</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G891" t="n">
-        <v>0.988330721855164</v>
+        <v>0.988330602645874</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>1.03222036361694</v>
+        <v>1.03222024440765</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G894" t="n">
-        <v>1.04034793376923</v>
+        <v>1.04034805297852</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G896" t="n">
-        <v>1.03059470653534</v>
+        <v>1.03059482574463</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G898" t="n">
-        <v>1.01271390914917</v>
+        <v>1.01271378993988</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G900" t="n">
-        <v>0.994832754135132</v>
+        <v>0.994832873344421</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G901" t="n">
-        <v>0.981828451156616</v>
+        <v>0.981828391551971</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G902" t="n">
-        <v>1.01271390914917</v>
+        <v>1.01271378993988</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G903" t="n">
-        <v>0.991581797599792</v>
+        <v>0.991581678390503</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G904" t="n">
-        <v>0.983454167842865</v>
+        <v>0.98345410823822</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G905" t="n">
-        <v>1.00133502483368</v>
+        <v>1.00133490562439</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.02409267425537</v>
+        <v>1.02409255504608</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G907" t="n">
-        <v>1.03222036361694</v>
+        <v>1.03222024440765</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G908" t="n">
-        <v>1.02246713638306</v>
+        <v>1.02246701717377</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G912" t="n">
-        <v>1.02409267425537</v>
+        <v>1.02409255504608</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G913" t="n">
-        <v>1.02409267425537</v>
+        <v>1.02409255504608</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>0.950943112373352</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G920" t="n">
-        <v>0.952568829059601</v>
+        <v>0.952568709850311</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G921" t="n">
-        <v>0.920057773590088</v>
+        <v>0.920057892799377</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G923" t="n">
-        <v>0.954194307327271</v>
+        <v>0.954194247722626</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G925" t="n">
-        <v>0.967198610305786</v>
+        <v>0.967198550701141</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G926" t="n">
-        <v>0.981828451156616</v>
+        <v>0.981828391551971</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G927" t="n">
-        <v>0.978577375411987</v>
+        <v>0.978577435016632</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>0.975326359272003</v>
+        <v>0.975326478481293</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G929" t="n">
-        <v>0.973700761795044</v>
+        <v>0.973700821399689</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G930" t="n">
-        <v>0.972075164318085</v>
+        <v>0.97207510471344</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G931" t="n">
-        <v>0.985079526901245</v>
+        <v>0.98507958650589</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G932" t="n">
-        <v>0.980202853679657</v>
+        <v>0.980202913284302</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G933" t="n">
-        <v>0.965573012828827</v>
+        <v>0.965573072433472</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G934" t="n">
-        <v>0.950943112373352</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.04034793376923</v>
+        <v>1.04034805297852</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G937" t="n">
-        <v>1.02409267425537</v>
+        <v>1.02409255504608</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G938" t="n">
-        <v>1.09236538410187</v>
+        <v>1.09236550331116</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G939" t="n">
-        <v>1.14275741577148</v>
+        <v>1.14275729656219</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G942" t="n">
-        <v>1.19640016555786</v>
+        <v>1.19640028476715</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G943" t="n">
-        <v>1.2029025554657</v>
+        <v>1.20290231704712</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G945" t="n">
-        <v>1.21753227710724</v>
+        <v>1.21753239631653</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G948" t="n">
-        <v>1.18014490604401</v>
+        <v>1.18014478683472</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G952" t="n">
-        <v>1.14925968647003</v>
+        <v>1.14925956726074</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G954" t="n">
-        <v>1.13462960720062</v>
+        <v>1.13462972640991</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G961" t="n">
-        <v>1.13462960720062</v>
+        <v>1.13462972640991</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G962" t="n">
-        <v>1.17039167881012</v>
+        <v>1.17039155960083</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G963" t="n">
-        <v>1.17364275455475</v>
+        <v>1.17364263534546</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G965" t="n">
-        <v>1.17039167881012</v>
+        <v>1.17039155960083</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G969" t="n">
-        <v>1.18502151966095</v>
+        <v>1.18502140045166</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G971" t="n">
-        <v>1.17039167881012</v>
+        <v>1.17039155960083</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G976" t="n">
-        <v>1.31018841266632</v>
+        <v>1.31018829345703</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G977" t="n">
-        <v>1.36058020591736</v>
+        <v>1.36058032512665</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G978" t="n">
-        <v>1.38008666038513</v>
+        <v>1.38008677959442</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G981" t="n">
-        <v>1.38008666038513</v>
+        <v>1.38008677959442</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G985" t="n">
-        <v>1.34920132160187</v>
+        <v>1.34920144081116</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>1.39796781539917</v>
+        <v>1.39796769618988</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G991" t="n">
-        <v>1.51988363265991</v>
+        <v>1.51988351345062</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G992" t="n">
-        <v>1.52150893211365</v>
+        <v>1.52150905132294</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G993" t="n">
-        <v>1.52313458919525</v>
+        <v>1.52313446998596</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G995" t="n">
-        <v>1.52801120281219</v>
+        <v>1.52801132202148</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G996" t="n">
-        <v>1.50037693977356</v>
+        <v>1.50037682056427</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G999" t="n">
-        <v>1.45486176013947</v>
+        <v>1.45486164093018</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.48412156105042</v>
+        <v>1.48412144184113</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.51500689983368</v>
+        <v>1.51500678062439</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.55401992797852</v>
+        <v>1.55401980876923</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.60116052627563</v>
+        <v>1.60116076469421</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.58327960968018</v>
+        <v>1.58327972888947</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.54426670074463</v>
+        <v>1.54426658153534</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.51988363265991</v>
+        <v>1.51988351345062</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.51663243770599</v>
+        <v>1.51663255691528</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.52150893211365</v>
+        <v>1.52150905132294</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.4694916009903</v>
+        <v>1.46949148178101</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.46624052524567</v>
+        <v>1.46624064445496</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.46298933029175</v>
+        <v>1.46298944950104</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.49712586402893</v>
+        <v>1.49712598323822</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.46298933029175</v>
+        <v>1.46298944950104</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.46786606311798</v>
+        <v>1.46786618232727</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.48737263679504</v>
+        <v>1.48737275600433</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.46624052524567</v>
+        <v>1.46624064445496</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.48737263679504</v>
+        <v>1.48737275600433</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.45323634147644</v>
+        <v>1.45323622226715</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.37358462810516</v>
+        <v>1.37358450889587</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.40284430980682</v>
+        <v>1.40284442901611</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.43047857284546</v>
+        <v>1.43047869205475</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.48737263679504</v>
+        <v>1.48737275600433</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.4938747882843</v>
+        <v>1.49387490749359</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.49550044536591</v>
+        <v>1.49550032615662</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.58002865314484</v>
+        <v>1.58002853393555</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.5979095697403</v>
+        <v>1.59790945053101</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.61416506767273</v>
+        <v>1.61416494846344</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.64179921150208</v>
+        <v>1.64179933071136</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.7393319606781</v>
+        <v>1.73933207988739</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.51988363265991</v>
+        <v>1.51988351345062</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.4938747882843</v>
+        <v>1.49387490749359</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.45486176013947</v>
+        <v>1.45486164093018</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.39796781539917</v>
+        <v>1.39796769618988</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.34920132160187</v>
+        <v>1.34920144081116</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.28580510616302</v>
+        <v>1.2858053445816</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.20777916908264</v>
+        <v>1.20777904987335</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.02409267425537</v>
+        <v>1.02409255504608</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.978577375411987</v>
+        <v>0.978577435016632</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.970449686050415</v>
+        <v>0.97044962644577</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.902176856994629</v>
+        <v>0.902176797389984</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.817648589611053</v>
+        <v>0.817648649215698</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.845282733440399</v>
+        <v>0.845282793045044</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.820899605751038</v>
+        <v>0.820899665355682</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.861538171768188</v>
+        <v>0.861538231372833</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.950943112373352</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.94281542301178</v>
+        <v>0.942815482616425</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.92655998468399</v>
+        <v>0.926559925079346</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.881044805049896</v>
+        <v>0.881044745445251</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.921683371067047</v>
+        <v>0.921683311462402</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.983454167842865</v>
+        <v>0.98345410823822</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.965573012828827</v>
+        <v>0.965573072433472</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.978577375411987</v>
+        <v>0.978577435016632</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.04685032367706</v>
+        <v>1.04685020446777</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.978577375411987</v>
+        <v>0.978577435016632</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.02246713638306</v>
+        <v>1.02246701717377</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.28199994564056</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.04197359085083</v>
+        <v>1.04197347164154</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.04522466659546</v>
+        <v>1.04522478580475</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.08098673820496</v>
+        <v>1.08098661899567</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.08098673820496</v>
+        <v>1.08098661899567</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.05010139942169</v>
+        <v>1.05010151863098</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.0387225151062</v>
+        <v>1.03872263431549</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.03059470653534</v>
+        <v>1.03059482574463</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.04034793376923</v>
+        <v>1.04034805297852</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.980202853679657</v>
+        <v>0.980202913284302</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.980202853679657</v>
+        <v>0.980202913284302</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.01271390914917</v>
+        <v>1.01271378993988</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.970449686050415</v>
+        <v>0.97044962644577</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.970449686050415</v>
+        <v>0.97044962644577</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.975326359272003</v>
+        <v>0.975326478481293</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.99970942735672</v>
+        <v>0.999709486961365</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.03222036361694</v>
+        <v>1.03222024440765</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.11512303352356</v>
+        <v>1.11512315273285</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.13950634002686</v>
+        <v>1.13950622081757</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.15576159954071</v>
+        <v>1.15576183795929</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.18989813327789</v>
+        <v>1.18989825248718</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.23866450786591</v>
+        <v>1.23866438865662</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.21915793418884</v>
+        <v>1.21915781497955</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.11349761486053</v>
+        <v>1.11349749565125</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.11187207698822</v>
+        <v>1.11187195777893</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.14113175868988</v>
+        <v>1.14113187789917</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.11024641990662</v>
+        <v>1.11024653911591</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.09886765480042</v>
+        <v>1.0988677740097</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.0972421169281</v>
+        <v>1.09724199771881</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.09886765480042</v>
+        <v>1.0988677740097</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.04522466659546</v>
+        <v>1.04522478580475</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.18502151966095</v>
+        <v>1.18502140045166</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.23053669929504</v>
+        <v>1.23053681850433</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.27930307388306</v>
+        <v>1.27930295467377</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.35570347309113</v>
+        <v>1.35570359230042</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.29393291473389</v>
+        <v>1.2939327955246</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.36058020591736</v>
+        <v>1.36058032512665</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.40284430980682</v>
+        <v>1.40284442901611</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.43047857284546</v>
+        <v>1.43047869205475</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.44998526573181</v>
+        <v>1.44998502731323</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.46298933029175</v>
+        <v>1.46298944950104</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.41422307491302</v>
+        <v>1.41422319412231</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.37358462810516</v>
+        <v>1.37358450889587</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.40609538555145</v>
+        <v>1.40609550476074</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.41422307491302</v>
+        <v>1.41422319412231</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.44510841369629</v>
+        <v>1.44510853290558</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.44185733795166</v>
+        <v>1.44185745716095</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.52313458919525</v>
+        <v>1.52313446998596</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.52476024627686</v>
+        <v>1.52476012706757</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.55401992797852</v>
+        <v>1.55401980876923</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.49875140190125</v>
+        <v>1.49875152111053</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.48412156105042</v>
+        <v>1.48412144184113</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.50525367259979</v>
+        <v>1.5052535533905</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.48412156105042</v>
+        <v>1.48412144184113</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.48899829387665</v>
+        <v>1.48899817466736</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.45323634147644</v>
+        <v>1.45323622226715</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.44510841369629</v>
+        <v>1.44510853290558</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.39959335327148</v>
+        <v>1.39959323406219</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.43047857284546</v>
+        <v>1.43047869205475</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.39796781539917</v>
+        <v>1.39796769618988</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.32806932926178</v>
+        <v>1.32806921005249</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.33294606208801</v>
+        <v>1.33294594287872</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.31994152069092</v>
+        <v>1.31994163990021</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.31669044494629</v>
+        <v>1.31669056415558</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.36383140087128</v>
+        <v>1.3638311624527</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.34432482719421</v>
+        <v>1.34432470798492</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.36058020591736</v>
+        <v>1.36058032512665</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.35895478725433</v>
+        <v>1.35895466804504</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.39796781539917</v>
+        <v>1.39796769618988</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.39796781539917</v>
+        <v>1.39796769618988</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.39959335327148</v>
+        <v>1.39959323406219</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.33944821357727</v>
+        <v>1.33944809436798</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.2029025554657</v>
+        <v>1.20290231704712</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.24191546440125</v>
+        <v>1.24191558361053</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1232" t="n">
-        <v>1.23378789424896</v>
+        <v>1.23378765583038</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.23378789424896</v>
+        <v>1.23378765583038</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.32806932926178</v>
+        <v>1.32806921005249</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.31994152069092</v>
+        <v>1.31994163990021</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.35570347309113</v>
+        <v>1.35570359230042</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.39796781539917</v>
+        <v>1.39796769618988</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.39959335327148</v>
+        <v>1.39959323406219</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.44835960865021</v>
+        <v>1.44835948944092</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.45486176013947</v>
+        <v>1.45486164093018</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.75</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.42235088348389</v>
+        <v>1.42235100269318</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>1.75</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.42235088348389</v>
+        <v>1.42235100269318</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.3898401260376</v>
+        <v>1.38984000682831</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.39146554470062</v>
+        <v>1.39146566390991</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.34432482719421</v>
+        <v>1.34432470798492</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.33294606208801</v>
+        <v>1.33294594287872</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.31669044494629</v>
+        <v>1.31669056415558</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.35570347309113</v>
+        <v>1.35570359230042</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.34920132160187</v>
+        <v>1.34920144081116</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.32969498634338</v>
+        <v>1.3296947479248</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.28580510616302</v>
+        <v>1.2858053445816</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.31018841266632</v>
+        <v>1.31018829345703</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.33944821357727</v>
+        <v>1.33944809436798</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.3524523973465</v>
+        <v>1.35245251655579</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.3898401260376</v>
+        <v>1.38984000682831</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.39471673965454</v>
+        <v>1.39471650123596</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.42072534561157</v>
+        <v>1.42072546482086</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.75</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.42235088348389</v>
+        <v>1.42235100269318</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.3898401260376</v>
+        <v>1.38984000682831</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.39471673965454</v>
+        <v>1.39471650123596</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.41097187995911</v>
+        <v>1.41097211837769</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.34920132160187</v>
+        <v>1.34920144081116</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.35570347309113</v>
+        <v>1.35570359230042</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.35570347309113</v>
+        <v>1.35570359230042</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.41909992694855</v>
+        <v>1.41909980773926</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.48899829387665</v>
+        <v>1.48899817466736</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.54751777648926</v>
+        <v>1.54751789569855</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.54751777648926</v>
+        <v>1.54751789569855</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.56052219867706</v>
+        <v>1.56052196025848</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.55564558506012</v>
+        <v>1.55564546585083</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.52801120281219</v>
+        <v>1.52801132202148</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.46298933029175</v>
+        <v>1.46298944950104</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.49550044536591</v>
+        <v>1.49550032615662</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.47761929035187</v>
+        <v>1.47761940956116</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.46624052524567</v>
+        <v>1.46624064445496</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.61416506767273</v>
+        <v>1.61416494846344</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.60928857326508</v>
+        <v>1.6092883348465</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.60116052627563</v>
+        <v>1.60116076469421</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.58002865314484</v>
+        <v>1.58002853393555</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.62066721916199</v>
+        <v>1.6206670999527</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.59303295612335</v>
+        <v>1.59303307533264</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992690086365</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.71088492870331</v>
+        <v>1.71088480949402</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.67431020736694</v>
+        <v>1.67431008815765</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.61416506767273</v>
+        <v>1.61416494846344</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.6222927570343</v>
+        <v>1.62229287624359</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.65805470943451</v>
+        <v>1.6580548286438</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.71494877338409</v>
+        <v>1.7149486541748</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.67431020736694</v>
+        <v>1.67431008815765</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.64179921150208</v>
+        <v>1.64179933071136</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.64179921150208</v>
+        <v>1.64179933071136</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.6222927570343</v>
+        <v>1.62229287624359</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.6296079158783</v>
+        <v>1.62960779666901</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.64179921150208</v>
+        <v>1.64179933071136</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.6621185541153</v>
+        <v>1.66211867332458</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.69869339466095</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.69869339466095</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.72307634353638</v>
+        <v>1.72307646274567</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992690086365</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992690086365</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992690086365</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992690086365</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992690086365</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.67431020736694</v>
+        <v>1.67431008815765</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.69869339466095</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.74745976924896</v>
+        <v>1.74745965003967</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.75152337551117</v>
+        <v>1.75152361392975</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.75558733940125</v>
+        <v>1.75558745861053</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.74745976924896</v>
+        <v>1.74745965003967</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.75152337551117</v>
+        <v>1.75152361392975</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.75558733940125</v>
+        <v>1.75558745861053</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.7393319606781</v>
+        <v>1.73933207988739</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.71088492870331</v>
+        <v>1.71088480949402</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.69869339466095</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.73526811599731</v>
+        <v>1.73526799678802</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.69869339466095</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.70275723934174</v>
+        <v>1.70275712013245</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.65805470943451</v>
+        <v>1.6580548286438</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.6621185541153</v>
+        <v>1.66211867332458</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992690086365</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.6621185541153</v>
+        <v>1.66211867332458</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.73526811599731</v>
+        <v>1.73526799678802</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.7393319606781</v>
+        <v>1.73933207988739</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.71494877338409</v>
+        <v>1.7149486541748</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.73120439052582</v>
+        <v>1.73120415210724</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.73120439052582</v>
+        <v>1.73120415210724</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.71494877338409</v>
+        <v>1.7149486541748</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.72307634353638</v>
+        <v>1.72307646274567</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.6621185541153</v>
+        <v>1.66211867332458</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.69869339466095</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.72307634353638</v>
+        <v>1.72307646274567</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.73526811599731</v>
+        <v>1.73526799678802</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.74745976924896</v>
+        <v>1.74745965003967</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.75152337551117</v>
+        <v>1.75152361392975</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.75152337551117</v>
+        <v>1.75152361392975</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.80841743946075</v>
+        <v>1.80841755867004</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.77997052669525</v>
+        <v>1.77997064590454</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.77590668201447</v>
+        <v>1.77590656280518</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.8775030374527</v>
+        <v>1.87750327587128</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.92626941204071</v>
+        <v>1.92626953125</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.91407799720764</v>
+        <v>1.91407787799835</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.89782249927521</v>
+        <v>1.8978226184845</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.88563084602356</v>
+        <v>1.88563096523285</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.91407799720764</v>
+        <v>1.91407787799835</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.91001403331757</v>
+        <v>1.91001379489899</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.89375829696655</v>
+        <v>1.89375853538513</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.84499228000641</v>
+        <v>1.84499216079712</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>2.25</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.82873702049255</v>
+        <v>1.82873690128326</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>2.25</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.82873702049255</v>
+        <v>1.82873690128326</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.85718405246735</v>
+        <v>1.85718393325806</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.85718405246735</v>
+        <v>1.85718393325806</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.85311996936798</v>
+        <v>1.85311985015869</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>2.25</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.82873702049255</v>
+        <v>1.82873690128326</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.89375829696655</v>
+        <v>1.89375853538513</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.89375829696655</v>
+        <v>1.89375853538513</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>2.25</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.82873702049255</v>
+        <v>1.82873690128326</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.85718405246735</v>
+        <v>1.85718393325806</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1462" t="n">
-        <v>1.84499228000641</v>
+        <v>1.84499216079712</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.84905600547791</v>
+        <v>1.84905624389648</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.85718405246735</v>
+        <v>1.85718393325806</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.84905600547791</v>
+        <v>1.84905624389648</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.88563084602356</v>
+        <v>1.88563096523285</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.84905600547791</v>
+        <v>1.84905624389648</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.9018862247467</v>
+        <v>1.90188610553741</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.8775030374527</v>
+        <v>1.87750327587128</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.85311996936798</v>
+        <v>1.85311985015869</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.82060897350311</v>
+        <v>1.8206090927124</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1477" t="n">
-        <v>1.8246728181839</v>
+        <v>1.82467293739319</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.8775030374527</v>
+        <v>1.87750327587128</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.92220568656921</v>
+        <v>1.92220556735992</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.89375829696655</v>
+        <v>1.89375853538513</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.8775030374527</v>
+        <v>1.87750327587128</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>1.91001403331757</v>
+        <v>1.91001379489899</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.91001403331757</v>
+        <v>1.91001379489899</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.97097182273865</v>
+        <v>1.97097194194794</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.9298369884491</v>
+        <v>1.92983722686768</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.8466922044754</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.84231615066528</v>
+        <v>1.84231603145599</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1498" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.78980350494385</v>
+        <v>1.78980362415314</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1502" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.73291504383087</v>
+        <v>1.73291492462158</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1520" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.84231615066528</v>
+        <v>1.84231603145599</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.84231615066528</v>
+        <v>1.84231603145599</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419641971588</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.90358066558838</v>
+        <v>1.90358078479767</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419641971588</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419641971588</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.8466922044754</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>2.125</v>
       </c>
       <c r="G1535" t="n">
-        <v>1.85982012748718</v>
+        <v>1.85982024669647</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.8466922044754</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.83793997764587</v>
+        <v>1.83794009685516</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.78980350494385</v>
+        <v>1.78980362415314</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.8466922044754</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.83793997764587</v>
+        <v>1.83794009685516</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.84231615066528</v>
+        <v>1.84231603145599</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.8466922044754</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419641971588</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>2.125</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.85982012748718</v>
+        <v>1.85982024669647</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.72416269779205</v>
+        <v>1.72416281700134</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.71716117858887</v>
+        <v>1.71716105937958</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.58938038349152</v>
+        <v>1.58938050270081</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.633141040802</v>
+        <v>1.63314116001129</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.75479531288147</v>
+        <v>1.75479519367218</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1602" t="n">
-        <v>1.78980350494385</v>
+        <v>1.78980362415314</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.81932306289673</v>
+        <v>1.81932294368744</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.81932306289673</v>
+        <v>1.81932294368744</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.84200775623322</v>
+        <v>1.84200763702393</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.80389726161957</v>
+        <v>1.80389714241028</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.8329336643219</v>
+        <v>1.83293378353119</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1636" t="n">
-        <v>1.8329336643219</v>
+        <v>1.83293378353119</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.72767615318298</v>
+        <v>1.72767627239227</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1645" t="n">
-        <v>1.73312044143677</v>
+        <v>1.73312056064606</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.52260541915894</v>
+        <v>1.52260529994965</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.49356877803802</v>
+        <v>1.49356889724731</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1659" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.4227921962738</v>
+        <v>1.42279207706451</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.30301630496979</v>
+        <v>1.3030161857605</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.34294164180756</v>
+        <v>1.34294152259827</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.33023798465729</v>
+        <v>1.33023810386658</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1678" t="n">
-        <v>1.48449492454529</v>
+        <v>1.484494805336</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.46271753311157</v>
+        <v>1.46271741390228</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.44638431072235</v>
+        <v>1.44638442993164</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.46271753311157</v>
+        <v>1.46271741390228</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.46997654438019</v>
+        <v>1.46997666358948</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.41734790802002</v>
+        <v>1.41734778881073</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.38649642467499</v>
+        <v>1.38649654388428</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>1.5</v>
       </c>
       <c r="G1701" t="n">
-        <v>1.36108946800232</v>
+        <v>1.36108934879303</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>1.5</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.36108946800232</v>
+        <v>1.36108934879303</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>1.35599994659424</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.23042476177216</v>
+        <v>1.23042488098145</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.27760934829712</v>
+        <v>1.27760922908783</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.26127624511719</v>
+        <v>1.2612761259079</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.24312841892242</v>
+        <v>1.24312829971313</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.34657108783722</v>
+        <v>1.34657120704651</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.33023798465729</v>
+        <v>1.33023810386658</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.29031276702881</v>
+        <v>1.2903128862381</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.37923717498779</v>
+        <v>1.37923729419708</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.34475636482239</v>
+        <v>1.3447562456131</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.34294164180756</v>
+        <v>1.34294152259827</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.40101480484009</v>
+        <v>1.4010146856308</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.40101480484009</v>
+        <v>1.4010146856308</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.41734790802002</v>
+        <v>1.41734778881073</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>1.5</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.36108946800232</v>
+        <v>1.36108934879303</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.37742257118225</v>
+        <v>1.37742245197296</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.37742257118225</v>
+        <v>1.37742245197296</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.34657108783722</v>
+        <v>1.34657120704651</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.37923717498779</v>
+        <v>1.37923729419708</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1787" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.46271753311157</v>
+        <v>1.46271741390228</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.49356877803802</v>
+        <v>1.49356889724731</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.46997654438019</v>
+        <v>1.46997666358948</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.48449492454529</v>
+        <v>1.484494805336</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.6242333650589</v>
+        <v>1.62423324584961</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.62786293029785</v>
+        <v>1.62786304950714</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1814" t="n">
-        <v>1.48449492454529</v>
+        <v>1.484494805336</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1819" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.37742257118225</v>
+        <v>1.37742245197296</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.37923717498779</v>
+        <v>1.37923729419708</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1829" t="n">
-        <v>1.38286697864532</v>
+        <v>1.38286685943604</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.27397966384888</v>
+        <v>1.27397978305817</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.24675786495209</v>
+        <v>1.24675798416138</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1843" t="n">
-        <v>1.21409177780151</v>
+        <v>1.2140918970108</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.23949873447418</v>
+        <v>1.23949885368347</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.21409177780151</v>
+        <v>1.2140918970108</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.21409177780151</v>
+        <v>1.2140918970108</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>1.5900000333786</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>1885</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>1.58800005912781</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>1.58599996566772</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>1.58599996566772</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>1.58800005912781</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>1.58800005912781</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74831366539001</v>
+        <v>2.74831414222717</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>2.69898533821106</v>
+        <v>2.69898557662964</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74831366539001</v>
+        <v>2.74831414222717</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G7" t="n">
-        <v>2.74690461158752</v>
+        <v>2.74690508842468</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8187837600708</v>
+        <v>2.81878352165222</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G9" t="n">
-        <v>2.71730756759644</v>
+        <v>2.71730732917786</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G11" t="n">
-        <v>2.48757648468018</v>
+        <v>2.48757672309875</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>2.43824815750122</v>
+        <v>2.43824791908264</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.50167083740234</v>
+        <v>2.50167059898376</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>2.56368398666382</v>
+        <v>2.56368374824524</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>2.45234155654907</v>
+        <v>2.45234203338623</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G18" t="n">
-        <v>2.39737510681152</v>
+        <v>2.3973753452301</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.25</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29026198387146</v>
+        <v>2.29026174545288</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G21" t="n">
-        <v>2.39455699920654</v>
+        <v>2.39455652236938</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G24" t="n">
-        <v>1.9745579957962</v>
+        <v>1.97455787658691</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G26" t="n">
-        <v>1.86885344982147</v>
+        <v>1.86885333061218</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G29" t="n">
-        <v>1.86039781570435</v>
+        <v>1.86039757728577</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.5</v>
       </c>
       <c r="G30" t="n">
-        <v>1.76173973083496</v>
+        <v>1.76173985004425</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G31" t="n">
-        <v>1.87730991840363</v>
+        <v>1.87730967998505</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G33" t="n">
-        <v>2.03657150268555</v>
+        <v>2.03657126426697</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G34" t="n">
-        <v>2.07039642333984</v>
+        <v>2.07039666175842</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G35" t="n">
-        <v>2.05207467079163</v>
+        <v>2.05207443237305</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G36" t="n">
-        <v>2.09294724464417</v>
+        <v>2.09294700622559</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G38" t="n">
-        <v>2.16059756278992</v>
+        <v>2.1605978012085</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G39" t="n">
-        <v>2.04784631729126</v>
+        <v>2.04784655570984</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G40" t="n">
-        <v>2.06616830825806</v>
+        <v>2.06616854667664</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>2.05771207809448</v>
+        <v>2.05771255493164</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G44" t="n">
-        <v>2.08730959892273</v>
+        <v>2.08730936050415</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G47" t="n">
-        <v>2.14932250976562</v>
+        <v>2.1493227481842</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>2.12818145751953</v>
+        <v>2.12818169593811</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G50" t="n">
-        <v>2.12677240371704</v>
+        <v>2.12677192687988</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G51" t="n">
-        <v>2.21274542808533</v>
+        <v>2.21274518966675</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G52" t="n">
-        <v>2.26348352432251</v>
+        <v>2.26348328590393</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G53" t="n">
-        <v>2.27053046226501</v>
+        <v>2.27053022384644</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G54" t="n">
-        <v>2.17469191551208</v>
+        <v>2.17469167709351</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G55" t="n">
-        <v>2.18596649169922</v>
+        <v>2.1859667301178</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G56" t="n">
-        <v>2.17892003059387</v>
+        <v>2.17891955375671</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G58" t="n">
-        <v>2.23670482635498</v>
+        <v>2.23670506477356</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>2.17751049995422</v>
+        <v>2.17751026153564</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G61" t="n">
-        <v>2.18314814567566</v>
+        <v>2.18314790725708</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>2.12818145751953</v>
+        <v>2.12818169593811</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G63" t="n">
-        <v>1.97737658023834</v>
+        <v>1.97737669944763</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>1.98724246025085</v>
+        <v>1.98724257946014</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G66" t="n">
-        <v>1.94496119022369</v>
+        <v>1.94496095180511</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G67" t="n">
-        <v>1.95482671260834</v>
+        <v>1.95482659339905</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.71600008010864</v>
       </c>
       <c r="G68" t="n">
-        <v>1.9139541387558</v>
+        <v>1.91395425796509</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G69" t="n">
-        <v>1.98724246025085</v>
+        <v>1.98724257946014</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.9745579957962</v>
+        <v>1.97455787658691</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>1.98019564151764</v>
+        <v>1.98019552230835</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G73" t="n">
-        <v>2.00838351249695</v>
+        <v>2.00838327407837</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G74" t="n">
-        <v>2.06616830825806</v>
+        <v>2.06616854667664</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G75" t="n">
-        <v>2.1070408821106</v>
+        <v>2.10704064369202</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>2.17046332359314</v>
+        <v>2.17046356201172</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G77" t="n">
-        <v>2.14791345596313</v>
+        <v>2.14791321754456</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G78" t="n">
-        <v>2.17751049995422</v>
+        <v>2.17751026153564</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>2.1070408821106</v>
+        <v>2.10704064369202</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G82" t="n">
-        <v>2.05771207809448</v>
+        <v>2.05771255493164</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G83" t="n">
-        <v>2.02670502662659</v>
+        <v>2.02670574188232</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G84" t="n">
-        <v>1.98724246025085</v>
+        <v>1.98724257946014</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G85" t="n">
-        <v>1.94918930530548</v>
+        <v>1.9491890668869</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>1.97314834594727</v>
+        <v>1.97314858436584</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G87" t="n">
-        <v>1.9562361240387</v>
+        <v>1.95623588562012</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G88" t="n">
-        <v>1.89845049381256</v>
+        <v>1.89845097064972</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G89" t="n">
-        <v>1.86321604251862</v>
+        <v>1.86321616172791</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.5</v>
       </c>
       <c r="G91" t="n">
-        <v>1.79777693748474</v>
+        <v>1.79777717590332</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>1.74024820327759</v>
+        <v>1.74024832248688</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G93" t="n">
-        <v>1.68559587001801</v>
+        <v>1.68559563159943</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G94" t="n">
-        <v>1.681281208992</v>
+        <v>1.68128097057343</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62662875652313</v>
+        <v>1.62662863731384</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G97" t="n">
-        <v>1.63957273960114</v>
+        <v>1.63957238197327</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.60361695289612</v>
+        <v>1.6036171913147</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.60361695289612</v>
+        <v>1.6036171913147</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G100" t="n">
-        <v>1.63957273960114</v>
+        <v>1.63957238197327</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G101" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991017341614</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G103" t="n">
-        <v>1.86249697208405</v>
+        <v>1.86249685287476</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G104" t="n">
-        <v>1.83373272418976</v>
+        <v>1.83373248577118</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G105" t="n">
-        <v>1.86249697208405</v>
+        <v>1.86249685287476</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>1.81215929985046</v>
+        <v>1.81215918064117</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>1.8265415430069</v>
+        <v>1.82654142379761</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G109" t="n">
-        <v>1.79490053653717</v>
+        <v>1.79490041732788</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>1.80640614032745</v>
+        <v>1.80640625953674</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G113" t="n">
-        <v>1.80496799945831</v>
+        <v>1.8049681186676</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.5</v>
       </c>
       <c r="G114" t="n">
-        <v>1.79777693748474</v>
+        <v>1.79777717590332</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G115" t="n">
-        <v>1.73305726051331</v>
+        <v>1.73305690288544</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G116" t="n">
-        <v>1.72011280059814</v>
+        <v>1.72011291980743</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G117" t="n">
-        <v>1.73880994319916</v>
+        <v>1.73880970478058</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G118" t="n">
-        <v>1.63381969928741</v>
+        <v>1.6338198184967</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G119" t="n">
-        <v>1.68559587001801</v>
+        <v>1.68559563159943</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G121" t="n">
-        <v>1.7531920671463</v>
+        <v>1.75319194793701</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>1.81215929985046</v>
+        <v>1.81215918064117</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G123" t="n">
-        <v>1.83804726600647</v>
+        <v>1.83804714679718</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G125" t="n">
-        <v>1.48999738693237</v>
+        <v>1.48999762535095</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G130" t="n">
-        <v>1.49287390708923</v>
+        <v>1.49287414550781</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G131" t="n">
-        <v>1.49862718582153</v>
+        <v>1.49862706661224</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G133" t="n">
-        <v>1.5086944103241</v>
+        <v>1.50869452953339</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G134" t="n">
-        <v>1.55615592002869</v>
+        <v>1.5561558008194</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G135" t="n">
-        <v>1.56047058105469</v>
+        <v>1.56047034263611</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G136" t="n">
-        <v>1.63238131999969</v>
+        <v>1.63238143920898</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G137" t="n">
-        <v>1.63381969928741</v>
+        <v>1.6338198184967</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G144" t="n">
-        <v>1.56190848350525</v>
+        <v>1.56190872192383</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G145" t="n">
-        <v>1.51300895214081</v>
+        <v>1.51300919055939</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.12599992752075</v>
       </c>
       <c r="G146" t="n">
-        <v>1.52882945537567</v>
+        <v>1.52882957458496</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G147" t="n">
-        <v>1.56766152381897</v>
+        <v>1.56766140460968</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G149" t="n">
-        <v>1.51876211166382</v>
+        <v>1.51876199245453</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39579391479492</v>
+        <v>1.39579403400421</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G152" t="n">
-        <v>1.3375461101532</v>
+        <v>1.33754599094391</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G154" t="n">
-        <v>1.42959237098694</v>
+        <v>1.42959225177765</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G156" t="n">
-        <v>1.44828915596008</v>
+        <v>1.44828903675079</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G157" t="n">
-        <v>1.48999738693237</v>
+        <v>1.48999762535095</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>1.56622326374054</v>
+        <v>1.56622350215912</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G160" t="n">
-        <v>1.53314411640167</v>
+        <v>1.53314435482025</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G161" t="n">
-        <v>1.5043797492981</v>
+        <v>1.50437986850739</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G163" t="n">
-        <v>1.4914356470108</v>
+        <v>1.49143552780151</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G164" t="n">
-        <v>1.5173237323761</v>
+        <v>1.51732385158539</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G165" t="n">
-        <v>1.53602051734924</v>
+        <v>1.53602063655853</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G166" t="n">
-        <v>1.52595317363739</v>
+        <v>1.52595293521881</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G167" t="n">
-        <v>1.54608821868896</v>
+        <v>1.54608833789825</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G168" t="n">
-        <v>1.52307677268982</v>
+        <v>1.52307665348053</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>1.51013243198395</v>
+        <v>1.51013255119324</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G170" t="n">
-        <v>1.51588547229767</v>
+        <v>1.51588559150696</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G171" t="n">
-        <v>1.5086944103241</v>
+        <v>1.50869452953339</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G172" t="n">
-        <v>1.53745877742767</v>
+        <v>1.53745901584625</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G173" t="n">
-        <v>1.55759394168854</v>
+        <v>1.55759382247925</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G175" t="n">
-        <v>1.54896485805511</v>
+        <v>1.54896461963654</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G176" t="n">
-        <v>1.55471754074097</v>
+        <v>1.55471765995026</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G177" t="n">
-        <v>1.56047058105469</v>
+        <v>1.56047034263611</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G178" t="n">
-        <v>1.54896485805511</v>
+        <v>1.54896461963654</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G180" t="n">
-        <v>1.49287390708923</v>
+        <v>1.49287414550781</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G181" t="n">
-        <v>1.49862718582153</v>
+        <v>1.49862706661224</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G185" t="n">
-        <v>1.47705352306366</v>
+        <v>1.47705340385437</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G188" t="n">
-        <v>1.48999738693237</v>
+        <v>1.48999762535095</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G191" t="n">
-        <v>1.48424446582794</v>
+        <v>1.48424458503723</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G196" t="n">
-        <v>1.51876211166382</v>
+        <v>1.51876199245453</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G197" t="n">
-        <v>1.54896485805511</v>
+        <v>1.54896461963654</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G198" t="n">
-        <v>1.60936975479126</v>
+        <v>1.60936999320984</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991017341614</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991017341614</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>1.6755279302597</v>
+        <v>1.67552804946899</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991017341614</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G204" t="n">
-        <v>1.68703401088715</v>
+        <v>1.68703389167786</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G205" t="n">
-        <v>1.70429253578186</v>
+        <v>1.70429229736328</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G206" t="n">
-        <v>1.72730422019958</v>
+        <v>1.72730398178101</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G207" t="n">
-        <v>1.73161888122559</v>
+        <v>1.7316187620163</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G208" t="n">
-        <v>1.73449528217316</v>
+        <v>1.73449516296387</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>1.74743914604187</v>
+        <v>1.74743926525116</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G210" t="n">
-        <v>1.77332735061646</v>
+        <v>1.77332723140717</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G212" t="n">
-        <v>1.71723663806915</v>
+        <v>1.71723675727844</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>1.74743914604187</v>
+        <v>1.74743926525116</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>1.6755279302597</v>
+        <v>1.67552804946899</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G216" t="n">
-        <v>1.58348166942596</v>
+        <v>1.58348202705383</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>1.51013243198395</v>
+        <v>1.51013255119324</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>1.51013243198395</v>
+        <v>1.51013255119324</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G221" t="n">
-        <v>1.42743480205536</v>
+        <v>1.42743492126465</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G223" t="n">
-        <v>1.42383933067322</v>
+        <v>1.42383944988251</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G225" t="n">
-        <v>1.45691859722137</v>
+        <v>1.45691847801208</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G226" t="n">
-        <v>1.39004123210907</v>
+        <v>1.39004111289978</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G227" t="n">
-        <v>1.41664826869965</v>
+        <v>1.41664814949036</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G228" t="n">
-        <v>1.39579391479492</v>
+        <v>1.39579403400421</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G229" t="n">
-        <v>1.3375461101532</v>
+        <v>1.33754599094391</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G231" t="n">
-        <v>1.3375461101532</v>
+        <v>1.33754599094391</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G233" t="n">
-        <v>1.33323132991791</v>
+        <v>1.3332314491272</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G236" t="n">
-        <v>1.32316374778748</v>
+        <v>1.32316398620605</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G237" t="n">
-        <v>1.34257984161377</v>
+        <v>1.34257996082306</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G238" t="n">
-        <v>1.38069260120392</v>
+        <v>1.38069272041321</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G240" t="n">
-        <v>1.40226602554321</v>
+        <v>1.40226590633392</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.95299994945526</v>
       </c>
       <c r="G241" t="n">
-        <v>1.40442323684692</v>
+        <v>1.40442335605621</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G244" t="n">
-        <v>1.44828915596008</v>
+        <v>1.44828903675079</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G248" t="n">
-        <v>1.53602051734924</v>
+        <v>1.53602063655853</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G251" t="n">
-        <v>1.5173237323761</v>
+        <v>1.51732385158539</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G252" t="n">
-        <v>1.54608821868896</v>
+        <v>1.54608833789825</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G253" t="n">
-        <v>1.56190848350525</v>
+        <v>1.56190872192383</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>1.56047058105469</v>
+        <v>1.56047034263611</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G255" t="n">
-        <v>1.56047058105469</v>
+        <v>1.56047034263611</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G256" t="n">
-        <v>1.55759394168854</v>
+        <v>1.55759382247925</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G257" t="n">
-        <v>1.5820437669754</v>
+        <v>1.58204364776611</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G258" t="n">
-        <v>1.60649359226227</v>
+        <v>1.60649347305298</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G259" t="n">
-        <v>1.64388740062714</v>
+        <v>1.64388728141785</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>1.64676380157471</v>
+        <v>1.64676356315613</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>1.66114604473114</v>
+        <v>1.66114592552185</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>1.69710159301758</v>
+        <v>1.697101354599</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G268" t="n">
-        <v>1.72011280059814</v>
+        <v>1.72011291980743</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G269" t="n">
-        <v>1.72298943996429</v>
+        <v>1.72298920154572</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G270" t="n">
-        <v>1.72442758083344</v>
+        <v>1.72442770004272</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G271" t="n">
-        <v>1.77476537227631</v>
+        <v>1.77476561069489</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G272" t="n">
-        <v>1.78483295440674</v>
+        <v>1.78483283519745</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G273" t="n">
-        <v>1.74168646335602</v>
+        <v>1.74168622493744</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G275" t="n">
-        <v>1.75463032722473</v>
+        <v>1.75463044643402</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>1.70429253578186</v>
+        <v>1.70429229736328</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G277" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991017341614</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>1.66114604473114</v>
+        <v>1.66114592552185</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G279" t="n">
-        <v>1.64244914054871</v>
+        <v>1.642449259758</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G280" t="n">
-        <v>1.71723663806915</v>
+        <v>1.71723675727844</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>1.70429253578186</v>
+        <v>1.70429229736328</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G282" t="n">
-        <v>1.71436011791229</v>
+        <v>1.71436023712158</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.63957273960114</v>
+        <v>1.63957238197327</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>1.70429253578186</v>
+        <v>1.70429229736328</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G287" t="n">
-        <v>1.66833710670471</v>
+        <v>1.66833686828613</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G288" t="n">
-        <v>1.64244914054871</v>
+        <v>1.642449259758</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>1.63957273960114</v>
+        <v>1.63957238197327</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G291" t="n">
-        <v>1.63094317913055</v>
+        <v>1.63094329833984</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G293" t="n">
-        <v>1.58635830879211</v>
+        <v>1.5863584280014</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G294" t="n">
-        <v>1.5173237323761</v>
+        <v>1.51732385158539</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G296" t="n">
-        <v>1.4914356470108</v>
+        <v>1.49143552780151</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>1.52451491355896</v>
+        <v>1.52451479434967</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G302" t="n">
-        <v>1.51876211166382</v>
+        <v>1.51876199245453</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>1.51013243198395</v>
+        <v>1.51013255119324</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G305" t="n">
-        <v>1.49718868732452</v>
+        <v>1.49718856811523</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G306" t="n">
-        <v>1.51157081127167</v>
+        <v>1.51157104969025</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G308" t="n">
-        <v>1.55903220176697</v>
+        <v>1.55903232097626</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G310" t="n">
-        <v>1.73305726051331</v>
+        <v>1.73305690288544</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>1.8265415430069</v>
+        <v>1.82654142379761</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G312" t="n">
-        <v>1.81503546237946</v>
+        <v>1.81503558158875</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>1.76901257038116</v>
+        <v>1.76901268959045</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G314" t="n">
-        <v>1.75750684738159</v>
+        <v>1.7575067281723</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G315" t="n">
-        <v>1.73305726051331</v>
+        <v>1.73305690288544</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>1.81215929985046</v>
+        <v>1.81215918064117</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>1.95166659355164</v>
+        <v>1.95166671276093</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G320" t="n">
-        <v>1.98043096065521</v>
+        <v>1.98043119907379</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G321" t="n">
-        <v>1.96604883670807</v>
+        <v>1.96604907512665</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G322" t="n">
-        <v>1.96317231655121</v>
+        <v>1.9631724357605</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G323" t="n">
-        <v>1.94303727149963</v>
+        <v>1.94303739070892</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G324" t="n">
-        <v>1.97467827796936</v>
+        <v>1.97467815876007</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G325" t="n">
-        <v>1.95885789394379</v>
+        <v>1.95885753631592</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.71199989318848</v>
       </c>
       <c r="G327" t="n">
-        <v>1.95022833347321</v>
+        <v>1.9502284526825</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G328" t="n">
-        <v>1.99625158309937</v>
+        <v>1.99625182151794</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>1.96317231655121</v>
+        <v>1.9631724357605</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G334" t="n">
-        <v>1.8135974407196</v>
+        <v>1.81359767913818</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G335" t="n">
-        <v>1.79058563709259</v>
+        <v>1.79058587551117</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G336" t="n">
-        <v>1.85386788845062</v>
+        <v>1.85386765003204</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G337" t="n">
-        <v>1.90852010250092</v>
+        <v>1.90852034091949</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G338" t="n">
-        <v>2.00488114356995</v>
+        <v>2.00488090515137</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G339" t="n">
-        <v>1.96748697757721</v>
+        <v>1.9674870967865</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.5</v>
       </c>
       <c r="G340" t="n">
-        <v>1.79777693748474</v>
+        <v>1.79777717590332</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G341" t="n">
-        <v>1.74586117267609</v>
+        <v>1.74586093425751</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G342" t="n">
-        <v>1.70136141777039</v>
+        <v>1.70136153697968</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G343" t="n">
-        <v>1.72954452037811</v>
+        <v>1.72954440116882</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G344" t="n">
-        <v>1.72361123561859</v>
+        <v>1.7236111164093</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G346" t="n">
-        <v>1.71619462966919</v>
+        <v>1.7161945104599</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G347" t="n">
-        <v>1.76514422893524</v>
+        <v>1.76514410972595</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G349" t="n">
-        <v>1.7147114276886</v>
+        <v>1.71471130847931</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G350" t="n">
-        <v>1.71322810649872</v>
+        <v>1.71322798728943</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G351" t="n">
-        <v>1.70581138134003</v>
+        <v>1.70581150054932</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G352" t="n">
-        <v>1.68652832508087</v>
+        <v>1.68652820587158</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G353" t="n">
-        <v>1.66279554367065</v>
+        <v>1.66279530525208</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G357" t="n">
-        <v>1.73547780513763</v>
+        <v>1.73547756671906</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G359" t="n">
-        <v>1.72064471244812</v>
+        <v>1.72064447402954</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G361" t="n">
-        <v>1.69246184825897</v>
+        <v>1.69246172904968</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="n">
-        <v>1.68207836151123</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>1.6983950138092</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G365" t="n">
-        <v>1.70284497737885</v>
+        <v>1.70284485816956</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G366" t="n">
-        <v>1.6983950138092</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>1.6983950138092</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>1.72064471244812</v>
+        <v>1.72064447402954</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G370" t="n">
-        <v>1.70136141777039</v>
+        <v>1.70136153697968</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G371" t="n">
-        <v>1.70432817935944</v>
+        <v>1.70432829856873</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G373" t="n">
-        <v>1.68207836151123</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G375" t="n">
-        <v>1.74141120910645</v>
+        <v>1.74141108989716</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G376" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>1.72806096076965</v>
+        <v>1.72806107997894</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G379" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G383" t="n">
-        <v>1.72806096076965</v>
+        <v>1.72806107997894</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>1.75031101703644</v>
+        <v>1.75031089782715</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G389" t="n">
-        <v>1.70284497737885</v>
+        <v>1.70284485816956</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>1.6983950138092</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G393" t="n">
-        <v>1.7147114276886</v>
+        <v>1.71471130847931</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G394" t="n">
-        <v>1.70877802371979</v>
+        <v>1.70877814292908</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G395" t="n">
-        <v>1.70581138134003</v>
+        <v>1.70581150054932</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G397" t="n">
-        <v>1.70136141777039</v>
+        <v>1.70136153697968</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G398" t="n">
-        <v>1.71322810649872</v>
+        <v>1.71322798728943</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G399" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G401" t="n">
-        <v>1.68504500389099</v>
+        <v>1.68504524230957</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G405" t="n">
-        <v>1.64351236820221</v>
+        <v>1.64351224899292</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G406" t="n">
-        <v>1.63312888145447</v>
+        <v>1.63312900066376</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>1.59456276893616</v>
+        <v>1.59456312656403</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G408" t="n">
-        <v>1.61384618282318</v>
+        <v>1.61384606361389</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G409" t="n">
-        <v>1.59159600734711</v>
+        <v>1.5915961265564</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G410" t="n">
-        <v>1.61087930202484</v>
+        <v>1.61087942123413</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G411" t="n">
-        <v>1.68207836151123</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G414" t="n">
-        <v>1.65686213970184</v>
+        <v>1.65686202049255</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G416" t="n">
-        <v>1.66576206684113</v>
+        <v>1.66576194763184</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G417" t="n">
-        <v>1.63312888145447</v>
+        <v>1.63312900066376</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G418" t="n">
-        <v>1.60346281528473</v>
+        <v>1.60346293449402</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G419" t="n">
-        <v>1.6049462556839</v>
+        <v>1.60494601726532</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G420" t="n">
-        <v>1.5975296497345</v>
+        <v>1.59752953052521</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G421" t="n">
-        <v>1.60791277885437</v>
+        <v>1.60791265964508</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G422" t="n">
-        <v>1.60197949409485</v>
+        <v>1.60197961330414</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G423" t="n">
-        <v>1.58417963981628</v>
+        <v>1.58417952060699</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>1.59456276893616</v>
+        <v>1.59456312656403</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G427" t="n">
-        <v>1.58269643783569</v>
+        <v>1.58269619941711</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G428" t="n">
-        <v>1.60049617290497</v>
+        <v>1.60049593448639</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G429" t="n">
-        <v>1.59159600734711</v>
+        <v>1.5915961265564</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G430" t="n">
-        <v>1.58714640140533</v>
+        <v>1.58714628219604</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>1.59456276893616</v>
+        <v>1.59456312656403</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G435" t="n">
-        <v>1.5990127325058</v>
+        <v>1.59901285171509</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>1.57231318950653</v>
+        <v>1.57231307029724</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G438" t="n">
-        <v>1.56192994117737</v>
+        <v>1.56192982196808</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>1.57231318950653</v>
+        <v>1.57231307029724</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G440" t="n">
-        <v>1.57231318950653</v>
+        <v>1.57231307029724</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G441" t="n">
-        <v>1.56637990474701</v>
+        <v>1.56637978553772</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G442" t="n">
-        <v>1.59307956695557</v>
+        <v>1.59307944774628</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G443" t="n">
-        <v>1.5737966299057</v>
+        <v>1.57379639148712</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G444" t="n">
-        <v>1.58566296100616</v>
+        <v>1.58566308021545</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>1.58714640140533</v>
+        <v>1.58714628219604</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G446" t="n">
-        <v>1.57972991466522</v>
+        <v>1.57972979545593</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G447" t="n">
-        <v>1.66576206684113</v>
+        <v>1.66576194763184</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>1.72806096076965</v>
+        <v>1.72806107997894</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G452" t="n">
-        <v>1.70136141777039</v>
+        <v>1.70136153697968</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G454" t="n">
-        <v>1.70432817935944</v>
+        <v>1.70432829856873</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G455" t="n">
-        <v>1.74437773227692</v>
+        <v>1.74437761306763</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G456" t="n">
-        <v>1.7933269739151</v>
+        <v>1.79332685470581</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G457" t="n">
-        <v>1.79629373550415</v>
+        <v>1.79629337787628</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G458" t="n">
-        <v>1.83189308643341</v>
+        <v>1.83189332485199</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>1.8393098115921</v>
+        <v>1.83930969238281</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G460" t="n">
-        <v>1.93720853328705</v>
+        <v>1.93720865249634</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G461" t="n">
-        <v>1.92089223861694</v>
+        <v>1.92089211940765</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.5</v>
       </c>
       <c r="G462" t="n">
-        <v>1.85414278507233</v>
+        <v>1.85414266586304</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G463" t="n">
-        <v>1.90605878829956</v>
+        <v>1.90605890750885</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.87490952014923</v>
+        <v>1.87490940093994</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G466" t="n">
-        <v>1.91199243068695</v>
+        <v>1.91199207305908</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G468" t="n">
-        <v>1.92089223861694</v>
+        <v>1.92089211940765</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G469" t="n">
-        <v>1.78887712955475</v>
+        <v>1.78887701034546</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G470" t="n">
-        <v>1.7933269739151</v>
+        <v>1.79332685470581</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G471" t="n">
-        <v>1.82892668247223</v>
+        <v>1.82892656326294</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G472" t="n">
-        <v>1.78887712955475</v>
+        <v>1.78887701034546</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G473" t="n">
-        <v>1.76514422893524</v>
+        <v>1.76514410972595</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G476" t="n">
-        <v>1.66279554367065</v>
+        <v>1.66279530525208</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G477" t="n">
-        <v>1.63757884502411</v>
+        <v>1.63757908344269</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G478" t="n">
-        <v>1.64054560661316</v>
+        <v>1.64054548740387</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G479" t="n">
-        <v>1.61977910995483</v>
+        <v>1.61977922916412</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G480" t="n">
-        <v>1.61829590797424</v>
+        <v>1.61829578876495</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G481" t="n">
-        <v>1.60049617290497</v>
+        <v>1.60049593448639</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G482" t="n">
-        <v>1.61681258678436</v>
+        <v>1.61681246757507</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G483" t="n">
-        <v>1.63164579868317</v>
+        <v>1.63164556026459</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G484" t="n">
-        <v>1.64796209335327</v>
+        <v>1.64796197414398</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G485" t="n">
-        <v>1.68652832508087</v>
+        <v>1.68652820587158</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G486" t="n">
-        <v>1.67021191120148</v>
+        <v>1.67021214962006</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G487" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.25</v>
       </c>
       <c r="G488" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G489" t="n">
-        <v>1.63757884502411</v>
+        <v>1.63757908344269</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G490" t="n">
-        <v>1.68207836151123</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G491" t="n">
-        <v>1.66724526882172</v>
+        <v>1.66724514961243</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G492" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G493" t="n">
-        <v>1.66131222248077</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G494" t="n">
-        <v>1.68652832508087</v>
+        <v>1.68652820587158</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.25</v>
       </c>
       <c r="G497" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G499" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G501" t="n">
-        <v>1.68207836151123</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G503" t="n">
-        <v>1.62867903709412</v>
+        <v>1.62867915630341</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G504" t="n">
-        <v>1.66724526882172</v>
+        <v>1.66724514961243</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G505" t="n">
-        <v>1.65834546089172</v>
+        <v>1.65834558010101</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>1.6983950138092</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G509" t="n">
-        <v>1.68504500389099</v>
+        <v>1.68504524230957</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G510" t="n">
-        <v>1.69542837142944</v>
+        <v>1.69542825222015</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G511" t="n">
-        <v>1.68207836151123</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G513" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G516" t="n">
-        <v>1.70581138134003</v>
+        <v>1.70581150054932</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G517" t="n">
-        <v>1.77256047725677</v>
+        <v>1.77256059646606</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G518" t="n">
-        <v>1.75031101703644</v>
+        <v>1.75031089782715</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.375</v>
       </c>
       <c r="G520" t="n">
-        <v>1.76143562793732</v>
+        <v>1.76143574714661</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>1.79110217094421</v>
+        <v>1.79110205173492</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76514422893524</v>
+        <v>1.76514410972595</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.7466025352478</v>
+        <v>1.74660265445709</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G526" t="n">
-        <v>1.79110217094421</v>
+        <v>1.79110205173492</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G528" t="n">
-        <v>1.77256047725677</v>
+        <v>1.77256059646606</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G531" t="n">
-        <v>1.82818496227264</v>
+        <v>1.82818448543549</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G532" t="n">
-        <v>1.77256047725677</v>
+        <v>1.77256059646606</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>1.74289417266846</v>
+        <v>1.74289441108704</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G536" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G537" t="n">
-        <v>1.66502034664154</v>
+        <v>1.66502010822296</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G538" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.25</v>
       </c>
       <c r="G539" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G540" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G541" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G542" t="n">
-        <v>1.62052071094513</v>
+        <v>1.62052083015442</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G544" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G545" t="n">
-        <v>1.69468665122986</v>
+        <v>1.69468653202057</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G546" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G547" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243707180023</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G549" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>1.66502034664154</v>
+        <v>1.66502010822296</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>1.66131222248077</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.25</v>
       </c>
       <c r="G553" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G554" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>1.65018713474274</v>
+        <v>1.65018725395203</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G556" t="n">
-        <v>1.63535380363464</v>
+        <v>1.63535392284393</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>1.63535380363464</v>
+        <v>1.63535392284393</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G558" t="n">
-        <v>1.63164579868317</v>
+        <v>1.63164556026459</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G559" t="n">
-        <v>1.64647889137268</v>
+        <v>1.64647912979126</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.25</v>
       </c>
       <c r="G560" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G561" t="n">
-        <v>1.69468665122986</v>
+        <v>1.69468653202057</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G563" t="n">
-        <v>1.66131222248077</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G564" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243707180023</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.25</v>
       </c>
       <c r="G565" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.25</v>
       </c>
       <c r="G566" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.25</v>
       </c>
       <c r="G567" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G568" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243707180023</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.25</v>
       </c>
       <c r="G570" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G571" t="n">
-        <v>1.64647889137268</v>
+        <v>1.64647912979126</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.25</v>
       </c>
       <c r="G573" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G574" t="n">
-        <v>1.66131222248077</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G575" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243707180023</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G576" t="n">
-        <v>1.64647889137268</v>
+        <v>1.64647912979126</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>1.68727016448975</v>
+        <v>1.68726992607117</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.6983950138092</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G581" t="n">
-        <v>1.67614495754242</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.25</v>
       </c>
       <c r="G583" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G584" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243707180023</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>1.68356156349182</v>
+        <v>1.68356168270111</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.25</v>
       </c>
       <c r="G586" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G587" t="n">
-        <v>1.64647889137268</v>
+        <v>1.64647912979126</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G588" t="n">
-        <v>1.66131222248077</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>1.66131222248077</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.25</v>
       </c>
       <c r="G590" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G591" t="n">
-        <v>1.66131222248077</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G592" t="n">
-        <v>1.65389537811279</v>
+        <v>1.65389561653137</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G593" t="n">
-        <v>1.6983950138092</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G594" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>1.70581138134003</v>
+        <v>1.70581150054932</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G596" t="n">
-        <v>1.69468665122986</v>
+        <v>1.69468653202057</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G598" t="n">
-        <v>1.72984230518341</v>
+        <v>1.72984218597412</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G599" t="n">
-        <v>1.72984230518341</v>
+        <v>1.72984218597412</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>1.70287370681763</v>
+        <v>1.70287382602692</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G607" t="n">
-        <v>1.5526202917099</v>
+        <v>1.55262017250061</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G608" t="n">
-        <v>1.5526202917099</v>
+        <v>1.55262017250061</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G611" t="n">
-        <v>1.53489792346954</v>
+        <v>1.53489780426025</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G615" t="n">
-        <v>1.51024103164673</v>
+        <v>1.51024091243744</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G620" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G622" t="n">
-        <v>1.55647277832031</v>
+        <v>1.5564728975296</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G623" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G625" t="n">
-        <v>1.62196791172028</v>
+        <v>1.62196803092957</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>1.62196791172028</v>
+        <v>1.62196803092957</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G628" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>1.59114670753479</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G630" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G632" t="n">
-        <v>1.61040985584259</v>
+        <v>1.61040997505188</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G634" t="n">
-        <v>1.55647277832031</v>
+        <v>1.5564728975296</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>1.5603255033493</v>
+        <v>1.56032562255859</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G643" t="n">
-        <v>1.61811530590057</v>
+        <v>1.61811518669128</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>1.62196791172028</v>
+        <v>1.62196803092957</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G645" t="n">
-        <v>1.59885203838348</v>
+        <v>1.59885215759277</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>1.60655736923218</v>
+        <v>1.60655725002289</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G650" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G651" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G652" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G655" t="n">
-        <v>1.59114670753479</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G658" t="n">
-        <v>1.66049468517303</v>
+        <v>1.66049456596375</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G659" t="n">
-        <v>1.61426270008087</v>
+        <v>1.61426258087158</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G660" t="n">
-        <v>1.62196791172028</v>
+        <v>1.62196803092957</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G661" t="n">
-        <v>1.59114670753479</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G662" t="n">
-        <v>1.59114670753479</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G663" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>1.57188332080841</v>
+        <v>1.5718834400177</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G669" t="n">
-        <v>1.54876756668091</v>
+        <v>1.54876744747162</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G670" t="n">
-        <v>1.54491496086121</v>
+        <v>1.54491484165192</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G671" t="n">
-        <v>1.53643894195557</v>
+        <v>1.53643906116486</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G674" t="n">
-        <v>1.5526202917099</v>
+        <v>1.55262017250061</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G675" t="n">
-        <v>1.53489792346954</v>
+        <v>1.53489780426025</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>1.5603255033493</v>
+        <v>1.56032562255859</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G679" t="n">
-        <v>1.55647277832031</v>
+        <v>1.5564728975296</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G680" t="n">
-        <v>1.54491496086121</v>
+        <v>1.54491484165192</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G682" t="n">
-        <v>1.54876756668091</v>
+        <v>1.54876744747162</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G685" t="n">
-        <v>1.59114670753479</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G686" t="n">
-        <v>1.54491496086121</v>
+        <v>1.54491484165192</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G687" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G690" t="n">
-        <v>1.57188332080841</v>
+        <v>1.5718834400177</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G695" t="n">
-        <v>1.57958877086639</v>
+        <v>1.5795886516571</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G697" t="n">
-        <v>1.59114670753479</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G698" t="n">
-        <v>1.61040985584259</v>
+        <v>1.61040997505188</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G699" t="n">
-        <v>1.61811530590057</v>
+        <v>1.61811518669128</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G701" t="n">
-        <v>1.61040985584259</v>
+        <v>1.61040997505188</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>1.54876756668091</v>
+        <v>1.54876744747162</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G704" t="n">
-        <v>1.5526202917099</v>
+        <v>1.55262017250061</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G708" t="n">
-        <v>1.49328923225403</v>
+        <v>1.49328935146332</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G710" t="n">
-        <v>1.42548263072968</v>
+        <v>1.42548251152039</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G711" t="n">
-        <v>1.4347288608551</v>
+        <v>1.43472909927368</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G712" t="n">
-        <v>1.41777729988098</v>
+        <v>1.41777718067169</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G718" t="n">
-        <v>1.25442481040955</v>
+        <v>1.25442469120026</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G722" t="n">
-        <v>1.29911553859711</v>
+        <v>1.29911541938782</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G725" t="n">
-        <v>1.30990278720856</v>
+        <v>1.30990290641785</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G726" t="n">
-        <v>1.31144404411316</v>
+        <v>1.31144392490387</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G728" t="n">
-        <v>1.29911553859711</v>
+        <v>1.29911541938782</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G729" t="n">
-        <v>1.31144404411316</v>
+        <v>1.31144392490387</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G730" t="n">
-        <v>1.30682075023651</v>
+        <v>1.30682063102722</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G732" t="n">
-        <v>1.28370475769043</v>
+        <v>1.28370487689972</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G733" t="n">
-        <v>1.28062260150909</v>
+        <v>1.2806224822998</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G734" t="n">
-        <v>1.23747277259827</v>
+        <v>1.23747301101685</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.5460000038147</v>
       </c>
       <c r="G738" t="n">
-        <v>1.19124102592468</v>
+        <v>1.19124114513397</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G739" t="n">
-        <v>1.14963233470917</v>
+        <v>1.14963245391846</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G740" t="n">
-        <v>1.1373039484024</v>
+        <v>1.13730382919312</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G741" t="n">
-        <v>1.13113975524902</v>
+        <v>1.13113963603973</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G744" t="n">
-        <v>1.2498015165329</v>
+        <v>1.24980139732361</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G746" t="n">
-        <v>1.23747277259827</v>
+        <v>1.23747301101685</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G747" t="n">
-        <v>1.24055504798889</v>
+        <v>1.24055528640747</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G748" t="n">
-        <v>1.23593199253082</v>
+        <v>1.23593187332153</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G750" t="n">
-        <v>1.24363720417023</v>
+        <v>1.24363708496094</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G751" t="n">
-        <v>1.26212990283966</v>
+        <v>1.26213002204895</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G754" t="n">
-        <v>1.18045353889465</v>
+        <v>1.18045365810394</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G756" t="n">
-        <v>1.15733778476715</v>
+        <v>1.15733766555786</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G758" t="n">
-        <v>1.09569525718689</v>
+        <v>1.09569537639618</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G761" t="n">
-        <v>1.07566130161285</v>
+        <v>1.07566142082214</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G762" t="n">
-        <v>1.08182561397552</v>
+        <v>1.08182573318481</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G763" t="n">
-        <v>1.10802352428436</v>
+        <v>1.10802376270294</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G765" t="n">
-        <v>1.13576292991638</v>
+        <v>1.13576281070709</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G766" t="n">
-        <v>1.15733778476715</v>
+        <v>1.15733766555786</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G770" t="n">
-        <v>1.15425550937653</v>
+        <v>1.15425562858582</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G774" t="n">
-        <v>1.1434680223465</v>
+        <v>1.14346814155579</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G775" t="n">
-        <v>1.14655041694641</v>
+        <v>1.14655029773712</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G778" t="n">
-        <v>1.14655041694641</v>
+        <v>1.14655029773712</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G779" t="n">
-        <v>1.13268053531647</v>
+        <v>1.13268089294434</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>1.12497556209564</v>
+        <v>1.12497544288635</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G781" t="n">
-        <v>1.13268053531647</v>
+        <v>1.13268089294434</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G783" t="n">
-        <v>1.10956490039825</v>
+        <v>1.10956478118896</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G784" t="n">
-        <v>1.10802352428436</v>
+        <v>1.10802376270294</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G785" t="n">
-        <v>1.10340070724487</v>
+        <v>1.10340058803558</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G786" t="n">
-        <v>1.07412052154541</v>
+        <v>1.07412040233612</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G789" t="n">
-        <v>1.13884496688843</v>
+        <v>1.13884508609772</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G790" t="n">
-        <v>1.14038610458374</v>
+        <v>1.14038598537445</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G791" t="n">
-        <v>1.14038610458374</v>
+        <v>1.14038598537445</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G792" t="n">
-        <v>1.15425550937653</v>
+        <v>1.15425562858582</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G793" t="n">
-        <v>1.17428934574127</v>
+        <v>1.17428946495056</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G794" t="n">
-        <v>1.1850768327713</v>
+        <v>1.18507671356201</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G797" t="n">
-        <v>1.24671936035156</v>
+        <v>1.24671924114227</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G798" t="n">
-        <v>1.23593199253082</v>
+        <v>1.23593187332153</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G799" t="n">
-        <v>1.24363720417023</v>
+        <v>1.24363708496094</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G800" t="n">
-        <v>1.24363720417023</v>
+        <v>1.24363708496094</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G801" t="n">
-        <v>1.24055504798889</v>
+        <v>1.24055528640747</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G805" t="n">
-        <v>1.25596570968628</v>
+        <v>1.25596559047699</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G806" t="n">
-        <v>1.30219769477844</v>
+        <v>1.30219757556915</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G809" t="n">
-        <v>1.27754056453705</v>
+        <v>1.27754044532776</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G810" t="n">
-        <v>1.24055504798889</v>
+        <v>1.24055528640747</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G812" t="n">
-        <v>1.18199491500854</v>
+        <v>1.18199467658997</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G821" t="n">
-        <v>1.13576292991638</v>
+        <v>1.13576281070709</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G824" t="n">
-        <v>1.13422179222107</v>
+        <v>1.13422167301178</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G825" t="n">
-        <v>1.15425550937653</v>
+        <v>1.15425562858582</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G828" t="n">
-        <v>1.14963233470917</v>
+        <v>1.14963245391846</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G830" t="n">
-        <v>1.15733778476715</v>
+        <v>1.15733766555786</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G832" t="n">
-        <v>1.16041994094849</v>
+        <v>1.1604198217392</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G833" t="n">
-        <v>1.16196095943451</v>
+        <v>1.16196084022522</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G834" t="n">
-        <v>1.19586420059204</v>
+        <v>1.19586431980133</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G835" t="n">
-        <v>1.26367092132568</v>
+        <v>1.26367104053497</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G842" t="n">
-        <v>1.26367092132568</v>
+        <v>1.26367104053497</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G844" t="n">
-        <v>1.28062260150909</v>
+        <v>1.2806224822998</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G845" t="n">
-        <v>1.28832805156708</v>
+        <v>1.28832817077637</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G847" t="n">
-        <v>1.2898690700531</v>
+        <v>1.28986918926239</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G849" t="n">
-        <v>1.29230749607086</v>
+        <v>1.29230737686157</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G850" t="n">
-        <v>1.26629853248596</v>
+        <v>1.26629865169525</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G851" t="n">
-        <v>1.24029004573822</v>
+        <v>1.24028992652893</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.5</v>
       </c>
       <c r="G852" t="n">
-        <v>1.21915793418884</v>
+        <v>1.21915805339813</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G853" t="n">
-        <v>1.22240900993347</v>
+        <v>1.22240889072418</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G855" t="n">
-        <v>1.14113175868988</v>
+        <v>1.14113187789917</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G856" t="n">
-        <v>1.11512303352356</v>
+        <v>1.11512315273285</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G858" t="n">
-        <v>1.11349761486053</v>
+        <v>1.11349749565125</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G860" t="n">
-        <v>1.09073996543884</v>
+        <v>1.09074008464813</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G863" t="n">
-        <v>1.06960785388947</v>
+        <v>1.06960773468018</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G866" t="n">
-        <v>1.00133502483368</v>
+        <v>1.00133514404297</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G869" t="n">
-        <v>1.01271378993988</v>
+        <v>1.01271390914917</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G870" t="n">
-        <v>1.03222036361694</v>
+        <v>1.03222024440765</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G871" t="n">
-        <v>1.00783717632294</v>
+        <v>1.00783729553223</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G872" t="n">
-        <v>0.976951897144318</v>
+        <v>0.976951956748962</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G874" t="n">
-        <v>0.972075223922729</v>
+        <v>0.972075283527374</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G875" t="n">
-        <v>0.95581978559494</v>
+        <v>0.955819725990295</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G876" t="n">
-        <v>0.936313152313232</v>
+        <v>0.936313211917877</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G877" t="n">
-        <v>0.911930084228516</v>
+        <v>0.91193014383316</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>0.910304486751556</v>
+        <v>0.910304605960846</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G879" t="n">
-        <v>0.928185522556305</v>
+        <v>0.92818558216095</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G880" t="n">
-        <v>0.924934446811676</v>
+        <v>0.924934387207031</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G881" t="n">
-        <v>0.936313152313232</v>
+        <v>0.936313211917877</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G882" t="n">
-        <v>0.950943171977997</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G883" t="n">
-        <v>0.95744526386261</v>
+        <v>0.957445323467255</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G884" t="n">
-        <v>0.939564406871796</v>
+        <v>0.939564347267151</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G886" t="n">
-        <v>0.95581978559494</v>
+        <v>0.955819725990295</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G887" t="n">
-        <v>0.965573012828827</v>
+        <v>0.965572953224182</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G888" t="n">
-        <v>0.965573012828827</v>
+        <v>0.965572953224182</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G890" t="n">
-        <v>0.976951897144318</v>
+        <v>0.976951956748962</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>1.03222036361694</v>
+        <v>1.03222024440765</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G896" t="n">
-        <v>1.03059470653534</v>
+        <v>1.03059482574463</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G898" t="n">
-        <v>1.01271378993988</v>
+        <v>1.01271390914917</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G899" t="n">
-        <v>0.976951897144318</v>
+        <v>0.976951956748962</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G900" t="n">
-        <v>0.994832813739777</v>
+        <v>0.994832873344421</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G901" t="n">
-        <v>0.981828331947327</v>
+        <v>0.981828391551971</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G902" t="n">
-        <v>1.01271378993988</v>
+        <v>1.01271390914917</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G903" t="n">
-        <v>0.991581797599792</v>
+        <v>0.991581678390503</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G905" t="n">
-        <v>1.00133502483368</v>
+        <v>1.00133514404297</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.02409255504608</v>
+        <v>1.02409267425537</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G907" t="n">
-        <v>1.03222036361694</v>
+        <v>1.03222024440765</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G910" t="n">
-        <v>1.00783717632294</v>
+        <v>1.00783729553223</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G911" t="n">
-        <v>1.01759040355682</v>
+        <v>1.01759028434753</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G912" t="n">
-        <v>1.02409255504608</v>
+        <v>1.02409267425537</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G913" t="n">
-        <v>1.02409255504608</v>
+        <v>1.02409267425537</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G914" t="n">
-        <v>1.01108825206757</v>
+        <v>1.01108813285828</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G915" t="n">
-        <v>1.00783717632294</v>
+        <v>1.00783729553223</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G917" t="n">
-        <v>1.00783717632294</v>
+        <v>1.00783729553223</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G918" t="n">
-        <v>0.949317574501038</v>
+        <v>0.949317514896393</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>0.950943171977997</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G920" t="n">
-        <v>0.952568829059601</v>
+        <v>0.952568650245667</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G922" t="n">
-        <v>0.928185522556305</v>
+        <v>0.92818558216095</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G923" t="n">
-        <v>0.954194307327271</v>
+        <v>0.954194128513336</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G924" t="n">
-        <v>0.949317574501038</v>
+        <v>0.949317514896393</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G926" t="n">
-        <v>0.981828331947327</v>
+        <v>0.981828391551971</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G927" t="n">
-        <v>0.978577375411987</v>
+        <v>0.978577315807343</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>0.975326418876648</v>
+        <v>0.975326478481293</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G929" t="n">
-        <v>0.973700821399689</v>
+        <v>0.973700761795044</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G930" t="n">
-        <v>0.972075223922729</v>
+        <v>0.972075283527374</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G932" t="n">
-        <v>0.980202972888947</v>
+        <v>0.980202794075012</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G933" t="n">
-        <v>0.965573012828827</v>
+        <v>0.965572953224182</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G934" t="n">
-        <v>0.950943171977997</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G937" t="n">
-        <v>1.02409255504608</v>
+        <v>1.02409267425537</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G939" t="n">
-        <v>1.14275729656219</v>
+        <v>1.14275741577148</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G942" t="n">
-        <v>1.19640028476715</v>
+        <v>1.19640016555786</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G943" t="n">
-        <v>1.2029025554657</v>
+        <v>1.20290243625641</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G945" t="n">
-        <v>1.21753227710724</v>
+        <v>1.21753239631653</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G946" t="n">
-        <v>1.20940458774567</v>
+        <v>1.20940470695496</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G947" t="n">
-        <v>1.19802594184875</v>
+        <v>1.19802582263947</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G950" t="n">
-        <v>1.14600825309753</v>
+        <v>1.14600837230682</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G951" t="n">
-        <v>1.14600825309753</v>
+        <v>1.14600837230682</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G953" t="n">
-        <v>1.14600825309753</v>
+        <v>1.14600837230682</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G954" t="n">
-        <v>1.13462972640991</v>
+        <v>1.13462960720062</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G955" t="n">
-        <v>1.12325072288513</v>
+        <v>1.12325084209442</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G957" t="n">
-        <v>1.09399092197418</v>
+        <v>1.09399104118347</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.32400000095367</v>
       </c>
       <c r="G958" t="n">
-        <v>1.07611000537872</v>
+        <v>1.07611012458801</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G959" t="n">
-        <v>1.09073996543884</v>
+        <v>1.09074008464813</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G960" t="n">
-        <v>1.11674857139587</v>
+        <v>1.11674869060516</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G961" t="n">
-        <v>1.13462972640991</v>
+        <v>1.13462960720062</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G963" t="n">
-        <v>1.17364275455475</v>
+        <v>1.17364263534546</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G967" t="n">
-        <v>1.18827247619629</v>
+        <v>1.18827259540558</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G969" t="n">
-        <v>1.18502151966095</v>
+        <v>1.18502140045166</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G975" t="n">
-        <v>1.25491976737976</v>
+        <v>1.25491988658905</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G976" t="n">
-        <v>1.31018841266632</v>
+        <v>1.31018829345703</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G977" t="n">
-        <v>1.36058020591736</v>
+        <v>1.36058032512665</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G978" t="n">
-        <v>1.38008666038513</v>
+        <v>1.38008677959442</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G981" t="n">
-        <v>1.38008666038513</v>
+        <v>1.38008677959442</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G985" t="n">
-        <v>1.34920144081116</v>
+        <v>1.34920132160187</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G986" t="n">
-        <v>1.36870789527893</v>
+        <v>1.36870801448822</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>1.39796769618988</v>
+        <v>1.39796781539917</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G988" t="n">
-        <v>1.49224925041199</v>
+        <v>1.4922491312027</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G989" t="n">
-        <v>1.50362813472748</v>
+        <v>1.50362801551819</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G990" t="n">
-        <v>1.50687921047211</v>
+        <v>1.50687909126282</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G991" t="n">
-        <v>1.51988351345062</v>
+        <v>1.51988363265991</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G992" t="n">
-        <v>1.52150905132294</v>
+        <v>1.52150893211365</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G994" t="n">
-        <v>1.53451335430145</v>
+        <v>1.53451347351074</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G995" t="n">
-        <v>1.52801132202148</v>
+        <v>1.52801120281219</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G999" t="n">
-        <v>1.45486176013947</v>
+        <v>1.45486164093018</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.48412144184113</v>
+        <v>1.48412156105042</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.51500689983368</v>
+        <v>1.51500678062439</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.50850450992584</v>
+        <v>1.50850462913513</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.55401992797852</v>
+        <v>1.55401980876923</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.60116064548492</v>
+        <v>1.60116076469421</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.51988351345062</v>
+        <v>1.51988363265991</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.51663243770599</v>
+        <v>1.51663255691528</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.52150905132294</v>
+        <v>1.52150893211365</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.46298933029175</v>
+        <v>1.46298944950104</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.48574697971344</v>
+        <v>1.48574709892273</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.49712598323822</v>
+        <v>1.49712586402893</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.46298933029175</v>
+        <v>1.46298944950104</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.53451335430145</v>
+        <v>1.53451347351074</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.48737263679504</v>
+        <v>1.48737275600433</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.44348299503326</v>
+        <v>1.44348287582397</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.48737263679504</v>
+        <v>1.48737275600433</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.37358450889587</v>
+        <v>1.37358462810516</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.40284430980682</v>
+        <v>1.40284419059753</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.43047869205475</v>
+        <v>1.43047857284546</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.48737263679504</v>
+        <v>1.48737275600433</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.49387490749359</v>
+        <v>1.4938747882843</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.50362813472748</v>
+        <v>1.50362801551819</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.58002853393555</v>
+        <v>1.58002865314484</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.61416506767273</v>
+        <v>1.61416494846344</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.7393319606781</v>
+        <v>1.73933207988739</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.51988351345062</v>
+        <v>1.51988363265991</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.49224925041199</v>
+        <v>1.4922491312027</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.49387490749359</v>
+        <v>1.4938747882843</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.45486176013947</v>
+        <v>1.45486164093018</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.39796769618988</v>
+        <v>1.39796781539917</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.34920144081116</v>
+        <v>1.34920132160187</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.28580522537231</v>
+        <v>1.28580510616302</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.20777916908264</v>
+        <v>1.20777904987335</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.18177032470703</v>
+        <v>1.18177044391632</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.02409255504608</v>
+        <v>1.02409267425537</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.978577375411987</v>
+        <v>0.978577315807343</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.97044974565506</v>
+        <v>0.970449686050415</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.817648589611053</v>
+        <v>0.817648649215698</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.861538171768188</v>
+        <v>0.861538112163544</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.934687674045563</v>
+        <v>0.934687733650208</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.950943171977997</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.94281542301178</v>
+        <v>0.942815482616425</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.926560044288635</v>
+        <v>0.92655998468399</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.879419267177582</v>
+        <v>0.879419207572937</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.921683371067047</v>
+        <v>0.921683251857758</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.965573012828827</v>
+        <v>0.965572953224182</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.978577375411987</v>
+        <v>0.978577315807343</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.996458411216736</v>
+        <v>0.996458351612091</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.04685032367706</v>
+        <v>1.04685008525848</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.01759040355682</v>
+        <v>1.01759028434753</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.01759040355682</v>
+        <v>1.01759028434753</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.996458411216736</v>
+        <v>0.996458351612091</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.978577375411987</v>
+        <v>0.978577315807343</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.01108825206757</v>
+        <v>1.01108813285828</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.04522478580475</v>
+        <v>1.04522466659546</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.08098673820496</v>
+        <v>1.08098661899567</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.08098673820496</v>
+        <v>1.08098661899567</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.03059470653534</v>
+        <v>1.03059482574463</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.0289694070816</v>
+        <v>1.02896916866302</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.01759040355682</v>
+        <v>1.01759028434753</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.01433944702148</v>
+        <v>1.01433932781219</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.980202972888947</v>
+        <v>0.980202794075012</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.980202972888947</v>
+        <v>0.980202794075012</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.01271378993988</v>
+        <v>1.01271390914917</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.97044974565506</v>
+        <v>0.970449686050415</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.95907074213028</v>
+        <v>0.959070801734924</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.97044974565506</v>
+        <v>0.970449686050415</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.975326418876648</v>
+        <v>0.975326478481293</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.999709486961365</v>
+        <v>0.99970954656601</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.03222036361694</v>
+        <v>1.03222024440765</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.11512303352356</v>
+        <v>1.11512315273285</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.15576171875</v>
+        <v>1.15576183795929</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.18989813327789</v>
+        <v>1.1898980140686</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.29068183898926</v>
+        <v>1.29068195819855</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.21915793418884</v>
+        <v>1.21915805339813</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.11349761486053</v>
+        <v>1.11349749565125</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.14113175868988</v>
+        <v>1.14113187789917</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.11024653911591</v>
+        <v>1.11024641990662</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.09886765480042</v>
+        <v>1.09886753559113</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.09724199771881</v>
+        <v>1.0972421169281</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.09886765480042</v>
+        <v>1.09886753559113</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.06798243522644</v>
+        <v>1.06798231601715</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.04522478580475</v>
+        <v>1.04522466659546</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.18502151966095</v>
+        <v>1.18502140045166</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.23053669929504</v>
+        <v>1.23053681850433</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.34107375144958</v>
+        <v>1.3410736322403</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.35570347309113</v>
+        <v>1.35570359230042</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.36058020591736</v>
+        <v>1.36058032512665</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.40284430980682</v>
+        <v>1.40284419059753</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.43047869205475</v>
+        <v>1.43047857284546</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.44998514652252</v>
+        <v>1.44998526573181</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.50687921047211</v>
+        <v>1.50687909126282</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.46298933029175</v>
+        <v>1.46298944950104</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.42722749710083</v>
+        <v>1.42722761631012</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.41422319412231</v>
+        <v>1.41422307491302</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.37358450889587</v>
+        <v>1.37358462810516</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.41422319412231</v>
+        <v>1.41422307491302</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.44510841369629</v>
+        <v>1.44510853290558</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.44185733795166</v>
+        <v>1.44185745716095</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.4467339515686</v>
+        <v>1.44673407077789</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.52476024627686</v>
+        <v>1.52476012706757</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.55401992797852</v>
+        <v>1.55401980876923</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.51175570487976</v>
+        <v>1.51175582408905</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.49062371253967</v>
+        <v>1.49062359333038</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.49875140190125</v>
+        <v>1.49875152111053</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.48412144184113</v>
+        <v>1.48412156105042</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.48412144184113</v>
+        <v>1.48412156105042</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.44510841369629</v>
+        <v>1.44510853290558</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.38821446895599</v>
+        <v>1.3882143497467</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.40121877193451</v>
+        <v>1.40121865272522</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.41584861278534</v>
+        <v>1.41584873199463</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.43047869205475</v>
+        <v>1.43047857284546</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.43698084354401</v>
+        <v>1.43698072433472</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.39796769618988</v>
+        <v>1.39796781539917</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.31994152069092</v>
+        <v>1.31994163990021</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.35082685947418</v>
+        <v>1.35082674026489</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.36058020591736</v>
+        <v>1.36058032512665</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.40121877193451</v>
+        <v>1.40121865272522</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.39796769618988</v>
+        <v>1.39796781539917</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.39796769618988</v>
+        <v>1.39796781539917</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.33619713783264</v>
+        <v>1.33619701862335</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.25004327297211</v>
+        <v>1.25004315376282</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.2029025554657</v>
+        <v>1.20290243625641</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.15088498592377</v>
+        <v>1.15088510513306</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.22891116142273</v>
+        <v>1.22891104221344</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.24191546440125</v>
+        <v>1.24191558361053</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.25491976737976</v>
+        <v>1.25491988658905</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.31994152069092</v>
+        <v>1.31994163990021</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.35082685947418</v>
+        <v>1.35082674026489</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.35570347309113</v>
+        <v>1.35570359230042</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.39796769618988</v>
+        <v>1.39796781539917</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.4467339515686</v>
+        <v>1.44673407077789</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.4467339515686</v>
+        <v>1.44673407077789</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.45486176013947</v>
+        <v>1.45486164093018</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.75</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.4223507642746</v>
+        <v>1.42235088348389</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.41259777545929</v>
+        <v>1.41259765625</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>1.75</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.4223507642746</v>
+        <v>1.42235088348389</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.3898401260376</v>
+        <v>1.38984000682831</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.35082685947418</v>
+        <v>1.35082674026489</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.35570347309113</v>
+        <v>1.35570359230042</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.34920144081116</v>
+        <v>1.34920132160187</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.28417956829071</v>
+        <v>1.2841796875</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.28580522537231</v>
+        <v>1.28580510616302</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.31018841266632</v>
+        <v>1.31018829345703</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.36870789527893</v>
+        <v>1.36870801448822</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.38821446895599</v>
+        <v>1.3882143497467</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.41259777545929</v>
+        <v>1.41259765625</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.3898401260376</v>
+        <v>1.38984000682831</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.39471662044525</v>
+        <v>1.39471673965454</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.42072534561157</v>
+        <v>1.42072546482086</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.75</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.4223507642746</v>
+        <v>1.42235088348389</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.3898401260376</v>
+        <v>1.38984000682831</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.39471662044525</v>
+        <v>1.39471673965454</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.34920144081116</v>
+        <v>1.34920132160187</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.35570347309113</v>
+        <v>1.35570359230042</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.33457148075104</v>
+        <v>1.33457159996033</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.35570347309113</v>
+        <v>1.35570359230042</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.3654568195343</v>
+        <v>1.36545670032501</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.52801132202148</v>
+        <v>1.52801120281219</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.46298933029175</v>
+        <v>1.46298944950104</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.49224925041199</v>
+        <v>1.4922491312027</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.56539869308472</v>
+        <v>1.56539881229401</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.61253952980042</v>
+        <v>1.61253941059113</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.61416506767273</v>
+        <v>1.61416494846344</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.60928845405579</v>
+        <v>1.60928857326508</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.60116064548492</v>
+        <v>1.60116076469421</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.58002853393555</v>
+        <v>1.58002865314484</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.62066733837128</v>
+        <v>1.62066721916199</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.65399098396301</v>
+        <v>1.6539911031723</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.63773560523987</v>
+        <v>1.63773548603058</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.61416506767273</v>
+        <v>1.61416494846344</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.71494877338409</v>
+        <v>1.7149486541748</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.69462954998016</v>
+        <v>1.69462943077087</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.69462954998016</v>
+        <v>1.69462943077087</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.6296079158783</v>
+        <v>1.62960767745972</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.66211867332458</v>
+        <v>1.6621185541153</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.72307634353638</v>
+        <v>1.72307622432709</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.65399098396301</v>
+        <v>1.6539911031723</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.74745965003967</v>
+        <v>1.74745953083038</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.75152337551117</v>
+        <v>1.75152349472046</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.75558733940125</v>
+        <v>1.75558745861053</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.74745965003967</v>
+        <v>1.74745953083038</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.75152337551117</v>
+        <v>1.75152349472046</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.75558733940125</v>
+        <v>1.75558745861053</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.7393319606781</v>
+        <v>1.73933207988739</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.63773560523987</v>
+        <v>1.63773548603058</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.66211867332458</v>
+        <v>1.6621185541153</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.64586317539215</v>
+        <v>1.64586329460144</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.64586317539215</v>
+        <v>1.64586329460144</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.65399098396301</v>
+        <v>1.6539911031723</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.66211867332458</v>
+        <v>1.6621185541153</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.7393319606781</v>
+        <v>1.73933207988739</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.71494877338409</v>
+        <v>1.7149486541748</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.71494877338409</v>
+        <v>1.7149486541748</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.72307634353638</v>
+        <v>1.72307622432709</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.66211867332458</v>
+        <v>1.6621185541153</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.72307634353638</v>
+        <v>1.72307622432709</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.74745965003967</v>
+        <v>1.74745953083038</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.75152337551117</v>
+        <v>1.75152349472046</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.75152337551117</v>
+        <v>1.75152349472046</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.74339592456818</v>
+        <v>1.74339580535889</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.80841732025146</v>
+        <v>1.80841743946075</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.77997052669525</v>
+        <v>1.77997064590454</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.77590656280518</v>
+        <v>1.77590668201447</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.83686447143555</v>
+        <v>1.83686435222626</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.79216206073761</v>
+        <v>1.79216194152832</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.83686447143555</v>
+        <v>1.83686435222626</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.92626941204071</v>
+        <v>1.92626953125</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.8978226184845</v>
+        <v>1.89782238006592</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.91814148426056</v>
+        <v>1.91814160346985</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.88563084602356</v>
+        <v>1.88563096523285</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.91001403331757</v>
+        <v>1.91001391410828</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.89375829696655</v>
+        <v>1.89375841617584</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.86124765872955</v>
+        <v>1.86124777793884</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.84499216079712</v>
+        <v>1.84499228000641</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>2.25</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.82873690128326</v>
+        <v>1.82873678207397</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>2.25</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.82873690128326</v>
+        <v>1.82873678207397</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.85718381404877</v>
+        <v>1.85718393325806</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.85718381404877</v>
+        <v>1.85718393325806</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.85312008857727</v>
+        <v>1.85311996936798</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.86937534809113</v>
+        <v>1.86937546730042</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>2.25</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.82873690128326</v>
+        <v>1.82873678207397</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.83686447143555</v>
+        <v>1.83686435222626</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.86124765872955</v>
+        <v>1.86124777793884</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.89375829696655</v>
+        <v>1.89375841617584</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.88156700134277</v>
+        <v>1.88156712055206</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.89375829696655</v>
+        <v>1.89375841617584</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>2.25</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.82873690128326</v>
+        <v>1.82873678207397</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.85718381404877</v>
+        <v>1.85718393325806</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1462" t="n">
-        <v>1.84499216079712</v>
+        <v>1.84499228000641</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.81248152256012</v>
+        <v>1.81248128414154</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.85718381404877</v>
+        <v>1.85718393325806</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.86937534809113</v>
+        <v>1.86937546730042</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.88563084602356</v>
+        <v>1.88563096523285</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.90188634395599</v>
+        <v>1.90188610553741</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.86124765872955</v>
+        <v>1.86124777793884</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1472" t="n">
-        <v>1.88156700134277</v>
+        <v>1.88156712055206</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.85312008857727</v>
+        <v>1.85311996936798</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1475" t="n">
-        <v>1.83280062675476</v>
+        <v>1.83280074596405</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.82060897350311</v>
+        <v>1.82060921192169</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.9222058057785</v>
+        <v>1.92220556735992</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.88156700134277</v>
+        <v>1.88156712055206</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.88156700134277</v>
+        <v>1.88156712055206</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.8409286737442</v>
+        <v>1.84092855453491</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.89375829696655</v>
+        <v>1.89375841617584</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>1.91001403331757</v>
+        <v>1.91001391410828</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.91001403331757</v>
+        <v>1.91001391410828</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.97097194194794</v>
+        <v>1.97097218036652</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.84231603145599</v>
+        <v>1.84231626987457</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.81605982780457</v>
+        <v>1.81605994701385</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.8204357624054</v>
+        <v>1.82043588161469</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.8204357624054</v>
+        <v>1.82043588161469</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.81605982780457</v>
+        <v>1.81605994701385</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G1519" t="n">
-        <v>1.74516785144806</v>
+        <v>1.74516773223877</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.84231603145599</v>
+        <v>1.84231626987457</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.85106825828552</v>
+        <v>1.85106813907623</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.84231603145599</v>
+        <v>1.84231626987457</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419641971588</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.90358066558838</v>
+        <v>1.90358054637909</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.89045262336731</v>
+        <v>1.8904527425766</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419641971588</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419641971588</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>2.125</v>
       </c>
       <c r="G1535" t="n">
-        <v>1.85982012748718</v>
+        <v>1.85982036590576</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.8204357624054</v>
+        <v>1.82043588161469</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>2</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.75041902065277</v>
+        <v>1.75041913986206</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.79417955875397</v>
+        <v>1.79417967796326</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.84231603145599</v>
+        <v>1.84231626987457</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.85106825828552</v>
+        <v>1.85106813907623</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.89045262336731</v>
+        <v>1.8904527425766</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419641971588</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>2.125</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.85982012748718</v>
+        <v>1.85982036590576</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.69790649414062</v>
+        <v>1.69790661334991</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.72416269779205</v>
+        <v>1.72416293621063</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.71716117858887</v>
+        <v>1.71716105937958</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1574" t="n">
-        <v>1.62438881397247</v>
+        <v>1.62438893318176</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.58938050270081</v>
+        <v>1.5893806219101</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.633141040802</v>
+        <v>1.63314116001129</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.63139057159424</v>
+        <v>1.63139069080353</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.72766363620758</v>
+        <v>1.72766375541687</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.72766363620758</v>
+        <v>1.72766375541687</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1587" t="n">
-        <v>1.75917112827301</v>
+        <v>1.7591712474823</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.79417955875397</v>
+        <v>1.79417967796326</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.79417955875397</v>
+        <v>1.79417967796326</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.77229940891266</v>
+        <v>1.77229952812195</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>2</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.75041902065277</v>
+        <v>1.75041913986206</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>2</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.75041902065277</v>
+        <v>1.75041913986206</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.75041902065277</v>
+        <v>1.75041913986206</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.75479531288147</v>
+        <v>1.75479519367218</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.79855561256409</v>
+        <v>1.79855573177338</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.8204357624054</v>
+        <v>1.82043588161469</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G1607" t="n">
-        <v>1.77229940891266</v>
+        <v>1.77229952812195</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>2</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.75041902065277</v>
+        <v>1.75041913986206</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.81932306289673</v>
+        <v>1.81932294368744</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.81932306289673</v>
+        <v>1.81932294368744</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.84200775623322</v>
+        <v>1.84200763702393</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.80389726161957</v>
+        <v>1.80389714241028</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.8329336643219</v>
+        <v>1.83293378353119</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1636" t="n">
-        <v>1.8329336643219</v>
+        <v>1.83293378353119</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.72767615318298</v>
+        <v>1.72767627239227</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1645" t="n">
-        <v>1.73312044143677</v>
+        <v>1.73312056064606</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.52260541915894</v>
+        <v>1.52260529994965</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.49356877803802</v>
+        <v>1.49356889724731</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1659" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.4227921962738</v>
+        <v>1.42279207706451</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.30301630496979</v>
+        <v>1.3030161857605</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.34294164180756</v>
+        <v>1.34294152259827</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.33023798465729</v>
+        <v>1.33023810386658</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1678" t="n">
-        <v>1.48449492454529</v>
+        <v>1.484494805336</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.46271753311157</v>
+        <v>1.46271741390228</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.44638431072235</v>
+        <v>1.44638442993164</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.46271753311157</v>
+        <v>1.46271741390228</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.46997654438019</v>
+        <v>1.46997666358948</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.41734790802002</v>
+        <v>1.41734778881073</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.38649642467499</v>
+        <v>1.38649654388428</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>1.5</v>
       </c>
       <c r="G1701" t="n">
-        <v>1.36108946800232</v>
+        <v>1.36108934879303</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>1.5</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.36108946800232</v>
+        <v>1.36108934879303</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>1.35599994659424</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.23042476177216</v>
+        <v>1.23042488098145</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.27760934829712</v>
+        <v>1.27760922908783</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.26127624511719</v>
+        <v>1.2612761259079</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.24312841892242</v>
+        <v>1.24312829971313</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.34657108783722</v>
+        <v>1.34657120704651</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.33023798465729</v>
+        <v>1.33023810386658</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.29031276702881</v>
+        <v>1.2903128862381</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.37923717498779</v>
+        <v>1.37923729419708</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.34475636482239</v>
+        <v>1.3447562456131</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.34294164180756</v>
+        <v>1.34294152259827</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.40101480484009</v>
+        <v>1.4010146856308</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.40101480484009</v>
+        <v>1.4010146856308</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.41734790802002</v>
+        <v>1.41734778881073</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>1.5</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.36108946800232</v>
+        <v>1.36108934879303</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.37742257118225</v>
+        <v>1.37742245197296</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.37742257118225</v>
+        <v>1.37742245197296</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.34657108783722</v>
+        <v>1.34657120704651</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.37923717498779</v>
+        <v>1.37923729419708</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1787" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.46271753311157</v>
+        <v>1.46271741390228</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.49356877803802</v>
+        <v>1.49356889724731</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.46997654438019</v>
+        <v>1.46997666358948</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.48449492454529</v>
+        <v>1.484494805336</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.6242333650589</v>
+        <v>1.62423324584961</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.62786293029785</v>
+        <v>1.62786304950714</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1814" t="n">
-        <v>1.48449492454529</v>
+        <v>1.484494805336</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1819" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.37742257118225</v>
+        <v>1.37742245197296</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.37923717498779</v>
+        <v>1.37923729419708</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1829" t="n">
-        <v>1.38286697864532</v>
+        <v>1.38286685943604</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.27397966384888</v>
+        <v>1.27397978305817</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.24675786495209</v>
+        <v>1.24675798416138</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1843" t="n">
-        <v>1.21409177780151</v>
+        <v>1.2140918970108</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.23949873447418</v>
+        <v>1.23949885368347</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.21409177780151</v>
+        <v>1.2140918970108</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.21409177780151</v>
+        <v>1.2140918970108</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>1.56200003623962</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>9476</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>1.56599998474121</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>1.54200005531311</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>1.50999999046326</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>1.52799999713898</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>5849</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>1.54999995231628</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>1.55999994277954</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>13515</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>1.54200005531311</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>1.54200005531311</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>1.53199994564056</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>10741</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>1.56200003623962</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>1.53199994564056</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>1.53199994564056</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>1.54999995231628</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>7358</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>1.57200002670288</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>1.53799998760223</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>1.53799998760223</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>23826</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>1.60199999809265</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>1.58200001716614</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74831414222717</v>
+        <v>2.74831390380859</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74831414222717</v>
+        <v>2.74831390380859</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6863009929657</v>
+        <v>2.68630075454712</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G6" t="n">
-        <v>2.75958895683289</v>
+        <v>2.75958919525146</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7469048500061</v>
+        <v>2.74690461158752</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.81878352165222</v>
+        <v>2.8187837600708</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G9" t="n">
-        <v>2.71730756759644</v>
+        <v>2.71730732917786</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>2.60737490653992</v>
+        <v>2.6073751449585</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G11" t="n">
-        <v>2.48757648468018</v>
+        <v>2.48757672309875</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36073160171509</v>
+        <v>2.36073112487793</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>2.45234203338623</v>
+        <v>2.45234227180481</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>2.1140878200531</v>
+        <v>2.11408758163452</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G24" t="n">
-        <v>1.97455811500549</v>
+        <v>1.97455823421478</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G25" t="n">
-        <v>1.87449109554291</v>
+        <v>1.87449133396149</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G26" t="n">
-        <v>1.86885356903076</v>
+        <v>1.86885368824005</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G27" t="n">
-        <v>1.72650516033173</v>
+        <v>1.72650504112244</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G28" t="n">
-        <v>1.71100175380707</v>
+        <v>1.71100163459778</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G29" t="n">
-        <v>1.86039733886719</v>
+        <v>1.86039745807648</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.5</v>
       </c>
       <c r="G30" t="n">
-        <v>1.76173985004425</v>
+        <v>1.76173996925354</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G35" t="n">
-        <v>2.05207443237305</v>
+        <v>2.05207467079163</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G37" t="n">
-        <v>2.15918827056885</v>
+        <v>2.15918850898743</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G40" t="n">
-        <v>2.06616878509521</v>
+        <v>2.06616854667664</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G42" t="n">
-        <v>2.06334972381592</v>
+        <v>2.0633499622345</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G43" t="n">
-        <v>2.07321548461914</v>
+        <v>2.07321524620056</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G46" t="n">
-        <v>2.15777921676636</v>
+        <v>2.15777897834778</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12113451957703</v>
+        <v>2.12113475799561</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>2.12818217277527</v>
+        <v>2.12818145751953</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G51" t="n">
-        <v>2.21274518966675</v>
+        <v>2.21274542808533</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G52" t="n">
-        <v>2.26348304748535</v>
+        <v>2.26348328590393</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G54" t="n">
-        <v>2.17469167709351</v>
+        <v>2.17469143867493</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G55" t="n">
-        <v>2.18596696853638</v>
+        <v>2.1859667301178</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G56" t="n">
-        <v>2.17891979217529</v>
+        <v>2.17892026901245</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G57" t="n">
-        <v>2.20147013664246</v>
+        <v>2.20147037506104</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G58" t="n">
-        <v>2.23670506477356</v>
+        <v>2.23670530319214</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>2.17751049995422</v>
+        <v>2.17751026153564</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3</v>
       </c>
       <c r="G60" t="n">
-        <v>2.1140878200531</v>
+        <v>2.11408758163452</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G61" t="n">
-        <v>2.18314790725708</v>
+        <v>2.18314814567566</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>2.12818217277527</v>
+        <v>2.12818145751953</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G63" t="n">
-        <v>1.9773770570755</v>
+        <v>1.97737681865692</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G64" t="n">
-        <v>1.89281320571899</v>
+        <v>1.89281344413757</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>1.98724257946014</v>
+        <v>1.98724269866943</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G66" t="n">
-        <v>1.94496083259583</v>
+        <v>1.94496059417725</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G67" t="n">
-        <v>1.95482659339905</v>
+        <v>1.95482647418976</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G69" t="n">
-        <v>1.98724257946014</v>
+        <v>1.98724269866943</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.97455811500549</v>
+        <v>1.97455823421478</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>1.98019540309906</v>
+        <v>1.98019576072693</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G73" t="n">
-        <v>2.00838351249695</v>
+        <v>2.00838327407837</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G74" t="n">
-        <v>2.06616878509521</v>
+        <v>2.06616854667664</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G75" t="n">
-        <v>2.1070408821106</v>
+        <v>2.10704112052917</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G77" t="n">
-        <v>2.14791321754456</v>
+        <v>2.14791345596313</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G78" t="n">
-        <v>2.17751049995422</v>
+        <v>2.17751026153564</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G79" t="n">
-        <v>2.18032932281494</v>
+        <v>2.18032956123352</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G80" t="n">
-        <v>2.12113451957703</v>
+        <v>2.12113475799561</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>2.1070408821106</v>
+        <v>2.10704112052917</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G84" t="n">
-        <v>1.98724257946014</v>
+        <v>1.98724269866943</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G85" t="n">
-        <v>1.9491890668869</v>
+        <v>1.94918918609619</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>1.97314834594727</v>
+        <v>1.97314846515656</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G87" t="n">
-        <v>1.95623588562012</v>
+        <v>1.95623564720154</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>1.7402480840683</v>
+        <v>1.74024832248688</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G94" t="n">
-        <v>1.68128097057343</v>
+        <v>1.681281208992</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G95" t="n">
-        <v>1.61224663257599</v>
+        <v>1.6122465133667</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62662863731384</v>
+        <v>1.62662875652313</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G102" t="n">
-        <v>1.78914761543274</v>
+        <v>1.78914749622345</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G103" t="n">
-        <v>1.86249697208405</v>
+        <v>1.86249709129333</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G104" t="n">
-        <v>1.83373236656189</v>
+        <v>1.83373260498047</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G105" t="n">
-        <v>1.86249697208405</v>
+        <v>1.86249709129333</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G106" t="n">
-        <v>1.84092342853546</v>
+        <v>1.84092366695404</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>1.81215918064117</v>
+        <v>1.81215906143188</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>1.8265415430069</v>
+        <v>1.82654142379761</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G109" t="n">
-        <v>1.79490077495575</v>
+        <v>1.79490065574646</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G110" t="n">
-        <v>1.83517062664032</v>
+        <v>1.83517074584961</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G111" t="n">
-        <v>1.83948528766632</v>
+        <v>1.83948564529419</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G113" t="n">
-        <v>1.8049681186676</v>
+        <v>1.80496823787689</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G116" t="n">
-        <v>1.72011268138885</v>
+        <v>1.72011291980743</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G117" t="n">
-        <v>1.73880970478058</v>
+        <v>1.73880982398987</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G118" t="n">
-        <v>1.63381969928741</v>
+        <v>1.63381958007812</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G120" t="n">
-        <v>1.75606882572174</v>
+        <v>1.75606858730316</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G121" t="n">
-        <v>1.75319182872772</v>
+        <v>1.75319218635559</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>1.81215918064117</v>
+        <v>1.81215906143188</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G123" t="n">
-        <v>1.83804702758789</v>
+        <v>1.83804726600647</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G124" t="n">
-        <v>1.61224663257599</v>
+        <v>1.6122465133667</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G125" t="n">
-        <v>1.48999762535095</v>
+        <v>1.48999774456024</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G133" t="n">
-        <v>1.50869464874268</v>
+        <v>1.5086944103241</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G136" t="n">
-        <v>1.63238167762756</v>
+        <v>1.63238155841827</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G137" t="n">
-        <v>1.63381969928741</v>
+        <v>1.63381958007812</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G139" t="n">
-        <v>1.62087547779083</v>
+        <v>1.6208758354187</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G140" t="n">
-        <v>1.62087547779083</v>
+        <v>1.6208758354187</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G141" t="n">
-        <v>1.61224663257599</v>
+        <v>1.6122465133667</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G147" t="n">
-        <v>1.56766164302826</v>
+        <v>1.56766152381897</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G148" t="n">
-        <v>1.48855936527252</v>
+        <v>1.48855924606323</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G150" t="n">
-        <v>1.48855936527252</v>
+        <v>1.48855924606323</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G152" t="n">
-        <v>1.33754599094391</v>
+        <v>1.3375461101532</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G154" t="n">
-        <v>1.42959225177765</v>
+        <v>1.42959213256836</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G155" t="n">
-        <v>1.43462598323822</v>
+        <v>1.43462586402893</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G157" t="n">
-        <v>1.48999762535095</v>
+        <v>1.48999774456024</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G158" t="n">
-        <v>1.48136818408966</v>
+        <v>1.48136830329895</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>1.56622338294983</v>
+        <v>1.56622326374054</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G160" t="n">
-        <v>1.53314423561096</v>
+        <v>1.53314411640167</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G162" t="n">
-        <v>1.50581812858582</v>
+        <v>1.5058182477951</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G164" t="n">
-        <v>1.5173237323761</v>
+        <v>1.51732385158539</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G165" t="n">
-        <v>1.53602075576782</v>
+        <v>1.53602051734924</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G166" t="n">
-        <v>1.52595293521881</v>
+        <v>1.5259530544281</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G167" t="n">
-        <v>1.54608845710754</v>
+        <v>1.54608821868896</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G168" t="n">
-        <v>1.52307677268982</v>
+        <v>1.52307665348053</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G171" t="n">
-        <v>1.50869464874268</v>
+        <v>1.5086944103241</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G173" t="n">
-        <v>1.55759370326996</v>
+        <v>1.55759382247925</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G174" t="n">
-        <v>1.56478500366211</v>
+        <v>1.5647851228714</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G179" t="n">
-        <v>1.50725638866425</v>
+        <v>1.50725615024567</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G182" t="n">
-        <v>1.4698623418808</v>
+        <v>1.46986246109009</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G183" t="n">
-        <v>1.45979487895966</v>
+        <v>1.45979499816895</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G184" t="n">
-        <v>1.48855936527252</v>
+        <v>1.48855924606323</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G186" t="n">
-        <v>1.48855936527252</v>
+        <v>1.48855924606323</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G188" t="n">
-        <v>1.48999762535095</v>
+        <v>1.48999774456024</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G189" t="n">
-        <v>1.45979487895966</v>
+        <v>1.45979499816895</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G190" t="n">
-        <v>1.4698623418808</v>
+        <v>1.46986246109009</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G193" t="n">
-        <v>1.4698623418808</v>
+        <v>1.46986246109009</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G194" t="n">
-        <v>1.46267127990723</v>
+        <v>1.46267139911652</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>1.67552804946899</v>
+        <v>1.67552816867828</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G204" t="n">
-        <v>1.68703365325928</v>
+        <v>1.68703389167786</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G206" t="n">
-        <v>1.72730398178101</v>
+        <v>1.7273041009903</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G207" t="n">
-        <v>1.73161888122559</v>
+        <v>1.7316187620163</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G208" t="n">
-        <v>1.73449528217316</v>
+        <v>1.73449504375458</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>1.74743914604187</v>
+        <v>1.74743902683258</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G210" t="n">
-        <v>1.77332711219788</v>
+        <v>1.77332723140717</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G211" t="n">
-        <v>1.75606882572174</v>
+        <v>1.75606858730316</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G212" t="n">
-        <v>1.71723651885986</v>
+        <v>1.71723663806915</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>1.74743914604187</v>
+        <v>1.74743902683258</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G214" t="n">
-        <v>1.71867477893829</v>
+        <v>1.718674659729</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>1.67552804946899</v>
+        <v>1.67552816867828</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G216" t="n">
-        <v>1.58348190784454</v>
+        <v>1.58348178863525</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G221" t="n">
-        <v>1.42743492126465</v>
+        <v>1.42743504047394</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G226" t="n">
-        <v>1.39004123210907</v>
+        <v>1.39004111289978</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G229" t="n">
-        <v>1.33754599094391</v>
+        <v>1.3375461101532</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G231" t="n">
-        <v>1.33754599094391</v>
+        <v>1.3375461101532</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G232" t="n">
-        <v>1.34473729133606</v>
+        <v>1.34473717212677</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G233" t="n">
-        <v>1.3332314491272</v>
+        <v>1.33323132991791</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G236" t="n">
-        <v>1.32316386699677</v>
+        <v>1.32316398620605</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G238" t="n">
-        <v>1.38069260120392</v>
+        <v>1.38069272041321</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G239" t="n">
-        <v>1.34545636177063</v>
+        <v>1.34545624256134</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G240" t="n">
-        <v>1.4022661447525</v>
+        <v>1.40226602554321</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.95299994945526</v>
       </c>
       <c r="G241" t="n">
-        <v>1.40442335605621</v>
+        <v>1.4044234752655</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G242" t="n">
-        <v>1.48712110519409</v>
+        <v>1.48712122440338</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G245" t="n">
-        <v>1.48855936527252</v>
+        <v>1.48855924606323</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G246" t="n">
-        <v>1.45979487895966</v>
+        <v>1.45979499816895</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G248" t="n">
-        <v>1.53602075576782</v>
+        <v>1.53602051734924</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G251" t="n">
-        <v>1.5173237323761</v>
+        <v>1.51732385158539</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G252" t="n">
-        <v>1.54608845710754</v>
+        <v>1.54608821868896</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G256" t="n">
-        <v>1.55759370326996</v>
+        <v>1.55759382247925</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G258" t="n">
-        <v>1.60649347305298</v>
+        <v>1.60649359226227</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G259" t="n">
-        <v>1.64388728141785</v>
+        <v>1.64388716220856</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>1.64676356315613</v>
+        <v>1.64676368236542</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G261" t="n">
-        <v>1.6582692861557</v>
+        <v>1.65826952457428</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G262" t="n">
-        <v>1.66546070575714</v>
+        <v>1.66546046733856</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>1.66114592552185</v>
+        <v>1.66114580631256</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>1.66546070575714</v>
+        <v>1.66546046733856</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G265" t="n">
-        <v>1.65683114528656</v>
+        <v>1.65683126449585</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>1.697101354599</v>
+        <v>1.69710123538971</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G268" t="n">
-        <v>1.72011268138885</v>
+        <v>1.72011291980743</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G269" t="n">
-        <v>1.72298943996429</v>
+        <v>1.722989320755</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G270" t="n">
-        <v>1.72442770004272</v>
+        <v>1.72442758083344</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G271" t="n">
-        <v>1.77476525306702</v>
+        <v>1.77476561069489</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G272" t="n">
-        <v>1.78483295440674</v>
+        <v>1.78483331203461</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G273" t="n">
-        <v>1.74168646335602</v>
+        <v>1.74168622493744</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G274" t="n">
-        <v>1.74887728691101</v>
+        <v>1.7488774061203</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G275" t="n">
-        <v>1.75463044643402</v>
+        <v>1.75463020801544</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>1.66114592552185</v>
+        <v>1.66114580631256</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G279" t="n">
-        <v>1.64244890213013</v>
+        <v>1.64244902133942</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G280" t="n">
-        <v>1.71723651885986</v>
+        <v>1.71723663806915</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G282" t="n">
-        <v>1.71435987949371</v>
+        <v>1.71436035633087</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G284" t="n">
-        <v>1.62087547779083</v>
+        <v>1.6208758354187</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G287" t="n">
-        <v>1.66833698749542</v>
+        <v>1.66833710670471</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G288" t="n">
-        <v>1.64244890213013</v>
+        <v>1.64244902133942</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G289" t="n">
-        <v>1.65970766544342</v>
+        <v>1.65970778465271</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G291" t="n">
-        <v>1.63094341754913</v>
+        <v>1.63094317913055</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G292" t="n">
-        <v>1.62375211715698</v>
+        <v>1.62375223636627</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G293" t="n">
-        <v>1.58635854721069</v>
+        <v>1.5863584280014</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G294" t="n">
-        <v>1.5173237323761</v>
+        <v>1.51732385158539</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G295" t="n">
-        <v>1.48136818408966</v>
+        <v>1.48136830329895</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G299" t="n">
-        <v>1.45979487895966</v>
+        <v>1.45979499816895</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>1.52451479434967</v>
+        <v>1.52451491355896</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G304" t="n">
-        <v>1.50150322914124</v>
+        <v>1.5015035867691</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G306" t="n">
-        <v>1.51157081127167</v>
+        <v>1.51157093048096</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G308" t="n">
-        <v>1.55903208255768</v>
+        <v>1.55903232097626</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>1.53889727592468</v>
+        <v>1.53889715671539</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>1.8265415430069</v>
+        <v>1.82654142379761</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>1.76901257038116</v>
+        <v>1.76901268959045</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G314" t="n">
-        <v>1.75750696659088</v>
+        <v>1.7575067281723</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>1.81215918064117</v>
+        <v>1.81215906143188</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G318" t="n">
-        <v>1.99049854278564</v>
+        <v>1.99049866199493</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>1.95166683197021</v>
+        <v>1.95166659355164</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G320" t="n">
-        <v>1.9804310798645</v>
+        <v>1.98043096065521</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G322" t="n">
-        <v>1.9631724357605</v>
+        <v>1.96317255496979</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G323" t="n">
-        <v>1.94303703308105</v>
+        <v>1.94303727149963</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G325" t="n">
-        <v>1.95885765552521</v>
+        <v>1.9588577747345</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.71199989318848</v>
       </c>
       <c r="G327" t="n">
-        <v>1.9502284526825</v>
+        <v>1.95022821426392</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>1.9631724357605</v>
+        <v>1.96317255496979</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>1.77620339393616</v>
+        <v>1.77620363235474</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G332" t="n">
-        <v>1.71004557609558</v>
+        <v>1.71004545688629</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G334" t="n">
-        <v>1.81359732151031</v>
+        <v>1.81359767913818</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G335" t="n">
-        <v>1.79058587551117</v>
+        <v>1.79058599472046</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G336" t="n">
-        <v>1.85386753082275</v>
+        <v>1.85386776924133</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G337" t="n">
-        <v>1.90852010250092</v>
+        <v>1.90851998329163</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G338" t="n">
-        <v>2.00488090515137</v>
+        <v>2.00488114356995</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G339" t="n">
-        <v>1.96748721599579</v>
+        <v>1.9674870967865</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G342" t="n">
-        <v>1.70136141777039</v>
+        <v>1.70136153697968</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G343" t="n">
-        <v>1.72954452037811</v>
+        <v>1.72954428195953</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G344" t="n">
-        <v>1.7236111164093</v>
+        <v>1.72361123561859</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G345" t="n">
-        <v>1.67762851715088</v>
+        <v>1.67762863636017</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G346" t="n">
-        <v>1.71619474887848</v>
+        <v>1.7161945104599</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G347" t="n">
-        <v>1.76514422893524</v>
+        <v>1.76514410972595</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G348" t="n">
-        <v>1.75179421901703</v>
+        <v>1.75179398059845</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G349" t="n">
-        <v>1.71471130847931</v>
+        <v>1.7147114276886</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G350" t="n">
-        <v>1.71322810649872</v>
+        <v>1.71322786808014</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G352" t="n">
-        <v>1.68652832508087</v>
+        <v>1.68652820587158</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G354" t="n">
-        <v>1.67169511318207</v>
+        <v>1.67169523239136</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G355" t="n">
-        <v>1.67911195755005</v>
+        <v>1.67911171913147</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G356" t="n">
-        <v>1.67762851715088</v>
+        <v>1.67762863636017</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G357" t="n">
-        <v>1.73547744750977</v>
+        <v>1.73547756671906</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G360" t="n">
-        <v>1.69394481182098</v>
+        <v>1.69394493103027</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G361" t="n">
-        <v>1.69246172904968</v>
+        <v>1.69246160984039</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="n">
-        <v>1.68207848072052</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G363" t="n">
-        <v>1.67911195755005</v>
+        <v>1.67911171913147</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>1.69839465618134</v>
+        <v>1.69839489459991</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G365" t="n">
-        <v>1.70284485816956</v>
+        <v>1.70284473896027</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G366" t="n">
-        <v>1.69839465618134</v>
+        <v>1.69839489459991</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>1.69839465618134</v>
+        <v>1.69839489459991</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G368" t="n">
-        <v>1.72212779521942</v>
+        <v>1.72212791442871</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G370" t="n">
-        <v>1.70136141777039</v>
+        <v>1.70136153697968</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G371" t="n">
-        <v>1.70432817935944</v>
+        <v>1.70432841777802</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>1.69097828865051</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G373" t="n">
-        <v>1.68207848072052</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G374" t="n">
-        <v>1.75772738456726</v>
+        <v>1.75772750377655</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G375" t="n">
-        <v>1.74141097068787</v>
+        <v>1.74141108989716</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G376" t="n">
-        <v>1.69097828865051</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>1.72806131839752</v>
+        <v>1.72806119918823</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G378" t="n">
-        <v>1.67762851715088</v>
+        <v>1.67762863636017</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G379" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G381" t="n">
-        <v>1.71916139125824</v>
+        <v>1.71916115283966</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G382" t="n">
-        <v>1.73102796077728</v>
+        <v>1.73102784156799</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G383" t="n">
-        <v>1.72806131839752</v>
+        <v>1.72806119918823</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>1.75031089782715</v>
+        <v>1.75031077861786</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G385" t="n">
-        <v>1.75921082496643</v>
+        <v>1.75921058654785</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G386" t="n">
-        <v>1.75921082496643</v>
+        <v>1.75921058654785</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G387" t="n">
-        <v>1.73696100711823</v>
+        <v>1.73696112632751</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G388" t="n">
-        <v>1.71174454689026</v>
+        <v>1.71174478530884</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G389" t="n">
-        <v>1.70284485816956</v>
+        <v>1.70284473896027</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G390" t="n">
-        <v>1.69394481182098</v>
+        <v>1.69394493103027</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G391" t="n">
-        <v>1.69394481182098</v>
+        <v>1.69394493103027</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>1.69839465618134</v>
+        <v>1.69839489459991</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G393" t="n">
-        <v>1.71471130847931</v>
+        <v>1.7147114276886</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G394" t="n">
-        <v>1.7087779045105</v>
+        <v>1.70877802371979</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G396" t="n">
-        <v>1.72212779521942</v>
+        <v>1.72212791442871</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G397" t="n">
-        <v>1.70136141777039</v>
+        <v>1.70136153697968</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G398" t="n">
-        <v>1.71322810649872</v>
+        <v>1.71322786808014</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G399" t="n">
-        <v>1.69097828865051</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G400" t="n">
-        <v>1.68949520587921</v>
+        <v>1.68949508666992</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G401" t="n">
-        <v>1.68504524230957</v>
+        <v>1.68504500389099</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G402" t="n">
-        <v>1.67762851715088</v>
+        <v>1.67762863636017</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G406" t="n">
-        <v>1.63312911987305</v>
+        <v>1.63312888145447</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>1.59456300735474</v>
+        <v>1.59456288814545</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G408" t="n">
-        <v>1.6138459444046</v>
+        <v>1.61384618282318</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G409" t="n">
-        <v>1.59159636497498</v>
+        <v>1.59159624576569</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G410" t="n">
-        <v>1.61087918281555</v>
+        <v>1.61087942123413</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G411" t="n">
-        <v>1.68207848072052</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G413" t="n">
-        <v>1.67762851715088</v>
+        <v>1.67762863636017</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G415" t="n">
-        <v>1.67466175556183</v>
+        <v>1.67466187477112</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G416" t="n">
-        <v>1.66576194763184</v>
+        <v>1.66576182842255</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G417" t="n">
-        <v>1.63312911987305</v>
+        <v>1.63312888145447</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G421" t="n">
-        <v>1.60791254043579</v>
+        <v>1.60791277885437</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G422" t="n">
-        <v>1.60197949409485</v>
+        <v>1.60197937488556</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G423" t="n">
-        <v>1.58417975902557</v>
+        <v>1.58417963981628</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>1.59456300735474</v>
+        <v>1.59456288814545</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G425" t="n">
-        <v>1.57082998752594</v>
+        <v>1.57082986831665</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G427" t="n">
-        <v>1.58269643783569</v>
+        <v>1.5826963186264</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G429" t="n">
-        <v>1.59159636497498</v>
+        <v>1.59159624576569</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G430" t="n">
-        <v>1.58714652061462</v>
+        <v>1.58714640140533</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G432" t="n">
-        <v>1.58121311664581</v>
+        <v>1.58121299743652</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G433" t="n">
-        <v>1.56786334514618</v>
+        <v>1.56786322593689</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>1.59456300735474</v>
+        <v>1.59456288814545</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G436" t="n">
-        <v>1.58121311664581</v>
+        <v>1.58121299743652</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G443" t="n">
-        <v>1.57379639148712</v>
+        <v>1.57379651069641</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>1.58714652061462</v>
+        <v>1.58714640140533</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G446" t="n">
-        <v>1.57972967624664</v>
+        <v>1.57972979545593</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G447" t="n">
-        <v>1.66576194763184</v>
+        <v>1.66576182842255</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G448" t="n">
-        <v>1.76217746734619</v>
+        <v>1.76217722892761</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G449" t="n">
-        <v>1.76217746734619</v>
+        <v>1.76217722892761</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G450" t="n">
-        <v>1.74882781505585</v>
+        <v>1.74882757663727</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>1.72806131839752</v>
+        <v>1.72806119918823</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G452" t="n">
-        <v>1.70136141777039</v>
+        <v>1.70136153697968</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G454" t="n">
-        <v>1.70432817935944</v>
+        <v>1.70432841777802</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G455" t="n">
-        <v>1.74437785148621</v>
+        <v>1.74437773227692</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G457" t="n">
-        <v>1.79629361629486</v>
+        <v>1.79629349708557</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G458" t="n">
-        <v>1.83189296722412</v>
+        <v>1.83189308643341</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G460" t="n">
-        <v>1.93720865249634</v>
+        <v>1.93720841407776</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G461" t="n">
-        <v>1.92089188098907</v>
+        <v>1.92089211940765</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.5</v>
       </c>
       <c r="G462" t="n">
-        <v>1.85414302349091</v>
+        <v>1.85414290428162</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G463" t="n">
-        <v>1.90605890750885</v>
+        <v>1.90605854988098</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G465" t="n">
-        <v>1.89122581481934</v>
+        <v>1.89122569561005</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G466" t="n">
-        <v>1.91199231147766</v>
+        <v>1.91199219226837</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G467" t="n">
-        <v>1.93572497367859</v>
+        <v>1.93572509288788</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G468" t="n">
-        <v>1.92089188098907</v>
+        <v>1.92089211940765</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G469" t="n">
-        <v>1.78887701034546</v>
+        <v>1.78887689113617</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G472" t="n">
-        <v>1.78887701034546</v>
+        <v>1.78887689113617</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G473" t="n">
-        <v>1.76514422893524</v>
+        <v>1.76514410972595</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G474" t="n">
-        <v>1.73102796077728</v>
+        <v>1.73102784156799</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G477" t="n">
-        <v>1.63757884502411</v>
+        <v>1.6375789642334</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G478" t="n">
-        <v>1.64054548740387</v>
+        <v>1.64054572582245</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G479" t="n">
-        <v>1.61977934837341</v>
+        <v>1.61977910995483</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G480" t="n">
-        <v>1.61829590797424</v>
+        <v>1.61829602718353</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G482" t="n">
-        <v>1.61681270599365</v>
+        <v>1.61681258678436</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G483" t="n">
-        <v>1.63164567947388</v>
+        <v>1.63164556026459</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G484" t="n">
-        <v>1.64796233177185</v>
+        <v>1.64796221256256</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G485" t="n">
-        <v>1.68652832508087</v>
+        <v>1.68652820587158</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G486" t="n">
-        <v>1.67021179199219</v>
+        <v>1.67021203041077</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G487" t="n">
-        <v>1.69097828865051</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.25</v>
       </c>
       <c r="G488" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G489" t="n">
-        <v>1.63757884502411</v>
+        <v>1.6375789642334</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G490" t="n">
-        <v>1.68207848072052</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G491" t="n">
-        <v>1.66724514961243</v>
+        <v>1.66724526882172</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G492" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G494" t="n">
-        <v>1.68652832508087</v>
+        <v>1.68652820587158</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G495" t="n">
-        <v>1.68949520587921</v>
+        <v>1.68949508666992</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G496" t="n">
-        <v>1.68949520587921</v>
+        <v>1.68949508666992</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.25</v>
       </c>
       <c r="G497" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G498" t="n">
-        <v>1.68949520587921</v>
+        <v>1.68949508666992</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.69097828865051</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G501" t="n">
-        <v>1.68207848072052</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G502" t="n">
-        <v>1.67466175556183</v>
+        <v>1.67466187477112</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G504" t="n">
-        <v>1.66724514961243</v>
+        <v>1.66724526882172</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G505" t="n">
-        <v>1.65834546089172</v>
+        <v>1.65834534168243</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G506" t="n">
-        <v>1.67169511318207</v>
+        <v>1.67169523239136</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.69097828865051</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>1.69839465618134</v>
+        <v>1.69839489459991</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G509" t="n">
-        <v>1.68504524230957</v>
+        <v>1.68504500389099</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G510" t="n">
-        <v>1.69542825222015</v>
+        <v>1.69542801380157</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G511" t="n">
-        <v>1.68207848072052</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G512" t="n">
-        <v>1.67466175556183</v>
+        <v>1.67466187477112</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G513" t="n">
-        <v>1.69097828865051</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>1.69097828865051</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G518" t="n">
-        <v>1.75031089782715</v>
+        <v>1.75031077861786</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G519" t="n">
-        <v>1.75772738456726</v>
+        <v>1.75772750377655</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.375</v>
       </c>
       <c r="G520" t="n">
-        <v>1.76143574714661</v>
+        <v>1.76143598556519</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76514422893524</v>
+        <v>1.76514410972595</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>1.75772738456726</v>
+        <v>1.75772750377655</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.74660265445709</v>
+        <v>1.7466025352478</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G525" t="n">
-        <v>1.75772738456726</v>
+        <v>1.75772750377655</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G527" t="n">
-        <v>1.78739380836487</v>
+        <v>1.78739392757416</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>1.75772738456726</v>
+        <v>1.75772750377655</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>1.79481017589569</v>
+        <v>1.79481053352356</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G531" t="n">
-        <v>1.82818496227264</v>
+        <v>1.82818508148193</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>1.74289417266846</v>
+        <v>1.74289429187775</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G536" t="n">
-        <v>1.69097828865051</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G538" t="n">
-        <v>1.69097828865051</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.25</v>
       </c>
       <c r="G539" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G540" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G541" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G542" t="n">
-        <v>1.62052071094513</v>
+        <v>1.62052083015442</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>1.63906228542328</v>
+        <v>1.63906216621399</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G544" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G545" t="n">
-        <v>1.69468653202057</v>
+        <v>1.69468677043915</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G548" t="n">
-        <v>1.64277052879333</v>
+        <v>1.64277040958405</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G551" t="n">
-        <v>1.65760350227356</v>
+        <v>1.65760374069214</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.25</v>
       </c>
       <c r="G553" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>1.65018725395203</v>
+        <v>1.65018701553345</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G556" t="n">
-        <v>1.63535404205322</v>
+        <v>1.63535392284393</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>1.63535404205322</v>
+        <v>1.63535392284393</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G558" t="n">
-        <v>1.63164567947388</v>
+        <v>1.63164556026459</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G559" t="n">
-        <v>1.6464786529541</v>
+        <v>1.64647889137268</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.25</v>
       </c>
       <c r="G560" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G561" t="n">
-        <v>1.69468653202057</v>
+        <v>1.69468677043915</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.25</v>
       </c>
       <c r="G565" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.25</v>
       </c>
       <c r="G566" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.25</v>
       </c>
       <c r="G567" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>1.63906228542328</v>
+        <v>1.63906216621399</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.25</v>
       </c>
       <c r="G570" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G571" t="n">
-        <v>1.6464786529541</v>
+        <v>1.64647889137268</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G572" t="n">
-        <v>1.65760350227356</v>
+        <v>1.65760374069214</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.25</v>
       </c>
       <c r="G573" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G576" t="n">
-        <v>1.6464786529541</v>
+        <v>1.64647889137268</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>1.68727004528046</v>
+        <v>1.68727016448975</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>1.70210349559784</v>
+        <v>1.70210301876068</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.69839465618134</v>
+        <v>1.69839489459991</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G581" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614507675171</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.25</v>
       </c>
       <c r="G583" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.25</v>
       </c>
       <c r="G586" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G587" t="n">
-        <v>1.6464786529541</v>
+        <v>1.64647889137268</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.25</v>
       </c>
       <c r="G590" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G592" t="n">
-        <v>1.65389561653137</v>
+        <v>1.65389549732208</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G593" t="n">
-        <v>1.69839465618134</v>
+        <v>1.69839489459991</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G594" t="n">
-        <v>1.69097828865051</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G596" t="n">
-        <v>1.69468653202057</v>
+        <v>1.69468677043915</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>1.70210349559784</v>
+        <v>1.70210301876068</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G600" t="n">
-        <v>1.7414003610611</v>
+        <v>1.74140024185181</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>1.70287370681763</v>
+        <v>1.70287358760834</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>1.69902110099792</v>
+        <v>1.69902098178864</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G605" t="n">
-        <v>1.62967336177826</v>
+        <v>1.62967324256897</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G606" t="n">
-        <v>1.64893674850464</v>
+        <v>1.64893662929535</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G607" t="n">
-        <v>1.55262017250061</v>
+        <v>1.5526202917099</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G608" t="n">
-        <v>1.55262017250061</v>
+        <v>1.5526202917099</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G610" t="n">
-        <v>1.48096072673798</v>
+        <v>1.48096084594727</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G613" t="n">
-        <v>1.46400916576385</v>
+        <v>1.46400904655457</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G615" t="n">
-        <v>1.51024091243744</v>
+        <v>1.51024103164673</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G619" t="n">
-        <v>1.49174821376801</v>
+        <v>1.49174809455872</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G620" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G621" t="n">
-        <v>1.58344149589539</v>
+        <v>1.5834413766861</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G622" t="n">
-        <v>1.5564728975296</v>
+        <v>1.55647277832031</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G623" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G624" t="n">
-        <v>1.56803095340729</v>
+        <v>1.568030834198</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G628" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G630" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.65664196014404</v>
+        <v>1.65664184093475</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G634" t="n">
-        <v>1.5564728975296</v>
+        <v>1.55647277832031</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G636" t="n">
-        <v>1.56803095340729</v>
+        <v>1.568030834198</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>1.5603255033493</v>
+        <v>1.56032562255859</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G638" t="n">
-        <v>1.56803095340729</v>
+        <v>1.568030834198</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>1.60655725002289</v>
+        <v>1.60655736923218</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G648" t="n">
-        <v>1.58344149589539</v>
+        <v>1.5834413766861</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G650" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G651" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G652" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>1.56803095340729</v>
+        <v>1.568030834198</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>1.58344149589539</v>
+        <v>1.5834413766861</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G657" t="n">
-        <v>1.62967336177826</v>
+        <v>1.62967324256897</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G658" t="n">
-        <v>1.66049468517303</v>
+        <v>1.66049456596375</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G659" t="n">
-        <v>1.61426258087158</v>
+        <v>1.61426281929016</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G663" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G664" t="n">
-        <v>1.58344149589539</v>
+        <v>1.5834413766861</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G666" t="n">
-        <v>1.58344149589539</v>
+        <v>1.5834413766861</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G668" t="n">
-        <v>1.56417810916901</v>
+        <v>1.5641782283783</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G669" t="n">
-        <v>1.54876744747162</v>
+        <v>1.54876756668091</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G670" t="n">
-        <v>1.54491496086121</v>
+        <v>1.5449150800705</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G673" t="n">
-        <v>1.56417810916901</v>
+        <v>1.5641782283783</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G674" t="n">
-        <v>1.55262017250061</v>
+        <v>1.5526202917099</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>1.5603255033493</v>
+        <v>1.56032562255859</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G679" t="n">
-        <v>1.5564728975296</v>
+        <v>1.55647277832031</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G680" t="n">
-        <v>1.54491496086121</v>
+        <v>1.5449150800705</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G682" t="n">
-        <v>1.54876744747162</v>
+        <v>1.54876756668091</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G683" t="n">
-        <v>1.56417810916901</v>
+        <v>1.5641782283783</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G686" t="n">
-        <v>1.54491496086121</v>
+        <v>1.5449150800705</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G687" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G688" t="n">
-        <v>1.56417810916901</v>
+        <v>1.5641782283783</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>1.56417810916901</v>
+        <v>1.5641782283783</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G691" t="n">
-        <v>1.56803095340729</v>
+        <v>1.568030834198</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G695" t="n">
-        <v>1.5795886516571</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>1.65664196014404</v>
+        <v>1.65664184093475</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G702" t="n">
-        <v>1.56417810916901</v>
+        <v>1.5641782283783</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>1.54876744747162</v>
+        <v>1.54876756668091</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G704" t="n">
-        <v>1.55262017250061</v>
+        <v>1.5526202917099</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G705" t="n">
-        <v>1.56417810916901</v>
+        <v>1.5641782283783</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G707" t="n">
-        <v>1.47479665279388</v>
+        <v>1.47479653358459</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G708" t="n">
-        <v>1.49328923225403</v>
+        <v>1.49328935146332</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G709" t="n">
-        <v>1.48096072673798</v>
+        <v>1.48096084594727</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G710" t="n">
-        <v>1.42548251152039</v>
+        <v>1.42548263072968</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G711" t="n">
-        <v>1.43472898006439</v>
+        <v>1.43472874164581</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G715" t="n">
-        <v>1.44089317321777</v>
+        <v>1.44089305400848</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G716" t="n">
-        <v>1.39157915115356</v>
+        <v>1.39157927036285</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G718" t="n">
-        <v>1.25442481040955</v>
+        <v>1.25442469120026</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G719" t="n">
-        <v>1.21281599998474</v>
+        <v>1.21281588077545</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G722" t="n">
-        <v>1.29911541938782</v>
+        <v>1.29911553859711</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G724" t="n">
-        <v>1.29449212551117</v>
+        <v>1.29449224472046</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G726" t="n">
-        <v>1.31144392490387</v>
+        <v>1.31144404411316</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G728" t="n">
-        <v>1.29911541938782</v>
+        <v>1.29911553859711</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G729" t="n">
-        <v>1.31144392490387</v>
+        <v>1.31144404411316</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G730" t="n">
-        <v>1.30682063102722</v>
+        <v>1.30682075023651</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G732" t="n">
-        <v>1.28370499610901</v>
+        <v>1.28370475769043</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G733" t="n">
-        <v>1.28062260150909</v>
+        <v>1.2806224822998</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G734" t="n">
-        <v>1.23747277259827</v>
+        <v>1.23747289180756</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G736" t="n">
-        <v>1.19278216362</v>
+        <v>1.19278204441071</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G742" t="n">
-        <v>1.17274820804596</v>
+        <v>1.17274832725525</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G743" t="n">
-        <v>1.22976768016815</v>
+        <v>1.22976744174957</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G744" t="n">
-        <v>1.2498015165329</v>
+        <v>1.24980139732361</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G746" t="n">
-        <v>1.23747277259827</v>
+        <v>1.23747289180756</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G749" t="n">
-        <v>1.27908170223236</v>
+        <v>1.27908158302307</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G750" t="n">
-        <v>1.24363708496094</v>
+        <v>1.24363720417023</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G752" t="n">
-        <v>1.22668552398682</v>
+        <v>1.22668564319611</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G753" t="n">
-        <v>1.20665168762207</v>
+        <v>1.20665156841278</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G754" t="n">
-        <v>1.18045353889465</v>
+        <v>1.18045365810394</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G755" t="n">
-        <v>1.17274820804596</v>
+        <v>1.17274832725525</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G758" t="n">
-        <v>1.09569537639618</v>
+        <v>1.09569525718689</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G759" t="n">
-        <v>1.10185945034027</v>
+        <v>1.10185956954956</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G764" t="n">
-        <v>1.1126469373703</v>
+        <v>1.11264681816101</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G769" t="n">
-        <v>1.16350209712982</v>
+        <v>1.16350185871124</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G770" t="n">
-        <v>1.15425562858582</v>
+        <v>1.15425550937653</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G773" t="n">
-        <v>1.11727011203766</v>
+        <v>1.11727023124695</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G774" t="n">
-        <v>1.14346826076508</v>
+        <v>1.14346814155579</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G779" t="n">
-        <v>1.13268089294434</v>
+        <v>1.13268077373505</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G781" t="n">
-        <v>1.13268089294434</v>
+        <v>1.13268077373505</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G782" t="n">
-        <v>1.12651646137238</v>
+        <v>1.12651634216309</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G785" t="n">
-        <v>1.10340070724487</v>
+        <v>1.10340058803558</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G786" t="n">
-        <v>1.07412040233612</v>
+        <v>1.07412052154541</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G787" t="n">
-        <v>1.06641507148743</v>
+        <v>1.06641495227814</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G788" t="n">
-        <v>1.06641507148743</v>
+        <v>1.06641495227814</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G789" t="n">
-        <v>1.13884496688843</v>
+        <v>1.13884484767914</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G790" t="n">
-        <v>1.14038586616516</v>
+        <v>1.14038610458374</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G791" t="n">
-        <v>1.14038586616516</v>
+        <v>1.14038610458374</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G792" t="n">
-        <v>1.15425562858582</v>
+        <v>1.15425550937653</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G793" t="n">
-        <v>1.17428934574127</v>
+        <v>1.17428958415985</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G794" t="n">
-        <v>1.1850768327713</v>
+        <v>1.18507695198059</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>1.18661797046661</v>
+        <v>1.18661785125732</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G796" t="n">
-        <v>1.22668552398682</v>
+        <v>1.22668564319611</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G799" t="n">
-        <v>1.24363708496094</v>
+        <v>1.24363720417023</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G800" t="n">
-        <v>1.24363708496094</v>
+        <v>1.24363720417023</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G806" t="n">
-        <v>1.30219745635986</v>
+        <v>1.30219757556915</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G809" t="n">
-        <v>1.27754044532776</v>
+        <v>1.27754056453705</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G811" t="n">
-        <v>1.21589803695679</v>
+        <v>1.21589815616608</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G812" t="n">
-        <v>1.18199479579926</v>
+        <v>1.18199467658997</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G813" t="n">
-        <v>1.16504311561584</v>
+        <v>1.16504299640656</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G814" t="n">
-        <v>1.16504311561584</v>
+        <v>1.16504299640656</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>1.17120730876923</v>
+        <v>1.17120718955994</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G816" t="n">
-        <v>1.16658413410187</v>
+        <v>1.16658401489258</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G817" t="n">
-        <v>1.16658413410187</v>
+        <v>1.16658401489258</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G818" t="n">
-        <v>1.16504311561584</v>
+        <v>1.16504299640656</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.17120730876923</v>
+        <v>1.17120718955994</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G822" t="n">
-        <v>1.17120730876923</v>
+        <v>1.17120718955994</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G823" t="n">
-        <v>1.14192700386047</v>
+        <v>1.14192712306976</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G825" t="n">
-        <v>1.15425562858582</v>
+        <v>1.15425550937653</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G827" t="n">
-        <v>1.17120730876923</v>
+        <v>1.17120718955994</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G833" t="n">
-        <v>1.16196095943451</v>
+        <v>1.1619610786438</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G834" t="n">
-        <v>1.19586443901062</v>
+        <v>1.19586420059204</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G835" t="n">
-        <v>1.26367104053497</v>
+        <v>1.26367092132568</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G836" t="n">
-        <v>1.27908170223236</v>
+        <v>1.27908158302307</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G842" t="n">
-        <v>1.26367104053497</v>
+        <v>1.26367092132568</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G844" t="n">
-        <v>1.28062260150909</v>
+        <v>1.2806224822998</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G850" t="n">
-        <v>1.26629865169525</v>
+        <v>1.26629877090454</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G851" t="n">
-        <v>1.24028992652893</v>
+        <v>1.24029004573822</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G859" t="n">
-        <v>1.08423781394958</v>
+        <v>1.0842376947403</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G861" t="n">
-        <v>1.08586323261261</v>
+        <v>1.0858633518219</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G866" t="n">
-        <v>1.00133490562439</v>
+        <v>1.00133502483368</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G868" t="n">
-        <v>1.00458598136902</v>
+        <v>1.00458610057831</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G869" t="n">
-        <v>1.01271378993988</v>
+        <v>1.01271367073059</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G871" t="n">
-        <v>1.00783717632294</v>
+        <v>1.00783729553223</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G874" t="n">
-        <v>0.97207510471344</v>
+        <v>0.972075223922729</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G875" t="n">
-        <v>0.95581990480423</v>
+        <v>0.95581978559494</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G877" t="n">
-        <v>0.911930084228516</v>
+        <v>0.91193014383316</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G882" t="n">
-        <v>0.950943052768707</v>
+        <v>0.950943112373352</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G883" t="n">
-        <v>0.957445383071899</v>
+        <v>0.957445323467255</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G884" t="n">
-        <v>0.939564347267151</v>
+        <v>0.939564406871796</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G885" t="n">
-        <v>0.933062195777893</v>
+        <v>0.933062136173248</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G886" t="n">
-        <v>0.95581990480423</v>
+        <v>0.95581978559494</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G887" t="n">
-        <v>0.965573072433472</v>
+        <v>0.965572953224182</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G888" t="n">
-        <v>0.965573072433472</v>
+        <v>0.965572953224182</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G889" t="n">
-        <v>0.983453989028931</v>
+        <v>0.98345410823822</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G893" t="n">
-        <v>1.03547132015228</v>
+        <v>1.03547143936157</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G898" t="n">
-        <v>1.01271378993988</v>
+        <v>1.01271367073059</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G900" t="n">
-        <v>0.994832873344421</v>
+        <v>0.994832754135132</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G901" t="n">
-        <v>0.981828391551971</v>
+        <v>0.981828272342682</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G902" t="n">
-        <v>1.01271378993988</v>
+        <v>1.01271367073059</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G904" t="n">
-        <v>0.983453989028931</v>
+        <v>0.98345410823822</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G905" t="n">
-        <v>1.00133490562439</v>
+        <v>1.00133502483368</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G910" t="n">
-        <v>1.00783717632294</v>
+        <v>1.00783729553223</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G914" t="n">
-        <v>1.01108825206757</v>
+        <v>1.01108813285828</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G915" t="n">
-        <v>1.00783717632294</v>
+        <v>1.00783729553223</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G917" t="n">
-        <v>1.00783717632294</v>
+        <v>1.00783729553223</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>0.950943052768707</v>
+        <v>0.950943112373352</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G920" t="n">
-        <v>0.952568709850311</v>
+        <v>0.952568650245667</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G921" t="n">
-        <v>0.920057892799377</v>
+        <v>0.920057773590088</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G923" t="n">
-        <v>0.954194188117981</v>
+        <v>0.954194307327271</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G926" t="n">
-        <v>0.981828391551971</v>
+        <v>0.981828272342682</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>0.975326359272003</v>
+        <v>0.975326478481293</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G930" t="n">
-        <v>0.97207510471344</v>
+        <v>0.972075223922729</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G933" t="n">
-        <v>0.965573072433472</v>
+        <v>0.965572953224182</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G934" t="n">
-        <v>0.950943052768707</v>
+        <v>0.950943112373352</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G943" t="n">
-        <v>1.20290231704712</v>
+        <v>1.20290243625641</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G948" t="n">
-        <v>1.18014478683472</v>
+        <v>1.18014490604401</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G949" t="n">
-        <v>1.15738725662231</v>
+        <v>1.15738713741302</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G957" t="n">
-        <v>1.09399092197418</v>
+        <v>1.09399104118347</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G964" t="n">
-        <v>1.16226387023926</v>
+        <v>1.16226375102997</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G966" t="n">
-        <v>1.19314932823181</v>
+        <v>1.19314920902252</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G967" t="n">
-        <v>1.18827259540558</v>
+        <v>1.18827247619629</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G972" t="n">
-        <v>1.16714036464691</v>
+        <v>1.1671404838562</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G974" t="n">
-        <v>1.27280080318451</v>
+        <v>1.2728009223938</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G985" t="n">
-        <v>1.34920144081116</v>
+        <v>1.34920132160187</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>1.39796769618988</v>
+        <v>1.39796781539917</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G989" t="n">
-        <v>1.50362801551819</v>
+        <v>1.50362813472748</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G994" t="n">
-        <v>1.53451335430145</v>
+        <v>1.53451347351074</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G996" t="n">
-        <v>1.50037693977356</v>
+        <v>1.50037705898285</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G997" t="n">
-        <v>1.50200259685516</v>
+        <v>1.50200271606445</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.47111713886261</v>
+        <v>1.4711172580719</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.51500689983368</v>
+        <v>1.51500678062439</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.55401992797852</v>
+        <v>1.55401980876923</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.60116076469421</v>
+        <v>1.60116064548492</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.55889654159546</v>
+        <v>1.55889666080475</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.58327972888947</v>
+        <v>1.58327960968018</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.58490538597107</v>
+        <v>1.58490526676178</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.55889654159546</v>
+        <v>1.55889666080475</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.54589223861694</v>
+        <v>1.54589211940765</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.50200259685516</v>
+        <v>1.50200271606445</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.46949148178101</v>
+        <v>1.4694916009903</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.45161068439484</v>
+        <v>1.45161056518555</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.53451335430145</v>
+        <v>1.53451347351074</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.46136379241943</v>
+        <v>1.46136391162872</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.43047857284546</v>
+        <v>1.43047869205475</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.50362801551819</v>
+        <v>1.50362813472748</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.58002853393555</v>
+        <v>1.58002865314484</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.73933207988739</v>
+        <v>1.7393319606781</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.68243777751923</v>
+        <v>1.68243789672852</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.39796769618988</v>
+        <v>1.39796781539917</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.34920144081116</v>
+        <v>1.34920132160187</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.18177032470703</v>
+        <v>1.18177044391632</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.97044962644577</v>
+        <v>0.97044974565506</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.897300183773041</v>
+        <v>0.897300243377686</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.902176737785339</v>
+        <v>0.902176797389984</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.845282793045044</v>
+        <v>0.845282733440399</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.885921478271484</v>
+        <v>0.88592141866684</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.950943052768707</v>
+        <v>0.950943112373352</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.881044685840607</v>
+        <v>0.881044805049896</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.921683371067047</v>
+        <v>0.921683311462402</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.983453989028931</v>
+        <v>0.98345410823822</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.965573072433472</v>
+        <v>0.965572953224182</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.996458351612091</v>
+        <v>0.996458292007446</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.996458351612091</v>
+        <v>0.996458292007446</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.01108825206757</v>
+        <v>1.01108813285828</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.28199994564056</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.04197347164154</v>
+        <v>1.04197359085083</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.04522478580475</v>
+        <v>1.04522466659546</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.0387225151062</v>
+        <v>1.03872263431549</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.0289694070816</v>
+        <v>1.02896928787231</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.01271378993988</v>
+        <v>1.01271367073059</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.97044962644577</v>
+        <v>0.97044974565506</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.959070861339569</v>
+        <v>0.959070801734924</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.97044962644577</v>
+        <v>0.97044974565506</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.975326359272003</v>
+        <v>0.975326478481293</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.999709486961365</v>
+        <v>0.999709606170654</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.05660343170166</v>
+        <v>1.05660355091095</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.08586323261261</v>
+        <v>1.0858633518219</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.15576183795929</v>
+        <v>1.15576171875</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.22403466701508</v>
+        <v>1.22403454780579</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.23866438865662</v>
+        <v>1.23866450786591</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.09886765480042</v>
+        <v>1.09886753559113</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.0972421169281</v>
+        <v>1.09724199771881</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.09886765480042</v>
+        <v>1.09886753559113</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.04522478580475</v>
+        <v>1.04522466659546</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.25979650020599</v>
+        <v>1.2597963809967</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.27930307388306</v>
+        <v>1.27930295467377</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.40446996688843</v>
+        <v>1.40446984767914</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.43047857284546</v>
+        <v>1.43047869205475</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.43210399150848</v>
+        <v>1.43210411071777</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.44998514652252</v>
+        <v>1.44998502731323</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.45161068439484</v>
+        <v>1.45161056518555</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.41422319412231</v>
+        <v>1.4142233133316</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.41422319412231</v>
+        <v>1.4142233133316</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.44510853290558</v>
+        <v>1.44510865211487</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.4467339515686</v>
+        <v>1.44673407077789</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.52638554573059</v>
+        <v>1.52638566493988</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.55401992797852</v>
+        <v>1.55401980876923</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.51175582408905</v>
+        <v>1.51175570487976</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.5052535533905</v>
+        <v>1.50525367259979</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1185" t="n">
-        <v>1.47111713886261</v>
+        <v>1.4711172580719</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.43210399150848</v>
+        <v>1.43210411071777</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.44510853290558</v>
+        <v>1.44510865211487</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.46136379241943</v>
+        <v>1.46136391162872</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.39959323406219</v>
+        <v>1.39959335327148</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.40121865272522</v>
+        <v>1.40121877193451</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.41584861278534</v>
+        <v>1.41584873199463</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.43047857284546</v>
+        <v>1.43047869205475</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.43698072433472</v>
+        <v>1.43698084354401</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.39796769618988</v>
+        <v>1.39796781539917</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.32806921005249</v>
+        <v>1.32806932926178</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.33294594287872</v>
+        <v>1.33294582366943</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.31669056415558</v>
+        <v>1.31669044494629</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.34432470798492</v>
+        <v>1.34432482719421</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.40121865272522</v>
+        <v>1.40121877193451</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.35895466804504</v>
+        <v>1.35895478725433</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.40446996688843</v>
+        <v>1.40446984767914</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.39796769618988</v>
+        <v>1.39796781539917</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.39796769618988</v>
+        <v>1.39796781539917</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.39959323406219</v>
+        <v>1.39959335327148</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.29718399047852</v>
+        <v>1.29718410968781</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.20290231704712</v>
+        <v>1.20290243625641</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.19314932823181</v>
+        <v>1.19314920902252</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.13300406932831</v>
+        <v>1.1330041885376</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.15413618087769</v>
+        <v>1.1541360616684</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.15088498592377</v>
+        <v>1.15088510513306</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.22891128063202</v>
+        <v>1.22891116142273</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1232" t="n">
-        <v>1.23378765583038</v>
+        <v>1.23378777503967</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.23378765583038</v>
+        <v>1.23378777503967</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G1235" t="n">
-        <v>1.31181383132935</v>
+        <v>1.31181395053864</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.32806921005249</v>
+        <v>1.32806932926178</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.39796769618988</v>
+        <v>1.39796781539917</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.39959323406219</v>
+        <v>1.39959335327148</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.4467339515686</v>
+        <v>1.44673407077789</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.4467339515686</v>
+        <v>1.44673407077789</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1247" t="n">
-        <v>1.46136379241943</v>
+        <v>1.46136391162872</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.75</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.42235100269318</v>
+        <v>1.42235088348389</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>1.75</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.42235100269318</v>
+        <v>1.42235088348389</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.3898401260376</v>
+        <v>1.38983988761902</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.39146566390991</v>
+        <v>1.39146554470062</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.34432470798492</v>
+        <v>1.34432482719421</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.33294594287872</v>
+        <v>1.33294582366943</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.31669056415558</v>
+        <v>1.31669044494629</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.34920144081116</v>
+        <v>1.34920132160187</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.32969486713409</v>
+        <v>1.32969498634338</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.3898401260376</v>
+        <v>1.38983988761902</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.39471662044525</v>
+        <v>1.39471650123596</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.42072546482086</v>
+        <v>1.42072522640228</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.75</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.42235100269318</v>
+        <v>1.42235088348389</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.3898401260376</v>
+        <v>1.38983988761902</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.39471662044525</v>
+        <v>1.39471650123596</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.4109719991684</v>
+        <v>1.41097211837769</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.34920144081116</v>
+        <v>1.34920132160187</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.33457148075104</v>
+        <v>1.33457136154175</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.47111713886261</v>
+        <v>1.4711172580719</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.56052196025848</v>
+        <v>1.56052207946777</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.57352650165558</v>
+        <v>1.57352638244629</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.50200259685516</v>
+        <v>1.50200271606445</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.6092883348465</v>
+        <v>1.60928845405579</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.60116076469421</v>
+        <v>1.60116064548492</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.58002853393555</v>
+        <v>1.58002865314484</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.59303295612335</v>
+        <v>1.59303307533264</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.5881564617157</v>
+        <v>1.58815634250641</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992713928223</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.65399098396301</v>
+        <v>1.65399086475372</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.63773548603058</v>
+        <v>1.63773536682129</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.58490538597107</v>
+        <v>1.58490526676178</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.58490538597107</v>
+        <v>1.58490526676178</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.69056558609009</v>
+        <v>1.6905654668808</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.76371502876282</v>
+        <v>1.76371514797211</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.71494877338409</v>
+        <v>1.7149486541748</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.68243777751923</v>
+        <v>1.68243789672852</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.69056558609009</v>
+        <v>1.6905654668808</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.62960779666901</v>
+        <v>1.6296079158783</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.69056558609009</v>
+        <v>1.6905654668808</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.69056558609009</v>
+        <v>1.6905654668808</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.68243777751923</v>
+        <v>1.68243789672852</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.68243777751923</v>
+        <v>1.68243789672852</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.68243777751923</v>
+        <v>1.68243789672852</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992713928223</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.67024636268616</v>
+        <v>1.67024624347687</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.67024636268616</v>
+        <v>1.67024624347687</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.67837417125702</v>
+        <v>1.67837405204773</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.67837417125702</v>
+        <v>1.67837405204773</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992713928223</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992713928223</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992713928223</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.67024636268616</v>
+        <v>1.67024624347687</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992713928223</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.65399098396301</v>
+        <v>1.65399086475372</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.67024636268616</v>
+        <v>1.67024624347687</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.67024636268616</v>
+        <v>1.67024624347687</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.69056558609009</v>
+        <v>1.6905654668808</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.74745976924896</v>
+        <v>1.74745965003967</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.74745976924896</v>
+        <v>1.74745965003967</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.73933207988739</v>
+        <v>1.7393319606781</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.68243777751923</v>
+        <v>1.68243789672852</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.69056558609009</v>
+        <v>1.6905654668808</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.69056558609009</v>
+        <v>1.6905654668808</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.73526799678802</v>
+        <v>1.73526811599731</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.69056558609009</v>
+        <v>1.6905654668808</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.68243777751923</v>
+        <v>1.68243789672852</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.63773548603058</v>
+        <v>1.63773536682129</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.67024636268616</v>
+        <v>1.67024624347687</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992713928223</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.65399098396301</v>
+        <v>1.65399086475372</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1409" t="n">
-        <v>1.58490538597107</v>
+        <v>1.58490526676178</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.73526799678802</v>
+        <v>1.73526811599731</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.73933207988739</v>
+        <v>1.7393319606781</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.71494877338409</v>
+        <v>1.7149486541748</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.73120415210724</v>
+        <v>1.73120427131653</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.73120415210724</v>
+        <v>1.73120427131653</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.71494877338409</v>
+        <v>1.7149486541748</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.73526799678802</v>
+        <v>1.73526811599731</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.74745976924896</v>
+        <v>1.74745965003967</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.75965118408203</v>
+        <v>1.75965106487274</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.77590656280518</v>
+        <v>1.77590668201447</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.7921621799469</v>
+        <v>1.79216194152832</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.87750315666199</v>
+        <v>1.8775030374527</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.92626941204071</v>
+        <v>1.92626953125</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.8978226184845</v>
+        <v>1.89782238006592</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.91814172267914</v>
+        <v>1.91814160346985</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.86124753952026</v>
+        <v>1.86124765872955</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>2.25</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.82873678207397</v>
+        <v>1.82873690128326</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>2.25</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.82873678207397</v>
+        <v>1.82873690128326</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.85718381404877</v>
+        <v>1.85718405246735</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.85718381404877</v>
+        <v>1.85718405246735</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>2.25</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.82873678207397</v>
+        <v>1.82873690128326</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.86124753952026</v>
+        <v>1.86124765872955</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.88156712055206</v>
+        <v>1.88156700134277</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>2.25</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.82873678207397</v>
+        <v>1.82873690128326</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.85718381404877</v>
+        <v>1.85718405246735</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.84905612468719</v>
+        <v>1.84905636310577</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.81248152256012</v>
+        <v>1.81248140335083</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.85718381404877</v>
+        <v>1.85718405246735</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.84905612468719</v>
+        <v>1.84905636310577</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.84905612468719</v>
+        <v>1.84905636310577</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.90188610553741</v>
+        <v>1.9018862247467</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.86124753952026</v>
+        <v>1.86124765872955</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1472" t="n">
-        <v>1.88156712055206</v>
+        <v>1.88156700134277</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.87750315666199</v>
+        <v>1.8775030374527</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.87750315666199</v>
+        <v>1.8775030374527</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.92220556735992</v>
+        <v>1.92220568656921</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1480" t="n">
-        <v>1.90595018863678</v>
+        <v>1.90595006942749</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.88156712055206</v>
+        <v>1.88156700134277</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.88156712055206</v>
+        <v>1.88156700134277</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.87750315666199</v>
+        <v>1.8775030374527</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.97097194194794</v>
+        <v>1.97097170352936</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.92983722686768</v>
+        <v>1.9298369884491</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.84669208526611</v>
+        <v>1.8466922044754</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.84231603145599</v>
+        <v>1.84231615066528</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1498" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.78980362415314</v>
+        <v>1.78980350494385</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1502" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.73291492462158</v>
+        <v>1.73291504383087</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1520" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.84231603145599</v>
+        <v>1.84231615066528</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.84231603145599</v>
+        <v>1.84231615066528</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.86419641971588</v>
+        <v>1.86419653892517</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.90358078479767</v>
+        <v>1.90358066558838</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.86419641971588</v>
+        <v>1.86419653892517</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.86419641971588</v>
+        <v>1.86419653892517</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.84669208526611</v>
+        <v>1.8466922044754</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>2.125</v>
       </c>
       <c r="G1535" t="n">
-        <v>1.85982024669647</v>
+        <v>1.85982012748718</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.84669208526611</v>
+        <v>1.8466922044754</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.83794009685516</v>
+        <v>1.83793997764587</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.78980362415314</v>
+        <v>1.78980350494385</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.84669208526611</v>
+        <v>1.8466922044754</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.83794009685516</v>
+        <v>1.83793997764587</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.84231603145599</v>
+        <v>1.84231615066528</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.84669208526611</v>
+        <v>1.8466922044754</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.86419641971588</v>
+        <v>1.86419653892517</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>2.125</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.85982024669647</v>
+        <v>1.85982012748718</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.72416281700134</v>
+        <v>1.72416269779205</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.71716105937958</v>
+        <v>1.71716117858887</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.58938050270081</v>
+        <v>1.58938038349152</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.63314116001129</v>
+        <v>1.633141040802</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.75479519367218</v>
+        <v>1.75479531288147</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1602" t="n">
-        <v>1.78980362415314</v>
+        <v>1.78980350494385</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.81932294368744</v>
+        <v>1.81932306289673</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.81932294368744</v>
+        <v>1.81932306289673</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.84200763702393</v>
+        <v>1.84200775623322</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.80389714241028</v>
+        <v>1.80389726161957</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.83293378353119</v>
+        <v>1.8329336643219</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1636" t="n">
-        <v>1.83293378353119</v>
+        <v>1.8329336643219</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.72767627239227</v>
+        <v>1.72767615318298</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1645" t="n">
-        <v>1.73312056064606</v>
+        <v>1.73312044143677</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.52260529994965</v>
+        <v>1.52260541915894</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.49356889724731</v>
+        <v>1.49356877803802</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.4427547454834</v>
+        <v>1.44275486469269</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1659" t="n">
-        <v>1.4427547454834</v>
+        <v>1.44275486469269</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.42279207706451</v>
+        <v>1.4227921962738</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.3030161857605</v>
+        <v>1.30301630496979</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.34294152259827</v>
+        <v>1.34294164180756</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.33023810386658</v>
+        <v>1.33023798465729</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1678" t="n">
-        <v>1.484494805336</v>
+        <v>1.48449492454529</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.46271741390228</v>
+        <v>1.46271753311157</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.44638442993164</v>
+        <v>1.44638431072235</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.46271741390228</v>
+        <v>1.46271753311157</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.46997666358948</v>
+        <v>1.46997654438019</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.41734778881073</v>
+        <v>1.41734790802002</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.38649654388428</v>
+        <v>1.38649642467499</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>1.5</v>
       </c>
       <c r="G1701" t="n">
-        <v>1.36108934879303</v>
+        <v>1.36108946800232</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.3737930059433</v>
+        <v>1.37379288673401</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>1.5</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.36108934879303</v>
+        <v>1.36108946800232</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>1.35599994659424</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.23042488098145</v>
+        <v>1.23042476177216</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.27760922908783</v>
+        <v>1.27760934829712</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.2612761259079</v>
+        <v>1.26127624511719</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.24312829971313</v>
+        <v>1.24312841892242</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.34657120704651</v>
+        <v>1.34657108783722</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.33023810386658</v>
+        <v>1.33023798465729</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.2903128862381</v>
+        <v>1.29031276702881</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.37923729419708</v>
+        <v>1.37923717498779</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.3447562456131</v>
+        <v>1.34475636482239</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.34294152259827</v>
+        <v>1.34294164180756</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.4010146856308</v>
+        <v>1.40101480484009</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.4010146856308</v>
+        <v>1.40101480484009</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.41734778881073</v>
+        <v>1.41734790802002</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.3737930059433</v>
+        <v>1.37379288673401</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>1.5</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.36108934879303</v>
+        <v>1.36108946800232</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.37742245197296</v>
+        <v>1.37742257118225</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.37742245197296</v>
+        <v>1.37742257118225</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.34657120704651</v>
+        <v>1.34657108783722</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.37923729419708</v>
+        <v>1.37923717498779</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1787" t="n">
-        <v>1.4427547454834</v>
+        <v>1.44275486469269</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.46271741390228</v>
+        <v>1.46271753311157</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.49356889724731</v>
+        <v>1.49356877803802</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.46997666358948</v>
+        <v>1.46997654438019</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.484494805336</v>
+        <v>1.48449492454529</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.62423324584961</v>
+        <v>1.6242333650589</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.62786304950714</v>
+        <v>1.62786293029785</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1814" t="n">
-        <v>1.484494805336</v>
+        <v>1.48449492454529</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1819" t="n">
-        <v>1.4427547454834</v>
+        <v>1.44275486469269</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.37742245197296</v>
+        <v>1.37742257118225</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.3737930059433</v>
+        <v>1.37379288673401</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.37923729419708</v>
+        <v>1.37923717498779</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1829" t="n">
-        <v>1.38286685943604</v>
+        <v>1.38286697864532</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.3737930059433</v>
+        <v>1.37379288673401</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.27397978305817</v>
+        <v>1.27397966384888</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.24675798416138</v>
+        <v>1.24675786495209</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1843" t="n">
-        <v>1.2140918970108</v>
+        <v>1.21409177780151</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.23949885368347</v>
+        <v>1.23949873447418</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.2340544462204</v>
+        <v>1.23405432701111</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.2340544462204</v>
+        <v>1.23405432701111</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.2340544462204</v>
+        <v>1.23405432701111</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.2340544462204</v>
+        <v>1.23405432701111</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.2140918970108</v>
+        <v>1.21409177780151</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.2140918970108</v>
+        <v>1.21409177780151</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>1.58200001716614</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>11588</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>1.55400002002716</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>1.55200004577637</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>1.55200004577637</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74831390380859</v>
+        <v>2.74831414222717</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74831390380859</v>
+        <v>2.74831414222717</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G7" t="n">
-        <v>2.74690461158752</v>
+        <v>2.7469048500061</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8187837600708</v>
+        <v>2.81878399848938</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G9" t="n">
-        <v>2.71730732917786</v>
+        <v>2.71730756759644</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6073751449585</v>
+        <v>2.60737538337708</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G11" t="n">
-        <v>2.48757672309875</v>
+        <v>2.4875762462616</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36073112487793</v>
+        <v>2.36073136329651</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G13" t="n">
-        <v>2.39314723014832</v>
+        <v>2.39314746856689</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.50167059898376</v>
+        <v>2.50167083740234</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>2.56368398666382</v>
+        <v>2.56368350982666</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>2.45234227180481</v>
+        <v>2.45234203338623</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G20" t="n">
-        <v>2.29730892181396</v>
+        <v>2.29730844497681</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G22" t="n">
-        <v>2.29871821403503</v>
+        <v>2.29871845245361</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>2.11408758163452</v>
+        <v>2.1140878200531</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G24" t="n">
-        <v>1.97455823421478</v>
+        <v>1.97455811500549</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G26" t="n">
-        <v>1.86885368824005</v>
+        <v>1.86885333061218</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G29" t="n">
-        <v>1.86039745807648</v>
+        <v>1.86039733886719</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.5</v>
       </c>
       <c r="G30" t="n">
-        <v>1.76173996925354</v>
+        <v>1.76173973083496</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G31" t="n">
-        <v>1.87731003761292</v>
+        <v>1.87730991840363</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G32" t="n">
-        <v>1.94777977466583</v>
+        <v>1.94777965545654</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G37" t="n">
-        <v>2.15918850898743</v>
+        <v>2.15918827056885</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G38" t="n">
-        <v>2.1605978012085</v>
+        <v>2.16059756278992</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G42" t="n">
-        <v>2.0633499622345</v>
+        <v>2.06334948539734</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G43" t="n">
-        <v>2.07321524620056</v>
+        <v>2.07321548461914</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G45" t="n">
-        <v>2.13522839546204</v>
+        <v>2.13522863388062</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>2.12818145751953</v>
+        <v>2.12818169593811</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G51" t="n">
-        <v>2.21274542808533</v>
+        <v>2.21274518966675</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G55" t="n">
-        <v>2.1859667301178</v>
+        <v>2.18596720695496</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G56" t="n">
-        <v>2.17892026901245</v>
+        <v>2.17891979217529</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G57" t="n">
-        <v>2.20147037506104</v>
+        <v>2.20147013664246</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G58" t="n">
-        <v>2.23670530319214</v>
+        <v>2.2367045879364</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>2.17751026153564</v>
+        <v>2.17751049995422</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3</v>
       </c>
       <c r="G60" t="n">
-        <v>2.11408758163452</v>
+        <v>2.1140878200531</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G61" t="n">
-        <v>2.18314814567566</v>
+        <v>2.18314790725708</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>2.12818145751953</v>
+        <v>2.12818169593811</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G63" t="n">
-        <v>1.97737681865692</v>
+        <v>1.97737669944763</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G64" t="n">
-        <v>1.89281344413757</v>
+        <v>1.89281332492828</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>1.98724269866943</v>
+        <v>1.98724210262299</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G69" t="n">
-        <v>1.98724269866943</v>
+        <v>1.98724210262299</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.97455823421478</v>
+        <v>1.97455811500549</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>1.92381989955902</v>
+        <v>1.92381978034973</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>1.98019576072693</v>
+        <v>1.98019540309906</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G75" t="n">
-        <v>2.10704112052917</v>
+        <v>2.1070408821106</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>2.17046332359314</v>
+        <v>2.17046308517456</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G77" t="n">
-        <v>2.14791345596313</v>
+        <v>2.14791321754456</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G78" t="n">
-        <v>2.17751026153564</v>
+        <v>2.17751049995422</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>2.10704112052917</v>
+        <v>2.1070408821106</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G84" t="n">
-        <v>1.98724269866943</v>
+        <v>1.98724210262299</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G85" t="n">
-        <v>1.94918918609619</v>
+        <v>1.94918894767761</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>1.97314846515656</v>
+        <v>1.97314858436584</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G88" t="n">
-        <v>1.89845085144043</v>
+        <v>1.89845097064972</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>1.87687909603119</v>
+        <v>1.87687861919403</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.5</v>
       </c>
       <c r="G91" t="n">
-        <v>1.79777705669403</v>
+        <v>1.79777681827545</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>1.74024832248688</v>
+        <v>1.74024796485901</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G93" t="n">
-        <v>1.68559563159943</v>
+        <v>1.68559575080872</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G94" t="n">
-        <v>1.681281208992</v>
+        <v>1.68128097057343</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G95" t="n">
-        <v>1.6122465133667</v>
+        <v>1.61224639415741</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62662875652313</v>
+        <v>1.62662851810455</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G97" t="n">
-        <v>1.63957262039185</v>
+        <v>1.63957273960114</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G100" t="n">
-        <v>1.63957262039185</v>
+        <v>1.63957273960114</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G101" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991017341614</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G102" t="n">
-        <v>1.78914749622345</v>
+        <v>1.78914761543274</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G103" t="n">
-        <v>1.86249709129333</v>
+        <v>1.86249697208405</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G105" t="n">
-        <v>1.86249709129333</v>
+        <v>1.86249697208405</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>1.81215906143188</v>
+        <v>1.81215929985046</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>1.82654142379761</v>
+        <v>1.82654130458832</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G109" t="n">
-        <v>1.79490065574646</v>
+        <v>1.79490077495575</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G110" t="n">
-        <v>1.83517074584961</v>
+        <v>1.8351708650589</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G111" t="n">
-        <v>1.83948564529419</v>
+        <v>1.8394855260849</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>1.80640649795532</v>
+        <v>1.80640614032745</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.5</v>
       </c>
       <c r="G114" t="n">
-        <v>1.79777705669403</v>
+        <v>1.79777681827545</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G115" t="n">
-        <v>1.73305714130402</v>
+        <v>1.73305702209473</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G117" t="n">
-        <v>1.73880982398987</v>
+        <v>1.73880994319916</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G118" t="n">
-        <v>1.63381958007812</v>
+        <v>1.6338198184967</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G119" t="n">
-        <v>1.68559563159943</v>
+        <v>1.68559575080872</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G120" t="n">
-        <v>1.75606858730316</v>
+        <v>1.75606846809387</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G121" t="n">
-        <v>1.75319218635559</v>
+        <v>1.7531920671463</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>1.81215906143188</v>
+        <v>1.81215929985046</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G124" t="n">
-        <v>1.6122465133667</v>
+        <v>1.61224639415741</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G125" t="n">
-        <v>1.48999774456024</v>
+        <v>1.48999750614166</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>1.46698606014252</v>
+        <v>1.46698594093323</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G129" t="n">
-        <v>1.47561538219452</v>
+        <v>1.47561550140381</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G130" t="n">
-        <v>1.49287402629852</v>
+        <v>1.49287390708923</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G131" t="n">
-        <v>1.49862706661224</v>
+        <v>1.49862694740295</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2</v>
       </c>
       <c r="G132" t="n">
-        <v>1.43822157382965</v>
+        <v>1.43822169303894</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G133" t="n">
-        <v>1.5086944103241</v>
+        <v>1.50869452953339</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G136" t="n">
-        <v>1.63238155841827</v>
+        <v>1.63238167762756</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G137" t="n">
-        <v>1.63381958007812</v>
+        <v>1.6338198184967</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G141" t="n">
-        <v>1.6122465133667</v>
+        <v>1.61224639415741</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.25</v>
       </c>
       <c r="G142" t="n">
-        <v>1.61799931526184</v>
+        <v>1.61799919605255</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.25</v>
       </c>
       <c r="G143" t="n">
-        <v>1.61799931526184</v>
+        <v>1.61799919605255</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.12599992752075</v>
       </c>
       <c r="G146" t="n">
-        <v>1.52882945537567</v>
+        <v>1.52882957458496</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G147" t="n">
-        <v>1.56766152381897</v>
+        <v>1.56766140460968</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39579391479492</v>
+        <v>1.39579403400421</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G152" t="n">
-        <v>1.3375461101532</v>
+        <v>1.33754622936249</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G153" t="n">
-        <v>1.3440181016922</v>
+        <v>1.34401786327362</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G154" t="n">
-        <v>1.42959213256836</v>
+        <v>1.42959237098694</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G155" t="n">
-        <v>1.43462586402893</v>
+        <v>1.43462610244751</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G156" t="n">
-        <v>1.44828915596008</v>
+        <v>1.44828903675079</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G157" t="n">
-        <v>1.48999774456024</v>
+        <v>1.48999750614166</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G158" t="n">
-        <v>1.48136830329895</v>
+        <v>1.48136806488037</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>1.56622326374054</v>
+        <v>1.56622314453125</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G160" t="n">
-        <v>1.53314411640167</v>
+        <v>1.53314423561096</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G161" t="n">
-        <v>1.5043797492981</v>
+        <v>1.50437986850739</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G162" t="n">
-        <v>1.5058182477951</v>
+        <v>1.50581800937653</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G163" t="n">
-        <v>1.4914356470108</v>
+        <v>1.49143576622009</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G165" t="n">
-        <v>1.53602051734924</v>
+        <v>1.53602063655853</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G166" t="n">
-        <v>1.5259530544281</v>
+        <v>1.52595293521881</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G167" t="n">
-        <v>1.54608821868896</v>
+        <v>1.54608845710754</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G168" t="n">
-        <v>1.52307665348053</v>
+        <v>1.52307653427124</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>1.51013267040253</v>
+        <v>1.51013255119324</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G170" t="n">
-        <v>1.51588559150696</v>
+        <v>1.51588571071625</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G171" t="n">
-        <v>1.5086944103241</v>
+        <v>1.50869452953339</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G176" t="n">
-        <v>1.55471754074097</v>
+        <v>1.55471765995026</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G180" t="n">
-        <v>1.49287402629852</v>
+        <v>1.49287390708923</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G181" t="n">
-        <v>1.49862706661224</v>
+        <v>1.49862694740295</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G182" t="n">
-        <v>1.46986246109009</v>
+        <v>1.4698623418808</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G187" t="n">
-        <v>1.48280644416809</v>
+        <v>1.48280668258667</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G188" t="n">
-        <v>1.48999774456024</v>
+        <v>1.48999750614166</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G190" t="n">
-        <v>1.46986246109009</v>
+        <v>1.4698623418808</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>1.46698606014252</v>
+        <v>1.46698594093323</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G193" t="n">
-        <v>1.46986246109009</v>
+        <v>1.4698623418808</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G194" t="n">
-        <v>1.46267139911652</v>
+        <v>1.46267116069794</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>1.46698606014252</v>
+        <v>1.46698594093323</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G198" t="n">
-        <v>1.60936987400055</v>
+        <v>1.60937011241913</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.25</v>
       </c>
       <c r="G199" t="n">
-        <v>1.61799931526184</v>
+        <v>1.61799919605255</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991017341614</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991017341614</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991017341614</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G205" t="n">
-        <v>1.70429253578186</v>
+        <v>1.70429241657257</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G207" t="n">
-        <v>1.7316187620163</v>
+        <v>1.73161864280701</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G208" t="n">
-        <v>1.73449504375458</v>
+        <v>1.73449528217316</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>1.74743902683258</v>
+        <v>1.74743890762329</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G210" t="n">
-        <v>1.77332723140717</v>
+        <v>1.77332735061646</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G211" t="n">
-        <v>1.75606858730316</v>
+        <v>1.75606846809387</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G212" t="n">
-        <v>1.71723663806915</v>
+        <v>1.71723675727844</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>1.74743902683258</v>
+        <v>1.74743890762329</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G214" t="n">
-        <v>1.718674659729</v>
+        <v>1.71867501735687</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G216" t="n">
-        <v>1.58348178863525</v>
+        <v>1.58348190784454</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G217" t="n">
-        <v>1.55327928066254</v>
+        <v>1.55327939987183</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>1.51013267040253</v>
+        <v>1.51013255119324</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>1.51013267040253</v>
+        <v>1.51013255119324</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>1.46698606014252</v>
+        <v>1.46698594093323</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G221" t="n">
-        <v>1.42743504047394</v>
+        <v>1.42743492126465</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G222" t="n">
-        <v>1.43246877193451</v>
+        <v>1.43246853351593</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G223" t="n">
-        <v>1.42383933067322</v>
+        <v>1.42383944988251</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>1.40586173534393</v>
+        <v>1.40586149692535</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G226" t="n">
-        <v>1.39004111289978</v>
+        <v>1.39004099369049</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G227" t="n">
-        <v>1.41664838790894</v>
+        <v>1.41664826869965</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G228" t="n">
-        <v>1.39579391479492</v>
+        <v>1.39579403400421</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G229" t="n">
-        <v>1.3375461101532</v>
+        <v>1.33754622936249</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G230" t="n">
-        <v>1.35840034484863</v>
+        <v>1.35840022563934</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G231" t="n">
-        <v>1.3375461101532</v>
+        <v>1.33754622936249</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G234" t="n">
-        <v>1.29799497127533</v>
+        <v>1.29799485206604</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G235" t="n">
-        <v>1.30806267261505</v>
+        <v>1.30806243419647</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G236" t="n">
-        <v>1.32316398620605</v>
+        <v>1.32316386699677</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.95299994945526</v>
       </c>
       <c r="G241" t="n">
-        <v>1.4044234752655</v>
+        <v>1.40442335605621</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G242" t="n">
-        <v>1.48712122440338</v>
+        <v>1.48712110519409</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>1.46698606014252</v>
+        <v>1.46698594093323</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G244" t="n">
-        <v>1.44828915596008</v>
+        <v>1.44828903675079</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G247" t="n">
-        <v>1.55327928066254</v>
+        <v>1.55327939987183</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G248" t="n">
-        <v>1.53602051734924</v>
+        <v>1.53602063655853</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G250" t="n">
-        <v>1.54464995861053</v>
+        <v>1.54465007781982</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G252" t="n">
-        <v>1.54608821868896</v>
+        <v>1.54608845710754</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G258" t="n">
-        <v>1.60649359226227</v>
+        <v>1.60649347305298</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G259" t="n">
-        <v>1.64388716220856</v>
+        <v>1.64388728141785</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>1.64676368236542</v>
+        <v>1.64676380157471</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G261" t="n">
-        <v>1.65826952457428</v>
+        <v>1.65826940536499</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>1.66114580631256</v>
+        <v>1.66114568710327</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G265" t="n">
-        <v>1.65683126449585</v>
+        <v>1.65683114528656</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>1.69710123538971</v>
+        <v>1.69710147380829</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G269" t="n">
-        <v>1.722989320755</v>
+        <v>1.72298943996429</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G271" t="n">
-        <v>1.77476561069489</v>
+        <v>1.77476537227631</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G272" t="n">
-        <v>1.78483331203461</v>
+        <v>1.78483307361603</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G273" t="n">
-        <v>1.74168622493744</v>
+        <v>1.74168646335602</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G275" t="n">
-        <v>1.75463020801544</v>
+        <v>1.75463044643402</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G276" t="n">
-        <v>1.70429253578186</v>
+        <v>1.70429241657257</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G277" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991017341614</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>1.66114580631256</v>
+        <v>1.66114568710327</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G280" t="n">
-        <v>1.71723663806915</v>
+        <v>1.71723675727844</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>1.70429253578186</v>
+        <v>1.70429241657257</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G282" t="n">
-        <v>1.71436035633087</v>
+        <v>1.71436023712158</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.63957262039185</v>
+        <v>1.63957273960114</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G286" t="n">
-        <v>1.70429253578186</v>
+        <v>1.70429241657257</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G287" t="n">
-        <v>1.66833710670471</v>
+        <v>1.66833686828613</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G289" t="n">
-        <v>1.65970778465271</v>
+        <v>1.65970754623413</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>1.63957262039185</v>
+        <v>1.63957273960114</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G292" t="n">
-        <v>1.62375223636627</v>
+        <v>1.62375211715698</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G293" t="n">
-        <v>1.5863584280014</v>
+        <v>1.58635854721069</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G295" t="n">
-        <v>1.48136830329895</v>
+        <v>1.48136806488037</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G296" t="n">
-        <v>1.4914356470108</v>
+        <v>1.49143576622009</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2</v>
       </c>
       <c r="G297" t="n">
-        <v>1.43822157382965</v>
+        <v>1.43822169303894</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G298" t="n">
-        <v>1.48280644416809</v>
+        <v>1.48280668258667</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>1.52451491355896</v>
+        <v>1.52451479434967</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>1.51013267040253</v>
+        <v>1.51013255119324</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G304" t="n">
-        <v>1.5015035867691</v>
+        <v>1.50150334835052</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G305" t="n">
-        <v>1.49718868732452</v>
+        <v>1.49718844890594</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G307" t="n">
-        <v>1.54464995861053</v>
+        <v>1.54465007781982</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G308" t="n">
-        <v>1.55903232097626</v>
+        <v>1.55903220176697</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>1.53889715671539</v>
+        <v>1.5388970375061</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G310" t="n">
-        <v>1.73305714130402</v>
+        <v>1.73305702209473</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>1.82654142379761</v>
+        <v>1.82654130458832</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G312" t="n">
-        <v>1.81503534317017</v>
+        <v>1.81503546237946</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>1.76901268959045</v>
+        <v>1.76901257038116</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G314" t="n">
-        <v>1.7575067281723</v>
+        <v>1.75750696659088</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G315" t="n">
-        <v>1.73305714130402</v>
+        <v>1.73305702209473</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>1.81215906143188</v>
+        <v>1.81215929985046</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>1.95166659355164</v>
+        <v>1.95166683197021</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G320" t="n">
-        <v>1.98043096065521</v>
+        <v>1.98043131828308</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G321" t="n">
-        <v>1.96604883670807</v>
+        <v>1.96604871749878</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G322" t="n">
-        <v>1.96317255496979</v>
+        <v>1.9631724357605</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G323" t="n">
-        <v>1.94303727149963</v>
+        <v>1.94303739070892</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G325" t="n">
-        <v>1.9588577747345</v>
+        <v>1.95885789394379</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G326" t="n">
-        <v>1.97036337852478</v>
+        <v>1.97036349773407</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G328" t="n">
-        <v>1.99625146389008</v>
+        <v>1.99625134468079</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>1.96317255496979</v>
+        <v>1.9631724357605</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>1.77620363235474</v>
+        <v>1.77620375156403</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G332" t="n">
-        <v>1.71004545688629</v>
+        <v>1.71004557609558</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G334" t="n">
-        <v>1.81359767913818</v>
+        <v>1.8135974407196</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G335" t="n">
-        <v>1.79058599472046</v>
+        <v>1.79058587551117</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G336" t="n">
-        <v>1.85386776924133</v>
+        <v>1.85386765003204</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G337" t="n">
-        <v>1.90851998329163</v>
+        <v>1.90852010250092</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.5</v>
       </c>
       <c r="G340" t="n">
-        <v>1.79777705669403</v>
+        <v>1.79777681827545</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G342" t="n">
-        <v>1.70136153697968</v>
+        <v>1.70136165618896</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G343" t="n">
-        <v>1.72954428195953</v>
+        <v>1.72954440116882</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G344" t="n">
-        <v>1.72361123561859</v>
+        <v>1.7236111164093</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G347" t="n">
-        <v>1.76514410972595</v>
+        <v>1.76514434814453</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G348" t="n">
-        <v>1.75179398059845</v>
+        <v>1.75179421901703</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G349" t="n">
-        <v>1.7147114276886</v>
+        <v>1.71471130847931</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G354" t="n">
-        <v>1.67169523239136</v>
+        <v>1.67169535160065</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G359" t="n">
-        <v>1.72064471244812</v>
+        <v>1.72064435482025</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G360" t="n">
-        <v>1.69394493103027</v>
+        <v>1.69394505023956</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G361" t="n">
-        <v>1.69246160984039</v>
+        <v>1.69246172904968</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G365" t="n">
-        <v>1.70284473896027</v>
+        <v>1.70284485816956</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G368" t="n">
-        <v>1.72212791442871</v>
+        <v>1.722128033638</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>1.72064471244812</v>
+        <v>1.72064435482025</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G370" t="n">
-        <v>1.70136153697968</v>
+        <v>1.70136165618896</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G371" t="n">
-        <v>1.70432841777802</v>
+        <v>1.70432806015015</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G374" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G375" t="n">
-        <v>1.74141108989716</v>
+        <v>1.74141097068787</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G376" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>1.72806119918823</v>
+        <v>1.72806131839752</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G379" t="n">
-        <v>1.67614507675171</v>
+        <v>1.67614531517029</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356192111969</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G381" t="n">
-        <v>1.71916115283966</v>
+        <v>1.71916139125824</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G383" t="n">
-        <v>1.72806119918823</v>
+        <v>1.72806131839752</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>1.75031077861786</v>
+        <v>1.75031089782715</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G385" t="n">
-        <v>1.75921058654785</v>
+        <v>1.75921070575714</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G386" t="n">
-        <v>1.75921058654785</v>
+        <v>1.75921070575714</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G388" t="n">
-        <v>1.71174478530884</v>
+        <v>1.71174466609955</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G389" t="n">
-        <v>1.70284473896027</v>
+        <v>1.70284485816956</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G390" t="n">
-        <v>1.69394493103027</v>
+        <v>1.69394505023956</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G391" t="n">
-        <v>1.69394493103027</v>
+        <v>1.69394505023956</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G393" t="n">
-        <v>1.7147114276886</v>
+        <v>1.71471130847931</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G394" t="n">
-        <v>1.70877802371979</v>
+        <v>1.70877778530121</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G396" t="n">
-        <v>1.72212791442871</v>
+        <v>1.722128033638</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G397" t="n">
-        <v>1.70136153697968</v>
+        <v>1.70136165618896</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G399" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G400" t="n">
-        <v>1.68949508666992</v>
+        <v>1.6894953250885</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G401" t="n">
-        <v>1.68504500389099</v>
+        <v>1.68504524230957</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>1.67614507675171</v>
+        <v>1.67614531517029</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356192111969</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G405" t="n">
-        <v>1.64351224899292</v>
+        <v>1.64351236820221</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G406" t="n">
-        <v>1.63312888145447</v>
+        <v>1.63312911987305</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>1.59456288814545</v>
+        <v>1.59456300735474</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G408" t="n">
-        <v>1.61384618282318</v>
+        <v>1.61384606361389</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G409" t="n">
-        <v>1.59159624576569</v>
+        <v>1.5915961265564</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G410" t="n">
-        <v>1.61087942123413</v>
+        <v>1.61087918281555</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356192111969</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G414" t="n">
-        <v>1.65686213970184</v>
+        <v>1.65686202049255</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G415" t="n">
-        <v>1.67466187477112</v>
+        <v>1.67466175556183</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G416" t="n">
-        <v>1.66576182842255</v>
+        <v>1.66576206684113</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G417" t="n">
-        <v>1.63312888145447</v>
+        <v>1.63312911987305</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G418" t="n">
-        <v>1.60346269607544</v>
+        <v>1.60346281528473</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G419" t="n">
-        <v>1.60494601726532</v>
+        <v>1.60494613647461</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G421" t="n">
-        <v>1.60791277885437</v>
+        <v>1.60791265964508</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G422" t="n">
-        <v>1.60197937488556</v>
+        <v>1.60197949409485</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G423" t="n">
-        <v>1.58417963981628</v>
+        <v>1.58417952060699</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>1.59456288814545</v>
+        <v>1.59456300735474</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G428" t="n">
-        <v>1.60049617290497</v>
+        <v>1.60049605369568</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G429" t="n">
-        <v>1.59159624576569</v>
+        <v>1.5915961265564</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>1.59456288814545</v>
+        <v>1.59456300735474</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G435" t="n">
-        <v>1.5990127325058</v>
+        <v>1.59901285171509</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>1.57231318950653</v>
+        <v>1.57231307029724</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G438" t="n">
-        <v>1.56192994117737</v>
+        <v>1.56192982196808</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>1.57231318950653</v>
+        <v>1.57231307029724</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G440" t="n">
-        <v>1.57231318950653</v>
+        <v>1.57231307029724</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G443" t="n">
-        <v>1.57379651069641</v>
+        <v>1.57379627227783</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G444" t="n">
-        <v>1.58566308021545</v>
+        <v>1.58566296100616</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G447" t="n">
-        <v>1.66576182842255</v>
+        <v>1.66576206684113</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G448" t="n">
-        <v>1.76217722892761</v>
+        <v>1.7621773481369</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G449" t="n">
-        <v>1.76217722892761</v>
+        <v>1.7621773481369</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G450" t="n">
-        <v>1.74882757663727</v>
+        <v>1.74882769584656</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>1.72806119918823</v>
+        <v>1.72806131839752</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G452" t="n">
-        <v>1.70136153697968</v>
+        <v>1.70136165618896</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G454" t="n">
-        <v>1.70432841777802</v>
+        <v>1.70432806015015</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G455" t="n">
-        <v>1.74437773227692</v>
+        <v>1.74437761306763</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G456" t="n">
-        <v>1.7933269739151</v>
+        <v>1.79332709312439</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G457" t="n">
-        <v>1.79629349708557</v>
+        <v>1.79629361629486</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G458" t="n">
-        <v>1.83189308643341</v>
+        <v>1.83189344406128</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>1.83930969238281</v>
+        <v>1.83930993080139</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G460" t="n">
-        <v>1.93720841407776</v>
+        <v>1.93720829486847</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G461" t="n">
-        <v>1.92089211940765</v>
+        <v>1.92089200019836</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.5</v>
       </c>
       <c r="G462" t="n">
-        <v>1.85414290428162</v>
+        <v>1.85414278507233</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G463" t="n">
-        <v>1.90605854988098</v>
+        <v>1.90605878829956</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G466" t="n">
-        <v>1.91199219226837</v>
+        <v>1.91199243068695</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G467" t="n">
-        <v>1.93572509288788</v>
+        <v>1.9357248544693</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G468" t="n">
-        <v>1.92089211940765</v>
+        <v>1.92089200019836</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G469" t="n">
-        <v>1.78887689113617</v>
+        <v>1.78887701034546</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G470" t="n">
-        <v>1.7933269739151</v>
+        <v>1.79332709312439</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G471" t="n">
-        <v>1.82892656326294</v>
+        <v>1.82892668247223</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G472" t="n">
-        <v>1.78887689113617</v>
+        <v>1.78887701034546</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G473" t="n">
-        <v>1.76514410972595</v>
+        <v>1.76514434814453</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G475" t="n">
-        <v>1.70729470252991</v>
+        <v>1.70729458332062</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G478" t="n">
-        <v>1.64054572582245</v>
+        <v>1.64054560661316</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G479" t="n">
-        <v>1.61977910995483</v>
+        <v>1.61977922916412</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G480" t="n">
-        <v>1.61829602718353</v>
+        <v>1.61829566955566</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G481" t="n">
-        <v>1.60049617290497</v>
+        <v>1.60049605369568</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G483" t="n">
-        <v>1.63164556026459</v>
+        <v>1.63164579868317</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G486" t="n">
-        <v>1.67021203041077</v>
+        <v>1.67021191120148</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G487" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G492" t="n">
-        <v>1.67614507675171</v>
+        <v>1.67614531517029</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G493" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131198406219</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G495" t="n">
-        <v>1.68949508666992</v>
+        <v>1.6894953250885</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G496" t="n">
-        <v>1.68949508666992</v>
+        <v>1.6894953250885</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G498" t="n">
-        <v>1.68949508666992</v>
+        <v>1.6894953250885</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G499" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356192111969</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G502" t="n">
-        <v>1.67466187477112</v>
+        <v>1.67466175556183</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G503" t="n">
-        <v>1.62867915630341</v>
+        <v>1.6286792755127</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G505" t="n">
-        <v>1.65834534168243</v>
+        <v>1.65834546089172</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G506" t="n">
-        <v>1.67169523239136</v>
+        <v>1.67169535160065</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G509" t="n">
-        <v>1.68504500389099</v>
+        <v>1.68504524230957</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G510" t="n">
-        <v>1.69542801380157</v>
+        <v>1.69542837142944</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G512" t="n">
-        <v>1.67466187477112</v>
+        <v>1.67466175556183</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G513" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G517" t="n">
-        <v>1.77256059646606</v>
+        <v>1.77256071567535</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G518" t="n">
-        <v>1.75031077861786</v>
+        <v>1.75031089782715</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G519" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.375</v>
       </c>
       <c r="G520" t="n">
-        <v>1.76143598556519</v>
+        <v>1.76143574714661</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76514410972595</v>
+        <v>1.76514434814453</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.7466025352478</v>
+        <v>1.74660265445709</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G525" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G527" t="n">
-        <v>1.78739392757416</v>
+        <v>1.78739368915558</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G528" t="n">
-        <v>1.77256059646606</v>
+        <v>1.77256071567535</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>1.79481053352356</v>
+        <v>1.79481029510498</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G531" t="n">
-        <v>1.82818508148193</v>
+        <v>1.82818472385406</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G532" t="n">
-        <v>1.77256059646606</v>
+        <v>1.77256071567535</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>1.74289429187775</v>
+        <v>1.74289405345917</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.67614507675171</v>
+        <v>1.67614531517029</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G536" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G537" t="n">
-        <v>1.66502034664154</v>
+        <v>1.66502010822296</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G538" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G540" t="n">
-        <v>1.67614507675171</v>
+        <v>1.67614531517029</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G541" t="n">
-        <v>1.67614507675171</v>
+        <v>1.67614531517029</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>1.63906216621399</v>
+        <v>1.63906240463257</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G544" t="n">
-        <v>1.67614507675171</v>
+        <v>1.67614531517029</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G545" t="n">
-        <v>1.69468677043915</v>
+        <v>1.69468665122986</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G546" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356192111969</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G547" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243707180023</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G549" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356192111969</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>1.66502034664154</v>
+        <v>1.66502010822296</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131198406219</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G554" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356192111969</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G556" t="n">
-        <v>1.63535392284393</v>
+        <v>1.63535404205322</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>1.63535392284393</v>
+        <v>1.63535404205322</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G558" t="n">
-        <v>1.63164556026459</v>
+        <v>1.63164579868317</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G561" t="n">
-        <v>1.69468677043915</v>
+        <v>1.69468665122986</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>1.67614507675171</v>
+        <v>1.67614531517029</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G563" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131198406219</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G564" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243707180023</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G568" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243707180023</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>1.63906216621399</v>
+        <v>1.63906240463257</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G574" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131198406219</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G575" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243707180023</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>1.70210301876068</v>
+        <v>1.70210325717926</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G581" t="n">
-        <v>1.67614507675171</v>
+        <v>1.67614531517029</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356192111969</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G584" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243707180023</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356192111969</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G588" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131198406219</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131198406219</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G591" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131198406219</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G594" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097828865051</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G596" t="n">
-        <v>1.69468677043915</v>
+        <v>1.69468665122986</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>1.70210301876068</v>
+        <v>1.70210325717926</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G601" t="n">
-        <v>1.72598969936371</v>
+        <v>1.725989818573</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>1.70287358760834</v>
+        <v>1.70287370681763</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G606" t="n">
-        <v>1.64893662929535</v>
+        <v>1.64893674850464</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G607" t="n">
-        <v>1.5526202917099</v>
+        <v>1.55262017250061</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G608" t="n">
-        <v>1.5526202917099</v>
+        <v>1.55262017250061</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G609" t="n">
-        <v>1.49791240692139</v>
+        <v>1.49791252613068</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G610" t="n">
-        <v>1.48096084594727</v>
+        <v>1.48096072673798</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G613" t="n">
-        <v>1.46400904655457</v>
+        <v>1.46400916576385</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G618" t="n">
-        <v>1.49791240692139</v>
+        <v>1.49791252613068</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G619" t="n">
-        <v>1.49174809455872</v>
+        <v>1.49174821376801</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G627" t="n">
-        <v>1.59499931335449</v>
+        <v>1.59499943256378</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.65664184093475</v>
+        <v>1.65664196014404</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G632" t="n">
-        <v>1.61040997505188</v>
+        <v>1.61040985584259</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>1.59499931335449</v>
+        <v>1.59499943256378</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G642" t="n">
-        <v>1.59499931335449</v>
+        <v>1.59499943256378</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G643" t="n">
-        <v>1.61811530590057</v>
+        <v>1.61811542510986</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G645" t="n">
-        <v>1.59885215759277</v>
+        <v>1.59885203838348</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>1.59499931335449</v>
+        <v>1.59499943256378</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G649" t="n">
-        <v>1.59499931335449</v>
+        <v>1.59499943256378</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G656" t="n">
-        <v>1.62582063674927</v>
+        <v>1.62582051753998</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G659" t="n">
-        <v>1.61426281929016</v>
+        <v>1.61426258087158</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G671" t="n">
-        <v>1.53643906116486</v>
+        <v>1.53643894195557</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G674" t="n">
-        <v>1.5526202917099</v>
+        <v>1.55262017250061</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2</v>
       </c>
       <c r="G681" t="n">
-        <v>1.54106223583221</v>
+        <v>1.54106211662292</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G698" t="n">
-        <v>1.61040997505188</v>
+        <v>1.61040985584259</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G699" t="n">
-        <v>1.61811530590057</v>
+        <v>1.61811542510986</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>1.65664184093475</v>
+        <v>1.65664196014404</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G701" t="n">
-        <v>1.61040997505188</v>
+        <v>1.61040985584259</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G704" t="n">
-        <v>1.5526202917099</v>
+        <v>1.55262017250061</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2</v>
       </c>
       <c r="G706" t="n">
-        <v>1.54106223583221</v>
+        <v>1.54106211662292</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G709" t="n">
-        <v>1.48096084594727</v>
+        <v>1.48096072673798</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G710" t="n">
-        <v>1.42548263072968</v>
+        <v>1.42548251152039</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G711" t="n">
-        <v>1.43472874164581</v>
+        <v>1.4347288608551</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G712" t="n">
-        <v>1.41777718067169</v>
+        <v>1.41777729988098</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G713" t="n">
-        <v>1.419318318367</v>
+        <v>1.41931819915771</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G715" t="n">
-        <v>1.44089305400848</v>
+        <v>1.44089329242706</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G716" t="n">
-        <v>1.39157927036285</v>
+        <v>1.39157915115356</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G721" t="n">
-        <v>1.24209606647491</v>
+        <v>1.2420961856842</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G725" t="n">
-        <v>1.30990278720856</v>
+        <v>1.30990290641785</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G730" t="n">
-        <v>1.30682075023651</v>
+        <v>1.30682063102722</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G731" t="n">
-        <v>1.29757440090179</v>
+        <v>1.29757452011108</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G733" t="n">
-        <v>1.2806224822998</v>
+        <v>1.28062260150909</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G734" t="n">
-        <v>1.23747289180756</v>
+        <v>1.23747277259827</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G735" t="n">
-        <v>1.18353569507599</v>
+        <v>1.18353581428528</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G736" t="n">
-        <v>1.19278204441071</v>
+        <v>1.19278216362</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G737" t="n">
-        <v>1.19894635677338</v>
+        <v>1.19894647598267</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G741" t="n">
-        <v>1.13113975524902</v>
+        <v>1.13113963603973</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G742" t="n">
-        <v>1.17274832725525</v>
+        <v>1.17274844646454</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G743" t="n">
-        <v>1.22976744174957</v>
+        <v>1.22976768016815</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G745" t="n">
-        <v>1.27137625217438</v>
+        <v>1.27137637138367</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G746" t="n">
-        <v>1.23747289180756</v>
+        <v>1.23747277259827</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G750" t="n">
-        <v>1.24363720417023</v>
+        <v>1.24363732337952</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G751" t="n">
-        <v>1.26213002204895</v>
+        <v>1.26212990283966</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G752" t="n">
-        <v>1.22668564319611</v>
+        <v>1.22668552398682</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G753" t="n">
-        <v>1.20665156841278</v>
+        <v>1.20665168762207</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G754" t="n">
-        <v>1.18045365810394</v>
+        <v>1.18045353889465</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G755" t="n">
-        <v>1.17274832725525</v>
+        <v>1.17274844646454</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G758" t="n">
-        <v>1.09569525718689</v>
+        <v>1.0956951379776</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G759" t="n">
-        <v>1.10185956954956</v>
+        <v>1.10185945034027</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G763" t="n">
-        <v>1.10802364349365</v>
+        <v>1.10802376270294</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G764" t="n">
-        <v>1.11264681816101</v>
+        <v>1.1126469373703</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G769" t="n">
-        <v>1.16350185871124</v>
+        <v>1.16350197792053</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G774" t="n">
-        <v>1.14346814155579</v>
+        <v>1.14346826076508</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>1.12497544288635</v>
+        <v>1.12497532367706</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G782" t="n">
-        <v>1.12651634216309</v>
+        <v>1.12651646137238</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G783" t="n">
-        <v>1.10956478118896</v>
+        <v>1.10956490039825</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G784" t="n">
-        <v>1.10802364349365</v>
+        <v>1.10802376270294</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G785" t="n">
-        <v>1.10340058803558</v>
+        <v>1.10340046882629</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G786" t="n">
-        <v>1.07412052154541</v>
+        <v>1.07412040233612</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G787" t="n">
-        <v>1.06641495227814</v>
+        <v>1.06641507148743</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G788" t="n">
-        <v>1.06641495227814</v>
+        <v>1.06641507148743</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G789" t="n">
-        <v>1.13884484767914</v>
+        <v>1.13884508609772</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G790" t="n">
-        <v>1.14038610458374</v>
+        <v>1.14038598537445</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G791" t="n">
-        <v>1.14038610458374</v>
+        <v>1.14038598537445</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G793" t="n">
-        <v>1.17428958415985</v>
+        <v>1.17428946495056</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G794" t="n">
-        <v>1.18507695198059</v>
+        <v>1.1850768327713</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G796" t="n">
-        <v>1.22668564319611</v>
+        <v>1.22668552398682</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G799" t="n">
-        <v>1.24363720417023</v>
+        <v>1.24363732337952</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G800" t="n">
-        <v>1.24363720417023</v>
+        <v>1.24363732337952</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G802" t="n">
-        <v>1.23439085483551</v>
+        <v>1.23439073562622</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G803" t="n">
-        <v>1.23439085483551</v>
+        <v>1.23439073562622</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G804" t="n">
-        <v>1.24209606647491</v>
+        <v>1.2420961856842</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G811" t="n">
-        <v>1.21589815616608</v>
+        <v>1.21589803695679</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G812" t="n">
-        <v>1.18199467658997</v>
+        <v>1.18199455738068</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G816" t="n">
-        <v>1.16658401489258</v>
+        <v>1.16658413410187</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G817" t="n">
-        <v>1.16658401489258</v>
+        <v>1.16658413410187</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G832" t="n">
-        <v>1.16041994094849</v>
+        <v>1.1604198217392</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G833" t="n">
-        <v>1.1619610786438</v>
+        <v>1.16196095943451</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G834" t="n">
-        <v>1.19586420059204</v>
+        <v>1.19586431980133</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G835" t="n">
-        <v>1.26367092132568</v>
+        <v>1.26367104053497</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G842" t="n">
-        <v>1.26367092132568</v>
+        <v>1.26367104053497</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G843" t="n">
-        <v>1.27137625217438</v>
+        <v>1.27137637138367</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G844" t="n">
-        <v>1.2806224822998</v>
+        <v>1.28062260150909</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G845" t="n">
-        <v>1.28832805156708</v>
+        <v>1.28832793235779</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G846" t="n">
-        <v>1.29141008853912</v>
+        <v>1.29140996932983</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G848" t="n">
-        <v>1.33944809436798</v>
+        <v>1.33944821357727</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G850" t="n">
-        <v>1.26629877090454</v>
+        <v>1.26629865169525</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G851" t="n">
-        <v>1.24029004573822</v>
+        <v>1.24028992652893</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G853" t="n">
-        <v>1.22240889072418</v>
+        <v>1.22240900993347</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G856" t="n">
-        <v>1.11512303352356</v>
+        <v>1.11512315273285</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G857" t="n">
-        <v>1.12162530422211</v>
+        <v>1.12162518501282</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G861" t="n">
-        <v>1.0858633518219</v>
+        <v>1.08586323261261</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G862" t="n">
-        <v>1.06473124027252</v>
+        <v>1.06473112106323</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G869" t="n">
-        <v>1.01271367073059</v>
+        <v>1.01271390914917</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G870" t="n">
-        <v>1.03222036361694</v>
+        <v>1.03222024440765</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G872" t="n">
-        <v>0.976951956748962</v>
+        <v>0.976951837539673</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G873" t="n">
-        <v>0.967198669910431</v>
+        <v>0.967198610305786</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G874" t="n">
-        <v>0.972075223922729</v>
+        <v>0.972075283527374</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G875" t="n">
-        <v>0.95581978559494</v>
+        <v>0.955819845199585</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>0.910304605960846</v>
+        <v>0.910304665565491</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G879" t="n">
-        <v>0.92818546295166</v>
+        <v>0.92818558216095</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G880" t="n">
-        <v>0.924934446811676</v>
+        <v>0.924934506416321</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G882" t="n">
-        <v>0.950943112373352</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G885" t="n">
-        <v>0.933062136173248</v>
+        <v>0.933062195777893</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G886" t="n">
-        <v>0.95581978559494</v>
+        <v>0.955819845199585</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G887" t="n">
-        <v>0.965572953224182</v>
+        <v>0.965573012828827</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G888" t="n">
-        <v>0.965572953224182</v>
+        <v>0.965573012828827</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G889" t="n">
-        <v>0.98345410823822</v>
+        <v>0.983454048633575</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G890" t="n">
-        <v>0.976951956748962</v>
+        <v>0.976951837539673</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>1.03222036361694</v>
+        <v>1.03222024440765</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G894" t="n">
-        <v>1.04034793376923</v>
+        <v>1.04034805297852</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G896" t="n">
-        <v>1.03059494495392</v>
+        <v>1.03059482574463</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G898" t="n">
-        <v>1.01271367073059</v>
+        <v>1.01271390914917</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G899" t="n">
-        <v>0.976951956748962</v>
+        <v>0.976951837539673</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G901" t="n">
-        <v>0.981828272342682</v>
+        <v>0.981828391551971</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G902" t="n">
-        <v>1.01271367073059</v>
+        <v>1.01271390914917</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G904" t="n">
-        <v>0.98345410823822</v>
+        <v>0.983454048633575</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G907" t="n">
-        <v>1.03222036361694</v>
+        <v>1.03222024440765</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G908" t="n">
-        <v>1.02246713638306</v>
+        <v>1.02246701717377</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>0.950943112373352</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G921" t="n">
-        <v>0.920057773590088</v>
+        <v>0.920057713985443</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G922" t="n">
-        <v>0.92818546295166</v>
+        <v>0.92818558216095</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G923" t="n">
-        <v>0.954194307327271</v>
+        <v>0.954194366931915</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G925" t="n">
-        <v>0.967198669910431</v>
+        <v>0.967198610305786</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G926" t="n">
-        <v>0.981828272342682</v>
+        <v>0.981828391551971</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G927" t="n">
-        <v>0.978577435016632</v>
+        <v>0.978577315807343</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>0.975326478481293</v>
+        <v>0.975326359272003</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G929" t="n">
-        <v>0.973700702190399</v>
+        <v>0.973700761795044</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G930" t="n">
-        <v>0.972075223922729</v>
+        <v>0.972075283527374</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G931" t="n">
-        <v>0.98507958650589</v>
+        <v>0.985079526901245</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G933" t="n">
-        <v>0.965572953224182</v>
+        <v>0.965573012828827</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G934" t="n">
-        <v>0.950943112373352</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.04034793376923</v>
+        <v>1.04034805297852</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G938" t="n">
-        <v>1.09236550331116</v>
+        <v>1.09236538410187</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G945" t="n">
-        <v>1.21753239631653</v>
+        <v>1.21753227710724</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G949" t="n">
-        <v>1.15738713741302</v>
+        <v>1.15738725662231</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G950" t="n">
-        <v>1.14600837230682</v>
+        <v>1.14600849151611</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G951" t="n">
-        <v>1.14600837230682</v>
+        <v>1.14600849151611</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G953" t="n">
-        <v>1.14600837230682</v>
+        <v>1.14600849151611</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G956" t="n">
-        <v>1.09561669826508</v>
+        <v>1.09561657905579</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G960" t="n">
-        <v>1.11674869060516</v>
+        <v>1.11674857139587</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G964" t="n">
-        <v>1.16226375102997</v>
+        <v>1.16226398944855</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G972" t="n">
-        <v>1.1671404838562</v>
+        <v>1.16714036464691</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G974" t="n">
-        <v>1.2728009223938</v>
+        <v>1.27280080318451</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G975" t="n">
-        <v>1.25491988658905</v>
+        <v>1.25492000579834</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G984" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G985" t="n">
-        <v>1.34920132160187</v>
+        <v>1.34920144081116</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G986" t="n">
-        <v>1.36870801448822</v>
+        <v>1.36870789527893</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G989" t="n">
-        <v>1.50362813472748</v>
+        <v>1.50362801551819</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G991" t="n">
-        <v>1.51988351345062</v>
+        <v>1.51988363265991</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G996" t="n">
-        <v>1.50037705898285</v>
+        <v>1.50037693977356</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G997" t="n">
-        <v>1.50200271606445</v>
+        <v>1.50200259685516</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.4711172580719</v>
+        <v>1.47111713886261</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.48412144184113</v>
+        <v>1.48412156105042</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.51500678062439</v>
+        <v>1.51500689983368</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.50850462913513</v>
+        <v>1.50850450992584</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.54101550579071</v>
+        <v>1.541015625</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.55889666080475</v>
+        <v>1.55889654159546</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.58490526676178</v>
+        <v>1.58490538597107</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.54426670074463</v>
+        <v>1.54426658153534</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.55889666080475</v>
+        <v>1.55889654159546</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.51988351345062</v>
+        <v>1.51988363265991</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.50200271606445</v>
+        <v>1.50200259685516</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.45161056518555</v>
+        <v>1.45161068439484</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.48737275600433</v>
+        <v>1.48737263679504</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.48737275600433</v>
+        <v>1.48737263679504</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.45323622226715</v>
+        <v>1.45323610305786</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.37358450889587</v>
+        <v>1.37358462810516</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.48737275600433</v>
+        <v>1.48737263679504</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.49550032615662</v>
+        <v>1.49550044536591</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.50362813472748</v>
+        <v>1.50362801551819</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.64179933071136</v>
+        <v>1.64179921150208</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.7393319606781</v>
+        <v>1.73933207988739</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.51988351345062</v>
+        <v>1.51988363265991</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.34920132160187</v>
+        <v>1.34920144081116</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.18177044391632</v>
+        <v>1.18177032470703</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.978577435016632</v>
+        <v>0.978577315807343</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.97044974565506</v>
+        <v>0.970449805259705</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.897300243377686</v>
+        <v>0.897300183773041</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.902176797389984</v>
+        <v>0.902176856994629</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.820899665355682</v>
+        <v>0.820899605751038</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.88592141866684</v>
+        <v>0.885921478271484</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.950943112373352</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.942815482616425</v>
+        <v>0.942815363407135</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.879419207572937</v>
+        <v>0.879419147968292</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.98345410823822</v>
+        <v>0.983454048633575</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.965572953224182</v>
+        <v>0.965573012828827</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.01921594142914</v>
+        <v>1.01921606063843</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.978577435016632</v>
+        <v>0.978577315807343</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.996458292007446</v>
+        <v>0.996458351612091</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.996458292007446</v>
+        <v>0.996458351612091</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.978577435016632</v>
+        <v>0.978577315807343</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.02246713638306</v>
+        <v>1.02246701717377</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.04522466659546</v>
+        <v>1.04522478580475</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.05497789382935</v>
+        <v>1.05497801303864</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.03872263431549</v>
+        <v>1.03872239589691</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.03059494495392</v>
+        <v>1.03059482574463</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.04034793376923</v>
+        <v>1.04034805297852</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.01271367073059</v>
+        <v>1.01271390914917</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.97044974565506</v>
+        <v>0.970449805259705</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.959070801734924</v>
+        <v>0.959070920944214</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.97044974565506</v>
+        <v>0.970449805259705</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.975326478481293</v>
+        <v>0.975326359272003</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.999709606170654</v>
+        <v>0.99970954656601</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.03222036361694</v>
+        <v>1.03222024440765</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.0858633518219</v>
+        <v>1.08586323261261</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.11512303352356</v>
+        <v>1.11512315273285</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.13950622081757</v>
+        <v>1.13950610160828</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.29068183898926</v>
+        <v>1.29068195819855</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.19965124130249</v>
+        <v>1.19965136051178</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.10374426841736</v>
+        <v>1.10374438762665</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.11187195777893</v>
+        <v>1.11187207698822</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.09886753559113</v>
+        <v>1.09886765480042</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.09724199771881</v>
+        <v>1.0972421169281</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.09886753559113</v>
+        <v>1.09886765480042</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.04522466659546</v>
+        <v>1.04522478580475</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.09561669826508</v>
+        <v>1.09561657905579</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.2597963809967</v>
+        <v>1.25979650020599</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.3410736322403</v>
+        <v>1.34107375144958</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.45161056518555</v>
+        <v>1.45161068439484</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.42722749710083</v>
+        <v>1.42722761631012</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.4142233133316</v>
+        <v>1.41422319412231</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.37358450889587</v>
+        <v>1.37358462810516</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.40609550476074</v>
+        <v>1.40609538555145</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.4142233133316</v>
+        <v>1.41422319412231</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.44185745716095</v>
+        <v>1.44185757637024</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.54264104366302</v>
+        <v>1.54264116287231</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.52476024627686</v>
+        <v>1.52476012706757</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.48412144184113</v>
+        <v>1.48412156105042</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.48412144184113</v>
+        <v>1.48412156105042</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.48899817466736</v>
+        <v>1.48899829387665</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1185" t="n">
-        <v>1.4711172580719</v>
+        <v>1.47111713886261</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.45323622226715</v>
+        <v>1.45323610305786</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.43698084354401</v>
+        <v>1.43698072433472</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.33294582366943</v>
+        <v>1.33294594287872</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.31994163990021</v>
+        <v>1.31994152069092</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.34432482719421</v>
+        <v>1.3443249464035</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.37033343315125</v>
+        <v>1.37033355236053</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.35895478725433</v>
+        <v>1.35895466804504</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.35407817363739</v>
+        <v>1.3540780544281</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.33944809436798</v>
+        <v>1.33944821357727</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.29718410968781</v>
+        <v>1.29718399047852</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.1330041885376</v>
+        <v>1.13300406932831</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.22891116142273</v>
+        <v>1.22891104221344</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.24191558361053</v>
+        <v>1.24191546440125</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.25491988658905</v>
+        <v>1.25492000579834</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G1235" t="n">
-        <v>1.31181395053864</v>
+        <v>1.31181383132935</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.31994163990021</v>
+        <v>1.31994152069092</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.75</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.42235088348389</v>
+        <v>1.4223507642746</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>1.75</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.42235088348389</v>
+        <v>1.4223507642746</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.38983988761902</v>
+        <v>1.38984000682831</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.34432482719421</v>
+        <v>1.3443249464035</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.33294582366943</v>
+        <v>1.33294594287872</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1260" t="n">
-        <v>1.35407817363739</v>
+        <v>1.3540780544281</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.34920132160187</v>
+        <v>1.34920144081116</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.32969498634338</v>
+        <v>1.32969486713409</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.33944809436798</v>
+        <v>1.33944821357727</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.36870801448822</v>
+        <v>1.36870789527893</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.35407817363739</v>
+        <v>1.3540780544281</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.38983988761902</v>
+        <v>1.38984000682831</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.39471650123596</v>
+        <v>1.39471662044525</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.42072522640228</v>
+        <v>1.42072534561157</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.75</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.42235088348389</v>
+        <v>1.4223507642746</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.38983988761902</v>
+        <v>1.38984000682831</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.39471650123596</v>
+        <v>1.39471662044525</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.41097211837769</v>
+        <v>1.4109719991684</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.37033343315125</v>
+        <v>1.37033355236053</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.34920132160187</v>
+        <v>1.34920144081116</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.35407817363739</v>
+        <v>1.3540780544281</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.33457136154175</v>
+        <v>1.33457148075104</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.4711172580719</v>
+        <v>1.47111713886261</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.48899817466736</v>
+        <v>1.48899829387665</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.54264104366302</v>
+        <v>1.54264116287231</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.54751789569855</v>
+        <v>1.54751777648926</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.54751789569855</v>
+        <v>1.54751777648926</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.57352638244629</v>
+        <v>1.57352650165558</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.55564558506012</v>
+        <v>1.55564546585083</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.50200271606445</v>
+        <v>1.50200259685516</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.49550032615662</v>
+        <v>1.49550044536591</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.61253952980042</v>
+        <v>1.61253941059113</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.60441184043884</v>
+        <v>1.60441172122955</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.59303307533264</v>
+        <v>1.59303295612335</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.64992713928223</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.71088480949402</v>
+        <v>1.71088492870331</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.63773536682129</v>
+        <v>1.63773548603058</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.58490526676178</v>
+        <v>1.58490538597107</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.58490526676178</v>
+        <v>1.58490538597107</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.60441184043884</v>
+        <v>1.60441172122955</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.65805470943451</v>
+        <v>1.65805459022522</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.64179933071136</v>
+        <v>1.64179921150208</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.64179933071136</v>
+        <v>1.64179921150208</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.64179933071136</v>
+        <v>1.64179921150208</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.64992713928223</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.67837405204773</v>
+        <v>1.67837417125702</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.67837405204773</v>
+        <v>1.67837417125702</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.64992713928223</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.64992713928223</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.64992713928223</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.64992713928223</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.75152361392975</v>
+        <v>1.75152349472046</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.75152361392975</v>
+        <v>1.75152349472046</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.7393319606781</v>
+        <v>1.73933207988739</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.71088480949402</v>
+        <v>1.71088492870331</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.73526811599731</v>
+        <v>1.73526799678802</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.68650186061859</v>
+        <v>1.6865017414093</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.70275712013245</v>
+        <v>1.70275723934174</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.65805470943451</v>
+        <v>1.65805459022522</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.63773536682129</v>
+        <v>1.63773548603058</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.64992713928223</v>
+        <v>1.64992702007294</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.64586317539215</v>
+        <v>1.64586329460144</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.64586317539215</v>
+        <v>1.64586329460144</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1409" t="n">
-        <v>1.58490526676178</v>
+        <v>1.58490538597107</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.73526811599731</v>
+        <v>1.73526799678802</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.7393319606781</v>
+        <v>1.73933207988739</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.73120427131653</v>
+        <v>1.73120439052582</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.73120427131653</v>
+        <v>1.73120439052582</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.73526811599731</v>
+        <v>1.73526799678802</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.75152361392975</v>
+        <v>1.75152349472046</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.75152361392975</v>
+        <v>1.75152349472046</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.75965106487274</v>
+        <v>1.75965118408203</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.74339580535889</v>
+        <v>1.7433956861496</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.80841755867004</v>
+        <v>1.80841743946075</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.83686459064484</v>
+        <v>1.83686447143555</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.83686459064484</v>
+        <v>1.83686447143555</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.8775030374527</v>
+        <v>1.87750315666199</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.91407799720764</v>
+        <v>1.91407787799835</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.91814160346985</v>
+        <v>1.91814184188843</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.88563096523285</v>
+        <v>1.88563072681427</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.91407799720764</v>
+        <v>1.91407787799835</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.84499228000641</v>
+        <v>1.84499216079712</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>2.25</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.82873690128326</v>
+        <v>1.82873678207397</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>2.25</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.82873690128326</v>
+        <v>1.82873678207397</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.85718405246735</v>
+        <v>1.85718417167664</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.85718405246735</v>
+        <v>1.85718417167664</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>2.25</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.82873690128326</v>
+        <v>1.82873678207397</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.83686459064484</v>
+        <v>1.83686447143555</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>2.25</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.82873690128326</v>
+        <v>1.82873678207397</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.85718405246735</v>
+        <v>1.85718417167664</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1462" t="n">
-        <v>1.84499228000641</v>
+        <v>1.84499216079712</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.84905636310577</v>
+        <v>1.84905624389648</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.85718405246735</v>
+        <v>1.85718417167664</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.84905636310577</v>
+        <v>1.84905624389648</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.88563096523285</v>
+        <v>1.88563072681427</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.84905636310577</v>
+        <v>1.84905624389648</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.9018862247467</v>
+        <v>1.90188610553741</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.8775030374527</v>
+        <v>1.87750315666199</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.82060921192169</v>
+        <v>1.82060933113098</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1477" t="n">
-        <v>1.82467293739319</v>
+        <v>1.82467305660248</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.8775030374527</v>
+        <v>1.87750315666199</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.92220568656921</v>
+        <v>1.9222058057785</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.84092855453491</v>
+        <v>1.84092843532562</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.8775030374527</v>
+        <v>1.87750315666199</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.8466922044754</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.80730783939362</v>
+        <v>1.80730772018433</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1498" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1502" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.73291504383087</v>
+        <v>1.73291492462158</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.82918798923492</v>
+        <v>1.82918787002563</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.83356404304504</v>
+        <v>1.83356392383575</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.83356404304504</v>
+        <v>1.83356392383575</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.8204357624054</v>
+        <v>1.82043588161469</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.82918798923492</v>
+        <v>1.82918787002563</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.8204357624054</v>
+        <v>1.82043588161469</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1520" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419630050659</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.90358066558838</v>
+        <v>1.90358078479767</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.89045262336731</v>
+        <v>1.8904527425766</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419630050659</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419630050659</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.8466922044754</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>2.125</v>
       </c>
       <c r="G1535" t="n">
-        <v>1.85982012748718</v>
+        <v>1.85982024669647</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.8466922044754</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.8204357624054</v>
+        <v>1.82043588161469</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1540" t="n">
-        <v>1.80730783939362</v>
+        <v>1.80730772018433</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.8466922044754</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.82918798923492</v>
+        <v>1.82918787002563</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.8466922044754</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.89045262336731</v>
+        <v>1.8904527425766</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.89482867717743</v>
+        <v>1.89482879638672</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419630050659</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>2.125</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.85982012748718</v>
+        <v>1.85982024669647</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.72416269779205</v>
+        <v>1.72416293621063</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.71716117858887</v>
+        <v>1.71716105937958</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1570" t="n">
-        <v>1.64539396762848</v>
+        <v>1.64539408683777</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1571" t="n">
-        <v>1.51936364173889</v>
+        <v>1.51936376094818</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.58938038349152</v>
+        <v>1.5893806219101</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.633141040802</v>
+        <v>1.63314116001129</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.73116457462311</v>
+        <v>1.73116445541382</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.83356404304504</v>
+        <v>1.83356392383575</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.82918798923492</v>
+        <v>1.82918787002563</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1597" t="n">
-        <v>1.76354742050171</v>
+        <v>1.76354730129242</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.75479531288147</v>
+        <v>1.75479519367218</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.79855573177338</v>
+        <v>1.79855561256409</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.8204357624054</v>
+        <v>1.82043588161469</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.77667546272278</v>
+        <v>1.77667534351349</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.81932306289673</v>
+        <v>1.81932294368744</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.81932306289673</v>
+        <v>1.81932294368744</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.84200775623322</v>
+        <v>1.84200763702393</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.80389726161957</v>
+        <v>1.80389714241028</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.8329336643219</v>
+        <v>1.83293378353119</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1636" t="n">
-        <v>1.8329336643219</v>
+        <v>1.83293378353119</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.72767615318298</v>
+        <v>1.72767627239227</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1645" t="n">
-        <v>1.73312044143677</v>
+        <v>1.73312056064606</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.52260541915894</v>
+        <v>1.52260529994965</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.49356877803802</v>
+        <v>1.49356889724731</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1659" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.4227921962738</v>
+        <v>1.42279207706451</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.30301630496979</v>
+        <v>1.3030161857605</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.34294164180756</v>
+        <v>1.34294152259827</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.33023798465729</v>
+        <v>1.33023810386658</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1678" t="n">
-        <v>1.48449492454529</v>
+        <v>1.484494805336</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.46271753311157</v>
+        <v>1.46271741390228</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.44638431072235</v>
+        <v>1.44638442993164</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.46271753311157</v>
+        <v>1.46271741390228</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.46997654438019</v>
+        <v>1.46997666358948</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.41734790802002</v>
+        <v>1.41734778881073</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.38649642467499</v>
+        <v>1.38649654388428</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>1.5</v>
       </c>
       <c r="G1701" t="n">
-        <v>1.36108946800232</v>
+        <v>1.36108934879303</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>1.5</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.36108946800232</v>
+        <v>1.36108934879303</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>1.35599994659424</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.23042476177216</v>
+        <v>1.23042488098145</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.27760934829712</v>
+        <v>1.27760922908783</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.26127624511719</v>
+        <v>1.2612761259079</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.24312841892242</v>
+        <v>1.24312829971313</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.34657108783722</v>
+        <v>1.34657120704651</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.33023798465729</v>
+        <v>1.33023810386658</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.29031276702881</v>
+        <v>1.2903128862381</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.37923717498779</v>
+        <v>1.37923729419708</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.34475636482239</v>
+        <v>1.3447562456131</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.34294164180756</v>
+        <v>1.34294152259827</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.40101480484009</v>
+        <v>1.4010146856308</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.40101480484009</v>
+        <v>1.4010146856308</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.41734790802002</v>
+        <v>1.41734778881073</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>1.5</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.36108946800232</v>
+        <v>1.36108934879303</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.37742257118225</v>
+        <v>1.37742245197296</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.37742257118225</v>
+        <v>1.37742245197296</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.34657108783722</v>
+        <v>1.34657120704651</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.37923717498779</v>
+        <v>1.37923729419708</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1787" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.46271753311157</v>
+        <v>1.46271741390228</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.49356877803802</v>
+        <v>1.49356889724731</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.46997654438019</v>
+        <v>1.46997666358948</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.48449492454529</v>
+        <v>1.484494805336</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.6242333650589</v>
+        <v>1.62423324584961</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.62786293029785</v>
+        <v>1.62786304950714</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1814" t="n">
-        <v>1.48449492454529</v>
+        <v>1.484494805336</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1819" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.37742257118225</v>
+        <v>1.37742245197296</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.37923717498779</v>
+        <v>1.37923729419708</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1829" t="n">
-        <v>1.38286697864532</v>
+        <v>1.38286685943604</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.27397966384888</v>
+        <v>1.27397978305817</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.24675786495209</v>
+        <v>1.24675798416138</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1843" t="n">
-        <v>1.21409177780151</v>
+        <v>1.2140918970108</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.23949873447418</v>
+        <v>1.23949885368347</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.21409177780151</v>
+        <v>1.2140918970108</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.21409177780151</v>
+        <v>1.2140918970108</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -71678,7 +71678,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="D2743" t="n">
-        <v>1.55400002002716</v>
+        <v>1.55200004577637</v>
       </c>
       <c r="E2743" t="n">
         <v>1.60000002384186</v>
@@ -71690,6 +71690,32 @@
         <v>1.55200004577637</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>29876</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>1.61800003051758</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>1.53799998760223</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>1.55200004577637</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>1.57599997520447</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>1.57599997520447</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>2.69898533821106</v>
+        <v>2.69898509979248</v>
       </c>
       <c r="H3" t="n">
         <v>10338</v>
@@ -514,7 +514,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G5" t="n">
-        <v>2.68630051612854</v>
+        <v>2.68630123138428</v>
       </c>
       <c r="H5" t="n">
         <v>17322</v>
@@ -572,7 +572,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G7" t="n">
-        <v>2.74690461158752</v>
+        <v>2.7469048500061</v>
       </c>
       <c r="H7" t="n">
         <v>35596</v>
@@ -630,7 +630,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G9" t="n">
-        <v>2.71730732917786</v>
+        <v>2.71730756759644</v>
       </c>
       <c r="H9" t="n">
         <v>107316</v>
@@ -746,7 +746,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G13" t="n">
-        <v>2.39314699172974</v>
+        <v>2.39314746856689</v>
       </c>
       <c r="H13" t="n">
         <v>77275</v>
@@ -775,7 +775,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>2.43824791908264</v>
+        <v>2.43824815750122</v>
       </c>
       <c r="H14" t="n">
         <v>56306</v>
@@ -804,7 +804,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.50167059898376</v>
+        <v>2.50167036056519</v>
       </c>
       <c r="H15" t="n">
         <v>141373</v>
@@ -833,7 +833,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>2.56368398666382</v>
+        <v>2.56368374824524</v>
       </c>
       <c r="H16" t="n">
         <v>75059</v>
@@ -862,7 +862,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>2.45234203338623</v>
+        <v>2.45234179496765</v>
       </c>
       <c r="H17" t="n">
         <v>23673</v>
@@ -891,7 +891,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3973753452301</v>
+        <v>2.39737558364868</v>
       </c>
       <c r="H18" t="n">
         <v>28661</v>
@@ -1036,7 +1036,7 @@
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>2.11408805847168</v>
+        <v>2.1140878200531</v>
       </c>
       <c r="H23" t="n">
         <v>108673</v>
@@ -1065,7 +1065,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G24" t="n">
-        <v>1.9745579957962</v>
+        <v>1.97455763816833</v>
       </c>
       <c r="H24" t="n">
         <v>138010</v>
@@ -1181,7 +1181,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G28" t="n">
-        <v>1.71100199222565</v>
+        <v>1.71100163459778</v>
       </c>
       <c r="H28" t="n">
         <v>532299</v>
@@ -1210,7 +1210,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G29" t="n">
-        <v>1.86039710044861</v>
+        <v>1.8603972196579</v>
       </c>
       <c r="H29" t="n">
         <v>494650</v>
@@ -1239,7 +1239,7 @@
         <v>2.5</v>
       </c>
       <c r="G30" t="n">
-        <v>1.76173996925354</v>
+        <v>1.76173973083496</v>
       </c>
       <c r="H30" t="n">
         <v>322108</v>
@@ -1268,7 +1268,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G31" t="n">
-        <v>1.87730991840363</v>
+        <v>1.87731003761292</v>
       </c>
       <c r="H31" t="n">
         <v>154548</v>
@@ -1297,7 +1297,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G32" t="n">
-        <v>1.94777929782867</v>
+        <v>1.94777965545654</v>
       </c>
       <c r="H32" t="n">
         <v>56948</v>
@@ -1355,7 +1355,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G34" t="n">
-        <v>2.07039642333984</v>
+        <v>2.07039666175842</v>
       </c>
       <c r="H34" t="n">
         <v>372234</v>
@@ -1384,7 +1384,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G35" t="n">
-        <v>2.05207443237305</v>
+        <v>2.05207419395447</v>
       </c>
       <c r="H35" t="n">
         <v>184129</v>
@@ -1413,7 +1413,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G36" t="n">
-        <v>2.09294700622559</v>
+        <v>2.09294724464417</v>
       </c>
       <c r="H36" t="n">
         <v>286614</v>
@@ -1442,7 +1442,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G37" t="n">
-        <v>2.15918827056885</v>
+        <v>2.15918803215027</v>
       </c>
       <c r="H37" t="n">
         <v>158423</v>
@@ -1471,7 +1471,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G38" t="n">
-        <v>2.16059756278992</v>
+        <v>2.1605978012085</v>
       </c>
       <c r="H38" t="n">
         <v>79649</v>
@@ -1500,7 +1500,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G39" t="n">
-        <v>2.04784607887268</v>
+        <v>2.04784655570984</v>
       </c>
       <c r="H39" t="n">
         <v>22200</v>
@@ -1558,7 +1558,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>2.05771231651306</v>
+        <v>2.05771207809448</v>
       </c>
       <c r="H41" t="n">
         <v>58452</v>
@@ -1587,7 +1587,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G42" t="n">
-        <v>2.0633499622345</v>
+        <v>2.06334948539734</v>
       </c>
       <c r="H42" t="n">
         <v>7283</v>
@@ -1616,7 +1616,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G43" t="n">
-        <v>2.07321524620056</v>
+        <v>2.07321548461914</v>
       </c>
       <c r="H43" t="n">
         <v>76461</v>
@@ -1674,7 +1674,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G45" t="n">
-        <v>2.13522863388062</v>
+        <v>2.13522839546204</v>
       </c>
       <c r="H45" t="n">
         <v>141970</v>
@@ -1703,7 +1703,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G46" t="n">
-        <v>2.1577787399292</v>
+        <v>2.15777897834778</v>
       </c>
       <c r="H46" t="n">
         <v>65121</v>
@@ -1732,7 +1732,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G47" t="n">
-        <v>2.14932250976562</v>
+        <v>2.14932227134705</v>
       </c>
       <c r="H47" t="n">
         <v>45138</v>
@@ -1819,7 +1819,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G50" t="n">
-        <v>2.12677216529846</v>
+        <v>2.12677240371704</v>
       </c>
       <c r="H50" t="n">
         <v>93185</v>
@@ -1848,7 +1848,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G51" t="n">
-        <v>2.21274542808533</v>
+        <v>2.21274518966675</v>
       </c>
       <c r="H51" t="n">
         <v>169907</v>
@@ -1935,7 +1935,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G54" t="n">
-        <v>2.17469143867493</v>
+        <v>2.17469167709351</v>
       </c>
       <c r="H54" t="n">
         <v>139285</v>
@@ -1964,7 +1964,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G55" t="n">
-        <v>2.1859667301178</v>
+        <v>2.18596696853638</v>
       </c>
       <c r="H55" t="n">
         <v>20070</v>
@@ -1993,7 +1993,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G56" t="n">
-        <v>2.17892003059387</v>
+        <v>2.17891979217529</v>
       </c>
       <c r="H56" t="n">
         <v>6270</v>
@@ -2022,7 +2022,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G57" t="n">
-        <v>2.20147013664246</v>
+        <v>2.20147037506104</v>
       </c>
       <c r="H57" t="n">
         <v>49719</v>
@@ -2051,7 +2051,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G58" t="n">
-        <v>2.23670530319214</v>
+        <v>2.23670482635498</v>
       </c>
       <c r="H58" t="n">
         <v>93732</v>
@@ -2080,7 +2080,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>2.17751026153564</v>
+        <v>2.17751049995422</v>
       </c>
       <c r="H59" t="n">
         <v>71887</v>
@@ -2109,7 +2109,7 @@
         <v>3</v>
       </c>
       <c r="G60" t="n">
-        <v>2.11408805847168</v>
+        <v>2.1140878200531</v>
       </c>
       <c r="H60" t="n">
         <v>13315</v>
@@ -2138,7 +2138,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G61" t="n">
-        <v>2.18314814567566</v>
+        <v>2.18314790725708</v>
       </c>
       <c r="H61" t="n">
         <v>10022</v>
@@ -2225,7 +2225,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G64" t="n">
-        <v>1.89281344413757</v>
+        <v>1.89281332492828</v>
       </c>
       <c r="H64" t="n">
         <v>198445</v>
@@ -2254,7 +2254,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>1.98724246025085</v>
+        <v>1.98724234104156</v>
       </c>
       <c r="H65" t="n">
         <v>88924</v>
@@ -2283,7 +2283,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G66" t="n">
-        <v>1.94496071338654</v>
+        <v>1.94496083259583</v>
       </c>
       <c r="H66" t="n">
         <v>23053</v>
@@ -2341,7 +2341,7 @@
         <v>2.71600008010864</v>
       </c>
       <c r="G68" t="n">
-        <v>1.9139541387558</v>
+        <v>1.91395425796509</v>
       </c>
       <c r="H68" t="n">
         <v>32713</v>
@@ -2370,7 +2370,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G69" t="n">
-        <v>1.98724246025085</v>
+        <v>1.98724234104156</v>
       </c>
       <c r="H69" t="n">
         <v>51935</v>
@@ -2399,7 +2399,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.9745579957962</v>
+        <v>1.97455763816833</v>
       </c>
       <c r="H70" t="n">
         <v>68876</v>
@@ -2428,7 +2428,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>1.9238201379776</v>
+        <v>1.92382001876831</v>
       </c>
       <c r="H71" t="n">
         <v>17504</v>
@@ -2486,7 +2486,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G73" t="n">
-        <v>2.00838351249695</v>
+        <v>2.00838327407837</v>
       </c>
       <c r="H73" t="n">
         <v>38548</v>
@@ -2544,7 +2544,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G75" t="n">
-        <v>2.10704064369202</v>
+        <v>2.1070408821106</v>
       </c>
       <c r="H75" t="n">
         <v>47034</v>
@@ -2573,7 +2573,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>2.17046332359314</v>
+        <v>2.17046356201172</v>
       </c>
       <c r="H76" t="n">
         <v>157055</v>
@@ -2602,7 +2602,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G77" t="n">
-        <v>2.14791345596313</v>
+        <v>2.14791321754456</v>
       </c>
       <c r="H77" t="n">
         <v>12373</v>
@@ -2631,7 +2631,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G78" t="n">
-        <v>2.17751026153564</v>
+        <v>2.17751049995422</v>
       </c>
       <c r="H78" t="n">
         <v>77091</v>
@@ -2718,7 +2718,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>2.10704064369202</v>
+        <v>2.1070408821106</v>
       </c>
       <c r="H81" t="n">
         <v>25322</v>
@@ -2747,7 +2747,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G82" t="n">
-        <v>2.05771231651306</v>
+        <v>2.05771207809448</v>
       </c>
       <c r="H82" t="n">
         <v>255389</v>
@@ -2776,7 +2776,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G83" t="n">
-        <v>2.02670550346375</v>
+        <v>2.02670526504517</v>
       </c>
       <c r="H83" t="n">
         <v>164177</v>
@@ -2805,7 +2805,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G84" t="n">
-        <v>1.98724246025085</v>
+        <v>1.98724234104156</v>
       </c>
       <c r="H84" t="n">
         <v>42849</v>
@@ -2834,7 +2834,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G85" t="n">
-        <v>1.94918859004974</v>
+        <v>1.94918930530548</v>
       </c>
       <c r="H85" t="n">
         <v>142278</v>
@@ -2863,7 +2863,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>1.97314870357513</v>
+        <v>1.97314858436584</v>
       </c>
       <c r="H86" t="n">
         <v>52750</v>
@@ -2950,7 +2950,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G89" t="n">
-        <v>1.86321580410004</v>
+        <v>1.86321592330933</v>
       </c>
       <c r="H89" t="n">
         <v>23082</v>
@@ -3008,7 +3008,7 @@
         <v>2.5</v>
       </c>
       <c r="G91" t="n">
-        <v>1.79777717590332</v>
+        <v>1.79777681827545</v>
       </c>
       <c r="H91" t="n">
         <v>242021</v>
@@ -3037,7 +3037,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>1.74024832248688</v>
+        <v>1.7402480840683</v>
       </c>
       <c r="H92" t="n">
         <v>93154</v>
@@ -3066,7 +3066,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G93" t="n">
-        <v>1.68559563159943</v>
+        <v>1.68559587001801</v>
       </c>
       <c r="H93" t="n">
         <v>125569</v>
@@ -3095,7 +3095,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G94" t="n">
-        <v>1.68128097057343</v>
+        <v>1.681281208992</v>
       </c>
       <c r="H94" t="n">
         <v>97874</v>
@@ -3153,7 +3153,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62662875652313</v>
+        <v>1.62662863731384</v>
       </c>
       <c r="H96" t="n">
         <v>316466</v>
@@ -3182,7 +3182,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G97" t="n">
-        <v>1.63957262039185</v>
+        <v>1.63957250118256</v>
       </c>
       <c r="H97" t="n">
         <v>216744</v>
@@ -3211,7 +3211,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.6036171913147</v>
+        <v>1.60361707210541</v>
       </c>
       <c r="H98" t="n">
         <v>199551</v>
@@ -3240,7 +3240,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.6036171913147</v>
+        <v>1.60361707210541</v>
       </c>
       <c r="H99" t="n">
         <v>183461</v>
@@ -3269,7 +3269,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G100" t="n">
-        <v>1.63957262039185</v>
+        <v>1.63957250118256</v>
       </c>
       <c r="H100" t="n">
         <v>213463</v>
@@ -3298,7 +3298,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G101" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991041183472</v>
       </c>
       <c r="H101" t="n">
         <v>233008</v>
@@ -3327,7 +3327,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G102" t="n">
-        <v>1.78914749622345</v>
+        <v>1.78914761543274</v>
       </c>
       <c r="H102" t="n">
         <v>446680</v>
@@ -3356,7 +3356,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G103" t="n">
-        <v>1.86249721050262</v>
+        <v>1.86249709129333</v>
       </c>
       <c r="H103" t="n">
         <v>317819</v>
@@ -3385,7 +3385,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G104" t="n">
-        <v>1.83373248577118</v>
+        <v>1.83373260498047</v>
       </c>
       <c r="H104" t="n">
         <v>76401</v>
@@ -3414,7 +3414,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G105" t="n">
-        <v>1.86249721050262</v>
+        <v>1.86249709129333</v>
       </c>
       <c r="H105" t="n">
         <v>30183</v>
@@ -3443,7 +3443,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G106" t="n">
-        <v>1.84092378616333</v>
+        <v>1.84092354774475</v>
       </c>
       <c r="H106" t="n">
         <v>112565</v>
@@ -3472,7 +3472,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>1.81215918064117</v>
+        <v>1.81215929985046</v>
       </c>
       <c r="H107" t="n">
         <v>68874</v>
@@ -3530,7 +3530,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G109" t="n">
-        <v>1.79490053653717</v>
+        <v>1.79490065574646</v>
       </c>
       <c r="H109" t="n">
         <v>138260</v>
@@ -3559,7 +3559,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G110" t="n">
-        <v>1.83517062664032</v>
+        <v>1.83517098426819</v>
       </c>
       <c r="H110" t="n">
         <v>87116</v>
@@ -3588,7 +3588,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G111" t="n">
-        <v>1.83948528766632</v>
+        <v>1.83948540687561</v>
       </c>
       <c r="H111" t="n">
         <v>113743</v>
@@ -3646,7 +3646,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G113" t="n">
-        <v>1.80496799945831</v>
+        <v>1.80496823787689</v>
       </c>
       <c r="H113" t="n">
         <v>31915</v>
@@ -3675,7 +3675,7 @@
         <v>2.5</v>
       </c>
       <c r="G114" t="n">
-        <v>1.79777717590332</v>
+        <v>1.79777681827545</v>
       </c>
       <c r="H114" t="n">
         <v>65250</v>
@@ -3704,7 +3704,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G115" t="n">
-        <v>1.73305726051331</v>
+        <v>1.73305714130402</v>
       </c>
       <c r="H115" t="n">
         <v>65890</v>
@@ -3733,7 +3733,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G116" t="n">
-        <v>1.72011315822601</v>
+        <v>1.72011280059814</v>
       </c>
       <c r="H116" t="n">
         <v>108775</v>
@@ -3791,7 +3791,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G118" t="n">
-        <v>1.6338198184967</v>
+        <v>1.63381969928741</v>
       </c>
       <c r="H118" t="n">
         <v>132672</v>
@@ -3820,7 +3820,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G119" t="n">
-        <v>1.68559563159943</v>
+        <v>1.68559587001801</v>
       </c>
       <c r="H119" t="n">
         <v>43254</v>
@@ -3907,7 +3907,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>1.81215918064117</v>
+        <v>1.81215929985046</v>
       </c>
       <c r="H122" t="n">
         <v>185327</v>
@@ -4023,7 +4023,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G126" t="n">
-        <v>1.5302677154541</v>
+        <v>1.53026783466339</v>
       </c>
       <c r="H126" t="n">
         <v>255565</v>
@@ -4110,7 +4110,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G129" t="n">
-        <v>1.47561526298523</v>
+        <v>1.47561538219452</v>
       </c>
       <c r="H129" t="n">
         <v>141074</v>
@@ -4139,7 +4139,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G130" t="n">
-        <v>1.49287378787994</v>
+        <v>1.49287402629852</v>
       </c>
       <c r="H130" t="n">
         <v>120762</v>
@@ -4197,7 +4197,7 @@
         <v>2</v>
       </c>
       <c r="G132" t="n">
-        <v>1.43822145462036</v>
+        <v>1.43822157382965</v>
       </c>
       <c r="H132" t="n">
         <v>100335</v>
@@ -4226,7 +4226,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G133" t="n">
-        <v>1.50869452953339</v>
+        <v>1.5086944103241</v>
       </c>
       <c r="H133" t="n">
         <v>18201</v>
@@ -4284,7 +4284,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G135" t="n">
-        <v>1.5604704618454</v>
+        <v>1.56047058105469</v>
       </c>
       <c r="H135" t="n">
         <v>94625</v>
@@ -4313,7 +4313,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G136" t="n">
-        <v>1.63238167762756</v>
+        <v>1.63238131999969</v>
       </c>
       <c r="H136" t="n">
         <v>98434</v>
@@ -4342,7 +4342,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G137" t="n">
-        <v>1.6338198184967</v>
+        <v>1.63381969928741</v>
       </c>
       <c r="H137" t="n">
         <v>41464</v>
@@ -4371,7 +4371,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G138" t="n">
-        <v>1.65395474433899</v>
+        <v>1.65395486354828</v>
       </c>
       <c r="H138" t="n">
         <v>51689</v>
@@ -4545,7 +4545,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G144" t="n">
-        <v>1.56190848350525</v>
+        <v>1.56190860271454</v>
       </c>
       <c r="H144" t="n">
         <v>42992</v>
@@ -4574,7 +4574,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G145" t="n">
-        <v>1.51300919055939</v>
+        <v>1.5130090713501</v>
       </c>
       <c r="H145" t="n">
         <v>118150</v>
@@ -4748,7 +4748,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G151" t="n">
-        <v>1.3957941532135</v>
+        <v>1.39579403400421</v>
       </c>
       <c r="H151" t="n">
         <v>157557</v>
@@ -4777,7 +4777,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G152" t="n">
-        <v>1.33754622936249</v>
+        <v>1.33754599094391</v>
       </c>
       <c r="H152" t="n">
         <v>136787</v>
@@ -4806,7 +4806,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G153" t="n">
-        <v>1.3440181016922</v>
+        <v>1.34401822090149</v>
       </c>
       <c r="H153" t="n">
         <v>101071</v>
@@ -4835,7 +4835,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G154" t="n">
-        <v>1.42959225177765</v>
+        <v>1.42959237098694</v>
       </c>
       <c r="H154" t="n">
         <v>120160</v>
@@ -4893,7 +4893,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G156" t="n">
-        <v>1.44828915596008</v>
+        <v>1.44828903675079</v>
       </c>
       <c r="H156" t="n">
         <v>46189</v>
@@ -4951,7 +4951,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G158" t="n">
-        <v>1.48136818408966</v>
+        <v>1.48136830329895</v>
       </c>
       <c r="H158" t="n">
         <v>66888</v>
@@ -5096,7 +5096,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G163" t="n">
-        <v>1.49143576622009</v>
+        <v>1.49143552780151</v>
       </c>
       <c r="H163" t="n">
         <v>102808</v>
@@ -5125,7 +5125,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G164" t="n">
-        <v>1.5173237323761</v>
+        <v>1.51732361316681</v>
       </c>
       <c r="H164" t="n">
         <v>103001</v>
@@ -5154,7 +5154,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G165" t="n">
-        <v>1.53602063655853</v>
+        <v>1.53602051734924</v>
       </c>
       <c r="H165" t="n">
         <v>71695</v>
@@ -5183,7 +5183,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G166" t="n">
-        <v>1.52595317363739</v>
+        <v>1.5259530544281</v>
       </c>
       <c r="H166" t="n">
         <v>74300</v>
@@ -5241,7 +5241,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G168" t="n">
-        <v>1.52307677268982</v>
+        <v>1.52307665348053</v>
       </c>
       <c r="H168" t="n">
         <v>57256</v>
@@ -5270,7 +5270,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>1.51013255119324</v>
+        <v>1.51013267040253</v>
       </c>
       <c r="H169" t="n">
         <v>64844</v>
@@ -5299,7 +5299,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G170" t="n">
-        <v>1.51588582992554</v>
+        <v>1.51588559150696</v>
       </c>
       <c r="H170" t="n">
         <v>58563</v>
@@ -5328,7 +5328,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G171" t="n">
-        <v>1.50869452953339</v>
+        <v>1.5086944103241</v>
       </c>
       <c r="H171" t="n">
         <v>138864</v>
@@ -5357,7 +5357,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G172" t="n">
-        <v>1.53745901584625</v>
+        <v>1.53745889663696</v>
       </c>
       <c r="H172" t="n">
         <v>152191</v>
@@ -5386,7 +5386,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G173" t="n">
-        <v>1.55759382247925</v>
+        <v>1.55759394168854</v>
       </c>
       <c r="H173" t="n">
         <v>105976</v>
@@ -5415,7 +5415,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G174" t="n">
-        <v>1.5647851228714</v>
+        <v>1.56478524208069</v>
       </c>
       <c r="H174" t="n">
         <v>39718</v>
@@ -5444,7 +5444,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G175" t="n">
-        <v>1.54896461963654</v>
+        <v>1.54896473884583</v>
       </c>
       <c r="H175" t="n">
         <v>69988</v>
@@ -5473,7 +5473,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G176" t="n">
-        <v>1.55471754074097</v>
+        <v>1.55471742153168</v>
       </c>
       <c r="H176" t="n">
         <v>108921</v>
@@ -5502,7 +5502,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G177" t="n">
-        <v>1.5604704618454</v>
+        <v>1.56047058105469</v>
       </c>
       <c r="H177" t="n">
         <v>16139</v>
@@ -5531,7 +5531,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G178" t="n">
-        <v>1.54896461963654</v>
+        <v>1.54896473884583</v>
       </c>
       <c r="H178" t="n">
         <v>110525</v>
@@ -5560,7 +5560,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G179" t="n">
-        <v>1.50725626945496</v>
+        <v>1.50725615024567</v>
       </c>
       <c r="H179" t="n">
         <v>115275</v>
@@ -5589,7 +5589,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G180" t="n">
-        <v>1.49287378787994</v>
+        <v>1.49287402629852</v>
       </c>
       <c r="H180" t="n">
         <v>65474</v>
@@ -5647,7 +5647,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G182" t="n">
-        <v>1.46986222267151</v>
+        <v>1.4698623418808</v>
       </c>
       <c r="H182" t="n">
         <v>47947</v>
@@ -5676,7 +5676,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G183" t="n">
-        <v>1.45979499816895</v>
+        <v>1.45979487895966</v>
       </c>
       <c r="H183" t="n">
         <v>30394</v>
@@ -5792,7 +5792,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G187" t="n">
-        <v>1.48280656337738</v>
+        <v>1.48280644416809</v>
       </c>
       <c r="H187" t="n">
         <v>8172</v>
@@ -5850,7 +5850,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G189" t="n">
-        <v>1.45979499816895</v>
+        <v>1.45979487895966</v>
       </c>
       <c r="H189" t="n">
         <v>11686</v>
@@ -5879,7 +5879,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G190" t="n">
-        <v>1.46986222267151</v>
+        <v>1.4698623418808</v>
       </c>
       <c r="H190" t="n">
         <v>50388</v>
@@ -5908,7 +5908,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G191" t="n">
-        <v>1.48424458503723</v>
+        <v>1.48424446582794</v>
       </c>
       <c r="H191" t="n">
         <v>3174</v>
@@ -5966,7 +5966,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G193" t="n">
-        <v>1.46986222267151</v>
+        <v>1.4698623418808</v>
       </c>
       <c r="H193" t="n">
         <v>21732</v>
@@ -5995,7 +5995,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G194" t="n">
-        <v>1.46267139911652</v>
+        <v>1.46267116069794</v>
       </c>
       <c r="H194" t="n">
         <v>82859</v>
@@ -6082,7 +6082,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G197" t="n">
-        <v>1.54896461963654</v>
+        <v>1.54896473884583</v>
       </c>
       <c r="H197" t="n">
         <v>54297</v>
@@ -6111,7 +6111,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G198" t="n">
-        <v>1.60936999320984</v>
+        <v>1.60936987400055</v>
       </c>
       <c r="H198" t="n">
         <v>215286</v>
@@ -6169,7 +6169,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991041183472</v>
       </c>
       <c r="H200" t="n">
         <v>205807</v>
@@ -6198,7 +6198,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991041183472</v>
       </c>
       <c r="H201" t="n">
         <v>93341</v>
@@ -6227,7 +6227,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>1.67552804946899</v>
+        <v>1.67552816867828</v>
       </c>
       <c r="H202" t="n">
         <v>28652</v>
@@ -6256,7 +6256,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991041183472</v>
       </c>
       <c r="H203" t="n">
         <v>74895</v>
@@ -6285,7 +6285,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G204" t="n">
-        <v>1.68703377246857</v>
+        <v>1.68703389167786</v>
       </c>
       <c r="H204" t="n">
         <v>57861</v>
@@ -6372,7 +6372,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G207" t="n">
-        <v>1.73161864280701</v>
+        <v>1.73161900043488</v>
       </c>
       <c r="H207" t="n">
         <v>57561</v>
@@ -6401,7 +6401,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G208" t="n">
-        <v>1.73449528217316</v>
+        <v>1.73449540138245</v>
       </c>
       <c r="H208" t="n">
         <v>42982</v>
@@ -6430,7 +6430,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>1.74743914604187</v>
+        <v>1.74743950366974</v>
       </c>
       <c r="H209" t="n">
         <v>56802</v>
@@ -6459,7 +6459,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G210" t="n">
-        <v>1.77332699298859</v>
+        <v>1.77332711219788</v>
       </c>
       <c r="H210" t="n">
         <v>264730</v>
@@ -6546,7 +6546,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>1.74743914604187</v>
+        <v>1.74743950366974</v>
       </c>
       <c r="H213" t="n">
         <v>87327</v>
@@ -6575,7 +6575,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G214" t="n">
-        <v>1.718674659729</v>
+        <v>1.71867477893829</v>
       </c>
       <c r="H214" t="n">
         <v>63356</v>
@@ -6604,7 +6604,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>1.67552804946899</v>
+        <v>1.67552816867828</v>
       </c>
       <c r="H215" t="n">
         <v>240056</v>
@@ -6691,7 +6691,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>1.51013255119324</v>
+        <v>1.51013267040253</v>
       </c>
       <c r="H218" t="n">
         <v>155544</v>
@@ -6720,7 +6720,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>1.51013255119324</v>
+        <v>1.51013267040253</v>
       </c>
       <c r="H219" t="n">
         <v>140088</v>
@@ -6778,7 +6778,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G221" t="n">
-        <v>1.42743492126465</v>
+        <v>1.42743468284607</v>
       </c>
       <c r="H221" t="n">
         <v>399624</v>
@@ -6807,7 +6807,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G222" t="n">
-        <v>1.43246865272522</v>
+        <v>1.43246877193451</v>
       </c>
       <c r="H222" t="n">
         <v>176278</v>
@@ -6836,7 +6836,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G223" t="n">
-        <v>1.42383944988251</v>
+        <v>1.42383933067322</v>
       </c>
       <c r="H223" t="n">
         <v>59778</v>
@@ -6865,7 +6865,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>1.40586173534393</v>
+        <v>1.40586161613464</v>
       </c>
       <c r="H224" t="n">
         <v>291769</v>
@@ -6923,7 +6923,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G226" t="n">
-        <v>1.39004111289978</v>
+        <v>1.39004123210907</v>
       </c>
       <c r="H226" t="n">
         <v>120366</v>
@@ -6981,7 +6981,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G228" t="n">
-        <v>1.3957941532135</v>
+        <v>1.39579403400421</v>
       </c>
       <c r="H228" t="n">
         <v>32138</v>
@@ -7010,7 +7010,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G229" t="n">
-        <v>1.33754622936249</v>
+        <v>1.33754599094391</v>
       </c>
       <c r="H229" t="n">
         <v>165879</v>
@@ -7068,7 +7068,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G231" t="n">
-        <v>1.33754622936249</v>
+        <v>1.33754599094391</v>
       </c>
       <c r="H231" t="n">
         <v>103896</v>
@@ -7097,7 +7097,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G232" t="n">
-        <v>1.34473705291748</v>
+        <v>1.34473717212677</v>
       </c>
       <c r="H232" t="n">
         <v>33971</v>
@@ -7126,7 +7126,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G233" t="n">
-        <v>1.3332314491272</v>
+        <v>1.33323132991791</v>
       </c>
       <c r="H233" t="n">
         <v>41061</v>
@@ -7184,7 +7184,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G235" t="n">
-        <v>1.30806243419647</v>
+        <v>1.30806255340576</v>
       </c>
       <c r="H235" t="n">
         <v>64519</v>
@@ -7300,7 +7300,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G239" t="n">
-        <v>1.34545636177063</v>
+        <v>1.34545648097992</v>
       </c>
       <c r="H239" t="n">
         <v>231772</v>
@@ -7329,7 +7329,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G240" t="n">
-        <v>1.4022661447525</v>
+        <v>1.40226602554321</v>
       </c>
       <c r="H240" t="n">
         <v>311388</v>
@@ -7358,7 +7358,7 @@
         <v>1.95299994945526</v>
       </c>
       <c r="G241" t="n">
-        <v>1.40442335605621</v>
+        <v>1.40442323684692</v>
       </c>
       <c r="H241" t="n">
         <v>228383</v>
@@ -7387,7 +7387,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G242" t="n">
-        <v>1.48712122440338</v>
+        <v>1.48712110519409</v>
       </c>
       <c r="H242" t="n">
         <v>292070</v>
@@ -7445,7 +7445,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G244" t="n">
-        <v>1.44828915596008</v>
+        <v>1.44828903675079</v>
       </c>
       <c r="H244" t="n">
         <v>309397</v>
@@ -7503,7 +7503,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G246" t="n">
-        <v>1.45979499816895</v>
+        <v>1.45979487895966</v>
       </c>
       <c r="H246" t="n">
         <v>300553</v>
@@ -7561,7 +7561,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G248" t="n">
-        <v>1.53602063655853</v>
+        <v>1.53602051734924</v>
       </c>
       <c r="H248" t="n">
         <v>216798</v>
@@ -7590,7 +7590,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G249" t="n">
-        <v>1.54177367687225</v>
+        <v>1.54177355766296</v>
       </c>
       <c r="H249" t="n">
         <v>107448</v>
@@ -7619,7 +7619,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G250" t="n">
-        <v>1.54465007781982</v>
+        <v>1.54464983940125</v>
       </c>
       <c r="H250" t="n">
         <v>107669</v>
@@ -7648,7 +7648,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G251" t="n">
-        <v>1.5173237323761</v>
+        <v>1.51732361316681</v>
       </c>
       <c r="H251" t="n">
         <v>66840</v>
@@ -7706,7 +7706,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G253" t="n">
-        <v>1.56190848350525</v>
+        <v>1.56190860271454</v>
       </c>
       <c r="H253" t="n">
         <v>96063</v>
@@ -7735,7 +7735,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>1.5604704618454</v>
+        <v>1.56047058105469</v>
       </c>
       <c r="H254" t="n">
         <v>51401</v>
@@ -7764,7 +7764,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G255" t="n">
-        <v>1.5604704618454</v>
+        <v>1.56047058105469</v>
       </c>
       <c r="H255" t="n">
         <v>23797</v>
@@ -7793,7 +7793,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G256" t="n">
-        <v>1.55759382247925</v>
+        <v>1.55759394168854</v>
       </c>
       <c r="H256" t="n">
         <v>50577</v>
@@ -7851,7 +7851,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G258" t="n">
-        <v>1.60649347305298</v>
+        <v>1.60649359226227</v>
       </c>
       <c r="H258" t="n">
         <v>92524</v>
@@ -7909,7 +7909,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>1.64676380157471</v>
+        <v>1.64676368236542</v>
       </c>
       <c r="H260" t="n">
         <v>278227</v>
@@ -7967,7 +7967,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G262" t="n">
-        <v>1.66546058654785</v>
+        <v>1.66546046733856</v>
       </c>
       <c r="H262" t="n">
         <v>37389</v>
@@ -7996,7 +7996,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>1.66114580631256</v>
+        <v>1.66114592552185</v>
       </c>
       <c r="H263" t="n">
         <v>109636</v>
@@ -8025,7 +8025,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>1.66546058654785</v>
+        <v>1.66546046733856</v>
       </c>
       <c r="H264" t="n">
         <v>230585</v>
@@ -8054,7 +8054,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G265" t="n">
-        <v>1.65683102607727</v>
+        <v>1.65683126449585</v>
       </c>
       <c r="H265" t="n">
         <v>154016</v>
@@ -8083,7 +8083,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G266" t="n">
-        <v>1.67408978939056</v>
+        <v>1.67409002780914</v>
       </c>
       <c r="H266" t="n">
         <v>106846</v>
@@ -8112,7 +8112,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>1.697101354599</v>
+        <v>1.69710147380829</v>
       </c>
       <c r="H267" t="n">
         <v>248065</v>
@@ -8141,7 +8141,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G268" t="n">
-        <v>1.72011315822601</v>
+        <v>1.72011280059814</v>
       </c>
       <c r="H268" t="n">
         <v>78748</v>
@@ -8170,7 +8170,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G269" t="n">
-        <v>1.72298955917358</v>
+        <v>1.72298943996429</v>
       </c>
       <c r="H269" t="n">
         <v>119208</v>
@@ -8199,7 +8199,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G270" t="n">
-        <v>1.72442770004272</v>
+        <v>1.7244279384613</v>
       </c>
       <c r="H270" t="n">
         <v>163949</v>
@@ -8228,7 +8228,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G271" t="n">
-        <v>1.77476537227631</v>
+        <v>1.7747654914856</v>
       </c>
       <c r="H271" t="n">
         <v>96436</v>
@@ -8315,7 +8315,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G274" t="n">
-        <v>1.7488774061203</v>
+        <v>1.74887728691101</v>
       </c>
       <c r="H274" t="n">
         <v>56096</v>
@@ -8402,7 +8402,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G277" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991041183472</v>
       </c>
       <c r="H277" t="n">
         <v>113971</v>
@@ -8431,7 +8431,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>1.66114580631256</v>
+        <v>1.66114592552185</v>
       </c>
       <c r="H278" t="n">
         <v>173082</v>
@@ -8460,7 +8460,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G279" t="n">
-        <v>1.64244902133942</v>
+        <v>1.64244890213013</v>
       </c>
       <c r="H279" t="n">
         <v>168716</v>
@@ -8576,7 +8576,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.63957262039185</v>
+        <v>1.63957250118256</v>
       </c>
       <c r="H283" t="n">
         <v>100008</v>
@@ -8634,7 +8634,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G285" t="n">
-        <v>1.65395474433899</v>
+        <v>1.65395486354828</v>
       </c>
       <c r="H285" t="n">
         <v>156406</v>
@@ -8721,7 +8721,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G288" t="n">
-        <v>1.64244902133942</v>
+        <v>1.64244890213013</v>
       </c>
       <c r="H288" t="n">
         <v>137257</v>
@@ -8779,7 +8779,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>1.63957262039185</v>
+        <v>1.63957250118256</v>
       </c>
       <c r="H290" t="n">
         <v>84656</v>
@@ -8808,7 +8808,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G291" t="n">
-        <v>1.63094329833984</v>
+        <v>1.63094305992126</v>
       </c>
       <c r="H291" t="n">
         <v>45265</v>
@@ -8895,7 +8895,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G294" t="n">
-        <v>1.5173237323761</v>
+        <v>1.51732361316681</v>
       </c>
       <c r="H294" t="n">
         <v>436962</v>
@@ -8924,7 +8924,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G295" t="n">
-        <v>1.48136818408966</v>
+        <v>1.48136830329895</v>
       </c>
       <c r="H295" t="n">
         <v>139909</v>
@@ -8953,7 +8953,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G296" t="n">
-        <v>1.49143576622009</v>
+        <v>1.49143552780151</v>
       </c>
       <c r="H296" t="n">
         <v>99146</v>
@@ -8982,7 +8982,7 @@
         <v>2</v>
       </c>
       <c r="G297" t="n">
-        <v>1.43822145462036</v>
+        <v>1.43822157382965</v>
       </c>
       <c r="H297" t="n">
         <v>281309</v>
@@ -9011,7 +9011,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G298" t="n">
-        <v>1.48280656337738</v>
+        <v>1.48280644416809</v>
       </c>
       <c r="H298" t="n">
         <v>126544</v>
@@ -9040,7 +9040,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G299" t="n">
-        <v>1.45979499816895</v>
+        <v>1.45979487895966</v>
       </c>
       <c r="H299" t="n">
         <v>173134</v>
@@ -9069,7 +9069,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>1.52451491355896</v>
+        <v>1.52451479434967</v>
       </c>
       <c r="H300" t="n">
         <v>252976</v>
@@ -9098,7 +9098,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G301" t="n">
-        <v>1.5216383934021</v>
+        <v>1.52163851261139</v>
       </c>
       <c r="H301" t="n">
         <v>197878</v>
@@ -9156,7 +9156,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>1.51013255119324</v>
+        <v>1.51013267040253</v>
       </c>
       <c r="H303" t="n">
         <v>163594</v>
@@ -9185,7 +9185,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G304" t="n">
-        <v>1.50150334835052</v>
+        <v>1.50150346755981</v>
       </c>
       <c r="H304" t="n">
         <v>195517</v>
@@ -9214,7 +9214,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G305" t="n">
-        <v>1.49718868732452</v>
+        <v>1.49718880653381</v>
       </c>
       <c r="H305" t="n">
         <v>130511</v>
@@ -9243,7 +9243,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G306" t="n">
-        <v>1.51157104969025</v>
+        <v>1.51157093048096</v>
       </c>
       <c r="H306" t="n">
         <v>342739</v>
@@ -9272,7 +9272,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G307" t="n">
-        <v>1.54465007781982</v>
+        <v>1.54464983940125</v>
       </c>
       <c r="H307" t="n">
         <v>276795</v>
@@ -9301,7 +9301,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G308" t="n">
-        <v>1.55903208255768</v>
+        <v>1.55903232097626</v>
       </c>
       <c r="H308" t="n">
         <v>181968</v>
@@ -9330,7 +9330,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>1.53889727592468</v>
+        <v>1.53889715671539</v>
       </c>
       <c r="H309" t="n">
         <v>473186</v>
@@ -9359,7 +9359,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G310" t="n">
-        <v>1.73305726051331</v>
+        <v>1.73305714130402</v>
       </c>
       <c r="H310" t="n">
         <v>2118328</v>
@@ -9417,7 +9417,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G312" t="n">
-        <v>1.81503582000732</v>
+        <v>1.81503558158875</v>
       </c>
       <c r="H312" t="n">
         <v>584553</v>
@@ -9446,7 +9446,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>1.76901245117188</v>
+        <v>1.76901268959045</v>
       </c>
       <c r="H313" t="n">
         <v>240440</v>
@@ -9475,7 +9475,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G314" t="n">
-        <v>1.75750696659088</v>
+        <v>1.7575067281723</v>
       </c>
       <c r="H314" t="n">
         <v>382673</v>
@@ -9504,7 +9504,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G315" t="n">
-        <v>1.73305726051331</v>
+        <v>1.73305714130402</v>
       </c>
       <c r="H315" t="n">
         <v>135784</v>
@@ -9533,7 +9533,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>1.81215918064117</v>
+        <v>1.81215929985046</v>
       </c>
       <c r="H316" t="n">
         <v>826864</v>
@@ -9591,7 +9591,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G318" t="n">
-        <v>1.99049878120422</v>
+        <v>1.99049866199493</v>
       </c>
       <c r="H318" t="n">
         <v>982630</v>
@@ -9620,7 +9620,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>1.95166683197021</v>
+        <v>1.95166671276093</v>
       </c>
       <c r="H319" t="n">
         <v>345138</v>
@@ -9707,7 +9707,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G322" t="n">
-        <v>1.96317231655121</v>
+        <v>1.96317267417908</v>
       </c>
       <c r="H322" t="n">
         <v>428819</v>
@@ -9765,7 +9765,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G324" t="n">
-        <v>1.97467827796936</v>
+        <v>1.97467803955078</v>
       </c>
       <c r="H324" t="n">
         <v>133183</v>
@@ -9794,7 +9794,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G325" t="n">
-        <v>1.95885765552521</v>
+        <v>1.95885789394379</v>
       </c>
       <c r="H325" t="n">
         <v>255642</v>
@@ -9823,7 +9823,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G326" t="n">
-        <v>1.97036361694336</v>
+        <v>1.97036349773407</v>
       </c>
       <c r="H326" t="n">
         <v>126422</v>
@@ -9852,7 +9852,7 @@
         <v>2.71199989318848</v>
       </c>
       <c r="G327" t="n">
-        <v>1.95022833347321</v>
+        <v>1.9502284526825</v>
       </c>
       <c r="H327" t="n">
         <v>147099</v>
@@ -9881,7 +9881,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G328" t="n">
-        <v>1.99625182151794</v>
+        <v>1.99625158309937</v>
       </c>
       <c r="H328" t="n">
         <v>411215</v>
@@ -9910,7 +9910,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>1.96317231655121</v>
+        <v>1.96317267417908</v>
       </c>
       <c r="H329" t="n">
         <v>315276</v>
@@ -9939,7 +9939,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G330" t="n">
-        <v>1.87400257587433</v>
+        <v>1.87400281429291</v>
       </c>
       <c r="H330" t="n">
         <v>719612</v>
@@ -9968,7 +9968,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>1.77620363235474</v>
+        <v>1.77620375156403</v>
       </c>
       <c r="H331" t="n">
         <v>509162</v>
@@ -9997,7 +9997,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G332" t="n">
-        <v>1.71004557609558</v>
+        <v>1.710045337677</v>
       </c>
       <c r="H332" t="n">
         <v>423853</v>
@@ -10084,7 +10084,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G335" t="n">
-        <v>1.79058563709259</v>
+        <v>1.79058575630188</v>
       </c>
       <c r="H335" t="n">
         <v>437211</v>
@@ -10113,7 +10113,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G336" t="n">
-        <v>1.85386788845062</v>
+        <v>1.85386765003204</v>
       </c>
       <c r="H336" t="n">
         <v>411061</v>
@@ -10142,7 +10142,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G337" t="n">
-        <v>1.90852010250092</v>
+        <v>1.90852034091949</v>
       </c>
       <c r="H337" t="n">
         <v>339495</v>
@@ -10171,7 +10171,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G338" t="n">
-        <v>2.00488090515137</v>
+        <v>2.00488066673279</v>
       </c>
       <c r="H338" t="n">
         <v>1142710</v>
@@ -10200,7 +10200,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G339" t="n">
-        <v>1.96748721599579</v>
+        <v>1.9674870967865</v>
       </c>
       <c r="H339" t="n">
         <v>358063</v>
@@ -10229,7 +10229,7 @@
         <v>2.5</v>
       </c>
       <c r="G340" t="n">
-        <v>1.79777717590332</v>
+        <v>1.79777681827545</v>
       </c>
       <c r="H340" t="n">
         <v>1136516</v>
@@ -10287,7 +10287,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G342" t="n">
-        <v>1.70136153697968</v>
+        <v>1.70136141777039</v>
       </c>
       <c r="H342" t="n">
         <v>961120</v>
@@ -10316,7 +10316,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G343" t="n">
-        <v>1.72954428195953</v>
+        <v>1.7295446395874</v>
       </c>
       <c r="H343" t="n">
         <v>724620</v>
@@ -10345,7 +10345,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G344" t="n">
-        <v>1.7236111164093</v>
+        <v>1.72361099720001</v>
       </c>
       <c r="H344" t="n">
         <v>420972</v>
@@ -10374,7 +10374,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G345" t="n">
-        <v>1.67762863636017</v>
+        <v>1.67762851715088</v>
       </c>
       <c r="H345" t="n">
         <v>473880</v>
@@ -10432,7 +10432,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G347" t="n">
-        <v>1.76514399051666</v>
+        <v>1.76514410972595</v>
       </c>
       <c r="H347" t="n">
         <v>696640</v>
@@ -10490,7 +10490,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G349" t="n">
-        <v>1.7147114276886</v>
+        <v>1.71471118927002</v>
       </c>
       <c r="H349" t="n">
         <v>228527</v>
@@ -10548,7 +10548,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G351" t="n">
-        <v>1.70581126213074</v>
+        <v>1.70581150054932</v>
       </c>
       <c r="H351" t="n">
         <v>296176</v>
@@ -10577,7 +10577,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G352" t="n">
-        <v>1.68652820587158</v>
+        <v>1.68652844429016</v>
       </c>
       <c r="H352" t="n">
         <v>226216</v>
@@ -10606,7 +10606,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G353" t="n">
-        <v>1.66279554367065</v>
+        <v>1.66279542446136</v>
       </c>
       <c r="H353" t="n">
         <v>369421</v>
@@ -10635,7 +10635,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G354" t="n">
-        <v>1.67169535160065</v>
+        <v>1.67169523239136</v>
       </c>
       <c r="H354" t="n">
         <v>556791</v>
@@ -10693,7 +10693,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G356" t="n">
-        <v>1.67762863636017</v>
+        <v>1.67762851715088</v>
       </c>
       <c r="H356" t="n">
         <v>106360</v>
@@ -10722,7 +10722,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G357" t="n">
-        <v>1.73547744750977</v>
+        <v>1.73547756671906</v>
       </c>
       <c r="H357" t="n">
         <v>773904</v>
@@ -10751,7 +10751,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G358" t="n">
-        <v>1.72509443759918</v>
+        <v>1.72509431838989</v>
       </c>
       <c r="H358" t="n">
         <v>175648</v>
@@ -10780,7 +10780,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G359" t="n">
-        <v>1.72064471244812</v>
+        <v>1.72064447402954</v>
       </c>
       <c r="H359" t="n">
         <v>272461</v>
@@ -10809,7 +10809,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G360" t="n">
-        <v>1.69394481182098</v>
+        <v>1.69394493103027</v>
       </c>
       <c r="H360" t="n">
         <v>170179</v>
@@ -10867,7 +10867,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="n">
-        <v>1.68207812309265</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H362" t="n">
         <v>79655</v>
@@ -10954,7 +10954,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G365" t="n">
-        <v>1.70284473896027</v>
+        <v>1.70284485816956</v>
       </c>
       <c r="H365" t="n">
         <v>103563</v>
@@ -11041,7 +11041,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G368" t="n">
-        <v>1.722128033638</v>
+        <v>1.72212779521942</v>
       </c>
       <c r="H368" t="n">
         <v>231003</v>
@@ -11070,7 +11070,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>1.72064471244812</v>
+        <v>1.72064447402954</v>
       </c>
       <c r="H369" t="n">
         <v>90559</v>
@@ -11099,7 +11099,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G370" t="n">
-        <v>1.70136153697968</v>
+        <v>1.70136141777039</v>
       </c>
       <c r="H370" t="n">
         <v>206893</v>
@@ -11128,7 +11128,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G371" t="n">
-        <v>1.70432829856873</v>
+        <v>1.70432817935944</v>
       </c>
       <c r="H371" t="n">
         <v>198744</v>
@@ -11157,7 +11157,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H372" t="n">
         <v>188976</v>
@@ -11186,7 +11186,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G373" t="n">
-        <v>1.68207812309265</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H373" t="n">
         <v>48951</v>
@@ -11244,7 +11244,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G375" t="n">
-        <v>1.74141097068787</v>
+        <v>1.74141120910645</v>
       </c>
       <c r="H375" t="n">
         <v>90743</v>
@@ -11273,7 +11273,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G376" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H376" t="n">
         <v>217080</v>
@@ -11302,7 +11302,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>1.72806119918823</v>
+        <v>1.72806107997894</v>
       </c>
       <c r="H377" t="n">
         <v>254953</v>
@@ -11331,7 +11331,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G378" t="n">
-        <v>1.67762863636017</v>
+        <v>1.67762851715088</v>
       </c>
       <c r="H378" t="n">
         <v>158070</v>
@@ -11389,7 +11389,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H380" t="n">
         <v>147433</v>
@@ -11418,7 +11418,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G381" t="n">
-        <v>1.71916127204895</v>
+        <v>1.71916139125824</v>
       </c>
       <c r="H381" t="n">
         <v>219366</v>
@@ -11476,7 +11476,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G383" t="n">
-        <v>1.72806119918823</v>
+        <v>1.72806107997894</v>
       </c>
       <c r="H383" t="n">
         <v>453984</v>
@@ -11534,7 +11534,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G385" t="n">
-        <v>1.75921058654785</v>
+        <v>1.75921070575714</v>
       </c>
       <c r="H385" t="n">
         <v>177686</v>
@@ -11563,7 +11563,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G386" t="n">
-        <v>1.75921058654785</v>
+        <v>1.75921070575714</v>
       </c>
       <c r="H386" t="n">
         <v>137675</v>
@@ -11592,7 +11592,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G387" t="n">
-        <v>1.73696100711823</v>
+        <v>1.73696112632751</v>
       </c>
       <c r="H387" t="n">
         <v>76021</v>
@@ -11621,7 +11621,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G388" t="n">
-        <v>1.71174466609955</v>
+        <v>1.71174478530884</v>
       </c>
       <c r="H388" t="n">
         <v>51635</v>
@@ -11650,7 +11650,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G389" t="n">
-        <v>1.70284473896027</v>
+        <v>1.70284485816956</v>
       </c>
       <c r="H389" t="n">
         <v>131273</v>
@@ -11679,7 +11679,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G390" t="n">
-        <v>1.69394481182098</v>
+        <v>1.69394493103027</v>
       </c>
       <c r="H390" t="n">
         <v>129919</v>
@@ -11708,7 +11708,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G391" t="n">
-        <v>1.69394481182098</v>
+        <v>1.69394493103027</v>
       </c>
       <c r="H391" t="n">
         <v>160218</v>
@@ -11766,7 +11766,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G393" t="n">
-        <v>1.7147114276886</v>
+        <v>1.71471118927002</v>
       </c>
       <c r="H393" t="n">
         <v>124941</v>
@@ -11795,7 +11795,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G394" t="n">
-        <v>1.70877802371979</v>
+        <v>1.70877814292908</v>
       </c>
       <c r="H394" t="n">
         <v>70335</v>
@@ -11824,7 +11824,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G395" t="n">
-        <v>1.70581126213074</v>
+        <v>1.70581150054932</v>
       </c>
       <c r="H395" t="n">
         <v>79866</v>
@@ -11853,7 +11853,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G396" t="n">
-        <v>1.722128033638</v>
+        <v>1.72212779521942</v>
       </c>
       <c r="H396" t="n">
         <v>119904</v>
@@ -11882,7 +11882,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G397" t="n">
-        <v>1.70136153697968</v>
+        <v>1.70136141777039</v>
       </c>
       <c r="H397" t="n">
         <v>48837</v>
@@ -11940,7 +11940,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G399" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H399" t="n">
         <v>80915</v>
@@ -11969,7 +11969,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G400" t="n">
-        <v>1.68949508666992</v>
+        <v>1.68949520587921</v>
       </c>
       <c r="H400" t="n">
         <v>71969</v>
@@ -11998,7 +11998,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G401" t="n">
-        <v>1.6850448846817</v>
+        <v>1.68504512310028</v>
       </c>
       <c r="H401" t="n">
         <v>265941</v>
@@ -12027,7 +12027,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G402" t="n">
-        <v>1.67762863636017</v>
+        <v>1.67762851715088</v>
       </c>
       <c r="H402" t="n">
         <v>222599</v>
@@ -12085,7 +12085,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H404" t="n">
         <v>193550</v>
@@ -12114,7 +12114,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G405" t="n">
-        <v>1.64351236820221</v>
+        <v>1.6435124874115</v>
       </c>
       <c r="H405" t="n">
         <v>250166</v>
@@ -12143,7 +12143,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G406" t="n">
-        <v>1.63312900066376</v>
+        <v>1.63312888145447</v>
       </c>
       <c r="H406" t="n">
         <v>206183</v>
@@ -12172,7 +12172,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>1.59456276893616</v>
+        <v>1.59456288814545</v>
       </c>
       <c r="H407" t="n">
         <v>284079</v>
@@ -12230,7 +12230,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G409" t="n">
-        <v>1.5915961265564</v>
+        <v>1.59159600734711</v>
       </c>
       <c r="H409" t="n">
         <v>149140</v>
@@ -12288,7 +12288,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G411" t="n">
-        <v>1.68207812309265</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H411" t="n">
         <v>346022</v>
@@ -12317,7 +12317,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H412" t="n">
         <v>177992</v>
@@ -12346,7 +12346,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G413" t="n">
-        <v>1.67762863636017</v>
+        <v>1.67762851715088</v>
       </c>
       <c r="H413" t="n">
         <v>124634</v>
@@ -12404,7 +12404,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G415" t="n">
-        <v>1.67466199398041</v>
+        <v>1.67466175556183</v>
       </c>
       <c r="H415" t="n">
         <v>54025</v>
@@ -12462,7 +12462,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G417" t="n">
-        <v>1.63312900066376</v>
+        <v>1.63312888145447</v>
       </c>
       <c r="H417" t="n">
         <v>163226</v>
@@ -12491,7 +12491,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G418" t="n">
-        <v>1.60346293449402</v>
+        <v>1.60346269607544</v>
       </c>
       <c r="H418" t="n">
         <v>126057</v>
@@ -12520,7 +12520,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G419" t="n">
-        <v>1.60494613647461</v>
+        <v>1.60494601726532</v>
       </c>
       <c r="H419" t="n">
         <v>38787</v>
@@ -12549,7 +12549,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G420" t="n">
-        <v>1.59752953052521</v>
+        <v>1.5975296497345</v>
       </c>
       <c r="H420" t="n">
         <v>72967</v>
@@ -12578,7 +12578,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G421" t="n">
-        <v>1.60791289806366</v>
+        <v>1.60791277885437</v>
       </c>
       <c r="H421" t="n">
         <v>112916</v>
@@ -12607,7 +12607,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G422" t="n">
-        <v>1.60197949409485</v>
+        <v>1.60197961330414</v>
       </c>
       <c r="H422" t="n">
         <v>60149</v>
@@ -12636,7 +12636,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G423" t="n">
-        <v>1.58417963981628</v>
+        <v>1.58417952060699</v>
       </c>
       <c r="H423" t="n">
         <v>39132</v>
@@ -12665,7 +12665,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>1.59456276893616</v>
+        <v>1.59456288814545</v>
       </c>
       <c r="H424" t="n">
         <v>23373</v>
@@ -12694,7 +12694,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G425" t="n">
-        <v>1.57082974910736</v>
+        <v>1.57082986831665</v>
       </c>
       <c r="H425" t="n">
         <v>149172</v>
@@ -12781,7 +12781,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G428" t="n">
-        <v>1.60049605369568</v>
+        <v>1.60049629211426</v>
       </c>
       <c r="H428" t="n">
         <v>74845</v>
@@ -12810,7 +12810,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G429" t="n">
-        <v>1.5915961265564</v>
+        <v>1.59159600734711</v>
       </c>
       <c r="H429" t="n">
         <v>17916</v>
@@ -12839,7 +12839,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G430" t="n">
-        <v>1.58714640140533</v>
+        <v>1.58714628219604</v>
       </c>
       <c r="H430" t="n">
         <v>22813</v>
@@ -12897,7 +12897,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G432" t="n">
-        <v>1.58121311664581</v>
+        <v>1.58121299743652</v>
       </c>
       <c r="H432" t="n">
         <v>24105</v>
@@ -12955,7 +12955,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>1.59456276893616</v>
+        <v>1.59456288814545</v>
       </c>
       <c r="H434" t="n">
         <v>146075</v>
@@ -12984,7 +12984,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G435" t="n">
-        <v>1.5990127325058</v>
+        <v>1.59901285171509</v>
       </c>
       <c r="H435" t="n">
         <v>216836</v>
@@ -13013,7 +13013,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G436" t="n">
-        <v>1.58121311664581</v>
+        <v>1.58121299743652</v>
       </c>
       <c r="H436" t="n">
         <v>116492</v>
@@ -13042,7 +13042,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>1.57231318950653</v>
+        <v>1.57231307029724</v>
       </c>
       <c r="H437" t="n">
         <v>157936</v>
@@ -13071,7 +13071,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G438" t="n">
-        <v>1.56192982196808</v>
+        <v>1.56192994117737</v>
       </c>
       <c r="H438" t="n">
         <v>66146</v>
@@ -13100,7 +13100,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>1.57231318950653</v>
+        <v>1.57231307029724</v>
       </c>
       <c r="H439" t="n">
         <v>118972</v>
@@ -13129,7 +13129,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G440" t="n">
-        <v>1.57231318950653</v>
+        <v>1.57231307029724</v>
       </c>
       <c r="H440" t="n">
         <v>164526</v>
@@ -13216,7 +13216,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G443" t="n">
-        <v>1.57379651069641</v>
+        <v>1.57379639148712</v>
       </c>
       <c r="H443" t="n">
         <v>111995</v>
@@ -13245,7 +13245,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G444" t="n">
-        <v>1.58566308021545</v>
+        <v>1.58566296100616</v>
       </c>
       <c r="H444" t="n">
         <v>225453</v>
@@ -13274,7 +13274,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>1.58714640140533</v>
+        <v>1.58714628219604</v>
       </c>
       <c r="H445" t="n">
         <v>94999</v>
@@ -13448,7 +13448,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>1.72806119918823</v>
+        <v>1.72806107997894</v>
       </c>
       <c r="H451" t="n">
         <v>194974</v>
@@ -13477,7 +13477,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G452" t="n">
-        <v>1.70136153697968</v>
+        <v>1.70136141777039</v>
       </c>
       <c r="H452" t="n">
         <v>187242</v>
@@ -13506,7 +13506,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G453" t="n">
-        <v>1.72509443759918</v>
+        <v>1.72509431838989</v>
       </c>
       <c r="H453" t="n">
         <v>131380</v>
@@ -13535,7 +13535,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G454" t="n">
-        <v>1.70432829856873</v>
+        <v>1.70432817935944</v>
       </c>
       <c r="H454" t="n">
         <v>119732</v>
@@ -13651,7 +13651,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G458" t="n">
-        <v>1.83189308643341</v>
+        <v>1.8318932056427</v>
       </c>
       <c r="H458" t="n">
         <v>603245</v>
@@ -13680,7 +13680,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>1.83930969238281</v>
+        <v>1.8393098115921</v>
       </c>
       <c r="H459" t="n">
         <v>503273</v>
@@ -13709,7 +13709,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G460" t="n">
-        <v>1.93720877170563</v>
+        <v>1.93720841407776</v>
       </c>
       <c r="H460" t="n">
         <v>2102244</v>
@@ -13738,7 +13738,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G461" t="n">
-        <v>1.92089223861694</v>
+        <v>1.92089211940765</v>
       </c>
       <c r="H461" t="n">
         <v>652481</v>
@@ -13767,7 +13767,7 @@
         <v>2.5</v>
       </c>
       <c r="G462" t="n">
-        <v>1.85414302349091</v>
+        <v>1.85414278507233</v>
       </c>
       <c r="H462" t="n">
         <v>565156</v>
@@ -13796,7 +13796,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G463" t="n">
-        <v>1.90605854988098</v>
+        <v>1.90605878829956</v>
       </c>
       <c r="H463" t="n">
         <v>445928</v>
@@ -13825,7 +13825,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.87490940093994</v>
+        <v>1.87490975856781</v>
       </c>
       <c r="H464" t="n">
         <v>236248</v>
@@ -13883,7 +13883,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G466" t="n">
-        <v>1.91199219226837</v>
+        <v>1.91199207305908</v>
       </c>
       <c r="H466" t="n">
         <v>472710</v>
@@ -13941,7 +13941,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G468" t="n">
-        <v>1.92089223861694</v>
+        <v>1.92089211940765</v>
       </c>
       <c r="H468" t="n">
         <v>895874</v>
@@ -13970,7 +13970,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G469" t="n">
-        <v>1.78887689113617</v>
+        <v>1.78887724876404</v>
       </c>
       <c r="H469" t="n">
         <v>1419623</v>
@@ -14057,7 +14057,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G472" t="n">
-        <v>1.78887689113617</v>
+        <v>1.78887724876404</v>
       </c>
       <c r="H472" t="n">
         <v>368047</v>
@@ -14086,7 +14086,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G473" t="n">
-        <v>1.76514399051666</v>
+        <v>1.76514410972595</v>
       </c>
       <c r="H473" t="n">
         <v>234010</v>
@@ -14144,7 +14144,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G475" t="n">
-        <v>1.7072948217392</v>
+        <v>1.70729470252991</v>
       </c>
       <c r="H475" t="n">
         <v>277320</v>
@@ -14173,7 +14173,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G476" t="n">
-        <v>1.66279554367065</v>
+        <v>1.66279542446136</v>
       </c>
       <c r="H476" t="n">
         <v>368436</v>
@@ -14202,7 +14202,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G477" t="n">
-        <v>1.63757908344269</v>
+        <v>1.63757884502411</v>
       </c>
       <c r="H477" t="n">
         <v>345521</v>
@@ -14289,7 +14289,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G480" t="n">
-        <v>1.61829590797424</v>
+        <v>1.61829578876495</v>
       </c>
       <c r="H480" t="n">
         <v>135534</v>
@@ -14318,7 +14318,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G481" t="n">
-        <v>1.60049605369568</v>
+        <v>1.60049629211426</v>
       </c>
       <c r="H481" t="n">
         <v>311351</v>
@@ -14434,7 +14434,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G485" t="n">
-        <v>1.68652820587158</v>
+        <v>1.68652844429016</v>
       </c>
       <c r="H485" t="n">
         <v>204828</v>
@@ -14463,7 +14463,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G486" t="n">
-        <v>1.67021191120148</v>
+        <v>1.67021179199219</v>
       </c>
       <c r="H486" t="n">
         <v>138055</v>
@@ -14492,7 +14492,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G487" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H487" t="n">
         <v>237309</v>
@@ -14521,7 +14521,7 @@
         <v>2.25</v>
       </c>
       <c r="G488" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H488" t="n">
         <v>210721</v>
@@ -14550,7 +14550,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G489" t="n">
-        <v>1.63757908344269</v>
+        <v>1.63757884502411</v>
       </c>
       <c r="H489" t="n">
         <v>137365</v>
@@ -14579,7 +14579,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G490" t="n">
-        <v>1.68207812309265</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H490" t="n">
         <v>107553</v>
@@ -14608,7 +14608,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G491" t="n">
-        <v>1.66724514961243</v>
+        <v>1.66724526882172</v>
       </c>
       <c r="H491" t="n">
         <v>229961</v>
@@ -14695,7 +14695,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G494" t="n">
-        <v>1.68652820587158</v>
+        <v>1.68652844429016</v>
       </c>
       <c r="H494" t="n">
         <v>85401</v>
@@ -14724,7 +14724,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G495" t="n">
-        <v>1.68949508666992</v>
+        <v>1.68949520587921</v>
       </c>
       <c r="H495" t="n">
         <v>157965</v>
@@ -14753,7 +14753,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G496" t="n">
-        <v>1.68949508666992</v>
+        <v>1.68949520587921</v>
       </c>
       <c r="H496" t="n">
         <v>61838</v>
@@ -14782,7 +14782,7 @@
         <v>2.25</v>
       </c>
       <c r="G497" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H497" t="n">
         <v>38866</v>
@@ -14811,7 +14811,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G498" t="n">
-        <v>1.68949508666992</v>
+        <v>1.68949520587921</v>
       </c>
       <c r="H498" t="n">
         <v>94690</v>
@@ -14840,7 +14840,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G499" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H499" t="n">
         <v>46806</v>
@@ -14869,7 +14869,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H500" t="n">
         <v>39718</v>
@@ -14898,7 +14898,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G501" t="n">
-        <v>1.68207812309265</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H501" t="n">
         <v>63302</v>
@@ -14927,7 +14927,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G502" t="n">
-        <v>1.67466199398041</v>
+        <v>1.67466175556183</v>
       </c>
       <c r="H502" t="n">
         <v>96652</v>
@@ -14956,7 +14956,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G503" t="n">
-        <v>1.62867891788483</v>
+        <v>1.62867915630341</v>
       </c>
       <c r="H503" t="n">
         <v>138203</v>
@@ -14985,7 +14985,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G504" t="n">
-        <v>1.66724514961243</v>
+        <v>1.66724526882172</v>
       </c>
       <c r="H504" t="n">
         <v>204470</v>
@@ -15014,7 +15014,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G505" t="n">
-        <v>1.65834534168243</v>
+        <v>1.65834546089172</v>
       </c>
       <c r="H505" t="n">
         <v>60467</v>
@@ -15043,7 +15043,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G506" t="n">
-        <v>1.67169535160065</v>
+        <v>1.67169523239136</v>
       </c>
       <c r="H506" t="n">
         <v>167675</v>
@@ -15072,7 +15072,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H507" t="n">
         <v>86918</v>
@@ -15130,7 +15130,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G509" t="n">
-        <v>1.6850448846817</v>
+        <v>1.68504512310028</v>
       </c>
       <c r="H509" t="n">
         <v>87281</v>
@@ -15159,7 +15159,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G510" t="n">
-        <v>1.69542813301086</v>
+        <v>1.69542837142944</v>
       </c>
       <c r="H510" t="n">
         <v>38185</v>
@@ -15188,7 +15188,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G511" t="n">
-        <v>1.68207812309265</v>
+        <v>1.68207824230194</v>
       </c>
       <c r="H511" t="n">
         <v>59713</v>
@@ -15217,7 +15217,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G512" t="n">
-        <v>1.67466199398041</v>
+        <v>1.67466175556183</v>
       </c>
       <c r="H512" t="n">
         <v>92185</v>
@@ -15246,7 +15246,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G513" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H513" t="n">
         <v>126057</v>
@@ -15275,7 +15275,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G514" t="n">
-        <v>1.67985355854034</v>
+        <v>1.67985343933105</v>
       </c>
       <c r="H514" t="n">
         <v>370861</v>
@@ -15304,7 +15304,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H515" t="n">
         <v>86940</v>
@@ -15333,7 +15333,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G516" t="n">
-        <v>1.70581126213074</v>
+        <v>1.70581150054932</v>
       </c>
       <c r="H516" t="n">
         <v>353654</v>
@@ -15449,7 +15449,7 @@
         <v>2.375</v>
       </c>
       <c r="G520" t="n">
-        <v>1.7614358663559</v>
+        <v>1.76143562793732</v>
       </c>
       <c r="H520" t="n">
         <v>189064</v>
@@ -15507,7 +15507,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76514399051666</v>
+        <v>1.76514410972595</v>
       </c>
       <c r="H522" t="n">
         <v>155399</v>
@@ -15652,7 +15652,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G527" t="n">
-        <v>1.78739392757416</v>
+        <v>1.78739380836487</v>
       </c>
       <c r="H527" t="n">
         <v>134301</v>
@@ -15913,7 +15913,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G536" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H536" t="n">
         <v>188147</v>
@@ -15971,7 +15971,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G538" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H538" t="n">
         <v>123991</v>
@@ -16000,7 +16000,7 @@
         <v>2.25</v>
       </c>
       <c r="G539" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H539" t="n">
         <v>227153</v>
@@ -16087,7 +16087,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G542" t="n">
-        <v>1.62052094936371</v>
+        <v>1.62052083015442</v>
       </c>
       <c r="H542" t="n">
         <v>134309</v>
@@ -16116,7 +16116,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>1.63906240463257</v>
+        <v>1.63906216621399</v>
       </c>
       <c r="H543" t="n">
         <v>116471</v>
@@ -16174,7 +16174,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G545" t="n">
-        <v>1.69468677043915</v>
+        <v>1.69468665122986</v>
       </c>
       <c r="H545" t="n">
         <v>84820</v>
@@ -16203,7 +16203,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G546" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H546" t="n">
         <v>105820</v>
@@ -16232,7 +16232,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G547" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243695259094</v>
       </c>
       <c r="H547" t="n">
         <v>42067</v>
@@ -16261,7 +16261,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G548" t="n">
-        <v>1.64277040958405</v>
+        <v>1.64277052879333</v>
       </c>
       <c r="H548" t="n">
         <v>197621</v>
@@ -16290,7 +16290,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G549" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H549" t="n">
         <v>103175</v>
@@ -16348,7 +16348,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G551" t="n">
-        <v>1.65760385990143</v>
+        <v>1.65760374069214</v>
       </c>
       <c r="H551" t="n">
         <v>53538</v>
@@ -16406,7 +16406,7 @@
         <v>2.25</v>
       </c>
       <c r="G553" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H553" t="n">
         <v>51958</v>
@@ -16435,7 +16435,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G554" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H554" t="n">
         <v>91123</v>
@@ -16464,7 +16464,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>1.65018701553345</v>
+        <v>1.65018725395203</v>
       </c>
       <c r="H555" t="n">
         <v>131578</v>
@@ -16493,7 +16493,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G556" t="n">
-        <v>1.63535380363464</v>
+        <v>1.63535404205322</v>
       </c>
       <c r="H556" t="n">
         <v>62408</v>
@@ -16522,7 +16522,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>1.63535380363464</v>
+        <v>1.63535404205322</v>
       </c>
       <c r="H557" t="n">
         <v>136348</v>
@@ -16580,7 +16580,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G559" t="n">
-        <v>1.64647889137268</v>
+        <v>1.64647901058197</v>
       </c>
       <c r="H559" t="n">
         <v>177477</v>
@@ -16609,7 +16609,7 @@
         <v>2.25</v>
       </c>
       <c r="G560" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H560" t="n">
         <v>115020</v>
@@ -16638,7 +16638,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G561" t="n">
-        <v>1.69468677043915</v>
+        <v>1.69468665122986</v>
       </c>
       <c r="H561" t="n">
         <v>213139</v>
@@ -16725,7 +16725,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G564" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243695259094</v>
       </c>
       <c r="H564" t="n">
         <v>92132</v>
@@ -16754,7 +16754,7 @@
         <v>2.25</v>
       </c>
       <c r="G565" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H565" t="n">
         <v>24724</v>
@@ -16783,7 +16783,7 @@
         <v>2.25</v>
       </c>
       <c r="G566" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H566" t="n">
         <v>45436</v>
@@ -16812,7 +16812,7 @@
         <v>2.25</v>
       </c>
       <c r="G567" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H567" t="n">
         <v>88183</v>
@@ -16841,7 +16841,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G568" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243695259094</v>
       </c>
       <c r="H568" t="n">
         <v>121619</v>
@@ -16870,7 +16870,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>1.63906240463257</v>
+        <v>1.63906216621399</v>
       </c>
       <c r="H569" t="n">
         <v>135132</v>
@@ -16899,7 +16899,7 @@
         <v>2.25</v>
       </c>
       <c r="G570" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H570" t="n">
         <v>127501</v>
@@ -16928,7 +16928,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G571" t="n">
-        <v>1.64647889137268</v>
+        <v>1.64647901058197</v>
       </c>
       <c r="H571" t="n">
         <v>119800</v>
@@ -16957,7 +16957,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G572" t="n">
-        <v>1.65760385990143</v>
+        <v>1.65760374069214</v>
       </c>
       <c r="H572" t="n">
         <v>54138</v>
@@ -16986,7 +16986,7 @@
         <v>2.25</v>
       </c>
       <c r="G573" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H573" t="n">
         <v>90720</v>
@@ -17044,7 +17044,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G575" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243695259094</v>
       </c>
       <c r="H575" t="n">
         <v>195222</v>
@@ -17073,7 +17073,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G576" t="n">
-        <v>1.64647889137268</v>
+        <v>1.64647901058197</v>
       </c>
       <c r="H576" t="n">
         <v>179332</v>
@@ -17102,7 +17102,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G577" t="n">
-        <v>1.67985355854034</v>
+        <v>1.67985343933105</v>
       </c>
       <c r="H577" t="n">
         <v>132861</v>
@@ -17131,7 +17131,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>1.68727004528046</v>
+        <v>1.68727016448975</v>
       </c>
       <c r="H578" t="n">
         <v>117418</v>
@@ -17160,7 +17160,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>1.70210313796997</v>
+        <v>1.70210337638855</v>
       </c>
       <c r="H579" t="n">
         <v>132014</v>
@@ -17247,7 +17247,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H582" t="n">
         <v>194562</v>
@@ -17276,7 +17276,7 @@
         <v>2.25</v>
       </c>
       <c r="G583" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H583" t="n">
         <v>156131</v>
@@ -17305,7 +17305,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G584" t="n">
-        <v>1.67243683338165</v>
+        <v>1.67243695259094</v>
       </c>
       <c r="H584" t="n">
         <v>64753</v>
@@ -17334,7 +17334,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>1.68356168270111</v>
+        <v>1.68356156349182</v>
       </c>
       <c r="H585" t="n">
         <v>250373</v>
@@ -17363,7 +17363,7 @@
         <v>2.25</v>
       </c>
       <c r="G586" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H586" t="n">
         <v>258292</v>
@@ -17392,7 +17392,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G587" t="n">
-        <v>1.64647889137268</v>
+        <v>1.64647901058197</v>
       </c>
       <c r="H587" t="n">
         <v>218687</v>
@@ -17479,7 +17479,7 @@
         <v>2.25</v>
       </c>
       <c r="G590" t="n">
-        <v>1.6687285900116</v>
+        <v>1.66872847080231</v>
       </c>
       <c r="H590" t="n">
         <v>102536</v>
@@ -17595,7 +17595,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G594" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H594" t="n">
         <v>78442</v>
@@ -17624,7 +17624,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>1.70581126213074</v>
+        <v>1.70581150054932</v>
       </c>
       <c r="H595" t="n">
         <v>176901</v>
@@ -17653,7 +17653,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G596" t="n">
-        <v>1.69468677043915</v>
+        <v>1.69468665122986</v>
       </c>
       <c r="H596" t="n">
         <v>284640</v>
@@ -17682,7 +17682,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>1.70210313796997</v>
+        <v>1.70210337638855</v>
       </c>
       <c r="H597" t="n">
         <v>185509</v>
@@ -17769,7 +17769,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G600" t="n">
-        <v>1.7414003610611</v>
+        <v>1.74140024185181</v>
       </c>
       <c r="H600" t="n">
         <v>160604</v>
@@ -17856,7 +17856,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>1.70287370681763</v>
+        <v>1.70287358760834</v>
       </c>
       <c r="H603" t="n">
         <v>264105</v>
@@ -17914,7 +17914,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G605" t="n">
-        <v>1.62967312335968</v>
+        <v>1.62967336177826</v>
       </c>
       <c r="H605" t="n">
         <v>582733</v>
@@ -17943,7 +17943,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G606" t="n">
-        <v>1.64893674850464</v>
+        <v>1.64893662929535</v>
       </c>
       <c r="H606" t="n">
         <v>281947</v>
@@ -17972,7 +17972,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G607" t="n">
-        <v>1.5526202917099</v>
+        <v>1.55262017250061</v>
       </c>
       <c r="H607" t="n">
         <v>737184</v>
@@ -18001,7 +18001,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G608" t="n">
-        <v>1.5526202917099</v>
+        <v>1.55262017250061</v>
       </c>
       <c r="H608" t="n">
         <v>471725</v>
@@ -18030,7 +18030,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G609" t="n">
-        <v>1.49791252613068</v>
+        <v>1.49791240692139</v>
       </c>
       <c r="H609" t="n">
         <v>541620</v>
@@ -18117,7 +18117,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G612" t="n">
-        <v>1.52102828025818</v>
+        <v>1.52102839946747</v>
       </c>
       <c r="H612" t="n">
         <v>204512</v>
@@ -18175,7 +18175,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G614" t="n">
-        <v>1.47171449661255</v>
+        <v>1.47171437740326</v>
       </c>
       <c r="H614" t="n">
         <v>573449</v>
@@ -18204,7 +18204,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G615" t="n">
-        <v>1.51024103164673</v>
+        <v>1.51024115085602</v>
       </c>
       <c r="H615" t="n">
         <v>203705</v>
@@ -18291,7 +18291,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G618" t="n">
-        <v>1.49791252613068</v>
+        <v>1.49791240692139</v>
       </c>
       <c r="H618" t="n">
         <v>153249</v>
@@ -18320,7 +18320,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G619" t="n">
-        <v>1.49174821376801</v>
+        <v>1.49174809455872</v>
       </c>
       <c r="H619" t="n">
         <v>204025</v>
@@ -18349,7 +18349,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G620" t="n">
-        <v>1.57958889007568</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H620" t="n">
         <v>1438144</v>
@@ -18436,7 +18436,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G623" t="n">
-        <v>1.57958889007568</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H623" t="n">
         <v>134903</v>
@@ -18581,7 +18581,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G628" t="n">
-        <v>1.57958889007568</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H628" t="n">
         <v>92826</v>
@@ -18610,7 +18610,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>1.59114694595337</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H629" t="n">
         <v>167995</v>
@@ -18639,7 +18639,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G630" t="n">
-        <v>1.57958889007568</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H630" t="n">
         <v>236416</v>
@@ -18668,7 +18668,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.65664196014404</v>
+        <v>1.65664184093475</v>
       </c>
       <c r="H631" t="n">
         <v>549717</v>
@@ -18726,7 +18726,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>1.6027045249939</v>
+        <v>1.60270464420319</v>
       </c>
       <c r="H633" t="n">
         <v>85820</v>
@@ -18900,7 +18900,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>1.58729386329651</v>
+        <v>1.5872939825058</v>
       </c>
       <c r="H639" t="n">
         <v>207577</v>
@@ -18958,7 +18958,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G641" t="n">
-        <v>1.58729386329651</v>
+        <v>1.5872939825058</v>
       </c>
       <c r="H641" t="n">
         <v>51370</v>
@@ -19132,7 +19132,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>1.60655736923218</v>
+        <v>1.60655748844147</v>
       </c>
       <c r="H647" t="n">
         <v>66972</v>
@@ -19219,7 +19219,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G650" t="n">
-        <v>1.57958889007568</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H650" t="n">
         <v>174966</v>
@@ -19248,7 +19248,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G651" t="n">
-        <v>1.57958889007568</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H651" t="n">
         <v>55715</v>
@@ -19277,7 +19277,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G652" t="n">
-        <v>1.57958889007568</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H652" t="n">
         <v>48077</v>
@@ -19364,7 +19364,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G655" t="n">
-        <v>1.59114694595337</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H655" t="n">
         <v>135733</v>
@@ -19422,7 +19422,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G657" t="n">
-        <v>1.62967312335968</v>
+        <v>1.62967336177826</v>
       </c>
       <c r="H657" t="n">
         <v>246235</v>
@@ -19538,7 +19538,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G661" t="n">
-        <v>1.59114694595337</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H661" t="n">
         <v>97105</v>
@@ -19567,7 +19567,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G662" t="n">
-        <v>1.59114694595337</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H662" t="n">
         <v>169428</v>
@@ -19596,7 +19596,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G663" t="n">
-        <v>1.57958889007568</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H663" t="n">
         <v>51749</v>
@@ -19654,7 +19654,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G665" t="n">
-        <v>1.58729386329651</v>
+        <v>1.5872939825058</v>
       </c>
       <c r="H665" t="n">
         <v>22720</v>
@@ -19770,7 +19770,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G669" t="n">
-        <v>1.54876756668091</v>
+        <v>1.54876744747162</v>
       </c>
       <c r="H669" t="n">
         <v>82171</v>
@@ -19799,7 +19799,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G670" t="n">
-        <v>1.54491496086121</v>
+        <v>1.54491484165192</v>
       </c>
       <c r="H670" t="n">
         <v>132245</v>
@@ -19857,7 +19857,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G672" t="n">
-        <v>1.52102828025818</v>
+        <v>1.52102839946747</v>
       </c>
       <c r="H672" t="n">
         <v>33416</v>
@@ -19915,7 +19915,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G674" t="n">
-        <v>1.5526202917099</v>
+        <v>1.55262017250061</v>
       </c>
       <c r="H674" t="n">
         <v>17422</v>
@@ -19973,7 +19973,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G676" t="n">
-        <v>1.58729386329651</v>
+        <v>1.5872939825058</v>
       </c>
       <c r="H676" t="n">
         <v>89787</v>
@@ -20089,7 +20089,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G680" t="n">
-        <v>1.54491496086121</v>
+        <v>1.54491484165192</v>
       </c>
       <c r="H680" t="n">
         <v>24130</v>
@@ -20147,7 +20147,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G682" t="n">
-        <v>1.54876756668091</v>
+        <v>1.54876744747162</v>
       </c>
       <c r="H682" t="n">
         <v>33294</v>
@@ -20234,7 +20234,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G685" t="n">
-        <v>1.59114694595337</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H685" t="n">
         <v>24270</v>
@@ -20263,7 +20263,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G686" t="n">
-        <v>1.54491496086121</v>
+        <v>1.54491484165192</v>
       </c>
       <c r="H686" t="n">
         <v>39065</v>
@@ -20292,7 +20292,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G687" t="n">
-        <v>1.57958889007568</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H687" t="n">
         <v>85226</v>
@@ -20524,7 +20524,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G695" t="n">
-        <v>1.57958889007568</v>
+        <v>1.57958877086639</v>
       </c>
       <c r="H695" t="n">
         <v>221005</v>
@@ -20553,7 +20553,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G696" t="n">
-        <v>1.58729386329651</v>
+        <v>1.5872939825058</v>
       </c>
       <c r="H696" t="n">
         <v>172666</v>
@@ -20582,7 +20582,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G697" t="n">
-        <v>1.59114694595337</v>
+        <v>1.59114682674408</v>
       </c>
       <c r="H697" t="n">
         <v>34635</v>
@@ -20669,7 +20669,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>1.65664196014404</v>
+        <v>1.65664184093475</v>
       </c>
       <c r="H700" t="n">
         <v>338735</v>
@@ -20756,7 +20756,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>1.54876756668091</v>
+        <v>1.54876744747162</v>
       </c>
       <c r="H703" t="n">
         <v>182516</v>
@@ -20785,7 +20785,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G704" t="n">
-        <v>1.5526202917099</v>
+        <v>1.55262017250061</v>
       </c>
       <c r="H704" t="n">
         <v>71375</v>
@@ -20901,7 +20901,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G708" t="n">
-        <v>1.49328935146332</v>
+        <v>1.49328923225403</v>
       </c>
       <c r="H708" t="n">
         <v>72542</v>
@@ -21017,7 +21017,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G712" t="n">
-        <v>1.41777718067169</v>
+        <v>1.41777729988098</v>
       </c>
       <c r="H712" t="n">
         <v>50778</v>
@@ -21075,7 +21075,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G714" t="n">
-        <v>1.42394149303436</v>
+        <v>1.42394161224365</v>
       </c>
       <c r="H714" t="n">
         <v>163026</v>
@@ -21104,7 +21104,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G715" t="n">
-        <v>1.44089317321777</v>
+        <v>1.44089329242706</v>
       </c>
       <c r="H715" t="n">
         <v>232230</v>
@@ -21133,7 +21133,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G716" t="n">
-        <v>1.39157903194427</v>
+        <v>1.39157915115356</v>
       </c>
       <c r="H716" t="n">
         <v>274472</v>
@@ -21191,7 +21191,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G718" t="n">
-        <v>1.25442481040955</v>
+        <v>1.25442457199097</v>
       </c>
       <c r="H718" t="n">
         <v>335970</v>
@@ -21249,7 +21249,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G720" t="n">
-        <v>1.25288355350494</v>
+        <v>1.25288367271423</v>
       </c>
       <c r="H720" t="n">
         <v>135997</v>
@@ -21307,7 +21307,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G722" t="n">
-        <v>1.29911553859711</v>
+        <v>1.29911541938782</v>
       </c>
       <c r="H722" t="n">
         <v>102885</v>
@@ -21336,7 +21336,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G723" t="n">
-        <v>1.31606709957123</v>
+        <v>1.31606698036194</v>
       </c>
       <c r="H723" t="n">
         <v>139138</v>
@@ -21365,7 +21365,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G724" t="n">
-        <v>1.29449212551117</v>
+        <v>1.29449224472046</v>
       </c>
       <c r="H724" t="n">
         <v>181223</v>
@@ -21394,7 +21394,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G725" t="n">
-        <v>1.30990278720856</v>
+        <v>1.30990290641785</v>
       </c>
       <c r="H725" t="n">
         <v>93287</v>
@@ -21423,7 +21423,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G726" t="n">
-        <v>1.31144404411316</v>
+        <v>1.31144392490387</v>
       </c>
       <c r="H726" t="n">
         <v>164730</v>
@@ -21452,7 +21452,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G727" t="n">
-        <v>1.29295122623444</v>
+        <v>1.29295110702515</v>
       </c>
       <c r="H727" t="n">
         <v>104518</v>
@@ -21481,7 +21481,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G728" t="n">
-        <v>1.29911553859711</v>
+        <v>1.29911541938782</v>
       </c>
       <c r="H728" t="n">
         <v>54482</v>
@@ -21510,7 +21510,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G729" t="n">
-        <v>1.31144404411316</v>
+        <v>1.31144392490387</v>
       </c>
       <c r="H729" t="n">
         <v>142990</v>
@@ -21539,7 +21539,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G730" t="n">
-        <v>1.30682063102722</v>
+        <v>1.30682075023651</v>
       </c>
       <c r="H730" t="n">
         <v>83714</v>
@@ -21597,7 +21597,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G732" t="n">
-        <v>1.28370475769043</v>
+        <v>1.28370487689972</v>
       </c>
       <c r="H732" t="n">
         <v>140675</v>
@@ -21626,7 +21626,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G733" t="n">
-        <v>1.28062260150909</v>
+        <v>1.28062272071838</v>
       </c>
       <c r="H733" t="n">
         <v>88818</v>
@@ -21684,7 +21684,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G735" t="n">
-        <v>1.18353569507599</v>
+        <v>1.18353581428528</v>
       </c>
       <c r="H735" t="n">
         <v>196589</v>
@@ -21771,7 +21771,7 @@
         <v>1.5460000038147</v>
       </c>
       <c r="G738" t="n">
-        <v>1.19124114513397</v>
+        <v>1.19124102592468</v>
       </c>
       <c r="H738" t="n">
         <v>130239</v>
@@ -21858,7 +21858,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G741" t="n">
-        <v>1.13113975524902</v>
+        <v>1.13113963603973</v>
       </c>
       <c r="H741" t="n">
         <v>295344</v>
@@ -21916,7 +21916,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G743" t="n">
-        <v>1.22976756095886</v>
+        <v>1.22976768016815</v>
       </c>
       <c r="H743" t="n">
         <v>288308</v>
@@ -21945,7 +21945,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G744" t="n">
-        <v>1.24980139732361</v>
+        <v>1.2498015165329</v>
       </c>
       <c r="H744" t="n">
         <v>234143</v>
@@ -22032,7 +22032,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G747" t="n">
-        <v>1.24055504798889</v>
+        <v>1.24055516719818</v>
       </c>
       <c r="H747" t="n">
         <v>219161</v>
@@ -22061,7 +22061,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G748" t="n">
-        <v>1.23593199253082</v>
+        <v>1.23593175411224</v>
       </c>
       <c r="H748" t="n">
         <v>167356</v>
@@ -22090,7 +22090,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G749" t="n">
-        <v>1.27908158302307</v>
+        <v>1.27908170223236</v>
       </c>
       <c r="H749" t="n">
         <v>271833</v>
@@ -22206,7 +22206,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G753" t="n">
-        <v>1.20665156841278</v>
+        <v>1.20665168762207</v>
       </c>
       <c r="H753" t="n">
         <v>86354</v>
@@ -22235,7 +22235,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G754" t="n">
-        <v>1.18045353889465</v>
+        <v>1.18045365810394</v>
       </c>
       <c r="H754" t="n">
         <v>351221</v>
@@ -22293,7 +22293,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G756" t="n">
-        <v>1.15733778476715</v>
+        <v>1.15733790397644</v>
       </c>
       <c r="H756" t="n">
         <v>162573</v>
@@ -22322,7 +22322,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G757" t="n">
-        <v>1.1203521490097</v>
+        <v>1.12035226821899</v>
       </c>
       <c r="H757" t="n">
         <v>278030</v>
@@ -22467,7 +22467,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G762" t="n">
-        <v>1.08182561397552</v>
+        <v>1.08182573318481</v>
       </c>
       <c r="H762" t="n">
         <v>82993</v>
@@ -22554,7 +22554,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G765" t="n">
-        <v>1.13576281070709</v>
+        <v>1.13576292991638</v>
       </c>
       <c r="H765" t="n">
         <v>224273</v>
@@ -22583,7 +22583,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G766" t="n">
-        <v>1.15733778476715</v>
+        <v>1.15733790397644</v>
       </c>
       <c r="H766" t="n">
         <v>124400</v>
@@ -22786,7 +22786,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G773" t="n">
-        <v>1.11727023124695</v>
+        <v>1.11727011203766</v>
       </c>
       <c r="H773" t="n">
         <v>94346</v>
@@ -22815,7 +22815,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G774" t="n">
-        <v>1.14346814155579</v>
+        <v>1.14346826076508</v>
       </c>
       <c r="H774" t="n">
         <v>64915</v>
@@ -22844,7 +22844,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G775" t="n">
-        <v>1.14655041694641</v>
+        <v>1.14655029773712</v>
       </c>
       <c r="H775" t="n">
         <v>29031</v>
@@ -22931,7 +22931,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G778" t="n">
-        <v>1.14655041694641</v>
+        <v>1.14655029773712</v>
       </c>
       <c r="H778" t="n">
         <v>100543</v>
@@ -23047,7 +23047,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G782" t="n">
-        <v>1.12651634216309</v>
+        <v>1.12651646137238</v>
       </c>
       <c r="H782" t="n">
         <v>241489</v>
@@ -23192,7 +23192,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G787" t="n">
-        <v>1.06641495227814</v>
+        <v>1.06641507148743</v>
       </c>
       <c r="H787" t="n">
         <v>298141</v>
@@ -23221,7 +23221,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G788" t="n">
-        <v>1.06641495227814</v>
+        <v>1.06641507148743</v>
       </c>
       <c r="H788" t="n">
         <v>548530</v>
@@ -23250,7 +23250,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G789" t="n">
-        <v>1.13884484767914</v>
+        <v>1.13884496688843</v>
       </c>
       <c r="H789" t="n">
         <v>460325</v>
@@ -23395,7 +23395,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G794" t="n">
-        <v>1.18507695198059</v>
+        <v>1.1850768327713</v>
       </c>
       <c r="H794" t="n">
         <v>357330</v>
@@ -23511,7 +23511,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G798" t="n">
-        <v>1.23593199253082</v>
+        <v>1.23593175411224</v>
       </c>
       <c r="H798" t="n">
         <v>460843</v>
@@ -23598,7 +23598,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G801" t="n">
-        <v>1.24055504798889</v>
+        <v>1.24055516719818</v>
       </c>
       <c r="H801" t="n">
         <v>270293</v>
@@ -23627,7 +23627,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G802" t="n">
-        <v>1.23439085483551</v>
+        <v>1.23439073562622</v>
       </c>
       <c r="H802" t="n">
         <v>274299</v>
@@ -23656,7 +23656,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G803" t="n">
-        <v>1.23439085483551</v>
+        <v>1.23439073562622</v>
       </c>
       <c r="H803" t="n">
         <v>192033</v>
@@ -23772,7 +23772,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G807" t="n">
-        <v>1.28524577617645</v>
+        <v>1.28524589538574</v>
       </c>
       <c r="H807" t="n">
         <v>453263</v>
@@ -23859,7 +23859,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G810" t="n">
-        <v>1.24055504798889</v>
+        <v>1.24055516719818</v>
       </c>
       <c r="H810" t="n">
         <v>527865</v>
@@ -23917,7 +23917,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G812" t="n">
-        <v>1.18199479579926</v>
+        <v>1.18199467658997</v>
       </c>
       <c r="H812" t="n">
         <v>368691</v>
@@ -23946,7 +23946,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G813" t="n">
-        <v>1.16504287719727</v>
+        <v>1.16504299640656</v>
       </c>
       <c r="H813" t="n">
         <v>362093</v>
@@ -23975,7 +23975,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G814" t="n">
-        <v>1.16504287719727</v>
+        <v>1.16504299640656</v>
       </c>
       <c r="H814" t="n">
         <v>258614</v>
@@ -24091,7 +24091,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G818" t="n">
-        <v>1.16504287719727</v>
+        <v>1.16504299640656</v>
       </c>
       <c r="H818" t="n">
         <v>438666</v>
@@ -24178,7 +24178,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G821" t="n">
-        <v>1.13576281070709</v>
+        <v>1.13576292991638</v>
       </c>
       <c r="H821" t="n">
         <v>558347</v>
@@ -24439,7 +24439,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G830" t="n">
-        <v>1.15733778476715</v>
+        <v>1.15733790397644</v>
       </c>
       <c r="H830" t="n">
         <v>184987</v>
@@ -24555,7 +24555,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G834" t="n">
-        <v>1.19586420059204</v>
+        <v>1.19586431980133</v>
       </c>
       <c r="H834" t="n">
         <v>1197779</v>
@@ -24584,7 +24584,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G835" t="n">
-        <v>1.26367092132568</v>
+        <v>1.26367104053497</v>
       </c>
       <c r="H835" t="n">
         <v>1706082</v>
@@ -24613,7 +24613,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G836" t="n">
-        <v>1.27908158302307</v>
+        <v>1.27908170223236</v>
       </c>
       <c r="H836" t="n">
         <v>1019190</v>
@@ -24642,7 +24642,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G837" t="n">
-        <v>1.29295122623444</v>
+        <v>1.29295110702515</v>
       </c>
       <c r="H837" t="n">
         <v>436363</v>
@@ -24729,7 +24729,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G840" t="n">
-        <v>1.29295122623444</v>
+        <v>1.29295110702515</v>
       </c>
       <c r="H840" t="n">
         <v>451183</v>
@@ -24787,7 +24787,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G842" t="n">
-        <v>1.26367092132568</v>
+        <v>1.26367104053497</v>
       </c>
       <c r="H842" t="n">
         <v>494881</v>
@@ -24845,7 +24845,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G844" t="n">
-        <v>1.28062260150909</v>
+        <v>1.28062272071838</v>
       </c>
       <c r="H844" t="n">
         <v>217625</v>
@@ -24874,7 +24874,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G845" t="n">
-        <v>1.28832817077637</v>
+        <v>1.28832793235779</v>
       </c>
       <c r="H845" t="n">
         <v>316477</v>
@@ -24932,7 +24932,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G847" t="n">
-        <v>1.2898690700531</v>
+        <v>1.28986895084381</v>
       </c>
       <c r="H847" t="n">
         <v>239893</v>
@@ -24961,7 +24961,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G848" t="n">
-        <v>1.33944809436798</v>
+        <v>1.33944821357727</v>
       </c>
       <c r="H848" t="n">
         <v>524876</v>
@@ -25019,7 +25019,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G850" t="n">
-        <v>1.26629853248596</v>
+        <v>1.26629865169525</v>
       </c>
       <c r="H850" t="n">
         <v>401129</v>
@@ -25048,7 +25048,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G851" t="n">
-        <v>1.24029004573822</v>
+        <v>1.24028992652893</v>
       </c>
       <c r="H851" t="n">
         <v>347713</v>
@@ -25077,7 +25077,7 @@
         <v>1.5</v>
       </c>
       <c r="G852" t="n">
-        <v>1.21915793418884</v>
+        <v>1.21915781497955</v>
       </c>
       <c r="H852" t="n">
         <v>543361</v>
@@ -25106,7 +25106,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G853" t="n">
-        <v>1.22240900993347</v>
+        <v>1.22240889072418</v>
       </c>
       <c r="H853" t="n">
         <v>572722</v>
@@ -25222,7 +25222,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G857" t="n">
-        <v>1.12162518501282</v>
+        <v>1.12162530422211</v>
       </c>
       <c r="H857" t="n">
         <v>623116</v>
@@ -25280,7 +25280,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G859" t="n">
-        <v>1.0842376947403</v>
+        <v>1.08423781394958</v>
       </c>
       <c r="H859" t="n">
         <v>412400</v>
@@ -25367,7 +25367,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G862" t="n">
-        <v>1.06473124027252</v>
+        <v>1.06473112106323</v>
       </c>
       <c r="H862" t="n">
         <v>258029</v>
@@ -25396,7 +25396,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G863" t="n">
-        <v>1.06960773468018</v>
+        <v>1.06960785388947</v>
       </c>
       <c r="H863" t="n">
         <v>233484</v>
@@ -25425,7 +25425,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G864" t="n">
-        <v>1.07285904884338</v>
+        <v>1.07285892963409</v>
       </c>
       <c r="H864" t="n">
         <v>330557</v>
@@ -25454,7 +25454,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G865" t="n">
-        <v>1.05010151863098</v>
+        <v>1.05010139942169</v>
       </c>
       <c r="H865" t="n">
         <v>592655</v>
@@ -25541,7 +25541,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G868" t="n">
-        <v>1.00458610057831</v>
+        <v>1.00458598136902</v>
       </c>
       <c r="H868" t="n">
         <v>281715</v>
@@ -25570,7 +25570,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G869" t="n">
-        <v>1.01271378993988</v>
+        <v>1.01271390914917</v>
       </c>
       <c r="H869" t="n">
         <v>559963</v>
@@ -25686,7 +25686,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G873" t="n">
-        <v>0.967198491096497</v>
+        <v>0.967198610305786</v>
       </c>
       <c r="H873" t="n">
         <v>284283</v>
@@ -25715,7 +25715,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G874" t="n">
-        <v>0.972075343132019</v>
+        <v>0.972075164318085</v>
       </c>
       <c r="H874" t="n">
         <v>257772</v>
@@ -25773,7 +25773,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G876" t="n">
-        <v>0.936313211917877</v>
+        <v>0.936313152313232</v>
       </c>
       <c r="H876" t="n">
         <v>358839</v>
@@ -25831,7 +25831,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>0.910304546356201</v>
+        <v>0.910304605960846</v>
       </c>
       <c r="H878" t="n">
         <v>168578</v>
@@ -25860,7 +25860,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G879" t="n">
-        <v>0.92818558216095</v>
+        <v>0.928185522556305</v>
       </c>
       <c r="H879" t="n">
         <v>313401</v>
@@ -25889,7 +25889,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G880" t="n">
-        <v>0.924934506416321</v>
+        <v>0.924934387207031</v>
       </c>
       <c r="H880" t="n">
         <v>487227</v>
@@ -25918,7 +25918,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G881" t="n">
-        <v>0.936313211917877</v>
+        <v>0.936313152313232</v>
       </c>
       <c r="H881" t="n">
         <v>449953</v>
@@ -25947,7 +25947,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G882" t="n">
-        <v>0.950943052768707</v>
+        <v>0.950943112373352</v>
       </c>
       <c r="H882" t="n">
         <v>558073</v>
@@ -26005,7 +26005,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G884" t="n">
-        <v>0.93956446647644</v>
+        <v>0.939564347267151</v>
       </c>
       <c r="H884" t="n">
         <v>221097</v>
@@ -26208,7 +26208,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G891" t="n">
-        <v>0.988330721855164</v>
+        <v>0.988330602645874</v>
       </c>
       <c r="H891" t="n">
         <v>484607</v>
@@ -26324,7 +26324,7 @@
         <v>1.25</v>
       </c>
       <c r="G895" t="n">
-        <v>1.01596486568451</v>
+        <v>1.0159649848938</v>
       </c>
       <c r="H895" t="n">
         <v>383692</v>
@@ -26382,7 +26382,7 @@
         <v>1.25</v>
       </c>
       <c r="G897" t="n">
-        <v>1.01596486568451</v>
+        <v>1.0159649848938</v>
       </c>
       <c r="H897" t="n">
         <v>304521</v>
@@ -26411,7 +26411,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G898" t="n">
-        <v>1.01271378993988</v>
+        <v>1.01271390914917</v>
       </c>
       <c r="H898" t="n">
         <v>139963</v>
@@ -26469,7 +26469,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G900" t="n">
-        <v>0.994832813739777</v>
+        <v>0.994832873344421</v>
       </c>
       <c r="H900" t="n">
         <v>266551</v>
@@ -26498,7 +26498,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G901" t="n">
-        <v>0.981828331947327</v>
+        <v>0.981828451156616</v>
       </c>
       <c r="H901" t="n">
         <v>152179</v>
@@ -26527,7 +26527,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G902" t="n">
-        <v>1.01271378993988</v>
+        <v>1.01271390914917</v>
       </c>
       <c r="H902" t="n">
         <v>531062</v>
@@ -26556,7 +26556,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G903" t="n">
-        <v>0.991581737995148</v>
+        <v>0.991581797599792</v>
       </c>
       <c r="H903" t="n">
         <v>267724</v>
@@ -26730,7 +26730,7 @@
         <v>1.25</v>
       </c>
       <c r="G909" t="n">
-        <v>1.01596486568451</v>
+        <v>1.0159649848938</v>
       </c>
       <c r="H909" t="n">
         <v>880947</v>
@@ -26788,7 +26788,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G911" t="n">
-        <v>1.01759052276611</v>
+        <v>1.01759040355682</v>
       </c>
       <c r="H911" t="n">
         <v>242367</v>
@@ -27020,7 +27020,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>0.950943052768707</v>
+        <v>0.950943112373352</v>
       </c>
       <c r="H919" t="n">
         <v>78870</v>
@@ -27078,7 +27078,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G921" t="n">
-        <v>0.920057773590088</v>
+        <v>0.920057833194733</v>
       </c>
       <c r="H921" t="n">
         <v>161762</v>
@@ -27107,7 +27107,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G922" t="n">
-        <v>0.92818558216095</v>
+        <v>0.928185522556305</v>
       </c>
       <c r="H922" t="n">
         <v>341470</v>
@@ -27136,7 +27136,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G923" t="n">
-        <v>0.954194307327271</v>
+        <v>0.954194188117981</v>
       </c>
       <c r="H923" t="n">
         <v>172760</v>
@@ -27194,7 +27194,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G925" t="n">
-        <v>0.967198491096497</v>
+        <v>0.967198610305786</v>
       </c>
       <c r="H925" t="n">
         <v>74506</v>
@@ -27223,7 +27223,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G926" t="n">
-        <v>0.981828331947327</v>
+        <v>0.981828451156616</v>
       </c>
       <c r="H926" t="n">
         <v>93608</v>
@@ -27281,7 +27281,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>0.975326299667358</v>
+        <v>0.975326359272003</v>
       </c>
       <c r="H928" t="n">
         <v>64154</v>
@@ -27310,7 +27310,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G929" t="n">
-        <v>0.973700702190399</v>
+        <v>0.973700761795044</v>
       </c>
       <c r="H929" t="n">
         <v>161453</v>
@@ -27339,7 +27339,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G930" t="n">
-        <v>0.972075343132019</v>
+        <v>0.972075164318085</v>
       </c>
       <c r="H930" t="n">
         <v>189441</v>
@@ -27397,7 +27397,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G932" t="n">
-        <v>0.980202972888947</v>
+        <v>0.980202853679657</v>
       </c>
       <c r="H932" t="n">
         <v>171505</v>
@@ -27455,7 +27455,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G934" t="n">
-        <v>0.950943052768707</v>
+        <v>0.950943112373352</v>
       </c>
       <c r="H934" t="n">
         <v>215787</v>
@@ -27484,7 +27484,7 @@
         <v>1.25</v>
       </c>
       <c r="G935" t="n">
-        <v>1.01596486568451</v>
+        <v>1.0159649848938</v>
       </c>
       <c r="H935" t="n">
         <v>631232</v>
@@ -27571,7 +27571,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G938" t="n">
-        <v>1.09236550331116</v>
+        <v>1.09236538410187</v>
       </c>
       <c r="H938" t="n">
         <v>1405944</v>
@@ -27600,7 +27600,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G939" t="n">
-        <v>1.14275729656219</v>
+        <v>1.14275741577148</v>
       </c>
       <c r="H939" t="n">
         <v>1400876</v>
@@ -27687,7 +27687,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G942" t="n">
-        <v>1.19640028476715</v>
+        <v>1.19640016555786</v>
       </c>
       <c r="H942" t="n">
         <v>683159</v>
@@ -27774,7 +27774,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G945" t="n">
-        <v>1.21753239631653</v>
+        <v>1.21753227710724</v>
       </c>
       <c r="H945" t="n">
         <v>851139</v>
@@ -27919,7 +27919,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G950" t="n">
-        <v>1.14600837230682</v>
+        <v>1.14600849151611</v>
       </c>
       <c r="H950" t="n">
         <v>820517</v>
@@ -27948,7 +27948,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G951" t="n">
-        <v>1.14600837230682</v>
+        <v>1.14600849151611</v>
       </c>
       <c r="H951" t="n">
         <v>546712</v>
@@ -28006,7 +28006,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G953" t="n">
-        <v>1.14600837230682</v>
+        <v>1.14600849151611</v>
       </c>
       <c r="H953" t="n">
         <v>165122</v>
@@ -28035,7 +28035,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G954" t="n">
-        <v>1.13462972640991</v>
+        <v>1.13462960720062</v>
       </c>
       <c r="H954" t="n">
         <v>389278</v>
@@ -28064,7 +28064,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G955" t="n">
-        <v>1.12325084209442</v>
+        <v>1.12325072288513</v>
       </c>
       <c r="H955" t="n">
         <v>226899</v>
@@ -28093,7 +28093,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G956" t="n">
-        <v>1.09561669826508</v>
+        <v>1.09561657905579</v>
       </c>
       <c r="H956" t="n">
         <v>303262</v>
@@ -28238,7 +28238,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G961" t="n">
-        <v>1.13462972640991</v>
+        <v>1.13462960720062</v>
       </c>
       <c r="H961" t="n">
         <v>380185</v>
@@ -28267,7 +28267,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G962" t="n">
-        <v>1.17039155960083</v>
+        <v>1.17039167881012</v>
       </c>
       <c r="H962" t="n">
         <v>292366</v>
@@ -28325,7 +28325,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G964" t="n">
-        <v>1.16226387023926</v>
+        <v>1.16226375102997</v>
       </c>
       <c r="H964" t="n">
         <v>427417</v>
@@ -28354,7 +28354,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G965" t="n">
-        <v>1.17039155960083</v>
+        <v>1.17039167881012</v>
       </c>
       <c r="H965" t="n">
         <v>347979</v>
@@ -28383,7 +28383,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G966" t="n">
-        <v>1.19314932823181</v>
+        <v>1.19314920902252</v>
       </c>
       <c r="H966" t="n">
         <v>565660</v>
@@ -28412,7 +28412,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G967" t="n">
-        <v>1.18827247619629</v>
+        <v>1.18827259540558</v>
       </c>
       <c r="H967" t="n">
         <v>656044</v>
@@ -28528,7 +28528,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G971" t="n">
-        <v>1.17039155960083</v>
+        <v>1.17039167881012</v>
       </c>
       <c r="H971" t="n">
         <v>245082</v>
@@ -28557,7 +28557,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G972" t="n">
-        <v>1.16714036464691</v>
+        <v>1.1671404838562</v>
       </c>
       <c r="H972" t="n">
         <v>258894</v>
@@ -28644,7 +28644,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G975" t="n">
-        <v>1.25491988658905</v>
+        <v>1.25491976737976</v>
       </c>
       <c r="H975" t="n">
         <v>1524999</v>
@@ -28673,7 +28673,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G976" t="n">
-        <v>1.31018841266632</v>
+        <v>1.31018829345703</v>
       </c>
       <c r="H976" t="n">
         <v>1546549</v>
@@ -28702,7 +28702,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G977" t="n">
-        <v>1.36058020591736</v>
+        <v>1.36058032512665</v>
       </c>
       <c r="H977" t="n">
         <v>1307448</v>
@@ -28731,7 +28731,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G978" t="n">
-        <v>1.38008666038513</v>
+        <v>1.38008654117584</v>
       </c>
       <c r="H978" t="n">
         <v>1454937</v>
@@ -28818,7 +28818,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G981" t="n">
-        <v>1.38008666038513</v>
+        <v>1.38008654117584</v>
       </c>
       <c r="H981" t="n">
         <v>773986</v>
@@ -28934,7 +28934,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G985" t="n">
-        <v>1.34920144081116</v>
+        <v>1.34920132160187</v>
       </c>
       <c r="H985" t="n">
         <v>973491</v>
@@ -28963,7 +28963,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G986" t="n">
-        <v>1.36870789527893</v>
+        <v>1.36870801448822</v>
       </c>
       <c r="H986" t="n">
         <v>413047</v>
@@ -29050,7 +29050,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G989" t="n">
-        <v>1.50362813472748</v>
+        <v>1.50362801551819</v>
       </c>
       <c r="H989" t="n">
         <v>2622875</v>
@@ -29137,7 +29137,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G992" t="n">
-        <v>1.52150905132294</v>
+        <v>1.52150893211365</v>
       </c>
       <c r="H992" t="n">
         <v>953321</v>
@@ -29166,7 +29166,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G993" t="n">
-        <v>1.52313446998596</v>
+        <v>1.52313458919525</v>
       </c>
       <c r="H993" t="n">
         <v>533400</v>
@@ -29195,7 +29195,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G994" t="n">
-        <v>1.53451347351074</v>
+        <v>1.53451335430145</v>
       </c>
       <c r="H994" t="n">
         <v>477838</v>
@@ -29224,7 +29224,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G995" t="n">
-        <v>1.52801108360291</v>
+        <v>1.52801120281219</v>
       </c>
       <c r="H995" t="n">
         <v>479945</v>
@@ -29253,7 +29253,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G996" t="n">
-        <v>1.50037705898285</v>
+        <v>1.50037693977356</v>
       </c>
       <c r="H996" t="n">
         <v>731136</v>
@@ -29340,7 +29340,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G999" t="n">
-        <v>1.45486176013947</v>
+        <v>1.45486164093018</v>
       </c>
       <c r="H999" t="n">
         <v>451260</v>
@@ -29369,7 +29369,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.4711172580719</v>
+        <v>1.47111713886261</v>
       </c>
       <c r="H1000" t="n">
         <v>528734</v>
@@ -29398,7 +29398,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.48412144184113</v>
+        <v>1.48412156105042</v>
       </c>
       <c r="H1001" t="n">
         <v>449526</v>
@@ -29485,7 +29485,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.541015625</v>
+        <v>1.54101550579071</v>
       </c>
       <c r="H1004" t="n">
         <v>525166</v>
@@ -29601,7 +29601,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.58327960968018</v>
+        <v>1.58327972888947</v>
       </c>
       <c r="H1008" t="n">
         <v>374651</v>
@@ -29630,7 +29630,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.58490526676178</v>
+        <v>1.58490538597107</v>
       </c>
       <c r="H1009" t="n">
         <v>362528</v>
@@ -29659,7 +29659,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.54426658153534</v>
+        <v>1.54426670074463</v>
       </c>
       <c r="H1010" t="n">
         <v>467043</v>
@@ -29833,7 +29833,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.52150905132294</v>
+        <v>1.52150893211365</v>
       </c>
       <c r="H1016" t="n">
         <v>237239</v>
@@ -29862,7 +29862,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.4694916009903</v>
+        <v>1.46949148178101</v>
       </c>
       <c r="H1017" t="n">
         <v>461028</v>
@@ -29920,7 +29920,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.46624040603638</v>
+        <v>1.46624052524567</v>
       </c>
       <c r="H1019" t="n">
         <v>398784</v>
@@ -29978,7 +29978,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1021" t="n">
         <v>307164</v>
@@ -30007,7 +30007,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.47436821460724</v>
+        <v>1.47436833381653</v>
       </c>
       <c r="H1022" t="n">
         <v>257400</v>
@@ -30152,7 +30152,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1027" t="n">
         <v>309303</v>
@@ -30181,7 +30181,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.53451347351074</v>
+        <v>1.53451335430145</v>
       </c>
       <c r="H1028" t="n">
         <v>871258</v>
@@ -30268,7 +30268,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.46624040603638</v>
+        <v>1.46624052524567</v>
       </c>
       <c r="H1031" t="n">
         <v>279862</v>
@@ -30355,7 +30355,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.47436821460724</v>
+        <v>1.47436833381653</v>
       </c>
       <c r="H1034" t="n">
         <v>319945</v>
@@ -30413,7 +30413,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.45323610305786</v>
+        <v>1.45323622226715</v>
       </c>
       <c r="H1036" t="n">
         <v>355571</v>
@@ -30529,7 +30529,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.43047869205475</v>
+        <v>1.43047857284546</v>
       </c>
       <c r="H1040" t="n">
         <v>462191</v>
@@ -30616,7 +30616,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.49550032615662</v>
+        <v>1.49550044536591</v>
       </c>
       <c r="H1043" t="n">
         <v>568502</v>
@@ -30645,7 +30645,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.50362813472748</v>
+        <v>1.50362801551819</v>
       </c>
       <c r="H1044" t="n">
         <v>774420</v>
@@ -30703,7 +30703,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.58002865314484</v>
+        <v>1.58002853393555</v>
       </c>
       <c r="H1046" t="n">
         <v>1055118</v>
@@ -30848,7 +30848,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.70682096481323</v>
+        <v>1.70682108402252</v>
       </c>
       <c r="H1051" t="n">
         <v>1021557</v>
@@ -30993,7 +30993,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.45486176013947</v>
+        <v>1.45486164093018</v>
       </c>
       <c r="H1056" t="n">
         <v>670082</v>
@@ -31051,7 +31051,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.34920144081116</v>
+        <v>1.34920132160187</v>
       </c>
       <c r="H1058" t="n">
         <v>1083954</v>
@@ -31109,7 +31109,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.28580522537231</v>
+        <v>1.28580510616302</v>
       </c>
       <c r="H1060" t="n">
         <v>925237</v>
@@ -31138,7 +31138,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.20777904987335</v>
+        <v>1.20777916908264</v>
       </c>
       <c r="H1061" t="n">
         <v>605848</v>
@@ -31254,7 +31254,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.97044974565506</v>
+        <v>0.970449686050415</v>
       </c>
       <c r="H1065" t="n">
         <v>869739</v>
@@ -31283,7 +31283,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.897300243377686</v>
+        <v>0.897300183773041</v>
       </c>
       <c r="H1066" t="n">
         <v>1281045</v>
@@ -31312,7 +31312,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.902176856994629</v>
+        <v>0.902176737785339</v>
       </c>
       <c r="H1067" t="n">
         <v>1423220</v>
@@ -31515,7 +31515,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.934687614440918</v>
+        <v>0.934687674045563</v>
       </c>
       <c r="H1074" t="n">
         <v>777347</v>
@@ -31544,7 +31544,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.950943052768707</v>
+        <v>0.950943112373352</v>
       </c>
       <c r="H1075" t="n">
         <v>1305539</v>
@@ -31573,7 +31573,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.942815363407135</v>
+        <v>0.94281542301178</v>
       </c>
       <c r="H1076" t="n">
         <v>748259</v>
@@ -31631,7 +31631,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.881044805049896</v>
+        <v>0.881044745445251</v>
       </c>
       <c r="H1078" t="n">
         <v>608610</v>
@@ -31660,7 +31660,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.879419147968292</v>
+        <v>0.879419207572937</v>
       </c>
       <c r="H1079" t="n">
         <v>573362</v>
@@ -31689,7 +31689,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.921683251857758</v>
+        <v>0.921683371067047</v>
       </c>
       <c r="H1080" t="n">
         <v>739356</v>
@@ -31776,7 +31776,7 @@
         <v>1.25</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.01596486568451</v>
+        <v>1.0159649848938</v>
       </c>
       <c r="H1083" t="n">
         <v>584779</v>
@@ -31863,7 +31863,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.996458411216736</v>
+        <v>0.996458351612091</v>
       </c>
       <c r="H1086" t="n">
         <v>740605</v>
@@ -31892,7 +31892,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.0744845867157</v>
+        <v>1.07448446750641</v>
       </c>
       <c r="H1087" t="n">
         <v>1037471</v>
@@ -31950,7 +31950,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.01759052276611</v>
+        <v>1.01759040355682</v>
       </c>
       <c r="H1089" t="n">
         <v>624117</v>
@@ -31979,7 +31979,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.01759052276611</v>
+        <v>1.01759040355682</v>
       </c>
       <c r="H1090" t="n">
         <v>519587</v>
@@ -32008,7 +32008,7 @@
         <v>1.25</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.01596486568451</v>
+        <v>1.0159649848938</v>
       </c>
       <c r="H1091" t="n">
         <v>496258</v>
@@ -32037,7 +32037,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.996458411216736</v>
+        <v>0.996458351612091</v>
       </c>
       <c r="H1092" t="n">
         <v>205552</v>
@@ -32153,7 +32153,7 @@
         <v>1.28199994564056</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.04197371006012</v>
+        <v>1.04197347164154</v>
       </c>
       <c r="H1096" t="n">
         <v>369586</v>
@@ -32182,7 +32182,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.04522466659546</v>
+        <v>1.04522478580475</v>
       </c>
       <c r="H1097" t="n">
         <v>636495</v>
@@ -32269,7 +32269,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.05010151863098</v>
+        <v>1.05010139942169</v>
       </c>
       <c r="H1100" t="n">
         <v>311723</v>
@@ -32414,7 +32414,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.02896928787231</v>
+        <v>1.0289694070816</v>
       </c>
       <c r="H1105" t="n">
         <v>508712</v>
@@ -32443,7 +32443,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.01759052276611</v>
+        <v>1.01759040355682</v>
       </c>
       <c r="H1106" t="n">
         <v>367108</v>
@@ -32501,7 +32501,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.980202972888947</v>
+        <v>0.980202853679657</v>
       </c>
       <c r="H1108" t="n">
         <v>640476</v>
@@ -32530,7 +32530,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.980202972888947</v>
+        <v>0.980202853679657</v>
       </c>
       <c r="H1109" t="n">
         <v>262178</v>
@@ -32559,7 +32559,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.01271378993988</v>
+        <v>1.01271390914917</v>
       </c>
       <c r="H1110" t="n">
         <v>381864</v>
@@ -32588,7 +32588,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.97044974565506</v>
+        <v>0.970449686050415</v>
       </c>
       <c r="H1111" t="n">
         <v>742959</v>
@@ -32617,7 +32617,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.95907074213028</v>
+        <v>0.959070861339569</v>
       </c>
       <c r="H1112" t="n">
         <v>542973</v>
@@ -32646,7 +32646,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.97044974565506</v>
+        <v>0.970449686050415</v>
       </c>
       <c r="H1113" t="n">
         <v>623582</v>
@@ -32675,7 +32675,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.975326299667358</v>
+        <v>0.975326359272003</v>
       </c>
       <c r="H1114" t="n">
         <v>1130624</v>
@@ -32704,7 +32704,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.999709486961365</v>
+        <v>0.99970954656601</v>
       </c>
       <c r="H1115" t="n">
         <v>313811</v>
@@ -32762,7 +32762,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.05660355091095</v>
+        <v>1.05660343170166</v>
       </c>
       <c r="H1117" t="n">
         <v>1221656</v>
@@ -32849,7 +32849,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.13950622081757</v>
+        <v>1.13950634002686</v>
       </c>
       <c r="H1120" t="n">
         <v>729359</v>
@@ -32907,7 +32907,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.18989813327789</v>
+        <v>1.1898980140686</v>
       </c>
       <c r="H1122" t="n">
         <v>1036253</v>
@@ -32965,7 +32965,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.23866450786591</v>
+        <v>1.23866438865662</v>
       </c>
       <c r="H1124" t="n">
         <v>1685924</v>
@@ -32994,7 +32994,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.29068171977997</v>
+        <v>1.29068183898926</v>
       </c>
       <c r="H1125" t="n">
         <v>1775298</v>
@@ -33023,7 +33023,7 @@
         <v>1.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.21915793418884</v>
+        <v>1.21915781497955</v>
       </c>
       <c r="H1126" t="n">
         <v>1345354</v>
@@ -33052,7 +33052,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.19965124130249</v>
+        <v>1.19965136051178</v>
       </c>
       <c r="H1127" t="n">
         <v>955320</v>
@@ -33110,7 +33110,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.10374438762665</v>
+        <v>1.10374426841736</v>
       </c>
       <c r="H1129" t="n">
         <v>718868</v>
@@ -33255,7 +33255,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.09724199771881</v>
+        <v>1.0972421169281</v>
       </c>
       <c r="H1134" t="n">
         <v>684979</v>
@@ -33400,7 +33400,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.04522466659546</v>
+        <v>1.04522478580475</v>
       </c>
       <c r="H1139" t="n">
         <v>375307</v>
@@ -33429,7 +33429,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.09561669826508</v>
+        <v>1.09561657905579</v>
       </c>
       <c r="H1140" t="n">
         <v>822817</v>
@@ -33545,7 +33545,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.2597963809967</v>
+        <v>1.25979650020599</v>
       </c>
       <c r="H1144" t="n">
         <v>1546205</v>
@@ -33603,7 +33603,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.34107375144958</v>
+        <v>1.3410736322403</v>
       </c>
       <c r="H1146" t="n">
         <v>2175140</v>
@@ -33690,7 +33690,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.36058020591736</v>
+        <v>1.36058032512665</v>
       </c>
       <c r="H1149" t="n">
         <v>1166397</v>
@@ -33777,7 +33777,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.40446984767914</v>
+        <v>1.40446996688843</v>
       </c>
       <c r="H1152" t="n">
         <v>1190639</v>
@@ -33806,7 +33806,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.43047869205475</v>
+        <v>1.43047857284546</v>
       </c>
       <c r="H1153" t="n">
         <v>1348043</v>
@@ -33864,7 +33864,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.44998514652252</v>
+        <v>1.44998526573181</v>
       </c>
       <c r="H1155" t="n">
         <v>1599256</v>
@@ -33951,7 +33951,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1158" t="n">
         <v>1784025</v>
@@ -34009,7 +34009,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1160" t="n">
         <v>1696767</v>
@@ -34038,7 +34038,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.42722749710083</v>
+        <v>1.42722761631012</v>
       </c>
       <c r="H1161" t="n">
         <v>1227223</v>
@@ -34067,7 +34067,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.41422319412231</v>
+        <v>1.41422307491302</v>
       </c>
       <c r="H1162" t="n">
         <v>710737</v>
@@ -34154,7 +34154,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.41422319412231</v>
+        <v>1.41422307491302</v>
       </c>
       <c r="H1165" t="n">
         <v>959990</v>
@@ -34270,7 +34270,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.44673407077789</v>
+        <v>1.4467339515686</v>
       </c>
       <c r="H1169" t="n">
         <v>752976</v>
@@ -34299,7 +34299,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.52313446998596</v>
+        <v>1.52313458919525</v>
       </c>
       <c r="H1170" t="n">
         <v>1389209</v>
@@ -34328,7 +34328,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.54264116287231</v>
+        <v>1.54264104366302</v>
       </c>
       <c r="H1171" t="n">
         <v>1189245</v>
@@ -34386,7 +34386,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.52476024627686</v>
+        <v>1.52476012706757</v>
       </c>
       <c r="H1173" t="n">
         <v>596935</v>
@@ -34444,7 +34444,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.51175570487976</v>
+        <v>1.51175582408905</v>
       </c>
       <c r="H1175" t="n">
         <v>769845</v>
@@ -34473,7 +34473,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.49062371253967</v>
+        <v>1.49062359333038</v>
       </c>
       <c r="H1176" t="n">
         <v>629898</v>
@@ -34502,7 +34502,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.49875128269196</v>
+        <v>1.49875140190125</v>
       </c>
       <c r="H1177" t="n">
         <v>453226</v>
@@ -34531,7 +34531,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.48412144184113</v>
+        <v>1.48412156105042</v>
       </c>
       <c r="H1178" t="n">
         <v>487014</v>
@@ -34618,7 +34618,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1181" t="n">
         <v>1042576</v>
@@ -34647,7 +34647,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.47924506664276</v>
+        <v>1.47924494743347</v>
       </c>
       <c r="H1182" t="n">
         <v>1296105</v>
@@ -34676,7 +34676,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.48412144184113</v>
+        <v>1.48412156105042</v>
       </c>
       <c r="H1183" t="n">
         <v>1441894</v>
@@ -34734,7 +34734,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1185" t="n">
-        <v>1.4711172580719</v>
+        <v>1.47111713886261</v>
       </c>
       <c r="H1185" t="n">
         <v>1016942</v>
@@ -34763,7 +34763,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.45323610305786</v>
+        <v>1.45323622226715</v>
       </c>
       <c r="H1186" t="n">
         <v>801592</v>
@@ -34995,7 +34995,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.41584873199463</v>
+        <v>1.41584861278534</v>
       </c>
       <c r="H1194" t="n">
         <v>747064</v>
@@ -35024,7 +35024,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.43047869205475</v>
+        <v>1.43047857284546</v>
       </c>
       <c r="H1195" t="n">
         <v>862823</v>
@@ -35169,7 +35169,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.32806932926178</v>
+        <v>1.32806921005249</v>
       </c>
       <c r="H1200" t="n">
         <v>2134415</v>
@@ -35198,7 +35198,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.33294594287872</v>
+        <v>1.33294606208801</v>
       </c>
       <c r="H1201" t="n">
         <v>1057873</v>
@@ -35227,7 +35227,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.31994163990021</v>
+        <v>1.31994152069092</v>
       </c>
       <c r="H1202" t="n">
         <v>1223640</v>
@@ -35343,7 +35343,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.34432482719421</v>
+        <v>1.34432470798492</v>
       </c>
       <c r="H1206" t="n">
         <v>595620</v>
@@ -35459,7 +35459,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.36058020591736</v>
+        <v>1.36058032512665</v>
       </c>
       <c r="H1210" t="n">
         <v>1643374</v>
@@ -35546,7 +35546,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.40446984767914</v>
+        <v>1.40446996688843</v>
       </c>
       <c r="H1213" t="n">
         <v>1175485</v>
@@ -35720,7 +35720,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.33619701862335</v>
+        <v>1.33619713783264</v>
       </c>
       <c r="H1219" t="n">
         <v>1345726</v>
@@ -35807,7 +35807,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.33944809436798</v>
+        <v>1.33944821357727</v>
       </c>
       <c r="H1222" t="n">
         <v>1303372</v>
@@ -35836,7 +35836,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.29718387126923</v>
+        <v>1.29718399047852</v>
       </c>
       <c r="H1223" t="n">
         <v>1269824</v>
@@ -35923,7 +35923,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.19314932823181</v>
+        <v>1.19314920902252</v>
       </c>
       <c r="H1226" t="n">
         <v>1199321</v>
@@ -35952,7 +35952,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.1330041885376</v>
+        <v>1.13300406932831</v>
       </c>
       <c r="H1227" t="n">
         <v>1020699</v>
@@ -35981,7 +35981,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.1541360616684</v>
+        <v>1.15413618087769</v>
       </c>
       <c r="H1228" t="n">
         <v>1314498</v>
@@ -36039,7 +36039,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.22891104221344</v>
+        <v>1.22891116142273</v>
       </c>
       <c r="H1230" t="n">
         <v>1744398</v>
@@ -36126,7 +36126,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.25491988658905</v>
+        <v>1.25491976737976</v>
       </c>
       <c r="H1233" t="n">
         <v>1914649</v>
@@ -36184,7 +36184,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G1235" t="n">
-        <v>1.31181395053864</v>
+        <v>1.31181383132935</v>
       </c>
       <c r="H1235" t="n">
         <v>1401626</v>
@@ -36213,7 +36213,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.32806932926178</v>
+        <v>1.32806921005249</v>
       </c>
       <c r="H1236" t="n">
         <v>1620142</v>
@@ -36242,7 +36242,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.31994163990021</v>
+        <v>1.31994152069092</v>
       </c>
       <c r="H1237" t="n">
         <v>589880</v>
@@ -36416,7 +36416,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.44673407077789</v>
+        <v>1.4467339515686</v>
       </c>
       <c r="H1243" t="n">
         <v>686032</v>
@@ -36503,7 +36503,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.44673407077789</v>
+        <v>1.4467339515686</v>
       </c>
       <c r="H1246" t="n">
         <v>1431331</v>
@@ -36561,7 +36561,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.45486176013947</v>
+        <v>1.45486164093018</v>
       </c>
       <c r="H1248" t="n">
         <v>247638</v>
@@ -36590,7 +36590,7 @@
         <v>1.75</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.42235088348389</v>
+        <v>1.42235100269318</v>
       </c>
       <c r="H1249" t="n">
         <v>382937</v>
@@ -36648,7 +36648,7 @@
         <v>1.75</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.42235088348389</v>
+        <v>1.42235100269318</v>
       </c>
       <c r="H1251" t="n">
         <v>406143</v>
@@ -36677,7 +36677,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.38984000682831</v>
+        <v>1.3898401260376</v>
       </c>
       <c r="H1252" t="n">
         <v>670834</v>
@@ -36706,7 +36706,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.39146554470062</v>
+        <v>1.39146566390991</v>
       </c>
       <c r="H1253" t="n">
         <v>264203</v>
@@ -36822,7 +36822,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.34432482719421</v>
+        <v>1.34432470798492</v>
       </c>
       <c r="H1257" t="n">
         <v>477576</v>
@@ -36851,7 +36851,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.33294594287872</v>
+        <v>1.33294606208801</v>
       </c>
       <c r="H1258" t="n">
         <v>364321</v>
@@ -36967,7 +36967,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.34920144081116</v>
+        <v>1.34920132160187</v>
       </c>
       <c r="H1262" t="n">
         <v>551734</v>
@@ -37083,7 +37083,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.28580522537231</v>
+        <v>1.28580510616302</v>
       </c>
       <c r="H1266" t="n">
         <v>354205</v>
@@ -37112,7 +37112,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.31018841266632</v>
+        <v>1.31018829345703</v>
       </c>
       <c r="H1267" t="n">
         <v>829953</v>
@@ -37141,7 +37141,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.33944809436798</v>
+        <v>1.33944821357727</v>
       </c>
       <c r="H1268" t="n">
         <v>326436</v>
@@ -37170,7 +37170,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.36870789527893</v>
+        <v>1.36870801448822</v>
       </c>
       <c r="H1269" t="n">
         <v>442963</v>
@@ -37257,7 +37257,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.35245251655579</v>
+        <v>1.3524523973465</v>
       </c>
       <c r="H1272" t="n">
         <v>326404</v>
@@ -37344,7 +37344,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.38984000682831</v>
+        <v>1.3898401260376</v>
       </c>
       <c r="H1275" t="n">
         <v>1009936</v>
@@ -37431,7 +37431,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.42072522640228</v>
+        <v>1.42072546482086</v>
       </c>
       <c r="H1278" t="n">
         <v>1674756</v>
@@ -37460,7 +37460,7 @@
         <v>1.75</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.42235088348389</v>
+        <v>1.42235100269318</v>
       </c>
       <c r="H1279" t="n">
         <v>258473</v>
@@ -37489,7 +37489,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.38984000682831</v>
+        <v>1.3898401260376</v>
       </c>
       <c r="H1280" t="n">
         <v>377389</v>
@@ -37576,7 +37576,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.41097211837769</v>
+        <v>1.41097187995911</v>
       </c>
       <c r="H1283" t="n">
         <v>270991</v>
@@ -37692,7 +37692,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.34920144081116</v>
+        <v>1.34920132160187</v>
       </c>
       <c r="H1287" t="n">
         <v>502247</v>
@@ -37837,7 +37837,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.3654568195343</v>
+        <v>1.36545670032501</v>
       </c>
       <c r="H1292" t="n">
         <v>591974</v>
@@ -37895,7 +37895,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.4711172580719</v>
+        <v>1.47111713886261</v>
       </c>
       <c r="H1294" t="n">
         <v>726732</v>
@@ -37953,7 +37953,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.54264116287231</v>
+        <v>1.54264104366302</v>
       </c>
       <c r="H1296" t="n">
         <v>830535</v>
@@ -37982,7 +37982,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.54751777648926</v>
+        <v>1.54751789569855</v>
       </c>
       <c r="H1297" t="n">
         <v>532427</v>
@@ -38011,7 +38011,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.54751777648926</v>
+        <v>1.54751789569855</v>
       </c>
       <c r="H1298" t="n">
         <v>870038</v>
@@ -38127,7 +38127,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.52801108360291</v>
+        <v>1.52801120281219</v>
       </c>
       <c r="H1302" t="n">
         <v>426223</v>
@@ -38214,7 +38214,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.49550032615662</v>
+        <v>1.49550044536591</v>
       </c>
       <c r="H1305" t="n">
         <v>387430</v>
@@ -38243,7 +38243,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.47761929035187</v>
+        <v>1.47761940956116</v>
       </c>
       <c r="H1306" t="n">
         <v>158784</v>
@@ -38272,7 +38272,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.46624040603638</v>
+        <v>1.46624052524567</v>
       </c>
       <c r="H1307" t="n">
         <v>421159</v>
@@ -38330,7 +38330,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.5182580947876</v>
+        <v>1.51825797557831</v>
       </c>
       <c r="H1309" t="n">
         <v>576309</v>
@@ -38359,7 +38359,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.56539881229401</v>
+        <v>1.56539869308472</v>
       </c>
       <c r="H1310" t="n">
         <v>1052487</v>
@@ -38388,7 +38388,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.61253941059113</v>
+        <v>1.61253952980042</v>
       </c>
       <c r="H1311" t="n">
         <v>1482799</v>
@@ -38504,7 +38504,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.58002865314484</v>
+        <v>1.58002853393555</v>
       </c>
       <c r="H1315" t="n">
         <v>459885</v>
@@ -38620,7 +38620,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.58815634250641</v>
+        <v>1.5881564617157</v>
       </c>
       <c r="H1319" t="n">
         <v>349706</v>
@@ -38678,7 +38678,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.71088492870331</v>
+        <v>1.71088480949402</v>
       </c>
       <c r="H1321" t="n">
         <v>2169514</v>
@@ -38707,7 +38707,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.67430996894836</v>
+        <v>1.67431020736694</v>
       </c>
       <c r="H1322" t="n">
         <v>699635</v>
@@ -38823,7 +38823,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.58490526676178</v>
+        <v>1.58490538597107</v>
       </c>
       <c r="H1326" t="n">
         <v>365123</v>
@@ -38852,7 +38852,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.58490526676178</v>
+        <v>1.58490538597107</v>
       </c>
       <c r="H1327" t="n">
         <v>422178</v>
@@ -39026,7 +39026,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.76371514797211</v>
+        <v>1.76371502876282</v>
       </c>
       <c r="H1333" t="n">
         <v>1218512</v>
@@ -39084,7 +39084,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.67430996894836</v>
+        <v>1.67431020736694</v>
       </c>
       <c r="H1335" t="n">
         <v>1044669</v>
@@ -39287,7 +39287,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.69462954998016</v>
+        <v>1.69462943077087</v>
       </c>
       <c r="H1342" t="n">
         <v>1018867</v>
@@ -39316,7 +39316,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.70682096481323</v>
+        <v>1.70682108402252</v>
       </c>
       <c r="H1343" t="n">
         <v>327559</v>
@@ -39345,7 +39345,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.69462954998016</v>
+        <v>1.69462943077087</v>
       </c>
       <c r="H1344" t="n">
         <v>293534</v>
@@ -39403,7 +39403,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.6296079158783</v>
+        <v>1.62960779666901</v>
       </c>
       <c r="H1346" t="n">
         <v>479194</v>
@@ -39490,7 +39490,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1349" t="n">
         <v>923072</v>
@@ -39519,7 +39519,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1350" t="n">
         <v>253626</v>
@@ -39548,7 +39548,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.69869315624237</v>
+        <v>1.69869339466095</v>
       </c>
       <c r="H1351" t="n">
         <v>281228</v>
@@ -39693,7 +39693,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.69869315624237</v>
+        <v>1.69869339466095</v>
       </c>
       <c r="H1356" t="n">
         <v>281877</v>
@@ -39751,7 +39751,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.70682096481323</v>
+        <v>1.70682108402252</v>
       </c>
       <c r="H1358" t="n">
         <v>419293</v>
@@ -39838,7 +39838,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1361" t="n">
         <v>844964</v>
@@ -39867,7 +39867,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1362" t="n">
         <v>379324</v>
@@ -39896,7 +39896,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1363" t="n">
         <v>166032</v>
@@ -39925,7 +39925,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.67837405204773</v>
+        <v>1.67837417125702</v>
       </c>
       <c r="H1364" t="n">
         <v>240834</v>
@@ -39954,7 +39954,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.67837405204773</v>
+        <v>1.67837417125702</v>
       </c>
       <c r="H1365" t="n">
         <v>365920</v>
@@ -40070,7 +40070,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1369" t="n">
         <v>108342</v>
@@ -40157,7 +40157,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1372" t="n">
         <v>152508</v>
@@ -40186,7 +40186,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.67430996894836</v>
+        <v>1.67431020736694</v>
       </c>
       <c r="H1373" t="n">
         <v>112605</v>
@@ -40215,7 +40215,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1374" t="n">
         <v>131123</v>
@@ -40273,7 +40273,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.69869315624237</v>
+        <v>1.69869339466095</v>
       </c>
       <c r="H1376" t="n">
         <v>214274</v>
@@ -40302,7 +40302,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.74745965003967</v>
+        <v>1.74745976924896</v>
       </c>
       <c r="H1377" t="n">
         <v>1197915</v>
@@ -40389,7 +40389,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.74745965003967</v>
+        <v>1.74745976924896</v>
       </c>
       <c r="H1380" t="n">
         <v>277313</v>
@@ -40534,7 +40534,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.71088492870331</v>
+        <v>1.71088480949402</v>
       </c>
       <c r="H1385" t="n">
         <v>420916</v>
@@ -40563,7 +40563,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.69869315624237</v>
+        <v>1.69869339466095</v>
       </c>
       <c r="H1386" t="n">
         <v>221998</v>
@@ -40621,7 +40621,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.70682096481323</v>
+        <v>1.70682108402252</v>
       </c>
       <c r="H1388" t="n">
         <v>404164</v>
@@ -40708,7 +40708,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.70682096481323</v>
+        <v>1.70682108402252</v>
       </c>
       <c r="H1391" t="n">
         <v>287635</v>
@@ -40737,7 +40737,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.70682096481323</v>
+        <v>1.70682108402252</v>
       </c>
       <c r="H1392" t="n">
         <v>236511</v>
@@ -40766,7 +40766,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.73526811599731</v>
+        <v>1.73526799678802</v>
       </c>
       <c r="H1393" t="n">
         <v>205037</v>
@@ -40824,7 +40824,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.68650186061859</v>
+        <v>1.6865017414093</v>
       </c>
       <c r="H1395" t="n">
         <v>269064</v>
@@ -40853,7 +40853,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1396" t="n">
         <v>277481</v>
@@ -40882,7 +40882,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.69869315624237</v>
+        <v>1.69869339466095</v>
       </c>
       <c r="H1397" t="n">
         <v>206245</v>
@@ -40969,7 +40969,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1400" t="n">
         <v>137616</v>
@@ -41056,7 +41056,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.67024624347687</v>
+        <v>1.67024636268616</v>
       </c>
       <c r="H1403" t="n">
         <v>165788</v>
@@ -41143,7 +41143,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.64586329460144</v>
+        <v>1.64586317539215</v>
       </c>
       <c r="H1406" t="n">
         <v>113237</v>
@@ -41172,7 +41172,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.64586329460144</v>
+        <v>1.64586317539215</v>
       </c>
       <c r="H1407" t="n">
         <v>108899</v>
@@ -41230,7 +41230,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1409" t="n">
-        <v>1.58490526676178</v>
+        <v>1.58490538597107</v>
       </c>
       <c r="H1409" t="n">
         <v>416693</v>
@@ -41346,7 +41346,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1413" t="n">
         <v>121732</v>
@@ -41375,7 +41375,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.73526811599731</v>
+        <v>1.73526799678802</v>
       </c>
       <c r="H1414" t="n">
         <v>499367</v>
@@ -41578,7 +41578,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.66618251800537</v>
+        <v>1.66618239879608</v>
       </c>
       <c r="H1421" t="n">
         <v>387180</v>
@@ -41636,7 +41636,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.69869315624237</v>
+        <v>1.69869339466095</v>
       </c>
       <c r="H1423" t="n">
         <v>326145</v>
@@ -41694,7 +41694,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.73526811599731</v>
+        <v>1.73526799678802</v>
       </c>
       <c r="H1425" t="n">
         <v>157467</v>
@@ -41723,7 +41723,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.74745965003967</v>
+        <v>1.74745976924896</v>
       </c>
       <c r="H1426" t="n">
         <v>340552</v>
@@ -41897,7 +41897,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.77997064590454</v>
+        <v>1.77997052669525</v>
       </c>
       <c r="H1432" t="n">
         <v>352102</v>
@@ -41926,7 +41926,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.77590668201447</v>
+        <v>1.77590656280518</v>
       </c>
       <c r="H1433" t="n">
         <v>310018</v>
@@ -41955,7 +41955,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.83686435222626</v>
+        <v>1.83686459064484</v>
       </c>
       <c r="H1434" t="n">
         <v>275788</v>
@@ -41984,7 +41984,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.79216206073761</v>
+        <v>1.79216229915619</v>
       </c>
       <c r="H1435" t="n">
         <v>582509</v>
@@ -42013,7 +42013,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.83686435222626</v>
+        <v>1.83686459064484</v>
       </c>
       <c r="H1436" t="n">
         <v>178254</v>
@@ -42042,7 +42042,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.87750315666199</v>
+        <v>1.8775030374527</v>
       </c>
       <c r="H1437" t="n">
         <v>495218</v>
@@ -42100,7 +42100,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.91407787799835</v>
+        <v>1.91407799720764</v>
       </c>
       <c r="H1439" t="n">
         <v>170379</v>
@@ -42129,7 +42129,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.89782238006592</v>
+        <v>1.89782249927521</v>
       </c>
       <c r="H1440" t="n">
         <v>174924</v>
@@ -42158,7 +42158,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.91814148426056</v>
+        <v>1.91814172267914</v>
       </c>
       <c r="H1441" t="n">
         <v>264470</v>
@@ -42187,7 +42187,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.88563072681427</v>
+        <v>1.88563084602356</v>
       </c>
       <c r="H1442" t="n">
         <v>157167</v>
@@ -42216,7 +42216,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.91407787799835</v>
+        <v>1.91407799720764</v>
       </c>
       <c r="H1443" t="n">
         <v>430200</v>
@@ -42245,7 +42245,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.91001391410828</v>
+        <v>1.91001403331757</v>
       </c>
       <c r="H1444" t="n">
         <v>336822</v>
@@ -42274,7 +42274,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.89375865459442</v>
+        <v>1.89375853538513</v>
       </c>
       <c r="H1445" t="n">
         <v>142420</v>
@@ -42303,7 +42303,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.86124753952026</v>
+        <v>1.86124765872955</v>
       </c>
       <c r="H1446" t="n">
         <v>243118</v>
@@ -42361,7 +42361,7 @@
         <v>2.25</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.82873666286469</v>
+        <v>1.82873678207397</v>
       </c>
       <c r="H1448" t="n">
         <v>162939</v>
@@ -42390,7 +42390,7 @@
         <v>2.25</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.82873666286469</v>
+        <v>1.82873678207397</v>
       </c>
       <c r="H1449" t="n">
         <v>121634</v>
@@ -42419,7 +42419,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.85718405246735</v>
+        <v>1.85718381404877</v>
       </c>
       <c r="H1450" t="n">
         <v>171793</v>
@@ -42448,7 +42448,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.85718405246735</v>
+        <v>1.85718381404877</v>
       </c>
       <c r="H1451" t="n">
         <v>132956</v>
@@ -42506,7 +42506,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.86937522888184</v>
+        <v>1.86937534809113</v>
       </c>
       <c r="H1453" t="n">
         <v>118290</v>
@@ -42535,7 +42535,7 @@
         <v>2.25</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.82873666286469</v>
+        <v>1.82873678207397</v>
       </c>
       <c r="H1454" t="n">
         <v>347999</v>
@@ -42564,7 +42564,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.83686435222626</v>
+        <v>1.83686459064484</v>
       </c>
       <c r="H1455" t="n">
         <v>520646</v>
@@ -42593,7 +42593,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.86124753952026</v>
+        <v>1.86124765872955</v>
       </c>
       <c r="H1456" t="n">
         <v>137423</v>
@@ -42622,7 +42622,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.89375865459442</v>
+        <v>1.89375853538513</v>
       </c>
       <c r="H1457" t="n">
         <v>156515</v>
@@ -42680,7 +42680,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.89375865459442</v>
+        <v>1.89375853538513</v>
       </c>
       <c r="H1459" t="n">
         <v>218467</v>
@@ -42709,7 +42709,7 @@
         <v>2.25</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.82873666286469</v>
+        <v>1.82873678207397</v>
       </c>
       <c r="H1460" t="n">
         <v>333689</v>
@@ -42738,7 +42738,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.85718405246735</v>
+        <v>1.85718381404877</v>
       </c>
       <c r="H1461" t="n">
         <v>270156</v>
@@ -42796,7 +42796,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.84905624389648</v>
+        <v>1.84905600547791</v>
       </c>
       <c r="H1463" t="n">
         <v>254982</v>
@@ -42854,7 +42854,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.85718405246735</v>
+        <v>1.85718381404877</v>
       </c>
       <c r="H1465" t="n">
         <v>176788</v>
@@ -42883,7 +42883,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.84905624389648</v>
+        <v>1.84905600547791</v>
       </c>
       <c r="H1466" t="n">
         <v>167487</v>
@@ -42912,7 +42912,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.86937522888184</v>
+        <v>1.86937534809113</v>
       </c>
       <c r="H1467" t="n">
         <v>180413</v>
@@ -42941,7 +42941,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.88563072681427</v>
+        <v>1.88563084602356</v>
       </c>
       <c r="H1468" t="n">
         <v>146074</v>
@@ -42970,7 +42970,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.84905624389648</v>
+        <v>1.84905600547791</v>
       </c>
       <c r="H1469" t="n">
         <v>137392</v>
@@ -42999,7 +42999,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.90188610553741</v>
+        <v>1.9018862247467</v>
       </c>
       <c r="H1470" t="n">
         <v>201354</v>
@@ -43028,7 +43028,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.86124753952026</v>
+        <v>1.86124765872955</v>
       </c>
       <c r="H1471" t="n">
         <v>137813</v>
@@ -43086,7 +43086,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.87750315666199</v>
+        <v>1.8775030374527</v>
       </c>
       <c r="H1473" t="n">
         <v>263544</v>
@@ -43144,7 +43144,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1475" t="n">
-        <v>1.83280062675476</v>
+        <v>1.83280074596405</v>
       </c>
       <c r="H1475" t="n">
         <v>258300</v>
@@ -43173,7 +43173,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.8206090927124</v>
+        <v>1.82060921192169</v>
       </c>
       <c r="H1476" t="n">
         <v>406976</v>
@@ -43231,7 +43231,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.87750315666199</v>
+        <v>1.8775030374527</v>
       </c>
       <c r="H1478" t="n">
         <v>823061</v>
@@ -43260,7 +43260,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.9222058057785</v>
+        <v>1.92220544815063</v>
       </c>
       <c r="H1479" t="n">
         <v>1286521</v>
@@ -43289,7 +43289,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1480" t="n">
-        <v>1.90595018863678</v>
+        <v>1.90595030784607</v>
       </c>
       <c r="H1480" t="n">
         <v>531799</v>
@@ -43405,7 +43405,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.89375865459442</v>
+        <v>1.89375853538513</v>
       </c>
       <c r="H1484" t="n">
         <v>532235</v>
@@ -43434,7 +43434,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.87750315666199</v>
+        <v>1.8775030374527</v>
       </c>
       <c r="H1485" t="n">
         <v>389959</v>
@@ -43463,7 +43463,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>1.91001391410828</v>
+        <v>1.91001403331757</v>
       </c>
       <c r="H1486" t="n">
         <v>616442</v>
@@ -43492,7 +43492,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.91001391410828</v>
+        <v>1.91001403331757</v>
       </c>
       <c r="H1487" t="n">
         <v>751901</v>
@@ -43521,7 +43521,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.97097194194794</v>
+        <v>1.97097206115723</v>
       </c>
       <c r="H1488" t="n">
         <v>1578081</v>
@@ -43579,7 +43579,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.92983675003052</v>
+        <v>1.92983722686768</v>
       </c>
       <c r="H1490" t="n">
         <v>1375919</v>
@@ -43608,7 +43608,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.84669196605682</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1491" t="n">
         <v>1332507</v>
@@ -43637,7 +43637,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.84231615066528</v>
+        <v>1.84231603145599</v>
       </c>
       <c r="H1492" t="n">
         <v>824274</v>
@@ -43724,7 +43724,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.80730772018433</v>
+        <v>1.80730783939362</v>
       </c>
       <c r="H1495" t="n">
         <v>413856</v>
@@ -43840,7 +43840,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.78980350494385</v>
+        <v>1.78980362415314</v>
       </c>
       <c r="H1499" t="n">
         <v>264006</v>
@@ -43869,7 +43869,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1500" t="n">
         <v>249659</v>
@@ -43927,7 +43927,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1502" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1502" t="n">
         <v>336795</v>
@@ -43956,7 +43956,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.73641562461853</v>
+        <v>1.73641574382782</v>
       </c>
       <c r="H1503" t="n">
         <v>1273153</v>
@@ -44043,7 +44043,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.81605994701385</v>
+        <v>1.81605982780457</v>
       </c>
       <c r="H1506" t="n">
         <v>401833</v>
@@ -44072,7 +44072,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.82918775081635</v>
+        <v>1.82918798923492</v>
       </c>
       <c r="H1507" t="n">
         <v>378872</v>
@@ -44130,7 +44130,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.83356392383575</v>
+        <v>1.83356404304504</v>
       </c>
       <c r="H1509" t="n">
         <v>133199</v>
@@ -44159,7 +44159,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.83356392383575</v>
+        <v>1.83356404304504</v>
       </c>
       <c r="H1510" t="n">
         <v>178953</v>
@@ -44246,7 +44246,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.82918775081635</v>
+        <v>1.82918798923492</v>
       </c>
       <c r="H1513" t="n">
         <v>100364</v>
@@ -44304,7 +44304,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.81605994701385</v>
+        <v>1.81605982780457</v>
       </c>
       <c r="H1515" t="n">
         <v>137062</v>
@@ -44449,7 +44449,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1520" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1520" t="n">
         <v>147164</v>
@@ -44478,7 +44478,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.80293154716492</v>
+        <v>1.80293166637421</v>
       </c>
       <c r="H1521" t="n">
         <v>256029</v>
@@ -44536,7 +44536,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.84231615066528</v>
+        <v>1.84231603145599</v>
       </c>
       <c r="H1523" t="n">
         <v>234544</v>
@@ -44565,7 +44565,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.85106813907623</v>
+        <v>1.85106825828552</v>
       </c>
       <c r="H1524" t="n">
         <v>117717</v>
@@ -44623,7 +44623,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.84231615066528</v>
+        <v>1.84231603145599</v>
       </c>
       <c r="H1526" t="n">
         <v>74592</v>
@@ -44652,7 +44652,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419641971588</v>
       </c>
       <c r="H1527" t="n">
         <v>273420</v>
@@ -44681,7 +44681,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.90358066558838</v>
+        <v>1.90358078479767</v>
       </c>
       <c r="H1528" t="n">
         <v>604117</v>
@@ -44710,7 +44710,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.8904527425766</v>
+        <v>1.89045262336731</v>
       </c>
       <c r="H1529" t="n">
         <v>254393</v>
@@ -44768,7 +44768,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419641971588</v>
       </c>
       <c r="H1531" t="n">
         <v>96323</v>
@@ -44826,7 +44826,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419641971588</v>
       </c>
       <c r="H1533" t="n">
         <v>65005</v>
@@ -44855,7 +44855,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.84669196605682</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1534" t="n">
         <v>84536</v>
@@ -44884,7 +44884,7 @@
         <v>2.125</v>
       </c>
       <c r="G1535" t="n">
-        <v>1.85982036590576</v>
+        <v>1.85982024669647</v>
       </c>
       <c r="H1535" t="n">
         <v>80682</v>
@@ -44913,7 +44913,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.84669196605682</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1536" t="n">
         <v>166806</v>
@@ -44942,7 +44942,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.83793997764587</v>
+        <v>1.83794009685516</v>
       </c>
       <c r="H1537" t="n">
         <v>87274</v>
@@ -45029,7 +45029,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1540" t="n">
-        <v>1.80730772018433</v>
+        <v>1.80730783939362</v>
       </c>
       <c r="H1540" t="n">
         <v>124792</v>
@@ -45087,7 +45087,7 @@
         <v>2</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.75041902065277</v>
+        <v>1.75041913986206</v>
       </c>
       <c r="H1542" t="n">
         <v>265279</v>
@@ -45116,7 +45116,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1543" t="n">
         <v>202207</v>
@@ -45145,7 +45145,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.78980350494385</v>
+        <v>1.78980362415314</v>
       </c>
       <c r="H1544" t="n">
         <v>169992</v>
@@ -45174,7 +45174,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.84669196605682</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1545" t="n">
         <v>230077</v>
@@ -45261,7 +45261,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.83793997764587</v>
+        <v>1.83794009685516</v>
       </c>
       <c r="H1548" t="n">
         <v>268263</v>
@@ -45290,7 +45290,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.82918775081635</v>
+        <v>1.82918798923492</v>
       </c>
       <c r="H1549" t="n">
         <v>247301</v>
@@ -45435,7 +45435,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1554" t="n">
-        <v>1.80293154716492</v>
+        <v>1.80293166637421</v>
       </c>
       <c r="H1554" t="n">
         <v>198028</v>
@@ -45464,7 +45464,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.84231615066528</v>
+        <v>1.84231603145599</v>
       </c>
       <c r="H1555" t="n">
         <v>375561</v>
@@ -45493,7 +45493,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.85106813907623</v>
+        <v>1.85106825828552</v>
       </c>
       <c r="H1556" t="n">
         <v>222785</v>
@@ -45522,7 +45522,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.84669196605682</v>
+        <v>1.84669208526611</v>
       </c>
       <c r="H1557" t="n">
         <v>393196</v>
@@ -45551,7 +45551,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.8904527425766</v>
+        <v>1.89045262336731</v>
       </c>
       <c r="H1558" t="n">
         <v>351717</v>
@@ -45580,7 +45580,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.89482855796814</v>
+        <v>1.89482867717743</v>
       </c>
       <c r="H1559" t="n">
         <v>227065</v>
@@ -45609,7 +45609,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.86419653892517</v>
+        <v>1.86419641971588</v>
       </c>
       <c r="H1560" t="n">
         <v>167809</v>
@@ -45638,7 +45638,7 @@
         <v>2.125</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.85982036590576</v>
+        <v>1.85982024669647</v>
       </c>
       <c r="H1561" t="n">
         <v>125973</v>
@@ -45696,7 +45696,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.80293154716492</v>
+        <v>1.80293166637421</v>
       </c>
       <c r="H1563" t="n">
         <v>167475</v>
@@ -45812,7 +45812,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.71716117858887</v>
+        <v>1.71716105937958</v>
       </c>
       <c r="H1567" t="n">
         <v>173759</v>
@@ -45870,7 +45870,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1569" t="n">
-        <v>1.70665860176086</v>
+        <v>1.70665872097015</v>
       </c>
       <c r="H1569" t="n">
         <v>255789</v>
@@ -45928,7 +45928,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1571" t="n">
-        <v>1.51936376094818</v>
+        <v>1.51936364173889</v>
       </c>
       <c r="H1571" t="n">
         <v>327505</v>
@@ -45986,7 +45986,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.51586282253265</v>
+        <v>1.51586294174194</v>
       </c>
       <c r="H1573" t="n">
         <v>227012</v>
@@ -46015,7 +46015,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1574" t="n">
-        <v>1.62438893318176</v>
+        <v>1.62438881397247</v>
       </c>
       <c r="H1574" t="n">
         <v>243572</v>
@@ -46102,7 +46102,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G1577" t="n">
-        <v>1.612135887146</v>
+        <v>1.61213600635529</v>
       </c>
       <c r="H1577" t="n">
         <v>150185</v>
@@ -46160,7 +46160,7 @@
         <v>1.95200002193451</v>
       </c>
       <c r="G1579" t="n">
-        <v>1.70840895175934</v>
+        <v>1.70840907096863</v>
       </c>
       <c r="H1579" t="n">
         <v>240111</v>
@@ -46218,7 +46218,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.63139057159424</v>
+        <v>1.63139069080353</v>
       </c>
       <c r="H1581" t="n">
         <v>227110</v>
@@ -46247,7 +46247,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.70665860176086</v>
+        <v>1.70665872097015</v>
       </c>
       <c r="H1582" t="n">
         <v>224919</v>
@@ -46276,7 +46276,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.74166691303253</v>
+        <v>1.74166703224182</v>
       </c>
       <c r="H1583" t="n">
         <v>179140</v>
@@ -46305,7 +46305,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.72766363620758</v>
+        <v>1.72766375541687</v>
       </c>
       <c r="H1584" t="n">
         <v>377494</v>
@@ -46334,7 +46334,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.72766363620758</v>
+        <v>1.72766375541687</v>
       </c>
       <c r="H1585" t="n">
         <v>187746</v>
@@ -46363,7 +46363,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.7311646938324</v>
+        <v>1.73116457462311</v>
       </c>
       <c r="H1586" t="n">
         <v>271843</v>
@@ -46450,7 +46450,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.83356392383575</v>
+        <v>1.83356404304504</v>
       </c>
       <c r="H1589" t="n">
         <v>214150</v>
@@ -46508,7 +46508,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.82918775081635</v>
+        <v>1.82918798923492</v>
       </c>
       <c r="H1591" t="n">
         <v>165528</v>
@@ -46595,7 +46595,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1594" t="n">
         <v>242325</v>
@@ -46682,7 +46682,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1597" t="n">
-        <v>1.76354730129242</v>
+        <v>1.76354742050171</v>
       </c>
       <c r="H1597" t="n">
         <v>75680</v>
@@ -46711,7 +46711,7 @@
         <v>2</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.75041902065277</v>
+        <v>1.75041913986206</v>
       </c>
       <c r="H1598" t="n">
         <v>245023</v>
@@ -46740,7 +46740,7 @@
         <v>2</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.75041902065277</v>
+        <v>1.75041913986206</v>
       </c>
       <c r="H1599" t="n">
         <v>74660</v>
@@ -46769,7 +46769,7 @@
         <v>2</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.75041902065277</v>
+        <v>1.75041913986206</v>
       </c>
       <c r="H1600" t="n">
         <v>109946</v>
@@ -46827,7 +46827,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1602" t="n">
-        <v>1.78980350494385</v>
+        <v>1.78980362415314</v>
       </c>
       <c r="H1602" t="n">
         <v>73878</v>
@@ -46856,7 +46856,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.79855561256409</v>
+        <v>1.79855573177338</v>
       </c>
       <c r="H1603" t="n">
         <v>105903</v>
@@ -46943,7 +46943,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.76792323589325</v>
+        <v>1.76792335510254</v>
       </c>
       <c r="H1606" t="n">
         <v>44910</v>
@@ -47001,7 +47001,7 @@
         <v>2</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.75041902065277</v>
+        <v>1.75041913986206</v>
       </c>
       <c r="H1608" t="n">
         <v>83651</v>
@@ -47146,7 +47146,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.81932306289673</v>
+        <v>1.81932294368744</v>
       </c>
       <c r="H1613" t="n">
         <v>252942</v>
@@ -47175,7 +47175,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.81932306289673</v>
+        <v>1.81932294368744</v>
       </c>
       <c r="H1614" t="n">
         <v>85301</v>
@@ -47291,7 +47291,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.84200775623322</v>
+        <v>1.84200763702393</v>
       </c>
       <c r="H1618" t="n">
         <v>223312</v>
@@ -47378,7 +47378,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.80389726161957</v>
+        <v>1.80389714241028</v>
       </c>
       <c r="H1621" t="n">
         <v>394095</v>
@@ -47726,7 +47726,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.8329336643219</v>
+        <v>1.83293378353119</v>
       </c>
       <c r="H1633" t="n">
         <v>54268</v>
@@ -47813,7 +47813,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1636" t="n">
-        <v>1.8329336643219</v>
+        <v>1.83293378353119</v>
       </c>
       <c r="H1636" t="n">
         <v>72431</v>
@@ -47987,7 +47987,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.72767615318298</v>
+        <v>1.72767627239227</v>
       </c>
       <c r="H1642" t="n">
         <v>156172</v>
@@ -48074,7 +48074,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1645" t="n">
-        <v>1.73312044143677</v>
+        <v>1.73312056064606</v>
       </c>
       <c r="H1645" t="n">
         <v>475615</v>
@@ -48161,7 +48161,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.52260541915894</v>
+        <v>1.52260529994965</v>
       </c>
       <c r="H1648" t="n">
         <v>1949495</v>
@@ -48219,7 +48219,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.49356877803802</v>
+        <v>1.49356889724731</v>
       </c>
       <c r="H1650" t="n">
         <v>173295</v>
@@ -48364,7 +48364,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1655" t="n">
         <v>120876</v>
@@ -48480,7 +48480,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1659" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1659" t="n">
         <v>56913</v>
@@ -48509,7 +48509,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.4227921962738</v>
+        <v>1.42279207706451</v>
       </c>
       <c r="H1660" t="n">
         <v>55532</v>
@@ -48596,7 +48596,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.30301630496979</v>
+        <v>1.3030161857605</v>
       </c>
       <c r="H1663" t="n">
         <v>152257</v>
@@ -48741,7 +48741,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.34294164180756</v>
+        <v>1.34294152259827</v>
       </c>
       <c r="H1668" t="n">
         <v>271091</v>
@@ -48770,7 +48770,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.33023798465729</v>
+        <v>1.33023810386658</v>
       </c>
       <c r="H1669" t="n">
         <v>81019</v>
@@ -49031,7 +49031,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1678" t="n">
-        <v>1.48449492454529</v>
+        <v>1.484494805336</v>
       </c>
       <c r="H1678" t="n">
         <v>178787</v>
@@ -49089,7 +49089,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.46271753311157</v>
+        <v>1.46271741390228</v>
       </c>
       <c r="H1680" t="n">
         <v>70226</v>
@@ -49118,7 +49118,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.44638431072235</v>
+        <v>1.44638442993164</v>
       </c>
       <c r="H1681" t="n">
         <v>85701</v>
@@ -49147,7 +49147,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.46271753311157</v>
+        <v>1.46271741390228</v>
       </c>
       <c r="H1682" t="n">
         <v>16925</v>
@@ -49205,7 +49205,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.46997654438019</v>
+        <v>1.46997666358948</v>
       </c>
       <c r="H1684" t="n">
         <v>105058</v>
@@ -49437,7 +49437,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.41734790802002</v>
+        <v>1.41734778881073</v>
       </c>
       <c r="H1692" t="n">
         <v>38155</v>
@@ -49669,7 +49669,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.38649642467499</v>
+        <v>1.38649654388428</v>
       </c>
       <c r="H1700" t="n">
         <v>49851</v>
@@ -49698,7 +49698,7 @@
         <v>1.5</v>
       </c>
       <c r="G1701" t="n">
-        <v>1.36108946800232</v>
+        <v>1.36108934879303</v>
       </c>
       <c r="H1701" t="n">
         <v>59908</v>
@@ -49727,7 +49727,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1702" t="n">
         <v>34634</v>
@@ -49959,7 +49959,7 @@
         <v>1.5</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.36108946800232</v>
+        <v>1.36108934879303</v>
       </c>
       <c r="H1710" t="n">
         <v>49351</v>
@@ -50133,7 +50133,7 @@
         <v>1.35599994659424</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.23042476177216</v>
+        <v>1.23042488098145</v>
       </c>
       <c r="H1716" t="n">
         <v>157421</v>
@@ -50394,7 +50394,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.27760934829712</v>
+        <v>1.27760922908783</v>
       </c>
       <c r="H1725" t="n">
         <v>68993</v>
@@ -50452,7 +50452,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.26127624511719</v>
+        <v>1.2612761259079</v>
       </c>
       <c r="H1727" t="n">
         <v>71841</v>
@@ -50481,7 +50481,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.24312841892242</v>
+        <v>1.24312829971313</v>
       </c>
       <c r="H1728" t="n">
         <v>93267</v>
@@ -50800,7 +50800,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.34657108783722</v>
+        <v>1.34657120704651</v>
       </c>
       <c r="H1739" t="n">
         <v>55655</v>
@@ -50829,7 +50829,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.33023798465729</v>
+        <v>1.33023810386658</v>
       </c>
       <c r="H1740" t="n">
         <v>97865</v>
@@ -50858,7 +50858,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.29031276702881</v>
+        <v>1.2903128862381</v>
       </c>
       <c r="H1741" t="n">
         <v>74502</v>
@@ -50945,7 +50945,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.37923717498779</v>
+        <v>1.37923729419708</v>
       </c>
       <c r="H1744" t="n">
         <v>94379</v>
@@ -50974,7 +50974,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.34475636482239</v>
+        <v>1.3447562456131</v>
       </c>
       <c r="H1745" t="n">
         <v>93982</v>
@@ -51003,7 +51003,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.34294164180756</v>
+        <v>1.34294152259827</v>
       </c>
       <c r="H1746" t="n">
         <v>103418</v>
@@ -51264,7 +51264,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.40101480484009</v>
+        <v>1.4010146856308</v>
       </c>
       <c r="H1755" t="n">
         <v>78871</v>
@@ -51351,7 +51351,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.40101480484009</v>
+        <v>1.4010146856308</v>
       </c>
       <c r="H1758" t="n">
         <v>39021</v>
@@ -51380,7 +51380,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.41734790802002</v>
+        <v>1.41734778881073</v>
       </c>
       <c r="H1759" t="n">
         <v>64502</v>
@@ -51467,7 +51467,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1762" t="n">
         <v>118998</v>
@@ -51699,7 +51699,7 @@
         <v>1.5</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.36108946800232</v>
+        <v>1.36108934879303</v>
       </c>
       <c r="H1770" t="n">
         <v>53618</v>
@@ -51728,7 +51728,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.37742257118225</v>
+        <v>1.37742245197296</v>
       </c>
       <c r="H1771" t="n">
         <v>97921</v>
@@ -51757,7 +51757,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.37742257118225</v>
+        <v>1.37742245197296</v>
       </c>
       <c r="H1772" t="n">
         <v>72275</v>
@@ -51844,7 +51844,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.34657108783722</v>
+        <v>1.34657120704651</v>
       </c>
       <c r="H1775" t="n">
         <v>21041</v>
@@ -51989,7 +51989,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.37923717498779</v>
+        <v>1.37923729419708</v>
       </c>
       <c r="H1780" t="n">
         <v>51470</v>
@@ -52192,7 +52192,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1787" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1787" t="n">
         <v>145760</v>
@@ -52221,7 +52221,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.46271753311157</v>
+        <v>1.46271741390228</v>
       </c>
       <c r="H1788" t="n">
         <v>116404</v>
@@ -52279,7 +52279,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.49356877803802</v>
+        <v>1.49356889724731</v>
       </c>
       <c r="H1790" t="n">
         <v>115523</v>
@@ -52337,7 +52337,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.46997654438019</v>
+        <v>1.46997666358948</v>
       </c>
       <c r="H1792" t="n">
         <v>35842</v>
@@ -52540,7 +52540,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.48449492454529</v>
+        <v>1.484494805336</v>
       </c>
       <c r="H1799" t="n">
         <v>148023</v>
@@ -52743,7 +52743,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.6242333650589</v>
+        <v>1.62423324584961</v>
       </c>
       <c r="H1806" t="n">
         <v>403949</v>
@@ -52859,7 +52859,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.62786293029785</v>
+        <v>1.62786304950714</v>
       </c>
       <c r="H1810" t="n">
         <v>198945</v>
@@ -52975,7 +52975,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1814" t="n">
-        <v>1.48449492454529</v>
+        <v>1.484494805336</v>
       </c>
       <c r="H1814" t="n">
         <v>499202</v>
@@ -53120,7 +53120,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1819" t="n">
-        <v>1.44275486469269</v>
+        <v>1.4427547454834</v>
       </c>
       <c r="H1819" t="n">
         <v>217610</v>
@@ -53265,7 +53265,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.37742257118225</v>
+        <v>1.37742245197296</v>
       </c>
       <c r="H1824" t="n">
         <v>270982</v>
@@ -53294,7 +53294,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1825" t="n">
         <v>120972</v>
@@ -53352,7 +53352,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.37923717498779</v>
+        <v>1.37923729419708</v>
       </c>
       <c r="H1827" t="n">
         <v>53687</v>
@@ -53410,7 +53410,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1829" t="n">
-        <v>1.38286697864532</v>
+        <v>1.38286685943604</v>
       </c>
       <c r="H1829" t="n">
         <v>94628</v>
@@ -53497,7 +53497,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.37379288673401</v>
+        <v>1.3737930059433</v>
       </c>
       <c r="H1832" t="n">
         <v>244109</v>
@@ -53729,7 +53729,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.27397966384888</v>
+        <v>1.27397978305817</v>
       </c>
       <c r="H1840" t="n">
         <v>208171</v>
@@ -53758,7 +53758,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.24675786495209</v>
+        <v>1.24675798416138</v>
       </c>
       <c r="H1841" t="n">
         <v>378238</v>
@@ -53816,7 +53816,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1843" t="n">
-        <v>1.21409177780151</v>
+        <v>1.2140918970108</v>
       </c>
       <c r="H1843" t="n">
         <v>719768</v>
@@ -53903,7 +53903,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.23949873447418</v>
+        <v>1.23949885368347</v>
       </c>
       <c r="H1846" t="n">
         <v>172765</v>
@@ -53932,7 +53932,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1847" t="n">
         <v>129520</v>
@@ -54077,7 +54077,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1852" t="n">
         <v>279885</v>
@@ -54164,7 +54164,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1855" t="n">
         <v>312198</v>
@@ -54251,7 +54251,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.23405432701111</v>
+        <v>1.2340544462204</v>
       </c>
       <c r="H1858" t="n">
         <v>147893</v>
@@ -54309,7 +54309,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.21409177780151</v>
+        <v>1.2140918970108</v>
       </c>
       <c r="H1860" t="n">
         <v>113649</v>
@@ -54396,7 +54396,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.21409177780151</v>
+        <v>1.2140918970108</v>
       </c>
       <c r="H1863" t="n">
         <v>154799</v>
@@ -79980,6 +79980,35 @@
         <v>121</v>
       </c>
       <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>1.57200002670288</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>1.5440000295639</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>1.57200002670288</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>1.57200002670288</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>6552</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74831414222717</v>
+        <v>2.74831390380859</v>
       </c>
       <c r="H2" t="n">
         <v>11649</v>
@@ -456,7 +456,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>2.69898509979248</v>
+        <v>2.69898533821106</v>
       </c>
       <c r="H3" t="n">
         <v>10338</v>
@@ -485,7 +485,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74831414222717</v>
+        <v>2.74831390380859</v>
       </c>
       <c r="H4" t="n">
         <v>9462</v>
@@ -514,7 +514,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G5" t="n">
-        <v>2.68630123138428</v>
+        <v>2.68630075454712</v>
       </c>
       <c r="H5" t="n">
         <v>17322</v>
@@ -543,7 +543,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G6" t="n">
-        <v>2.75958967208862</v>
+        <v>2.75958919525146</v>
       </c>
       <c r="H6" t="n">
         <v>23950</v>
@@ -688,7 +688,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G11" t="n">
-        <v>2.48757648468018</v>
+        <v>2.48757672309875</v>
       </c>
       <c r="H11" t="n">
         <v>21140</v>
@@ -717,7 +717,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36073112487793</v>
+        <v>2.36073136329651</v>
       </c>
       <c r="H12" t="n">
         <v>72103</v>
@@ -746,7 +746,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G13" t="n">
-        <v>2.39314746856689</v>
+        <v>2.39314723014832</v>
       </c>
       <c r="H13" t="n">
         <v>77275</v>
@@ -775,7 +775,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>2.43824815750122</v>
+        <v>2.43824791908264</v>
       </c>
       <c r="H14" t="n">
         <v>56306</v>
@@ -804,7 +804,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.50167036056519</v>
+        <v>2.50167083740234</v>
       </c>
       <c r="H15" t="n">
         <v>141373</v>
@@ -862,7 +862,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>2.45234179496765</v>
+        <v>2.45234203338623</v>
       </c>
       <c r="H17" t="n">
         <v>23673</v>
@@ -891,7 +891,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G18" t="n">
-        <v>2.39737558364868</v>
+        <v>2.3973753452301</v>
       </c>
       <c r="H18" t="n">
         <v>28661</v>
@@ -949,7 +949,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G20" t="n">
-        <v>2.29730892181396</v>
+        <v>2.29730868339539</v>
       </c>
       <c r="H20" t="n">
         <v>15863</v>
@@ -1007,7 +1007,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G22" t="n">
-        <v>2.29871821403503</v>
+        <v>2.29871797561646</v>
       </c>
       <c r="H22" t="n">
         <v>226114</v>
@@ -1065,7 +1065,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G24" t="n">
-        <v>1.97455763816833</v>
+        <v>1.97455811500549</v>
       </c>
       <c r="H24" t="n">
         <v>138010</v>
@@ -1094,7 +1094,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G25" t="n">
-        <v>1.8744912147522</v>
+        <v>1.87449133396149</v>
       </c>
       <c r="H25" t="n">
         <v>340240</v>
@@ -1123,7 +1123,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G26" t="n">
-        <v>1.86885368824005</v>
+        <v>1.86885356903076</v>
       </c>
       <c r="H26" t="n">
         <v>671185</v>
@@ -1152,7 +1152,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G27" t="n">
-        <v>1.72650504112244</v>
+        <v>1.72650516033173</v>
       </c>
       <c r="H27" t="n">
         <v>216589</v>
@@ -1210,7 +1210,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G29" t="n">
-        <v>1.8603972196579</v>
+        <v>1.86039745807648</v>
       </c>
       <c r="H29" t="n">
         <v>494650</v>
@@ -1239,7 +1239,7 @@
         <v>2.5</v>
       </c>
       <c r="G30" t="n">
-        <v>1.76173973083496</v>
+        <v>1.76173985004425</v>
       </c>
       <c r="H30" t="n">
         <v>322108</v>
@@ -1268,7 +1268,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G31" t="n">
-        <v>1.87731003761292</v>
+        <v>1.87730991840363</v>
       </c>
       <c r="H31" t="n">
         <v>154548</v>
@@ -1297,7 +1297,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G32" t="n">
-        <v>1.94777965545654</v>
+        <v>1.94777953624725</v>
       </c>
       <c r="H32" t="n">
         <v>56948</v>
@@ -1384,7 +1384,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G35" t="n">
-        <v>2.05207419395447</v>
+        <v>2.05207443237305</v>
       </c>
       <c r="H35" t="n">
         <v>184129</v>
@@ -1413,7 +1413,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G36" t="n">
-        <v>2.09294724464417</v>
+        <v>2.09294676780701</v>
       </c>
       <c r="H36" t="n">
         <v>286614</v>
@@ -1442,7 +1442,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G37" t="n">
-        <v>2.15918803215027</v>
+        <v>2.15918850898743</v>
       </c>
       <c r="H37" t="n">
         <v>158423</v>
@@ -1471,7 +1471,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G38" t="n">
-        <v>2.1605978012085</v>
+        <v>2.16059803962708</v>
       </c>
       <c r="H38" t="n">
         <v>79649</v>
@@ -1500,7 +1500,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G39" t="n">
-        <v>2.04784655570984</v>
+        <v>2.04784631729126</v>
       </c>
       <c r="H39" t="n">
         <v>22200</v>
@@ -1529,7 +1529,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G40" t="n">
-        <v>2.06616830825806</v>
+        <v>2.06616854667664</v>
       </c>
       <c r="H40" t="n">
         <v>10895</v>
@@ -1558,7 +1558,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>2.05771207809448</v>
+        <v>2.05771231651306</v>
       </c>
       <c r="H41" t="n">
         <v>58452</v>
@@ -1587,7 +1587,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G42" t="n">
-        <v>2.06334948539734</v>
+        <v>2.06334972381592</v>
       </c>
       <c r="H42" t="n">
         <v>7283</v>
@@ -1674,7 +1674,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G45" t="n">
-        <v>2.13522839546204</v>
+        <v>2.13522863388062</v>
       </c>
       <c r="H45" t="n">
         <v>141970</v>
@@ -1703,7 +1703,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G46" t="n">
-        <v>2.15777897834778</v>
+        <v>2.1577787399292</v>
       </c>
       <c r="H46" t="n">
         <v>65121</v>
@@ -1790,7 +1790,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>2.12818169593811</v>
+        <v>2.12818193435669</v>
       </c>
       <c r="H49" t="n">
         <v>64501</v>
@@ -1819,7 +1819,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G50" t="n">
-        <v>2.12677240371704</v>
+        <v>2.12677216529846</v>
       </c>
       <c r="H50" t="n">
         <v>93185</v>
@@ -1848,7 +1848,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G51" t="n">
-        <v>2.21274518966675</v>
+        <v>2.21274542808533</v>
       </c>
       <c r="H51" t="n">
         <v>169907</v>
@@ -1877,7 +1877,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G52" t="n">
-        <v>2.26348328590393</v>
+        <v>2.26348352432251</v>
       </c>
       <c r="H52" t="n">
         <v>74146</v>
@@ -1935,7 +1935,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G54" t="n">
-        <v>2.17469167709351</v>
+        <v>2.17469143867493</v>
       </c>
       <c r="H54" t="n">
         <v>139285</v>
@@ -2022,7 +2022,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G57" t="n">
-        <v>2.20147037506104</v>
+        <v>2.20147013664246</v>
       </c>
       <c r="H57" t="n">
         <v>49719</v>
@@ -2080,7 +2080,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>2.17751049995422</v>
+        <v>2.17751026153564</v>
       </c>
       <c r="H59" t="n">
         <v>71887</v>
@@ -2138,7 +2138,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G61" t="n">
-        <v>2.18314790725708</v>
+        <v>2.18314814567566</v>
       </c>
       <c r="H61" t="n">
         <v>10022</v>
@@ -2167,7 +2167,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>2.12818169593811</v>
+        <v>2.12818193435669</v>
       </c>
       <c r="H62" t="n">
         <v>20518</v>
@@ -2196,7 +2196,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G63" t="n">
-        <v>1.97737681865692</v>
+        <v>1.97737693786621</v>
       </c>
       <c r="H63" t="n">
         <v>35478</v>
@@ -2283,7 +2283,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G66" t="n">
-        <v>1.94496083259583</v>
+        <v>1.9449610710144</v>
       </c>
       <c r="H66" t="n">
         <v>23053</v>
@@ -2341,7 +2341,7 @@
         <v>2.71600008010864</v>
       </c>
       <c r="G68" t="n">
-        <v>1.91395425796509</v>
+        <v>1.91395390033722</v>
       </c>
       <c r="H68" t="n">
         <v>32713</v>
@@ -2399,7 +2399,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>1.97455763816833</v>
+        <v>1.97455811500549</v>
       </c>
       <c r="H70" t="n">
         <v>68876</v>
@@ -2428,7 +2428,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>1.92382001876831</v>
+        <v>1.92381978034973</v>
       </c>
       <c r="H71" t="n">
         <v>17504</v>
@@ -2515,7 +2515,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G74" t="n">
-        <v>2.06616830825806</v>
+        <v>2.06616854667664</v>
       </c>
       <c r="H74" t="n">
         <v>97706</v>
@@ -2573,7 +2573,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>2.17046356201172</v>
+        <v>2.17046332359314</v>
       </c>
       <c r="H76" t="n">
         <v>157055</v>
@@ -2631,7 +2631,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G78" t="n">
-        <v>2.17751049995422</v>
+        <v>2.17751026153564</v>
       </c>
       <c r="H78" t="n">
         <v>77091</v>
@@ -2660,7 +2660,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G79" t="n">
-        <v>2.18032932281494</v>
+        <v>2.18032908439636</v>
       </c>
       <c r="H79" t="n">
         <v>73179</v>
@@ -2747,7 +2747,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G82" t="n">
-        <v>2.05771207809448</v>
+        <v>2.05771231651306</v>
       </c>
       <c r="H82" t="n">
         <v>255389</v>
@@ -2834,7 +2834,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G85" t="n">
-        <v>1.94918930530548</v>
+        <v>1.94918918609619</v>
       </c>
       <c r="H85" t="n">
         <v>142278</v>
@@ -2892,7 +2892,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G87" t="n">
-        <v>1.95623600482941</v>
+        <v>1.95623564720154</v>
       </c>
       <c r="H87" t="n">
         <v>73663</v>
@@ -2921,7 +2921,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G88" t="n">
-        <v>1.89845085144043</v>
+        <v>1.89845061302185</v>
       </c>
       <c r="H88" t="n">
         <v>36792</v>
@@ -2950,7 +2950,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G89" t="n">
-        <v>1.86321592330933</v>
+        <v>1.86321604251862</v>
       </c>
       <c r="H89" t="n">
         <v>23082</v>
@@ -2979,7 +2979,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>1.8768789768219</v>
+        <v>1.87687909603119</v>
       </c>
       <c r="H90" t="n">
         <v>235784</v>
@@ -3008,7 +3008,7 @@
         <v>2.5</v>
       </c>
       <c r="G91" t="n">
-        <v>1.79777681827545</v>
+        <v>1.79777693748474</v>
       </c>
       <c r="H91" t="n">
         <v>242021</v>
@@ -3095,7 +3095,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G94" t="n">
-        <v>1.681281208992</v>
+        <v>1.68128097057343</v>
       </c>
       <c r="H94" t="n">
         <v>97874</v>
@@ -3153,7 +3153,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62662863731384</v>
+        <v>1.62662851810455</v>
       </c>
       <c r="H96" t="n">
         <v>316466</v>
@@ -3182,7 +3182,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G97" t="n">
-        <v>1.63957250118256</v>
+        <v>1.63957273960114</v>
       </c>
       <c r="H97" t="n">
         <v>216744</v>
@@ -3211,7 +3211,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.60361707210541</v>
+        <v>1.60361695289612</v>
       </c>
       <c r="H98" t="n">
         <v>199551</v>
@@ -3240,7 +3240,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.60361707210541</v>
+        <v>1.60361695289612</v>
       </c>
       <c r="H99" t="n">
         <v>183461</v>
@@ -3269,7 +3269,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G100" t="n">
-        <v>1.63957250118256</v>
+        <v>1.63957273960114</v>
       </c>
       <c r="H100" t="n">
         <v>213463</v>
@@ -3298,7 +3298,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G101" t="n">
-        <v>1.68991041183472</v>
+        <v>1.68991029262543</v>
       </c>
       <c r="H101" t="n">
         <v>233008</v>
@@ -3327,7 +3327,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G102" t="n">
-        <v>1.78914761543274</v>
+        <v>1.78914737701416</v>
       </c>
       <c r="H102" t="n">
         <v>446680</v>
@@ -3356,7 +3356,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G103" t="n">
-        <v>1.86249709129333</v>
+        <v>1.86249685287476</v>
       </c>
       <c r="H103" t="n">
         <v>317819</v>
@@ -3414,7 +3414,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G105" t="n">
-        <v>1.86249709129333</v>
+        <v>1.86249685287476</v>
       </c>
       <c r="H105" t="n">
         <v>30183</v>
@@ -3472,7 +3472,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>1.81215929985046</v>
+        <v>1.81215918064117</v>
       </c>
       <c r="H107" t="n">
         <v>68874</v>
@@ -3501,7 +3501,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>1.82654130458832</v>
+        <v>1.8265415430069</v>
       </c>
       <c r="H108" t="n">
         <v>6332</v>
@@ -3530,7 +3530,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G109" t="n">
-        <v>1.79490065574646</v>
+        <v>1.79490077495575</v>
       </c>
       <c r="H109" t="n">
         <v>138260</v>
@@ -3559,7 +3559,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G110" t="n">
-        <v>1.83517098426819</v>
+        <v>1.83517074584961</v>
       </c>
       <c r="H110" t="n">
         <v>87116</v>
@@ -3588,7 +3588,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G111" t="n">
-        <v>1.83948540687561</v>
+        <v>1.83948528766632</v>
       </c>
       <c r="H111" t="n">
         <v>113743</v>
@@ -3646,7 +3646,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G113" t="n">
-        <v>1.80496823787689</v>
+        <v>1.80496799945831</v>
       </c>
       <c r="H113" t="n">
         <v>31915</v>
@@ -3675,7 +3675,7 @@
         <v>2.5</v>
       </c>
       <c r="G114" t="n">
-        <v>1.79777681827545</v>
+        <v>1.79777693748474</v>
       </c>
       <c r="H114" t="n">
         <v>65250</v>
@@ -3733,7 +3733,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G116" t="n">
-        <v>1.72011280059814</v>
+        <v>1.72011291980743</v>
       </c>
       <c r="H116" t="n">
         <v>108775</v>
@@ -3762,7 +3762,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G117" t="n">
-        <v>1.73880994319916</v>
+        <v>1.73880982398987</v>
       </c>
       <c r="H117" t="n">
         <v>8962</v>
@@ -3791,7 +3791,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G118" t="n">
-        <v>1.63381969928741</v>
+        <v>1.6338198184967</v>
       </c>
       <c r="H118" t="n">
         <v>132672</v>
@@ -3878,7 +3878,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G121" t="n">
-        <v>1.7531920671463</v>
+        <v>1.75319218635559</v>
       </c>
       <c r="H121" t="n">
         <v>37124</v>
@@ -3907,7 +3907,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>1.81215929985046</v>
+        <v>1.81215918064117</v>
       </c>
       <c r="H122" t="n">
         <v>185327</v>
@@ -3994,7 +3994,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G125" t="n">
-        <v>1.48999762535095</v>
+        <v>1.48999738693237</v>
       </c>
       <c r="H125" t="n">
         <v>94566</v>
@@ -4023,7 +4023,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G126" t="n">
-        <v>1.53026783466339</v>
+        <v>1.5302677154541</v>
       </c>
       <c r="H126" t="n">
         <v>255565</v>
@@ -4081,7 +4081,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H128" t="n">
         <v>171705</v>
@@ -4110,7 +4110,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G129" t="n">
-        <v>1.47561538219452</v>
+        <v>1.47561526298523</v>
       </c>
       <c r="H129" t="n">
         <v>141074</v>
@@ -4139,7 +4139,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G130" t="n">
-        <v>1.49287402629852</v>
+        <v>1.49287390708923</v>
       </c>
       <c r="H130" t="n">
         <v>120762</v>
@@ -4226,7 +4226,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G133" t="n">
-        <v>1.5086944103241</v>
+        <v>1.50869452953339</v>
       </c>
       <c r="H133" t="n">
         <v>18201</v>
@@ -4284,7 +4284,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G135" t="n">
-        <v>1.56047058105469</v>
+        <v>1.5604704618454</v>
       </c>
       <c r="H135" t="n">
         <v>94625</v>
@@ -4313,7 +4313,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G136" t="n">
-        <v>1.63238131999969</v>
+        <v>1.63238155841827</v>
       </c>
       <c r="H136" t="n">
         <v>98434</v>
@@ -4342,7 +4342,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G137" t="n">
-        <v>1.63381969928741</v>
+        <v>1.6338198184967</v>
       </c>
       <c r="H137" t="n">
         <v>41464</v>
@@ -4371,7 +4371,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G138" t="n">
-        <v>1.65395486354828</v>
+        <v>1.65395474433899</v>
       </c>
       <c r="H138" t="n">
         <v>51689</v>
@@ -4574,7 +4574,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G145" t="n">
-        <v>1.5130090713501</v>
+        <v>1.51300930976868</v>
       </c>
       <c r="H145" t="n">
         <v>118150</v>
@@ -4603,7 +4603,7 @@
         <v>2.12599992752075</v>
       </c>
       <c r="G146" t="n">
-        <v>1.52882957458496</v>
+        <v>1.52882945537567</v>
       </c>
       <c r="H146" t="n">
         <v>27532</v>
@@ -4661,7 +4661,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G148" t="n">
-        <v>1.48855924606323</v>
+        <v>1.48855936527252</v>
       </c>
       <c r="H148" t="n">
         <v>109814</v>
@@ -4690,7 +4690,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G149" t="n">
-        <v>1.51876199245453</v>
+        <v>1.51876187324524</v>
       </c>
       <c r="H149" t="n">
         <v>255392</v>
@@ -4719,7 +4719,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G150" t="n">
-        <v>1.48855924606323</v>
+        <v>1.48855936527252</v>
       </c>
       <c r="H150" t="n">
         <v>211962</v>
@@ -4806,7 +4806,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G153" t="n">
-        <v>1.34401822090149</v>
+        <v>1.34401786327362</v>
       </c>
       <c r="H153" t="n">
         <v>101071</v>
@@ -4835,7 +4835,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G154" t="n">
-        <v>1.42959237098694</v>
+        <v>1.42959225177765</v>
       </c>
       <c r="H154" t="n">
         <v>120160</v>
@@ -4864,7 +4864,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G155" t="n">
-        <v>1.43462610244751</v>
+        <v>1.43462598323822</v>
       </c>
       <c r="H155" t="n">
         <v>54589</v>
@@ -4893,7 +4893,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G156" t="n">
-        <v>1.44828903675079</v>
+        <v>1.44828915596008</v>
       </c>
       <c r="H156" t="n">
         <v>46189</v>
@@ -4922,7 +4922,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G157" t="n">
-        <v>1.48999762535095</v>
+        <v>1.48999738693237</v>
       </c>
       <c r="H157" t="n">
         <v>64387</v>
@@ -4951,7 +4951,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G158" t="n">
-        <v>1.48136830329895</v>
+        <v>1.48136818408966</v>
       </c>
       <c r="H158" t="n">
         <v>66888</v>
@@ -4980,7 +4980,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>1.56622326374054</v>
+        <v>1.56622338294983</v>
       </c>
       <c r="H159" t="n">
         <v>153564</v>
@@ -5009,7 +5009,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G160" t="n">
-        <v>1.53314411640167</v>
+        <v>1.53314423561096</v>
       </c>
       <c r="H160" t="n">
         <v>39208</v>
@@ -5038,7 +5038,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G161" t="n">
-        <v>1.50437963008881</v>
+        <v>1.50437986850739</v>
       </c>
       <c r="H161" t="n">
         <v>53000</v>
@@ -5096,7 +5096,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G163" t="n">
-        <v>1.49143552780151</v>
+        <v>1.49143576622009</v>
       </c>
       <c r="H163" t="n">
         <v>102808</v>
@@ -5125,7 +5125,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G164" t="n">
-        <v>1.51732361316681</v>
+        <v>1.5173237323761</v>
       </c>
       <c r="H164" t="n">
         <v>103001</v>
@@ -5154,7 +5154,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G165" t="n">
-        <v>1.53602051734924</v>
+        <v>1.53602063655853</v>
       </c>
       <c r="H165" t="n">
         <v>71695</v>
@@ -5212,7 +5212,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G167" t="n">
-        <v>1.54608821868896</v>
+        <v>1.54608833789825</v>
       </c>
       <c r="H167" t="n">
         <v>87448</v>
@@ -5328,7 +5328,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G171" t="n">
-        <v>1.5086944103241</v>
+        <v>1.50869452953339</v>
       </c>
       <c r="H171" t="n">
         <v>138864</v>
@@ -5415,7 +5415,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G174" t="n">
-        <v>1.56478524208069</v>
+        <v>1.5647851228714</v>
       </c>
       <c r="H174" t="n">
         <v>39718</v>
@@ -5502,7 +5502,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G177" t="n">
-        <v>1.56047058105469</v>
+        <v>1.5604704618454</v>
       </c>
       <c r="H177" t="n">
         <v>16139</v>
@@ -5589,7 +5589,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G180" t="n">
-        <v>1.49287402629852</v>
+        <v>1.49287390708923</v>
       </c>
       <c r="H180" t="n">
         <v>65474</v>
@@ -5647,7 +5647,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G182" t="n">
-        <v>1.4698623418808</v>
+        <v>1.46986246109009</v>
       </c>
       <c r="H182" t="n">
         <v>47947</v>
@@ -5705,7 +5705,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G184" t="n">
-        <v>1.48855924606323</v>
+        <v>1.48855936527252</v>
       </c>
       <c r="H184" t="n">
         <v>31709</v>
@@ -5734,7 +5734,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G185" t="n">
-        <v>1.47705352306366</v>
+        <v>1.47705340385437</v>
       </c>
       <c r="H185" t="n">
         <v>12250</v>
@@ -5763,7 +5763,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G186" t="n">
-        <v>1.48855924606323</v>
+        <v>1.48855936527252</v>
       </c>
       <c r="H186" t="n">
         <v>5248</v>
@@ -5792,7 +5792,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G187" t="n">
-        <v>1.48280644416809</v>
+        <v>1.48280656337738</v>
       </c>
       <c r="H187" t="n">
         <v>8172</v>
@@ -5821,7 +5821,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G188" t="n">
-        <v>1.48999762535095</v>
+        <v>1.48999738693237</v>
       </c>
       <c r="H188" t="n">
         <v>3505</v>
@@ -5879,7 +5879,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G190" t="n">
-        <v>1.4698623418808</v>
+        <v>1.46986246109009</v>
       </c>
       <c r="H190" t="n">
         <v>50388</v>
@@ -5908,7 +5908,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G191" t="n">
-        <v>1.48424446582794</v>
+        <v>1.48424458503723</v>
       </c>
       <c r="H191" t="n">
         <v>3174</v>
@@ -5937,7 +5937,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H192" t="n">
         <v>8474</v>
@@ -5966,7 +5966,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G193" t="n">
-        <v>1.4698623418808</v>
+        <v>1.46986246109009</v>
       </c>
       <c r="H193" t="n">
         <v>21732</v>
@@ -5995,7 +5995,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G194" t="n">
-        <v>1.46267116069794</v>
+        <v>1.46267127990723</v>
       </c>
       <c r="H194" t="n">
         <v>82859</v>
@@ -6024,7 +6024,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H195" t="n">
         <v>15113</v>
@@ -6053,7 +6053,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G196" t="n">
-        <v>1.51876199245453</v>
+        <v>1.51876187324524</v>
       </c>
       <c r="H196" t="n">
         <v>72181</v>
@@ -6169,7 +6169,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>1.68991041183472</v>
+        <v>1.68991029262543</v>
       </c>
       <c r="H200" t="n">
         <v>205807</v>
@@ -6198,7 +6198,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>1.68991041183472</v>
+        <v>1.68991029262543</v>
       </c>
       <c r="H201" t="n">
         <v>93341</v>
@@ -6256,7 +6256,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>1.68991041183472</v>
+        <v>1.68991029262543</v>
       </c>
       <c r="H203" t="n">
         <v>74895</v>
@@ -6285,7 +6285,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G204" t="n">
-        <v>1.68703389167786</v>
+        <v>1.68703377246857</v>
       </c>
       <c r="H204" t="n">
         <v>57861</v>
@@ -6372,7 +6372,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G207" t="n">
-        <v>1.73161900043488</v>
+        <v>1.73161864280701</v>
       </c>
       <c r="H207" t="n">
         <v>57561</v>
@@ -6401,7 +6401,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G208" t="n">
-        <v>1.73449540138245</v>
+        <v>1.73449516296387</v>
       </c>
       <c r="H208" t="n">
         <v>42982</v>
@@ -6430,7 +6430,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>1.74743950366974</v>
+        <v>1.74743902683258</v>
       </c>
       <c r="H209" t="n">
         <v>56802</v>
@@ -6517,7 +6517,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G212" t="n">
-        <v>1.71723663806915</v>
+        <v>1.71723675727844</v>
       </c>
       <c r="H212" t="n">
         <v>49779</v>
@@ -6546,7 +6546,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>1.74743950366974</v>
+        <v>1.74743902683258</v>
       </c>
       <c r="H213" t="n">
         <v>87327</v>
@@ -6662,7 +6662,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G217" t="n">
-        <v>1.55327939987183</v>
+        <v>1.55327951908112</v>
       </c>
       <c r="H217" t="n">
         <v>114963</v>
@@ -6749,7 +6749,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H220" t="n">
         <v>269993</v>
@@ -6778,7 +6778,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G221" t="n">
-        <v>1.42743468284607</v>
+        <v>1.42743492126465</v>
       </c>
       <c r="H221" t="n">
         <v>399624</v>
@@ -6865,7 +6865,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>1.40586161613464</v>
+        <v>1.40586149692535</v>
       </c>
       <c r="H224" t="n">
         <v>291769</v>
@@ -6894,7 +6894,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G225" t="n">
-        <v>1.45691847801208</v>
+        <v>1.4569183588028</v>
       </c>
       <c r="H225" t="n">
         <v>220241</v>
@@ -6923,7 +6923,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G226" t="n">
-        <v>1.39004123210907</v>
+        <v>1.39004111289978</v>
       </c>
       <c r="H226" t="n">
         <v>120366</v>
@@ -7039,7 +7039,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G230" t="n">
-        <v>1.35840034484863</v>
+        <v>1.35840046405792</v>
       </c>
       <c r="H230" t="n">
         <v>71664</v>
@@ -7126,7 +7126,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G233" t="n">
-        <v>1.33323132991791</v>
+        <v>1.3332314491272</v>
       </c>
       <c r="H233" t="n">
         <v>41061</v>
@@ -7155,7 +7155,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G234" t="n">
-        <v>1.29799497127533</v>
+        <v>1.29799509048462</v>
       </c>
       <c r="H234" t="n">
         <v>45856</v>
@@ -7271,7 +7271,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G238" t="n">
-        <v>1.38069260120392</v>
+        <v>1.38069272041321</v>
       </c>
       <c r="H238" t="n">
         <v>163588</v>
@@ -7300,7 +7300,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G239" t="n">
-        <v>1.34545648097992</v>
+        <v>1.34545636177063</v>
       </c>
       <c r="H239" t="n">
         <v>231772</v>
@@ -7329,7 +7329,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G240" t="n">
-        <v>1.40226602554321</v>
+        <v>1.40226590633392</v>
       </c>
       <c r="H240" t="n">
         <v>311388</v>
@@ -7387,7 +7387,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G242" t="n">
-        <v>1.48712110519409</v>
+        <v>1.48712134361267</v>
       </c>
       <c r="H242" t="n">
         <v>292070</v>
@@ -7416,7 +7416,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>1.46698594093323</v>
+        <v>1.46698606014252</v>
       </c>
       <c r="H243" t="n">
         <v>271260</v>
@@ -7445,7 +7445,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G244" t="n">
-        <v>1.44828903675079</v>
+        <v>1.44828915596008</v>
       </c>
       <c r="H244" t="n">
         <v>309397</v>
@@ -7474,7 +7474,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G245" t="n">
-        <v>1.48855924606323</v>
+        <v>1.48855936527252</v>
       </c>
       <c r="H245" t="n">
         <v>233960</v>
@@ -7532,7 +7532,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G247" t="n">
-        <v>1.55327939987183</v>
+        <v>1.55327951908112</v>
       </c>
       <c r="H247" t="n">
         <v>317915</v>
@@ -7561,7 +7561,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G248" t="n">
-        <v>1.53602051734924</v>
+        <v>1.53602063655853</v>
       </c>
       <c r="H248" t="n">
         <v>216798</v>
@@ -7619,7 +7619,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G250" t="n">
-        <v>1.54464983940125</v>
+        <v>1.54464995861053</v>
       </c>
       <c r="H250" t="n">
         <v>107669</v>
@@ -7648,7 +7648,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G251" t="n">
-        <v>1.51732361316681</v>
+        <v>1.5173237323761</v>
       </c>
       <c r="H251" t="n">
         <v>66840</v>
@@ -7677,7 +7677,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G252" t="n">
-        <v>1.54608821868896</v>
+        <v>1.54608833789825</v>
       </c>
       <c r="H252" t="n">
         <v>165938</v>
@@ -7735,7 +7735,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>1.56047058105469</v>
+        <v>1.5604704618454</v>
       </c>
       <c r="H254" t="n">
         <v>51401</v>
@@ -7764,7 +7764,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G255" t="n">
-        <v>1.56047058105469</v>
+        <v>1.5604704618454</v>
       </c>
       <c r="H255" t="n">
         <v>23797</v>
@@ -7822,7 +7822,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G257" t="n">
-        <v>1.5820437669754</v>
+        <v>1.58204388618469</v>
       </c>
       <c r="H257" t="n">
         <v>82049</v>
@@ -7851,7 +7851,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G258" t="n">
-        <v>1.60649359226227</v>
+        <v>1.60649347305298</v>
       </c>
       <c r="H258" t="n">
         <v>92524</v>
@@ -7909,7 +7909,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>1.64676368236542</v>
+        <v>1.64676380157471</v>
       </c>
       <c r="H260" t="n">
         <v>278227</v>
@@ -7967,7 +7967,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G262" t="n">
-        <v>1.66546046733856</v>
+        <v>1.66546058654785</v>
       </c>
       <c r="H262" t="n">
         <v>37389</v>
@@ -7996,7 +7996,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>1.66114592552185</v>
+        <v>1.66114580631256</v>
       </c>
       <c r="H263" t="n">
         <v>109636</v>
@@ -8025,7 +8025,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G264" t="n">
-        <v>1.66546046733856</v>
+        <v>1.66546058654785</v>
       </c>
       <c r="H264" t="n">
         <v>230585</v>
@@ -8112,7 +8112,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>1.69710147380829</v>
+        <v>1.697101354599</v>
       </c>
       <c r="H267" t="n">
         <v>248065</v>
@@ -8141,7 +8141,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G268" t="n">
-        <v>1.72011280059814</v>
+        <v>1.72011291980743</v>
       </c>
       <c r="H268" t="n">
         <v>78748</v>
@@ -8170,7 +8170,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G269" t="n">
-        <v>1.72298943996429</v>
+        <v>1.722989320755</v>
       </c>
       <c r="H269" t="n">
         <v>119208</v>
@@ -8199,7 +8199,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G270" t="n">
-        <v>1.7244279384613</v>
+        <v>1.72442770004272</v>
       </c>
       <c r="H270" t="n">
         <v>163949</v>
@@ -8257,7 +8257,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G272" t="n">
-        <v>1.78483319282532</v>
+        <v>1.78483307361603</v>
       </c>
       <c r="H272" t="n">
         <v>141307</v>
@@ -8286,7 +8286,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G273" t="n">
-        <v>1.74168622493744</v>
+        <v>1.74168634414673</v>
       </c>
       <c r="H273" t="n">
         <v>60014</v>
@@ -8315,7 +8315,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G274" t="n">
-        <v>1.74887728691101</v>
+        <v>1.7488774061203</v>
       </c>
       <c r="H274" t="n">
         <v>56096</v>
@@ -8344,7 +8344,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G275" t="n">
-        <v>1.75463044643402</v>
+        <v>1.75463020801544</v>
       </c>
       <c r="H275" t="n">
         <v>71837</v>
@@ -8402,7 +8402,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G277" t="n">
-        <v>1.68991041183472</v>
+        <v>1.68991029262543</v>
       </c>
       <c r="H277" t="n">
         <v>113971</v>
@@ -8431,7 +8431,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>1.66114592552185</v>
+        <v>1.66114580631256</v>
       </c>
       <c r="H278" t="n">
         <v>173082</v>
@@ -8460,7 +8460,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G279" t="n">
-        <v>1.64244890213013</v>
+        <v>1.64244902133942</v>
       </c>
       <c r="H279" t="n">
         <v>168716</v>
@@ -8489,7 +8489,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G280" t="n">
-        <v>1.71723663806915</v>
+        <v>1.71723675727844</v>
       </c>
       <c r="H280" t="n">
         <v>72996</v>
@@ -8576,7 +8576,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.63957250118256</v>
+        <v>1.63957273960114</v>
       </c>
       <c r="H283" t="n">
         <v>100008</v>
@@ -8634,7 +8634,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G285" t="n">
-        <v>1.65395486354828</v>
+        <v>1.65395474433899</v>
       </c>
       <c r="H285" t="n">
         <v>156406</v>
@@ -8692,7 +8692,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G287" t="n">
-        <v>1.66833698749542</v>
+        <v>1.66833674907684</v>
       </c>
       <c r="H287" t="n">
         <v>166610</v>
@@ -8721,7 +8721,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G288" t="n">
-        <v>1.64244890213013</v>
+        <v>1.64244902133942</v>
       </c>
       <c r="H288" t="n">
         <v>137257</v>
@@ -8750,7 +8750,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G289" t="n">
-        <v>1.65970778465271</v>
+        <v>1.65970766544342</v>
       </c>
       <c r="H289" t="n">
         <v>313466</v>
@@ -8779,7 +8779,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>1.63957250118256</v>
+        <v>1.63957273960114</v>
       </c>
       <c r="H290" t="n">
         <v>84656</v>
@@ -8808,7 +8808,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G291" t="n">
-        <v>1.63094305992126</v>
+        <v>1.63094317913055</v>
       </c>
       <c r="H291" t="n">
         <v>45265</v>
@@ -8837,7 +8837,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G292" t="n">
-        <v>1.62375211715698</v>
+        <v>1.62375223636627</v>
       </c>
       <c r="H292" t="n">
         <v>137492</v>
@@ -8895,7 +8895,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G294" t="n">
-        <v>1.51732361316681</v>
+        <v>1.5173237323761</v>
       </c>
       <c r="H294" t="n">
         <v>436962</v>
@@ -8924,7 +8924,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G295" t="n">
-        <v>1.48136830329895</v>
+        <v>1.48136818408966</v>
       </c>
       <c r="H295" t="n">
         <v>139909</v>
@@ -8953,7 +8953,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G296" t="n">
-        <v>1.49143552780151</v>
+        <v>1.49143576622009</v>
       </c>
       <c r="H296" t="n">
         <v>99146</v>
@@ -9011,7 +9011,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G298" t="n">
-        <v>1.48280644416809</v>
+        <v>1.48280656337738</v>
       </c>
       <c r="H298" t="n">
         <v>126544</v>
@@ -9069,7 +9069,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>1.52451479434967</v>
+        <v>1.52451491355896</v>
       </c>
       <c r="H300" t="n">
         <v>252976</v>
@@ -9098,7 +9098,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G301" t="n">
-        <v>1.52163851261139</v>
+        <v>1.5216383934021</v>
       </c>
       <c r="H301" t="n">
         <v>197878</v>
@@ -9127,7 +9127,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G302" t="n">
-        <v>1.51876199245453</v>
+        <v>1.51876187324524</v>
       </c>
       <c r="H302" t="n">
         <v>144408</v>
@@ -9185,7 +9185,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G304" t="n">
-        <v>1.50150346755981</v>
+        <v>1.50150322914124</v>
       </c>
       <c r="H304" t="n">
         <v>195517</v>
@@ -9214,7 +9214,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G305" t="n">
-        <v>1.49718880653381</v>
+        <v>1.49718856811523</v>
       </c>
       <c r="H305" t="n">
         <v>130511</v>
@@ -9272,7 +9272,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G307" t="n">
-        <v>1.54464983940125</v>
+        <v>1.54464995861053</v>
       </c>
       <c r="H307" t="n">
         <v>276795</v>
@@ -9388,7 +9388,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G311" t="n">
-        <v>1.82654130458832</v>
+        <v>1.8265415430069</v>
       </c>
       <c r="H311" t="n">
         <v>1327276</v>
@@ -9417,7 +9417,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G312" t="n">
-        <v>1.81503558158875</v>
+        <v>1.81503546237946</v>
       </c>
       <c r="H312" t="n">
         <v>584553</v>
@@ -9533,7 +9533,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>1.81215929985046</v>
+        <v>1.81215918064117</v>
       </c>
       <c r="H316" t="n">
         <v>826864</v>
@@ -9562,7 +9562,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>2.0494658946991</v>
+        <v>2.04946541786194</v>
       </c>
       <c r="H317" t="n">
         <v>1769450</v>
@@ -9591,7 +9591,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G318" t="n">
-        <v>1.99049866199493</v>
+        <v>1.99049842357635</v>
       </c>
       <c r="H318" t="n">
         <v>982630</v>
@@ -9620,7 +9620,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>1.95166671276093</v>
+        <v>1.95166683197021</v>
       </c>
       <c r="H319" t="n">
         <v>345138</v>
@@ -9678,7 +9678,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G321" t="n">
-        <v>1.96604883670807</v>
+        <v>1.96604895591736</v>
       </c>
       <c r="H321" t="n">
         <v>556298</v>
@@ -9707,7 +9707,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G322" t="n">
-        <v>1.96317267417908</v>
+        <v>1.9631724357605</v>
       </c>
       <c r="H322" t="n">
         <v>428819</v>
@@ -9736,7 +9736,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G323" t="n">
-        <v>1.94303727149963</v>
+        <v>1.94303750991821</v>
       </c>
       <c r="H323" t="n">
         <v>580907</v>
@@ -9765,7 +9765,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G324" t="n">
-        <v>1.97467803955078</v>
+        <v>1.97467851638794</v>
       </c>
       <c r="H324" t="n">
         <v>133183</v>
@@ -9823,7 +9823,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G326" t="n">
-        <v>1.97036349773407</v>
+        <v>1.97036373615265</v>
       </c>
       <c r="H326" t="n">
         <v>126422</v>
@@ -9881,7 +9881,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G328" t="n">
-        <v>1.99625158309937</v>
+        <v>1.99625134468079</v>
       </c>
       <c r="H328" t="n">
         <v>411215</v>
@@ -9910,7 +9910,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>1.96317267417908</v>
+        <v>1.9631724357605</v>
       </c>
       <c r="H329" t="n">
         <v>315276</v>
@@ -9939,7 +9939,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G330" t="n">
-        <v>1.87400281429291</v>
+        <v>1.87400269508362</v>
       </c>
       <c r="H330" t="n">
         <v>719612</v>
@@ -9997,7 +9997,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G332" t="n">
-        <v>1.710045337677</v>
+        <v>1.71004557609558</v>
       </c>
       <c r="H332" t="n">
         <v>423853</v>
@@ -10026,7 +10026,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G333" t="n">
-        <v>1.76182150840759</v>
+        <v>1.76182162761688</v>
       </c>
       <c r="H333" t="n">
         <v>201401</v>
@@ -10055,7 +10055,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G334" t="n">
-        <v>1.8135974407196</v>
+        <v>1.81359755992889</v>
       </c>
       <c r="H334" t="n">
         <v>247772</v>
@@ -10084,7 +10084,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G335" t="n">
-        <v>1.79058575630188</v>
+        <v>1.79058599472046</v>
       </c>
       <c r="H335" t="n">
         <v>437211</v>
@@ -10113,7 +10113,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G336" t="n">
-        <v>1.85386765003204</v>
+        <v>1.85386753082275</v>
       </c>
       <c r="H336" t="n">
         <v>411061</v>
@@ -10171,7 +10171,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G338" t="n">
-        <v>2.00488066673279</v>
+        <v>2.00488090515137</v>
       </c>
       <c r="H338" t="n">
         <v>1142710</v>
@@ -10200,7 +10200,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G339" t="n">
-        <v>1.9674870967865</v>
+        <v>1.96748745441437</v>
       </c>
       <c r="H339" t="n">
         <v>358063</v>
@@ -10229,7 +10229,7 @@
         <v>2.5</v>
       </c>
       <c r="G340" t="n">
-        <v>1.79777681827545</v>
+        <v>1.79777693748474</v>
       </c>
       <c r="H340" t="n">
         <v>1136516</v>
@@ -10258,7 +10258,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G341" t="n">
-        <v>1.7458610534668</v>
+        <v>1.74586117267609</v>
       </c>
       <c r="H341" t="n">
         <v>1340489</v>
@@ -10316,7 +10316,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G343" t="n">
-        <v>1.7295446395874</v>
+        <v>1.72954428195953</v>
       </c>
       <c r="H343" t="n">
         <v>724620</v>
@@ -10345,7 +10345,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G344" t="n">
-        <v>1.72361099720001</v>
+        <v>1.72361123561859</v>
       </c>
       <c r="H344" t="n">
         <v>420972</v>
@@ -10374,7 +10374,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G345" t="n">
-        <v>1.67762851715088</v>
+        <v>1.67762839794159</v>
       </c>
       <c r="H345" t="n">
         <v>473880</v>
@@ -10403,7 +10403,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G346" t="n">
-        <v>1.71619462966919</v>
+        <v>1.7161945104599</v>
       </c>
       <c r="H346" t="n">
         <v>736976</v>
@@ -10432,7 +10432,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G347" t="n">
-        <v>1.76514410972595</v>
+        <v>1.76514399051666</v>
       </c>
       <c r="H347" t="n">
         <v>696640</v>
@@ -10461,7 +10461,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G348" t="n">
-        <v>1.75179409980774</v>
+        <v>1.75179421901703</v>
       </c>
       <c r="H348" t="n">
         <v>412804</v>
@@ -10490,7 +10490,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G349" t="n">
-        <v>1.71471118927002</v>
+        <v>1.7147114276886</v>
       </c>
       <c r="H349" t="n">
         <v>228527</v>
@@ -10519,7 +10519,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G350" t="n">
-        <v>1.71322798728943</v>
+        <v>1.71322786808014</v>
       </c>
       <c r="H350" t="n">
         <v>292359</v>
@@ -10548,7 +10548,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G351" t="n">
-        <v>1.70581150054932</v>
+        <v>1.70581138134003</v>
       </c>
       <c r="H351" t="n">
         <v>296176</v>
@@ -10577,7 +10577,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G352" t="n">
-        <v>1.68652844429016</v>
+        <v>1.68652832508087</v>
       </c>
       <c r="H352" t="n">
         <v>226216</v>
@@ -10664,7 +10664,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G355" t="n">
-        <v>1.67911171913147</v>
+        <v>1.67911183834076</v>
       </c>
       <c r="H355" t="n">
         <v>121579</v>
@@ -10693,7 +10693,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G356" t="n">
-        <v>1.67762851715088</v>
+        <v>1.67762839794159</v>
       </c>
       <c r="H356" t="n">
         <v>106360</v>
@@ -10780,7 +10780,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G359" t="n">
-        <v>1.72064447402954</v>
+        <v>1.72064435482025</v>
       </c>
       <c r="H359" t="n">
         <v>272461</v>
@@ -10838,7 +10838,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G361" t="n">
-        <v>1.69246172904968</v>
+        <v>1.69246160984039</v>
       </c>
       <c r="H361" t="n">
         <v>151546</v>
@@ -10867,7 +10867,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207836151123</v>
       </c>
       <c r="H362" t="n">
         <v>79655</v>
@@ -10896,7 +10896,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G363" t="n">
-        <v>1.67911171913147</v>
+        <v>1.67911183834076</v>
       </c>
       <c r="H363" t="n">
         <v>136307</v>
@@ -10925,7 +10925,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>1.69839489459991</v>
+        <v>1.6983950138092</v>
       </c>
       <c r="H364" t="n">
         <v>79641</v>
@@ -10954,7 +10954,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G365" t="n">
-        <v>1.70284485816956</v>
+        <v>1.70284497737885</v>
       </c>
       <c r="H365" t="n">
         <v>103563</v>
@@ -10983,7 +10983,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G366" t="n">
-        <v>1.69839489459991</v>
+        <v>1.6983950138092</v>
       </c>
       <c r="H366" t="n">
         <v>141224</v>
@@ -11012,7 +11012,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>1.69839489459991</v>
+        <v>1.6983950138092</v>
       </c>
       <c r="H367" t="n">
         <v>184395</v>
@@ -11070,7 +11070,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>1.72064447402954</v>
+        <v>1.72064435482025</v>
       </c>
       <c r="H369" t="n">
         <v>90559</v>
@@ -11157,7 +11157,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>1.69097816944122</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H372" t="n">
         <v>188976</v>
@@ -11186,7 +11186,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G373" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207836151123</v>
       </c>
       <c r="H373" t="n">
         <v>48951</v>
@@ -11215,7 +11215,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G374" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H374" t="n">
         <v>503636</v>
@@ -11273,7 +11273,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G376" t="n">
-        <v>1.69097816944122</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H376" t="n">
         <v>217080</v>
@@ -11302,7 +11302,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>1.72806107997894</v>
+        <v>1.72806119918823</v>
       </c>
       <c r="H377" t="n">
         <v>254953</v>
@@ -11331,7 +11331,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G378" t="n">
-        <v>1.67762851715088</v>
+        <v>1.67762839794159</v>
       </c>
       <c r="H378" t="n">
         <v>158070</v>
@@ -11360,7 +11360,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G379" t="n">
-        <v>1.67614507675171</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H379" t="n">
         <v>56186</v>
@@ -11389,7 +11389,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.68356156349182</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H380" t="n">
         <v>147433</v>
@@ -11476,7 +11476,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G383" t="n">
-        <v>1.72806107997894</v>
+        <v>1.72806119918823</v>
       </c>
       <c r="H383" t="n">
         <v>453984</v>
@@ -11505,7 +11505,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>1.75031089782715</v>
+        <v>1.75031077861786</v>
       </c>
       <c r="H384" t="n">
         <v>517240</v>
@@ -11592,7 +11592,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G387" t="n">
-        <v>1.73696112632751</v>
+        <v>1.7369612455368</v>
       </c>
       <c r="H387" t="n">
         <v>76021</v>
@@ -11621,7 +11621,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G388" t="n">
-        <v>1.71174478530884</v>
+        <v>1.71174466609955</v>
       </c>
       <c r="H388" t="n">
         <v>51635</v>
@@ -11650,7 +11650,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G389" t="n">
-        <v>1.70284485816956</v>
+        <v>1.70284497737885</v>
       </c>
       <c r="H389" t="n">
         <v>131273</v>
@@ -11737,7 +11737,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>1.69839489459991</v>
+        <v>1.6983950138092</v>
       </c>
       <c r="H392" t="n">
         <v>294047</v>
@@ -11766,7 +11766,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G393" t="n">
-        <v>1.71471118927002</v>
+        <v>1.7147114276886</v>
       </c>
       <c r="H393" t="n">
         <v>124941</v>
@@ -11795,7 +11795,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G394" t="n">
-        <v>1.70877814292908</v>
+        <v>1.70877802371979</v>
       </c>
       <c r="H394" t="n">
         <v>70335</v>
@@ -11824,7 +11824,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G395" t="n">
-        <v>1.70581150054932</v>
+        <v>1.70581138134003</v>
       </c>
       <c r="H395" t="n">
         <v>79866</v>
@@ -11911,7 +11911,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G398" t="n">
-        <v>1.71322798728943</v>
+        <v>1.71322786808014</v>
       </c>
       <c r="H398" t="n">
         <v>167655</v>
@@ -11940,7 +11940,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G399" t="n">
-        <v>1.69097816944122</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H399" t="n">
         <v>80915</v>
@@ -11969,7 +11969,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G400" t="n">
-        <v>1.68949520587921</v>
+        <v>1.68949508666992</v>
       </c>
       <c r="H400" t="n">
         <v>71969</v>
@@ -12027,7 +12027,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G402" t="n">
-        <v>1.67762851715088</v>
+        <v>1.67762839794159</v>
       </c>
       <c r="H402" t="n">
         <v>222599</v>
@@ -12056,7 +12056,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>1.67614507675171</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H403" t="n">
         <v>357624</v>
@@ -12085,7 +12085,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>1.68356156349182</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H404" t="n">
         <v>193550</v>
@@ -12114,7 +12114,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G405" t="n">
-        <v>1.6435124874115</v>
+        <v>1.64351224899292</v>
       </c>
       <c r="H405" t="n">
         <v>250166</v>
@@ -12172,7 +12172,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>1.59456288814545</v>
+        <v>1.59456300735474</v>
       </c>
       <c r="H407" t="n">
         <v>284079</v>
@@ -12201,7 +12201,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G408" t="n">
-        <v>1.61384618282318</v>
+        <v>1.61384606361389</v>
       </c>
       <c r="H408" t="n">
         <v>160068</v>
@@ -12230,7 +12230,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G409" t="n">
-        <v>1.59159600734711</v>
+        <v>1.5915961265564</v>
       </c>
       <c r="H409" t="n">
         <v>149140</v>
@@ -12288,7 +12288,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G411" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207836151123</v>
       </c>
       <c r="H411" t="n">
         <v>346022</v>
@@ -12317,7 +12317,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>1.68356156349182</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H412" t="n">
         <v>177992</v>
@@ -12346,7 +12346,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G413" t="n">
-        <v>1.67762851715088</v>
+        <v>1.67762839794159</v>
       </c>
       <c r="H413" t="n">
         <v>124634</v>
@@ -12375,7 +12375,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G414" t="n">
-        <v>1.65686213970184</v>
+        <v>1.65686202049255</v>
       </c>
       <c r="H414" t="n">
         <v>79267</v>
@@ -12404,7 +12404,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G415" t="n">
-        <v>1.67466175556183</v>
+        <v>1.67466187477112</v>
       </c>
       <c r="H415" t="n">
         <v>54025</v>
@@ -12636,7 +12636,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G423" t="n">
-        <v>1.58417952060699</v>
+        <v>1.58417963981628</v>
       </c>
       <c r="H423" t="n">
         <v>39132</v>
@@ -12665,7 +12665,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>1.59456288814545</v>
+        <v>1.59456300735474</v>
       </c>
       <c r="H424" t="n">
         <v>23373</v>
@@ -12723,7 +12723,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G426" t="n">
-        <v>1.55896329879761</v>
+        <v>1.5589634180069</v>
       </c>
       <c r="H426" t="n">
         <v>84811</v>
@@ -12781,7 +12781,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G428" t="n">
-        <v>1.60049629211426</v>
+        <v>1.60049605369568</v>
       </c>
       <c r="H428" t="n">
         <v>74845</v>
@@ -12810,7 +12810,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G429" t="n">
-        <v>1.59159600734711</v>
+        <v>1.5915961265564</v>
       </c>
       <c r="H429" t="n">
         <v>17916</v>
@@ -12839,7 +12839,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G430" t="n">
-        <v>1.58714628219604</v>
+        <v>1.58714640140533</v>
       </c>
       <c r="H430" t="n">
         <v>22813</v>
@@ -12868,7 +12868,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G431" t="n">
-        <v>1.57824647426605</v>
+        <v>1.57824635505676</v>
       </c>
       <c r="H431" t="n">
         <v>99193</v>
@@ -12897,7 +12897,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G432" t="n">
-        <v>1.58121299743652</v>
+        <v>1.58121311664581</v>
       </c>
       <c r="H432" t="n">
         <v>24105</v>
@@ -12926,7 +12926,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G433" t="n">
-        <v>1.56786322593689</v>
+        <v>1.56786346435547</v>
       </c>
       <c r="H433" t="n">
         <v>67599</v>
@@ -12955,7 +12955,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>1.59456288814545</v>
+        <v>1.59456300735474</v>
       </c>
       <c r="H434" t="n">
         <v>146075</v>
@@ -12984,7 +12984,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G435" t="n">
-        <v>1.59901285171509</v>
+        <v>1.5990127325058</v>
       </c>
       <c r="H435" t="n">
         <v>216836</v>
@@ -13013,7 +13013,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G436" t="n">
-        <v>1.58121299743652</v>
+        <v>1.58121311664581</v>
       </c>
       <c r="H436" t="n">
         <v>116492</v>
@@ -13042,7 +13042,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>1.57231307029724</v>
+        <v>1.57231318950653</v>
       </c>
       <c r="H437" t="n">
         <v>157936</v>
@@ -13071,7 +13071,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G438" t="n">
-        <v>1.56192994117737</v>
+        <v>1.56192982196808</v>
       </c>
       <c r="H438" t="n">
         <v>66146</v>
@@ -13100,7 +13100,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>1.57231307029724</v>
+        <v>1.57231318950653</v>
       </c>
       <c r="H439" t="n">
         <v>118972</v>
@@ -13129,7 +13129,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G440" t="n">
-        <v>1.57231307029724</v>
+        <v>1.57231318950653</v>
       </c>
       <c r="H440" t="n">
         <v>164526</v>
@@ -13158,7 +13158,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G441" t="n">
-        <v>1.56637990474701</v>
+        <v>1.56637978553772</v>
       </c>
       <c r="H441" t="n">
         <v>138503</v>
@@ -13187,7 +13187,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G442" t="n">
-        <v>1.59307944774628</v>
+        <v>1.59307956695557</v>
       </c>
       <c r="H442" t="n">
         <v>240142</v>
@@ -13274,7 +13274,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G445" t="n">
-        <v>1.58714628219604</v>
+        <v>1.58714640140533</v>
       </c>
       <c r="H445" t="n">
         <v>94999</v>
@@ -13361,7 +13361,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G448" t="n">
-        <v>1.76217722892761</v>
+        <v>1.7621773481369</v>
       </c>
       <c r="H448" t="n">
         <v>1246215</v>
@@ -13390,7 +13390,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G449" t="n">
-        <v>1.76217722892761</v>
+        <v>1.7621773481369</v>
       </c>
       <c r="H449" t="n">
         <v>653821</v>
@@ -13448,7 +13448,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>1.72806107997894</v>
+        <v>1.72806119918823</v>
       </c>
       <c r="H451" t="n">
         <v>194974</v>
@@ -13564,7 +13564,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G455" t="n">
-        <v>1.74437773227692</v>
+        <v>1.74437761306763</v>
       </c>
       <c r="H455" t="n">
         <v>306209</v>
@@ -13622,7 +13622,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G457" t="n">
-        <v>1.79629349708557</v>
+        <v>1.79629361629486</v>
       </c>
       <c r="H457" t="n">
         <v>481923</v>
@@ -13651,7 +13651,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G458" t="n">
-        <v>1.8318932056427</v>
+        <v>1.83189332485199</v>
       </c>
       <c r="H458" t="n">
         <v>603245</v>
@@ -13680,7 +13680,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>1.8393098115921</v>
+        <v>1.83930993080139</v>
       </c>
       <c r="H459" t="n">
         <v>503273</v>
@@ -13709,7 +13709,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G460" t="n">
-        <v>1.93720841407776</v>
+        <v>1.93720817565918</v>
       </c>
       <c r="H460" t="n">
         <v>2102244</v>
@@ -13738,7 +13738,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G461" t="n">
-        <v>1.92089211940765</v>
+        <v>1.92089188098907</v>
       </c>
       <c r="H461" t="n">
         <v>652481</v>
@@ -13796,7 +13796,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G463" t="n">
-        <v>1.90605878829956</v>
+        <v>1.90605854988098</v>
       </c>
       <c r="H463" t="n">
         <v>445928</v>
@@ -13912,7 +13912,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G467" t="n">
-        <v>1.93572497367859</v>
+        <v>1.93572509288788</v>
       </c>
       <c r="H467" t="n">
         <v>227515</v>
@@ -13941,7 +13941,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G468" t="n">
-        <v>1.92089211940765</v>
+        <v>1.92089188098907</v>
       </c>
       <c r="H468" t="n">
         <v>895874</v>
@@ -13970,7 +13970,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G469" t="n">
-        <v>1.78887724876404</v>
+        <v>1.78887701034546</v>
       </c>
       <c r="H469" t="n">
         <v>1419623</v>
@@ -14057,7 +14057,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G472" t="n">
-        <v>1.78887724876404</v>
+        <v>1.78887701034546</v>
       </c>
       <c r="H472" t="n">
         <v>368047</v>
@@ -14086,7 +14086,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G473" t="n">
-        <v>1.76514410972595</v>
+        <v>1.76514399051666</v>
       </c>
       <c r="H473" t="n">
         <v>234010</v>
@@ -14144,7 +14144,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G475" t="n">
-        <v>1.70729470252991</v>
+        <v>1.7072948217392</v>
       </c>
       <c r="H475" t="n">
         <v>277320</v>
@@ -14202,7 +14202,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G477" t="n">
-        <v>1.63757884502411</v>
+        <v>1.6375789642334</v>
       </c>
       <c r="H477" t="n">
         <v>345521</v>
@@ -14318,7 +14318,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G481" t="n">
-        <v>1.60049629211426</v>
+        <v>1.60049605369568</v>
       </c>
       <c r="H481" t="n">
         <v>311351</v>
@@ -14376,7 +14376,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G483" t="n">
-        <v>1.63164567947388</v>
+        <v>1.63164591789246</v>
       </c>
       <c r="H483" t="n">
         <v>127058</v>
@@ -14405,7 +14405,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G484" t="n">
-        <v>1.64796221256256</v>
+        <v>1.64796209335327</v>
       </c>
       <c r="H484" t="n">
         <v>79231</v>
@@ -14434,7 +14434,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G485" t="n">
-        <v>1.68652844429016</v>
+        <v>1.68652832508087</v>
       </c>
       <c r="H485" t="n">
         <v>204828</v>
@@ -14463,7 +14463,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G486" t="n">
-        <v>1.67021179199219</v>
+        <v>1.67021191120148</v>
       </c>
       <c r="H486" t="n">
         <v>138055</v>
@@ -14492,7 +14492,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G487" t="n">
-        <v>1.69097816944122</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H487" t="n">
         <v>237309</v>
@@ -14550,7 +14550,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G489" t="n">
-        <v>1.63757884502411</v>
+        <v>1.6375789642334</v>
       </c>
       <c r="H489" t="n">
         <v>137365</v>
@@ -14579,7 +14579,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G490" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207836151123</v>
       </c>
       <c r="H490" t="n">
         <v>107553</v>
@@ -14637,7 +14637,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G492" t="n">
-        <v>1.67614507675171</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H492" t="n">
         <v>73596</v>
@@ -14666,7 +14666,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G493" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131198406219</v>
       </c>
       <c r="H493" t="n">
         <v>309875</v>
@@ -14695,7 +14695,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G494" t="n">
-        <v>1.68652844429016</v>
+        <v>1.68652832508087</v>
       </c>
       <c r="H494" t="n">
         <v>85401</v>
@@ -14724,7 +14724,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G495" t="n">
-        <v>1.68949520587921</v>
+        <v>1.68949508666992</v>
       </c>
       <c r="H495" t="n">
         <v>157965</v>
@@ -14753,7 +14753,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G496" t="n">
-        <v>1.68949520587921</v>
+        <v>1.68949508666992</v>
       </c>
       <c r="H496" t="n">
         <v>61838</v>
@@ -14811,7 +14811,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G498" t="n">
-        <v>1.68949520587921</v>
+        <v>1.68949508666992</v>
       </c>
       <c r="H498" t="n">
         <v>94690</v>
@@ -14840,7 +14840,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G499" t="n">
-        <v>1.68356156349182</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H499" t="n">
         <v>46806</v>
@@ -14869,7 +14869,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.69097816944122</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H500" t="n">
         <v>39718</v>
@@ -14898,7 +14898,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G501" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207836151123</v>
       </c>
       <c r="H501" t="n">
         <v>63302</v>
@@ -14927,7 +14927,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G502" t="n">
-        <v>1.67466175556183</v>
+        <v>1.67466187477112</v>
       </c>
       <c r="H502" t="n">
         <v>96652</v>
@@ -15072,7 +15072,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.69097816944122</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H507" t="n">
         <v>86918</v>
@@ -15101,7 +15101,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>1.69839489459991</v>
+        <v>1.6983950138092</v>
       </c>
       <c r="H508" t="n">
         <v>69025</v>
@@ -15188,7 +15188,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G511" t="n">
-        <v>1.68207824230194</v>
+        <v>1.68207836151123</v>
       </c>
       <c r="H511" t="n">
         <v>59713</v>
@@ -15217,7 +15217,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G512" t="n">
-        <v>1.67466175556183</v>
+        <v>1.67466187477112</v>
       </c>
       <c r="H512" t="n">
         <v>92185</v>
@@ -15246,7 +15246,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G513" t="n">
-        <v>1.69097816944122</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H513" t="n">
         <v>126057</v>
@@ -15304,7 +15304,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>1.69097816944122</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H515" t="n">
         <v>86940</v>
@@ -15333,7 +15333,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G516" t="n">
-        <v>1.70581150054932</v>
+        <v>1.70581138134003</v>
       </c>
       <c r="H516" t="n">
         <v>353654</v>
@@ -15391,7 +15391,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G518" t="n">
-        <v>1.75031089782715</v>
+        <v>1.75031077861786</v>
       </c>
       <c r="H518" t="n">
         <v>282131</v>
@@ -15420,7 +15420,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G519" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H519" t="n">
         <v>190065</v>
@@ -15449,7 +15449,7 @@
         <v>2.375</v>
       </c>
       <c r="G520" t="n">
-        <v>1.76143562793732</v>
+        <v>1.76143574714661</v>
       </c>
       <c r="H520" t="n">
         <v>189064</v>
@@ -15478,7 +15478,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>1.79110193252563</v>
+        <v>1.79110217094421</v>
       </c>
       <c r="H521" t="n">
         <v>200009</v>
@@ -15507,7 +15507,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76514410972595</v>
+        <v>1.76514399051666</v>
       </c>
       <c r="H522" t="n">
         <v>155399</v>
@@ -15536,7 +15536,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H523" t="n">
         <v>124342</v>
@@ -15565,7 +15565,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.74660241603851</v>
+        <v>1.74660265445709</v>
       </c>
       <c r="H524" t="n">
         <v>125547</v>
@@ -15594,7 +15594,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G525" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H525" t="n">
         <v>44234</v>
@@ -15623,7 +15623,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G526" t="n">
-        <v>1.79110193252563</v>
+        <v>1.79110217094421</v>
       </c>
       <c r="H526" t="n">
         <v>125260</v>
@@ -15652,7 +15652,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G527" t="n">
-        <v>1.78739380836487</v>
+        <v>1.78739392757416</v>
       </c>
       <c r="H527" t="n">
         <v>134301</v>
@@ -15710,7 +15710,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>1.75772750377655</v>
+        <v>1.75772738456726</v>
       </c>
       <c r="H529" t="n">
         <v>161504</v>
@@ -15768,7 +15768,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G531" t="n">
-        <v>1.82818484306335</v>
+        <v>1.82818472385406</v>
       </c>
       <c r="H531" t="n">
         <v>328327</v>
@@ -15855,7 +15855,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G534" t="n">
-        <v>1.70951986312866</v>
+        <v>1.70951962471008</v>
       </c>
       <c r="H534" t="n">
         <v>147585</v>
@@ -15884,7 +15884,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.67614507675171</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H535" t="n">
         <v>219143</v>
@@ -15913,7 +15913,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G536" t="n">
-        <v>1.69097816944122</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H536" t="n">
         <v>188147</v>
@@ -15942,7 +15942,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G537" t="n">
-        <v>1.66502022743225</v>
+        <v>1.66502010822296</v>
       </c>
       <c r="H537" t="n">
         <v>199771</v>
@@ -15971,7 +15971,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G538" t="n">
-        <v>1.69097816944122</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H538" t="n">
         <v>123991</v>
@@ -16029,7 +16029,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G540" t="n">
-        <v>1.67614507675171</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H540" t="n">
         <v>202006</v>
@@ -16058,7 +16058,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G541" t="n">
-        <v>1.67614507675171</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H541" t="n">
         <v>93257</v>
@@ -16116,7 +16116,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>1.63906216621399</v>
+        <v>1.63906240463257</v>
       </c>
       <c r="H543" t="n">
         <v>116471</v>
@@ -16145,7 +16145,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G544" t="n">
-        <v>1.67614507675171</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H544" t="n">
         <v>342817</v>
@@ -16203,7 +16203,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G546" t="n">
-        <v>1.68356156349182</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H546" t="n">
         <v>105820</v>
@@ -16261,7 +16261,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G548" t="n">
-        <v>1.64277052879333</v>
+        <v>1.64277040958405</v>
       </c>
       <c r="H548" t="n">
         <v>197621</v>
@@ -16290,7 +16290,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G549" t="n">
-        <v>1.68356156349182</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H549" t="n">
         <v>103175</v>
@@ -16319,7 +16319,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>1.66502022743225</v>
+        <v>1.66502010822296</v>
       </c>
       <c r="H550" t="n">
         <v>79116</v>
@@ -16348,7 +16348,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G551" t="n">
-        <v>1.65760374069214</v>
+        <v>1.65760362148285</v>
       </c>
       <c r="H551" t="n">
         <v>53538</v>
@@ -16377,7 +16377,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131198406219</v>
       </c>
       <c r="H552" t="n">
         <v>59842</v>
@@ -16435,7 +16435,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G554" t="n">
-        <v>1.68356156349182</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H554" t="n">
         <v>91123</v>
@@ -16493,7 +16493,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G556" t="n">
-        <v>1.63535404205322</v>
+        <v>1.63535392284393</v>
       </c>
       <c r="H556" t="n">
         <v>62408</v>
@@ -16522,7 +16522,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>1.63535404205322</v>
+        <v>1.63535392284393</v>
       </c>
       <c r="H557" t="n">
         <v>136348</v>
@@ -16551,7 +16551,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G558" t="n">
-        <v>1.63164567947388</v>
+        <v>1.63164591789246</v>
       </c>
       <c r="H558" t="n">
         <v>123184</v>
@@ -16667,7 +16667,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>1.67614507675171</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H562" t="n">
         <v>140407</v>
@@ -16696,7 +16696,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G563" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131198406219</v>
       </c>
       <c r="H563" t="n">
         <v>46104</v>
@@ -16870,7 +16870,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>1.63906216621399</v>
+        <v>1.63906240463257</v>
       </c>
       <c r="H569" t="n">
         <v>135132</v>
@@ -16957,7 +16957,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G572" t="n">
-        <v>1.65760374069214</v>
+        <v>1.65760362148285</v>
       </c>
       <c r="H572" t="n">
         <v>54138</v>
@@ -17015,7 +17015,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G574" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131198406219</v>
       </c>
       <c r="H574" t="n">
         <v>64589</v>
@@ -17160,7 +17160,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>1.70210337638855</v>
+        <v>1.70210313796997</v>
       </c>
       <c r="H579" t="n">
         <v>132014</v>
@@ -17189,7 +17189,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.69839489459991</v>
+        <v>1.6983950138092</v>
       </c>
       <c r="H580" t="n">
         <v>175180</v>
@@ -17218,7 +17218,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G581" t="n">
-        <v>1.67614507675171</v>
+        <v>1.676145195961</v>
       </c>
       <c r="H581" t="n">
         <v>144783</v>
@@ -17247,7 +17247,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>1.68356156349182</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H582" t="n">
         <v>194562</v>
@@ -17334,7 +17334,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>1.68356156349182</v>
+        <v>1.6835618019104</v>
       </c>
       <c r="H585" t="n">
         <v>250373</v>
@@ -17421,7 +17421,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G588" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131198406219</v>
       </c>
       <c r="H588" t="n">
         <v>79711</v>
@@ -17450,7 +17450,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131198406219</v>
       </c>
       <c r="H589" t="n">
         <v>42981</v>
@@ -17508,7 +17508,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G591" t="n">
-        <v>1.66131210327148</v>
+        <v>1.66131198406219</v>
       </c>
       <c r="H591" t="n">
         <v>110080</v>
@@ -17537,7 +17537,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G592" t="n">
-        <v>1.65389549732208</v>
+        <v>1.65389537811279</v>
       </c>
       <c r="H592" t="n">
         <v>114980</v>
@@ -17566,7 +17566,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G593" t="n">
-        <v>1.69839489459991</v>
+        <v>1.6983950138092</v>
       </c>
       <c r="H593" t="n">
         <v>157651</v>
@@ -17595,7 +17595,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G594" t="n">
-        <v>1.69097816944122</v>
+        <v>1.6909784078598</v>
       </c>
       <c r="H594" t="n">
         <v>78442</v>
@@ -17624,7 +17624,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>1.70581150054932</v>
+        <v>1.70581138134003</v>
       </c>
       <c r="H595" t="n">
         <v>176901</v>
@@ -17682,7 +17682,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>1.70210337638855</v>
+        <v>1.70210313796997</v>
       </c>
       <c r="H597" t="n">
         <v>185509</v>
@@ -17711,7 +17711,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G598" t="n">
-        <v>1.72984230518341</v>
+        <v>1.72984218597412</v>
       </c>
       <c r="H598" t="n">
         <v>216867</v>
@@ -17740,7 +17740,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G599" t="n">
-        <v>1.72984230518341</v>
+        <v>1.72984218597412</v>
       </c>
       <c r="H599" t="n">
         <v>213296</v>
@@ -17769,7 +17769,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G600" t="n">
-        <v>1.74140024185181</v>
+        <v>1.74140012264252</v>
       </c>
       <c r="H600" t="n">
         <v>160604</v>
@@ -17798,7 +17798,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G601" t="n">
-        <v>1.72598969936371</v>
+        <v>1.725989818573</v>
       </c>
       <c r="H601" t="n">
         <v>263886</v>
@@ -17885,7 +17885,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>1.69902098178864</v>
+        <v>1.69902086257935</v>
       </c>
       <c r="H604" t="n">
         <v>151879</v>
@@ -17914,7 +17914,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G605" t="n">
-        <v>1.62967336177826</v>
+        <v>1.62967324256897</v>
       </c>
       <c r="H605" t="n">
         <v>582733</v>
@@ -17943,7 +17943,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G606" t="n">
-        <v>1.64893662929535</v>
+        <v>1.64893651008606</v>
       </c>
       <c r="H606" t="n">
         <v>281947</v>
@@ -17972,7 +17972,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G607" t="n">
-        <v>1.55262017250061</v>
+        <v>1.5526202917099</v>
       </c>
       <c r="H607" t="n">
         <v>737184</v>
@@ -18001,7 +18001,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G608" t="n">
-        <v>1.55262017250061</v>
+        <v>1.5526202917099</v>
       </c>
       <c r="H608" t="n">
         <v>471725</v>
@@ -18204,7 +18204,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G615" t="n">
-        <v>1.51024115085602</v>
+        <v>1.51024091243744</v>
       </c>
       <c r="H615" t="n">
         <v>203705</v>
@@ -18233,7 +18233,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G616" t="n">
-        <v>1.48404288291931</v>
+        <v>1.4840430021286</v>
       </c>
       <c r="H616" t="n">
         <v>168974</v>
@@ -18320,7 +18320,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G619" t="n">
-        <v>1.49174809455872</v>
+        <v>1.49174821376801</v>
       </c>
       <c r="H619" t="n">
         <v>204025</v>
@@ -18378,7 +18378,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G621" t="n">
-        <v>1.5834413766861</v>
+        <v>1.58344149589539</v>
       </c>
       <c r="H621" t="n">
         <v>333930</v>
@@ -18465,7 +18465,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G624" t="n">
-        <v>1.568030834198</v>
+        <v>1.56803095340729</v>
       </c>
       <c r="H624" t="n">
         <v>193703</v>
@@ -18668,7 +18668,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.65664184093475</v>
+        <v>1.65664172172546</v>
       </c>
       <c r="H631" t="n">
         <v>549717</v>
@@ -18697,7 +18697,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G632" t="n">
-        <v>1.61040985584259</v>
+        <v>1.61040997505188</v>
       </c>
       <c r="H632" t="n">
         <v>855956</v>
@@ -18726,7 +18726,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>1.60270464420319</v>
+        <v>1.60270476341248</v>
       </c>
       <c r="H633" t="n">
         <v>85820</v>
@@ -18784,7 +18784,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G635" t="n">
-        <v>1.5757360458374</v>
+        <v>1.57573616504669</v>
       </c>
       <c r="H635" t="n">
         <v>242640</v>
@@ -18813,7 +18813,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G636" t="n">
-        <v>1.568030834198</v>
+        <v>1.56803095340729</v>
       </c>
       <c r="H636" t="n">
         <v>66719</v>
@@ -18842,7 +18842,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>1.5603255033493</v>
+        <v>1.56032562255859</v>
       </c>
       <c r="H637" t="n">
         <v>214757</v>
@@ -18871,7 +18871,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G638" t="n">
-        <v>1.568030834198</v>
+        <v>1.56803095340729</v>
       </c>
       <c r="H638" t="n">
         <v>161379</v>
@@ -18900,7 +18900,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>1.5872939825058</v>
+        <v>1.58729410171509</v>
       </c>
       <c r="H639" t="n">
         <v>207577</v>
@@ -18958,7 +18958,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G641" t="n">
-        <v>1.5872939825058</v>
+        <v>1.58729410171509</v>
       </c>
       <c r="H641" t="n">
         <v>51370</v>
@@ -19161,7 +19161,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G648" t="n">
-        <v>1.5834413766861</v>
+        <v>1.58344149589539</v>
       </c>
       <c r="H648" t="n">
         <v>146801</v>
@@ -19306,7 +19306,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G653" t="n">
-        <v>1.568030834198</v>
+        <v>1.56803095340729</v>
       </c>
       <c r="H653" t="n">
         <v>135437</v>
@@ -19335,7 +19335,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>1.5834413766861</v>
+        <v>1.58344149589539</v>
       </c>
       <c r="H654" t="n">
         <v>118580</v>
@@ -19393,7 +19393,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G656" t="n">
-        <v>1.62582051753998</v>
+        <v>1.62582063674927</v>
       </c>
       <c r="H656" t="n">
         <v>262107</v>
@@ -19422,7 +19422,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G657" t="n">
-        <v>1.62967336177826</v>
+        <v>1.62967324256897</v>
       </c>
       <c r="H657" t="n">
         <v>246235</v>
@@ -19451,7 +19451,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G658" t="n">
-        <v>1.66049468517303</v>
+        <v>1.66049456596375</v>
       </c>
       <c r="H658" t="n">
         <v>104995</v>
@@ -19625,7 +19625,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G664" t="n">
-        <v>1.5834413766861</v>
+        <v>1.58344149589539</v>
       </c>
       <c r="H664" t="n">
         <v>30952</v>
@@ -19654,7 +19654,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G665" t="n">
-        <v>1.5872939825058</v>
+        <v>1.58729410171509</v>
       </c>
       <c r="H665" t="n">
         <v>22720</v>
@@ -19683,7 +19683,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G666" t="n">
-        <v>1.5834413766861</v>
+        <v>1.58344149589539</v>
       </c>
       <c r="H666" t="n">
         <v>44250</v>
@@ -19712,7 +19712,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>1.57188332080841</v>
+        <v>1.5718834400177</v>
       </c>
       <c r="H667" t="n">
         <v>64941</v>
@@ -19741,7 +19741,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G668" t="n">
-        <v>1.5641782283783</v>
+        <v>1.56417810916901</v>
       </c>
       <c r="H668" t="n">
         <v>69258</v>
@@ -19770,7 +19770,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G669" t="n">
-        <v>1.54876744747162</v>
+        <v>1.54876756668091</v>
       </c>
       <c r="H669" t="n">
         <v>82171</v>
@@ -19799,7 +19799,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G670" t="n">
-        <v>1.54491484165192</v>
+        <v>1.54491496086121</v>
       </c>
       <c r="H670" t="n">
         <v>132245</v>
@@ -19828,7 +19828,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G671" t="n">
-        <v>1.53643894195557</v>
+        <v>1.53643906116486</v>
       </c>
       <c r="H671" t="n">
         <v>43814</v>
@@ -19886,7 +19886,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G673" t="n">
-        <v>1.5641782283783</v>
+        <v>1.56417810916901</v>
       </c>
       <c r="H673" t="n">
         <v>29557</v>
@@ -19915,7 +19915,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G674" t="n">
-        <v>1.55262017250061</v>
+        <v>1.5526202917099</v>
       </c>
       <c r="H674" t="n">
         <v>17422</v>
@@ -19973,7 +19973,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G676" t="n">
-        <v>1.5872939825058</v>
+        <v>1.58729410171509</v>
       </c>
       <c r="H676" t="n">
         <v>89787</v>
@@ -20002,7 +20002,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>1.5757360458374</v>
+        <v>1.57573616504669</v>
       </c>
       <c r="H677" t="n">
         <v>10443</v>
@@ -20031,7 +20031,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>1.5603255033493</v>
+        <v>1.56032562255859</v>
       </c>
       <c r="H678" t="n">
         <v>28611</v>
@@ -20089,7 +20089,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G680" t="n">
-        <v>1.54491484165192</v>
+        <v>1.54491496086121</v>
       </c>
       <c r="H680" t="n">
         <v>24130</v>
@@ -20147,7 +20147,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G682" t="n">
-        <v>1.54876744747162</v>
+        <v>1.54876756668091</v>
       </c>
       <c r="H682" t="n">
         <v>33294</v>
@@ -20176,7 +20176,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G683" t="n">
-        <v>1.5641782283783</v>
+        <v>1.56417810916901</v>
       </c>
       <c r="H683" t="n">
         <v>29291</v>
@@ -20205,7 +20205,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G684" t="n">
-        <v>1.5757360458374</v>
+        <v>1.57573616504669</v>
       </c>
       <c r="H684" t="n">
         <v>80695</v>
@@ -20263,7 +20263,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G686" t="n">
-        <v>1.54491484165192</v>
+        <v>1.54491496086121</v>
       </c>
       <c r="H686" t="n">
         <v>39065</v>
@@ -20321,7 +20321,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G688" t="n">
-        <v>1.5641782283783</v>
+        <v>1.56417810916901</v>
       </c>
       <c r="H688" t="n">
         <v>28414</v>
@@ -20350,7 +20350,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>1.5641782283783</v>
+        <v>1.56417810916901</v>
       </c>
       <c r="H689" t="n">
         <v>7879</v>
@@ -20379,7 +20379,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G690" t="n">
-        <v>1.57188332080841</v>
+        <v>1.5718834400177</v>
       </c>
       <c r="H690" t="n">
         <v>148590</v>
@@ -20408,7 +20408,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G691" t="n">
-        <v>1.568030834198</v>
+        <v>1.56803095340729</v>
       </c>
       <c r="H691" t="n">
         <v>18850</v>
@@ -20437,7 +20437,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G692" t="n">
-        <v>1.5757360458374</v>
+        <v>1.57573616504669</v>
       </c>
       <c r="H692" t="n">
         <v>147847</v>
@@ -20466,7 +20466,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>1.5757360458374</v>
+        <v>1.57573616504669</v>
       </c>
       <c r="H693" t="n">
         <v>65979</v>
@@ -20495,7 +20495,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>1.5757360458374</v>
+        <v>1.57573616504669</v>
       </c>
       <c r="H694" t="n">
         <v>114935</v>
@@ -20553,7 +20553,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G696" t="n">
-        <v>1.5872939825058</v>
+        <v>1.58729410171509</v>
       </c>
       <c r="H696" t="n">
         <v>172666</v>
@@ -20611,7 +20611,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G698" t="n">
-        <v>1.61040985584259</v>
+        <v>1.61040997505188</v>
       </c>
       <c r="H698" t="n">
         <v>224600</v>
@@ -20669,7 +20669,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>1.65664184093475</v>
+        <v>1.65664172172546</v>
       </c>
       <c r="H700" t="n">
         <v>338735</v>
@@ -20698,7 +20698,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G701" t="n">
-        <v>1.61040985584259</v>
+        <v>1.61040997505188</v>
       </c>
       <c r="H701" t="n">
         <v>376283</v>
@@ -20727,7 +20727,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G702" t="n">
-        <v>1.5641782283783</v>
+        <v>1.56417810916901</v>
       </c>
       <c r="H702" t="n">
         <v>302442</v>
@@ -20756,7 +20756,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>1.54876744747162</v>
+        <v>1.54876756668091</v>
       </c>
       <c r="H703" t="n">
         <v>182516</v>
@@ -20785,7 +20785,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G704" t="n">
-        <v>1.55262017250061</v>
+        <v>1.5526202917099</v>
       </c>
       <c r="H704" t="n">
         <v>71375</v>
@@ -20814,7 +20814,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G705" t="n">
-        <v>1.5641782283783</v>
+        <v>1.56417810916901</v>
       </c>
       <c r="H705" t="n">
         <v>50205</v>
@@ -20988,7 +20988,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G711" t="n">
-        <v>1.4347288608551</v>
+        <v>1.43472874164581</v>
       </c>
       <c r="H711" t="n">
         <v>153665</v>
@@ -21017,7 +21017,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G712" t="n">
-        <v>1.41777729988098</v>
+        <v>1.41777718067169</v>
       </c>
       <c r="H712" t="n">
         <v>50778</v>
@@ -21046,7 +21046,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G713" t="n">
-        <v>1.419318318367</v>
+        <v>1.41931843757629</v>
       </c>
       <c r="H713" t="n">
         <v>83766</v>
@@ -21075,7 +21075,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G714" t="n">
-        <v>1.42394161224365</v>
+        <v>1.42394149303436</v>
       </c>
       <c r="H714" t="n">
         <v>163026</v>
@@ -21104,7 +21104,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G715" t="n">
-        <v>1.44089329242706</v>
+        <v>1.44089317321777</v>
       </c>
       <c r="H715" t="n">
         <v>232230</v>
@@ -21133,7 +21133,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G716" t="n">
-        <v>1.39157915115356</v>
+        <v>1.39157927036285</v>
       </c>
       <c r="H716" t="n">
         <v>274472</v>
@@ -21191,7 +21191,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G718" t="n">
-        <v>1.25442457199097</v>
+        <v>1.25442469120026</v>
       </c>
       <c r="H718" t="n">
         <v>335970</v>
@@ -21220,7 +21220,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G719" t="n">
-        <v>1.21281599998474</v>
+        <v>1.21281588077545</v>
       </c>
       <c r="H719" t="n">
         <v>139380</v>
@@ -21278,7 +21278,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G721" t="n">
-        <v>1.2420961856842</v>
+        <v>1.24209606647491</v>
       </c>
       <c r="H721" t="n">
         <v>109578</v>
@@ -21365,7 +21365,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G724" t="n">
-        <v>1.29449224472046</v>
+        <v>1.29449212551117</v>
       </c>
       <c r="H724" t="n">
         <v>181223</v>
@@ -21597,7 +21597,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G732" t="n">
-        <v>1.28370487689972</v>
+        <v>1.28370475769043</v>
       </c>
       <c r="H732" t="n">
         <v>140675</v>
@@ -21626,7 +21626,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G733" t="n">
-        <v>1.28062272071838</v>
+        <v>1.28062260150909</v>
       </c>
       <c r="H733" t="n">
         <v>88818</v>
@@ -21684,7 +21684,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G735" t="n">
-        <v>1.18353581428528</v>
+        <v>1.18353569507599</v>
       </c>
       <c r="H735" t="n">
         <v>196589</v>
@@ -21713,7 +21713,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G736" t="n">
-        <v>1.19278204441071</v>
+        <v>1.19278216362</v>
       </c>
       <c r="H736" t="n">
         <v>132815</v>
@@ -21800,7 +21800,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G739" t="n">
-        <v>1.14963233470917</v>
+        <v>1.14963245391846</v>
       </c>
       <c r="H739" t="n">
         <v>267990</v>
@@ -21916,7 +21916,7 @@
         <v>1.59599995613098</v>
       </c>
       <c r="G743" t="n">
-        <v>1.22976768016815</v>
+        <v>1.22976756095886</v>
       </c>
       <c r="H743" t="n">
         <v>288308</v>
@@ -22032,7 +22032,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G747" t="n">
-        <v>1.24055516719818</v>
+        <v>1.24055504798889</v>
       </c>
       <c r="H747" t="n">
         <v>219161</v>
@@ -22061,7 +22061,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G748" t="n">
-        <v>1.23593175411224</v>
+        <v>1.23593187332153</v>
       </c>
       <c r="H748" t="n">
         <v>167356</v>
@@ -22148,7 +22148,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G751" t="n">
-        <v>1.26212990283966</v>
+        <v>1.26213002204895</v>
       </c>
       <c r="H751" t="n">
         <v>79516</v>
@@ -22177,7 +22177,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G752" t="n">
-        <v>1.22668564319611</v>
+        <v>1.22668552398682</v>
       </c>
       <c r="H752" t="n">
         <v>91194</v>
@@ -22322,7 +22322,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G757" t="n">
-        <v>1.12035226821899</v>
+        <v>1.1203521490097</v>
       </c>
       <c r="H757" t="n">
         <v>278030</v>
@@ -22496,7 +22496,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G763" t="n">
-        <v>1.10802364349365</v>
+        <v>1.10802352428436</v>
       </c>
       <c r="H763" t="n">
         <v>105826</v>
@@ -22525,7 +22525,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G764" t="n">
-        <v>1.1126469373703</v>
+        <v>1.11264681816101</v>
       </c>
       <c r="H764" t="n">
         <v>52158</v>
@@ -22815,7 +22815,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G774" t="n">
-        <v>1.14346826076508</v>
+        <v>1.1434680223465</v>
       </c>
       <c r="H774" t="n">
         <v>64915</v>
@@ -22960,7 +22960,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G779" t="n">
-        <v>1.13268065452576</v>
+        <v>1.13268077373505</v>
       </c>
       <c r="H779" t="n">
         <v>70973</v>
@@ -23018,7 +23018,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G781" t="n">
-        <v>1.13268065452576</v>
+        <v>1.13268077373505</v>
       </c>
       <c r="H781" t="n">
         <v>229666</v>
@@ -23105,7 +23105,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G784" t="n">
-        <v>1.10802364349365</v>
+        <v>1.10802352428436</v>
       </c>
       <c r="H784" t="n">
         <v>288285</v>
@@ -23134,7 +23134,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G785" t="n">
-        <v>1.10340070724487</v>
+        <v>1.10340058803558</v>
       </c>
       <c r="H785" t="n">
         <v>131201</v>
@@ -23250,7 +23250,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G789" t="n">
-        <v>1.13884496688843</v>
+        <v>1.13884508609772</v>
       </c>
       <c r="H789" t="n">
         <v>460325</v>
@@ -23453,7 +23453,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G796" t="n">
-        <v>1.22668564319611</v>
+        <v>1.22668552398682</v>
       </c>
       <c r="H796" t="n">
         <v>484647</v>
@@ -23482,7 +23482,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G797" t="n">
-        <v>1.24671924114227</v>
+        <v>1.24671936035156</v>
       </c>
       <c r="H797" t="n">
         <v>447249</v>
@@ -23511,7 +23511,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G798" t="n">
-        <v>1.23593175411224</v>
+        <v>1.23593187332153</v>
       </c>
       <c r="H798" t="n">
         <v>460843</v>
@@ -23598,7 +23598,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G801" t="n">
-        <v>1.24055516719818</v>
+        <v>1.24055504798889</v>
       </c>
       <c r="H801" t="n">
         <v>270293</v>
@@ -23685,7 +23685,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G804" t="n">
-        <v>1.2420961856842</v>
+        <v>1.24209606647491</v>
       </c>
       <c r="H804" t="n">
         <v>506783</v>
@@ -23743,7 +23743,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G806" t="n">
-        <v>1.30219769477844</v>
+        <v>1.30219757556915</v>
       </c>
       <c r="H806" t="n">
         <v>932950</v>
@@ -23801,7 +23801,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G808" t="n">
-        <v>1.28678691387177</v>
+        <v>1.28678703308105</v>
       </c>
       <c r="H808" t="n">
         <v>401489</v>
@@ -23859,7 +23859,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G810" t="n">
-        <v>1.24055516719818</v>
+        <v>1.24055504798889</v>
       </c>
       <c r="H810" t="n">
         <v>527865</v>
@@ -23917,7 +23917,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G812" t="n">
-        <v>1.18199467658997</v>
+        <v>1.18199479579926</v>
       </c>
       <c r="H812" t="n">
         <v>368691</v>
@@ -24004,7 +24004,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>1.17120730876923</v>
+        <v>1.17120718955994</v>
       </c>
       <c r="H815" t="n">
         <v>386583</v>
@@ -24033,7 +24033,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G816" t="n">
-        <v>1.16658413410187</v>
+        <v>1.16658401489258</v>
       </c>
       <c r="H816" t="n">
         <v>480960</v>
@@ -24062,7 +24062,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G817" t="n">
-        <v>1.16658413410187</v>
+        <v>1.16658401489258</v>
       </c>
       <c r="H817" t="n">
         <v>450971</v>
@@ -24149,7 +24149,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.17120730876923</v>
+        <v>1.17120718955994</v>
       </c>
       <c r="H820" t="n">
         <v>647734</v>
@@ -24207,7 +24207,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G822" t="n">
-        <v>1.17120730876923</v>
+        <v>1.17120718955994</v>
       </c>
       <c r="H822" t="n">
         <v>400468</v>
@@ -24265,7 +24265,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G824" t="n">
-        <v>1.13422191143036</v>
+        <v>1.13422179222107</v>
       </c>
       <c r="H824" t="n">
         <v>196688</v>
@@ -24352,7 +24352,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G827" t="n">
-        <v>1.17120730876923</v>
+        <v>1.17120718955994</v>
       </c>
       <c r="H827" t="n">
         <v>703089</v>
@@ -24381,7 +24381,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G828" t="n">
-        <v>1.14963233470917</v>
+        <v>1.14963245391846</v>
       </c>
       <c r="H828" t="n">
         <v>627801</v>
@@ -24584,7 +24584,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G835" t="n">
-        <v>1.26367104053497</v>
+        <v>1.26367092132568</v>
       </c>
       <c r="H835" t="n">
         <v>1706082</v>
@@ -24700,7 +24700,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G839" t="n">
-        <v>1.30527973175049</v>
+        <v>1.3052796125412</v>
       </c>
       <c r="H839" t="n">
         <v>224654</v>
@@ -24758,7 +24758,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G841" t="n">
-        <v>1.28678691387177</v>
+        <v>1.28678703308105</v>
       </c>
       <c r="H841" t="n">
         <v>628238</v>
@@ -24787,7 +24787,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G842" t="n">
-        <v>1.26367104053497</v>
+        <v>1.26367092132568</v>
       </c>
       <c r="H842" t="n">
         <v>494881</v>
@@ -24845,7 +24845,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G844" t="n">
-        <v>1.28062272071838</v>
+        <v>1.28062260150909</v>
       </c>
       <c r="H844" t="n">
         <v>217625</v>
@@ -24932,7 +24932,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G847" t="n">
-        <v>1.28986895084381</v>
+        <v>1.28986918926239</v>
       </c>
       <c r="H847" t="n">
         <v>239893</v>
@@ -24961,7 +24961,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G848" t="n">
-        <v>1.33944821357727</v>
+        <v>1.33944809436798</v>
       </c>
       <c r="H848" t="n">
         <v>524876</v>
@@ -24990,7 +24990,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G849" t="n">
-        <v>1.29230737686157</v>
+        <v>1.29230749607086</v>
       </c>
       <c r="H849" t="n">
         <v>481253</v>
@@ -25019,7 +25019,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G850" t="n">
-        <v>1.26629865169525</v>
+        <v>1.26629853248596</v>
       </c>
       <c r="H850" t="n">
         <v>401129</v>
@@ -25077,7 +25077,7 @@
         <v>1.5</v>
       </c>
       <c r="G852" t="n">
-        <v>1.21915781497955</v>
+        <v>1.21915793418884</v>
       </c>
       <c r="H852" t="n">
         <v>543361</v>
@@ -25135,7 +25135,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G854" t="n">
-        <v>1.17689383029938</v>
+        <v>1.1768935918808</v>
       </c>
       <c r="H854" t="n">
         <v>682139</v>
@@ -25164,7 +25164,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G855" t="n">
-        <v>1.14113187789917</v>
+        <v>1.14113175868988</v>
       </c>
       <c r="H855" t="n">
         <v>813355</v>
@@ -25251,7 +25251,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G858" t="n">
-        <v>1.11349749565125</v>
+        <v>1.11349761486053</v>
       </c>
       <c r="H858" t="n">
         <v>252388</v>
@@ -25367,7 +25367,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G862" t="n">
-        <v>1.06473112106323</v>
+        <v>1.06473135948181</v>
       </c>
       <c r="H862" t="n">
         <v>258029</v>
@@ -25425,7 +25425,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G864" t="n">
-        <v>1.07285892963409</v>
+        <v>1.07285904884338</v>
       </c>
       <c r="H864" t="n">
         <v>330557</v>
@@ -25483,7 +25483,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G866" t="n">
-        <v>1.00133502483368</v>
+        <v>1.00133490562439</v>
       </c>
       <c r="H866" t="n">
         <v>724865</v>
@@ -25541,7 +25541,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G868" t="n">
-        <v>1.00458598136902</v>
+        <v>1.00458610057831</v>
       </c>
       <c r="H868" t="n">
         <v>281715</v>
@@ -25570,7 +25570,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G869" t="n">
-        <v>1.01271390914917</v>
+        <v>1.01271378993988</v>
       </c>
       <c r="H869" t="n">
         <v>559963</v>
@@ -25657,7 +25657,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G872" t="n">
-        <v>0.976951897144318</v>
+        <v>0.976951837539673</v>
       </c>
       <c r="H872" t="n">
         <v>360512</v>
@@ -25686,7 +25686,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G873" t="n">
-        <v>0.967198610305786</v>
+        <v>0.967198669910431</v>
       </c>
       <c r="H873" t="n">
         <v>284283</v>
@@ -25715,7 +25715,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G874" t="n">
-        <v>0.972075164318085</v>
+        <v>0.97207510471344</v>
       </c>
       <c r="H874" t="n">
         <v>257772</v>
@@ -25744,7 +25744,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G875" t="n">
-        <v>0.95581990480423</v>
+        <v>0.95581978559494</v>
       </c>
       <c r="H875" t="n">
         <v>647591</v>
@@ -25802,7 +25802,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G877" t="n">
-        <v>0.91193014383316</v>
+        <v>0.911930084228516</v>
       </c>
       <c r="H877" t="n">
         <v>519138</v>
@@ -25831,7 +25831,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G878" t="n">
-        <v>0.910304605960846</v>
+        <v>0.910304546356201</v>
       </c>
       <c r="H878" t="n">
         <v>168578</v>
@@ -25860,7 +25860,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G879" t="n">
-        <v>0.928185522556305</v>
+        <v>0.92818546295166</v>
       </c>
       <c r="H879" t="n">
         <v>313401</v>
@@ -25889,7 +25889,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G880" t="n">
-        <v>0.924934387207031</v>
+        <v>0.924934446811676</v>
       </c>
       <c r="H880" t="n">
         <v>487227</v>
@@ -25947,7 +25947,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G882" t="n">
-        <v>0.950943112373352</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H882" t="n">
         <v>558073</v>
@@ -26063,7 +26063,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G886" t="n">
-        <v>0.95581990480423</v>
+        <v>0.95581978559494</v>
       </c>
       <c r="H886" t="n">
         <v>245568</v>
@@ -26092,7 +26092,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G887" t="n">
-        <v>0.965573012828827</v>
+        <v>0.965573072433472</v>
       </c>
       <c r="H887" t="n">
         <v>179644</v>
@@ -26121,7 +26121,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G888" t="n">
-        <v>0.965573012828827</v>
+        <v>0.965573072433472</v>
       </c>
       <c r="H888" t="n">
         <v>298561</v>
@@ -26150,7 +26150,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G889" t="n">
-        <v>0.983454048633575</v>
+        <v>0.98345410823822</v>
       </c>
       <c r="H889" t="n">
         <v>871314</v>
@@ -26179,7 +26179,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G890" t="n">
-        <v>0.976951897144318</v>
+        <v>0.976951837539673</v>
       </c>
       <c r="H890" t="n">
         <v>184117</v>
@@ -26208,7 +26208,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G891" t="n">
-        <v>0.988330602645874</v>
+        <v>0.988330721855164</v>
       </c>
       <c r="H891" t="n">
         <v>484607</v>
@@ -26266,7 +26266,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G893" t="n">
-        <v>1.03547143936157</v>
+        <v>1.03547132015228</v>
       </c>
       <c r="H893" t="n">
         <v>262605</v>
@@ -26411,7 +26411,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G898" t="n">
-        <v>1.01271390914917</v>
+        <v>1.01271378993988</v>
       </c>
       <c r="H898" t="n">
         <v>139963</v>
@@ -26440,7 +26440,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G899" t="n">
-        <v>0.976951897144318</v>
+        <v>0.976951837539673</v>
       </c>
       <c r="H899" t="n">
         <v>509228</v>
@@ -26469,7 +26469,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G900" t="n">
-        <v>0.994832873344421</v>
+        <v>0.994832754135132</v>
       </c>
       <c r="H900" t="n">
         <v>266551</v>
@@ -26498,7 +26498,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G901" t="n">
-        <v>0.981828451156616</v>
+        <v>0.981828391551971</v>
       </c>
       <c r="H901" t="n">
         <v>152179</v>
@@ -26527,7 +26527,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G902" t="n">
-        <v>1.01271390914917</v>
+        <v>1.01271378993988</v>
       </c>
       <c r="H902" t="n">
         <v>531062</v>
@@ -26585,7 +26585,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G904" t="n">
-        <v>0.983454048633575</v>
+        <v>0.98345410823822</v>
       </c>
       <c r="H904" t="n">
         <v>215882</v>
@@ -26614,7 +26614,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G905" t="n">
-        <v>1.00133502483368</v>
+        <v>1.00133490562439</v>
       </c>
       <c r="H905" t="n">
         <v>179778</v>
@@ -26643,7 +26643,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.02409255504608</v>
+        <v>1.02409267425537</v>
       </c>
       <c r="H906" t="n">
         <v>1264666</v>
@@ -26817,7 +26817,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G912" t="n">
-        <v>1.02409255504608</v>
+        <v>1.02409267425537</v>
       </c>
       <c r="H912" t="n">
         <v>582808</v>
@@ -26846,7 +26846,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G913" t="n">
-        <v>1.02409255504608</v>
+        <v>1.02409267425537</v>
       </c>
       <c r="H913" t="n">
         <v>228992</v>
@@ -27020,7 +27020,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G919" t="n">
-        <v>0.950943112373352</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H919" t="n">
         <v>78870</v>
@@ -27049,7 +27049,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G920" t="n">
-        <v>0.952568709850311</v>
+        <v>0.952568829059601</v>
       </c>
       <c r="H920" t="n">
         <v>300930</v>
@@ -27078,7 +27078,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G921" t="n">
-        <v>0.920057833194733</v>
+        <v>0.920057773590088</v>
       </c>
       <c r="H921" t="n">
         <v>161762</v>
@@ -27107,7 +27107,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G922" t="n">
-        <v>0.928185522556305</v>
+        <v>0.92818546295166</v>
       </c>
       <c r="H922" t="n">
         <v>341470</v>
@@ -27136,7 +27136,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G923" t="n">
-        <v>0.954194188117981</v>
+        <v>0.954194307327271</v>
       </c>
       <c r="H923" t="n">
         <v>172760</v>
@@ -27194,7 +27194,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G925" t="n">
-        <v>0.967198610305786</v>
+        <v>0.967198669910431</v>
       </c>
       <c r="H925" t="n">
         <v>74506</v>
@@ -27223,7 +27223,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G926" t="n">
-        <v>0.981828451156616</v>
+        <v>0.981828391551971</v>
       </c>
       <c r="H926" t="n">
         <v>93608</v>
@@ -27252,7 +27252,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G927" t="n">
-        <v>0.978577375411987</v>
+        <v>0.978577435016632</v>
       </c>
       <c r="H927" t="n">
         <v>266840</v>
@@ -27310,7 +27310,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G929" t="n">
-        <v>0.973700761795044</v>
+        <v>0.973700702190399</v>
       </c>
       <c r="H929" t="n">
         <v>161453</v>
@@ -27339,7 +27339,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G930" t="n">
-        <v>0.972075164318085</v>
+        <v>0.97207510471344</v>
       </c>
       <c r="H930" t="n">
         <v>189441</v>
@@ -27368,7 +27368,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G931" t="n">
-        <v>0.985079646110535</v>
+        <v>0.985079526901245</v>
       </c>
       <c r="H931" t="n">
         <v>318556</v>
@@ -27397,7 +27397,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G932" t="n">
-        <v>0.980202853679657</v>
+        <v>0.980202913284302</v>
       </c>
       <c r="H932" t="n">
         <v>171505</v>
@@ -27426,7 +27426,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G933" t="n">
-        <v>0.965573012828827</v>
+        <v>0.965573072433472</v>
       </c>
       <c r="H933" t="n">
         <v>137394</v>
@@ -27455,7 +27455,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G934" t="n">
-        <v>0.950943112373352</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H934" t="n">
         <v>215787</v>
@@ -27542,7 +27542,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G937" t="n">
-        <v>1.02409255504608</v>
+        <v>1.02409267425537</v>
       </c>
       <c r="H937" t="n">
         <v>325256</v>
@@ -27571,7 +27571,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G938" t="n">
-        <v>1.09236538410187</v>
+        <v>1.09236550331116</v>
       </c>
       <c r="H938" t="n">
         <v>1405944</v>
@@ -27600,7 +27600,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G939" t="n">
-        <v>1.14275741577148</v>
+        <v>1.14275729656219</v>
       </c>
       <c r="H939" t="n">
         <v>1400876</v>
@@ -27658,7 +27658,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G941" t="n">
-        <v>1.17689383029938</v>
+        <v>1.1768935918808</v>
       </c>
       <c r="H941" t="n">
         <v>840392</v>
@@ -27687,7 +27687,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G942" t="n">
-        <v>1.19640016555786</v>
+        <v>1.19640028476715</v>
       </c>
       <c r="H942" t="n">
         <v>683159</v>
@@ -27774,7 +27774,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G945" t="n">
-        <v>1.21753227710724</v>
+        <v>1.21753239631653</v>
       </c>
       <c r="H945" t="n">
         <v>851139</v>
@@ -27861,7 +27861,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G948" t="n">
-        <v>1.18014490604401</v>
+        <v>1.18014478683472</v>
       </c>
       <c r="H948" t="n">
         <v>311419</v>
@@ -27919,7 +27919,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G950" t="n">
-        <v>1.14600849151611</v>
+        <v>1.14600825309753</v>
       </c>
       <c r="H950" t="n">
         <v>820517</v>
@@ -27948,7 +27948,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G951" t="n">
-        <v>1.14600849151611</v>
+        <v>1.14600825309753</v>
       </c>
       <c r="H951" t="n">
         <v>546712</v>
@@ -28006,7 +28006,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G953" t="n">
-        <v>1.14600849151611</v>
+        <v>1.14600825309753</v>
       </c>
       <c r="H953" t="n">
         <v>165122</v>
@@ -28093,7 +28093,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G956" t="n">
-        <v>1.09561657905579</v>
+        <v>1.09561669826508</v>
       </c>
       <c r="H956" t="n">
         <v>303262</v>
@@ -28122,7 +28122,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G957" t="n">
-        <v>1.09399092197418</v>
+        <v>1.09399104118347</v>
       </c>
       <c r="H957" t="n">
         <v>189301</v>
@@ -28209,7 +28209,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G960" t="n">
-        <v>1.11674869060516</v>
+        <v>1.11674857139587</v>
       </c>
       <c r="H960" t="n">
         <v>536537</v>
@@ -28267,7 +28267,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G962" t="n">
-        <v>1.17039167881012</v>
+        <v>1.17039155960083</v>
       </c>
       <c r="H962" t="n">
         <v>292366</v>
@@ -28296,7 +28296,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G963" t="n">
-        <v>1.17364275455475</v>
+        <v>1.17364263534546</v>
       </c>
       <c r="H963" t="n">
         <v>247126</v>
@@ -28325,7 +28325,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G964" t="n">
-        <v>1.16226375102997</v>
+        <v>1.16226387023926</v>
       </c>
       <c r="H964" t="n">
         <v>427417</v>
@@ -28354,7 +28354,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G965" t="n">
-        <v>1.17039167881012</v>
+        <v>1.17039155960083</v>
       </c>
       <c r="H965" t="n">
         <v>347979</v>
@@ -28383,7 +28383,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G966" t="n">
-        <v>1.19314920902252</v>
+        <v>1.19314932823181</v>
       </c>
       <c r="H966" t="n">
         <v>565660</v>
@@ -28441,7 +28441,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G968" t="n">
-        <v>1.18339586257935</v>
+        <v>1.18339598178864</v>
       </c>
       <c r="H968" t="n">
         <v>275067</v>
@@ -28470,7 +28470,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G969" t="n">
-        <v>1.18502140045166</v>
+        <v>1.18502151966095</v>
       </c>
       <c r="H969" t="n">
         <v>99659</v>
@@ -28528,7 +28528,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G971" t="n">
-        <v>1.17039167881012</v>
+        <v>1.17039155960083</v>
       </c>
       <c r="H971" t="n">
         <v>245082</v>
@@ -28586,7 +28586,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G973" t="n">
-        <v>1.26467323303223</v>
+        <v>1.26467311382294</v>
       </c>
       <c r="H973" t="n">
         <v>2359685</v>
@@ -28644,7 +28644,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G975" t="n">
-        <v>1.25491976737976</v>
+        <v>1.25492000579834</v>
       </c>
       <c r="H975" t="n">
         <v>1524999</v>
@@ -28673,7 +28673,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G976" t="n">
-        <v>1.31018829345703</v>
+        <v>1.31018841266632</v>
       </c>
       <c r="H976" t="n">
         <v>1546549</v>
@@ -28702,7 +28702,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G977" t="n">
-        <v>1.36058032512665</v>
+        <v>1.36058020591736</v>
       </c>
       <c r="H977" t="n">
         <v>1307448</v>
@@ -28731,7 +28731,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G978" t="n">
-        <v>1.38008654117584</v>
+        <v>1.38008677959442</v>
       </c>
       <c r="H978" t="n">
         <v>1454937</v>
@@ -28818,7 +28818,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G981" t="n">
-        <v>1.38008654117584</v>
+        <v>1.38008677959442</v>
       </c>
       <c r="H981" t="n">
         <v>773986</v>
@@ -28905,7 +28905,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G984" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H984" t="n">
         <v>685025</v>
@@ -28934,7 +28934,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G985" t="n">
-        <v>1.34920132160187</v>
+        <v>1.34920144081116</v>
       </c>
       <c r="H985" t="n">
         <v>973491</v>
@@ -28992,7 +28992,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>1.39796781539917</v>
+        <v>1.39796769618988</v>
       </c>
       <c r="H987" t="n">
         <v>1419810</v>
@@ -29108,7 +29108,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G991" t="n">
-        <v>1.51988351345062</v>
+        <v>1.51988363265991</v>
       </c>
       <c r="H991" t="n">
         <v>554070</v>
@@ -29137,7 +29137,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G992" t="n">
-        <v>1.52150893211365</v>
+        <v>1.52150905132294</v>
       </c>
       <c r="H992" t="n">
         <v>953321</v>
@@ -29311,7 +29311,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G998" t="n">
-        <v>1.45811295509338</v>
+        <v>1.45811283588409</v>
       </c>
       <c r="H998" t="n">
         <v>783048</v>
@@ -29340,7 +29340,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G999" t="n">
-        <v>1.45486164093018</v>
+        <v>1.45486176013947</v>
       </c>
       <c r="H999" t="n">
         <v>451260</v>
@@ -29601,7 +29601,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.58327972888947</v>
+        <v>1.58327960968018</v>
       </c>
       <c r="H1008" t="n">
         <v>374651</v>
@@ -29717,7 +29717,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.54589223861694</v>
+        <v>1.54589211940765</v>
       </c>
       <c r="H1012" t="n">
         <v>206909</v>
@@ -29746,7 +29746,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.51988351345062</v>
+        <v>1.51988363265991</v>
       </c>
       <c r="H1013" t="n">
         <v>347234</v>
@@ -29775,7 +29775,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.51663255691528</v>
+        <v>1.51663243770599</v>
       </c>
       <c r="H1014" t="n">
         <v>315138</v>
@@ -29833,7 +29833,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.52150893211365</v>
+        <v>1.52150905132294</v>
       </c>
       <c r="H1016" t="n">
         <v>237239</v>
@@ -29862,7 +29862,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.46949148178101</v>
+        <v>1.4694916009903</v>
       </c>
       <c r="H1017" t="n">
         <v>461028</v>
@@ -29949,7 +29949,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.46298944950104</v>
+        <v>1.46298933029175</v>
       </c>
       <c r="H1020" t="n">
         <v>203350</v>
@@ -29978,7 +29978,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.47924494743347</v>
+        <v>1.47924506664276</v>
       </c>
       <c r="H1021" t="n">
         <v>307164</v>
@@ -30094,7 +30094,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.46298944950104</v>
+        <v>1.46298933029175</v>
       </c>
       <c r="H1025" t="n">
         <v>529724</v>
@@ -30152,7 +30152,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.47924494743347</v>
+        <v>1.47924506664276</v>
       </c>
       <c r="H1027" t="n">
         <v>309303</v>
@@ -30210,7 +30210,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.48737263679504</v>
+        <v>1.48737275600433</v>
       </c>
       <c r="H1029" t="n">
         <v>427649</v>
@@ -30239,7 +30239,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.45811295509338</v>
+        <v>1.45811283588409</v>
       </c>
       <c r="H1030" t="n">
         <v>504872</v>
@@ -30297,7 +30297,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.46136391162872</v>
+        <v>1.46136379241943</v>
       </c>
       <c r="H1032" t="n">
         <v>449756</v>
@@ -30384,7 +30384,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.48737263679504</v>
+        <v>1.48737275600433</v>
       </c>
       <c r="H1035" t="n">
         <v>310049</v>
@@ -30413,7 +30413,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.45323622226715</v>
+        <v>1.45323634147644</v>
       </c>
       <c r="H1036" t="n">
         <v>355571</v>
@@ -30442,7 +30442,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H1037" t="n">
         <v>891765</v>
@@ -30471,7 +30471,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.37358462810516</v>
+        <v>1.37358450889587</v>
       </c>
       <c r="H1038" t="n">
         <v>478695</v>
@@ -30558,7 +30558,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.48737263679504</v>
+        <v>1.48737275600433</v>
       </c>
       <c r="H1041" t="n">
         <v>575646</v>
@@ -30587,7 +30587,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.49387490749359</v>
+        <v>1.4938747882843</v>
       </c>
       <c r="H1042" t="n">
         <v>1257845</v>
@@ -30616,7 +30616,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.49550044536591</v>
+        <v>1.49550032615662</v>
       </c>
       <c r="H1043" t="n">
         <v>568502</v>
@@ -30703,7 +30703,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.58002853393555</v>
+        <v>1.58002865314484</v>
       </c>
       <c r="H1046" t="n">
         <v>1055118</v>
@@ -30732,7 +30732,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.5979095697403</v>
+        <v>1.59790945053101</v>
       </c>
       <c r="H1047" t="n">
         <v>539223</v>
@@ -30761,7 +30761,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.61416494846344</v>
+        <v>1.61416506767273</v>
       </c>
       <c r="H1048" t="n">
         <v>578409</v>
@@ -30790,7 +30790,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.64179933071136</v>
+        <v>1.64179921150208</v>
       </c>
       <c r="H1049" t="n">
         <v>1164464</v>
@@ -30819,7 +30819,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.73933207988739</v>
+        <v>1.7393319606781</v>
       </c>
       <c r="H1050" t="n">
         <v>1389374</v>
@@ -30848,7 +30848,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.70682108402252</v>
+        <v>1.70682096481323</v>
       </c>
       <c r="H1051" t="n">
         <v>1021557</v>
@@ -30906,7 +30906,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.51988351345062</v>
+        <v>1.51988363265991</v>
       </c>
       <c r="H1053" t="n">
         <v>1451082</v>
@@ -30964,7 +30964,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.49387490749359</v>
+        <v>1.4938747882843</v>
       </c>
       <c r="H1055" t="n">
         <v>880804</v>
@@ -30993,7 +30993,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.45486164093018</v>
+        <v>1.45486176013947</v>
       </c>
       <c r="H1056" t="n">
         <v>670082</v>
@@ -31022,7 +31022,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.39796781539917</v>
+        <v>1.39796769618988</v>
       </c>
       <c r="H1057" t="n">
         <v>851747</v>
@@ -31051,7 +31051,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.34920132160187</v>
+        <v>1.34920144081116</v>
       </c>
       <c r="H1058" t="n">
         <v>1083954</v>
@@ -31109,7 +31109,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.28580510616302</v>
+        <v>1.28580522537231</v>
       </c>
       <c r="H1060" t="n">
         <v>925237</v>
@@ -31138,7 +31138,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.20777916908264</v>
+        <v>1.20777904987335</v>
       </c>
       <c r="H1061" t="n">
         <v>605848</v>
@@ -31196,7 +31196,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.02409255504608</v>
+        <v>1.02409267425537</v>
       </c>
       <c r="H1063" t="n">
         <v>757008</v>
@@ -31225,7 +31225,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.978577375411987</v>
+        <v>0.978577435016632</v>
       </c>
       <c r="H1064" t="n">
         <v>797870</v>
@@ -31254,7 +31254,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.970449686050415</v>
+        <v>0.97044962644577</v>
       </c>
       <c r="H1065" t="n">
         <v>869739</v>
@@ -31312,7 +31312,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.902176737785339</v>
+        <v>0.902176856994629</v>
       </c>
       <c r="H1067" t="n">
         <v>1423220</v>
@@ -31341,7 +31341,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.817648589611053</v>
+        <v>0.817648649215698</v>
       </c>
       <c r="H1068" t="n">
         <v>842683</v>
@@ -31370,7 +31370,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.845282733440399</v>
+        <v>0.845282793045044</v>
       </c>
       <c r="H1069" t="n">
         <v>1004100</v>
@@ -31428,7 +31428,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.820899665355682</v>
+        <v>0.820899605751038</v>
       </c>
       <c r="H1071" t="n">
         <v>902725</v>
@@ -31457,7 +31457,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.861538171768188</v>
+        <v>0.861538231372833</v>
       </c>
       <c r="H1072" t="n">
         <v>976710</v>
@@ -31544,7 +31544,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.950943112373352</v>
+        <v>0.950943052768707</v>
       </c>
       <c r="H1075" t="n">
         <v>1305539</v>
@@ -31573,7 +31573,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.94281542301178</v>
+        <v>0.942815482616425</v>
       </c>
       <c r="H1076" t="n">
         <v>748259</v>
@@ -31718,7 +31718,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.983454048633575</v>
+        <v>0.98345410823822</v>
       </c>
       <c r="H1081" t="n">
         <v>1103385</v>
@@ -31747,7 +31747,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.965573012828827</v>
+        <v>0.965573072433472</v>
       </c>
       <c r="H1082" t="n">
         <v>663447</v>
@@ -31805,7 +31805,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.01921594142914</v>
+        <v>1.01921606063843</v>
       </c>
       <c r="H1084" t="n">
         <v>845070</v>
@@ -31834,7 +31834,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.978577375411987</v>
+        <v>0.978577435016632</v>
       </c>
       <c r="H1085" t="n">
         <v>860231</v>
@@ -31921,7 +31921,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.04685032367706</v>
+        <v>1.04685020446777</v>
       </c>
       <c r="H1088" t="n">
         <v>980898</v>
@@ -32066,7 +32066,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.978577375411987</v>
+        <v>0.978577435016632</v>
       </c>
       <c r="H1093" t="n">
         <v>452159</v>
@@ -32153,7 +32153,7 @@
         <v>1.28199994564056</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.04197347164154</v>
+        <v>1.04197359085083</v>
       </c>
       <c r="H1096" t="n">
         <v>369586</v>
@@ -32182,7 +32182,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.04522478580475</v>
+        <v>1.04522466659546</v>
       </c>
       <c r="H1097" t="n">
         <v>636495</v>
@@ -32211,7 +32211,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.08098673820496</v>
+        <v>1.08098661899567</v>
       </c>
       <c r="H1098" t="n">
         <v>667615</v>
@@ -32240,7 +32240,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.08098673820496</v>
+        <v>1.08098661899567</v>
       </c>
       <c r="H1099" t="n">
         <v>522910</v>
@@ -32501,7 +32501,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.980202853679657</v>
+        <v>0.980202913284302</v>
       </c>
       <c r="H1108" t="n">
         <v>640476</v>
@@ -32530,7 +32530,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.980202853679657</v>
+        <v>0.980202913284302</v>
       </c>
       <c r="H1109" t="n">
         <v>262178</v>
@@ -32559,7 +32559,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.01271390914917</v>
+        <v>1.01271378993988</v>
       </c>
       <c r="H1110" t="n">
         <v>381864</v>
@@ -32588,7 +32588,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.970449686050415</v>
+        <v>0.97044962644577</v>
       </c>
       <c r="H1111" t="n">
         <v>742959</v>
@@ -32646,7 +32646,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.970449686050415</v>
+        <v>0.97044962644577</v>
       </c>
       <c r="H1113" t="n">
         <v>623582</v>
@@ -32704,7 +32704,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.99970954656601</v>
+        <v>0.999709486961365</v>
       </c>
       <c r="H1115" t="n">
         <v>313811</v>
@@ -32849,7 +32849,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.13950634002686</v>
+        <v>1.13950622081757</v>
       </c>
       <c r="H1120" t="n">
         <v>729359</v>
@@ -32907,7 +32907,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.1898980140686</v>
+        <v>1.18989825248718</v>
       </c>
       <c r="H1122" t="n">
         <v>1036253</v>
@@ -32936,7 +32936,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.22403454780579</v>
+        <v>1.22403466701508</v>
       </c>
       <c r="H1123" t="n">
         <v>1408209</v>
@@ -32965,7 +32965,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.23866438865662</v>
+        <v>1.23866450786591</v>
       </c>
       <c r="H1124" t="n">
         <v>1685924</v>
@@ -33023,7 +33023,7 @@
         <v>1.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.21915781497955</v>
+        <v>1.21915793418884</v>
       </c>
       <c r="H1126" t="n">
         <v>1345354</v>
@@ -33052,7 +33052,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.19965136051178</v>
+        <v>1.19965124130249</v>
       </c>
       <c r="H1127" t="n">
         <v>955320</v>
@@ -33081,7 +33081,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.11349749565125</v>
+        <v>1.11349761486053</v>
       </c>
       <c r="H1128" t="n">
         <v>1234769</v>
@@ -33139,7 +33139,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.11187207698822</v>
+        <v>1.11187195777893</v>
       </c>
       <c r="H1130" t="n">
         <v>826238</v>
@@ -33168,7 +33168,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.14113187789917</v>
+        <v>1.14113175868988</v>
       </c>
       <c r="H1131" t="n">
         <v>1477312</v>
@@ -33197,7 +33197,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.11024653911591</v>
+        <v>1.11024641990662</v>
       </c>
       <c r="H1132" t="n">
         <v>966335</v>
@@ -33284,7 +33284,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.0874890089035</v>
+        <v>1.08748888969421</v>
       </c>
       <c r="H1135" t="n">
         <v>975260</v>
@@ -33400,7 +33400,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.04522478580475</v>
+        <v>1.04522466659546</v>
       </c>
       <c r="H1139" t="n">
         <v>375307</v>
@@ -33429,7 +33429,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.09561657905579</v>
+        <v>1.09561669826508</v>
       </c>
       <c r="H1140" t="n">
         <v>822817</v>
@@ -33458,7 +33458,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.18502140045166</v>
+        <v>1.18502151966095</v>
       </c>
       <c r="H1141" t="n">
         <v>2508659</v>
@@ -33487,7 +33487,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.18339586257935</v>
+        <v>1.18339598178864</v>
       </c>
       <c r="H1142" t="n">
         <v>1523197</v>
@@ -33632,7 +33632,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.35570359230042</v>
+        <v>1.35570347309113</v>
       </c>
       <c r="H1147" t="n">
         <v>1885073</v>
@@ -33690,7 +33690,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.36058032512665</v>
+        <v>1.36058020591736</v>
       </c>
       <c r="H1149" t="n">
         <v>1166397</v>
@@ -33719,7 +33719,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H1150" t="n">
         <v>2070745</v>
@@ -33777,7 +33777,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.40446996688843</v>
+        <v>1.40446984767914</v>
       </c>
       <c r="H1152" t="n">
         <v>1190639</v>
@@ -33835,7 +33835,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.43210411071777</v>
+        <v>1.43210399150848</v>
       </c>
       <c r="H1154" t="n">
         <v>1536729</v>
@@ -33864,7 +33864,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.44998526573181</v>
+        <v>1.44998514652252</v>
       </c>
       <c r="H1155" t="n">
         <v>1599256</v>
@@ -33951,7 +33951,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.47924494743347</v>
+        <v>1.47924506664276</v>
       </c>
       <c r="H1158" t="n">
         <v>1784025</v>
@@ -33980,7 +33980,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.46298944950104</v>
+        <v>1.46298933029175</v>
       </c>
       <c r="H1159" t="n">
         <v>1036959</v>
@@ -34009,7 +34009,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.47924494743347</v>
+        <v>1.47924506664276</v>
       </c>
       <c r="H1160" t="n">
         <v>1696767</v>
@@ -34038,7 +34038,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.42722761631012</v>
+        <v>1.42722749710083</v>
       </c>
       <c r="H1161" t="n">
         <v>1227223</v>
@@ -34067,7 +34067,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.41422307491302</v>
+        <v>1.41422319412231</v>
       </c>
       <c r="H1162" t="n">
         <v>710737</v>
@@ -34096,7 +34096,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.37358462810516</v>
+        <v>1.37358450889587</v>
       </c>
       <c r="H1163" t="n">
         <v>1109167</v>
@@ -34125,7 +34125,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.40609550476074</v>
+        <v>1.40609538555145</v>
       </c>
       <c r="H1164" t="n">
         <v>863877</v>
@@ -34154,7 +34154,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.41422307491302</v>
+        <v>1.41422319412231</v>
       </c>
       <c r="H1165" t="n">
         <v>959990</v>
@@ -34212,7 +34212,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.44510841369629</v>
+        <v>1.44510853290558</v>
       </c>
       <c r="H1167" t="n">
         <v>750992</v>
@@ -34328,7 +34328,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.54264104366302</v>
+        <v>1.54264116287231</v>
       </c>
       <c r="H1171" t="n">
         <v>1189245</v>
@@ -34357,7 +34357,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.52638566493988</v>
+        <v>1.52638554573059</v>
       </c>
       <c r="H1172" t="n">
         <v>759564</v>
@@ -34386,7 +34386,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.52476012706757</v>
+        <v>1.52476024627686</v>
       </c>
       <c r="H1173" t="n">
         <v>596935</v>
@@ -34444,7 +34444,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.51175582408905</v>
+        <v>1.51175570487976</v>
       </c>
       <c r="H1175" t="n">
         <v>769845</v>
@@ -34473,7 +34473,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.49062359333038</v>
+        <v>1.49062383174896</v>
       </c>
       <c r="H1176" t="n">
         <v>629898</v>
@@ -34560,7 +34560,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.45811295509338</v>
+        <v>1.45811283588409</v>
       </c>
       <c r="H1179" t="n">
         <v>551417</v>
@@ -34589,7 +34589,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.5052535533905</v>
+        <v>1.50525367259979</v>
       </c>
       <c r="H1180" t="n">
         <v>1305331</v>
@@ -34618,7 +34618,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.47924494743347</v>
+        <v>1.47924506664276</v>
       </c>
       <c r="H1181" t="n">
         <v>1042576</v>
@@ -34647,7 +34647,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.47924494743347</v>
+        <v>1.47924506664276</v>
       </c>
       <c r="H1182" t="n">
         <v>1296105</v>
@@ -34705,7 +34705,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.48899817466736</v>
+        <v>1.48899829387665</v>
       </c>
       <c r="H1184" t="n">
         <v>959385</v>
@@ -34763,7 +34763,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.45323622226715</v>
+        <v>1.45323634147644</v>
       </c>
       <c r="H1186" t="n">
         <v>801592</v>
@@ -34792,7 +34792,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.43210411071777</v>
+        <v>1.43210399150848</v>
       </c>
       <c r="H1187" t="n">
         <v>761360</v>
@@ -34850,7 +34850,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.44510841369629</v>
+        <v>1.44510853290558</v>
       </c>
       <c r="H1189" t="n">
         <v>956615</v>
@@ -34879,7 +34879,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.46136391162872</v>
+        <v>1.46136379241943</v>
       </c>
       <c r="H1190" t="n">
         <v>931984</v>
@@ -34908,7 +34908,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.39959323406219</v>
+        <v>1.39959335327148</v>
       </c>
       <c r="H1191" t="n">
         <v>705649</v>
@@ -34966,7 +34966,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.40121877193451</v>
+        <v>1.40121865272522</v>
       </c>
       <c r="H1193" t="n">
         <v>915457</v>
@@ -35140,7 +35140,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.39796781539917</v>
+        <v>1.39796769618988</v>
       </c>
       <c r="H1199" t="n">
         <v>897331</v>
@@ -35169,7 +35169,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.32806921005249</v>
+        <v>1.32806932926178</v>
       </c>
       <c r="H1200" t="n">
         <v>2134415</v>
@@ -35198,7 +35198,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.33294606208801</v>
+        <v>1.33294594287872</v>
       </c>
       <c r="H1201" t="n">
         <v>1057873</v>
@@ -35227,7 +35227,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.31994152069092</v>
+        <v>1.31994163990021</v>
       </c>
       <c r="H1202" t="n">
         <v>1223640</v>
@@ -35285,7 +35285,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.31669056415558</v>
+        <v>1.31669044494629</v>
       </c>
       <c r="H1204" t="n">
         <v>981753</v>
@@ -35343,7 +35343,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.34432470798492</v>
+        <v>1.34432482719421</v>
       </c>
       <c r="H1206" t="n">
         <v>595620</v>
@@ -35372,7 +35372,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H1207" t="n">
         <v>1031195</v>
@@ -35430,7 +35430,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.37033355236053</v>
+        <v>1.37033343315125</v>
       </c>
       <c r="H1209" t="n">
         <v>1084333</v>
@@ -35459,7 +35459,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.36058032512665</v>
+        <v>1.36058020591736</v>
       </c>
       <c r="H1210" t="n">
         <v>1643374</v>
@@ -35488,7 +35488,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.40121877193451</v>
+        <v>1.40121865272522</v>
       </c>
       <c r="H1211" t="n">
         <v>963351</v>
@@ -35517,7 +35517,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G1212" t="n">
-        <v>1.35895466804504</v>
+        <v>1.35895478725433</v>
       </c>
       <c r="H1212" t="n">
         <v>756295</v>
@@ -35546,7 +35546,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.40446996688843</v>
+        <v>1.40446984767914</v>
       </c>
       <c r="H1213" t="n">
         <v>1175485</v>
@@ -35575,7 +35575,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.39796781539917</v>
+        <v>1.39796769618988</v>
       </c>
       <c r="H1214" t="n">
         <v>1081407</v>
@@ -35604,7 +35604,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.39796781539917</v>
+        <v>1.39796769618988</v>
       </c>
       <c r="H1215" t="n">
         <v>756838</v>
@@ -35633,7 +35633,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H1216" t="n">
         <v>1277266</v>
@@ -35662,7 +35662,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.39959323406219</v>
+        <v>1.39959335327148</v>
       </c>
       <c r="H1217" t="n">
         <v>1603197</v>
@@ -35691,7 +35691,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.3540780544281</v>
+        <v>1.35407817363739</v>
       </c>
       <c r="H1218" t="n">
         <v>1322683</v>
@@ -35720,7 +35720,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.33619713783264</v>
+        <v>1.33619701862335</v>
       </c>
       <c r="H1219" t="n">
         <v>1345726</v>
@@ -35749,7 +35749,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.38171219825745</v>
+        <v>1.38171231746674</v>
       </c>
       <c r="H1220" t="n">
         <v>1874653</v>
@@ -35807,7 +35807,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.33944821357727</v>
+        <v>1.33944809436798</v>
       </c>
       <c r="H1222" t="n">
         <v>1303372</v>
@@ -35923,7 +35923,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.19314920902252</v>
+        <v>1.19314932823181</v>
       </c>
       <c r="H1226" t="n">
         <v>1199321</v>
@@ -36039,7 +36039,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.22891116142273</v>
+        <v>1.22891128063202</v>
       </c>
       <c r="H1230" t="n">
         <v>1744398</v>
@@ -36068,7 +36068,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.24191558361053</v>
+        <v>1.24191546440125</v>
       </c>
       <c r="H1231" t="n">
         <v>884745</v>
@@ -36126,7 +36126,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.25491976737976</v>
+        <v>1.25492000579834</v>
       </c>
       <c r="H1233" t="n">
         <v>1914649</v>
@@ -36213,7 +36213,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.32806921005249</v>
+        <v>1.32806932926178</v>
       </c>
       <c r="H1236" t="n">
         <v>1620142</v>
@@ -36242,7 +36242,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1237" t="n">
-        <v>1.31994152069092</v>
+        <v>1.31994163990021</v>
       </c>
       <c r="H1237" t="n">
         <v>589880</v>
@@ -36300,7 +36300,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.35570359230042</v>
+        <v>1.35570347309113</v>
       </c>
       <c r="H1239" t="n">
         <v>937918</v>
@@ -36329,7 +36329,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.39796781539917</v>
+        <v>1.39796769618988</v>
       </c>
       <c r="H1240" t="n">
         <v>1046205</v>
@@ -36358,7 +36358,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.39959323406219</v>
+        <v>1.39959335327148</v>
       </c>
       <c r="H1241" t="n">
         <v>966177</v>
@@ -36532,7 +36532,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1247" t="n">
-        <v>1.46136391162872</v>
+        <v>1.46136379241943</v>
       </c>
       <c r="H1247" t="n">
         <v>1551782</v>
@@ -36561,7 +36561,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.45486164093018</v>
+        <v>1.45486176013947</v>
       </c>
       <c r="H1248" t="n">
         <v>247638</v>
@@ -36590,7 +36590,7 @@
         <v>1.75</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.42235100269318</v>
+        <v>1.42235088348389</v>
       </c>
       <c r="H1249" t="n">
         <v>382937</v>
@@ -36648,7 +36648,7 @@
         <v>1.75</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.42235100269318</v>
+        <v>1.42235088348389</v>
       </c>
       <c r="H1251" t="n">
         <v>406143</v>
@@ -36706,7 +36706,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.39146566390991</v>
+        <v>1.39146554470062</v>
       </c>
       <c r="H1253" t="n">
         <v>264203</v>
@@ -36822,7 +36822,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.34432470798492</v>
+        <v>1.34432482719421</v>
       </c>
       <c r="H1257" t="n">
         <v>477576</v>
@@ -36851,7 +36851,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.33294606208801</v>
+        <v>1.33294594287872</v>
       </c>
       <c r="H1258" t="n">
         <v>364321</v>
@@ -36880,7 +36880,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.31669056415558</v>
+        <v>1.31669044494629</v>
       </c>
       <c r="H1259" t="n">
         <v>264977</v>
@@ -36909,7 +36909,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1260" t="n">
-        <v>1.3540780544281</v>
+        <v>1.35407817363739</v>
       </c>
       <c r="H1260" t="n">
         <v>686878</v>
@@ -36938,7 +36938,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.35570359230042</v>
+        <v>1.35570347309113</v>
       </c>
       <c r="H1261" t="n">
         <v>245928</v>
@@ -36967,7 +36967,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.34920132160187</v>
+        <v>1.34920144081116</v>
       </c>
       <c r="H1262" t="n">
         <v>551734</v>
@@ -37083,7 +37083,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.28580510616302</v>
+        <v>1.28580522537231</v>
       </c>
       <c r="H1266" t="n">
         <v>354205</v>
@@ -37112,7 +37112,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1267" t="n">
-        <v>1.31018829345703</v>
+        <v>1.31018841266632</v>
       </c>
       <c r="H1267" t="n">
         <v>829953</v>
@@ -37141,7 +37141,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.33944821357727</v>
+        <v>1.33944809436798</v>
       </c>
       <c r="H1268" t="n">
         <v>326436</v>
@@ -37228,7 +37228,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.3540780544281</v>
+        <v>1.35407817363739</v>
       </c>
       <c r="H1271" t="n">
         <v>742072</v>
@@ -37257,7 +37257,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.3524523973465</v>
+        <v>1.35245251655579</v>
       </c>
       <c r="H1272" t="n">
         <v>326404</v>
@@ -37431,7 +37431,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.42072546482086</v>
+        <v>1.42072534561157</v>
       </c>
       <c r="H1278" t="n">
         <v>1674756</v>
@@ -37460,7 +37460,7 @@
         <v>1.75</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.42235100269318</v>
+        <v>1.42235088348389</v>
       </c>
       <c r="H1279" t="n">
         <v>258473</v>
@@ -37576,7 +37576,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.41097187995911</v>
+        <v>1.4109719991684</v>
       </c>
       <c r="H1283" t="n">
         <v>270991</v>
@@ -37634,7 +37634,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.37033355236053</v>
+        <v>1.37033343315125</v>
       </c>
       <c r="H1285" t="n">
         <v>647257</v>
@@ -37663,7 +37663,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.32319271564484</v>
+        <v>1.32319283485413</v>
       </c>
       <c r="H1286" t="n">
         <v>678042</v>
@@ -37692,7 +37692,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.34920132160187</v>
+        <v>1.34920144081116</v>
       </c>
       <c r="H1287" t="n">
         <v>502247</v>
@@ -37721,7 +37721,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.35570359230042</v>
+        <v>1.35570347309113</v>
       </c>
       <c r="H1288" t="n">
         <v>517753</v>
@@ -37750,7 +37750,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.3540780544281</v>
+        <v>1.35407817363739</v>
       </c>
       <c r="H1289" t="n">
         <v>813059</v>
@@ -37808,7 +37808,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.35570359230042</v>
+        <v>1.35570347309113</v>
       </c>
       <c r="H1291" t="n">
         <v>142709</v>
@@ -37837,7 +37837,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.36545670032501</v>
+        <v>1.3654568195343</v>
       </c>
       <c r="H1292" t="n">
         <v>591974</v>
@@ -37866,7 +37866,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.41909992694855</v>
+        <v>1.41909980773926</v>
       </c>
       <c r="H1293" t="n">
         <v>906495</v>
@@ -37924,7 +37924,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.48899817466736</v>
+        <v>1.48899829387665</v>
       </c>
       <c r="H1295" t="n">
         <v>884356</v>
@@ -37953,7 +37953,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.54264104366302</v>
+        <v>1.54264116287231</v>
       </c>
       <c r="H1296" t="n">
         <v>830535</v>
@@ -37982,7 +37982,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.54751789569855</v>
+        <v>1.54751777648926</v>
       </c>
       <c r="H1297" t="n">
         <v>532427</v>
@@ -38011,7 +38011,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.54751789569855</v>
+        <v>1.54751777648926</v>
       </c>
       <c r="H1298" t="n">
         <v>870038</v>
@@ -38098,7 +38098,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.55564546585083</v>
+        <v>1.55564558506012</v>
       </c>
       <c r="H1301" t="n">
         <v>516135</v>
@@ -38185,7 +38185,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.46298944950104</v>
+        <v>1.46298933029175</v>
       </c>
       <c r="H1304" t="n">
         <v>451401</v>
@@ -38214,7 +38214,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.49550044536591</v>
+        <v>1.49550032615662</v>
       </c>
       <c r="H1305" t="n">
         <v>387430</v>
@@ -38243,7 +38243,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.47761940956116</v>
+        <v>1.47761929035187</v>
       </c>
       <c r="H1306" t="n">
         <v>158784</v>
@@ -38417,7 +38417,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.61416494846344</v>
+        <v>1.61416506767273</v>
       </c>
       <c r="H1312" t="n">
         <v>815685</v>
@@ -38504,7 +38504,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.58002853393555</v>
+        <v>1.58002865314484</v>
       </c>
       <c r="H1315" t="n">
         <v>459885</v>
@@ -38620,7 +38620,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.5881564617157</v>
+        <v>1.58815634250641</v>
       </c>
       <c r="H1319" t="n">
         <v>349706</v>
@@ -38649,7 +38649,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992713928223</v>
       </c>
       <c r="H1320" t="n">
         <v>793792</v>
@@ -38678,7 +38678,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.71088480949402</v>
+        <v>1.71088492870331</v>
       </c>
       <c r="H1321" t="n">
         <v>2169514</v>
@@ -38707,7 +38707,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.67431020736694</v>
+        <v>1.67431008815765</v>
       </c>
       <c r="H1322" t="n">
         <v>699635</v>
@@ -38765,7 +38765,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.63773560523987</v>
+        <v>1.63773548603058</v>
       </c>
       <c r="H1324" t="n">
         <v>543198</v>
@@ -38794,7 +38794,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.61416494846344</v>
+        <v>1.61416506767273</v>
       </c>
       <c r="H1325" t="n">
         <v>483271</v>
@@ -38881,7 +38881,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.6222927570343</v>
+        <v>1.62229287624359</v>
       </c>
       <c r="H1328" t="n">
         <v>481806</v>
@@ -38968,7 +38968,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1331" t="n">
         <v>617156</v>
@@ -38997,7 +38997,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.76777899265289</v>
+        <v>1.76777875423431</v>
       </c>
       <c r="H1332" t="n">
         <v>1402885</v>
@@ -39026,7 +39026,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.76371502876282</v>
+        <v>1.76371514797211</v>
       </c>
       <c r="H1333" t="n">
         <v>1218512</v>
@@ -39055,7 +39055,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.7149486541748</v>
+        <v>1.71494889259338</v>
       </c>
       <c r="H1334" t="n">
         <v>658847</v>
@@ -39084,7 +39084,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.67431020736694</v>
+        <v>1.67431008815765</v>
       </c>
       <c r="H1335" t="n">
         <v>1044669</v>
@@ -39142,7 +39142,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.64179933071136</v>
+        <v>1.64179921150208</v>
       </c>
       <c r="H1337" t="n">
         <v>311937</v>
@@ -39200,7 +39200,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.64179933071136</v>
+        <v>1.64179921150208</v>
       </c>
       <c r="H1339" t="n">
         <v>183609</v>
@@ -39258,7 +39258,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1341" t="n">
         <v>711159</v>
@@ -39316,7 +39316,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.70682108402252</v>
+        <v>1.70682096481323</v>
       </c>
       <c r="H1343" t="n">
         <v>327559</v>
@@ -39374,7 +39374,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.6222927570343</v>
+        <v>1.62229287624359</v>
       </c>
       <c r="H1345" t="n">
         <v>566407</v>
@@ -39403,7 +39403,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.62960779666901</v>
+        <v>1.6296079158783</v>
       </c>
       <c r="H1346" t="n">
         <v>479194</v>
@@ -39432,7 +39432,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.64179933071136</v>
+        <v>1.64179921150208</v>
       </c>
       <c r="H1347" t="n">
         <v>693288</v>
@@ -39461,7 +39461,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.66211867332458</v>
+        <v>1.6621185541153</v>
       </c>
       <c r="H1348" t="n">
         <v>269810</v>
@@ -39548,7 +39548,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.69869339466095</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1351" t="n">
         <v>281228</v>
@@ -39577,7 +39577,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1352" t="n">
         <v>377374</v>
@@ -39606,7 +39606,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1353" t="n">
         <v>123816</v>
@@ -39693,7 +39693,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.69869339466095</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1356" t="n">
         <v>281877</v>
@@ -39751,7 +39751,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.70682108402252</v>
+        <v>1.70682096481323</v>
       </c>
       <c r="H1358" t="n">
         <v>419293</v>
@@ -39780,7 +39780,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.72307634353638</v>
+        <v>1.72307646274567</v>
       </c>
       <c r="H1359" t="n">
         <v>494187</v>
@@ -39809,7 +39809,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992713928223</v>
       </c>
       <c r="H1360" t="n">
         <v>900910</v>
@@ -39983,7 +39983,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992713928223</v>
       </c>
       <c r="H1366" t="n">
         <v>293083</v>
@@ -40012,7 +40012,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992713928223</v>
       </c>
       <c r="H1367" t="n">
         <v>167738</v>
@@ -40041,7 +40041,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992713928223</v>
       </c>
       <c r="H1368" t="n">
         <v>94403</v>
@@ -40099,7 +40099,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992713928223</v>
       </c>
       <c r="H1370" t="n">
         <v>142206</v>
@@ -40186,7 +40186,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.67431020736694</v>
+        <v>1.67431008815765</v>
       </c>
       <c r="H1373" t="n">
         <v>112605</v>
@@ -40244,7 +40244,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1375" t="n">
         <v>619469</v>
@@ -40273,7 +40273,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.69869339466095</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1376" t="n">
         <v>214274</v>
@@ -40331,7 +40331,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.75152361392975</v>
+        <v>1.75152349472046</v>
       </c>
       <c r="H1378" t="n">
         <v>296800</v>
@@ -40418,7 +40418,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.75152361392975</v>
+        <v>1.75152349472046</v>
       </c>
       <c r="H1381" t="n">
         <v>185270</v>
@@ -40447,7 +40447,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.76777899265289</v>
+        <v>1.76777875423431</v>
       </c>
       <c r="H1382" t="n">
         <v>315363</v>
@@ -40505,7 +40505,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.73933207988739</v>
+        <v>1.7393319606781</v>
       </c>
       <c r="H1384" t="n">
         <v>205848</v>
@@ -40534,7 +40534,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.71088480949402</v>
+        <v>1.71088492870331</v>
       </c>
       <c r="H1385" t="n">
         <v>420916</v>
@@ -40563,7 +40563,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.69869339466095</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1386" t="n">
         <v>221998</v>
@@ -40621,7 +40621,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.70682108402252</v>
+        <v>1.70682096481323</v>
       </c>
       <c r="H1388" t="n">
         <v>404164</v>
@@ -40650,7 +40650,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1389" t="n">
         <v>274746</v>
@@ -40679,7 +40679,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1390" t="n">
         <v>289204</v>
@@ -40708,7 +40708,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.70682108402252</v>
+        <v>1.70682096481323</v>
       </c>
       <c r="H1391" t="n">
         <v>287635</v>
@@ -40737,7 +40737,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.70682108402252</v>
+        <v>1.70682096481323</v>
       </c>
       <c r="H1392" t="n">
         <v>236511</v>
@@ -40766,7 +40766,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.73526799678802</v>
+        <v>1.73526811599731</v>
       </c>
       <c r="H1393" t="n">
         <v>205037</v>
@@ -40795,7 +40795,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.6905654668808</v>
+        <v>1.69056558609009</v>
       </c>
       <c r="H1394" t="n">
         <v>298187</v>
@@ -40824,7 +40824,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.6865017414093</v>
+        <v>1.68650186061859</v>
       </c>
       <c r="H1395" t="n">
         <v>269064</v>
@@ -40882,7 +40882,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.69869339466095</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1397" t="n">
         <v>206245</v>
@@ -40940,7 +40940,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.70275723934174</v>
+        <v>1.70275712013245</v>
       </c>
       <c r="H1399" t="n">
         <v>116193</v>
@@ -41027,7 +41027,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.63773560523987</v>
+        <v>1.63773548603058</v>
       </c>
       <c r="H1402" t="n">
         <v>449748</v>
@@ -41085,7 +41085,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.66211867332458</v>
+        <v>1.6621185541153</v>
       </c>
       <c r="H1404" t="n">
         <v>208073</v>
@@ -41114,7 +41114,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.64992702007294</v>
+        <v>1.64992713928223</v>
       </c>
       <c r="H1405" t="n">
         <v>58898</v>
@@ -41317,7 +41317,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.66211867332458</v>
+        <v>1.6621185541153</v>
       </c>
       <c r="H1412" t="n">
         <v>190201</v>
@@ -41375,7 +41375,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.73526799678802</v>
+        <v>1.73526811599731</v>
       </c>
       <c r="H1414" t="n">
         <v>499367</v>
@@ -41404,7 +41404,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.73933207988739</v>
+        <v>1.7393319606781</v>
       </c>
       <c r="H1415" t="n">
         <v>229253</v>
@@ -41433,7 +41433,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.7149486541748</v>
+        <v>1.71494889259338</v>
       </c>
       <c r="H1416" t="n">
         <v>144494</v>
@@ -41520,7 +41520,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.7149486541748</v>
+        <v>1.71494889259338</v>
       </c>
       <c r="H1419" t="n">
         <v>366475</v>
@@ -41549,7 +41549,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.72307634353638</v>
+        <v>1.72307646274567</v>
       </c>
       <c r="H1420" t="n">
         <v>331772</v>
@@ -41607,7 +41607,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.66211867332458</v>
+        <v>1.6621185541153</v>
       </c>
       <c r="H1422" t="n">
         <v>536424</v>
@@ -41636,7 +41636,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.69869339466095</v>
+        <v>1.69869327545166</v>
       </c>
       <c r="H1423" t="n">
         <v>326145</v>
@@ -41665,7 +41665,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.72307634353638</v>
+        <v>1.72307646274567</v>
       </c>
       <c r="H1424" t="n">
         <v>311828</v>
@@ -41694,7 +41694,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.73526799678802</v>
+        <v>1.73526811599731</v>
       </c>
       <c r="H1425" t="n">
         <v>157467</v>
@@ -41752,7 +41752,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.75152361392975</v>
+        <v>1.75152349472046</v>
       </c>
       <c r="H1427" t="n">
         <v>512952</v>
@@ -41781,7 +41781,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.75152361392975</v>
+        <v>1.75152349472046</v>
       </c>
       <c r="H1428" t="n">
         <v>320809</v>
@@ -41839,7 +41839,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.74339580535889</v>
+        <v>1.74339592456818</v>
       </c>
       <c r="H1430" t="n">
         <v>235338</v>
@@ -41868,7 +41868,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.80841743946075</v>
+        <v>1.80841755867004</v>
       </c>
       <c r="H1431" t="n">
         <v>573208</v>
@@ -41897,7 +41897,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.77997052669525</v>
+        <v>1.77997064590454</v>
       </c>
       <c r="H1432" t="n">
         <v>352102</v>
@@ -41926,7 +41926,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.77590656280518</v>
+        <v>1.77590668201447</v>
       </c>
       <c r="H1433" t="n">
         <v>310018</v>
@@ -41984,7 +41984,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.79216229915619</v>
+        <v>1.79216194152832</v>
       </c>
       <c r="H1435" t="n">
         <v>582509</v>
@@ -42042,7 +42042,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.8775030374527</v>
+        <v>1.87750315666199</v>
       </c>
       <c r="H1437" t="n">
         <v>495218</v>
@@ -42129,7 +42129,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.89782249927521</v>
+        <v>1.8978226184845</v>
       </c>
       <c r="H1440" t="n">
         <v>174924</v>
@@ -42187,7 +42187,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.88563084602356</v>
+        <v>1.88563096523285</v>
       </c>
       <c r="H1442" t="n">
         <v>157167</v>
@@ -42245,7 +42245,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.91001403331757</v>
+        <v>1.91001391410828</v>
       </c>
       <c r="H1444" t="n">
         <v>336822</v>
@@ -42274,7 +42274,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.89375853538513</v>
+        <v>1.89375841617584</v>
       </c>
       <c r="H1445" t="n">
         <v>142420</v>
@@ -42303,7 +42303,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.86124765872955</v>
+        <v>1.86124753952026</v>
       </c>
       <c r="H1446" t="n">
         <v>243118</v>
@@ -42361,7 +42361,7 @@
         <v>2.25</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.82873678207397</v>
+        <v>1.82873702049255</v>
       </c>
       <c r="H1448" t="n">
         <v>162939</v>
@@ -42390,7 +42390,7 @@
         <v>2.25</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.82873678207397</v>
+        <v>1.82873702049255</v>
       </c>
       <c r="H1449" t="n">
         <v>121634</v>
@@ -42419,7 +42419,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.85718381404877</v>
+        <v>1.85718405246735</v>
       </c>
       <c r="H1450" t="n">
         <v>171793</v>
@@ -42448,7 +42448,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.85718381404877</v>
+        <v>1.85718405246735</v>
       </c>
       <c r="H1451" t="n">
         <v>132956</v>
@@ -42535,7 +42535,7 @@
         <v>2.25</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.82873678207397</v>
+        <v>1.82873702049255</v>
       </c>
       <c r="H1454" t="n">
         <v>347999</v>
@@ -42593,7 +42593,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.86124765872955</v>
+        <v>1.86124753952026</v>
       </c>
       <c r="H1456" t="n">
         <v>137423</v>
@@ -42622,7 +42622,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.89375853538513</v>
+        <v>1.89375841617584</v>
       </c>
       <c r="H1457" t="n">
         <v>156515</v>
@@ -42651,7 +42651,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.88156700134277</v>
+        <v>1.88156712055206</v>
       </c>
       <c r="H1458" t="n">
         <v>213358</v>
@@ -42680,7 +42680,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.89375853538513</v>
+        <v>1.89375841617584</v>
       </c>
       <c r="H1459" t="n">
         <v>218467</v>
@@ -42709,7 +42709,7 @@
         <v>2.25</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.82873678207397</v>
+        <v>1.82873702049255</v>
       </c>
       <c r="H1460" t="n">
         <v>333689</v>
@@ -42738,7 +42738,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.85718381404877</v>
+        <v>1.85718405246735</v>
       </c>
       <c r="H1461" t="n">
         <v>270156</v>
@@ -42796,7 +42796,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.84905600547791</v>
+        <v>1.84905612468719</v>
       </c>
       <c r="H1463" t="n">
         <v>254982</v>
@@ -42825,7 +42825,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.81248140335083</v>
+        <v>1.81248152256012</v>
       </c>
       <c r="H1464" t="n">
         <v>170419</v>
@@ -42854,7 +42854,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.85718381404877</v>
+        <v>1.85718405246735</v>
       </c>
       <c r="H1465" t="n">
         <v>176788</v>
@@ -42883,7 +42883,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.84905600547791</v>
+        <v>1.84905612468719</v>
       </c>
       <c r="H1466" t="n">
         <v>167487</v>
@@ -42941,7 +42941,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.88563084602356</v>
+        <v>1.88563096523285</v>
       </c>
       <c r="H1468" t="n">
         <v>146074</v>
@@ -42970,7 +42970,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.84905600547791</v>
+        <v>1.84905612468719</v>
       </c>
       <c r="H1469" t="n">
         <v>137392</v>
@@ -42999,7 +42999,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.9018862247467</v>
+        <v>1.90188610553741</v>
       </c>
       <c r="H1470" t="n">
         <v>201354</v>
@@ -43028,7 +43028,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.86124765872955</v>
+        <v>1.86124753952026</v>
       </c>
       <c r="H1471" t="n">
         <v>137813</v>
@@ -43057,7 +43057,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1472" t="n">
-        <v>1.88156700134277</v>
+        <v>1.88156712055206</v>
       </c>
       <c r="H1472" t="n">
         <v>350263</v>
@@ -43086,7 +43086,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.8775030374527</v>
+        <v>1.87750315666199</v>
       </c>
       <c r="H1473" t="n">
         <v>263544</v>
@@ -43173,7 +43173,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.82060921192169</v>
+        <v>1.8206090927124</v>
       </c>
       <c r="H1476" t="n">
         <v>406976</v>
@@ -43202,7 +43202,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1477" t="n">
-        <v>1.82467305660248</v>
+        <v>1.82467269897461</v>
       </c>
       <c r="H1477" t="n">
         <v>257885</v>
@@ -43231,7 +43231,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.8775030374527</v>
+        <v>1.87750315666199</v>
       </c>
       <c r="H1478" t="n">
         <v>823061</v>
@@ -43260,7 +43260,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.92220544815063</v>
+        <v>1.92220568656921</v>
       </c>
       <c r="H1479" t="n">
         <v>1286521</v>
@@ -43289,7 +43289,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G1480" t="n">
-        <v>1.90595030784607</v>
+        <v>1.90595018863678</v>
       </c>
       <c r="H1480" t="n">
         <v>531799</v>
@@ -43318,7 +43318,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.88156700134277</v>
+        <v>1.88156712055206</v>
       </c>
       <c r="H1481" t="n">
         <v>814392</v>
@@ -43347,7 +43347,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.88156700134277</v>
+        <v>1.88156712055206</v>
       </c>
       <c r="H1482" t="n">
         <v>261221</v>
@@ -43405,7 +43405,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.89375853538513</v>
+        <v>1.89375841617584</v>
       </c>
       <c r="H1484" t="n">
         <v>532235</v>
@@ -43434,7 +43434,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.8775030374527</v>
+        <v>1.87750315666199</v>
       </c>
       <c r="H1485" t="n">
         <v>389959</v>
@@ -43463,7 +43463,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>1.91001403331757</v>
+        <v>1.91001391410828</v>
       </c>
       <c r="H1486" t="n">
         <v>616442</v>
@@ -43492,7 +43492,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.91001403331757</v>
+        <v>1.91001391410828</v>
       </c>
       <c r="H1487" t="n">
         <v>751901</v>
@@ -43521,7 +43521,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.97097206115723</v>
+        <v>1.97097194194794</v>
       </c>
       <c r="H1488" t="n">
         <v>1578081</v>
@@ -43579,7 +43579,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.92983722686768</v>
+        <v>1.9298369884491</v>
       </c>
       <c r="H1490" t="n">
         <v>1375919</v>
@@ -43608,7 +43608,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.84669208526611</v>
+        <v>1.8466922044754</v>
       </c>
       <c r="H1491" t="n">
         <v>1332507</v>
@@ -43637,7 +43637,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.84231603145599</v>
+        <v>1.84231615066528</v>
       </c>
       <c r="H1492" t="n">
         <v>824274</v>
@@ -43753,7 +43753,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1496" t="n">
         <v>532900</v>
@@ -43782,7 +43782,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1497" t="n">
         <v>605383</v>
@@ -43811,7 +43811,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1498" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1498" t="n">
         <v>1138195</v>
@@ -43840,7 +43840,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.78980362415314</v>
+        <v>1.78980350494385</v>
       </c>
       <c r="H1499" t="n">
         <v>264006</v>
@@ -43869,7 +43869,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1500" t="n">
         <v>249659</v>
@@ -43927,7 +43927,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1502" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1502" t="n">
         <v>336795</v>
@@ -43985,7 +43985,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.73291492462158</v>
+        <v>1.73291504383087</v>
       </c>
       <c r="H1504" t="n">
         <v>251101</v>
@@ -44449,7 +44449,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1520" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1520" t="n">
         <v>147164</v>
@@ -44536,7 +44536,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.84231603145599</v>
+        <v>1.84231615066528</v>
       </c>
       <c r="H1523" t="n">
         <v>234544</v>
@@ -44623,7 +44623,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.84231603145599</v>
+        <v>1.84231615066528</v>
       </c>
       <c r="H1526" t="n">
         <v>74592</v>
@@ -44652,7 +44652,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.86419641971588</v>
+        <v>1.86419653892517</v>
       </c>
       <c r="H1527" t="n">
         <v>273420</v>
@@ -44681,7 +44681,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.90358078479767</v>
+        <v>1.90358066558838</v>
       </c>
       <c r="H1528" t="n">
         <v>604117</v>
@@ -44768,7 +44768,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.86419641971588</v>
+        <v>1.86419653892517</v>
       </c>
       <c r="H1531" t="n">
         <v>96323</v>
@@ -44826,7 +44826,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.86419641971588</v>
+        <v>1.86419653892517</v>
       </c>
       <c r="H1533" t="n">
         <v>65005</v>
@@ -44855,7 +44855,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.84669208526611</v>
+        <v>1.8466922044754</v>
       </c>
       <c r="H1534" t="n">
         <v>84536</v>
@@ -44884,7 +44884,7 @@
         <v>2.125</v>
       </c>
       <c r="G1535" t="n">
-        <v>1.85982024669647</v>
+        <v>1.85982012748718</v>
       </c>
       <c r="H1535" t="n">
         <v>80682</v>
@@ -44913,7 +44913,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.84669208526611</v>
+        <v>1.8466922044754</v>
       </c>
       <c r="H1536" t="n">
         <v>166806</v>
@@ -44942,7 +44942,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.83794009685516</v>
+        <v>1.83793997764587</v>
       </c>
       <c r="H1537" t="n">
         <v>87274</v>
@@ -45116,7 +45116,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1543" t="n">
         <v>202207</v>
@@ -45145,7 +45145,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.78980362415314</v>
+        <v>1.78980350494385</v>
       </c>
       <c r="H1544" t="n">
         <v>169992</v>
@@ -45174,7 +45174,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.84669208526611</v>
+        <v>1.8466922044754</v>
       </c>
       <c r="H1545" t="n">
         <v>230077</v>
@@ -45261,7 +45261,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.83794009685516</v>
+        <v>1.83793997764587</v>
       </c>
       <c r="H1548" t="n">
         <v>268263</v>
@@ -45377,7 +45377,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1552" t="n">
         <v>480966</v>
@@ -45464,7 +45464,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.84231603145599</v>
+        <v>1.84231615066528</v>
       </c>
       <c r="H1555" t="n">
         <v>375561</v>
@@ -45522,7 +45522,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.84669208526611</v>
+        <v>1.8466922044754</v>
       </c>
       <c r="H1557" t="n">
         <v>393196</v>
@@ -45609,7 +45609,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.86419641971588</v>
+        <v>1.86419653892517</v>
       </c>
       <c r="H1560" t="n">
         <v>167809</v>
@@ -45638,7 +45638,7 @@
         <v>2.125</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.85982024669647</v>
+        <v>1.85982012748718</v>
       </c>
       <c r="H1561" t="n">
         <v>125973</v>
@@ -45725,7 +45725,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1564" t="n">
         <v>111857</v>
@@ -45783,7 +45783,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.72416281700134</v>
+        <v>1.72416269779205</v>
       </c>
       <c r="H1566" t="n">
         <v>333662</v>
@@ -45812,7 +45812,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.71716105937958</v>
+        <v>1.71716117858887</v>
       </c>
       <c r="H1567" t="n">
         <v>173759</v>
@@ -46073,7 +46073,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.58938050270081</v>
+        <v>1.58938038349152</v>
       </c>
       <c r="H1576" t="n">
         <v>224701</v>
@@ -46131,7 +46131,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.63314116001129</v>
+        <v>1.633141040802</v>
       </c>
       <c r="H1578" t="n">
         <v>169103</v>
@@ -46479,7 +46479,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1590" t="n">
         <v>247253</v>
@@ -46595,7 +46595,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1594" t="n">
         <v>242325</v>
@@ -46798,7 +46798,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.75479519367218</v>
+        <v>1.75479531288147</v>
       </c>
       <c r="H1601" t="n">
         <v>81343</v>
@@ -46827,7 +46827,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1602" t="n">
-        <v>1.78980362415314</v>
+        <v>1.78980350494385</v>
       </c>
       <c r="H1602" t="n">
         <v>73878</v>
@@ -46914,7 +46914,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1605" t="n">
         <v>108149</v>
@@ -46943,7 +46943,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.76792335510254</v>
+        <v>1.76792323589325</v>
       </c>
       <c r="H1606" t="n">
         <v>44910</v>
@@ -47030,7 +47030,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.77667534351349</v>
+        <v>1.77667546272278</v>
       </c>
       <c r="H1609" t="n">
         <v>68878</v>
@@ -47146,7 +47146,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.81932294368744</v>
+        <v>1.81932306289673</v>
       </c>
       <c r="H1613" t="n">
         <v>252942</v>
@@ -47175,7 +47175,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.81932294368744</v>
+        <v>1.81932306289673</v>
       </c>
       <c r="H1614" t="n">
         <v>85301</v>
@@ -47291,7 +47291,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.84200763702393</v>
+        <v>1.84200775623322</v>
       </c>
       <c r="H1618" t="n">
         <v>223312</v>
@@ -47378,7 +47378,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.80389714241028</v>
+        <v>1.80389726161957</v>
       </c>
       <c r="H1621" t="n">
         <v>394095</v>
@@ -47726,7 +47726,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.83293378353119</v>
+        <v>1.8329336643219</v>
       </c>
       <c r="H1633" t="n">
         <v>54268</v>
@@ -47813,7 +47813,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1636" t="n">
-        <v>1.83293378353119</v>
+        <v>1.8329336643219</v>
       </c>
       <c r="H1636" t="n">
         <v>72431</v>
@@ -47987,7 +47987,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.72767627239227</v>
+        <v>1.72767615318298</v>
       </c>
       <c r="H1642" t="n">
         <v>156172</v>
@@ -48074,7 +48074,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1645" t="n">
-        <v>1.73312056064606</v>
+        <v>1.73312044143677</v>
       </c>
       <c r="H1645" t="n">
         <v>475615</v>
@@ -48161,7 +48161,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.52260529994965</v>
+        <v>1.52260541915894</v>
       </c>
       <c r="H1648" t="n">
         <v>1949495</v>
@@ -48219,7 +48219,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.49356889724731</v>
+        <v>1.49356877803802</v>
       </c>
       <c r="H1650" t="n">
         <v>173295</v>
@@ -48364,7 +48364,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.4427547454834</v>
+        <v>1.44275486469269</v>
       </c>
       <c r="H1655" t="n">
         <v>120876</v>
@@ -48480,7 +48480,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1659" t="n">
-        <v>1.4427547454834</v>
+        <v>1.44275486469269</v>
       </c>
       <c r="H1659" t="n">
         <v>56913</v>
@@ -48509,7 +48509,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.42279207706451</v>
+        <v>1.4227921962738</v>
       </c>
       <c r="H1660" t="n">
         <v>55532</v>
@@ -48596,7 +48596,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.3030161857605</v>
+        <v>1.30301630496979</v>
       </c>
       <c r="H1663" t="n">
         <v>152257</v>
@@ -48741,7 +48741,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.34294152259827</v>
+        <v>1.34294164180756</v>
       </c>
       <c r="H1668" t="n">
         <v>271091</v>
@@ -48770,7 +48770,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.33023810386658</v>
+        <v>1.33023798465729</v>
       </c>
       <c r="H1669" t="n">
         <v>81019</v>
@@ -49031,7 +49031,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1678" t="n">
-        <v>1.484494805336</v>
+        <v>1.48449492454529</v>
       </c>
       <c r="H1678" t="n">
         <v>178787</v>
@@ -49089,7 +49089,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.46271741390228</v>
+        <v>1.46271753311157</v>
       </c>
       <c r="H1680" t="n">
         <v>70226</v>
@@ -49118,7 +49118,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.44638442993164</v>
+        <v>1.44638431072235</v>
       </c>
       <c r="H1681" t="n">
         <v>85701</v>
@@ -49147,7 +49147,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.46271741390228</v>
+        <v>1.46271753311157</v>
       </c>
       <c r="H1682" t="n">
         <v>16925</v>
@@ -49205,7 +49205,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.46997666358948</v>
+        <v>1.46997654438019</v>
       </c>
       <c r="H1684" t="n">
         <v>105058</v>
@@ -49437,7 +49437,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.41734778881073</v>
+        <v>1.41734790802002</v>
       </c>
       <c r="H1692" t="n">
         <v>38155</v>
@@ -49669,7 +49669,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.38649654388428</v>
+        <v>1.38649642467499</v>
       </c>
       <c r="H1700" t="n">
         <v>49851</v>
@@ -49698,7 +49698,7 @@
         <v>1.5</v>
       </c>
       <c r="G1701" t="n">
-        <v>1.36108934879303</v>
+        <v>1.36108946800232</v>
       </c>
       <c r="H1701" t="n">
         <v>59908</v>
@@ -49727,7 +49727,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.3737930059433</v>
+        <v>1.37379288673401</v>
       </c>
       <c r="H1702" t="n">
         <v>34634</v>
@@ -49959,7 +49959,7 @@
         <v>1.5</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.36108934879303</v>
+        <v>1.36108946800232</v>
       </c>
       <c r="H1710" t="n">
         <v>49351</v>
@@ -50133,7 +50133,7 @@
         <v>1.35599994659424</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.23042488098145</v>
+        <v>1.23042476177216</v>
       </c>
       <c r="H1716" t="n">
         <v>157421</v>
@@ -50394,7 +50394,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.27760922908783</v>
+        <v>1.27760934829712</v>
       </c>
       <c r="H1725" t="n">
         <v>68993</v>
@@ -50452,7 +50452,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.2612761259079</v>
+        <v>1.26127624511719</v>
       </c>
       <c r="H1727" t="n">
         <v>71841</v>
@@ -50481,7 +50481,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.24312829971313</v>
+        <v>1.24312841892242</v>
       </c>
       <c r="H1728" t="n">
         <v>93267</v>
@@ -50800,7 +50800,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.34657120704651</v>
+        <v>1.34657108783722</v>
       </c>
       <c r="H1739" t="n">
         <v>55655</v>
@@ -50829,7 +50829,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.33023810386658</v>
+        <v>1.33023798465729</v>
       </c>
       <c r="H1740" t="n">
         <v>97865</v>
@@ -50858,7 +50858,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.2903128862381</v>
+        <v>1.29031276702881</v>
       </c>
       <c r="H1741" t="n">
         <v>74502</v>
@@ -50945,7 +50945,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.37923729419708</v>
+        <v>1.37923717498779</v>
       </c>
       <c r="H1744" t="n">
         <v>94379</v>
@@ -50974,7 +50974,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.3447562456131</v>
+        <v>1.34475636482239</v>
       </c>
       <c r="H1745" t="n">
         <v>93982</v>
@@ -51003,7 +51003,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.34294152259827</v>
+        <v>1.34294164180756</v>
       </c>
       <c r="H1746" t="n">
         <v>103418</v>
@@ -51264,7 +51264,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.4010146856308</v>
+        <v>1.40101480484009</v>
       </c>
       <c r="H1755" t="n">
         <v>78871</v>
@@ -51351,7 +51351,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.4010146856308</v>
+        <v>1.40101480484009</v>
       </c>
       <c r="H1758" t="n">
         <v>39021</v>
@@ -51380,7 +51380,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.41734778881073</v>
+        <v>1.41734790802002</v>
       </c>
       <c r="H1759" t="n">
         <v>64502</v>
@@ -51467,7 +51467,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.3737930059433</v>
+        <v>1.37379288673401</v>
       </c>
       <c r="H1762" t="n">
         <v>118998</v>
@@ -51699,7 +51699,7 @@
         <v>1.5</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.36108934879303</v>
+        <v>1.36108946800232</v>
       </c>
       <c r="H1770" t="n">
         <v>53618</v>
@@ -51728,7 +51728,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.37742245197296</v>
+        <v>1.37742257118225</v>
       </c>
       <c r="H1771" t="n">
         <v>97921</v>
@@ -51757,7 +51757,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.37742245197296</v>
+        <v>1.37742257118225</v>
       </c>
       <c r="H1772" t="n">
         <v>72275</v>
@@ -51844,7 +51844,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.34657120704651</v>
+        <v>1.34657108783722</v>
       </c>
       <c r="H1775" t="n">
         <v>21041</v>
@@ -51989,7 +51989,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.37923729419708</v>
+        <v>1.37923717498779</v>
       </c>
       <c r="H1780" t="n">
         <v>51470</v>
@@ -52192,7 +52192,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1787" t="n">
-        <v>1.4427547454834</v>
+        <v>1.44275486469269</v>
       </c>
       <c r="H1787" t="n">
         <v>145760</v>
@@ -52221,7 +52221,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.46271741390228</v>
+        <v>1.46271753311157</v>
       </c>
       <c r="H1788" t="n">
         <v>116404</v>
@@ -52279,7 +52279,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.49356889724731</v>
+        <v>1.49356877803802</v>
       </c>
       <c r="H1790" t="n">
         <v>115523</v>
@@ -52337,7 +52337,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.46997666358948</v>
+        <v>1.46997654438019</v>
       </c>
       <c r="H1792" t="n">
         <v>35842</v>
@@ -52540,7 +52540,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.484494805336</v>
+        <v>1.48449492454529</v>
       </c>
       <c r="H1799" t="n">
         <v>148023</v>
@@ -52743,7 +52743,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.62423324584961</v>
+        <v>1.6242333650589</v>
       </c>
       <c r="H1806" t="n">
         <v>403949</v>
@@ -52859,7 +52859,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.62786304950714</v>
+        <v>1.62786293029785</v>
       </c>
       <c r="H1810" t="n">
         <v>198945</v>
@@ -52975,7 +52975,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1814" t="n">
-        <v>1.484494805336</v>
+        <v>1.48449492454529</v>
       </c>
       <c r="H1814" t="n">
         <v>499202</v>
@@ -53120,7 +53120,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1819" t="n">
-        <v>1.4427547454834</v>
+        <v>1.44275486469269</v>
       </c>
       <c r="H1819" t="n">
         <v>217610</v>
@@ -53265,7 +53265,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.37742245197296</v>
+        <v>1.37742257118225</v>
       </c>
       <c r="H1824" t="n">
         <v>270982</v>
@@ -53294,7 +53294,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.3737930059433</v>
+        <v>1.37379288673401</v>
       </c>
       <c r="H1825" t="n">
         <v>120972</v>
@@ -53352,7 +53352,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.37923729419708</v>
+        <v>1.37923717498779</v>
       </c>
       <c r="H1827" t="n">
         <v>53687</v>
@@ -53410,7 +53410,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1829" t="n">
-        <v>1.38286685943604</v>
+        <v>1.38286697864532</v>
       </c>
       <c r="H1829" t="n">
         <v>94628</v>
@@ -53497,7 +53497,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.3737930059433</v>
+        <v>1.37379288673401</v>
       </c>
       <c r="H1832" t="n">
         <v>244109</v>
@@ -53729,7 +53729,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.27397978305817</v>
+        <v>1.27397966384888</v>
       </c>
       <c r="H1840" t="n">
         <v>208171</v>
@@ -53758,7 +53758,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.24675798416138</v>
+        <v>1.24675786495209</v>
       </c>
       <c r="H1841" t="n">
         <v>378238</v>
@@ -53816,7 +53816,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1843" t="n">
-        <v>1.2140918970108</v>
+        <v>1.21409177780151</v>
       </c>
       <c r="H1843" t="n">
         <v>719768</v>
@@ -53903,7 +53903,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.23949885368347</v>
+        <v>1.23949873447418</v>
       </c>
       <c r="H1846" t="n">
         <v>172765</v>
@@ -53932,7 +53932,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.2340544462204</v>
+        <v>1.23405432701111</v>
       </c>
       <c r="H1847" t="n">
         <v>129520</v>
@@ -54077,7 +54077,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.2340544462204</v>
+        <v>1.23405432701111</v>
       </c>
       <c r="H1852" t="n">
         <v>279885</v>
@@ -54164,7 +54164,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.2340544462204</v>
+        <v>1.23405432701111</v>
       </c>
       <c r="H1855" t="n">
         <v>312198</v>
@@ -54251,7 +54251,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.2340544462204</v>
+        <v>1.23405432701111</v>
       </c>
       <c r="H1858" t="n">
         <v>147893</v>
@@ -54309,7 +54309,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.2140918970108</v>
+        <v>1.21409177780151</v>
       </c>
       <c r="H1860" t="n">
         <v>113649</v>
@@ -54396,7 +54396,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.2140918970108</v>
+        <v>1.21409177780151</v>
       </c>
       <c r="H1863" t="n">
         <v>154799</v>
@@ -80009,6 +80009,35 @@
         <v>6552</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>1.58200001716614</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>1.58200001716614</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>291</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BST.MI.xlsx
+++ b/data/BST.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74831390380859</v>
+        <v>2.74831414222717</v>
       </c>
       <c r="H2" t="n">
         <v>11649</v>
@@ -456,7 +456,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>2.69898533821106</v>
+        <v>2.69898557662964</v>
       </c>
       <c r="H3" t="n">
         <v>10338</v>
@@ -485,7 +485,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74831390380859</v>
+        <v>2.74831414222717</v>
       </c>
       <c r="H4" t="n">
         <v>9462</v>
@@ -514,7 +514,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G5" t="n">
-        <v>2.68630075454712</v>
+        <v>2.68630123138428</v>
       </c>
       <c r="H5" t="n">
         <v>17322</v>
@@ -630,7 +630,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G9" t="n">
-        <v>2.71730756759644</v>
+        <v>2.71730732917786</v>
       </c>
       <c r="H9" t="n">
         <v>107316</v>
@@ -659,7 +659,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G10" t="n">
-        <v>2.60737490653992</v>
+        <v>2.60737466812134</v>
       </c>
       <c r="H10" t="n">
         <v>69347</v>
@@ -688,7 +688,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G11" t="n">
-        <v>2.48757672309875</v>
+        <v>2.48757648468018</v>
       </c>
       <c r="H11" t="n">
         <v>21140</v>
@@ -804,7 +804,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.50167083740234</v>
+        <v>2.50167059898376</v>
       </c>
       <c r="H15" t="n">
         <v>141373</v>
@@ -862,7 +862,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>2.45234203338623</v>
+        <v>2.45234227180481</v>
       </c>
       <c r="H17" t="n">
         <v>23673</v>
@@ -920,7 +920,7 @@
         <v>3.25</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29026174545288</v>
+        <v>2.2902615070343</v>
       </c>
       <c r="H19" t="n">
         <v>36778</v>
@@ -949,7 +949,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G20" t="n">
-        <v>2.29730868339539</v>
+        <v>2.29730892181396</v>
       </c>
       <c r="H20" t="n">
         <v>15863</v>
@@ -978,7 +978,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G21" t="n">
-        <v>2.39455676078796</v>
+        <v>2.39455652236938</v>
       </c>
       <c r="H21" t="n">
         <v>45946</v>
@@ -1007,7 +1007,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G22" t="n">
-        <v>2.29871797561646</v>
+        <v>2.29871869087219</v>
       </c>
       <c r="H22" t="n">
         <v>226114</v>
@@ -1036,7 +1036,7 @@
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>2.1140878200531</v>
+        <v>2.11408805847168</v>
       </c>
       <c r="H23" t="n">
         <v>108673</v>
@@ -1123,7 +1123,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G26" t="n">
-        <v>1.86885356903076</v>
+        <v>1.86885368824005</v>
       </c>
       <c r="H26" t="n">
         <v>671185</v>
@@ -1152,7 +1152,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G27" t="n">
-        <v>1.72650516033173</v>
+        <v>1.72650504112244</v>
       </c>
       <c r="H27" t="n">
         <v>216589</v>
@@ -1181,7 +1181,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G28" t="n">
-        <v>1.71100163459778</v>
+        <v>1.71100187301636</v>
       </c>
       <c r="H28" t="n">
         <v>532299</v>
@@ -1210,7 +1210,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G29" t="n">
-        <v>1.86039745807648</v>
+        <v>1.86039733886719</v>
       </c>
       <c r="H29" t="n">
         <v>494650</v>
@@ -1239,7 +1239,7 @@
         <v>2.5</v>
       </c>
       <c r="G30" t="n">
-        <v>1.76173985004425</v>
+        <v>1.76173973083496</v>
       </c>
       <c r="H30" t="n">
         <v>322108</v>
@@ -1355,7 +1355,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G34" t="n">
-        <v>2.07039666175842</v>
+        <v>2.070396900177</v>
       </c>
       <c r="H34" t="n">
         <v>372234</v>
@@ -1413,7 +1413,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G36" t="n">
-        <v>2.09294676780701</v>
+        <v>2.09294700622559</v>
       </c>
       <c r="H36" t="n">
         <v>286614</v>
@@ -1442,7 +1442,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G37" t="n">
-        <v>2.15918850898743</v>
+        <v>2.15918803215027</v>
       </c>
       <c r="H37" t="n">
         <v>158423</v>
@@ -1471,7 +1471,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G38" t="n">
-        <v>2.16059803962708</v>
+        <v>2.1605978012085</v>
       </c>
       <c r="H38" t="n">
         <v>79649</v>
@@ -1587,7 +1587,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G42" t="n">
-        <v>2.06334972381592</v>
+        <v>2.06334948539734</v>
       </c>
       <c r="H42" t="n">
         <v>7283</v>
@@ -1616,7 +1616,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G43" t="n">
-        <v>2.07321548461914</v>
+        <v>2.07321524620056</v>
       </c>
       <c r="H43" t="n">
         <v>76461</v>
@@ -1703,7 +1703,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G46" t="n">
-        <v>2.1577787399292</v>
+        <v>2.15777897834778</v>
       </c>
       <c r="H46" t="n">
         <v>65121</v>
@@ -1732,7 +1732,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G47" t="n">
-        <v>2.14932227134705</v>
+        <v>2.14932250976562</v>
       </c>
       <c r="H47" t="n">
         <v>45138</v>
@@ -1761,7 +1761,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12113475799561</v>
+        <v>2.12113451957703</v>
       </c>
       <c r="H48" t="n">
         <v>75156</v>
@@ -1819,7 +1819,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G50" t="n">
-        <v>2.12677216529846</v>
+        <v>2.12677240371704</v>
       </c>
       <c r="H50" t="n">
         <v>93185</v>
@@ -1848,7 +1848,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G51" t="n">
-        <v>2.21274542808533</v>
+        <v>2.21274518966675</v>
       </c>
       <c r="H51" t="n">
         <v>169907</v>
@@ -1877,7 +1877,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G52" t="n">
-        <v>2.26348352432251</v>
+        <v>2.26348328590393</v>
       </c>
       <c r="H52" t="n">
         <v>74146</v>
@@ -1906,7 +1906,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G53" t="n">
-        <v>2.27053022384644</v>
+        <v>2.27052998542786</v>
       </c>
       <c r="H53" t="n">
         <v>68321</v>
@@ -1935,7 +1935,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G54" t="n">
-        <v>2.17469143867493</v>
+        <v>2.17469191551208</v>
       </c>
       <c r="H54" t="n">
         <v>139285</v>
@@ -1964,7 +1964,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G55" t="n">
-        <v>2.18596696853638</v>
+        <v>2.1859667301178</v>
       </c>
       <c r="H55" t="n">
         <v>20070</v>
@@ -2051,7 +2051,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G58" t="n">
-        <v>2.23670482635498</v>
+        <v>2.23670530319214</v>
       </c>
       <c r="H58" t="n">
         <v>93732</v>
@@ -2080,7 +2080,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G59" t="n">
-        <v>2.17751026153564</v>
+        <v>2.17751049995422</v>
       </c>
       <c r="H59" t="n">
         <v>71887</v>
@@ -2109,7 +2109,7 @@
         <v>3</v>
       </c>
       <c r="G60" t="n">
-        <v>2.1140878200531</v>
+        <v>2.11408805847168</v>
       </c>
       <c r="H60" t="n">
         <v>13315</v>
@@ -2196,7 +2196,7 @@
         <v>2.80599999427795</v>
       </c>
       <c r="G63" t="n">
-        <v>1.97737693786621</v>
+        <v>1.97737669944763</v>
       </c>
       <c r="H63" t="n">
         <v>35478</v>
@@ -2225,7 +2225,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G64" t="n">
-        <v>1.89281332492828</v>
+        <v>1.89281344413757</v>
       </c>
       <c r="H64" t="n">
         <v>198445</v>
@@ -2254,7 +2254,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>1.98724234104156</v>
+        <v>1.98724257946014</v>
       </c>
       <c r="H65" t="n">
         <v>88924</v>
@@ -2283,7 +2283,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G66" t="n">
-        <v>1.9449610710144</v>
+        <v>1.94496095180511</v>
       </c>
       <c r="H66" t="n">
         <v>23053</v>
@@ -2312,7 +2312,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G67" t="n">
-        <v>1.95482647418976</v>
+        <v>1.95482635498047</v>
       </c>
       <c r="H67" t="n">
         <v>116949</v>
@@ -2341,7 +2341,7 @@
         <v>2.71600008010864</v>
       </c>
       <c r="G68" t="n">
-        <v>1.91395390033722</v>
+        <v>1.91395425796509</v>
       </c>
       <c r="H68" t="n">
         <v>32713</v>
@@ -2370,7 +2370,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G69" t="n">
-        <v>1.98724234104156</v>
+        <v>1.98724257946014</v>
       </c>
       <c r="H69" t="n">
         <v>51935</v>
@@ -2428,7 +2428,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G71" t="n">
-        <v>1.92381978034973</v>
+        <v>1.9238201379776</v>
       </c>
       <c r="H71" t="n">
         <v>17504</v>
@@ -2457,7 +2457,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>1.98019540309906</v>
+        <v>1.98019552230835</v>
       </c>
       <c r="H72" t="n">
         <v>67165</v>
@@ -2573,7 +2573,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>2.17046332359314</v>
+        <v>2.17046356201172</v>
       </c>
       <c r="H76" t="n">
         <v>157055</v>
@@ -2602,7 +2602,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G77" t="n">
-        <v>2.14791321754456</v>
+        <v>2.14791297912598</v>
       </c>
       <c r="H77" t="n">
         <v>12373</v>
@@ -2631,7 +2631,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G78" t="n">
-        <v>2.17751026153564</v>
+        <v>2.17751049995422</v>
       </c>
       <c r="H78" t="n">
         <v>77091</v>
@@ -2660,7 +2660,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G79" t="n">
-        <v>2.18032908439636</v>
+        <v>2.18032932281494</v>
       </c>
       <c r="H79" t="n">
         <v>73179</v>
@@ -2689,7 +2689,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G80" t="n">
-        <v>2.12113475799561</v>
+        <v>2.12113451957703</v>
       </c>
       <c r="H80" t="n">
         <v>9388</v>
@@ -2776,7 +2776,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G83" t="n">
-        <v>2.02670526504517</v>
+        <v>2.02670550346375</v>
       </c>
       <c r="H83" t="n">
         <v>164177</v>
@@ -2805,7 +2805,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G84" t="n">
-        <v>1.98724234104156</v>
+        <v>1.98724257946014</v>
       </c>
       <c r="H84" t="n">
         <v>42849</v>
@@ -2834,7 +2834,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G85" t="n">
-        <v>1.94918918609619</v>
+        <v>1.9491890668869</v>
       </c>
       <c r="H85" t="n">
         <v>142278</v>
@@ -2863,7 +2863,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>1.97314858436584</v>
+        <v>1.97314882278442</v>
       </c>
       <c r="H86" t="n">
         <v>52750</v>
@@ -2921,7 +2921,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G88" t="n">
-        <v>1.89845061302185</v>
+        <v>1.89845073223114</v>
       </c>
       <c r="H88" t="n">
         <v>36792</v>
@@ -2950,7 +2950,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G89" t="n">
-        <v>1.86321604251862</v>
+        <v>1.86321616172791</v>
       </c>
       <c r="H89" t="n">
         <v>23082</v>
@@ -2979,7 +2979,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>1.87687909603119</v>
+        <v>1.87687885761261</v>
       </c>
       <c r="H90" t="n">
         <v>235784</v>
@@ -3037,7 +3037,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>1.7402480840683</v>
+        <v>1.74024820327759</v>
       </c>
       <c r="H92" t="n">
         <v>93154</v>
@@ -3066,7 +3066,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G93" t="n">
-        <v>1.68559587001801</v>
+        <v>1.68559575080872</v>
       </c>
       <c r="H93" t="n">
         <v>125569</v>
@@ -3124,7 +3124,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G95" t="n">
-        <v>1.6122465133667</v>
+        <v>1.61224627494812</v>
       </c>
       <c r="H95" t="n">
         <v>248217</v>
@@ -3153,7 +3153,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62662851810455</v>
+        <v>1.62662887573242</v>
       </c>
       <c r="H96" t="n">
         <v>316466</v>
@@ -3182,7 +3182,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G97" t="n">
-        <v>1.63957273960114</v>
+        <v>1.63957262039185</v>
       </c>
       <c r="H97" t="n">
         <v>216744</v>
@@ -3269,7 +3269,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G100" t="n">
-        <v>1.63957273960114</v>
+        <v>1.63957262039185</v>
       </c>
       <c r="H100" t="n">
         <v>213463</v>
@@ -3298,7 +3298,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G101" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991017341614</v>
       </c>
       <c r="H101" t="n">
         <v>233008</v>
@@ -3356,7 +3356,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G103" t="n">
-        <v>1.86249685287476</v>
+        <v>1.86249697208405</v>
       </c>
       <c r="H103" t="n">
         <v>317819</v>
@@ -3414,7 +3414,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G105" t="n">
-        <v>1.86249685287476</v>
+        <v>1.86249697208405</v>
       </c>
       <c r="H105" t="n">
         <v>30183</v>
@@ -3443,7 +3443,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G106" t="n">
-        <v>1.84092354774475</v>
+        <v>1.84092378616333</v>
       </c>
       <c r="H106" t="n">
         <v>112565</v>
@@ -3472,7 +3472,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>1.81215918064117</v>
+        <v>1.81215906143188</v>
       </c>
       <c r="H107" t="n">
         <v>68874</v>
@@ -3530,7 +3530,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G109" t="n">
-        <v>1.79490077495575</v>
+        <v>1.79490053653717</v>
       </c>
       <c r="H109" t="n">
         <v>138260</v>
@@ -3588,7 +3588,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G111" t="n">
-        <v>1.83948528766632</v>
+        <v>1.83948540687561</v>
       </c>
       <c r="H111" t="n">
         <v>113743</v>
@@ -3617,7 +3617,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>1.80640625953674</v>
+        <v>1.80640637874603</v>
       </c>
       <c r="H112" t="n">
         <v>67273</v>
@@ -3704,7 +3704,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G115" t="n">
-        <v>1.73305714130402</v>
+        <v>1.73305702209473</v>
       </c>
       <c r="H115" t="n">
         <v>65890</v>
@@ -3820,7 +3820,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G119" t="n">
-        <v>1.68559587001801</v>
+        <v>1.68559575080872</v>
       </c>
       <c r="H119" t="n">
         <v>43254</v>
@@ -3849,7 +3849,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G120" t="n">
-        <v>1.75606846809387</v>
+        <v>1.75606858730316</v>
       </c>
       <c r="H120" t="n">
         <v>51272</v>
@@ -3878,7 +3878,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G121" t="n">
-        <v>1.75319218635559</v>
+        <v>1.7531920671463</v>
       </c>
       <c r="H121" t="n">
         <v>37124</v>
@@ -3907,7 +3907,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>1.81215918064117</v>
+        <v>1.81215906143188</v>
       </c>
       <c r="H122" t="n">
         <v>185327</v>
@@ -3936,7 +3936,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G123" t="n">
-        <v>1.83804714679718</v>
+        <v>1.83804738521576</v>
       </c>
       <c r="H123" t="n">
         <v>48383</v>
@@ -3965,7 +3965,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G124" t="n">
-        <v>1.6122465133667</v>
+        <v>1.61224627494812</v>
       </c>
       <c r="H124" t="n">
         <v>89074</v>
@@ -3994,7 +3994,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G125" t="n">
-        <v>1.48999738693237</v>
+        <v>1.48999762535095</v>
       </c>
       <c r="H125" t="n">
         <v>94566</v>
@@ -4023,7 +4023,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G126" t="n">
-        <v>1.5302677154541</v>
+        <v>1.53026783466339</v>
       </c>
       <c r="H126" t="n">
         <v>255565</v>
@@ -4110,7 +4110,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G129" t="n">
-        <v>1.47561526298523</v>
+        <v>1.47561538219452</v>
       </c>
       <c r="H129" t="n">
         <v>141074</v>
@@ -4168,7 +4168,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G131" t="n">
-        <v>1.49862706661224</v>
+        <v>1.49862694740295</v>
       </c>
       <c r="H131" t="n">
         <v>64983</v>
@@ -4284,7 +4284,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G135" t="n">
-        <v>1.5604704618454</v>
+        <v>1.56047034263611</v>
       </c>
       <c r="H135" t="n">
         <v>94625</v>
@@ -4313,7 +4313,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G136" t="n">
-        <v>1.63238155841827</v>
+        <v>1.63238167762756</v>
       </c>
       <c r="H136" t="n">
         <v>98434</v>
@@ -4400,7 +4400,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G139" t="n">
-        <v>1.62087571620941</v>
+        <v>1.62087595462799</v>
       </c>
       <c r="H139" t="n">
         <v>42187</v>
@@ -4429,7 +4429,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G140" t="n">
-        <v>1.62087571620941</v>
+        <v>1.62087595462799</v>
       </c>
       <c r="H140" t="n">
         <v>61870</v>
@@ -4458,7 +4458,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G141" t="n">
-        <v>1.6122465133667</v>
+        <v>1.61224627494812</v>
       </c>
       <c r="H141" t="n">
         <v>23242</v>
@@ -4487,7 +4487,7 @@
         <v>2.25</v>
       </c>
       <c r="G142" t="n">
-        <v>1.61799919605255</v>
+        <v>1.61799931526184</v>
       </c>
       <c r="H142" t="n">
         <v>34967</v>
@@ -4516,7 +4516,7 @@
         <v>2.25</v>
       </c>
       <c r="G143" t="n">
-        <v>1.61799919605255</v>
+        <v>1.61799931526184</v>
       </c>
       <c r="H143" t="n">
         <v>101012</v>
@@ -4545,7 +4545,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G144" t="n">
-        <v>1.56190860271454</v>
+        <v>1.56190848350525</v>
       </c>
       <c r="H144" t="n">
         <v>42992</v>
@@ -4574,7 +4574,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G145" t="n">
-        <v>1.51300930976868</v>
+        <v>1.51300919055939</v>
       </c>
       <c r="H145" t="n">
         <v>118150</v>
@@ -4632,7 +4632,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G147" t="n">
-        <v>1.56766152381897</v>
+        <v>1.56766140460968</v>
       </c>
       <c r="H147" t="n">
         <v>31863</v>
@@ -4661,7 +4661,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G148" t="n">
-        <v>1.48855936527252</v>
+        <v>1.48855924606323</v>
       </c>
       <c r="H148" t="n">
         <v>109814</v>
@@ -4690,7 +4690,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G149" t="n">
-        <v>1.51876187324524</v>
+        <v>1.51876211166382</v>
       </c>
       <c r="H149" t="n">
         <v>255392</v>
@@ -4719,7 +4719,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G150" t="n">
-        <v>1.48855936527252</v>
+        <v>1.48855924606323</v>
       </c>
       <c r="H150" t="n">
         <v>211962</v>
@@ -4777,7 +4777,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G152" t="n">
-        <v>1.33754599094391</v>
+        <v>1.33754622936249</v>
       </c>
       <c r="H152" t="n">
         <v>136787</v>
@@ -4806,7 +4806,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G153" t="n">
-        <v>1.34401786327362</v>
+        <v>1.34401822090149</v>
       </c>
       <c r="H153" t="n">
         <v>101071</v>
@@ -4893,7 +4893,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G156" t="n">
-        <v>1.44828915596008</v>
+        <v>1.44828903675079</v>
       </c>
       <c r="H156" t="n">
         <v>46189</v>
@@ -4922,7 +4922,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G157" t="n">
-        <v>1.48999738693237</v>
+        <v>1.48999762535095</v>
       </c>
       <c r="H157" t="n">
         <v>64387</v>
@@ -4980,7 +4980,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>1.56622338294983</v>
+        <v>1.56622326374054</v>
       </c>
       <c r="H159" t="n">
         <v>153564</v>
@@ -5096,7 +5096,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G163" t="n">
-        <v>1.49143576622009</v>
+        <v>1.4914356470108</v>
       </c>
       <c r="H163" t="n">
         <v>102808</v>
@@ -5154,7 +5154,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G165" t="n">
-        <v>1.53602063655853</v>
+        <v>1.53602075576782</v>
       </c>
       <c r="H165" t="n">
         <v>71695</v>
@@ -5183,7 +5183,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G166" t="n">
-        <v>1.5259530544281</v>
+        <v>1.52595329284668</v>
       </c>
       <c r="H166" t="n">
         <v>74300</v>
@@ -5212,7 +5212,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G167" t="n">
-        <v>1.54608833789825</v>
+        <v>1.54608821868896</v>
       </c>
       <c r="H167" t="n">
         <v>87448</v>
@@ -5241,7 +5241,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G168" t="n">
-        <v>1.52307665348053</v>
+        <v>1.52307677268982</v>
       </c>
       <c r="H168" t="n">
         <v>57256</v>
@@ -5270,7 +5270,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>1.51013267040253</v>
+        <v>1.51013255119324</v>
       </c>
       <c r="H169" t="n">
         <v>64844</v>
@@ -5299,7 +5299,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G170" t="n">
-        <v>1.51588559150696</v>
+        <v>1.51588547229767</v>
       </c>
       <c r="H170" t="n">
         <v>58563</v>
@@ -5357,7 +5357,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G172" t="n">
-        <v>1.53745889663696</v>
+        <v>1.53745901584625</v>
       </c>
       <c r="H172" t="n">
         <v>152191</v>
@@ -5386,7 +5386,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G173" t="n">
-        <v>1.55759394168854</v>
+        <v>1.55759382247925</v>
       </c>
       <c r="H173" t="n">
         <v>105976</v>
@@ -5415,7 +5415,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G174" t="n">
-        <v>1.5647851228714</v>
+        <v>1.56478488445282</v>
       </c>
       <c r="H174" t="n">
         <v>39718</v>
@@ -5444,7 +5444,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G175" t="n">
-        <v>1.54896473884583</v>
+        <v>1.54896461963654</v>
       </c>
       <c r="H175" t="n">
         <v>69988</v>
@@ -5502,7 +5502,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G177" t="n">
-        <v>1.5604704618454</v>
+        <v>1.56047034263611</v>
       </c>
       <c r="H177" t="n">
         <v>16139</v>
@@ -5531,7 +5531,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G178" t="n">
-        <v>1.54896473884583</v>
+        <v>1.54896461963654</v>
       </c>
       <c r="H178" t="n">
         <v>110525</v>
@@ -5560,7 +5560,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G179" t="n">
-        <v>1.50725615024567</v>
+        <v>1.50725626945496</v>
       </c>
       <c r="H179" t="n">
         <v>115275</v>
@@ -5618,7 +5618,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G181" t="n">
-        <v>1.49862706661224</v>
+        <v>1.49862694740295</v>
       </c>
       <c r="H181" t="n">
         <v>57907</v>
@@ -5647,7 +5647,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G182" t="n">
-        <v>1.46986246109009</v>
+        <v>1.46986222267151</v>
       </c>
       <c r="H182" t="n">
         <v>47947</v>
@@ -5705,7 +5705,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G184" t="n">
-        <v>1.48855936527252</v>
+        <v>1.48855924606323</v>
       </c>
       <c r="H184" t="n">
         <v>31709</v>
@@ -5734,7 +5734,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G185" t="n">
-        <v>1.47705340385437</v>
+        <v>1.47705352306366</v>
       </c>
       <c r="H185" t="n">
         <v>12250</v>
@@ -5763,7 +5763,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G186" t="n">
-        <v>1.48855936527252</v>
+        <v>1.48855924606323</v>
       </c>
       <c r="H186" t="n">
         <v>5248</v>
@@ -5792,7 +5792,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G187" t="n">
-        <v>1.48280656337738</v>
+        <v>1.48280644416809</v>
       </c>
       <c r="H187" t="n">
         <v>8172</v>
@@ -5821,7 +5821,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G188" t="n">
-        <v>1.48999738693237</v>
+        <v>1.48999762535095</v>
       </c>
       <c r="H188" t="n">
         <v>3505</v>
@@ -5879,7 +5879,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G190" t="n">
-        <v>1.46986246109009</v>
+        <v>1.46986222267151</v>
       </c>
       <c r="H190" t="n">
         <v>50388</v>
@@ -5966,7 +5966,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G193" t="n">
-        <v>1.46986246109009</v>
+        <v>1.46986222267151</v>
       </c>
       <c r="H193" t="n">
         <v>21732</v>
@@ -6053,7 +6053,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G196" t="n">
-        <v>1.51876187324524</v>
+        <v>1.51876211166382</v>
       </c>
       <c r="H196" t="n">
         <v>72181</v>
@@ -6082,7 +6082,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G197" t="n">
-        <v>1.54896473884583</v>
+        <v>1.54896461963654</v>
       </c>
       <c r="H197" t="n">
         <v>54297</v>
@@ -6111,7 +6111,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G198" t="n">
-        <v>1.60936987400055</v>
+        <v>1.60936975479126</v>
       </c>
       <c r="H198" t="n">
         <v>215286</v>
@@ -6140,7 +6140,7 @@
         <v>2.25</v>
       </c>
       <c r="G199" t="n">
-        <v>1.61799919605255</v>
+        <v>1.61799931526184</v>
       </c>
       <c r="H199" t="n">
         <v>36269</v>
@@ -6169,7 +6169,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991017341614</v>
       </c>
       <c r="H200" t="n">
         <v>205807</v>
@@ -6198,7 +6198,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991017341614</v>
       </c>
       <c r="H201" t="n">
         <v>93341</v>
@@ -6227,7 +6227,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>1.67552816867828</v>
+        <v>1.67552781105042</v>
       </c>
       <c r="H202" t="n">
         <v>28652</v>
@@ -6256,7 +6256,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991017341614</v>
       </c>
       <c r="H203" t="n">
         <v>74895</v>
@@ -6285,7 +6285,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G204" t="n">
-        <v>1.68703377246857</v>
+        <v>1.68703389167786</v>
       </c>
       <c r="H204" t="n">
         <v>57861</v>
@@ -6343,7 +6343,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G206" t="n">
-        <v>1.7273041009903</v>
+        <v>1.72730422019958</v>
       </c>
       <c r="H206" t="n">
         <v>94014</v>
@@ -6372,7 +6372,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G207" t="n">
-        <v>1.73161864280701</v>
+        <v>1.7316187620163</v>
       </c>
       <c r="H207" t="n">
         <v>57561</v>
@@ -6430,7 +6430,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>1.74743902683258</v>
+        <v>1.74743926525116</v>
       </c>
       <c r="H209" t="n">
         <v>56802</v>
@@ -6459,7 +6459,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G210" t="n">
-        <v>1.77332711219788</v>
+        <v>1.77332723140717</v>
       </c>
       <c r="H210" t="n">
         <v>264730</v>
@@ -6488,7 +6488,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G211" t="n">
-        <v>1.75606846809387</v>
+        <v>1.75606858730316</v>
       </c>
       <c r="H211" t="n">
         <v>51514</v>
@@ -6517,7 +6517,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G212" t="n">
-        <v>1.71723675727844</v>
+        <v>1.71723651885986</v>
       </c>
       <c r="H212" t="n">
         <v>49779</v>
@@ -6546,7 +6546,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G213" t="n">
-        <v>1.74743902683258</v>
+        <v>1.74743926525116</v>
       </c>
       <c r="H213" t="n">
         <v>87327</v>
@@ -6575,7 +6575,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G214" t="n">
-        <v>1.71867477893829</v>
+        <v>1.71867489814758</v>
       </c>
       <c r="H214" t="n">
         <v>63356</v>
@@ -6604,7 +6604,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>1.67552816867828</v>
+        <v>1.67552781105042</v>
       </c>
       <c r="H215" t="n">
         <v>240056</v>
@@ -6633,7 +6633,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G216" t="n">
-        <v>1.58348178863525</v>
+        <v>1.58348190784454</v>
       </c>
       <c r="H216" t="n">
         <v>233085</v>
@@ -6662,7 +6662,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G217" t="n">
-        <v>1.55327951908112</v>
+        <v>1.55327916145325</v>
       </c>
       <c r="H217" t="n">
         <v>114963</v>
@@ -6691,7 +6691,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>1.51013267040253</v>
+        <v>1.51013255119324</v>
       </c>
       <c r="H218" t="n">
         <v>155544</v>
@@ -6720,7 +6720,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>1.51013267040253</v>
+        <v>1.51013255119324</v>
       </c>
       <c r="H219" t="n">
         <v>140088</v>
@@ -6807,7 +6807,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G222" t="n">
-        <v>1.43246877193451</v>
+        <v>1.43246865272522</v>
       </c>
       <c r="H222" t="n">
         <v>176278</v>
@@ -6836,7 +6836,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G223" t="n">
-        <v>1.42383933067322</v>
+        <v>1.42383921146393</v>
       </c>
       <c r="H223" t="n">
         <v>59778</v>
@@ -6865,7 +6865,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>1.40586149692535</v>
+        <v>1.40586173534393</v>
       </c>
       <c r="H224" t="n">
         <v>291769</v>
@@ -6952,7 +6952,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G227" t="n">
-        <v>1.41664826869965</v>
+        <v>1.41664814949036</v>
       </c>
       <c r="H227" t="n">
         <v>121901</v>
@@ -7010,7 +7010,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G229" t="n">
-        <v>1.33754599094391</v>
+        <v>1.33754622936249</v>
       </c>
       <c r="H229" t="n">
         <v>165879</v>
@@ -7039,7 +7039,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G230" t="n">
-        <v>1.35840046405792</v>
+        <v>1.35840034484863</v>
       </c>
       <c r="H230" t="n">
         <v>71664</v>
@@ -7068,7 +7068,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G231" t="n">
-        <v>1.33754599094391</v>
+        <v>1.33754622936249</v>
       </c>
       <c r="H231" t="n">
         <v>103896</v>
@@ -7126,7 +7126,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G233" t="n">
-        <v>1.3332314491272</v>
+        <v>1.33323132991791</v>
       </c>
       <c r="H233" t="n">
         <v>41061</v>
@@ -7155,7 +7155,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G234" t="n">
-        <v>1.29799509048462</v>
+        <v>1.29799497127533</v>
       </c>
       <c r="H234" t="n">
         <v>45856</v>
@@ -7213,7 +7213,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G236" t="n">
-        <v>1.32316386699677</v>
+        <v>1.32316398620605</v>
       </c>
       <c r="H236" t="n">
         <v>77271</v>
@@ -7271,7 +7271,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G238" t="n">
-        <v>1.38069272041321</v>
+        <v>1.38069260120392</v>
       </c>
       <c r="H238" t="n">
         <v>163588</v>
@@ -7329,7 +7329,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G240" t="n">
-        <v>1.40226590633392</v>
+        <v>1.40226602554321</v>
       </c>
       <c r="H240" t="n">
         <v>311388</v>
@@ -7358,7 +7358,7 @@
         <v>1.95299994945526</v>
       </c>
       <c r="G241" t="n">
-        <v>1.40442323684692</v>
+        <v>1.40442335605621</v>
       </c>
       <c r="H241" t="n">
         <v>228383</v>
@@ -7387,7 +7387,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G242" t="n">
-        <v>1.48712134361267</v>
+        <v>1.48712122440338</v>
       </c>
       <c r="H242" t="n">
         <v>292070</v>
@@ -7445,7 +7445,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G244" t="n">
-        <v>1.44828915596008</v>
+        <v>1.44828903675079</v>
       </c>
       <c r="H244" t="n">
         <v>309397</v>
@@ -7474,7 +7474,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G245" t="n">
-        <v>1.48855936527252</v>
+        <v>1.48855924606323</v>
       </c>
       <c r="H245" t="n">
         <v>233960</v>
@@ -7532,7 +7532,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G247" t="n">
-        <v>1.55327951908112</v>
+        <v>1.55327916145325</v>
       </c>
       <c r="H247" t="n">
         <v>317915</v>
@@ -7561,7 +7561,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G248" t="n">
-        <v>1.53602063655853</v>
+        <v>1.53602075576782</v>
       </c>
       <c r="H248" t="n">
         <v>216798</v>
@@ -7619,7 +7619,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G250" t="n">
-        <v>1.54464995861053</v>
+        <v>1.54465019702911</v>
       </c>
       <c r="H250" t="n">
         <v>107669</v>
@@ -7677,7 +7677,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G252" t="n">
-        <v>1.54608833789825</v>
+        <v>1.54608821868896</v>
       </c>
       <c r="H252" t="n">
         <v>165938</v>
@@ -7706,7 +7706,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G253" t="n">
-        <v>1.56190860271454</v>
+        <v>1.56190848350525</v>
       </c>
       <c r="H253" t="n">
         <v>96063</v>
@@ -7735,7 +7735,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>1.5604704618454</v>
+        <v>1.56047034263611</v>
       </c>
       <c r="H254" t="n">
         <v>51401</v>
@@ -7764,7 +7764,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G255" t="n">
-        <v>1.5604704618454</v>
+        <v>1.56047034263611</v>
       </c>
       <c r="H255" t="n">
         <v>23797</v>
@@ -7793,7 +7793,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G256" t="n">
-        <v>1.55759394168854</v>
+        <v>1.55759382247925</v>
       </c>
       <c r="H256" t="n">
         <v>50577</v>
@@ -7822,7 +7822,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G257" t="n">
-        <v>1.58204388618469</v>
+        <v>1.5820437669754</v>
       </c>
       <c r="H257" t="n">
         <v>82049</v>
@@ -7880,7 +7880,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G259" t="n">
-        <v>1.64388740062714</v>
+        <v>1.64388751983643</v>
       </c>
       <c r="H259" t="n">
         <v>395698</v>
@@ -7938,7 +7938,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G261" t="n">
-        <v>1.65826940536499</v>
+        <v>1.6582692861557</v>
       </c>
       <c r="H261" t="n">
         <v>152954</v>
@@ -7996,7 +7996,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>1.66114580631256</v>
+        <v>1.66114568710327</v>
       </c>
       <c r="H263" t="n">
         <v>109636</v>
@@ -8083,7 +8083,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G266" t="n">
-        <v>1.67409002780914</v>
+        <v>1.67408990859985</v>
       </c>
       <c r="H266" t="n">
         <v>106846</v>
@@ -8228,7 +8228,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G271" t="n">
-        <v>1.7747654914856</v>
+        <v>1.77476537227631</v>
       </c>
       <c r="H271" t="n">
         <v>96436</v>
@@ -8286,7 +8286,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G273" t="n">
-        <v>1.74168634414673</v>
+        <v>1.74168622493744</v>
       </c>
       <c r="H273" t="n">
         <v>60014</v>
@@ -8315,7 +8315,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G274" t="n">
-        <v>1.7488774061203</v>
+        <v>1.74887728691101</v>
       </c>
       <c r="H274" t="n">
         <v>56096</v>
@@ -8344,7 +8344,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G275" t="n">
-        <v>1.75463020801544</v>
+        <v>1.75463056564331</v>
       </c>
       <c r="H275" t="n">
         <v>71837</v>
@@ -8402,7 +8402,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G277" t="n">
-        <v>1.68991029262543</v>
+        <v>1.68991017341614</v>
       </c>
       <c r="H277" t="n">
         <v>113971</v>
@@ -8431,7 +8431,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G278" t="n">
-        <v>1.66114580631256</v>
+        <v>1.66114568710327</v>
       </c>
       <c r="H278" t="n">
         <v>173082</v>
@@ -8489,7 +8489,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G280" t="n">
-        <v>1.71723675727844</v>
+        <v>1.71723651885986</v>
       </c>
       <c r="H280" t="n">
         <v>72996</v>
@@ -8547,7 +8547,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G282" t="n">
-        <v>1.71436011791229</v>
+        <v>1.71436023712158</v>
       </c>
       <c r="H282" t="n">
         <v>19896</v>
@@ -8576,7 +8576,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.63957273960114</v>
+        <v>1.63957262039185</v>
       </c>
       <c r="H283" t="n">
         <v>100008</v>
@@ -8605,7 +8605,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G284" t="n">
-        <v>1.62087571620941</v>
+        <v>1.62087595462799</v>
       </c>
       <c r="H284" t="n">
         <v>46637</v>
@@ -8692,7 +8692,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G287" t="n">
-        <v>1.66833674907684</v>
+        <v>1.66833698749542</v>
       </c>
       <c r="H287" t="n">
         <v>166610</v>
@@ -8779,7 +8779,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>1.63957273960114</v>
+        <v>1.63957262039185</v>
       </c>
       <c r="H290" t="n">
         <v>84656</v>
@@ -8808,7 +8808,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G291" t="n">
-        <v>1.63094317913055</v>
+        <v>1.63094329833984</v>
       </c>
       <c r="H291" t="n">
         <v>45265</v>
@@ -8953,7 +8953,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G296" t="n">
-        <v>1.49143576622009</v>
+        <v>1.4914356470108</v>
       </c>
       <c r="H296" t="n">
         <v>99146</v>
@@ -9011,7 +9011,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G298" t="n">
-        <v>1.48280656337738</v>
+        <v>1.48280644416809</v>
       </c>
       <c r="H298" t="n">
         <v>126544</v>
@@ -9069,7 +9069,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>1.52451491355896</v>
+        <v>1.52451479434967</v>
       </c>
       <c r="H300" t="n">
         <v>252976</v>
@@ -9098,7 +9098,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G301" t="n">
-        <v>1.5216383934021</v>
+        <v>1.52163851261139</v>
       </c>
       <c r="H301" t="n">
         <v>197878</v>
@@ -9127,7 +9127,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G302" t="n">
-        <v>1.51876187324524</v>
+        <v>1.51876211166382</v>
       </c>
       <c r="H302" t="n">
         <v>144408</v>
@@ -9156,7 +9156,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>1.51013267040253</v>
+        <v>1.51013255119324</v>
       </c>
       <c r="H303" t="n">
         <v>163594</v>
@@ -9185,7 +9185,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G304" t="n">
-        <v>1.50150322914124</v>
+        <v>1.50150334835052</v>
       </c>
       <c r="H304" t="n">
         <v>195517</v>
@@ -9214,7 +9214,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G305" t="n">
-        <v>1.49718856811523</v>
+        <v>1.49718868732452</v>
       </c>
       <c r="H305" t="n">
         <v>130511</v>
@@ -9243,7 +9243,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G306" t="n">
-        <v>1.51157093048096</v>
+        <v>1.51157104969025</v>
       </c>
       <c r="H306" t="n">
         <v>342739</v>
@@ -9272,7 +9272,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G307" t="n">
-        <v>1.54464995861053</v>
+        <v>1.54465019702911</v>
       </c>
       <c r="H307" t="n">
         <v>276795</v>
@@ -9301,7 +9301,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G308" t="n">
-        <v>1.55903232097626</v>
+        <v>1.55903208255768</v>
       </c>
       <c r="H308" t="n">
         <v>181968</v>
@@ -9330,7 +9330,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>1.53889715671539</v>
+        <v>1.53889727592468</v>
       </c>
       <c r="H309" t="n">
         <v>473186</v>
@@ -9359,7 +9359,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G310" t="n">
-        <v>1.73305714130402</v>
+        <v>1.73305702209473</v>
       </c>
       <c r="H310" t="n">
         <v>2118328</v>
@@ -9475,7 +9475,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G314" t="n">
-        <v>1.7575067281723</v>
+        <v>1.75750696659088</v>
       </c>
       <c r="H314" t="n">
         <v>382673</v>
@@ -9504,7 +9504,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G315" t="n">
-        <v>1.73305714130402</v>
+        <v>1.73305702209473</v>
       </c>
       <c r="H315" t="n">
         <v>135784</v>
@@ -9533,7 +9533,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>1.81215918064117</v>
+        <v>1.81215906143188</v>
       </c>
       <c r="H316" t="n">
         <v>826864</v>
@@ -9562,7 +9562,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>2.04946541786194</v>
+        <v>2.04946565628052</v>
       </c>
       <c r="H317" t="n">
         <v>1769450</v>
@@ -9591,7 +9591,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G318" t="n">
-        <v>1.99049842357635</v>
+        <v>1.99049878120422</v>
       </c>
       <c r="H318" t="n">
         <v>982630</v>
@@ -9620,7 +9620,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>1.95166683197021</v>
+        <v>1.9516669511795</v>
       </c>
       <c r="H319" t="n">
         <v>345138</v>
@@ -9649,7 +9649,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G320" t="n">
-        <v>1.98043119907379</v>
+        <v>1.98043096065521</v>
       </c>
       <c r="H320" t="n">
         <v>550774</v>
@@ -9678,7 +9678,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G321" t="n">
-        <v>1.96604895591736</v>
+        <v>1.96604907512665</v>
       </c>
       <c r="H321" t="n">
         <v>556298</v>
@@ -9707,7 +9707,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G322" t="n">
-        <v>1.9631724357605</v>
+        <v>1.96317267417908</v>
       </c>
       <c r="H322" t="n">
         <v>428819</v>
@@ -9736,7 +9736,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G323" t="n">
-        <v>1.94303750991821</v>
+        <v>1.94303739070892</v>
       </c>
       <c r="H323" t="n">
         <v>580907</v>
@@ -9765,7 +9765,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G324" t="n">
-        <v>1.97467851638794</v>
+        <v>1.97467815876007</v>
       </c>
       <c r="H324" t="n">
         <v>133183</v>
@@ -9794,7 +9794,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G325" t="n">
-        <v>1.95885789394379</v>
+        <v>1.9588577747345</v>
       </c>
       <c r="H325" t="n">
         <v>255642</v>
@@ -9823,7 +9823,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G326" t="n">
-        <v>1.97036373615265</v>
+        <v>1.97036349773407</v>
       </c>
       <c r="H326" t="n">
         <v>126422</v>
@@ -9910,7 +9910,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>1.9631724357605</v>
+        <v>1.96317267417908</v>
       </c>
       <c r="H329" t="n">
         <v>315276</v>
@@ -9939,7 +9939,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G330" t="n">
-        <v>1.87400269508362</v>
+        <v>1.87400257587433</v>
       </c>
       <c r="H330" t="n">
         <v>719612</v>
@@ -9968,7 +9968,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>1.77620375156403</v>
+        <v>1.77620363235474</v>
       </c>
       <c r="H331" t="n">
         <v>509162</v>
@@ -9997,7 +9997,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G332" t="n">
-        <v>1.71004557609558</v>
+        <v>1.71004569530487</v>
       </c>
       <c r="H332" t="n">
         <v>423853</v>
@@ -10026,7 +10026,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G333" t="n">
-        <v>1.76182162761688</v>
+        <v>1.7618213891983</v>
       </c>
       <c r="H333" t="n">
         <v>201401</v>
@@ -10055,7 +10055,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G334" t="n">
-        <v>1.81359755992889</v>
+        <v>1.81359732151031</v>
       </c>
       <c r="H334" t="n">
         <v>247772</v>
@@ -10084,7 +10084,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G335" t="n">
-        <v>1.79058599472046</v>
+        <v>1.79058587551117</v>
       </c>
       <c r="H335" t="n">
         <v>437211</v>
@@ -10113,7 +10113,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G336" t="n">
-        <v>1.85386753082275</v>
+        <v>1.85386765003204</v>
       </c>
       <c r="H336" t="n">
         <v>411061</v>
@@ -10142,7 +10142,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G337" t="n">
-        <v>1.90852034091949</v>
+        <v>1.90852010250092</v>
       </c>
       <c r="H337" t="n">
         <v>339495</v>
@@ -10200,7 +10200,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G339" t="n">
-        <v>1.96748745441437</v>
+        <v>1.96748733520508</v>
       </c>
       <c r="H339" t="n">
         <v>358063</v>
@@ -10258,7 +10258,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G341" t="n">
-        <v>1.74586117267609</v>
+        <v>1.7458610534668</v>
       </c>
       <c r="H341" t="n">
         <v>1340489</v>
@@ -10287,7 +10287,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G342" t="n">
-        <v>1.70136141777039</v>
+        <v>1.70136153697968</v>
       </c>
       <c r="H342" t="n">
         <v>961120</v>
@@ -10316,7 +10316,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G343" t="n">
-        <v>1.72954428195953</v>
+        <v>1.7295446395874</v>
       </c>
       <c r="H343" t="n">
         <v>724620</v>
@@ -10345,7 +10345,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G344" t="n">
-        <v>1.72361123561859</v>
+        <v>1.7236111164093</v>
       </c>
       <c r="H344" t="n">
         <v>420972</v>
@@ -10374,7 +10374,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G345" t="n">
-        <v>1.67762839794159</v>
+        <v>1.67762851715088</v>
       </c>
       <c r="H345" t="n">
         <v>473880</v>
@@ -10403,7 +10403,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G346" t="n">
-        <v>1.7161945104599</v>
+        <v>1.71619439125061</v>
       </c>
       <c r="H346" t="n">
         <v>736976</v>
@@ -10432,7 +10432,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G347" t="n">
-        <v>1.76514399051666</v>
+        <v>1.76514446735382</v>
       </c>
       <c r="H347" t="n">
         <v>696640</v>
@@ -10490,7 +10490,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G349" t="n">
-        <v>1.7147114276886</v>
+        <v>1.71471130847931</v>
       </c>
       <c r="H349" t="n">
         <v>228527</v>
@@ -10606,7 +10606,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G353" t="n">
-        <v>1.66279542446136</v>
+        <v>1.66279530525208</v>
       </c>
       <c r="H353" t="n">
         <v>369421</v>
@@ -10664,7 +10664,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G355" t="n">
-        <v>1.67911183834076</v>
+        <v>1.67911171913147</v>
       </c>
       <c r="H355" t="n">
         <v>121579</v>
@@ -10693,7 +10693,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G356" t="n">
-        <v>1.67762839794159</v>
+        <v>1.67762851715088</v>
       </c>
       <c r="H356" t="n">
         <v>106360</v>
@@ -10751,7 +10751,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G358" t="n">
-        <v>1.72509431838989</v>
+        <v>1.72509455680847</v>
       </c>
       <c r="H358" t="n">
         <v>175648</v>
@@ -10780,7 +10780,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G359" t="n">
-        <v>1.72064435482025</v>
+        <v>1.72064447402954</v>
       </c>
       <c r="H359" t="n">
         <v>272461</v>
@@ -10838,7 +10838,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G361" t="n">
-        <v>1.69246160984039</v>
+        <v>1.69246172904968</v>
       </c>
       <c r="H361" t="n">
         <v>151546</v>
@@ -10896,7 +10896,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G363" t="n">
-        <v>1.67911183834076</v>
+        <v>1.67911171913147</v>
       </c>
       <c r="H363" t="n">
         <v>136307</v>
@@ -10925,7 +10925,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>1.6983950138092</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H364" t="n">
         <v>79641</v>
@@ -10983,7 +10983,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G366" t="n">
-        <v>1.6983950138092</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H366" t="n">
         <v>141224</v>
@@ -11012,7 +11012,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>1.6983950138092</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H367" t="n">
         <v>184395</v>
@@ -11041,7 +11041,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G368" t="n">
-        <v>1.72212779521942</v>
+        <v>1.72212791442871</v>
       </c>
       <c r="H368" t="n">
         <v>231003</v>
@@ -11070,7 +11070,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>1.72064435482025</v>
+        <v>1.72064447402954</v>
       </c>
       <c r="H369" t="n">
         <v>90559</v>
@@ -11099,7 +11099,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G370" t="n">
-        <v>1.70136141777039</v>
+        <v>1.70136153697968</v>
       </c>
       <c r="H370" t="n">
         <v>206893</v>
@@ -11128,7 +11128,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G371" t="n">
-        <v>1.70432817935944</v>
+        <v>1.70432829856873</v>
       </c>
       <c r="H371" t="n">
         <v>198744</v>
@@ -11157,7 +11157,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H372" t="n">
         <v>188976</v>
@@ -11215,7 +11215,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G374" t="n">
-        <v>1.75772738456726</v>
+        <v>1.75772762298584</v>
       </c>
       <c r="H374" t="n">
         <v>503636</v>
@@ -11244,7 +11244,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G375" t="n">
-        <v>1.74141120910645</v>
+        <v>1.74141108989716</v>
       </c>
       <c r="H375" t="n">
         <v>90743</v>
@@ -11273,7 +11273,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G376" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H376" t="n">
         <v>217080</v>
@@ -11302,7 +11302,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>1.72806119918823</v>
+        <v>1.72806096076965</v>
       </c>
       <c r="H377" t="n">
         <v>254953</v>
@@ -11331,7 +11331,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G378" t="n">
-        <v>1.67762839794159</v>
+        <v>1.67762851715088</v>
       </c>
       <c r="H378" t="n">
         <v>158070</v>
@@ -11360,7 +11360,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G379" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614495754242</v>
       </c>
       <c r="H379" t="n">
         <v>56186</v>
@@ -11418,7 +11418,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G381" t="n">
-        <v>1.71916139125824</v>
+        <v>1.71916151046753</v>
       </c>
       <c r="H381" t="n">
         <v>219366</v>
@@ -11476,7 +11476,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G383" t="n">
-        <v>1.72806119918823</v>
+        <v>1.72806096076965</v>
       </c>
       <c r="H383" t="n">
         <v>453984</v>
@@ -11505,7 +11505,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>1.75031077861786</v>
+        <v>1.75031101703644</v>
       </c>
       <c r="H384" t="n">
         <v>517240</v>
@@ -11592,7 +11592,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G387" t="n">
-        <v>1.7369612455368</v>
+        <v>1.73696112632751</v>
       </c>
       <c r="H387" t="n">
         <v>76021</v>
@@ -11621,7 +11621,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G388" t="n">
-        <v>1.71174466609955</v>
+        <v>1.71174490451813</v>
       </c>
       <c r="H388" t="n">
         <v>51635</v>
@@ -11737,7 +11737,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>1.6983950138092</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H392" t="n">
         <v>294047</v>
@@ -11766,7 +11766,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G393" t="n">
-        <v>1.7147114276886</v>
+        <v>1.71471130847931</v>
       </c>
       <c r="H393" t="n">
         <v>124941</v>
@@ -11853,7 +11853,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G396" t="n">
-        <v>1.72212779521942</v>
+        <v>1.72212791442871</v>
       </c>
       <c r="H396" t="n">
         <v>119904</v>
@@ -11882,7 +11882,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G397" t="n">
-        <v>1.70136141777039</v>
+        <v>1.70136153697968</v>
       </c>
       <c r="H397" t="n">
         <v>48837</v>
@@ -11940,7 +11940,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G399" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H399" t="n">
         <v>80915</v>
@@ -11969,7 +11969,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G400" t="n">
-        <v>1.68949508666992</v>
+        <v>1.68949496746063</v>
       </c>
       <c r="H400" t="n">
         <v>71969</v>
@@ -12027,7 +12027,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G402" t="n">
-        <v>1.67762839794159</v>
+        <v>1.67762851715088</v>
       </c>
       <c r="H402" t="n">
         <v>222599</v>
@@ -12056,7 +12056,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614495754242</v>
       </c>
       <c r="H403" t="n">
         <v>357624</v>
@@ -12114,7 +12114,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G405" t="n">
-        <v>1.64351224899292</v>
+        <v>1.64351236820221</v>
       </c>
       <c r="H405" t="n">
         <v>250166</v>
@@ -12143,7 +12143,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G406" t="n">
-        <v>1.63312888145447</v>
+        <v>1.63312900066376</v>
       </c>
       <c r="H406" t="n">
         <v>206183</v>
@@ -12172,7 +12172,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>1.59456300735474</v>
+        <v>1.59456288814545</v>
       </c>
       <c r="H407" t="n">
         <v>284079</v>
@@ -12201,7 +12201,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G408" t="n">
-        <v>1.61384606361389</v>
+        <v>1.61384618282318</v>
       </c>
       <c r="H408" t="n">
         <v>160068</v>
@@ -12230,7 +12230,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G409" t="n">
-        <v>1.5915961265564</v>
+        <v>1.59159636497498</v>
       </c>
       <c r="H409" t="n">
         <v>149140</v>
@@ -12259,7 +12259,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G410" t="n">
-        <v>1.61087930202484</v>
+        <v>1.61087942123413</v>
       </c>
       <c r="H410" t="n">
         <v>101473</v>
@@ -12346,7 +12346,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G413" t="n">
-        <v>1.67762839794159</v>
+        <v>1.67762851715088</v>
       </c>
       <c r="H413" t="n">
         <v>124634</v>
@@ -12404,7 +12404,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G415" t="n">
-        <v>1.67466187477112</v>
+        <v>1.67466175556183</v>
       </c>
       <c r="H415" t="n">
         <v>54025</v>
@@ -12433,7 +12433,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G416" t="n">
-        <v>1.66576194763184</v>
+        <v>1.66576206684113</v>
       </c>
       <c r="H416" t="n">
         <v>141111</v>
@@ -12462,7 +12462,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G417" t="n">
-        <v>1.63312888145447</v>
+        <v>1.63312900066376</v>
       </c>
       <c r="H417" t="n">
         <v>163226</v>
@@ -12491,7 +12491,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G418" t="n">
-        <v>1.60346269607544</v>
+        <v>1.60346281528473</v>
       </c>
       <c r="H418" t="n">
         <v>126057</v>
@@ -12520,7 +12520,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G419" t="n">
-        <v>1.60494601726532</v>
+        <v>1.6049462556839</v>
       </c>
       <c r="H419" t="n">
         <v>38787</v>
@@ -12549,7 +12549,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G420" t="n">
-        <v>1.5975296497345</v>
+        <v>1.59752941131592</v>
       </c>
       <c r="H420" t="n">
         <v>72967</v>
@@ -12578,7 +12578,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G421" t="n">
-        <v>1.60791277885437</v>
+        <v>1.60791265964508</v>
       </c>
       <c r="H421" t="n">
         <v>112916</v>
@@ -12665,7 +12665,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>1.59456300735474</v>
+        <v>1.59456288814545</v>
       </c>
       <c r="H424" t="n">
         <v>23373</v>
@@ -12723,7 +12723,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G426" t="n">
-        <v>1.5589634180069</v>
+        <v>1.55896317958832</v>
       </c>
       <c r="H426" t="n">
         <v>84811</v>
@@ -12752,7 +12752,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G427" t="n">
-        <v>1.5826963186264</v>
+        <v>1.58269643783569</v>
       </c>
       <c r="H427" t="n">
         <v>37428</v>
@@ -12810,7 +12810,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G429" t="n">
-        <v>1.5915961265564</v>
+        <v>1.59159636497498</v>
       </c>
       <c r="H429" t="n">
         <v>17916</v>
@@ -12897,7 +12897,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G432" t="n">
-        <v>1.58121311664581</v>
+        <v>1.58121299743652</v>
       </c>
       <c r="H432" t="n">
         <v>24105</v>
@@ -12926,7 +12926,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G433" t="n">
-        <v>1.56786346435547</v>
+        <v>1.56786334514618</v>
       </c>
       <c r="H433" t="n">
         <v>67599</v>
@@ -12955,7 +12955,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>1.59456300735474</v>
+        <v>1.59456288814545</v>
       </c>
       <c r="H434" t="n">
         <v>146075</v>
@@ -12984,7 +12984,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G435" t="n">
-        <v>1.5990127325058</v>
+        <v>1.59901261329651</v>
       </c>
       <c r="H435" t="n">
         <v>216836</v>
@@ -13013,7 +13013,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G436" t="n">
-        <v>1.58121311664581</v>
+        <v>1.58121299743652</v>
       </c>
       <c r="H436" t="n">
         <v>116492</v>
@@ -13042,7 +13042,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>1.57231318950653</v>
+        <v>1.57231295108795</v>
       </c>
       <c r="H437" t="n">
         <v>157936</v>
@@ -13071,7 +13071,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G438" t="n">
-        <v>1.56192982196808</v>
+        <v>1.56192994117737</v>
       </c>
       <c r="H438" t="n">
         <v>66146</v>
@@ -13100,7 +13100,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G439" t="n">
-        <v>1.57231318950653</v>
+        <v>1.57231295108795</v>
       </c>
       <c r="H439" t="n">
         <v>118972</v>
@@ -13129,7 +13129,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G440" t="n">
-        <v>1.57231318950653</v>
+        <v>1.57231295108795</v>
       </c>
       <c r="H440" t="n">
         <v>164526</v>
@@ -13187,7 +13187,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G442" t="n">
-        <v>1.59307956695557</v>
+        <v>1.59307944774628</v>
       </c>
       <c r="H442" t="n">
         <v>240142</v>
@@ -13245,7 +13245,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G444" t="n">
-        <v>1.58566296100616</v>
+        <v>1.58566308021545</v>
       </c>
       <c r="H444" t="n">
         <v>225453</v>
@@ -13303,7 +13303,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G446" t="n">
-        <v>1.57972979545593</v>
+        <v>1.57972991466522</v>
       </c>
       <c r="H446" t="n">
         <v>509147</v>
@@ -13332,7 +13332,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G447" t="n">
-        <v>1.66576194763184</v>
+        <v>1.66576206684113</v>
       </c>
       <c r="H447" t="n">
         <v>795650</v>
@@ -13419,7 +13419,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G450" t="n">
-        <v>1.74882757663727</v>
+        <v>1.74882769584656</v>
       </c>
       <c r="H450" t="n">
         <v>419346</v>
@@ -13448,7 +13448,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>1.72806119918823</v>
+        <v>1.72806096076965</v>
       </c>
       <c r="H451" t="n">
         <v>194974</v>
@@ -13477,7 +13477,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G452" t="n">
-        <v>1.70136141777039</v>
+        <v>1.70136153697968</v>
       </c>
       <c r="H452" t="n">
         <v>187242</v>
@@ -13506,7 +13506,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G453" t="n">
-        <v>1.72509431838989</v>
+        <v>1.72509455680847</v>
       </c>
       <c r="H453" t="n">
         <v>131380</v>
@@ -13535,7 +13535,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G454" t="n">
-        <v>1.70432817935944</v>
+        <v>1.70432829856873</v>
       </c>
       <c r="H454" t="n">
         <v>119732</v>
@@ -13564,7 +13564,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G455" t="n">
-        <v>1.74437761306763</v>
+        <v>1.74437749385834</v>
       </c>
       <c r="H455" t="n">
         <v>306209</v>
@@ -13622,7 +13622,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G457" t="n">
-        <v>1.79629361629486</v>
+        <v>1.79629337787628</v>
       </c>
       <c r="H457" t="n">
         <v>481923</v>
@@ -13680,7 +13680,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G459" t="n">
-        <v>1.83930993080139</v>
+        <v>1.83930969238281</v>
       </c>
       <c r="H459" t="n">
         <v>503273</v>
@@ -13709,7 +13709,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G460" t="n">
-        <v>1.93720817565918</v>
+        <v>1.93720865249634</v>
       </c>
       <c r="H460" t="n">
         <v>2102244</v>
@@ -13796,7 +13796,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G463" t="n">
-        <v>1.90605854988098</v>
+        <v>1.90605914592743</v>
       </c>
       <c r="H463" t="n">
         <v>445928</v>
@@ -13825,7 +13825,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G464" t="n">
-        <v>1.87490975856781</v>
+        <v>1.87490928173065</v>
       </c>
       <c r="H464" t="n">
         <v>236248</v>
@@ -13912,7 +13912,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G467" t="n">
-        <v>1.93572509288788</v>
+        <v>1.93572497367859</v>
       </c>
       <c r="H467" t="n">
         <v>227515</v>
@@ -13970,7 +13970,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G469" t="n">
-        <v>1.78887701034546</v>
+        <v>1.78887677192688</v>
       </c>
       <c r="H469" t="n">
         <v>1419623</v>
@@ -14028,7 +14028,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G471" t="n">
-        <v>1.82892644405365</v>
+        <v>1.82892632484436</v>
       </c>
       <c r="H471" t="n">
         <v>281645</v>
@@ -14057,7 +14057,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G472" t="n">
-        <v>1.78887701034546</v>
+        <v>1.78887677192688</v>
       </c>
       <c r="H472" t="n">
         <v>368047</v>
@@ -14086,7 +14086,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G473" t="n">
-        <v>1.76514399051666</v>
+        <v>1.76514446735382</v>
       </c>
       <c r="H473" t="n">
         <v>234010</v>
@@ -14144,7 +14144,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G475" t="n">
-        <v>1.7072948217392</v>
+        <v>1.70729470252991</v>
       </c>
       <c r="H475" t="n">
         <v>277320</v>
@@ -14173,7 +14173,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G476" t="n">
-        <v>1.66279542446136</v>
+        <v>1.66279530525208</v>
       </c>
       <c r="H476" t="n">
         <v>368436</v>
@@ -14231,7 +14231,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G478" t="n">
-        <v>1.64054560661316</v>
+        <v>1.64054536819458</v>
       </c>
       <c r="H478" t="n">
         <v>289704</v>
@@ -14260,7 +14260,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G479" t="n">
-        <v>1.61977922916412</v>
+        <v>1.6197794675827</v>
       </c>
       <c r="H479" t="n">
         <v>273523</v>
@@ -14289,7 +14289,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G480" t="n">
-        <v>1.61829578876495</v>
+        <v>1.61829590797424</v>
       </c>
       <c r="H480" t="n">
         <v>135534</v>
@@ -14376,7 +14376,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G483" t="n">
-        <v>1.63164591789246</v>
+        <v>1.63164567947388</v>
       </c>
       <c r="H483" t="n">
         <v>127058</v>
@@ -14405,7 +14405,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G484" t="n">
-        <v>1.64796209335327</v>
+        <v>1.64796221256256</v>
       </c>
       <c r="H484" t="n">
         <v>79231</v>
@@ -14463,7 +14463,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G486" t="n">
-        <v>1.67021191120148</v>
+        <v>1.67021214962006</v>
       </c>
       <c r="H486" t="n">
         <v>138055</v>
@@ -14492,7 +14492,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G487" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H487" t="n">
         <v>237309</v>
@@ -14608,7 +14608,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G491" t="n">
-        <v>1.66724526882172</v>
+        <v>1.66724514961243</v>
       </c>
       <c r="H491" t="n">
         <v>229961</v>
@@ -14637,7 +14637,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G492" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614495754242</v>
       </c>
       <c r="H492" t="n">
         <v>73596</v>
@@ -14666,7 +14666,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G493" t="n">
-        <v>1.66131198406219</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H493" t="n">
         <v>309875</v>
@@ -14724,7 +14724,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G495" t="n">
-        <v>1.68949508666992</v>
+        <v>1.68949496746063</v>
       </c>
       <c r="H495" t="n">
         <v>157965</v>
@@ -14753,7 +14753,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G496" t="n">
-        <v>1.68949508666992</v>
+        <v>1.68949496746063</v>
       </c>
       <c r="H496" t="n">
         <v>61838</v>
@@ -14811,7 +14811,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G498" t="n">
-        <v>1.68949508666992</v>
+        <v>1.68949496746063</v>
       </c>
       <c r="H498" t="n">
         <v>94690</v>
@@ -14869,7 +14869,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H500" t="n">
         <v>39718</v>
@@ -14927,7 +14927,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G502" t="n">
-        <v>1.67466187477112</v>
+        <v>1.67466175556183</v>
       </c>
       <c r="H502" t="n">
         <v>96652</v>
@@ -14956,7 +14956,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G503" t="n">
-        <v>1.62867915630341</v>
+        <v>1.6286792755127</v>
       </c>
       <c r="H503" t="n">
         <v>138203</v>
@@ -14985,7 +14985,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G504" t="n">
-        <v>1.66724526882172</v>
+        <v>1.66724514961243</v>
       </c>
       <c r="H504" t="n">
         <v>204470</v>
@@ -15014,7 +15014,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G505" t="n">
-        <v>1.65834546089172</v>
+        <v>1.65834558010101</v>
       </c>
       <c r="H505" t="n">
         <v>60467</v>
@@ -15072,7 +15072,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H507" t="n">
         <v>86918</v>
@@ -15101,7 +15101,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>1.6983950138092</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H508" t="n">
         <v>69025</v>
@@ -15159,7 +15159,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G510" t="n">
-        <v>1.69542837142944</v>
+        <v>1.69542849063873</v>
       </c>
       <c r="H510" t="n">
         <v>38185</v>
@@ -15217,7 +15217,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G512" t="n">
-        <v>1.67466187477112</v>
+        <v>1.67466175556183</v>
       </c>
       <c r="H512" t="n">
         <v>92185</v>
@@ -15246,7 +15246,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G513" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H513" t="n">
         <v>126057</v>
@@ -15275,7 +15275,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G514" t="n">
-        <v>1.67985343933105</v>
+        <v>1.67985355854034</v>
       </c>
       <c r="H514" t="n">
         <v>370861</v>
@@ -15304,7 +15304,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G515" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H515" t="n">
         <v>86940</v>
@@ -15362,7 +15362,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G517" t="n">
-        <v>1.77256059646606</v>
+        <v>1.77256071567535</v>
       </c>
       <c r="H517" t="n">
         <v>556872</v>
@@ -15391,7 +15391,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G518" t="n">
-        <v>1.75031077861786</v>
+        <v>1.75031101703644</v>
       </c>
       <c r="H518" t="n">
         <v>282131</v>
@@ -15420,7 +15420,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G519" t="n">
-        <v>1.75772738456726</v>
+        <v>1.75772762298584</v>
       </c>
       <c r="H519" t="n">
         <v>190065</v>
@@ -15449,7 +15449,7 @@
         <v>2.375</v>
       </c>
       <c r="G520" t="n">
-        <v>1.76143574714661</v>
+        <v>1.76143598556519</v>
       </c>
       <c r="H520" t="n">
         <v>189064</v>
@@ -15478,7 +15478,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>1.79110217094421</v>
+        <v>1.79110205173492</v>
       </c>
       <c r="H521" t="n">
         <v>200009</v>
@@ -15507,7 +15507,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>1.76514399051666</v>
+        <v>1.76514446735382</v>
       </c>
       <c r="H522" t="n">
         <v>155399</v>
@@ -15536,7 +15536,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>1.75772738456726</v>
+        <v>1.75772762298584</v>
       </c>
       <c r="H523" t="n">
         <v>124342</v>
@@ -15565,7 +15565,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G524" t="n">
-        <v>1.74660265445709</v>
+        <v>1.7466025352478</v>
       </c>
       <c r="H524" t="n">
         <v>125547</v>
@@ -15594,7 +15594,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G525" t="n">
-        <v>1.75772738456726</v>
+        <v>1.75772762298584</v>
       </c>
       <c r="H525" t="n">
         <v>44234</v>
@@ -15623,7 +15623,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G526" t="n">
-        <v>1.79110217094421</v>
+        <v>1.79110205173492</v>
       </c>
       <c r="H526" t="n">
         <v>125260</v>
@@ -15681,7 +15681,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G528" t="n">
-        <v>1.77256059646606</v>
+        <v>1.77256071567535</v>
       </c>
       <c r="H528" t="n">
         <v>84539</v>
@@ -15710,7 +15710,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>1.75772738456726</v>
+        <v>1.75772762298584</v>
       </c>
       <c r="H529" t="n">
         <v>161504</v>
@@ -15739,7 +15739,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>1.79481029510498</v>
+        <v>1.79481041431427</v>
       </c>
       <c r="H530" t="n">
         <v>112821</v>
@@ -15768,7 +15768,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G531" t="n">
-        <v>1.82818472385406</v>
+        <v>1.82818496227264</v>
       </c>
       <c r="H531" t="n">
         <v>328327</v>
@@ -15797,7 +15797,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G532" t="n">
-        <v>1.77256059646606</v>
+        <v>1.77256071567535</v>
       </c>
       <c r="H532" t="n">
         <v>261495</v>
@@ -15855,7 +15855,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G534" t="n">
-        <v>1.70951962471008</v>
+        <v>1.70951974391937</v>
       </c>
       <c r="H534" t="n">
         <v>147585</v>
@@ -15884,7 +15884,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614495754242</v>
       </c>
       <c r="H535" t="n">
         <v>219143</v>
@@ -15913,7 +15913,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G536" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H536" t="n">
         <v>188147</v>
@@ -15971,7 +15971,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G538" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H538" t="n">
         <v>123991</v>
@@ -16029,7 +16029,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G540" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614495754242</v>
       </c>
       <c r="H540" t="n">
         <v>202006</v>
@@ -16058,7 +16058,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G541" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614495754242</v>
       </c>
       <c r="H541" t="n">
         <v>93257</v>
@@ -16145,7 +16145,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G544" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614495754242</v>
       </c>
       <c r="H544" t="n">
         <v>342817</v>
@@ -16174,7 +16174,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G545" t="n">
-        <v>1.69468665122986</v>
+        <v>1.69468641281128</v>
       </c>
       <c r="H545" t="n">
         <v>84820</v>
@@ -16261,7 +16261,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G548" t="n">
-        <v>1.64277040958405</v>
+        <v>1.64277052879333</v>
       </c>
       <c r="H548" t="n">
         <v>197621</v>
@@ -16348,7 +16348,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G551" t="n">
-        <v>1.65760362148285</v>
+        <v>1.65760374069214</v>
       </c>
       <c r="H551" t="n">
         <v>53538</v>
@@ -16377,7 +16377,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G552" t="n">
-        <v>1.66131198406219</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H552" t="n">
         <v>59842</v>
@@ -16464,7 +16464,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>1.65018725395203</v>
+        <v>1.65018713474274</v>
       </c>
       <c r="H555" t="n">
         <v>131578</v>
@@ -16551,7 +16551,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G558" t="n">
-        <v>1.63164591789246</v>
+        <v>1.63164567947388</v>
       </c>
       <c r="H558" t="n">
         <v>123184</v>
@@ -16638,7 +16638,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G561" t="n">
-        <v>1.69468665122986</v>
+        <v>1.69468641281128</v>
       </c>
       <c r="H561" t="n">
         <v>213139</v>
@@ -16667,7 +16667,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614495754242</v>
       </c>
       <c r="H562" t="n">
         <v>140407</v>
@@ -16696,7 +16696,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G563" t="n">
-        <v>1.66131198406219</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H563" t="n">
         <v>46104</v>
@@ -16957,7 +16957,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G572" t="n">
-        <v>1.65760362148285</v>
+        <v>1.65760374069214</v>
       </c>
       <c r="H572" t="n">
         <v>54138</v>
@@ -17015,7 +17015,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G574" t="n">
-        <v>1.66131198406219</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H574" t="n">
         <v>64589</v>
@@ -17102,7 +17102,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G577" t="n">
-        <v>1.67985343933105</v>
+        <v>1.67985355854034</v>
       </c>
       <c r="H577" t="n">
         <v>132861</v>
@@ -17131,7 +17131,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>1.68727016448975</v>
+        <v>1.68727004528046</v>
       </c>
       <c r="H578" t="n">
         <v>117418</v>
@@ -17189,7 +17189,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G580" t="n">
-        <v>1.6983950138092</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H580" t="n">
         <v>175180</v>
@@ -17218,7 +17218,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G581" t="n">
-        <v>1.676145195961</v>
+        <v>1.67614495754242</v>
       </c>
       <c r="H581" t="n">
         <v>144783</v>
@@ -17421,7 +17421,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G588" t="n">
-        <v>1.66131198406219</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H588" t="n">
         <v>79711</v>
@@ -17450,7 +17450,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>1.66131198406219</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H589" t="n">
         <v>42981</v>
@@ -17508,7 +17508,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G591" t="n">
-        <v>1.66131198406219</v>
+        <v>1.66131210327148</v>
       </c>
       <c r="H591" t="n">
         <v>110080</v>
@@ -17537,7 +17537,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G592" t="n">
-        <v>1.65389537811279</v>
+        <v>1.6538952589035</v>
       </c>
       <c r="H592" t="n">
         <v>114980</v>
@@ -17566,7 +17566,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G593" t="n">
-        <v>1.6983950138092</v>
+        <v>1.69839477539062</v>
       </c>
       <c r="H593" t="n">
         <v>157651</v>
@@ -17595,7 +17595,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G594" t="n">
-        <v>1.6909784078598</v>
+        <v>1.69097816944122</v>
       </c>
       <c r="H594" t="n">
         <v>78442</v>
@@ -17653,7 +17653,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G596" t="n">
-        <v>1.69468665122986</v>
+        <v>1.69468641281128</v>
       </c>
       <c r="H596" t="n">
         <v>284640</v>
@@ -17798,7 +17798,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G601" t="n">
-        <v>1.725989818573</v>
+        <v>1.72598969936371</v>
       </c>
       <c r="H601" t="n">
         <v>263886</v>
@@ -17827,7 +17827,7 @@
         <v>2.25</v>
       </c>
       <c r="G602" t="n">
-        <v>1.73369491100311</v>
+        <v>1.73369479179382</v>
       </c>
       <c r="H602" t="n">
         <v>312670</v>
@@ -17856,7 +17856,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>1.70287358760834</v>
+        <v>1.70287394523621</v>
       </c>
       <c r="H603" t="n">
         <v>264105</v>
@@ -17885,7 +17885,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>1.69902086257935</v>
+        <v>1.69902098178864</v>
       </c>
       <c r="H604" t="n">
         <v>151879</v>
@@ -17943,7 +17943,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G606" t="n">
-        <v>1.64893651008606</v>
+        <v>1.64893674850464</v>
       </c>
       <c r="H606" t="n">
         <v>281947</v>
@@ -18030,7 +18030,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G609" t="n">
-        <v>1.49791240692139</v>
+        <v>1.49791264533997</v>
       </c>
       <c r="H609" t="n">
         <v>541620</v>
@@ -18175,7 +18175,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G614" t="n">
-        <v>1.47171437740326</v>
+        <v>1.47171425819397</v>
       </c>
       <c r="H614" t="n">
         <v>573449</v>
@@ -18291,7 +18291,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G618" t="n">
-        <v>1.49791240692139</v>
+        <v>1.49791264533997</v>
       </c>
       <c r="H618" t="n">
         <v>153249</v>
@@ -18378,7 +18378,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G621" t="n">
-        <v>1.58344149589539</v>
+        <v>1.5834413766861</v>
       </c>
       <c r="H621" t="n">
         <v>333930</v>
@@ -18407,7 +18407,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G622" t="n">
-        <v>1.55647277832031</v>
+        <v>1.5564728975296</v>
       </c>
       <c r="H622" t="n">
         <v>216580</v>
@@ -18610,7 +18610,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G629" t="n">
-        <v>1.59114682674408</v>
+        <v>1.59114670753479</v>
       </c>
       <c r="H629" t="n">
         <v>167995</v>
@@ -18668,7 +18668,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.65664172172546</v>
+        <v>1.65664184093475</v>
       </c>
       <c r="H631" t="n">
         <v>549717</v>
@@ -18697,7 +18697,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G632" t="n">
-        <v>1.61040997505188</v>
+        <v>1.61040985584259</v>
       </c>
       <c r="H632" t="n">
         <v>855956</v>
@@ -18726,7 +18726,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>1.60270476341248</v>
+        <v>1.60270464420319</v>
       </c>
       <c r="H633" t="n">
         <v>85820</v>
@@ -18755,7 +18755,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G634" t="n">
-        <v>1.55647277832031</v>
+        <v>1.5564728975296</v>
       </c>
       <c r="H634" t="n">
         <v>127877</v>
@@ -18900,7 +18900,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G639" t="n">
-        <v>1.58729410171509</v>
+        <v>1.58729386329651</v>
       </c>
       <c r="H639" t="n">
         <v>207577</v>
@@ -18958,7 +18958,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G641" t="n">
-        <v>1.58729410171509</v>
+        <v>1.58729386329651</v>
       </c>
       <c r="H641" t="n">
         <v>51370</v>
@@ -19016,7 +19016,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G643" t="n">
-        <v>1.61811530590057</v>
+        <v>1.61811518669128</v>
       </c>
       <c r="H643" t="n">
         <v>102424</v>
@@ -19074,7 +19074,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G645" t="n">
-        <v>1.59885203838348</v>
+        <v>1.59885215759277</v>
       </c>
       <c r="H645" t="n">
         <v>144536</v>
@@ -19132,7 +19132,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>1.60655748844147</v>
+        <v>1.60655736923218</v>
       </c>
       <c r="H647" t="n">
         <v>66972</v>
@@ -19161,7 +19161,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G648" t="n">
-        <v>1.58344149589539</v>
+        <v>1.5834413766861</v>
       </c>
       <c r="H648" t="n">
         <v>146801</v>
@@ -19335,7 +19335,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>1.58344149589539</v>
+        <v>1.5834413766861</v>
       </c>
       <c r="H654" t="n">
         <v>118580</v>
@@ -19364,7 +19364,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G655" t="n">
-        <v>1.59114682674408</v>
+        <v>1.591